--- a/IPO_analysis.xlsx
+++ b/IPO_analysis.xlsx
@@ -618,7 +618,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>기준일 2026-09-12 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
+          <t>기준일 2026-09-13 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
         </is>
       </c>
     </row>

--- a/IPO_analysis.xlsx
+++ b/IPO_analysis.xlsx
@@ -592,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K135"/>
+  <dimension ref="A1:K136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -618,14 +618,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>기준일 2026-09-13 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
+          <t>기준일 2026-09-14 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>■ 심사 신청(진행중)  (46건)</t>
+          <t>■ 심사 신청(진행중)  (45건)</t>
         </is>
       </c>
       <c r="B4" s="4" t="n"/>
@@ -699,12 +699,12 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>엑티브온</t>
+          <t>(주)태석광학</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
@@ -722,17 +722,29 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr"/>
-      <c r="G6" s="7" t="inlineStr"/>
-      <c r="H6" s="7" t="inlineStr"/>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>79,804</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>4,721</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
+          <t>7,228</t>
+        </is>
+      </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>생활용품 도매업</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>키움</t>
+          <t>신한, 대신</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
@@ -744,12 +756,12 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>씨앤엠</t>
+          <t>엑티브온</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -759,7 +771,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -767,29 +779,17 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>238,489</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>19,869</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>112,262</t>
-        </is>
-      </c>
+      <c r="F7" s="7" t="inlineStr"/>
+      <c r="G7" s="7" t="inlineStr"/>
+      <c r="H7" s="7" t="inlineStr"/>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>전동기, 발전기 및 전기 변환 · 공급 · 제어 장치 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>키움</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
@@ -801,17 +801,17 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>무신사</t>
+          <t>씨앤엠</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>유가</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -826,27 +826,27 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>1,352,930</t>
+          <t>238,489</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>-10,571</t>
+          <t>19,869</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>243,731</t>
+          <t>112,262</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>섬유, 의복, 신발 및 가죽제품 소매업</t>
+          <t>전동기, 발전기 및 전기 변환 · 공급 · 제어 장치 제조업</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>한국, 씨티그룹글로벌마켓증권(주), KB, 제이피모간증권회사 서울지점</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr">
@@ -858,17 +858,17 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>마더스제약</t>
+          <t>무신사</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>유가</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -883,27 +883,27 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>228,830</t>
+          <t>1,352,930</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>11,204</t>
+          <t>-10,571</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>57,394</t>
+          <t>243,731</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>의약품 제조업</t>
+          <t>섬유, 의복, 신발 및 가죽제품 소매업</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>NH, KB</t>
+          <t>한국, 씨티그룹글로벌마켓증권(주), KB, 제이피모간증권회사 서울지점</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>이나인페이</t>
+          <t>마더스제약</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -940,27 +940,27 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>64,711</t>
+          <t>228,830</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>19,586</t>
+          <t>11,204</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>79,855</t>
+          <t>57,394</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>의약품 제조업</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>NH, KB</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
@@ -972,12 +972,12 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>어피닛</t>
+          <t>이나인페이</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -997,27 +997,27 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>169,126</t>
+          <t>64,711</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>26,009</t>
+          <t>19,586</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>61,466</t>
+          <t>79,855</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>미래, 하나</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
@@ -1029,12 +1029,12 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>라이드플럭스</t>
+          <t>어피닛</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -1054,17 +1054,17 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>4,044</t>
+          <t>169,126</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>-31,423</t>
+          <t>26,009</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>-77,243</t>
+          <t>61,466</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>주식회사 우리투자증권, 한국</t>
+          <t>미래, 하나</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
@@ -1086,12 +1086,12 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>신영스팩12호</t>
+          <t>라이드플럭스</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1109,17 +1109,29 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr"/>
-      <c r="G13" s="7" t="inlineStr"/>
-      <c r="H13" s="7" t="inlineStr"/>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>4,044</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>-31,423</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>-77,243</t>
+        </is>
+      </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>신영</t>
+          <t>주식회사 우리투자증권, 한국</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
@@ -1131,12 +1143,12 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>우리투자제1호스팩</t>
+          <t>신영스팩12호</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -1159,12 +1171,12 @@
       <c r="H14" s="7" t="inlineStr"/>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>주식회사 우리투자증권</t>
+          <t>신영</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
@@ -1176,12 +1188,12 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>동원파츠</t>
+          <t>우리투자제1호스팩</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -1199,29 +1211,17 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>92,255</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>3,443</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>27,535</t>
-        </is>
-      </c>
+      <c r="F15" s="7" t="inlineStr"/>
+      <c r="G15" s="7" t="inlineStr"/>
+      <c r="H15" s="7" t="inlineStr"/>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>주식회사 우리투자증권</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>영광와이케이엠씨</t>
+          <t>케이티이</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -1372,27 +1372,27 @@
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>51,609</t>
+          <t>173,901</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>2,708</t>
+          <t>14,243</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>28,213</t>
+          <t>94,928</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>기타 금속 가공제품 제조업</t>
+          <t>전동기, 발전기 및 전기 변환 · 공급 · 제어 장치 제조업</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K18" s="6" t="inlineStr">
@@ -1404,12 +1404,12 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>케이티이</t>
+          <t>데스틴파워</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>173,901</t>
+          <t>29,851</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>14,243</t>
+          <t>5,852</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>94,928</t>
+          <t>-30,114</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>데스틴파워</t>
+          <t>유림테크</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -1486,27 +1486,27 @@
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>29,851</t>
+          <t>102,586</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>5,852</t>
+          <t>-18,278</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>-30,114</t>
+          <t>-4,832</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>전동기, 발전기 및 전기 변환 · 공급 · 제어 장치 제조업</t>
+          <t>자동차 신품 부품 제조업</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K20" s="6" t="inlineStr">
@@ -1518,12 +1518,12 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>유림테크</t>
+          <t>솔리스</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -1541,29 +1541,17 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>102,586</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>-18,278</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>-4,832</t>
-        </is>
-      </c>
+      <c r="F21" s="7" t="inlineStr"/>
+      <c r="G21" s="7" t="inlineStr"/>
+      <c r="H21" s="7" t="inlineStr"/>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>자동차 신품 부품 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>한화</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
@@ -1580,7 +1568,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>솔리스</t>
+          <t>이노보테라퓨틱스</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1590,7 +1578,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -1598,17 +1586,29 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr"/>
-      <c r="G22" s="7" t="inlineStr"/>
-      <c r="H22" s="7" t="inlineStr"/>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>-5,429</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>-53,200</t>
+        </is>
+      </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>의약품 제조업</t>
         </is>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>한화</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K22" s="6" t="inlineStr">
@@ -1620,17 +1620,17 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>이노보테라퓨틱스</t>
+          <t>에스에프씨</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>유가</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -1645,27 +1645,27 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>160,792</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>-5,429</t>
+          <t>25,509</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>-53,200</t>
+          <t>243,562</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>의약품 제조업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>미래, 한국</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
@@ -1677,17 +1677,17 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>에스에프씨</t>
+          <t>제논</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>유가</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -1702,27 +1702,27 @@
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>160,792</t>
+          <t>11,744</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>25,509</t>
+          <t>1,139</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>243,562</t>
+          <t>-1,220</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>미래, 한국</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K24" s="6" t="inlineStr">
@@ -1734,12 +1734,12 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>제논</t>
+          <t>넥스아이</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -1759,27 +1759,27 @@
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>11,744</t>
+          <t>5,110</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>1,139</t>
+          <t>-52,331</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>-1,220</t>
+          <t>-82,348</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>의약품 제조업</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>넥스아이</t>
+          <t>아델</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -1816,27 +1816,27 @@
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>5,110</t>
+          <t>62,057</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>-52,331</t>
+          <t>-64,210</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>-82,348</t>
+          <t>-80,776</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>의약품 제조업</t>
+          <t>그외 기타 전문, 과학 및 기술 서비스업</t>
         </is>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>삼성, 미래</t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr">
@@ -1848,12 +1848,12 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>아델</t>
+          <t>에버온</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -1873,27 +1873,27 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>62,057</t>
+          <t>65,225</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>-64,210</t>
+          <t>-3,606</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>-80,776</t>
+          <t>54,955</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>그외 기타 전문, 과학 및 기술 서비스업</t>
+          <t>전기업</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>삼성, 미래</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
@@ -1905,12 +1905,12 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>에버온</t>
+          <t>엔키화이트햇</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -1930,27 +1930,27 @@
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>65,225</t>
+          <t>14,176</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>-3,606</t>
+          <t>-3,211</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>54,955</t>
+          <t>8,338</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>전기업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>신영</t>
         </is>
       </c>
       <c r="K28" s="6" t="inlineStr">
@@ -1962,12 +1962,12 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>엔키화이트햇</t>
+          <t>씨아이에스케미칼</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
@@ -1987,27 +1987,27 @@
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>14,176</t>
+          <t>15,985</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>-3,211</t>
+          <t>-11,440</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>8,338</t>
+          <t>23,706</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>기초 화학물질 제조업</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>신영</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>씨아이에스케미칼</t>
+          <t>엠디에스코리아</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -2044,27 +2044,27 @@
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>15,985</t>
+          <t>97,972</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>-11,440</t>
+          <t>6,512</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>23,706</t>
+          <t>53,818</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>기초 화학물질 제조업</t>
+          <t>기타 식품 제조업</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
@@ -2076,12 +2076,12 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>엠디에스코리아</t>
+          <t>동승</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -2101,27 +2101,27 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>97,972</t>
+          <t>78,625</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>6,512</t>
+          <t>14,525</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>53,818</t>
+          <t>5,438</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>기타 식품 제조업</t>
+          <t>부동산 임대 및 공급업</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K31" s="6" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>동승</t>
+          <t>셀트릭스</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -2158,27 +2158,27 @@
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>78,625</t>
+          <t>16,976</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>14,525</t>
+          <t>4,545</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>5,438</t>
+          <t>2,213</t>
         </is>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>부동산 임대 및 공급업</t>
+          <t>의료용품 및 기타 의약 관련제품 제조업</t>
         </is>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>IBK</t>
         </is>
       </c>
       <c r="K32" s="6" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>셀트릭스</t>
+          <t>에프엠더블유</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -2215,27 +2215,27 @@
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>16,976</t>
+          <t>30,282</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>4,545</t>
+          <t>4,762</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>2,213</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>의료용품 및 기타 의약 관련제품 제조업</t>
+          <t>기타 식품 제조업</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>IBK</t>
+          <t>유진</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
@@ -2247,22 +2247,22 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>에프엠더블유</t>
+          <t>소노인터내셔널</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>유가</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -2272,27 +2272,27 @@
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>30,282</t>
+          <t>2,093,051</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>4,762</t>
+          <t>-148,064</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>852,372</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>기타 식품 제조업</t>
+          <t>일반 및 생활 숙박시설 운영업</t>
         </is>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>유진</t>
+          <t>대신, 미래</t>
         </is>
       </c>
       <c r="K34" s="6" t="inlineStr">
@@ -2304,17 +2304,17 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>소노인터내셔널</t>
+          <t>싸이몬</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>유가</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -2329,27 +2329,27 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>2,093,051</t>
+          <t>48,695</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>-148,064</t>
+          <t>15,714</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>852,372</t>
+          <t>61,761</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>일반 및 생활 숙박시설 운영업</t>
+          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업</t>
         </is>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>대신, 미래</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K35" s="6" t="inlineStr">
@@ -2361,12 +2361,12 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>싸이몬</t>
+          <t>바이다</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
@@ -2386,27 +2386,27 @@
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>48,695</t>
+          <t>14,432</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>15,714</t>
+          <t>-3,951</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>61,761</t>
+          <t>15,108</t>
         </is>
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업</t>
+          <t>전자부품 제조업</t>
         </is>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K36" s="6" t="inlineStr">
@@ -2418,12 +2418,12 @@
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>바이다</t>
+          <t>럭스코</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -2433,7 +2433,7 @@
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
@@ -2443,27 +2443,27 @@
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>14,432</t>
+          <t>67,976</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>-3,951</t>
+          <t>6,893</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>15,108</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>전자부품 제조업</t>
+          <t>전동기, 발전기 및 전기 변환 · 공급 · 제어 장치 제조업</t>
         </is>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>IBK</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>럭스코</t>
+          <t>아이알큐더스</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -2500,27 +2500,27 @@
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>67,976</t>
+          <t>10,231</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>6,893</t>
+          <t>-986</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>1,800</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>전동기, 발전기 및 전기 변환 · 공급 · 제어 장치 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>IBK</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="K38" s="6" t="inlineStr">
@@ -2532,12 +2532,12 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>아이알큐더스</t>
+          <t>영광</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -2557,27 +2557,27 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>10,231</t>
+          <t>113,133</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>-986</t>
+          <t>10,328</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>1,800</t>
+          <t>3,052</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
         </is>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr">
@@ -2589,12 +2589,12 @@
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>영광</t>
+          <t>씨엔티테크</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -2614,27 +2614,27 @@
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>113,133</t>
+          <t>27,015</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>10,328</t>
+          <t>3,987</t>
         </is>
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>3,052</t>
+          <t>2,613</t>
         </is>
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>한화, 하나</t>
         </is>
       </c>
       <c r="K40" s="6" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>씨엔티테크</t>
+          <t>제이앤티지</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -2671,27 +2671,27 @@
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>27,015</t>
+          <t>72,378</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>3,987</t>
+          <t>9,904</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>2,613</t>
+          <t>6,743</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>전자부품 제조업</t>
         </is>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>한화, 하나</t>
+          <t>대신, NH</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
@@ -2703,12 +2703,12 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>제이앤티지</t>
+          <t>인터엑스</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -2728,27 +2728,27 @@
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>72,378</t>
+          <t>8,645</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>9,904</t>
+          <t>-20,272</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>6,743</t>
+          <t>4,530</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>전자부품 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>대신, NH</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K42" s="6" t="inlineStr">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>인터엑스</t>
+          <t>케이엠에프</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -2785,27 +2785,27 @@
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>8,645</t>
+          <t>25,751</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>-20,272</t>
+          <t>11,463</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>4,530</t>
+          <t>642</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>기타 식품 제조업</t>
         </is>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>IBK</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
@@ -2817,12 +2817,12 @@
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>케이엠에프</t>
+          <t>삼홍아크튜리온</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -2842,27 +2842,27 @@
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>25,751</t>
+          <t>26,162</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>11,463</t>
+          <t>-10,314</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>6,369</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>기타 식품 제조업</t>
+          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
         </is>
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>IBK</t>
+          <t>삼성, 미래</t>
         </is>
       </c>
       <c r="K44" s="6" t="inlineStr">
@@ -2874,12 +2874,12 @@
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>삼홍아크튜리온</t>
+          <t>넥스트에어로스페이스</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -2899,27 +2899,27 @@
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>26,162</t>
+          <t>12,084</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>-10,314</t>
+          <t>-17,270</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>6,369</t>
+          <t>6,158</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
+          <t>유인 항공기, 항공우주선 및 보조장치 제조업</t>
         </is>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>삼성, 미래</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K45" s="6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>넥스트에어로스페이스</t>
+          <t>비앤비코리아</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -2956,27 +2956,27 @@
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>12,084</t>
+          <t>141,169</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>-17,270</t>
+          <t>21,406</t>
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>6,158</t>
+          <t>43,932</t>
         </is>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>유인 항공기, 항공우주선 및 보조장치 제조업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K46" s="6" t="inlineStr">
@@ -2988,12 +2988,12 @@
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>비앤비코리아</t>
+          <t>오토핸즈</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
@@ -3013,22 +3013,22 @@
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>141,169</t>
+          <t>238,564</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>21,406</t>
+          <t>6,047</t>
         </is>
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>43,932</t>
+          <t>6,129</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>자동차 판매업</t>
         </is>
       </c>
       <c r="J47" s="6" t="inlineStr">
@@ -3045,12 +3045,12 @@
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>오토핸즈</t>
+          <t>아이벡스메디칼시스템즈</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -3060,7 +3060,7 @@
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
@@ -3070,27 +3070,27 @@
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>238,564</t>
+          <t>15,282</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>6,047</t>
+          <t>-7,227</t>
         </is>
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>6,129</t>
+          <t>744</t>
         </is>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
-          <t>자동차 판매업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K48" s="6" t="inlineStr">
@@ -3102,12 +3102,12 @@
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>아이벡스메디칼시스템즈</t>
+          <t>옵토닉스</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -3127,27 +3127,27 @@
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>15,282</t>
+          <t>25,368</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>-7,227</t>
+          <t>1,901</t>
         </is>
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>730</t>
         </is>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>광학렌즈 및 광학요소 제조업</t>
         </is>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K49" s="6" t="inlineStr">
@@ -3159,12 +3159,12 @@
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>옵토닉스</t>
+          <t>피지티</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -3184,22 +3184,22 @@
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>25,368</t>
+          <t>40,141</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>1,901</t>
+          <t>-69,722</t>
         </is>
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>6,029</t>
         </is>
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
-          <t>광학렌즈 및 광학요소 제조업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="J50" s="6" t="inlineStr">
@@ -3213,146 +3213,146 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>피지티</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>■ 심사 승인  (62건)</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="n"/>
+      <c r="C52" s="4" t="n"/>
+      <c r="D52" s="4" t="n"/>
+      <c r="E52" s="4" t="n"/>
+      <c r="F52" s="4" t="n"/>
+      <c r="G52" s="4" t="n"/>
+      <c r="H52" s="4" t="n"/>
+      <c r="I52" s="4" t="n"/>
+      <c r="J52" s="4" t="n"/>
+      <c r="K52" s="4" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>일자</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>회사명</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>시장</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>상장유형</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>기준연도</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>자기자본</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>업종</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>대표주관사</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="inlineStr">
+        <is>
+          <t>현황</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>영광와이케이엠씨</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
         <is>
           <t>코스닥</t>
         </is>
       </c>
-      <c r="D51" s="6" t="inlineStr">
+      <c r="D54" s="6" t="inlineStr">
         <is>
           <t>신규상장</t>
         </is>
       </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="E54" s="6" t="inlineStr">
         <is>
           <t>FY25</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>40,141</t>
-        </is>
-      </c>
-      <c r="G51" s="7" t="inlineStr">
-        <is>
-          <t>-69,722</t>
-        </is>
-      </c>
-      <c r="H51" s="7" t="inlineStr">
-        <is>
-          <t>6,029</t>
-        </is>
-      </c>
-      <c r="I51" s="6" t="inlineStr">
-        <is>
-          <t>기타 화학제품 제조업</t>
-        </is>
-      </c>
-      <c r="J51" s="6" t="inlineStr">
-        <is>
-          <t>한국</t>
-        </is>
-      </c>
-      <c r="K51" s="6" t="inlineStr">
-        <is>
-          <t>예심 진행중</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>■ 심사 승인  (60건)</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="n"/>
-      <c r="C53" s="4" t="n"/>
-      <c r="D53" s="4" t="n"/>
-      <c r="E53" s="4" t="n"/>
-      <c r="F53" s="4" t="n"/>
-      <c r="G53" s="4" t="n"/>
-      <c r="H53" s="4" t="n"/>
-      <c r="I53" s="4" t="n"/>
-      <c r="J53" s="4" t="n"/>
-      <c r="K53" s="4" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>일자</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>회사명</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>시장</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>상장유형</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>기준연도</t>
-        </is>
-      </c>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="G54" s="5" t="inlineStr">
-        <is>
-          <t>순이익</t>
-        </is>
-      </c>
-      <c r="H54" s="5" t="inlineStr">
-        <is>
-          <t>자기자본</t>
-        </is>
-      </c>
-      <c r="I54" s="5" t="inlineStr">
-        <is>
-          <t>업종</t>
-        </is>
-      </c>
-      <c r="J54" s="5" t="inlineStr">
-        <is>
-          <t>대표주관사</t>
-        </is>
-      </c>
-      <c r="K54" s="5" t="inlineStr">
-        <is>
-          <t>현황</t>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>51,609</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>2,708</t>
+        </is>
+      </c>
+      <c r="H54" s="7" t="inlineStr">
+        <is>
+          <t>28,213</t>
+        </is>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>기타 금속 가공제품 제조업</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>대신</t>
+        </is>
+      </c>
+      <c r="K54" s="6" t="inlineStr">
+        <is>
+          <t>상장전</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>이에스티</t>
+          <t>동원파츠</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -3372,17 +3372,17 @@
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>33,190</t>
+          <t>92,255</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>2,966</t>
+          <t>3,443</t>
         </is>
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
-          <t>4,325</t>
+          <t>27,535</t>
         </is>
       </c>
       <c r="I55" s="6" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K55" s="6" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>에이엘로봇</t>
+          <t>이에스티</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
@@ -3429,22 +3429,22 @@
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>14,985</t>
+          <t>33,190</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>-21,891</t>
+          <t>2,966</t>
         </is>
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>4,325</t>
         </is>
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
-          <t>산업용 로봇 제조업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="J56" s="6" t="inlineStr">
@@ -3461,12 +3461,12 @@
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>아이엠스팩1호</t>
+          <t>에이엘로봇</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -3484,17 +3484,29 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F57" s="7" t="inlineStr"/>
-      <c r="G57" s="7" t="inlineStr"/>
-      <c r="H57" s="7" t="inlineStr"/>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>14,985</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>-21,891</t>
+        </is>
+      </c>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>산업용 로봇 제조업</t>
         </is>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
-          <t>iM증권</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K57" s="6" t="inlineStr">
@@ -3506,12 +3518,12 @@
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>에이엔에이치스트럭쳐</t>
+          <t>아이엠스팩1호</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
@@ -3529,29 +3541,17 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F58" s="7" t="inlineStr">
-        <is>
-          <t>19,784</t>
-        </is>
-      </c>
-      <c r="G58" s="7" t="inlineStr">
-        <is>
-          <t>-4,296</t>
-        </is>
-      </c>
-      <c r="H58" s="7" t="inlineStr">
-        <is>
-          <t>24,561</t>
-        </is>
-      </c>
+      <c r="F58" s="7" t="inlineStr"/>
+      <c r="G58" s="7" t="inlineStr"/>
+      <c r="H58" s="7" t="inlineStr"/>
       <c r="I58" s="6" t="inlineStr">
         <is>
-          <t>건축기술, 엔지니어링 및 관련 기술 서비스업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="J58" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>iM증권</t>
         </is>
       </c>
       <c r="K58" s="6" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>인텔리빅스</t>
+          <t>에이엔에이치스트럭쳐</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
@@ -3588,27 +3588,27 @@
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>46,644</t>
+          <t>19,784</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>5,357</t>
+          <t>-4,296</t>
         </is>
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>1,048</t>
+          <t>24,561</t>
         </is>
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>건축기술, 엔지니어링 및 관련 기술 서비스업</t>
         </is>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K59" s="6" t="inlineStr">
@@ -3620,12 +3620,12 @@
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>하나에어로다이내믹스</t>
+          <t>인텔리빅스</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
@@ -3645,27 +3645,27 @@
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>33,286</t>
+          <t>46,644</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>2,420</t>
+          <t>5,357</t>
         </is>
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>1,048</t>
         </is>
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
-          <t>항공기,우주선 및 부품 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
-          <t>IBK</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K60" s="6" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>다비오</t>
+          <t>하나에어로다이내믹스</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
@@ -3702,27 +3702,27 @@
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>9,251</t>
+          <t>33,286</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>-3,473</t>
+          <t>2,420</t>
         </is>
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>890</t>
         </is>
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>항공기,우주선 및 부품 제조업</t>
         </is>
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>IBK</t>
         </is>
       </c>
       <c r="K61" s="6" t="inlineStr">
@@ -3734,12 +3734,12 @@
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>티앤이코리아</t>
+          <t>다비오</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
@@ -3759,27 +3759,27 @@
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>22,339</t>
+          <t>9,251</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>-7,091</t>
+          <t>-3,473</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I62" s="6" t="inlineStr">
         <is>
-          <t>일반 목적용 기계 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J62" s="6" t="inlineStr">
         <is>
-          <t>신한</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K62" s="6" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>유캐스트</t>
+          <t>티앤이코리아</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
@@ -3816,27 +3816,27 @@
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>5,934</t>
+          <t>22,339</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>-3,557</t>
+          <t>-7,091</t>
         </is>
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>1,881</t>
+          <t>481</t>
         </is>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
-          <t>통신 및 방송 장비 제조업</t>
+          <t>일반 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
-          <t>유진</t>
+          <t>신한</t>
         </is>
       </c>
       <c r="K63" s="6" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>엘리스그룹</t>
+          <t>유캐스트</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
@@ -3873,27 +3873,27 @@
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>39,513</t>
+          <t>5,934</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>15,666</t>
+          <t>-3,557</t>
         </is>
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>85,400</t>
+          <t>1,881</t>
         </is>
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>통신 및 방송 장비 제조업</t>
         </is>
       </c>
       <c r="J64" s="6" t="inlineStr">
         <is>
-          <t>미래, 삼성</t>
+          <t>유진</t>
         </is>
       </c>
       <c r="K64" s="6" t="inlineStr">
@@ -3905,12 +3905,12 @@
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>엘리스그룹</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="D65" s="6" t="inlineStr">
         <is>
-          <t>이전상장</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
@@ -3930,27 +3930,27 @@
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>48,646</t>
+          <t>39,513</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>6,017</t>
+          <t>15,666</t>
         </is>
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
-          <t>18,795</t>
+          <t>85,400</t>
         </is>
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
-          <t>하나</t>
+          <t>미래, 삼성</t>
         </is>
       </c>
       <c r="K65" s="6" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>바로팜</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>이전상장</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -3987,27 +3987,27 @@
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>96,724</t>
+          <t>48,646</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>-9,679</t>
+          <t>6,017</t>
         </is>
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
-          <t>30,673</t>
+          <t>18,795</t>
         </is>
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
-          <t>상품 중개업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="J66" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>하나</t>
         </is>
       </c>
       <c r="K66" s="6" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>크리에이츠</t>
+          <t>바로팜</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
@@ -4044,27 +4044,27 @@
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>76,395</t>
+          <t>96,724</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>23,749</t>
+          <t>-9,679</t>
         </is>
       </c>
       <c r="H67" s="7" t="inlineStr">
         <is>
-          <t>2,335</t>
+          <t>30,673</t>
         </is>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
-          <t>그외 기타 제품 제조업</t>
+          <t>상품 중개업</t>
         </is>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K67" s="6" t="inlineStr">
@@ -4076,12 +4076,12 @@
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>래블업</t>
+          <t>크리에이츠</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
@@ -4101,27 +4101,27 @@
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>6,712</t>
+          <t>76,395</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>-1,526</t>
+          <t>23,749</t>
         </is>
       </c>
       <c r="H68" s="7" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>2,335</t>
         </is>
       </c>
       <c r="I68" s="6" t="inlineStr">
         <is>
-          <t>데이터베이스 및 온라인정보 제공업</t>
+          <t>그외 기타 제품 제조업</t>
         </is>
       </c>
       <c r="J68" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K68" s="6" t="inlineStr">
@@ -4138,7 +4138,7 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>래블업</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
@@ -4158,27 +4158,27 @@
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>39,319</t>
+          <t>6,712</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>4,739</t>
+          <t>-1,526</t>
         </is>
       </c>
       <c r="H69" s="7" t="inlineStr">
         <is>
-          <t>1,250</t>
+          <t>373</t>
         </is>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>데이터베이스 및 온라인정보 제공업</t>
         </is>
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K69" s="6" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>엠비디</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
@@ -4215,27 +4215,27 @@
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>1,524</t>
+          <t>39,319</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>-2,125</t>
+          <t>4,739</t>
         </is>
       </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
-          <t>2,753</t>
+          <t>1,250</t>
         </is>
       </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
-          <t>물질 검사, 측정 및 분석기구 제조업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="J70" s="6" t="inlineStr">
         <is>
-          <t>하나</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K70" s="6" t="inlineStr">
@@ -4247,12 +4247,12 @@
     <row r="71">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>에스케이증권제14호기업인수목적</t>
+          <t>엠비디</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
@@ -4272,27 +4272,27 @@
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,524</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-2,125</t>
         </is>
       </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2,753</t>
         </is>
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>물질 검사, 측정 및 분석기구 제조업</t>
         </is>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>하나</t>
         </is>
       </c>
       <c r="K71" s="6" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>케이비제34호스팩</t>
+          <t>에스케이증권제14호기업인수목적</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
@@ -4339,7 +4339,7 @@
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I72" s="6" t="inlineStr">
@@ -4349,7 +4349,7 @@
       </c>
       <c r="J72" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="K72" s="6" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>한국제17호스팩</t>
+          <t>케이비제34호스팩</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I73" s="6" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="K73" s="6" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>한화플러스제6호스팩</t>
+          <t>한국제17호스팩</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="H74" s="7" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I74" s="6" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="J74" s="6" t="inlineStr">
         <is>
-          <t>한화</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K74" s="6" t="inlineStr">
@@ -4475,12 +4475,12 @@
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>엔에이치스팩34호</t>
+          <t>한화플러스제6호스팩</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
@@ -4510,34 +4510,34 @@
       </c>
       <c r="H75" s="7" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I75" s="6" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>한화</t>
         </is>
       </c>
       <c r="K75" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-09-10)</t>
+          <t>상장전</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>글로벌테크놀로지</t>
+          <t>엔에이치스팩34호</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
@@ -4557,32 +4557,32 @@
       </c>
       <c r="F76" s="7" t="inlineStr">
         <is>
-          <t>29,689</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>-25,889</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H76" s="7" t="inlineStr">
         <is>
-          <t>6,402</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I76" s="6" t="inlineStr">
         <is>
-          <t>반도체 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="J76" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K76" s="6" t="inlineStr">
         <is>
-          <t>상장전</t>
+          <t>상장완료 (2026-09-10)</t>
         </is>
       </c>
     </row>
@@ -4594,7 +4594,7 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>글로벌테크놀로지</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
@@ -4609,32 +4609,32 @@
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>FY24</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>48,504</t>
+          <t>29,689</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>3,668</t>
+          <t>-25,889</t>
         </is>
       </c>
       <c r="H77" s="7" t="inlineStr">
         <is>
-          <t>8,448</t>
+          <t>6,402</t>
         </is>
       </c>
       <c r="I77" s="6" t="inlineStr">
         <is>
-          <t>항공기,우주선 및 부품 제조업</t>
+          <t>반도체 제조업</t>
         </is>
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K77" s="6" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>디티에스</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
@@ -4671,22 +4671,22 @@
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>142,718</t>
+          <t>48,504</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>18,765</t>
+          <t>3,668</t>
         </is>
       </c>
       <c r="H78" s="7" t="inlineStr">
         <is>
-          <t>63,153</t>
+          <t>8,448</t>
         </is>
       </c>
       <c r="I78" s="6" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>항공기,우주선 및 부품 제조업</t>
         </is>
       </c>
       <c r="J78" s="6" t="inlineStr">
@@ -4703,12 +4703,12 @@
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>네오사피엔스</t>
+          <t>디티에스</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
@@ -4723,27 +4723,27 @@
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>FY25</t>
+          <t>FY24</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>10,649</t>
+          <t>142,718</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr">
         <is>
-          <t>-6,994</t>
+          <t>18,765</t>
         </is>
       </c>
       <c r="H79" s="7" t="inlineStr">
         <is>
-          <t>-39,962</t>
+          <t>63,153</t>
         </is>
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="J79" s="6" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>엠에스바이오</t>
+          <t>네오사피엔스</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
@@ -4785,27 +4785,27 @@
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>23,787</t>
+          <t>10,649</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
-          <t>7,288</t>
+          <t>-6,994</t>
         </is>
       </c>
       <c r="H80" s="7" t="inlineStr">
         <is>
-          <t>1,942</t>
+          <t>-39,962</t>
         </is>
       </c>
       <c r="I80" s="6" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J80" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K80" s="6" t="inlineStr">
@@ -4817,12 +4817,12 @@
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>기도산업</t>
+          <t>엠에스바이오</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
@@ -4842,32 +4842,32 @@
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>346,551</t>
+          <t>23,787</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
         <is>
-          <t>35,334</t>
+          <t>7,288</t>
         </is>
       </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
-          <t>145,991</t>
+          <t>1,942</t>
         </is>
       </c>
       <c r="I81" s="6" t="inlineStr">
         <is>
-          <t>봉제의복 제조업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="J81" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="K81" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-08-21)</t>
+          <t>상장전</t>
         </is>
       </c>
     </row>
@@ -4879,7 +4879,7 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>브릴스</t>
+          <t>기도산업</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
@@ -4899,32 +4899,32 @@
       </c>
       <c r="F82" s="7" t="inlineStr">
         <is>
-          <t>23,759</t>
+          <t>346,551</t>
         </is>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
-          <t>1,744</t>
+          <t>35,334</t>
         </is>
       </c>
       <c r="H82" s="7" t="inlineStr">
         <is>
-          <t>4,785</t>
+          <t>145,991</t>
         </is>
       </c>
       <c r="I82" s="6" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>봉제의복 제조업</t>
         </is>
       </c>
       <c r="J82" s="6" t="inlineStr">
         <is>
-          <t>IBK</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K82" s="6" t="inlineStr">
         <is>
-          <t>상장전</t>
+          <t>상장완료 (2026-08-21)</t>
         </is>
       </c>
     </row>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>와이즈플래닛컴퍼니</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
@@ -4956,27 +4956,27 @@
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>44,578</t>
+          <t>23,759</t>
         </is>
       </c>
       <c r="G83" s="7" t="inlineStr">
         <is>
-          <t>7,748</t>
+          <t>1,744</t>
         </is>
       </c>
       <c r="H83" s="7" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>4,785</t>
         </is>
       </c>
       <c r="I83" s="6" t="inlineStr">
         <is>
-          <t>광고물 문안, 도안, 설계 등 작성업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>IBK</t>
         </is>
       </c>
       <c r="K83" s="6" t="inlineStr">
@@ -4988,12 +4988,12 @@
     <row r="84">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>니어스랩</t>
+          <t>와이즈플래닛컴퍼니</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
@@ -5013,32 +5013,32 @@
       </c>
       <c r="F84" s="7" t="inlineStr">
         <is>
-          <t>6,361</t>
+          <t>44,578</t>
         </is>
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
-          <t>-7,287</t>
+          <t>7,748</t>
         </is>
       </c>
       <c r="H84" s="7" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>959</t>
         </is>
       </c>
       <c r="I84" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>광고물 문안, 도안, 설계 등 작성업</t>
         </is>
       </c>
       <c r="J84" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K84" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-08-24)</t>
+          <t>상장전</t>
         </is>
       </c>
     </row>
@@ -5050,7 +5050,7 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>해치텍</t>
+          <t>니어스랩</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
@@ -5070,32 +5070,32 @@
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>14,079</t>
+          <t>6,361</t>
         </is>
       </c>
       <c r="G85" s="7" t="inlineStr">
         <is>
-          <t>-8,009</t>
+          <t>-7,287</t>
         </is>
       </c>
       <c r="H85" s="7" t="inlineStr">
         <is>
-          <t>2,229</t>
+          <t>127</t>
         </is>
       </c>
       <c r="I85" s="6" t="inlineStr">
         <is>
-          <t>반도체 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J85" s="6" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K85" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-08-25)</t>
+          <t>상장완료 (2026-08-24)</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5107,7 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>해치텍</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
@@ -5127,44 +5127,44 @@
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
-          <t>7,936</t>
+          <t>14,079</t>
         </is>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
-          <t>-62,995</t>
+          <t>-8,009</t>
         </is>
       </c>
       <c r="H86" s="7" t="inlineStr">
         <is>
-          <t>8,341</t>
+          <t>2,229</t>
         </is>
       </c>
       <c r="I86" s="6" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>반도체 제조업</t>
         </is>
       </c>
       <c r="J86" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="K86" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-09-04)</t>
+          <t>상장완료 (2026-08-25)</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>에이치엘지노믹스</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
@@ -5184,32 +5184,32 @@
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>28,877</t>
+          <t>7,936</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>8,452</t>
+          <t>-62,995</t>
         </is>
       </c>
       <c r="H87" s="7" t="inlineStr">
         <is>
-          <t>83,552</t>
+          <t>8,341</t>
         </is>
       </c>
       <c r="I87" s="6" t="inlineStr">
         <is>
-          <t>기초 의약물질 제조업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="J87" s="6" t="inlineStr">
         <is>
-          <t>KB, IBK</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K87" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-07-24)</t>
+          <t>상장완료 (2026-09-04)</t>
         </is>
       </c>
     </row>
@@ -5221,7 +5221,7 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>딜리셔스</t>
+          <t>에이치엘지노믹스</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
@@ -5241,44 +5241,44 @@
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
-          <t>25,149</t>
+          <t>28,877</t>
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>-20,419</t>
+          <t>8,452</t>
         </is>
       </c>
       <c r="H88" s="7" t="inlineStr">
         <is>
-          <t>-114,384</t>
+          <t>83,552</t>
         </is>
       </c>
       <c r="I88" s="6" t="inlineStr">
         <is>
-          <t>무점포 소매업</t>
+          <t>기초 의약물질 제조업</t>
         </is>
       </c>
       <c r="J88" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>KB, IBK</t>
         </is>
       </c>
       <c r="K88" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-08-12)</t>
+          <t>상장완료 (2026-07-24)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스</t>
+          <t>딜리셔스</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
@@ -5298,44 +5298,44 @@
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>2,588,400</t>
+          <t>25,149</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr">
         <is>
-          <t>15,755,864</t>
+          <t>-20,419</t>
         </is>
       </c>
       <c r="H89" s="7" t="inlineStr">
         <is>
-          <t>30,841,690</t>
+          <t>-114,384</t>
         </is>
       </c>
       <c r="I89" s="6" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>무점포 소매업</t>
         </is>
       </c>
       <c r="J89" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K89" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-08-18)</t>
+          <t>상장완료 (2026-08-12)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>한국제16호스팩</t>
+          <t>인제니아테라퓨틱스</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
@@ -5353,30 +5353,46 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F90" s="7" t="inlineStr"/>
-      <c r="G90" s="7" t="inlineStr"/>
-      <c r="H90" s="7" t="inlineStr"/>
-      <c r="I90" s="6" t="inlineStr"/>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>2,588,400</t>
+        </is>
+      </c>
+      <c r="G90" s="7" t="inlineStr">
+        <is>
+          <t>15,755,864</t>
+        </is>
+      </c>
+      <c r="H90" s="7" t="inlineStr">
+        <is>
+          <t>30,841,690</t>
+        </is>
+      </c>
+      <c r="I90" s="6" t="inlineStr">
+        <is>
+          <t>자연과학 및 공학 연구개발업</t>
+        </is>
+      </c>
       <c r="J90" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K90" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-06-30)</t>
+          <t>상장완료 (2026-08-18)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>레메디</t>
+          <t>한국제16호스팩</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
@@ -5394,34 +5410,18 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F91" s="7" t="inlineStr">
-        <is>
-          <t>13,441</t>
-        </is>
-      </c>
-      <c r="G91" s="7" t="inlineStr">
-        <is>
-          <t>741</t>
-        </is>
-      </c>
-      <c r="H91" s="7" t="inlineStr">
-        <is>
-          <t>5,870</t>
-        </is>
-      </c>
-      <c r="I91" s="6" t="inlineStr">
-        <is>
-          <t>의료용 기기 제조업</t>
-        </is>
-      </c>
+      <c r="F91" s="7" t="inlineStr"/>
+      <c r="G91" s="7" t="inlineStr"/>
+      <c r="H91" s="7" t="inlineStr"/>
+      <c r="I91" s="6" t="inlineStr"/>
       <c r="J91" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K91" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-07-13)</t>
+          <t>상장완료 (2026-06-30)</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5433,7 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>케이앤에스아이앤씨</t>
+          <t>레메디</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
@@ -5453,44 +5453,44 @@
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>13,482</t>
+          <t>13,441</t>
         </is>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
-          <t>-2,213</t>
+          <t>741</t>
         </is>
       </c>
       <c r="H92" s="7" t="inlineStr">
         <is>
-          <t>4,273</t>
+          <t>5,870</t>
         </is>
       </c>
       <c r="I92" s="6" t="inlineStr">
         <is>
-          <t>통신 및 방송 장비 제조업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="J92" s="6" t="inlineStr">
         <is>
-          <t>IBK</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="K92" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-08-13)</t>
+          <t>상장완료 (2026-07-13)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>메리츠제2호스팩</t>
+          <t>케이앤에스아이앤씨</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
@@ -5508,30 +5508,46 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F93" s="7" t="inlineStr"/>
-      <c r="G93" s="7" t="inlineStr"/>
-      <c r="H93" s="7" t="inlineStr"/>
-      <c r="I93" s="6" t="inlineStr"/>
+      <c r="F93" s="7" t="inlineStr">
+        <is>
+          <t>13,482</t>
+        </is>
+      </c>
+      <c r="G93" s="7" t="inlineStr">
+        <is>
+          <t>-2,213</t>
+        </is>
+      </c>
+      <c r="H93" s="7" t="inlineStr">
+        <is>
+          <t>4,273</t>
+        </is>
+      </c>
+      <c r="I93" s="6" t="inlineStr">
+        <is>
+          <t>통신 및 방송 장비 제조업</t>
+        </is>
+      </c>
       <c r="J93" s="6" t="inlineStr">
         <is>
-          <t>메리츠</t>
+          <t>IBK</t>
         </is>
       </c>
       <c r="K93" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-06-19)</t>
+          <t>상장완료 (2026-08-13)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>빅웨이브로보틱스</t>
+          <t>메리츠제2호스팩</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
@@ -5546,49 +5562,33 @@
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>FY24</t>
-        </is>
-      </c>
-      <c r="F94" s="7" t="inlineStr">
-        <is>
-          <t>13,851</t>
-        </is>
-      </c>
-      <c r="G94" s="7" t="inlineStr">
-        <is>
-          <t>-5,856</t>
-        </is>
-      </c>
-      <c r="H94" s="7" t="inlineStr">
-        <is>
-          <t>9,470</t>
-        </is>
-      </c>
-      <c r="I94" s="6" t="inlineStr">
-        <is>
-          <t>소프트웨어 개발 및 공급업</t>
-        </is>
-      </c>
+          <t>FY25</t>
+        </is>
+      </c>
+      <c r="F94" s="7" t="inlineStr"/>
+      <c r="G94" s="7" t="inlineStr"/>
+      <c r="H94" s="7" t="inlineStr"/>
+      <c r="I94" s="6" t="inlineStr"/>
       <c r="J94" s="6" t="inlineStr">
         <is>
-          <t>유진, 미래</t>
+          <t>메리츠</t>
         </is>
       </c>
       <c r="K94" s="6" t="inlineStr">
         <is>
-          <t>상장전</t>
+          <t>상장완료 (2026-06-19)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>매드업</t>
+          <t>빅웨이브로보틱스</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
@@ -5608,44 +5608,44 @@
       </c>
       <c r="F95" s="7" t="inlineStr">
         <is>
-          <t>34,989</t>
+          <t>13,851</t>
         </is>
       </c>
       <c r="G95" s="7" t="inlineStr">
         <is>
-          <t>-2,747</t>
+          <t>-5,856</t>
         </is>
       </c>
       <c r="H95" s="7" t="inlineStr">
         <is>
-          <t>-15,766</t>
+          <t>9,470</t>
         </is>
       </c>
       <c r="I95" s="6" t="inlineStr">
         <is>
-          <t>광고</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J95" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>유진, 미래</t>
         </is>
       </c>
       <c r="K95" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-07-01)</t>
+          <t>상장전</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>져스텍</t>
+          <t>매드업</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
@@ -5665,32 +5665,32 @@
       </c>
       <c r="F96" s="7" t="inlineStr">
         <is>
-          <t>19,851</t>
+          <t>34,989</t>
         </is>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>-2,747</t>
         </is>
       </c>
       <c r="H96" s="7" t="inlineStr">
         <is>
-          <t>10,953</t>
+          <t>-15,766</t>
         </is>
       </c>
       <c r="I96" s="6" t="inlineStr">
         <is>
-          <t>기계</t>
+          <t>광고</t>
         </is>
       </c>
       <c r="J96" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K96" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-06-29)</t>
+          <t>상장완료 (2026-07-01)</t>
         </is>
       </c>
     </row>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>스트라드비젼</t>
+          <t>져스텍</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
@@ -5722,44 +5722,44 @@
       </c>
       <c r="F97" s="7" t="inlineStr">
         <is>
-          <t>11,539</t>
+          <t>19,851</t>
         </is>
       </c>
       <c r="G97" s="7" t="inlineStr">
         <is>
-          <t>-65,529</t>
+          <t>444</t>
         </is>
       </c>
       <c r="H97" s="7" t="inlineStr">
         <is>
-          <t>-245,151</t>
+          <t>10,953</t>
         </is>
       </c>
       <c r="I97" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어</t>
+          <t>기계</t>
         </is>
       </c>
       <c r="J97" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K97" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-06-30)</t>
+          <t>상장완료 (2026-06-29)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>대신밸런스제20호스팩</t>
+          <t>스트라드비젼</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
@@ -5774,33 +5774,49 @@
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>FY25</t>
-        </is>
-      </c>
-      <c r="F98" s="7" t="inlineStr"/>
-      <c r="G98" s="7" t="inlineStr"/>
-      <c r="H98" s="7" t="inlineStr"/>
-      <c r="I98" s="6" t="inlineStr"/>
+          <t>FY24</t>
+        </is>
+      </c>
+      <c r="F98" s="7" t="inlineStr">
+        <is>
+          <t>11,539</t>
+        </is>
+      </c>
+      <c r="G98" s="7" t="inlineStr">
+        <is>
+          <t>-65,529</t>
+        </is>
+      </c>
+      <c r="H98" s="7" t="inlineStr">
+        <is>
+          <t>-245,151</t>
+        </is>
+      </c>
+      <c r="I98" s="6" t="inlineStr">
+        <is>
+          <t>소프트웨어</t>
+        </is>
+      </c>
       <c r="J98" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="K98" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-06-05)</t>
+          <t>상장완료 (2026-06-30)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>피스피스스튜디오</t>
+          <t>대신밸런스제20호스팩</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
@@ -5815,37 +5831,21 @@
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>FY24</t>
-        </is>
-      </c>
-      <c r="F99" s="7" t="inlineStr">
-        <is>
-          <t>113,777</t>
-        </is>
-      </c>
-      <c r="G99" s="7" t="inlineStr">
-        <is>
-          <t>17,603</t>
-        </is>
-      </c>
-      <c r="H99" s="7" t="inlineStr">
-        <is>
-          <t>55,861</t>
-        </is>
-      </c>
-      <c r="I99" s="6" t="inlineStr">
-        <is>
-          <t>섬유,의류,신발,호화품</t>
-        </is>
-      </c>
+          <t>FY25</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr"/>
+      <c r="G99" s="7" t="inlineStr"/>
+      <c r="H99" s="7" t="inlineStr"/>
+      <c r="I99" s="6" t="inlineStr"/>
       <c r="J99" s="6" t="inlineStr">
         <is>
-          <t>NH, 미래</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K99" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-06-08)</t>
+          <t>상장완료 (2026-06-05)</t>
         </is>
       </c>
     </row>
@@ -5857,7 +5857,7 @@
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>폴레드</t>
+          <t>피스피스스튜디오</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
@@ -5877,32 +5877,32 @@
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>52,808</t>
+          <t>113,777</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>17,603</t>
         </is>
       </c>
       <c r="H100" s="7" t="inlineStr">
         <is>
-          <t>25,416</t>
+          <t>55,861</t>
         </is>
       </c>
       <c r="I100" s="6" t="inlineStr">
         <is>
-          <t>가정용기기와용품</t>
+          <t>섬유,의류,신발,호화품</t>
         </is>
       </c>
       <c r="J100" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>NH, 미래</t>
         </is>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-05-14)</t>
+          <t>상장완료 (2026-06-08)</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>레몬헬스케어</t>
+          <t>폴레드</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
@@ -5934,44 +5934,44 @@
       </c>
       <c r="F101" s="7" t="inlineStr">
         <is>
-          <t>14,877</t>
+          <t>52,808</t>
         </is>
       </c>
       <c r="G101" s="7" t="inlineStr">
         <is>
-          <t>-2,898</t>
+          <t>543</t>
         </is>
       </c>
       <c r="H101" s="7" t="inlineStr">
         <is>
-          <t>-31,162</t>
+          <t>25,416</t>
         </is>
       </c>
       <c r="I101" s="6" t="inlineStr">
         <is>
-          <t>건강관리업체및서비스</t>
+          <t>가정용기기와용품</t>
         </is>
       </c>
       <c r="J101" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K101" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-07-06)</t>
+          <t>상장완료 (2026-05-14)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>마키나락스</t>
+          <t>레몬헬스케어</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
@@ -5991,32 +5991,32 @@
       </c>
       <c r="F102" s="7" t="inlineStr">
         <is>
-          <t>8,294</t>
+          <t>14,877</t>
         </is>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
-          <t>-6,073</t>
+          <t>-2,898</t>
         </is>
       </c>
       <c r="H102" s="7" t="inlineStr">
         <is>
-          <t>2,680</t>
+          <t>-31,162</t>
         </is>
       </c>
       <c r="I102" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어</t>
+          <t>건강관리업체및서비스</t>
         </is>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="K102" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-05-20)</t>
+          <t>상장완료 (2026-07-06)</t>
         </is>
       </c>
     </row>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>채비</t>
+          <t>마키나락스</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
@@ -6048,44 +6048,44 @@
       </c>
       <c r="F103" s="7" t="inlineStr">
         <is>
-          <t>85,082</t>
+          <t>8,294</t>
         </is>
       </c>
       <c r="G103" s="7" t="inlineStr">
         <is>
-          <t>-54,495</t>
+          <t>-6,073</t>
         </is>
       </c>
       <c r="H103" s="7" t="inlineStr">
         <is>
-          <t>96,866</t>
+          <t>2,680</t>
         </is>
       </c>
       <c r="I103" s="6" t="inlineStr">
         <is>
-          <t>전기제품</t>
+          <t>소프트웨어</t>
         </is>
       </c>
       <c r="J103" s="6" t="inlineStr">
         <is>
-          <t>KB, 삼성, 대신, 하나</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K103" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-04-29)</t>
+          <t>상장완료 (2026-05-20)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>키움히어로제2호스팩</t>
+          <t>채비</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
@@ -6103,30 +6103,46 @@
           <t>FY24</t>
         </is>
       </c>
-      <c r="F104" s="7" t="inlineStr"/>
-      <c r="G104" s="7" t="inlineStr"/>
-      <c r="H104" s="7" t="inlineStr"/>
-      <c r="I104" s="6" t="inlineStr"/>
+      <c r="F104" s="7" t="inlineStr">
+        <is>
+          <t>85,082</t>
+        </is>
+      </c>
+      <c r="G104" s="7" t="inlineStr">
+        <is>
+          <t>-54,495</t>
+        </is>
+      </c>
+      <c r="H104" s="7" t="inlineStr">
+        <is>
+          <t>96,866</t>
+        </is>
+      </c>
+      <c r="I104" s="6" t="inlineStr">
+        <is>
+          <t>전기제품</t>
+        </is>
+      </c>
       <c r="J104" s="6" t="inlineStr">
         <is>
-          <t>키움</t>
+          <t>KB, 삼성, 대신, 하나</t>
         </is>
       </c>
       <c r="K104" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-04-23)</t>
+          <t>상장완료 (2026-04-29)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>세미티에스</t>
+          <t>키움히어로제2호스팩</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
@@ -6136,7 +6152,7 @@
       </c>
       <c r="D105" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E105" s="6" t="inlineStr">
@@ -6144,46 +6160,30 @@
           <t>FY24</t>
         </is>
       </c>
-      <c r="F105" s="7" t="inlineStr">
-        <is>
-          <t>20,808</t>
-        </is>
-      </c>
-      <c r="G105" s="7" t="inlineStr">
-        <is>
-          <t>7,337</t>
-        </is>
-      </c>
-      <c r="H105" s="7" t="inlineStr">
-        <is>
-          <t>26,616</t>
-        </is>
-      </c>
-      <c r="I105" s="6" t="inlineStr">
-        <is>
-          <t>반도체와반도체장비</t>
-        </is>
-      </c>
+      <c r="F105" s="7" t="inlineStr"/>
+      <c r="G105" s="7" t="inlineStr"/>
+      <c r="H105" s="7" t="inlineStr"/>
+      <c r="I105" s="6" t="inlineStr"/>
       <c r="J105" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>키움</t>
         </is>
       </c>
       <c r="K105" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-02-05)</t>
+          <t>상장완료 (2026-04-23)</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>교보20호스팩</t>
+          <t>세미티에스</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
@@ -6201,30 +6201,46 @@
           <t>FY24</t>
         </is>
       </c>
-      <c r="F106" s="7" t="inlineStr"/>
-      <c r="G106" s="7" t="inlineStr"/>
-      <c r="H106" s="7" t="inlineStr"/>
-      <c r="I106" s="6" t="inlineStr"/>
+      <c r="F106" s="7" t="inlineStr">
+        <is>
+          <t>20,808</t>
+        </is>
+      </c>
+      <c r="G106" s="7" t="inlineStr">
+        <is>
+          <t>7,337</t>
+        </is>
+      </c>
+      <c r="H106" s="7" t="inlineStr">
+        <is>
+          <t>26,616</t>
+        </is>
+      </c>
+      <c r="I106" s="6" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
       <c r="J106" s="6" t="inlineStr">
         <is>
-          <t>교보</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K106" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-04-02)</t>
+          <t>상장완료 (2026-02-05)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>케이피항공산업</t>
+          <t>교보20호스팩</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
@@ -6234,7 +6250,7 @@
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
@@ -6242,34 +6258,18 @@
           <t>FY24</t>
         </is>
       </c>
-      <c r="F107" s="7" t="inlineStr">
-        <is>
-          <t>49,651</t>
-        </is>
-      </c>
-      <c r="G107" s="7" t="inlineStr">
-        <is>
-          <t>3,018</t>
-        </is>
-      </c>
-      <c r="H107" s="7" t="inlineStr">
-        <is>
-          <t>15,901</t>
-        </is>
-      </c>
-      <c r="I107" s="6" t="inlineStr">
-        <is>
-          <t>우주항공과국방</t>
-        </is>
-      </c>
+      <c r="F107" s="7" t="inlineStr"/>
+      <c r="G107" s="7" t="inlineStr"/>
+      <c r="H107" s="7" t="inlineStr"/>
+      <c r="I107" s="6" t="inlineStr"/>
       <c r="J107" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>교보</t>
         </is>
       </c>
       <c r="K107" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-01-29)</t>
+          <t>상장완료 (2026-04-02)</t>
         </is>
       </c>
     </row>
@@ -6281,7 +6281,7 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>한패스</t>
+          <t>케이피항공산업</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
@@ -6301,44 +6301,44 @@
       </c>
       <c r="F108" s="7" t="inlineStr">
         <is>
-          <t>55,297</t>
+          <t>49,651</t>
         </is>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
-          <t>4,403</t>
+          <t>3,018</t>
         </is>
       </c>
       <c r="H108" s="7" t="inlineStr">
         <is>
-          <t>-28,065</t>
+          <t>15,901</t>
         </is>
       </c>
       <c r="I108" s="6" t="inlineStr">
         <is>
-          <t>IT서비스</t>
+          <t>우주항공과국방</t>
         </is>
       </c>
       <c r="J108" s="6" t="inlineStr">
         <is>
-          <t>한국, 대신</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K108" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-03-25)</t>
+          <t>상장완료 (2026-01-29)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="6" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>신한제18호스팩</t>
+          <t>한패스</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
@@ -6356,30 +6356,46 @@
           <t>FY24</t>
         </is>
       </c>
-      <c r="F109" s="7" t="inlineStr"/>
-      <c r="G109" s="7" t="inlineStr"/>
-      <c r="H109" s="7" t="inlineStr"/>
-      <c r="I109" s="6" t="inlineStr"/>
+      <c r="F109" s="7" t="inlineStr">
+        <is>
+          <t>55,297</t>
+        </is>
+      </c>
+      <c r="G109" s="7" t="inlineStr">
+        <is>
+          <t>4,403</t>
+        </is>
+      </c>
+      <c r="H109" s="7" t="inlineStr">
+        <is>
+          <t>-28,065</t>
+        </is>
+      </c>
+      <c r="I109" s="6" t="inlineStr">
+        <is>
+          <t>IT서비스</t>
+        </is>
+      </c>
       <c r="J109" s="6" t="inlineStr">
         <is>
-          <t>신한</t>
+          <t>한국, 대신</t>
         </is>
       </c>
       <c r="K109" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-04-30)</t>
+          <t>상장완료 (2026-03-25)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>엔에이치스팩33호</t>
+          <t>신한제18호스팩</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
@@ -6403,24 +6419,24 @@
       <c r="I110" s="6" t="inlineStr"/>
       <c r="J110" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>신한</t>
         </is>
       </c>
       <c r="K110" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-03-27)</t>
+          <t>상장완료 (2026-04-30)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="6" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>신한제17호스팩</t>
+          <t>엔에이치스팩33호</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
@@ -6444,24 +6460,24 @@
       <c r="I111" s="6" t="inlineStr"/>
       <c r="J111" s="6" t="inlineStr">
         <is>
-          <t>신한</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K111" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-04-01)</t>
+          <t>상장완료 (2026-03-27)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>아이엠바이오로직스</t>
+          <t>신한제17호스팩</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
@@ -6479,34 +6495,18 @@
           <t>FY24</t>
         </is>
       </c>
-      <c r="F112" s="7" t="inlineStr">
-        <is>
-          <t>27,594</t>
-        </is>
-      </c>
-      <c r="G112" s="7" t="inlineStr">
-        <is>
-          <t>-11,884</t>
-        </is>
-      </c>
-      <c r="H112" s="7" t="inlineStr">
-        <is>
-          <t>-77,202</t>
-        </is>
-      </c>
-      <c r="I112" s="6" t="inlineStr">
-        <is>
-          <t>제약</t>
-        </is>
-      </c>
+      <c r="F112" s="7" t="inlineStr"/>
+      <c r="G112" s="7" t="inlineStr"/>
+      <c r="H112" s="7" t="inlineStr"/>
+      <c r="I112" s="6" t="inlineStr"/>
       <c r="J112" s="6" t="inlineStr">
         <is>
-          <t>한국, 신한</t>
+          <t>신한</t>
         </is>
       </c>
       <c r="K112" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-03-20)</t>
+          <t>상장완료 (2026-04-01)</t>
         </is>
       </c>
     </row>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>에스팀</t>
+          <t>아이엠바이오로직스</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
@@ -6538,232 +6538,232 @@
       </c>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>35,574</t>
+          <t>27,594</t>
         </is>
       </c>
       <c r="G113" s="7" t="inlineStr">
         <is>
-          <t>1,372</t>
+          <t>-11,884</t>
         </is>
       </c>
       <c r="H113" s="7" t="inlineStr">
         <is>
-          <t>12,331</t>
+          <t>-77,202</t>
         </is>
       </c>
       <c r="I113" s="6" t="inlineStr">
         <is>
-          <t>광고</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="J113" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>한국, 신한</t>
         </is>
       </c>
       <c r="K113" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-03-06)</t>
+          <t>상장완료 (2026-03-20)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
         <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>에스팀</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="inlineStr">
+        <is>
+          <t>신규상장</t>
+        </is>
+      </c>
+      <c r="E114" s="6" t="inlineStr">
+        <is>
+          <t>FY24</t>
+        </is>
+      </c>
+      <c r="F114" s="7" t="inlineStr">
+        <is>
+          <t>35,574</t>
+        </is>
+      </c>
+      <c r="G114" s="7" t="inlineStr">
+        <is>
+          <t>1,372</t>
+        </is>
+      </c>
+      <c r="H114" s="7" t="inlineStr">
+        <is>
+          <t>12,331</t>
+        </is>
+      </c>
+      <c r="I114" s="6" t="inlineStr">
+        <is>
+          <t>광고</t>
+        </is>
+      </c>
+      <c r="J114" s="6" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="K114" s="6" t="inlineStr">
+        <is>
+          <t>상장완료 (2026-03-06)</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
           <t>2026-01-12</t>
         </is>
       </c>
-      <c r="B114" s="6" t="inlineStr">
+      <c r="B115" s="6" t="inlineStr">
         <is>
           <t>케이뱅크</t>
         </is>
       </c>
-      <c r="C114" s="6" t="inlineStr">
+      <c r="C115" s="6" t="inlineStr">
         <is>
           <t>유가</t>
         </is>
       </c>
-      <c r="D114" s="6" t="inlineStr">
+      <c r="D115" s="6" t="inlineStr">
         <is>
           <t>신규상장</t>
         </is>
       </c>
-      <c r="E114" s="6" t="inlineStr">
+      <c r="E115" s="6" t="inlineStr">
         <is>
           <t>FY24</t>
         </is>
       </c>
-      <c r="F114" s="7" t="inlineStr">
+      <c r="F115" s="7" t="inlineStr">
         <is>
           <t>1,228,501</t>
         </is>
       </c>
-      <c r="G114" s="7" t="inlineStr">
+      <c r="G115" s="7" t="inlineStr">
         <is>
           <t>128,053</t>
         </is>
       </c>
-      <c r="H114" s="7" t="inlineStr">
+      <c r="H115" s="7" t="inlineStr">
         <is>
           <t>1,995,845</t>
         </is>
       </c>
-      <c r="I114" s="6" t="inlineStr">
+      <c r="I115" s="6" t="inlineStr">
         <is>
           <t>은행</t>
         </is>
       </c>
-      <c r="J114" s="6" t="inlineStr">
+      <c r="J115" s="6" t="inlineStr">
         <is>
           <t>NH, 삼성</t>
         </is>
       </c>
-      <c r="K114" s="6" t="inlineStr">
+      <c r="K115" s="6" t="inlineStr">
         <is>
           <t>상장완료 (2026-03-05)</t>
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="3" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="3" t="inlineStr">
         <is>
           <t>■ 철회·미승인  (18건)</t>
         </is>
       </c>
-      <c r="B116" s="4" t="n"/>
-      <c r="C116" s="4" t="n"/>
-      <c r="D116" s="4" t="n"/>
-      <c r="E116" s="4" t="n"/>
-      <c r="F116" s="4" t="n"/>
-      <c r="G116" s="4" t="n"/>
-      <c r="H116" s="4" t="n"/>
-      <c r="I116" s="4" t="n"/>
-      <c r="J116" s="4" t="n"/>
-      <c r="K116" s="4" t="n"/>
-    </row>
-    <row r="117">
-      <c r="A117" s="5" t="inlineStr">
+      <c r="B117" s="4" t="n"/>
+      <c r="C117" s="4" t="n"/>
+      <c r="D117" s="4" t="n"/>
+      <c r="E117" s="4" t="n"/>
+      <c r="F117" s="4" t="n"/>
+      <c r="G117" s="4" t="n"/>
+      <c r="H117" s="4" t="n"/>
+      <c r="I117" s="4" t="n"/>
+      <c r="J117" s="4" t="n"/>
+      <c r="K117" s="4" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr">
         <is>
           <t>일자</t>
         </is>
       </c>
-      <c r="B117" s="5" t="inlineStr">
+      <c r="B118" s="5" t="inlineStr">
         <is>
           <t>회사명</t>
         </is>
       </c>
-      <c r="C117" s="5" t="inlineStr">
+      <c r="C118" s="5" t="inlineStr">
         <is>
           <t>시장</t>
         </is>
       </c>
-      <c r="D117" s="5" t="inlineStr">
+      <c r="D118" s="5" t="inlineStr">
         <is>
           <t>상장유형</t>
         </is>
       </c>
-      <c r="E117" s="5" t="inlineStr">
+      <c r="E118" s="5" t="inlineStr">
         <is>
           <t>기준연도</t>
         </is>
       </c>
-      <c r="F117" s="5" t="inlineStr">
+      <c r="F118" s="5" t="inlineStr">
         <is>
           <t>매출액</t>
         </is>
       </c>
-      <c r="G117" s="5" t="inlineStr">
+      <c r="G118" s="5" t="inlineStr">
         <is>
           <t>순이익</t>
         </is>
       </c>
-      <c r="H117" s="5" t="inlineStr">
+      <c r="H118" s="5" t="inlineStr">
         <is>
           <t>자기자본</t>
         </is>
       </c>
-      <c r="I117" s="5" t="inlineStr">
+      <c r="I118" s="5" t="inlineStr">
         <is>
           <t>업종</t>
         </is>
       </c>
-      <c r="J117" s="5" t="inlineStr">
+      <c r="J118" s="5" t="inlineStr">
         <is>
           <t>대표주관사</t>
         </is>
       </c>
-      <c r="K117" s="5" t="inlineStr">
+      <c r="K118" s="5" t="inlineStr">
         <is>
           <t>현황</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B118" s="6" t="inlineStr">
-        <is>
-          <t>텔레픽스</t>
-        </is>
-      </c>
-      <c r="C118" s="6" t="inlineStr">
-        <is>
-          <t>코스닥</t>
-        </is>
-      </c>
-      <c r="D118" s="6" t="inlineStr">
-        <is>
-          <t>신규상장</t>
-        </is>
-      </c>
-      <c r="E118" s="6" t="inlineStr">
-        <is>
-          <t>FY25</t>
-        </is>
-      </c>
-      <c r="F118" s="7" t="inlineStr">
-        <is>
-          <t>4,896</t>
-        </is>
-      </c>
-      <c r="G118" s="7" t="inlineStr">
-        <is>
-          <t>-16,214</t>
-        </is>
-      </c>
-      <c r="H118" s="7" t="inlineStr">
-        <is>
-          <t>9,146</t>
-        </is>
-      </c>
-      <c r="I118" s="6" t="inlineStr">
-        <is>
-          <t>소프트웨어 개발 및 공급업</t>
-        </is>
-      </c>
-      <c r="J118" s="6" t="inlineStr">
-        <is>
-          <t>미래</t>
-        </is>
-      </c>
-      <c r="K118" s="6" t="inlineStr">
-        <is>
-          <t>심사 철회</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>씨엠디엘</t>
+          <t>텔레픽스</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
@@ -6773,37 +6773,37 @@
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
         <is>
-          <t>FY24</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="F119" s="7" t="inlineStr">
         <is>
-          <t>39,991</t>
+          <t>4,896</t>
         </is>
       </c>
       <c r="G119" s="7" t="inlineStr">
         <is>
-          <t>3,541</t>
+          <t>-16,214</t>
         </is>
       </c>
       <c r="H119" s="7" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>9,146</t>
         </is>
       </c>
       <c r="I119" s="6" t="inlineStr">
         <is>
-          <t>기타 기초 유기 화학물질 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J119" s="6" t="inlineStr">
         <is>
-          <t>교보</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K119" s="6" t="inlineStr">
@@ -6815,12 +6815,12 @@
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>모비어스</t>
+          <t>씨엠디엘</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
@@ -6830,37 +6830,37 @@
       </c>
       <c r="D120" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
         <is>
-          <t>FY25</t>
+          <t>FY24</t>
         </is>
       </c>
       <c r="F120" s="7" t="inlineStr">
         <is>
-          <t>31,989</t>
+          <t>39,991</t>
         </is>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
-          <t>-45,307</t>
+          <t>3,541</t>
         </is>
       </c>
       <c r="H120" s="7" t="inlineStr">
         <is>
-          <t>-96,707</t>
+          <t>503</t>
         </is>
       </c>
       <c r="I120" s="6" t="inlineStr">
         <is>
-          <t>컴퓨터 프로그래밍, 시스템 통합 및 관리업</t>
+          <t>기타 기초 유기 화학물질 제조업</t>
         </is>
       </c>
       <c r="J120" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>교보</t>
         </is>
       </c>
       <c r="K120" s="6" t="inlineStr">
@@ -6872,12 +6872,12 @@
     <row r="121">
       <c r="A121" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>넥스트젠바이오</t>
+          <t>모비어스</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
@@ -6892,32 +6892,32 @@
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
-          <t>FY24</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="F121" s="7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>31,989</t>
         </is>
       </c>
       <c r="G121" s="7" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>-45,307</t>
         </is>
       </c>
       <c r="H121" s="7" t="inlineStr">
         <is>
-          <t>4,792</t>
+          <t>-96,707</t>
         </is>
       </c>
       <c r="I121" s="6" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>컴퓨터 프로그래밍, 시스템 통합 및 관리업</t>
         </is>
       </c>
       <c r="J121" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K121" s="6" t="inlineStr">
@@ -6929,12 +6929,12 @@
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>파워큐브세미</t>
+          <t>넥스트젠바이오</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
@@ -6949,32 +6949,32 @@
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
-          <t>FY25</t>
+          <t>FY24</t>
         </is>
       </c>
       <c r="F122" s="7" t="inlineStr">
         <is>
-          <t>10,341</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G122" s="7" t="inlineStr">
         <is>
-          <t>-10,837</t>
+          <t>69</t>
         </is>
       </c>
       <c r="H122" s="7" t="inlineStr">
         <is>
-          <t>841</t>
+          <t>4,792</t>
         </is>
       </c>
       <c r="I122" s="6" t="inlineStr">
         <is>
-          <t>반도체 제조업</t>
+          <t>자연과학 및 공학 연구개발업</t>
         </is>
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>
-          <t>하나, BNK</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K122" s="6" t="inlineStr">
@@ -6986,12 +6986,12 @@
     <row r="123">
       <c r="A123" s="6" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>제이피이노베이션</t>
+          <t>파워큐브세미</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
@@ -7011,27 +7011,27 @@
       </c>
       <c r="F123" s="7" t="inlineStr">
         <is>
-          <t>56,324</t>
+          <t>10,341</t>
         </is>
       </c>
       <c r="G123" s="7" t="inlineStr">
         <is>
-          <t>5,588</t>
+          <t>-10,837</t>
         </is>
       </c>
       <c r="H123" s="7" t="inlineStr">
         <is>
-          <t>3,684</t>
+          <t>841</t>
         </is>
       </c>
       <c r="I123" s="6" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>반도체 제조업</t>
         </is>
       </c>
       <c r="J123" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>하나, BNK</t>
         </is>
       </c>
       <c r="K123" s="6" t="inlineStr">
@@ -7043,12 +7043,12 @@
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>케이솔루션</t>
+          <t>제이피이노베이션</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="D124" s="6" t="inlineStr">
         <is>
-          <t>스팩 존속합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E124" s="6" t="inlineStr">
@@ -7068,27 +7068,27 @@
       </c>
       <c r="F124" s="7" t="inlineStr">
         <is>
-          <t>34,565</t>
+          <t>56,324</t>
         </is>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
-          <t>1,158</t>
+          <t>5,588</t>
         </is>
       </c>
       <c r="H124" s="7" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>3,684</t>
         </is>
       </c>
       <c r="I124" s="6" t="inlineStr">
         <is>
-          <t>차체 및 특장차 제조업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="J124" s="6" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K124" s="6" t="inlineStr">
@@ -7100,12 +7100,12 @@
     <row r="125">
       <c r="A125" s="6" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>디토닉</t>
+          <t>케이솔루션</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
@@ -7115,37 +7115,37 @@
       </c>
       <c r="D125" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 존속합병</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr">
         <is>
-          <t>FY24</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="F125" s="7" t="inlineStr">
         <is>
-          <t>31,293</t>
+          <t>34,565</t>
         </is>
       </c>
       <c r="G125" s="7" t="inlineStr">
         <is>
-          <t>-1,633</t>
+          <t>1,158</t>
         </is>
       </c>
       <c r="H125" s="7" t="inlineStr">
         <is>
-          <t>-21,926</t>
+          <t>653</t>
         </is>
       </c>
       <c r="I125" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>차체 및 특장차 제조업</t>
         </is>
       </c>
       <c r="J125" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="K125" s="6" t="inlineStr">
@@ -7157,12 +7157,12 @@
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>에스케이팩</t>
+          <t>디토닉</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
@@ -7172,7 +7172,7 @@
       </c>
       <c r="D126" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
@@ -7182,27 +7182,27 @@
       </c>
       <c r="F126" s="7" t="inlineStr">
         <is>
-          <t>27,310</t>
+          <t>31,293</t>
         </is>
       </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
-          <t>2,257</t>
+          <t>-1,633</t>
         </is>
       </c>
       <c r="H126" s="7" t="inlineStr">
         <is>
-          <t>3,207</t>
+          <t>-21,926</t>
         </is>
       </c>
       <c r="I126" s="6" t="inlineStr">
         <is>
-          <t>용기 세척, 포장 및 충전기 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J126" s="6" t="inlineStr">
         <is>
-          <t>교보</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K126" s="6" t="inlineStr">
@@ -7214,12 +7214,12 @@
     <row r="127">
       <c r="A127" s="6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>메타넷엑스</t>
+          <t>에스케이팩</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="D127" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr">
@@ -7239,27 +7239,27 @@
       </c>
       <c r="F127" s="7" t="inlineStr">
         <is>
-          <t>244,130</t>
+          <t>27,310</t>
         </is>
       </c>
       <c r="G127" s="7" t="inlineStr">
         <is>
-          <t>13,455</t>
+          <t>2,257</t>
         </is>
       </c>
       <c r="H127" s="7" t="inlineStr">
         <is>
-          <t>9,995</t>
+          <t>3,207</t>
         </is>
       </c>
       <c r="I127" s="6" t="inlineStr">
         <is>
-          <t>컴퓨터 프로그래밍, 시스템 통합 및 관리업</t>
+          <t>용기 세척, 포장 및 충전기 제조업</t>
         </is>
       </c>
       <c r="J127" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>교보</t>
         </is>
       </c>
       <c r="K127" s="6" t="inlineStr">
@@ -7271,12 +7271,12 @@
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>무아스</t>
+          <t>메타넷엑스</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
@@ -7296,27 +7296,27 @@
       </c>
       <c r="F128" s="7" t="inlineStr">
         <is>
-          <t>41,813</t>
+          <t>244,130</t>
         </is>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
-          <t>3,903</t>
+          <t>13,455</t>
         </is>
       </c>
       <c r="H128" s="7" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>9,995</t>
         </is>
       </c>
       <c r="I128" s="6" t="inlineStr">
         <is>
-          <t>가정용 전기기기 제조업</t>
+          <t>컴퓨터 프로그래밍, 시스템 통합 및 관리업</t>
         </is>
       </c>
       <c r="J128" s="6" t="inlineStr">
         <is>
-          <t>신한</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K128" s="6" t="inlineStr">
@@ -7333,7 +7333,7 @@
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>유빅스테라퓨틱스</t>
+          <t>무아스</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
@@ -7343,7 +7343,7 @@
       </c>
       <c r="D129" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr">
@@ -7353,27 +7353,27 @@
       </c>
       <c r="F129" s="7" t="inlineStr">
         <is>
-          <t>1,071</t>
+          <t>41,813</t>
         </is>
       </c>
       <c r="G129" s="7" t="inlineStr">
         <is>
-          <t>-15,145</t>
+          <t>3,903</t>
         </is>
       </c>
       <c r="H129" s="7" t="inlineStr">
         <is>
-          <t>5,489</t>
+          <t>532</t>
         </is>
       </c>
       <c r="I129" s="6" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>가정용 전기기기 제조업</t>
         </is>
       </c>
       <c r="J129" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>신한</t>
         </is>
       </c>
       <c r="K129" s="6" t="inlineStr">
@@ -7385,12 +7385,12 @@
     <row r="130">
       <c r="A130" s="6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>코드잇</t>
+          <t>유빅스테라퓨틱스</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
@@ -7410,27 +7410,27 @@
       </c>
       <c r="F130" s="7" t="inlineStr">
         <is>
-          <t>30,747</t>
+          <t>1,071</t>
         </is>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
-          <t>6,652</t>
+          <t>-15,145</t>
         </is>
       </c>
       <c r="H130" s="7" t="inlineStr">
         <is>
-          <t>2,403</t>
+          <t>5,489</t>
         </is>
       </c>
       <c r="I130" s="6" t="inlineStr">
         <is>
-          <t>교육지원 서비스업</t>
+          <t>자연과학 및 공학 연구개발업</t>
         </is>
       </c>
       <c r="J130" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K130" s="6" t="inlineStr">
@@ -7442,12 +7442,12 @@
     <row r="131">
       <c r="A131" s="6" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>한컴인스페이스</t>
+          <t>코드잇</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
@@ -7467,44 +7467,44 @@
       </c>
       <c r="F131" s="7" t="inlineStr">
         <is>
-          <t>23,492</t>
+          <t>30,747</t>
         </is>
       </c>
       <c r="G131" s="7" t="inlineStr">
         <is>
-          <t>-3,104</t>
+          <t>6,652</t>
         </is>
       </c>
       <c r="H131" s="7" t="inlineStr">
         <is>
-          <t>5,815</t>
+          <t>2,403</t>
         </is>
       </c>
       <c r="I131" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>교육지원 서비스업</t>
         </is>
       </c>
       <c r="J131" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K131" s="6" t="inlineStr">
         <is>
-          <t>심사 미승인</t>
+          <t>심사 철회</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>크몽</t>
+          <t>한컴인스페이스</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
@@ -7524,44 +7524,44 @@
       </c>
       <c r="F132" s="7" t="inlineStr">
         <is>
-          <t>48,572</t>
+          <t>23,492</t>
         </is>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
-          <t>3,988</t>
+          <t>-3,104</t>
         </is>
       </c>
       <c r="H132" s="7" t="inlineStr">
         <is>
-          <t>4,930</t>
+          <t>5,815</t>
         </is>
       </c>
       <c r="I132" s="6" t="inlineStr">
         <is>
-          <t>기타 정보 서비스업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J132" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K132" s="6" t="inlineStr">
         <is>
-          <t>심사 철회</t>
+          <t>심사 미승인</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="6" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>한화플러스제6호스팩</t>
+          <t>크몽</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
@@ -7581,27 +7581,27 @@
       </c>
       <c r="F133" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>48,572</t>
         </is>
       </c>
       <c r="G133" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3,988</t>
         </is>
       </c>
       <c r="H133" s="7" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4,930</t>
         </is>
       </c>
       <c r="I133" s="6" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>기타 정보 서비스업</t>
         </is>
       </c>
       <c r="J133" s="6" t="inlineStr">
         <is>
-          <t>한화</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K133" s="6" t="inlineStr">
@@ -7613,17 +7613,17 @@
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>에식스솔루션즈</t>
+          <t>한화플러스제6호스팩</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
         <is>
-          <t>유가</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D134" s="6" t="inlineStr">
@@ -7638,27 +7638,27 @@
       </c>
       <c r="F134" s="7" t="inlineStr">
         <is>
-          <t>2,461</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H134" s="7" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I134" s="6" t="inlineStr">
         <is>
-          <t>절연선 및 케이블 제조업</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="J134" s="6" t="inlineStr">
         <is>
-          <t>한국, 미래</t>
+          <t>한화</t>
         </is>
       </c>
       <c r="K134" s="6" t="inlineStr">
@@ -7670,55 +7670,112 @@
     <row r="135">
       <c r="A135" s="6" t="inlineStr">
         <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B135" s="6" t="inlineStr">
+        <is>
+          <t>에식스솔루션즈</t>
+        </is>
+      </c>
+      <c r="C135" s="6" t="inlineStr">
+        <is>
+          <t>유가</t>
+        </is>
+      </c>
+      <c r="D135" s="6" t="inlineStr">
+        <is>
+          <t>신규상장</t>
+        </is>
+      </c>
+      <c r="E135" s="6" t="inlineStr">
+        <is>
+          <t>FY24</t>
+        </is>
+      </c>
+      <c r="F135" s="7" t="inlineStr">
+        <is>
+          <t>2,461</t>
+        </is>
+      </c>
+      <c r="G135" s="7" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="H135" s="7" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I135" s="6" t="inlineStr">
+        <is>
+          <t>절연선 및 케이블 제조업</t>
+        </is>
+      </c>
+      <c r="J135" s="6" t="inlineStr">
+        <is>
+          <t>한국, 미래</t>
+        </is>
+      </c>
+      <c r="K135" s="6" t="inlineStr">
+        <is>
+          <t>심사 철회</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
           <t>2026-01-23</t>
         </is>
       </c>
-      <c r="B135" s="6" t="inlineStr">
+      <c r="B136" s="6" t="inlineStr">
         <is>
           <t>에코크레이션</t>
         </is>
       </c>
-      <c r="C135" s="6" t="inlineStr">
+      <c r="C136" s="6" t="inlineStr">
         <is>
           <t>코스닥</t>
         </is>
       </c>
-      <c r="D135" s="6" t="inlineStr">
+      <c r="D136" s="6" t="inlineStr">
         <is>
           <t>신규상장</t>
         </is>
       </c>
-      <c r="E135" s="6" t="inlineStr">
+      <c r="E136" s="6" t="inlineStr">
         <is>
           <t>FY24</t>
         </is>
       </c>
-      <c r="F135" s="7" t="inlineStr">
+      <c r="F136" s="7" t="inlineStr">
         <is>
           <t>18,544</t>
         </is>
       </c>
-      <c r="G135" s="7" t="inlineStr">
+      <c r="G136" s="7" t="inlineStr">
         <is>
           <t>-15,634</t>
         </is>
       </c>
-      <c r="H135" s="7" t="inlineStr">
+      <c r="H136" s="7" t="inlineStr">
         <is>
           <t>4,550</t>
         </is>
       </c>
-      <c r="I135" s="6" t="inlineStr">
+      <c r="I136" s="6" t="inlineStr">
         <is>
           <t>일반 목적용 기계 제조업</t>
         </is>
       </c>
-      <c r="J135" s="6" t="inlineStr">
+      <c r="J136" s="6" t="inlineStr">
         <is>
           <t>키움</t>
         </is>
       </c>
-      <c r="K135" s="6" t="inlineStr">
+      <c r="K136" s="6" t="inlineStr">
         <is>
           <t>심사 철회</t>
         </is>
@@ -7735,7 +7792,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R80"/>
+  <dimension ref="A1:R82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -11173,7 +11230,7 @@
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>■ 공모 진행 (예심 승인법인)  (28건)</t>
+          <t>■ 공모 진행 (예심 승인법인)  (30건)</t>
         </is>
       </c>
       <c r="B48" s="4" t="n"/>
@@ -11485,40 +11542,48 @@
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>브릴스</t>
+          <t>빅웨이브로보틱스</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>08-31~09-04</t>
+          <t>09-07~09-11</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>16,500~19,500</t>
+          <t>15,000~18,000</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>1,200,000</t>
+          <t>1,600,000</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>19,800,000,000</t>
+          <t>28,800,000,000</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>13.44 (PSR)</t>
-        </is>
-      </c>
-      <c r="G53" s="6" t="inlineStr"/>
-      <c r="H53" s="6" t="inlineStr"/>
-      <c r="I53" s="6" t="inlineStr"/>
+          <t>11.15 (PSR)</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>18,000</t>
+        </is>
+      </c>
+      <c r="H53" s="6" t="n">
+        <v>1109.37</v>
+      </c>
+      <c r="I53" s="6" t="n">
+        <v>2255</v>
+      </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>09-08~09-09</t>
+          <t>09-15~09-16</t>
         </is>
       </c>
       <c r="K53" s="6" t="inlineStr"/>
@@ -11526,55 +11591,59 @@
       <c r="M53" s="6" t="inlineStr"/>
       <c r="N53" s="6" t="inlineStr">
         <is>
-          <t>아이비케이투자증권</t>
-        </is>
-      </c>
-      <c r="O53" s="6" t="inlineStr"/>
+          <t>유진투자증권</t>
+        </is>
+      </c>
+      <c r="O53" s="6" t="inlineStr">
+        <is>
+          <t>미래</t>
+        </is>
+      </c>
       <c r="P53" s="7" t="inlineStr">
         <is>
-          <t>713,790,000</t>
+          <t>378,216,000</t>
         </is>
       </c>
       <c r="Q53" s="6" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>정정</t>
+          <t>발행조건확정</t>
         </is>
       </c>
     </row>
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>빅웨이브로보틱스</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>09-07~09-11</t>
+          <t>08-31~09-04</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>15,000~18,000</t>
+          <t>16,500~19,500</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>1,600,000</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>24,000,000,000</t>
+          <t>19,800,000,000</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>11.15 (PSR)</t>
+          <t>13.44 (PSR)</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr"/>
@@ -11582,7 +11651,7 @@
       <c r="I54" s="6" t="inlineStr"/>
       <c r="J54" s="6" t="inlineStr">
         <is>
-          <t>09-15~09-16</t>
+          <t>09-08~09-09</t>
         </is>
       </c>
       <c r="K54" s="6" t="inlineStr"/>
@@ -11590,22 +11659,18 @@
       <c r="M54" s="6" t="inlineStr"/>
       <c r="N54" s="6" t="inlineStr">
         <is>
-          <t>유진투자증권</t>
-        </is>
-      </c>
-      <c r="O54" s="6" t="inlineStr">
-        <is>
-          <t>미래</t>
-        </is>
-      </c>
+          <t>아이비케이투자증권</t>
+        </is>
+      </c>
+      <c r="O54" s="6" t="inlineStr"/>
       <c r="P54" s="7" t="inlineStr">
         <is>
-          <t>378,216,000</t>
+          <t>713,790,000</t>
         </is>
       </c>
       <c r="Q54" s="6" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
@@ -13026,22 +13091,150 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="20" t="inlineStr">
-        <is>
-          <t>※ 상장 완료 = KIND 신규상장 페이지 기준(스팩합병 포함) · 스팩 공모상장은 밴드·밸류에이션 등 해당없음(공모가 2,000원 고정).</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="20" t="inlineStr">
-        <is>
-          <t>※ 기재정정 신고서 내 정정 전·후 병존 → 자동수집은 "정정 후" 값만 취함.</t>
+    <row r="77" ht="30" customHeight="1">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>영광와이케이엠씨</t>
+        </is>
+      </c>
+      <c r="B77" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="C77" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="D77" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="E77" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="F77" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="G77" s="6" t="inlineStr"/>
+      <c r="H77" s="6" t="inlineStr"/>
+      <c r="I77" s="6" t="inlineStr"/>
+      <c r="J77" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="K77" s="6" t="inlineStr"/>
+      <c r="L77" s="6" t="inlineStr"/>
+      <c r="M77" s="6" t="inlineStr"/>
+      <c r="N77" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="O77" s="6" t="inlineStr"/>
+      <c r="P77" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="Q77" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="R77" s="6" t="inlineStr">
+        <is>
+          <t>신고서 대기</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="30" customHeight="1">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>동원파츠</t>
+        </is>
+      </c>
+      <c r="B78" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="C78" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="D78" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="E78" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="F78" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr"/>
+      <c r="H78" s="6" t="inlineStr"/>
+      <c r="I78" s="6" t="inlineStr"/>
+      <c r="J78" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="K78" s="6" t="inlineStr"/>
+      <c r="L78" s="6" t="inlineStr"/>
+      <c r="M78" s="6" t="inlineStr"/>
+      <c r="N78" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="O78" s="6" t="inlineStr"/>
+      <c r="P78" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="Q78" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="R78" s="6" t="inlineStr">
+        <is>
+          <t>신고서 대기</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="20" t="inlineStr">
+        <is>
+          <t>※ 상장 완료 = KIND 신규상장 페이지 기준(스팩합병 포함) · 스팩 공모상장은 밴드·밸류에이션 등 해당없음(공모가 2,000원 고정).</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="20" t="inlineStr">
+        <is>
+          <t>※ 기재정정 신고서 내 정정 전·후 병존 → 자동수집은 "정정 후" 값만 취함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="20" t="inlineStr">
         <is>
           <t>※ 청약경쟁률=일반투자자 청약수량÷최종배정수량 · "MM-DD~"는 종료일 자동수집 예정.</t>
         </is>
@@ -13318,10 +13511,10 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>0</v>
@@ -13510,30 +13703,30 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>NH투자증권</t>
+          <t>유진투자증권</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>43,600,000,000</t>
+          <t>45,600,000,000</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>유진투자증권</t>
+          <t>NH투자증권</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>40,800,000,000</t>
+          <t>43,600,000,000</t>
         </is>
       </c>
     </row>

--- a/IPO_analysis.xlsx
+++ b/IPO_analysis.xlsx
@@ -618,7 +618,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>기준일 2026-09-14 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
+          <t>기준일 2026-09-15 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
         </is>
       </c>
     </row>
@@ -11298,7 +11298,11 @@
           <t>09-10~09-11</t>
         </is>
       </c>
-      <c r="K49" s="6" t="inlineStr"/>
+      <c r="K49" s="6" t="inlineStr">
+        <is>
+          <t>4,885.53</t>
+        </is>
+      </c>
       <c r="L49" s="6" t="inlineStr"/>
       <c r="M49" s="6" t="inlineStr"/>
       <c r="N49" s="6" t="inlineStr">
@@ -11319,7 +11323,7 @@
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
-          <t>발행조건확정</t>
+          <t>청약완료·상장대기</t>
         </is>
       </c>
     </row>
@@ -11370,7 +11374,11 @@
           <t>09-10~09-11</t>
         </is>
       </c>
-      <c r="K50" s="6" t="inlineStr"/>
+      <c r="K50" s="6" t="inlineStr">
+        <is>
+          <t>6,777.78</t>
+        </is>
+      </c>
       <c r="L50" s="6" t="inlineStr"/>
       <c r="M50" s="6" t="inlineStr"/>
       <c r="N50" s="18" t="inlineStr">
@@ -11391,146 +11399,150 @@
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
-          <t>발행조건확정</t>
+          <t>청약완료·상장대기</t>
         </is>
       </c>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>와이즈플래닛컴퍼니</t>
+          <t>한국제17호스팩</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>09-04~09-10</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>10,000~12,000</t>
+          <t>09-07~09-08</t>
+        </is>
+      </c>
+      <c r="C51" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>1,600,000</t>
+          <t>7,000,000</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>19,200,000,000</t>
-        </is>
-      </c>
-      <c r="F51" s="6" t="inlineStr">
-        <is>
-          <t>20.04배 (PER)</t>
+          <t>14,000,000,000</t>
+        </is>
+      </c>
+      <c r="F51" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="H51" s="6" t="n">
-        <v>1248.47</v>
+        <v>1270.51</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>2323</v>
+        <v>2040</v>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
-          <t>09-14~09-15</t>
-        </is>
-      </c>
-      <c r="K51" s="6" t="inlineStr"/>
+          <t>09-10~09-11</t>
+        </is>
+      </c>
+      <c r="K51" s="6" t="inlineStr">
+        <is>
+          <t>8,291.55</t>
+        </is>
+      </c>
       <c r="L51" s="6" t="inlineStr"/>
       <c r="M51" s="6" t="inlineStr"/>
-      <c r="N51" s="6" t="inlineStr">
-        <is>
-          <t>대신증권</t>
+      <c r="N51" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="O51" s="6" t="inlineStr"/>
-      <c r="P51" s="7" t="inlineStr">
-        <is>
-          <t>494,400,000</t>
+      <c r="P51" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="Q51" s="6" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
-          <t>발행조건확정</t>
+          <t>청약완료·상장대기</t>
         </is>
       </c>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>한국제17호스팩</t>
+          <t>와이즈플래닛컴퍼니</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>09-07~09-08</t>
-        </is>
-      </c>
-      <c r="C52" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>09-04~09-10</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>10,000~12,000</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>7,000,000</t>
+          <t>1,600,000</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>14,000,000,000</t>
-        </is>
-      </c>
-      <c r="F52" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>19,200,000,000</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>20.04배 (PER)</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="H52" s="6" t="n">
-        <v>1270.51</v>
+        <v>1248.47</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>2040</v>
+        <v>2323</v>
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
-          <t>09-10~09-11</t>
+          <t>09-14~09-15</t>
         </is>
       </c>
       <c r="K52" s="6" t="inlineStr"/>
       <c r="L52" s="6" t="inlineStr"/>
       <c r="M52" s="6" t="inlineStr"/>
-      <c r="N52" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="N52" s="6" t="inlineStr">
+        <is>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="O52" s="6" t="inlineStr"/>
-      <c r="P52" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P52" s="7" t="inlineStr">
+        <is>
+          <t>494,400,000</t>
         </is>
       </c>
       <c r="Q52" s="6" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
@@ -11618,40 +11630,48 @@
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>브릴스</t>
+          <t>글로벌테크놀로지</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>08-31~09-04</t>
+          <t>09-07~09-11</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>16,500~19,500</t>
+          <t>13,000~15,000</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>1,200,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>19,800,000,000</t>
+          <t>40,000,000,000</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>13.44 (PSR)</t>
-        </is>
-      </c>
-      <c r="G54" s="6" t="inlineStr"/>
-      <c r="H54" s="6" t="inlineStr"/>
-      <c r="I54" s="6" t="inlineStr"/>
+          <t>19.22배 (PER)</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="n">
+        <v>123.19</v>
+      </c>
+      <c r="I54" s="6" t="n">
+        <v>961</v>
+      </c>
       <c r="J54" s="6" t="inlineStr">
         <is>
-          <t>09-08~09-09</t>
+          <t>09-16~09-17</t>
         </is>
       </c>
       <c r="K54" s="6" t="inlineStr"/>
@@ -11659,60 +11679,68 @@
       <c r="M54" s="6" t="inlineStr"/>
       <c r="N54" s="6" t="inlineStr">
         <is>
-          <t>아이비케이투자증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="O54" s="6" t="inlineStr"/>
       <c r="P54" s="7" t="inlineStr">
         <is>
-          <t>713,790,000</t>
-        </is>
-      </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>3.5%</t>
+          <t>2,119,999,960</t>
+        </is>
+      </c>
+      <c r="Q54" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>정정</t>
+          <t>발행조건확정</t>
         </is>
       </c>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>글로벌테크놀로지</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>09-07~09-11</t>
+          <t>09-08~09-14</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>13,000~15,000</t>
+          <t>12,400~14,600</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>52,000,000,000</t>
+          <t>43,800,000,000</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>19.22배 (PER)</t>
-        </is>
-      </c>
-      <c r="G55" s="6" t="inlineStr"/>
-      <c r="H55" s="6" t="inlineStr"/>
-      <c r="I55" s="6" t="inlineStr"/>
+          <t>32.57배 (PER)</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>14,600</t>
+        </is>
+      </c>
+      <c r="H55" s="6" t="n">
+        <v>868.64</v>
+      </c>
+      <c r="I55" s="6" t="n">
+        <v>2269</v>
+      </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
           <t>09-16~09-17</t>
@@ -11723,55 +11751,55 @@
       <c r="M55" s="6" t="inlineStr"/>
       <c r="N55" s="6" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="O55" s="6" t="inlineStr"/>
       <c r="P55" s="7" t="inlineStr">
         <is>
-          <t>2,119,999,960</t>
-        </is>
-      </c>
-      <c r="Q55" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>1,413,399,926</t>
+        </is>
+      </c>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>정정</t>
+          <t>발행조건확정</t>
         </is>
       </c>
     </row>
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>09-08~09-14</t>
+          <t>08-31~09-04</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>12,400~14,600</t>
+          <t>16,500~19,500</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>37,200,000,000</t>
+          <t>19,800,000,000</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>32.57배 (PER)</t>
+          <t>13.44 (PSR)</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr"/>
@@ -11779,7 +11807,7 @@
       <c r="I56" s="6" t="inlineStr"/>
       <c r="J56" s="6" t="inlineStr">
         <is>
-          <t>09-16~09-17</t>
+          <t>09-08~09-09</t>
         </is>
       </c>
       <c r="K56" s="6" t="inlineStr"/>
@@ -11787,18 +11815,18 @@
       <c r="M56" s="6" t="inlineStr"/>
       <c r="N56" s="6" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>아이비케이투자증권</t>
         </is>
       </c>
       <c r="O56" s="6" t="inlineStr"/>
       <c r="P56" s="7" t="inlineStr">
         <is>
-          <t>1,413,399,926</t>
+          <t>713,790,000</t>
         </is>
       </c>
       <c r="Q56" s="6" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
@@ -12390,32 +12418,32 @@
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>크리에이츠</t>
+          <t>다비오</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>10-12~10-16</t>
+          <t>10-07~10-14</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>15,000~18,000</t>
+          <t>12,300~16,600</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>1,400,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>21,000,000,000</t>
+          <t>12,300,000,000</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>19.15배 (PER)</t>
+          <t>26.70배 (PER)</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr"/>
@@ -12423,7 +12451,7 @@
       <c r="I66" s="6" t="inlineStr"/>
       <c r="J66" s="6" t="inlineStr">
         <is>
-          <t>10-20~10-21</t>
+          <t>10-19~10-20</t>
         </is>
       </c>
       <c r="K66" s="6" t="inlineStr"/>
@@ -12431,18 +12459,18 @@
       <c r="M66" s="6" t="inlineStr"/>
       <c r="N66" s="6" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="O66" s="6" t="inlineStr"/>
       <c r="P66" s="7" t="inlineStr">
         <is>
-          <t>865,200,000</t>
+          <t>570,105,000</t>
         </is>
       </c>
       <c r="Q66" s="6" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="R66" s="6" t="inlineStr">
@@ -12454,59 +12482,59 @@
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>바로팜</t>
-        </is>
-      </c>
-      <c r="B67" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>크리에이츠</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>10-12~10-16</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>16,400~20,200</t>
+          <t>15,000~18,000</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>1,780,000</t>
+          <t>1,400,000</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>29,192,000,000</t>
+          <t>21,000,000,000</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>24.95배 (PER)</t>
+          <t>19.15배 (PER)</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr"/>
       <c r="H67" s="6" t="inlineStr"/>
       <c r="I67" s="6" t="inlineStr"/>
-      <c r="J67" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="J67" s="6" t="inlineStr">
+        <is>
+          <t>10-20~10-21</t>
         </is>
       </c>
       <c r="K67" s="6" t="inlineStr"/>
       <c r="L67" s="6" t="inlineStr"/>
       <c r="M67" s="6" t="inlineStr"/>
-      <c r="N67" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="N67" s="6" t="inlineStr">
+        <is>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="O67" s="6" t="inlineStr"/>
-      <c r="P67" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="Q67" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P67" s="7" t="inlineStr">
+        <is>
+          <t>865,200,000</t>
+        </is>
+      </c>
+      <c r="Q67" s="6" t="inlineStr">
+        <is>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="R67" s="6" t="inlineStr">
@@ -12518,7 +12546,7 @@
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>디티에스</t>
+          <t>바로팜</t>
         </is>
       </c>
       <c r="B68" s="18" t="inlineStr">
@@ -12526,24 +12554,24 @@
           <t>수집예정</t>
         </is>
       </c>
-      <c r="C68" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="D68" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="E68" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="F68" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>16,400~20,200</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>1,780,000</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>29,192,000,000</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>24.95배 (PER)</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr"/>
@@ -12575,14 +12603,14 @@
       </c>
       <c r="R68" s="6" t="inlineStr">
         <is>
-          <t>신고서 대기</t>
+          <t>최초</t>
         </is>
       </c>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>한화플러스제6호스팩</t>
+          <t>디티에스</t>
         </is>
       </c>
       <c r="B69" s="18" t="inlineStr">
@@ -12646,7 +12674,7 @@
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>다비오</t>
+          <t>한화플러스제6호스팩</t>
         </is>
       </c>
       <c r="B70" s="18" t="inlineStr">
@@ -13628,7 +13656,7 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
@@ -13636,22 +13664,22 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>122,800,000,000</t>
+          <t>122,050,000,000</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>103,150,000,000</t>
+          <t>110,800,000,000</t>
         </is>
       </c>
     </row>

--- a/IPO_analysis.xlsx
+++ b/IPO_analysis.xlsx
@@ -618,7 +618,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>기준일 2026-09-15 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
+          <t>기준일 2026-09-16 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
         </is>
       </c>
     </row>
@@ -11482,48 +11482,48 @@
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>와이즈플래닛컴퍼니</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>09-04~09-10</t>
+          <t>08-31~09-04</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>10,000~12,000</t>
+          <t>16,500~19,500</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>1,600,000</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>19,200,000,000</t>
+          <t>23,400,000,000</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>20.04배 (PER)</t>
+          <t>13.44 (PSR)</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>19,500</t>
         </is>
       </c>
       <c r="H52" s="6" t="n">
-        <v>1248.47</v>
+        <v>1187.74</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>2323</v>
+        <v>2181</v>
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
-          <t>09-14~09-15</t>
+          <t>09-08~09-09</t>
         </is>
       </c>
       <c r="K52" s="6" t="inlineStr"/>
@@ -11531,18 +11531,18 @@
       <c r="M52" s="6" t="inlineStr"/>
       <c r="N52" s="6" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>아이비케이투자증권</t>
         </is>
       </c>
       <c r="O52" s="6" t="inlineStr"/>
       <c r="P52" s="7" t="inlineStr">
         <is>
-          <t>494,400,000</t>
+          <t>713,790,000</t>
         </is>
       </c>
       <c r="Q52" s="6" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
@@ -11554,17 +11554,17 @@
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>빅웨이브로보틱스</t>
+          <t>와이즈플래닛컴퍼니</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>09-07~09-11</t>
+          <t>09-04~09-10</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>15,000~18,000</t>
+          <t>10,000~12,000</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
@@ -11574,28 +11574,28 @@
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>28,800,000,000</t>
+          <t>19,200,000,000</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>11.15 (PSR)</t>
+          <t>20.04배 (PER)</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>18,000</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="H53" s="6" t="n">
-        <v>1109.37</v>
+        <v>1248.47</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>2255</v>
+        <v>2323</v>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>09-15~09-16</t>
+          <t>09-14~09-15</t>
         </is>
       </c>
       <c r="K53" s="6" t="inlineStr"/>
@@ -11603,17 +11603,13 @@
       <c r="M53" s="6" t="inlineStr"/>
       <c r="N53" s="6" t="inlineStr">
         <is>
-          <t>유진투자증권</t>
-        </is>
-      </c>
-      <c r="O53" s="6" t="inlineStr">
-        <is>
-          <t>미래</t>
-        </is>
-      </c>
+          <t>대신증권</t>
+        </is>
+      </c>
+      <c r="O53" s="6" t="inlineStr"/>
       <c r="P53" s="7" t="inlineStr">
         <is>
-          <t>378,216,000</t>
+          <t>494,400,000</t>
         </is>
       </c>
       <c r="Q53" s="6" t="inlineStr">
@@ -11630,7 +11626,7 @@
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>글로벌테크놀로지</t>
+          <t>빅웨이브로보틱스</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
@@ -11640,38 +11636,38 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>13,000~15,000</t>
+          <t>15,000~18,000</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>1,600,000</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>40,000,000,000</t>
+          <t>28,800,000,000</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>19.22배 (PER)</t>
+          <t>11.15 (PSR)</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>18,000</t>
         </is>
       </c>
       <c r="H54" s="6" t="n">
-        <v>123.19</v>
+        <v>1109.37</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>961</v>
+        <v>2255</v>
       </c>
       <c r="J54" s="6" t="inlineStr">
         <is>
-          <t>09-16~09-17</t>
+          <t>09-15~09-16</t>
         </is>
       </c>
       <c r="K54" s="6" t="inlineStr"/>
@@ -11679,18 +11675,22 @@
       <c r="M54" s="6" t="inlineStr"/>
       <c r="N54" s="6" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
-        </is>
-      </c>
-      <c r="O54" s="6" t="inlineStr"/>
+          <t>유진투자증권</t>
+        </is>
+      </c>
+      <c r="O54" s="6" t="inlineStr">
+        <is>
+          <t>미래</t>
+        </is>
+      </c>
       <c r="P54" s="7" t="inlineStr">
         <is>
-          <t>2,119,999,960</t>
-        </is>
-      </c>
-      <c r="Q54" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>378,216,000</t>
+        </is>
+      </c>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
@@ -11702,44 +11702,44 @@
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>글로벌테크놀로지</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>09-08~09-14</t>
+          <t>09-07~09-11</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>12,400~14,600</t>
+          <t>13,000~15,000</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>43,800,000,000</t>
+          <t>40,000,000,000</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>32.57배 (PER)</t>
+          <t>19.22배 (PER)</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>14,600</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="H55" s="6" t="n">
-        <v>868.64</v>
+        <v>123.19</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>2269</v>
+        <v>961</v>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
@@ -11751,18 +11751,18 @@
       <c r="M55" s="6" t="inlineStr"/>
       <c r="N55" s="6" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="O55" s="6" t="inlineStr"/>
       <c r="P55" s="7" t="inlineStr">
         <is>
-          <t>1,413,399,926</t>
-        </is>
-      </c>
-      <c r="Q55" s="6" t="inlineStr">
-        <is>
-          <t>3.7%</t>
+          <t>2,119,999,960</t>
+        </is>
+      </c>
+      <c r="Q55" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
@@ -11774,40 +11774,48 @@
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>브릴스</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>08-31~09-04</t>
+          <t>09-08~09-14</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>16,500~19,500</t>
+          <t>12,400~14,600</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>1,200,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>19,800,000,000</t>
+          <t>43,800,000,000</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>13.44 (PSR)</t>
-        </is>
-      </c>
-      <c r="G56" s="6" t="inlineStr"/>
-      <c r="H56" s="6" t="inlineStr"/>
-      <c r="I56" s="6" t="inlineStr"/>
+          <t>32.57배 (PER)</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>14,600</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="n">
+        <v>868.64</v>
+      </c>
+      <c r="I56" s="6" t="n">
+        <v>2269</v>
+      </c>
       <c r="J56" s="6" t="inlineStr">
         <is>
-          <t>09-08~09-09</t>
+          <t>09-16~09-17</t>
         </is>
       </c>
       <c r="K56" s="6" t="inlineStr"/>
@@ -11815,23 +11823,23 @@
       <c r="M56" s="6" t="inlineStr"/>
       <c r="N56" s="6" t="inlineStr">
         <is>
-          <t>아이비케이투자증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="O56" s="6" t="inlineStr"/>
       <c r="P56" s="7" t="inlineStr">
         <is>
-          <t>713,790,000</t>
+          <t>1,413,399,926</t>
         </is>
       </c>
       <c r="Q56" s="6" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>정정</t>
+          <t>발행조건확정</t>
         </is>
       </c>
     </row>
@@ -12546,59 +12554,59 @@
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>바로팜</t>
-        </is>
-      </c>
-      <c r="B68" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>인텔리빅스</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>10-12~10-16</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>16,400~20,200</t>
+          <t>7,600~9,000</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>1,780,000</t>
+          <t>2,500,000</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>29,192,000,000</t>
+          <t>19,000,000,000</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>24.95배 (PER)</t>
+          <t>22.02배 (PER)</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr"/>
       <c r="H68" s="6" t="inlineStr"/>
       <c r="I68" s="6" t="inlineStr"/>
-      <c r="J68" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="J68" s="6" t="inlineStr">
+        <is>
+          <t>10-21~10-22</t>
         </is>
       </c>
       <c r="K68" s="6" t="inlineStr"/>
       <c r="L68" s="6" t="inlineStr"/>
       <c r="M68" s="6" t="inlineStr"/>
-      <c r="N68" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="N68" s="6" t="inlineStr">
+        <is>
+          <t>미래에셋증권</t>
         </is>
       </c>
       <c r="O68" s="6" t="inlineStr"/>
-      <c r="P68" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="Q68" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P68" s="7" t="inlineStr">
+        <is>
+          <t>782,800,000</t>
+        </is>
+      </c>
+      <c r="Q68" s="6" t="inlineStr">
+        <is>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="R68" s="6" t="inlineStr">
@@ -12610,7 +12618,7 @@
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>디티에스</t>
+          <t>바로팜</t>
         </is>
       </c>
       <c r="B69" s="18" t="inlineStr">
@@ -12618,24 +12626,24 @@
           <t>수집예정</t>
         </is>
       </c>
-      <c r="C69" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="D69" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="E69" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="F69" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>16,400~20,200</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>1,780,000</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>29,192,000,000</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>24.95배 (PER)</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr"/>
@@ -12667,14 +12675,14 @@
       </c>
       <c r="R69" s="6" t="inlineStr">
         <is>
-          <t>신고서 대기</t>
+          <t>최초</t>
         </is>
       </c>
     </row>
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>한화플러스제6호스팩</t>
+          <t>디티에스</t>
         </is>
       </c>
       <c r="B70" s="18" t="inlineStr">
@@ -12738,7 +12746,7 @@
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>하나에어로다이내믹스</t>
+          <t>한화플러스제6호스팩</t>
         </is>
       </c>
       <c r="B71" s="18" t="inlineStr">
@@ -12802,7 +12810,7 @@
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>에이엔에이치스트럭쳐</t>
+          <t>하나에어로다이내믹스</t>
         </is>
       </c>
       <c r="B72" s="18" t="inlineStr">
@@ -12866,7 +12874,7 @@
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>인텔리빅스</t>
+          <t>에이엔에이치스트럭쳐</t>
         </is>
       </c>
       <c r="B73" s="18" t="inlineStr">
@@ -13671,30 +13679,30 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>미래에셋증권</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>110,800,000,000</t>
+          <t>115,560,000,000</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>미래에셋증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>96,560,000,000</t>
+          <t>110,800,000,000</t>
         </is>
       </c>
     </row>
@@ -13709,7 +13717,7 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>72,600,000,000</t>
+          <t>76,200,000,000</t>
         </is>
       </c>
     </row>

--- a/IPO_analysis.xlsx
+++ b/IPO_analysis.xlsx
@@ -592,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K136"/>
+  <dimension ref="A1:K137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -618,14 +618,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>기준일 2026-09-16 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
+          <t>기준일 2026-09-17 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>■ 심사 신청(진행중)  (45건)</t>
+          <t>■ 심사 신청(진행중)  (44건)</t>
         </is>
       </c>
       <c r="B4" s="4" t="n"/>
@@ -699,12 +699,12 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>(주)태석광학</t>
+          <t>노바셀테크놀로지</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -724,27 +724,27 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>79,804</t>
+          <t>377</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>4,721</t>
+          <t>-4,606</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>7,228</t>
+          <t>-15,458</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>생활용품 도매업</t>
+          <t>자연과학 및 공학 연구개발업</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>신한, 대신</t>
+          <t>키움</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
@@ -756,12 +756,12 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>엑티브온</t>
+          <t>(주)태석광학</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -779,17 +779,29 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr"/>
-      <c r="G7" s="7" t="inlineStr"/>
-      <c r="H7" s="7" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr">
+        <is>
+          <t>79,804</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="inlineStr">
+        <is>
+          <t>4,721</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>7,228</t>
+        </is>
+      </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>생활용품 도매업</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>키움</t>
+          <t>신한, 대신</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
@@ -801,12 +813,12 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>씨앤엠</t>
+          <t>엑티브온</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -816,7 +828,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -824,29 +836,17 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>238,489</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>19,869</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>112,262</t>
-        </is>
-      </c>
+      <c r="F8" s="7" t="inlineStr"/>
+      <c r="G8" s="7" t="inlineStr"/>
+      <c r="H8" s="7" t="inlineStr"/>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>전동기, 발전기 및 전기 변환 · 공급 · 제어 장치 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>키움</t>
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr">
@@ -858,17 +858,17 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>무신사</t>
+          <t>씨앤엠</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>유가</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
@@ -883,27 +883,27 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>1,352,930</t>
+          <t>238,489</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>-10,571</t>
+          <t>19,869</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>243,731</t>
+          <t>112,262</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>섬유, 의복, 신발 및 가죽제품 소매업</t>
+          <t>전동기, 발전기 및 전기 변환 · 공급 · 제어 장치 제조업</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>한국, 씨티그룹글로벌마켓증권(주), KB, 제이피모간증권회사 서울지점</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
@@ -915,17 +915,17 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>마더스제약</t>
+          <t>무신사</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>유가</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
@@ -940,27 +940,27 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>228,830</t>
+          <t>1,352,930</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>11,204</t>
+          <t>-10,571</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>57,394</t>
+          <t>243,731</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>의약품 제조업</t>
+          <t>섬유, 의복, 신발 및 가죽제품 소매업</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>NH, KB</t>
+          <t>한국, 씨티그룹글로벌마켓증권(주), KB, 제이피모간증권회사 서울지점</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>이나인페이</t>
+          <t>마더스제약</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -997,27 +997,27 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>64,711</t>
+          <t>228,830</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>19,586</t>
+          <t>11,204</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>79,855</t>
+          <t>57,394</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>의약품 제조업</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>NH, KB</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
@@ -1029,12 +1029,12 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>어피닛</t>
+          <t>이나인페이</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -1054,27 +1054,27 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>169,126</t>
+          <t>64,711</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>26,009</t>
+          <t>19,586</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>61,466</t>
+          <t>79,855</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>미래, 하나</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
@@ -1086,12 +1086,12 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>라이드플럭스</t>
+          <t>어피닛</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1111,17 +1111,17 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>4,044</t>
+          <t>169,126</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>-31,423</t>
+          <t>26,009</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>-77,243</t>
+          <t>61,466</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>주식회사 우리투자증권, 한국</t>
+          <t>미래, 하나</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
@@ -1143,12 +1143,12 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>신영스팩12호</t>
+          <t>라이드플럭스</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -1166,17 +1166,29 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr"/>
-      <c r="G14" s="7" t="inlineStr"/>
-      <c r="H14" s="7" t="inlineStr"/>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>4,044</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>-31,423</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>-77,243</t>
+        </is>
+      </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>신영</t>
+          <t>주식회사 우리투자증권, 한국</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
@@ -1188,12 +1200,12 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>우리투자제1호스팩</t>
+          <t>신영스팩12호</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -1216,12 +1228,12 @@
       <c r="H15" s="7" t="inlineStr"/>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>주식회사 우리투자증권</t>
+          <t>신영</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
@@ -1233,17 +1245,17 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>에스텍시스템</t>
+          <t>우리투자제1호스팩</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>유가</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
@@ -1256,29 +1268,17 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>975,224</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>24,647</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>237,182</t>
-        </is>
-      </c>
+      <c r="F16" s="7" t="inlineStr"/>
+      <c r="G16" s="7" t="inlineStr"/>
+      <c r="H16" s="7" t="inlineStr"/>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>경비, 경호 및 탐정업</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>주식회사 우리투자증권</t>
         </is>
       </c>
       <c r="K16" s="6" t="inlineStr">
@@ -1290,17 +1290,17 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>범한메카텍</t>
+          <t>에스텍시스템</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>유가</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -1315,27 +1315,27 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>339,209</t>
+          <t>975,224</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>-18,141</t>
+          <t>24,647</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>265,955</t>
+          <t>237,182</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
+          <t>경비, 경호 및 탐정업</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>유진, NH</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>케이티이</t>
+          <t>범한메카텍</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -1372,27 +1372,27 @@
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>173,901</t>
+          <t>339,209</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>14,243</t>
+          <t>-18,141</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>94,928</t>
+          <t>265,955</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>전동기, 발전기 및 전기 변환 · 공급 · 제어 장치 제조업</t>
+          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>유진, NH</t>
         </is>
       </c>
       <c r="K18" s="6" t="inlineStr">
@@ -1404,12 +1404,12 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>데스틴파워</t>
+          <t>케이티이</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>29,851</t>
+          <t>173,901</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>5,852</t>
+          <t>14,243</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>-30,114</t>
+          <t>94,928</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>유림테크</t>
+          <t>데스틴파워</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -1486,27 +1486,27 @@
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>102,586</t>
+          <t>29,851</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>-18,278</t>
+          <t>5,852</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>-4,832</t>
+          <t>-30,114</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>자동차 신품 부품 제조업</t>
+          <t>전동기, 발전기 및 전기 변환 · 공급 · 제어 장치 제조업</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K20" s="6" t="inlineStr">
@@ -1518,12 +1518,12 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>솔리스</t>
+          <t>유림테크</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
@@ -1541,17 +1541,29 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F21" s="7" t="inlineStr"/>
-      <c r="G21" s="7" t="inlineStr"/>
-      <c r="H21" s="7" t="inlineStr"/>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>102,586</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="inlineStr">
+        <is>
+          <t>-18,278</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>-4,832</t>
+        </is>
+      </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>자동차 신품 부품 제조업</t>
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>한화</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
@@ -1568,7 +1580,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>이노보테라퓨틱스</t>
+          <t>솔리스</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1578,7 +1590,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -1586,29 +1598,17 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>-5,429</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>-53,200</t>
-        </is>
-      </c>
+      <c r="F22" s="7" t="inlineStr"/>
+      <c r="G22" s="7" t="inlineStr"/>
+      <c r="H22" s="7" t="inlineStr"/>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>의약품 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>한화</t>
         </is>
       </c>
       <c r="K22" s="6" t="inlineStr">
@@ -1620,17 +1620,17 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>에스에프씨</t>
+          <t>이노보테라퓨틱스</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>유가</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
@@ -1645,27 +1645,27 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>160,792</t>
+          <t>209</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>25,509</t>
+          <t>-5,429</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>243,562</t>
+          <t>-53,200</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>의약품 제조업</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>미래, 한국</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
@@ -1677,17 +1677,17 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>제논</t>
+          <t>에스에프씨</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>유가</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
@@ -1702,27 +1702,27 @@
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>11,744</t>
+          <t>160,792</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>1,139</t>
+          <t>25,509</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>-1,220</t>
+          <t>243,562</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>미래, 한국</t>
         </is>
       </c>
       <c r="K24" s="6" t="inlineStr">
@@ -1734,12 +1734,12 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>넥스아이</t>
+          <t>제논</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -1759,27 +1759,27 @@
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>5,110</t>
+          <t>11,744</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>-52,331</t>
+          <t>1,139</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>-82,348</t>
+          <t>-1,220</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>의약품 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
@@ -2760,12 +2760,12 @@
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>케이엠에프</t>
+          <t>삼홍아크튜리온</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -2785,27 +2785,27 @@
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>25,751</t>
+          <t>26,162</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>11,463</t>
+          <t>-10,314</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>6,369</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>기타 식품 제조업</t>
+          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
         </is>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>IBK</t>
+          <t>삼성, 미래</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
@@ -2817,12 +2817,12 @@
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>삼홍아크튜리온</t>
+          <t>넥스트에어로스페이스</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -2842,27 +2842,27 @@
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>26,162</t>
+          <t>12,084</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>-10,314</t>
+          <t>-17,270</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>6,369</t>
+          <t>6,158</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
+          <t>유인 항공기, 항공우주선 및 보조장치 제조업</t>
         </is>
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>삼성, 미래</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K44" s="6" t="inlineStr">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>넥스트에어로스페이스</t>
+          <t>비앤비코리아</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -2899,27 +2899,27 @@
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>12,084</t>
+          <t>141,169</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>-17,270</t>
+          <t>21,406</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>6,158</t>
+          <t>43,932</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>유인 항공기, 항공우주선 및 보조장치 제조업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K45" s="6" t="inlineStr">
@@ -2931,12 +2931,12 @@
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>비앤비코리아</t>
+          <t>오토핸즈</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -2956,22 +2956,22 @@
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>141,169</t>
+          <t>238,564</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>21,406</t>
+          <t>6,047</t>
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>43,932</t>
+          <t>6,129</t>
         </is>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>자동차 판매업</t>
         </is>
       </c>
       <c r="J46" s="6" t="inlineStr">
@@ -2988,12 +2988,12 @@
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>오토핸즈</t>
+          <t>아이벡스메디칼시스템즈</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
@@ -3013,27 +3013,27 @@
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>238,564</t>
+          <t>15,282</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>6,047</t>
+          <t>-7,227</t>
         </is>
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>6,129</t>
+          <t>744</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>자동차 판매업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K47" s="6" t="inlineStr">
@@ -3045,12 +3045,12 @@
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>아이벡스메디칼시스템즈</t>
+          <t>옵토닉스</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -3070,27 +3070,27 @@
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>15,282</t>
+          <t>25,368</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>-7,227</t>
+          <t>1,901</t>
         </is>
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>730</t>
         </is>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>광학렌즈 및 광학요소 제조업</t>
         </is>
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K48" s="6" t="inlineStr">
@@ -3102,12 +3102,12 @@
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>옵토닉스</t>
+          <t>피지티</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -3127,22 +3127,22 @@
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>25,368</t>
+          <t>40,141</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>1,901</t>
+          <t>-69,722</t>
         </is>
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>6,029</t>
         </is>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>광학렌즈 및 광학요소 제조업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="J49" s="6" t="inlineStr">
@@ -3156,146 +3156,146 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>피지티</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>■ 심사 승인  (64건)</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="n"/>
+      <c r="C51" s="4" t="n"/>
+      <c r="D51" s="4" t="n"/>
+      <c r="E51" s="4" t="n"/>
+      <c r="F51" s="4" t="n"/>
+      <c r="G51" s="4" t="n"/>
+      <c r="H51" s="4" t="n"/>
+      <c r="I51" s="4" t="n"/>
+      <c r="J51" s="4" t="n"/>
+      <c r="K51" s="4" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>일자</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>회사명</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>시장</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>상장유형</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>기준연도</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>자기자본</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>업종</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>대표주관사</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>현황</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>케이엠에프</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
         <is>
           <t>코스닥</t>
         </is>
       </c>
-      <c r="D50" s="6" t="inlineStr">
+      <c r="D53" s="6" t="inlineStr">
         <is>
           <t>신규상장</t>
         </is>
       </c>
-      <c r="E50" s="6" t="inlineStr">
+      <c r="E53" s="6" t="inlineStr">
         <is>
           <t>FY25</t>
         </is>
       </c>
-      <c r="F50" s="7" t="inlineStr">
-        <is>
-          <t>40,141</t>
-        </is>
-      </c>
-      <c r="G50" s="7" t="inlineStr">
-        <is>
-          <t>-69,722</t>
-        </is>
-      </c>
-      <c r="H50" s="7" t="inlineStr">
-        <is>
-          <t>6,029</t>
-        </is>
-      </c>
-      <c r="I50" s="6" t="inlineStr">
-        <is>
-          <t>기타 화학제품 제조업</t>
-        </is>
-      </c>
-      <c r="J50" s="6" t="inlineStr">
-        <is>
-          <t>한국</t>
-        </is>
-      </c>
-      <c r="K50" s="6" t="inlineStr">
-        <is>
-          <t>예심 진행중</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>■ 심사 승인  (62건)</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="n"/>
-      <c r="C52" s="4" t="n"/>
-      <c r="D52" s="4" t="n"/>
-      <c r="E52" s="4" t="n"/>
-      <c r="F52" s="4" t="n"/>
-      <c r="G52" s="4" t="n"/>
-      <c r="H52" s="4" t="n"/>
-      <c r="I52" s="4" t="n"/>
-      <c r="J52" s="4" t="n"/>
-      <c r="K52" s="4" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="5" t="inlineStr">
-        <is>
-          <t>일자</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>회사명</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>시장</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>상장유형</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t>기준연도</t>
-        </is>
-      </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="G53" s="5" t="inlineStr">
-        <is>
-          <t>순이익</t>
-        </is>
-      </c>
-      <c r="H53" s="5" t="inlineStr">
-        <is>
-          <t>자기자본</t>
-        </is>
-      </c>
-      <c r="I53" s="5" t="inlineStr">
-        <is>
-          <t>업종</t>
-        </is>
-      </c>
-      <c r="J53" s="5" t="inlineStr">
-        <is>
-          <t>대표주관사</t>
-        </is>
-      </c>
-      <c r="K53" s="5" t="inlineStr">
-        <is>
-          <t>현황</t>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>25,751</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>11,463</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>기타 식품 제조업</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>IBK</t>
+        </is>
+      </c>
+      <c r="K53" s="6" t="inlineStr">
+        <is>
+          <t>상장전</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>영광와이케이엠씨</t>
+          <t>넥스아이</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
@@ -3315,27 +3315,27 @@
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>51,609</t>
+          <t>5,110</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>2,708</t>
+          <t>-52,331</t>
         </is>
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>28,213</t>
+          <t>-82,348</t>
         </is>
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
-          <t>기타 금속 가공제품 제조업</t>
+          <t>의약품 제조업</t>
         </is>
       </c>
       <c r="J54" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K54" s="6" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>동원파츠</t>
+          <t>영광와이케이엠씨</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -3372,27 +3372,27 @@
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>92,255</t>
+          <t>51,609</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>3,443</t>
+          <t>2,708</t>
         </is>
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
-          <t>27,535</t>
+          <t>28,213</t>
         </is>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>기타 금속 가공제품 제조업</t>
         </is>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K55" s="6" t="inlineStr">
@@ -3404,12 +3404,12 @@
     <row r="56">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>이에스티</t>
+          <t>동원파츠</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
@@ -3429,17 +3429,17 @@
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>33,190</t>
+          <t>92,255</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>2,966</t>
+          <t>3,443</t>
         </is>
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>4,325</t>
+          <t>27,535</t>
         </is>
       </c>
       <c r="I56" s="6" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="J56" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K56" s="6" t="inlineStr">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>에이엘로봇</t>
+          <t>이에스티</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -3486,22 +3486,22 @@
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>14,985</t>
+          <t>33,190</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>-21,891</t>
+          <t>2,966</t>
         </is>
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>4,325</t>
         </is>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
-          <t>산업용 로봇 제조업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="J57" s="6" t="inlineStr">
@@ -3518,12 +3518,12 @@
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>아이엠스팩1호</t>
+          <t>에이엘로봇</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
@@ -3541,17 +3541,29 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F58" s="7" t="inlineStr"/>
-      <c r="G58" s="7" t="inlineStr"/>
-      <c r="H58" s="7" t="inlineStr"/>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>14,985</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>-21,891</t>
+        </is>
+      </c>
+      <c r="H58" s="7" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>산업용 로봇 제조업</t>
         </is>
       </c>
       <c r="J58" s="6" t="inlineStr">
         <is>
-          <t>iM증권</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K58" s="6" t="inlineStr">
@@ -3563,12 +3575,12 @@
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>에이엔에이치스트럭쳐</t>
+          <t>아이엠스팩1호</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
@@ -3586,29 +3598,17 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F59" s="7" t="inlineStr">
-        <is>
-          <t>19,784</t>
-        </is>
-      </c>
-      <c r="G59" s="7" t="inlineStr">
-        <is>
-          <t>-4,296</t>
-        </is>
-      </c>
-      <c r="H59" s="7" t="inlineStr">
-        <is>
-          <t>24,561</t>
-        </is>
-      </c>
+      <c r="F59" s="7" t="inlineStr"/>
+      <c r="G59" s="7" t="inlineStr"/>
+      <c r="H59" s="7" t="inlineStr"/>
       <c r="I59" s="6" t="inlineStr">
         <is>
-          <t>건축기술, 엔지니어링 및 관련 기술 서비스업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>iM증권</t>
         </is>
       </c>
       <c r="K59" s="6" t="inlineStr">
@@ -3625,7 +3625,7 @@
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>인텔리빅스</t>
+          <t>에이엔에이치스트럭쳐</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
@@ -3645,27 +3645,27 @@
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>46,644</t>
+          <t>19,784</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>5,357</t>
+          <t>-4,296</t>
         </is>
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
-          <t>1,048</t>
+          <t>24,561</t>
         </is>
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>건축기술, 엔지니어링 및 관련 기술 서비스업</t>
         </is>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K60" s="6" t="inlineStr">
@@ -3677,12 +3677,12 @@
     <row r="61">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>하나에어로다이내믹스</t>
+          <t>인텔리빅스</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
@@ -3702,27 +3702,27 @@
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>33,286</t>
+          <t>46,644</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>2,420</t>
+          <t>5,357</t>
         </is>
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>1,048</t>
         </is>
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
-          <t>항공기,우주선 및 부품 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
-          <t>IBK</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K61" s="6" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>다비오</t>
+          <t>하나에어로다이내믹스</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
@@ -3759,27 +3759,27 @@
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>9,251</t>
+          <t>33,286</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>-3,473</t>
+          <t>2,420</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>890</t>
         </is>
       </c>
       <c r="I62" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>항공기,우주선 및 부품 제조업</t>
         </is>
       </c>
       <c r="J62" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>IBK</t>
         </is>
       </c>
       <c r="K62" s="6" t="inlineStr">
@@ -3791,12 +3791,12 @@
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>티앤이코리아</t>
+          <t>다비오</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
@@ -3816,27 +3816,27 @@
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>22,339</t>
+          <t>9,251</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>-7,091</t>
+          <t>-3,473</t>
         </is>
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
-          <t>일반 목적용 기계 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
-          <t>신한</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K63" s="6" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>유캐스트</t>
+          <t>티앤이코리아</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
@@ -3873,27 +3873,27 @@
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>5,934</t>
+          <t>22,339</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>-3,557</t>
+          <t>-7,091</t>
         </is>
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>1,881</t>
+          <t>481</t>
         </is>
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
-          <t>통신 및 방송 장비 제조업</t>
+          <t>일반 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="J64" s="6" t="inlineStr">
         <is>
-          <t>유진</t>
+          <t>신한</t>
         </is>
       </c>
       <c r="K64" s="6" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>엘리스그룹</t>
+          <t>유캐스트</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
@@ -3930,27 +3930,27 @@
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>39,513</t>
+          <t>5,934</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>15,666</t>
+          <t>-3,557</t>
         </is>
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
-          <t>85,400</t>
+          <t>1,881</t>
         </is>
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>통신 및 방송 장비 제조업</t>
         </is>
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
-          <t>미래, 삼성</t>
+          <t>유진</t>
         </is>
       </c>
       <c r="K65" s="6" t="inlineStr">
@@ -3962,12 +3962,12 @@
     <row r="66">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>엘리스그룹</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="D66" s="6" t="inlineStr">
         <is>
-          <t>이전상장</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
@@ -3987,27 +3987,27 @@
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>48,646</t>
+          <t>39,513</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>6,017</t>
+          <t>15,666</t>
         </is>
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
-          <t>18,795</t>
+          <t>85,400</t>
         </is>
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J66" s="6" t="inlineStr">
         <is>
-          <t>하나</t>
+          <t>미래, 삼성</t>
         </is>
       </c>
       <c r="K66" s="6" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>바로팜</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
@@ -4034,7 +4034,7 @@
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>이전상장</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
@@ -4044,27 +4044,27 @@
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>96,724</t>
+          <t>48,646</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>-9,679</t>
+          <t>6,017</t>
         </is>
       </c>
       <c r="H67" s="7" t="inlineStr">
         <is>
-          <t>30,673</t>
+          <t>18,795</t>
         </is>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
-          <t>상품 중개업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>하나</t>
         </is>
       </c>
       <c r="K67" s="6" t="inlineStr">
@@ -4081,7 +4081,7 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>크리에이츠</t>
+          <t>바로팜</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
@@ -4101,27 +4101,27 @@
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>76,395</t>
+          <t>96,724</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>23,749</t>
+          <t>-9,679</t>
         </is>
       </c>
       <c r="H68" s="7" t="inlineStr">
         <is>
-          <t>2,335</t>
+          <t>30,673</t>
         </is>
       </c>
       <c r="I68" s="6" t="inlineStr">
         <is>
-          <t>그외 기타 제품 제조업</t>
+          <t>상품 중개업</t>
         </is>
       </c>
       <c r="J68" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K68" s="6" t="inlineStr">
@@ -4133,12 +4133,12 @@
     <row r="69">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>래블업</t>
+          <t>크리에이츠</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
@@ -4158,27 +4158,27 @@
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>6,712</t>
+          <t>76,395</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>-1,526</t>
+          <t>23,749</t>
         </is>
       </c>
       <c r="H69" s="7" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>2,335</t>
         </is>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
-          <t>데이터베이스 및 온라인정보 제공업</t>
+          <t>그외 기타 제품 제조업</t>
         </is>
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K69" s="6" t="inlineStr">
@@ -4195,7 +4195,7 @@
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>래블업</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
@@ -4215,27 +4215,27 @@
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>39,319</t>
+          <t>6,712</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>4,739</t>
+          <t>-1,526</t>
         </is>
       </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
-          <t>1,250</t>
+          <t>373</t>
         </is>
       </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>데이터베이스 및 온라인정보 제공업</t>
         </is>
       </c>
       <c r="J70" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K70" s="6" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>엠비디</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
@@ -4272,27 +4272,27 @@
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>1,524</t>
+          <t>39,319</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>-2,125</t>
+          <t>4,739</t>
         </is>
       </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
-          <t>2,753</t>
+          <t>1,250</t>
         </is>
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
-          <t>물질 검사, 측정 및 분석기구 제조업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>하나</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K71" s="6" t="inlineStr">
@@ -4304,12 +4304,12 @@
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>에스케이증권제14호기업인수목적</t>
+          <t>엠비디</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
@@ -4329,27 +4329,27 @@
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,524</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-2,125</t>
         </is>
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2,753</t>
         </is>
       </c>
       <c r="I72" s="6" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>물질 검사, 측정 및 분석기구 제조업</t>
         </is>
       </c>
       <c r="J72" s="6" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>하나</t>
         </is>
       </c>
       <c r="K72" s="6" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>케이비제34호스팩</t>
+          <t>에스케이증권제14호기업인수목적</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I73" s="6" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="K73" s="6" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>한국제17호스팩</t>
+          <t>케이비제34호스팩</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="H74" s="7" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I74" s="6" t="inlineStr">
@@ -4463,7 +4463,7 @@
       </c>
       <c r="J74" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="K74" s="6" t="inlineStr">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>한화플러스제6호스팩</t>
+          <t>한국제17호스팩</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="H75" s="7" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I75" s="6" t="inlineStr">
@@ -4520,7 +4520,7 @@
       </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
-          <t>한화</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K75" s="6" t="inlineStr">
@@ -4532,12 +4532,12 @@
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>엔에이치스팩34호</t>
+          <t>한화플러스제6호스팩</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
@@ -4567,34 +4567,34 @@
       </c>
       <c r="H76" s="7" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I76" s="6" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="J76" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>한화</t>
         </is>
       </c>
       <c r="K76" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-09-10)</t>
+          <t>상장전</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>글로벌테크놀로지</t>
+          <t>엔에이치스팩34호</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
@@ -4614,32 +4614,32 @@
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>29,689</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>-25,889</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H77" s="7" t="inlineStr">
         <is>
-          <t>6,402</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I77" s="6" t="inlineStr">
         <is>
-          <t>반도체 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
-          <t>상장전</t>
+          <t>상장완료 (2026-09-10)</t>
         </is>
       </c>
     </row>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>글로벌테크놀로지</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
@@ -4666,32 +4666,32 @@
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>FY24</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>48,504</t>
+          <t>29,689</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>3,668</t>
+          <t>-25,889</t>
         </is>
       </c>
       <c r="H78" s="7" t="inlineStr">
         <is>
-          <t>8,448</t>
+          <t>6,402</t>
         </is>
       </c>
       <c r="I78" s="6" t="inlineStr">
         <is>
-          <t>항공기,우주선 및 부품 제조업</t>
+          <t>반도체 제조업</t>
         </is>
       </c>
       <c r="J78" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K78" s="6" t="inlineStr">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>디티에스</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
@@ -4728,22 +4728,22 @@
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>142,718</t>
+          <t>48,504</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr">
         <is>
-          <t>18,765</t>
+          <t>3,668</t>
         </is>
       </c>
       <c r="H79" s="7" t="inlineStr">
         <is>
-          <t>63,153</t>
+          <t>8,448</t>
         </is>
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>항공기,우주선 및 부품 제조업</t>
         </is>
       </c>
       <c r="J79" s="6" t="inlineStr">
@@ -4760,12 +4760,12 @@
     <row r="80">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>네오사피엔스</t>
+          <t>디티에스</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
@@ -4780,27 +4780,27 @@
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>FY25</t>
+          <t>FY24</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>10,649</t>
+          <t>142,718</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
-          <t>-6,994</t>
+          <t>18,765</t>
         </is>
       </c>
       <c r="H80" s="7" t="inlineStr">
         <is>
-          <t>-39,962</t>
+          <t>63,153</t>
         </is>
       </c>
       <c r="I80" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="J80" s="6" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>엠에스바이오</t>
+          <t>네오사피엔스</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
@@ -4842,44 +4842,44 @@
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>23,787</t>
+          <t>10,649</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
         <is>
-          <t>7,288</t>
+          <t>-6,994</t>
         </is>
       </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
-          <t>1,942</t>
+          <t>-39,962</t>
         </is>
       </c>
       <c r="I81" s="6" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J81" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K81" s="6" t="inlineStr">
         <is>
-          <t>상장전</t>
+          <t>상장승인(상장예정)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>기도산업</t>
+          <t>엠에스바이오</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
@@ -4899,32 +4899,32 @@
       </c>
       <c r="F82" s="7" t="inlineStr">
         <is>
-          <t>346,551</t>
+          <t>23,787</t>
         </is>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
-          <t>35,334</t>
+          <t>7,288</t>
         </is>
       </c>
       <c r="H82" s="7" t="inlineStr">
         <is>
-          <t>145,991</t>
+          <t>1,942</t>
         </is>
       </c>
       <c r="I82" s="6" t="inlineStr">
         <is>
-          <t>봉제의복 제조업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="J82" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="K82" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-08-21)</t>
+          <t>상장전</t>
         </is>
       </c>
     </row>
@@ -4936,7 +4936,7 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>브릴스</t>
+          <t>기도산업</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
@@ -4956,32 +4956,32 @@
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>23,759</t>
+          <t>346,551</t>
         </is>
       </c>
       <c r="G83" s="7" t="inlineStr">
         <is>
-          <t>1,744</t>
+          <t>35,334</t>
         </is>
       </c>
       <c r="H83" s="7" t="inlineStr">
         <is>
-          <t>4,785</t>
+          <t>145,991</t>
         </is>
       </c>
       <c r="I83" s="6" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>봉제의복 제조업</t>
         </is>
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
-          <t>IBK</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K83" s="6" t="inlineStr">
         <is>
-          <t>상장전</t>
+          <t>상장완료 (2026-08-21)</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>와이즈플래닛컴퍼니</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
@@ -5013,27 +5013,27 @@
       </c>
       <c r="F84" s="7" t="inlineStr">
         <is>
-          <t>44,578</t>
+          <t>23,759</t>
         </is>
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
-          <t>7,748</t>
+          <t>1,744</t>
         </is>
       </c>
       <c r="H84" s="7" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>4,785</t>
         </is>
       </c>
       <c r="I84" s="6" t="inlineStr">
         <is>
-          <t>광고물 문안, 도안, 설계 등 작성업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="J84" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>IBK</t>
         </is>
       </c>
       <c r="K84" s="6" t="inlineStr">
@@ -5045,12 +5045,12 @@
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>니어스랩</t>
+          <t>와이즈플래닛컴퍼니</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
@@ -5070,32 +5070,32 @@
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>6,361</t>
+          <t>44,578</t>
         </is>
       </c>
       <c r="G85" s="7" t="inlineStr">
         <is>
-          <t>-7,287</t>
+          <t>7,748</t>
         </is>
       </c>
       <c r="H85" s="7" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>959</t>
         </is>
       </c>
       <c r="I85" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>광고물 문안, 도안, 설계 등 작성업</t>
         </is>
       </c>
       <c r="J85" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K85" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-08-24)</t>
+          <t>상장전</t>
         </is>
       </c>
     </row>
@@ -5107,7 +5107,7 @@
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>해치텍</t>
+          <t>니어스랩</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
@@ -5127,32 +5127,32 @@
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
-          <t>14,079</t>
+          <t>6,361</t>
         </is>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
-          <t>-8,009</t>
+          <t>-7,287</t>
         </is>
       </c>
       <c r="H86" s="7" t="inlineStr">
         <is>
-          <t>2,229</t>
+          <t>127</t>
         </is>
       </c>
       <c r="I86" s="6" t="inlineStr">
         <is>
-          <t>반도체 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J86" s="6" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K86" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-08-25)</t>
+          <t>상장완료 (2026-08-24)</t>
         </is>
       </c>
     </row>
@@ -5164,7 +5164,7 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>해치텍</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
@@ -5184,44 +5184,44 @@
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>7,936</t>
+          <t>14,079</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>-62,995</t>
+          <t>-8,009</t>
         </is>
       </c>
       <c r="H87" s="7" t="inlineStr">
         <is>
-          <t>8,341</t>
+          <t>2,229</t>
         </is>
       </c>
       <c r="I87" s="6" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>반도체 제조업</t>
         </is>
       </c>
       <c r="J87" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="K87" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-09-04)</t>
+          <t>상장완료 (2026-08-25)</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>에이치엘지노믹스</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
@@ -5241,32 +5241,32 @@
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
-          <t>28,877</t>
+          <t>7,936</t>
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>8,452</t>
+          <t>-62,995</t>
         </is>
       </c>
       <c r="H88" s="7" t="inlineStr">
         <is>
-          <t>83,552</t>
+          <t>8,341</t>
         </is>
       </c>
       <c r="I88" s="6" t="inlineStr">
         <is>
-          <t>기초 의약물질 제조업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="J88" s="6" t="inlineStr">
         <is>
-          <t>KB, IBK</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K88" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-07-24)</t>
+          <t>상장완료 (2026-09-04)</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>딜리셔스</t>
+          <t>에이치엘지노믹스</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
@@ -5298,44 +5298,44 @@
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>25,149</t>
+          <t>28,877</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr">
         <is>
-          <t>-20,419</t>
+          <t>8,452</t>
         </is>
       </c>
       <c r="H89" s="7" t="inlineStr">
         <is>
-          <t>-114,384</t>
+          <t>83,552</t>
         </is>
       </c>
       <c r="I89" s="6" t="inlineStr">
         <is>
-          <t>무점포 소매업</t>
+          <t>기초 의약물질 제조업</t>
         </is>
       </c>
       <c r="J89" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>KB, IBK</t>
         </is>
       </c>
       <c r="K89" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-08-12)</t>
+          <t>상장완료 (2026-07-24)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스</t>
+          <t>딜리셔스</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
@@ -5355,44 +5355,44 @@
       </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
-          <t>2,588,400</t>
+          <t>25,149</t>
         </is>
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>15,755,864</t>
+          <t>-20,419</t>
         </is>
       </c>
       <c r="H90" s="7" t="inlineStr">
         <is>
-          <t>30,841,690</t>
+          <t>-114,384</t>
         </is>
       </c>
       <c r="I90" s="6" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>무점포 소매업</t>
         </is>
       </c>
       <c r="J90" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K90" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-08-18)</t>
+          <t>상장완료 (2026-08-12)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>한국제16호스팩</t>
+          <t>인제니아테라퓨틱스</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
@@ -5410,30 +5410,46 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F91" s="7" t="inlineStr"/>
-      <c r="G91" s="7" t="inlineStr"/>
-      <c r="H91" s="7" t="inlineStr"/>
-      <c r="I91" s="6" t="inlineStr"/>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>2,588,400</t>
+        </is>
+      </c>
+      <c r="G91" s="7" t="inlineStr">
+        <is>
+          <t>15,755,864</t>
+        </is>
+      </c>
+      <c r="H91" s="7" t="inlineStr">
+        <is>
+          <t>30,841,690</t>
+        </is>
+      </c>
+      <c r="I91" s="6" t="inlineStr">
+        <is>
+          <t>자연과학 및 공학 연구개발업</t>
+        </is>
+      </c>
       <c r="J91" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K91" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-06-30)</t>
+          <t>상장완료 (2026-08-18)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>레메디</t>
+          <t>한국제16호스팩</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
@@ -5451,34 +5467,18 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F92" s="7" t="inlineStr">
-        <is>
-          <t>13,441</t>
-        </is>
-      </c>
-      <c r="G92" s="7" t="inlineStr">
-        <is>
-          <t>741</t>
-        </is>
-      </c>
-      <c r="H92" s="7" t="inlineStr">
-        <is>
-          <t>5,870</t>
-        </is>
-      </c>
-      <c r="I92" s="6" t="inlineStr">
-        <is>
-          <t>의료용 기기 제조업</t>
-        </is>
-      </c>
+      <c r="F92" s="7" t="inlineStr"/>
+      <c r="G92" s="7" t="inlineStr"/>
+      <c r="H92" s="7" t="inlineStr"/>
+      <c r="I92" s="6" t="inlineStr"/>
       <c r="J92" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K92" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-07-13)</t>
+          <t>상장완료 (2026-06-30)</t>
         </is>
       </c>
     </row>
@@ -5490,7 +5490,7 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>케이앤에스아이앤씨</t>
+          <t>레메디</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
@@ -5510,44 +5510,44 @@
       </c>
       <c r="F93" s="7" t="inlineStr">
         <is>
-          <t>13,482</t>
+          <t>13,441</t>
         </is>
       </c>
       <c r="G93" s="7" t="inlineStr">
         <is>
-          <t>-2,213</t>
+          <t>741</t>
         </is>
       </c>
       <c r="H93" s="7" t="inlineStr">
         <is>
-          <t>4,273</t>
+          <t>5,870</t>
         </is>
       </c>
       <c r="I93" s="6" t="inlineStr">
         <is>
-          <t>통신 및 방송 장비 제조업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="J93" s="6" t="inlineStr">
         <is>
-          <t>IBK</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="K93" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-08-13)</t>
+          <t>상장완료 (2026-07-13)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>메리츠제2호스팩</t>
+          <t>케이앤에스아이앤씨</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
@@ -5565,30 +5565,46 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F94" s="7" t="inlineStr"/>
-      <c r="G94" s="7" t="inlineStr"/>
-      <c r="H94" s="7" t="inlineStr"/>
-      <c r="I94" s="6" t="inlineStr"/>
+      <c r="F94" s="7" t="inlineStr">
+        <is>
+          <t>13,482</t>
+        </is>
+      </c>
+      <c r="G94" s="7" t="inlineStr">
+        <is>
+          <t>-2,213</t>
+        </is>
+      </c>
+      <c r="H94" s="7" t="inlineStr">
+        <is>
+          <t>4,273</t>
+        </is>
+      </c>
+      <c r="I94" s="6" t="inlineStr">
+        <is>
+          <t>통신 및 방송 장비 제조업</t>
+        </is>
+      </c>
       <c r="J94" s="6" t="inlineStr">
         <is>
-          <t>메리츠</t>
+          <t>IBK</t>
         </is>
       </c>
       <c r="K94" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-06-19)</t>
+          <t>상장완료 (2026-08-13)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>빅웨이브로보틱스</t>
+          <t>메리츠제2호스팩</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
@@ -5603,49 +5619,33 @@
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>FY24</t>
-        </is>
-      </c>
-      <c r="F95" s="7" t="inlineStr">
-        <is>
-          <t>13,851</t>
-        </is>
-      </c>
-      <c r="G95" s="7" t="inlineStr">
-        <is>
-          <t>-5,856</t>
-        </is>
-      </c>
-      <c r="H95" s="7" t="inlineStr">
-        <is>
-          <t>9,470</t>
-        </is>
-      </c>
-      <c r="I95" s="6" t="inlineStr">
-        <is>
-          <t>소프트웨어 개발 및 공급업</t>
-        </is>
-      </c>
+          <t>FY25</t>
+        </is>
+      </c>
+      <c r="F95" s="7" t="inlineStr"/>
+      <c r="G95" s="7" t="inlineStr"/>
+      <c r="H95" s="7" t="inlineStr"/>
+      <c r="I95" s="6" t="inlineStr"/>
       <c r="J95" s="6" t="inlineStr">
         <is>
-          <t>유진, 미래</t>
+          <t>메리츠</t>
         </is>
       </c>
       <c r="K95" s="6" t="inlineStr">
         <is>
-          <t>상장전</t>
+          <t>상장완료 (2026-06-19)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>매드업</t>
+          <t>빅웨이브로보틱스</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
@@ -5665,44 +5665,44 @@
       </c>
       <c r="F96" s="7" t="inlineStr">
         <is>
-          <t>34,989</t>
+          <t>13,851</t>
         </is>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>-2,747</t>
+          <t>-5,856</t>
         </is>
       </c>
       <c r="H96" s="7" t="inlineStr">
         <is>
-          <t>-15,766</t>
+          <t>9,470</t>
         </is>
       </c>
       <c r="I96" s="6" t="inlineStr">
         <is>
-          <t>광고</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J96" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>유진, 미래</t>
         </is>
       </c>
       <c r="K96" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-07-01)</t>
+          <t>상장전</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>져스텍</t>
+          <t>매드업</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
@@ -5722,32 +5722,32 @@
       </c>
       <c r="F97" s="7" t="inlineStr">
         <is>
-          <t>19,851</t>
+          <t>34,989</t>
         </is>
       </c>
       <c r="G97" s="7" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>-2,747</t>
         </is>
       </c>
       <c r="H97" s="7" t="inlineStr">
         <is>
-          <t>10,953</t>
+          <t>-15,766</t>
         </is>
       </c>
       <c r="I97" s="6" t="inlineStr">
         <is>
-          <t>기계</t>
+          <t>광고</t>
         </is>
       </c>
       <c r="J97" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K97" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-06-29)</t>
+          <t>상장완료 (2026-07-01)</t>
         </is>
       </c>
     </row>
@@ -5759,7 +5759,7 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>스트라드비젼</t>
+          <t>져스텍</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
@@ -5779,44 +5779,44 @@
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>11,539</t>
+          <t>19,851</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>-65,529</t>
+          <t>444</t>
         </is>
       </c>
       <c r="H98" s="7" t="inlineStr">
         <is>
-          <t>-245,151</t>
+          <t>10,953</t>
         </is>
       </c>
       <c r="I98" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어</t>
+          <t>기계</t>
         </is>
       </c>
       <c r="J98" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K98" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-06-30)</t>
+          <t>상장완료 (2026-06-29)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>대신밸런스제20호스팩</t>
+          <t>스트라드비젼</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
@@ -5831,33 +5831,49 @@
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>FY25</t>
-        </is>
-      </c>
-      <c r="F99" s="7" t="inlineStr"/>
-      <c r="G99" s="7" t="inlineStr"/>
-      <c r="H99" s="7" t="inlineStr"/>
-      <c r="I99" s="6" t="inlineStr"/>
+          <t>FY24</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr">
+        <is>
+          <t>11,539</t>
+        </is>
+      </c>
+      <c r="G99" s="7" t="inlineStr">
+        <is>
+          <t>-65,529</t>
+        </is>
+      </c>
+      <c r="H99" s="7" t="inlineStr">
+        <is>
+          <t>-245,151</t>
+        </is>
+      </c>
+      <c r="I99" s="6" t="inlineStr">
+        <is>
+          <t>소프트웨어</t>
+        </is>
+      </c>
       <c r="J99" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="K99" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-06-05)</t>
+          <t>상장완료 (2026-06-30)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>피스피스스튜디오</t>
+          <t>대신밸런스제20호스팩</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
@@ -5872,37 +5888,21 @@
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>FY24</t>
-        </is>
-      </c>
-      <c r="F100" s="7" t="inlineStr">
-        <is>
-          <t>113,777</t>
-        </is>
-      </c>
-      <c r="G100" s="7" t="inlineStr">
-        <is>
-          <t>17,603</t>
-        </is>
-      </c>
-      <c r="H100" s="7" t="inlineStr">
-        <is>
-          <t>55,861</t>
-        </is>
-      </c>
-      <c r="I100" s="6" t="inlineStr">
-        <is>
-          <t>섬유,의류,신발,호화품</t>
-        </is>
-      </c>
+          <t>FY25</t>
+        </is>
+      </c>
+      <c r="F100" s="7" t="inlineStr"/>
+      <c r="G100" s="7" t="inlineStr"/>
+      <c r="H100" s="7" t="inlineStr"/>
+      <c r="I100" s="6" t="inlineStr"/>
       <c r="J100" s="6" t="inlineStr">
         <is>
-          <t>NH, 미래</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-06-08)</t>
+          <t>상장완료 (2026-06-05)</t>
         </is>
       </c>
     </row>
@@ -5914,7 +5914,7 @@
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>폴레드</t>
+          <t>피스피스스튜디오</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
@@ -5934,32 +5934,32 @@
       </c>
       <c r="F101" s="7" t="inlineStr">
         <is>
-          <t>52,808</t>
+          <t>113,777</t>
         </is>
       </c>
       <c r="G101" s="7" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>17,603</t>
         </is>
       </c>
       <c r="H101" s="7" t="inlineStr">
         <is>
-          <t>25,416</t>
+          <t>55,861</t>
         </is>
       </c>
       <c r="I101" s="6" t="inlineStr">
         <is>
-          <t>가정용기기와용품</t>
+          <t>섬유,의류,신발,호화품</t>
         </is>
       </c>
       <c r="J101" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>NH, 미래</t>
         </is>
       </c>
       <c r="K101" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-05-14)</t>
+          <t>상장완료 (2026-06-08)</t>
         </is>
       </c>
     </row>
@@ -5971,7 +5971,7 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>레몬헬스케어</t>
+          <t>폴레드</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
@@ -5991,44 +5991,44 @@
       </c>
       <c r="F102" s="7" t="inlineStr">
         <is>
-          <t>14,877</t>
+          <t>52,808</t>
         </is>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
-          <t>-2,898</t>
+          <t>543</t>
         </is>
       </c>
       <c r="H102" s="7" t="inlineStr">
         <is>
-          <t>-31,162</t>
+          <t>25,416</t>
         </is>
       </c>
       <c r="I102" s="6" t="inlineStr">
         <is>
-          <t>건강관리업체및서비스</t>
+          <t>가정용기기와용품</t>
         </is>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K102" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-07-06)</t>
+          <t>상장완료 (2026-05-14)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>마키나락스</t>
+          <t>레몬헬스케어</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
@@ -6048,32 +6048,32 @@
       </c>
       <c r="F103" s="7" t="inlineStr">
         <is>
-          <t>8,294</t>
+          <t>14,877</t>
         </is>
       </c>
       <c r="G103" s="7" t="inlineStr">
         <is>
-          <t>-6,073</t>
+          <t>-2,898</t>
         </is>
       </c>
       <c r="H103" s="7" t="inlineStr">
         <is>
-          <t>2,680</t>
+          <t>-31,162</t>
         </is>
       </c>
       <c r="I103" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어</t>
+          <t>건강관리업체및서비스</t>
         </is>
       </c>
       <c r="J103" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="K103" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-05-20)</t>
+          <t>상장완료 (2026-07-06)</t>
         </is>
       </c>
     </row>
@@ -6085,7 +6085,7 @@
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>채비</t>
+          <t>마키나락스</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
@@ -6105,44 +6105,44 @@
       </c>
       <c r="F104" s="7" t="inlineStr">
         <is>
-          <t>85,082</t>
+          <t>8,294</t>
         </is>
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
-          <t>-54,495</t>
+          <t>-6,073</t>
         </is>
       </c>
       <c r="H104" s="7" t="inlineStr">
         <is>
-          <t>96,866</t>
+          <t>2,680</t>
         </is>
       </c>
       <c r="I104" s="6" t="inlineStr">
         <is>
-          <t>전기제품</t>
+          <t>소프트웨어</t>
         </is>
       </c>
       <c r="J104" s="6" t="inlineStr">
         <is>
-          <t>KB, 삼성, 대신, 하나</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K104" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-04-29)</t>
+          <t>상장완료 (2026-05-20)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>키움히어로제2호스팩</t>
+          <t>채비</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
@@ -6160,30 +6160,46 @@
           <t>FY24</t>
         </is>
       </c>
-      <c r="F105" s="7" t="inlineStr"/>
-      <c r="G105" s="7" t="inlineStr"/>
-      <c r="H105" s="7" t="inlineStr"/>
-      <c r="I105" s="6" t="inlineStr"/>
+      <c r="F105" s="7" t="inlineStr">
+        <is>
+          <t>85,082</t>
+        </is>
+      </c>
+      <c r="G105" s="7" t="inlineStr">
+        <is>
+          <t>-54,495</t>
+        </is>
+      </c>
+      <c r="H105" s="7" t="inlineStr">
+        <is>
+          <t>96,866</t>
+        </is>
+      </c>
+      <c r="I105" s="6" t="inlineStr">
+        <is>
+          <t>전기제품</t>
+        </is>
+      </c>
       <c r="J105" s="6" t="inlineStr">
         <is>
-          <t>키움</t>
+          <t>KB, 삼성, 대신, 하나</t>
         </is>
       </c>
       <c r="K105" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-04-23)</t>
+          <t>상장완료 (2026-04-29)</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>세미티에스</t>
+          <t>키움히어로제2호스팩</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
@@ -6193,7 +6209,7 @@
       </c>
       <c r="D106" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E106" s="6" t="inlineStr">
@@ -6201,46 +6217,30 @@
           <t>FY24</t>
         </is>
       </c>
-      <c r="F106" s="7" t="inlineStr">
-        <is>
-          <t>20,808</t>
-        </is>
-      </c>
-      <c r="G106" s="7" t="inlineStr">
-        <is>
-          <t>7,337</t>
-        </is>
-      </c>
-      <c r="H106" s="7" t="inlineStr">
-        <is>
-          <t>26,616</t>
-        </is>
-      </c>
-      <c r="I106" s="6" t="inlineStr">
-        <is>
-          <t>반도체와반도체장비</t>
-        </is>
-      </c>
+      <c r="F106" s="7" t="inlineStr"/>
+      <c r="G106" s="7" t="inlineStr"/>
+      <c r="H106" s="7" t="inlineStr"/>
+      <c r="I106" s="6" t="inlineStr"/>
       <c r="J106" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>키움</t>
         </is>
       </c>
       <c r="K106" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-02-05)</t>
+          <t>상장완료 (2026-04-23)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>교보20호스팩</t>
+          <t>세미티에스</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
@@ -6258,30 +6258,46 @@
           <t>FY24</t>
         </is>
       </c>
-      <c r="F107" s="7" t="inlineStr"/>
-      <c r="G107" s="7" t="inlineStr"/>
-      <c r="H107" s="7" t="inlineStr"/>
-      <c r="I107" s="6" t="inlineStr"/>
+      <c r="F107" s="7" t="inlineStr">
+        <is>
+          <t>20,808</t>
+        </is>
+      </c>
+      <c r="G107" s="7" t="inlineStr">
+        <is>
+          <t>7,337</t>
+        </is>
+      </c>
+      <c r="H107" s="7" t="inlineStr">
+        <is>
+          <t>26,616</t>
+        </is>
+      </c>
+      <c r="I107" s="6" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
       <c r="J107" s="6" t="inlineStr">
         <is>
-          <t>교보</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K107" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-04-02)</t>
+          <t>상장완료 (2026-02-05)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>케이피항공산업</t>
+          <t>교보20호스팩</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
@@ -6291,7 +6307,7 @@
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
@@ -6299,34 +6315,18 @@
           <t>FY24</t>
         </is>
       </c>
-      <c r="F108" s="7" t="inlineStr">
-        <is>
-          <t>49,651</t>
-        </is>
-      </c>
-      <c r="G108" s="7" t="inlineStr">
-        <is>
-          <t>3,018</t>
-        </is>
-      </c>
-      <c r="H108" s="7" t="inlineStr">
-        <is>
-          <t>15,901</t>
-        </is>
-      </c>
-      <c r="I108" s="6" t="inlineStr">
-        <is>
-          <t>우주항공과국방</t>
-        </is>
-      </c>
+      <c r="F108" s="7" t="inlineStr"/>
+      <c r="G108" s="7" t="inlineStr"/>
+      <c r="H108" s="7" t="inlineStr"/>
+      <c r="I108" s="6" t="inlineStr"/>
       <c r="J108" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>교보</t>
         </is>
       </c>
       <c r="K108" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-01-29)</t>
+          <t>상장완료 (2026-04-02)</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>한패스</t>
+          <t>케이피항공산업</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
@@ -6358,44 +6358,44 @@
       </c>
       <c r="F109" s="7" t="inlineStr">
         <is>
-          <t>55,297</t>
+          <t>49,651</t>
         </is>
       </c>
       <c r="G109" s="7" t="inlineStr">
         <is>
-          <t>4,403</t>
+          <t>3,018</t>
         </is>
       </c>
       <c r="H109" s="7" t="inlineStr">
         <is>
-          <t>-28,065</t>
+          <t>15,901</t>
         </is>
       </c>
       <c r="I109" s="6" t="inlineStr">
         <is>
-          <t>IT서비스</t>
+          <t>우주항공과국방</t>
         </is>
       </c>
       <c r="J109" s="6" t="inlineStr">
         <is>
-          <t>한국, 대신</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K109" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-03-25)</t>
+          <t>상장완료 (2026-01-29)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>신한제18호스팩</t>
+          <t>한패스</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
@@ -6413,30 +6413,46 @@
           <t>FY24</t>
         </is>
       </c>
-      <c r="F110" s="7" t="inlineStr"/>
-      <c r="G110" s="7" t="inlineStr"/>
-      <c r="H110" s="7" t="inlineStr"/>
-      <c r="I110" s="6" t="inlineStr"/>
+      <c r="F110" s="7" t="inlineStr">
+        <is>
+          <t>55,297</t>
+        </is>
+      </c>
+      <c r="G110" s="7" t="inlineStr">
+        <is>
+          <t>4,403</t>
+        </is>
+      </c>
+      <c r="H110" s="7" t="inlineStr">
+        <is>
+          <t>-28,065</t>
+        </is>
+      </c>
+      <c r="I110" s="6" t="inlineStr">
+        <is>
+          <t>IT서비스</t>
+        </is>
+      </c>
       <c r="J110" s="6" t="inlineStr">
         <is>
-          <t>신한</t>
+          <t>한국, 대신</t>
         </is>
       </c>
       <c r="K110" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-04-30)</t>
+          <t>상장완료 (2026-03-25)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="6" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>엔에이치스팩33호</t>
+          <t>신한제18호스팩</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
@@ -6460,24 +6476,24 @@
       <c r="I111" s="6" t="inlineStr"/>
       <c r="J111" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>신한</t>
         </is>
       </c>
       <c r="K111" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-03-27)</t>
+          <t>상장완료 (2026-04-30)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>신한제17호스팩</t>
+          <t>엔에이치스팩33호</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
@@ -6501,24 +6517,24 @@
       <c r="I112" s="6" t="inlineStr"/>
       <c r="J112" s="6" t="inlineStr">
         <is>
-          <t>신한</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K112" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-04-01)</t>
+          <t>상장완료 (2026-03-27)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="6" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>아이엠바이오로직스</t>
+          <t>신한제17호스팩</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
@@ -6536,34 +6552,18 @@
           <t>FY24</t>
         </is>
       </c>
-      <c r="F113" s="7" t="inlineStr">
-        <is>
-          <t>27,594</t>
-        </is>
-      </c>
-      <c r="G113" s="7" t="inlineStr">
-        <is>
-          <t>-11,884</t>
-        </is>
-      </c>
-      <c r="H113" s="7" t="inlineStr">
-        <is>
-          <t>-77,202</t>
-        </is>
-      </c>
-      <c r="I113" s="6" t="inlineStr">
-        <is>
-          <t>제약</t>
-        </is>
-      </c>
+      <c r="F113" s="7" t="inlineStr"/>
+      <c r="G113" s="7" t="inlineStr"/>
+      <c r="H113" s="7" t="inlineStr"/>
+      <c r="I113" s="6" t="inlineStr"/>
       <c r="J113" s="6" t="inlineStr">
         <is>
-          <t>한국, 신한</t>
+          <t>신한</t>
         </is>
       </c>
       <c r="K113" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-03-20)</t>
+          <t>상장완료 (2026-04-01)</t>
         </is>
       </c>
     </row>
@@ -6575,7 +6575,7 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>에스팀</t>
+          <t>아이엠바이오로직스</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
@@ -6595,232 +6595,232 @@
       </c>
       <c r="F114" s="7" t="inlineStr">
         <is>
-          <t>35,574</t>
+          <t>27,594</t>
         </is>
       </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
-          <t>1,372</t>
+          <t>-11,884</t>
         </is>
       </c>
       <c r="H114" s="7" t="inlineStr">
         <is>
-          <t>12,331</t>
+          <t>-77,202</t>
         </is>
       </c>
       <c r="I114" s="6" t="inlineStr">
         <is>
-          <t>광고</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="J114" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>한국, 신한</t>
         </is>
       </c>
       <c r="K114" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-03-06)</t>
+          <t>상장완료 (2026-03-20)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="6" t="inlineStr">
         <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>에스팀</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="D115" s="6" t="inlineStr">
+        <is>
+          <t>신규상장</t>
+        </is>
+      </c>
+      <c r="E115" s="6" t="inlineStr">
+        <is>
+          <t>FY24</t>
+        </is>
+      </c>
+      <c r="F115" s="7" t="inlineStr">
+        <is>
+          <t>35,574</t>
+        </is>
+      </c>
+      <c r="G115" s="7" t="inlineStr">
+        <is>
+          <t>1,372</t>
+        </is>
+      </c>
+      <c r="H115" s="7" t="inlineStr">
+        <is>
+          <t>12,331</t>
+        </is>
+      </c>
+      <c r="I115" s="6" t="inlineStr">
+        <is>
+          <t>광고</t>
+        </is>
+      </c>
+      <c r="J115" s="6" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="K115" s="6" t="inlineStr">
+        <is>
+          <t>상장완료 (2026-03-06)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="6" t="inlineStr">
+        <is>
           <t>2026-01-12</t>
         </is>
       </c>
-      <c r="B115" s="6" t="inlineStr">
+      <c r="B116" s="6" t="inlineStr">
         <is>
           <t>케이뱅크</t>
         </is>
       </c>
-      <c r="C115" s="6" t="inlineStr">
+      <c r="C116" s="6" t="inlineStr">
         <is>
           <t>유가</t>
         </is>
       </c>
-      <c r="D115" s="6" t="inlineStr">
+      <c r="D116" s="6" t="inlineStr">
         <is>
           <t>신규상장</t>
         </is>
       </c>
-      <c r="E115" s="6" t="inlineStr">
+      <c r="E116" s="6" t="inlineStr">
         <is>
           <t>FY24</t>
         </is>
       </c>
-      <c r="F115" s="7" t="inlineStr">
+      <c r="F116" s="7" t="inlineStr">
         <is>
           <t>1,228,501</t>
         </is>
       </c>
-      <c r="G115" s="7" t="inlineStr">
+      <c r="G116" s="7" t="inlineStr">
         <is>
           <t>128,053</t>
         </is>
       </c>
-      <c r="H115" s="7" t="inlineStr">
+      <c r="H116" s="7" t="inlineStr">
         <is>
           <t>1,995,845</t>
         </is>
       </c>
-      <c r="I115" s="6" t="inlineStr">
+      <c r="I116" s="6" t="inlineStr">
         <is>
           <t>은행</t>
         </is>
       </c>
-      <c r="J115" s="6" t="inlineStr">
+      <c r="J116" s="6" t="inlineStr">
         <is>
           <t>NH, 삼성</t>
         </is>
       </c>
-      <c r="K115" s="6" t="inlineStr">
+      <c r="K116" s="6" t="inlineStr">
         <is>
           <t>상장완료 (2026-03-05)</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="3" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
         <is>
           <t>■ 철회·미승인  (18건)</t>
         </is>
       </c>
-      <c r="B117" s="4" t="n"/>
-      <c r="C117" s="4" t="n"/>
-      <c r="D117" s="4" t="n"/>
-      <c r="E117" s="4" t="n"/>
-      <c r="F117" s="4" t="n"/>
-      <c r="G117" s="4" t="n"/>
-      <c r="H117" s="4" t="n"/>
-      <c r="I117" s="4" t="n"/>
-      <c r="J117" s="4" t="n"/>
-      <c r="K117" s="4" t="n"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="5" t="inlineStr">
+      <c r="B118" s="4" t="n"/>
+      <c r="C118" s="4" t="n"/>
+      <c r="D118" s="4" t="n"/>
+      <c r="E118" s="4" t="n"/>
+      <c r="F118" s="4" t="n"/>
+      <c r="G118" s="4" t="n"/>
+      <c r="H118" s="4" t="n"/>
+      <c r="I118" s="4" t="n"/>
+      <c r="J118" s="4" t="n"/>
+      <c r="K118" s="4" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="inlineStr">
         <is>
           <t>일자</t>
         </is>
       </c>
-      <c r="B118" s="5" t="inlineStr">
+      <c r="B119" s="5" t="inlineStr">
         <is>
           <t>회사명</t>
         </is>
       </c>
-      <c r="C118" s="5" t="inlineStr">
+      <c r="C119" s="5" t="inlineStr">
         <is>
           <t>시장</t>
         </is>
       </c>
-      <c r="D118" s="5" t="inlineStr">
+      <c r="D119" s="5" t="inlineStr">
         <is>
           <t>상장유형</t>
         </is>
       </c>
-      <c r="E118" s="5" t="inlineStr">
+      <c r="E119" s="5" t="inlineStr">
         <is>
           <t>기준연도</t>
         </is>
       </c>
-      <c r="F118" s="5" t="inlineStr">
+      <c r="F119" s="5" t="inlineStr">
         <is>
           <t>매출액</t>
         </is>
       </c>
-      <c r="G118" s="5" t="inlineStr">
+      <c r="G119" s="5" t="inlineStr">
         <is>
           <t>순이익</t>
         </is>
       </c>
-      <c r="H118" s="5" t="inlineStr">
+      <c r="H119" s="5" t="inlineStr">
         <is>
           <t>자기자본</t>
         </is>
       </c>
-      <c r="I118" s="5" t="inlineStr">
+      <c r="I119" s="5" t="inlineStr">
         <is>
           <t>업종</t>
         </is>
       </c>
-      <c r="J118" s="5" t="inlineStr">
+      <c r="J119" s="5" t="inlineStr">
         <is>
           <t>대표주관사</t>
         </is>
       </c>
-      <c r="K118" s="5" t="inlineStr">
+      <c r="K119" s="5" t="inlineStr">
         <is>
           <t>현황</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B119" s="6" t="inlineStr">
-        <is>
-          <t>텔레픽스</t>
-        </is>
-      </c>
-      <c r="C119" s="6" t="inlineStr">
-        <is>
-          <t>코스닥</t>
-        </is>
-      </c>
-      <c r="D119" s="6" t="inlineStr">
-        <is>
-          <t>신규상장</t>
-        </is>
-      </c>
-      <c r="E119" s="6" t="inlineStr">
-        <is>
-          <t>FY25</t>
-        </is>
-      </c>
-      <c r="F119" s="7" t="inlineStr">
-        <is>
-          <t>4,896</t>
-        </is>
-      </c>
-      <c r="G119" s="7" t="inlineStr">
-        <is>
-          <t>-16,214</t>
-        </is>
-      </c>
-      <c r="H119" s="7" t="inlineStr">
-        <is>
-          <t>9,146</t>
-        </is>
-      </c>
-      <c r="I119" s="6" t="inlineStr">
-        <is>
-          <t>소프트웨어 개발 및 공급업</t>
-        </is>
-      </c>
-      <c r="J119" s="6" t="inlineStr">
-        <is>
-          <t>미래</t>
-        </is>
-      </c>
-      <c r="K119" s="6" t="inlineStr">
-        <is>
-          <t>심사 철회</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>씨엠디엘</t>
+          <t>텔레픽스</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
@@ -6830,37 +6830,37 @@
       </c>
       <c r="D120" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E120" s="6" t="inlineStr">
         <is>
-          <t>FY24</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="F120" s="7" t="inlineStr">
         <is>
-          <t>39,991</t>
+          <t>4,896</t>
         </is>
       </c>
       <c r="G120" s="7" t="inlineStr">
         <is>
-          <t>3,541</t>
+          <t>-16,214</t>
         </is>
       </c>
       <c r="H120" s="7" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>9,146</t>
         </is>
       </c>
       <c r="I120" s="6" t="inlineStr">
         <is>
-          <t>기타 기초 유기 화학물질 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J120" s="6" t="inlineStr">
         <is>
-          <t>교보</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K120" s="6" t="inlineStr">
@@ -6872,12 +6872,12 @@
     <row r="121">
       <c r="A121" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>모비어스</t>
+          <t>씨엠디엘</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
@@ -6887,37 +6887,37 @@
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
-          <t>FY25</t>
+          <t>FY24</t>
         </is>
       </c>
       <c r="F121" s="7" t="inlineStr">
         <is>
-          <t>31,989</t>
+          <t>39,991</t>
         </is>
       </c>
       <c r="G121" s="7" t="inlineStr">
         <is>
-          <t>-45,307</t>
+          <t>3,541</t>
         </is>
       </c>
       <c r="H121" s="7" t="inlineStr">
         <is>
-          <t>-96,707</t>
+          <t>503</t>
         </is>
       </c>
       <c r="I121" s="6" t="inlineStr">
         <is>
-          <t>컴퓨터 프로그래밍, 시스템 통합 및 관리업</t>
+          <t>기타 기초 유기 화학물질 제조업</t>
         </is>
       </c>
       <c r="J121" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>교보</t>
         </is>
       </c>
       <c r="K121" s="6" t="inlineStr">
@@ -6929,12 +6929,12 @@
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>넥스트젠바이오</t>
+          <t>모비어스</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
@@ -6949,32 +6949,32 @@
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
-          <t>FY24</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="F122" s="7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>31,989</t>
         </is>
       </c>
       <c r="G122" s="7" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>-45,307</t>
         </is>
       </c>
       <c r="H122" s="7" t="inlineStr">
         <is>
-          <t>4,792</t>
+          <t>-96,707</t>
         </is>
       </c>
       <c r="I122" s="6" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>컴퓨터 프로그래밍, 시스템 통합 및 관리업</t>
         </is>
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K122" s="6" t="inlineStr">
@@ -6986,12 +6986,12 @@
     <row r="123">
       <c r="A123" s="6" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>파워큐브세미</t>
+          <t>넥스트젠바이오</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
@@ -7006,32 +7006,32 @@
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>FY25</t>
+          <t>FY24</t>
         </is>
       </c>
       <c r="F123" s="7" t="inlineStr">
         <is>
-          <t>10,341</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G123" s="7" t="inlineStr">
         <is>
-          <t>-10,837</t>
+          <t>69</t>
         </is>
       </c>
       <c r="H123" s="7" t="inlineStr">
         <is>
-          <t>841</t>
+          <t>4,792</t>
         </is>
       </c>
       <c r="I123" s="6" t="inlineStr">
         <is>
-          <t>반도체 제조업</t>
+          <t>자연과학 및 공학 연구개발업</t>
         </is>
       </c>
       <c r="J123" s="6" t="inlineStr">
         <is>
-          <t>하나, BNK</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K123" s="6" t="inlineStr">
@@ -7043,12 +7043,12 @@
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>제이피이노베이션</t>
+          <t>파워큐브세미</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
@@ -7068,27 +7068,27 @@
       </c>
       <c r="F124" s="7" t="inlineStr">
         <is>
-          <t>56,324</t>
+          <t>10,341</t>
         </is>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
-          <t>5,588</t>
+          <t>-10,837</t>
         </is>
       </c>
       <c r="H124" s="7" t="inlineStr">
         <is>
-          <t>3,684</t>
+          <t>841</t>
         </is>
       </c>
       <c r="I124" s="6" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>반도체 제조업</t>
         </is>
       </c>
       <c r="J124" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>하나, BNK</t>
         </is>
       </c>
       <c r="K124" s="6" t="inlineStr">
@@ -7100,12 +7100,12 @@
     <row r="125">
       <c r="A125" s="6" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>케이솔루션</t>
+          <t>제이피이노베이션</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
@@ -7115,7 +7115,7 @@
       </c>
       <c r="D125" s="6" t="inlineStr">
         <is>
-          <t>스팩 존속합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E125" s="6" t="inlineStr">
@@ -7125,27 +7125,27 @@
       </c>
       <c r="F125" s="7" t="inlineStr">
         <is>
-          <t>34,565</t>
+          <t>56,324</t>
         </is>
       </c>
       <c r="G125" s="7" t="inlineStr">
         <is>
-          <t>1,158</t>
+          <t>5,588</t>
         </is>
       </c>
       <c r="H125" s="7" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>3,684</t>
         </is>
       </c>
       <c r="I125" s="6" t="inlineStr">
         <is>
-          <t>차체 및 특장차 제조업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="J125" s="6" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K125" s="6" t="inlineStr">
@@ -7157,12 +7157,12 @@
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>디토닉</t>
+          <t>케이솔루션</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
@@ -7172,37 +7172,37 @@
       </c>
       <c r="D126" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 존속합병</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
         <is>
-          <t>FY24</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="F126" s="7" t="inlineStr">
         <is>
-          <t>31,293</t>
+          <t>34,565</t>
         </is>
       </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
-          <t>-1,633</t>
+          <t>1,158</t>
         </is>
       </c>
       <c r="H126" s="7" t="inlineStr">
         <is>
-          <t>-21,926</t>
+          <t>653</t>
         </is>
       </c>
       <c r="I126" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>차체 및 특장차 제조업</t>
         </is>
       </c>
       <c r="J126" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="K126" s="6" t="inlineStr">
@@ -7214,12 +7214,12 @@
     <row r="127">
       <c r="A127" s="6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>에스케이팩</t>
+          <t>디토닉</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
@@ -7229,7 +7229,7 @@
       </c>
       <c r="D127" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr">
@@ -7239,27 +7239,27 @@
       </c>
       <c r="F127" s="7" t="inlineStr">
         <is>
-          <t>27,310</t>
+          <t>31,293</t>
         </is>
       </c>
       <c r="G127" s="7" t="inlineStr">
         <is>
-          <t>2,257</t>
+          <t>-1,633</t>
         </is>
       </c>
       <c r="H127" s="7" t="inlineStr">
         <is>
-          <t>3,207</t>
+          <t>-21,926</t>
         </is>
       </c>
       <c r="I127" s="6" t="inlineStr">
         <is>
-          <t>용기 세척, 포장 및 충전기 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J127" s="6" t="inlineStr">
         <is>
-          <t>교보</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K127" s="6" t="inlineStr">
@@ -7271,12 +7271,12 @@
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>메타넷엑스</t>
+          <t>에스케이팩</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
@@ -7296,27 +7296,27 @@
       </c>
       <c r="F128" s="7" t="inlineStr">
         <is>
-          <t>244,130</t>
+          <t>27,310</t>
         </is>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
-          <t>13,455</t>
+          <t>2,257</t>
         </is>
       </c>
       <c r="H128" s="7" t="inlineStr">
         <is>
-          <t>9,995</t>
+          <t>3,207</t>
         </is>
       </c>
       <c r="I128" s="6" t="inlineStr">
         <is>
-          <t>컴퓨터 프로그래밍, 시스템 통합 및 관리업</t>
+          <t>용기 세척, 포장 및 충전기 제조업</t>
         </is>
       </c>
       <c r="J128" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>교보</t>
         </is>
       </c>
       <c r="K128" s="6" t="inlineStr">
@@ -7328,12 +7328,12 @@
     <row r="129">
       <c r="A129" s="6" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>무아스</t>
+          <t>메타넷엑스</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
@@ -7343,7 +7343,7 @@
       </c>
       <c r="D129" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr">
@@ -7353,27 +7353,27 @@
       </c>
       <c r="F129" s="7" t="inlineStr">
         <is>
-          <t>41,813</t>
+          <t>244,130</t>
         </is>
       </c>
       <c r="G129" s="7" t="inlineStr">
         <is>
-          <t>3,903</t>
+          <t>13,455</t>
         </is>
       </c>
       <c r="H129" s="7" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>9,995</t>
         </is>
       </c>
       <c r="I129" s="6" t="inlineStr">
         <is>
-          <t>가정용 전기기기 제조업</t>
+          <t>컴퓨터 프로그래밍, 시스템 통합 및 관리업</t>
         </is>
       </c>
       <c r="J129" s="6" t="inlineStr">
         <is>
-          <t>신한</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K129" s="6" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>유빅스테라퓨틱스</t>
+          <t>무아스</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="D130" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
@@ -7410,27 +7410,27 @@
       </c>
       <c r="F130" s="7" t="inlineStr">
         <is>
-          <t>1,071</t>
+          <t>41,813</t>
         </is>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
-          <t>-15,145</t>
+          <t>3,903</t>
         </is>
       </c>
       <c r="H130" s="7" t="inlineStr">
         <is>
-          <t>5,489</t>
+          <t>532</t>
         </is>
       </c>
       <c r="I130" s="6" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>가정용 전기기기 제조업</t>
         </is>
       </c>
       <c r="J130" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>신한</t>
         </is>
       </c>
       <c r="K130" s="6" t="inlineStr">
@@ -7442,12 +7442,12 @@
     <row r="131">
       <c r="A131" s="6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>코드잇</t>
+          <t>유빅스테라퓨틱스</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
@@ -7467,27 +7467,27 @@
       </c>
       <c r="F131" s="7" t="inlineStr">
         <is>
-          <t>30,747</t>
+          <t>1,071</t>
         </is>
       </c>
       <c r="G131" s="7" t="inlineStr">
         <is>
-          <t>6,652</t>
+          <t>-15,145</t>
         </is>
       </c>
       <c r="H131" s="7" t="inlineStr">
         <is>
-          <t>2,403</t>
+          <t>5,489</t>
         </is>
       </c>
       <c r="I131" s="6" t="inlineStr">
         <is>
-          <t>교육지원 서비스업</t>
+          <t>자연과학 및 공학 연구개발업</t>
         </is>
       </c>
       <c r="J131" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K131" s="6" t="inlineStr">
@@ -7499,12 +7499,12 @@
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>한컴인스페이스</t>
+          <t>코드잇</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
@@ -7524,44 +7524,44 @@
       </c>
       <c r="F132" s="7" t="inlineStr">
         <is>
-          <t>23,492</t>
+          <t>30,747</t>
         </is>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
-          <t>-3,104</t>
+          <t>6,652</t>
         </is>
       </c>
       <c r="H132" s="7" t="inlineStr">
         <is>
-          <t>5,815</t>
+          <t>2,403</t>
         </is>
       </c>
       <c r="I132" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>교육지원 서비스업</t>
         </is>
       </c>
       <c r="J132" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K132" s="6" t="inlineStr">
         <is>
-          <t>심사 미승인</t>
+          <t>심사 철회</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="6" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>크몽</t>
+          <t>한컴인스페이스</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
@@ -7581,44 +7581,44 @@
       </c>
       <c r="F133" s="7" t="inlineStr">
         <is>
-          <t>48,572</t>
+          <t>23,492</t>
         </is>
       </c>
       <c r="G133" s="7" t="inlineStr">
         <is>
-          <t>3,988</t>
+          <t>-3,104</t>
         </is>
       </c>
       <c r="H133" s="7" t="inlineStr">
         <is>
-          <t>4,930</t>
+          <t>5,815</t>
         </is>
       </c>
       <c r="I133" s="6" t="inlineStr">
         <is>
-          <t>기타 정보 서비스업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J133" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K133" s="6" t="inlineStr">
         <is>
-          <t>심사 철회</t>
+          <t>심사 미승인</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>한화플러스제6호스팩</t>
+          <t>크몽</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
@@ -7638,27 +7638,27 @@
       </c>
       <c r="F134" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>48,572</t>
         </is>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3,988</t>
         </is>
       </c>
       <c r="H134" s="7" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4,930</t>
         </is>
       </c>
       <c r="I134" s="6" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>기타 정보 서비스업</t>
         </is>
       </c>
       <c r="J134" s="6" t="inlineStr">
         <is>
-          <t>한화</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K134" s="6" t="inlineStr">
@@ -7670,17 +7670,17 @@
     <row r="135">
       <c r="A135" s="6" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>에식스솔루션즈</t>
+          <t>한화플러스제6호스팩</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
         <is>
-          <t>유가</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D135" s="6" t="inlineStr">
@@ -7695,27 +7695,27 @@
       </c>
       <c r="F135" s="7" t="inlineStr">
         <is>
-          <t>2,461</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G135" s="7" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H135" s="7" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I135" s="6" t="inlineStr">
         <is>
-          <t>절연선 및 케이블 제조업</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="J135" s="6" t="inlineStr">
         <is>
-          <t>한국, 미래</t>
+          <t>한화</t>
         </is>
       </c>
       <c r="K135" s="6" t="inlineStr">
@@ -7727,55 +7727,112 @@
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
         <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B136" s="6" t="inlineStr">
+        <is>
+          <t>에식스솔루션즈</t>
+        </is>
+      </c>
+      <c r="C136" s="6" t="inlineStr">
+        <is>
+          <t>유가</t>
+        </is>
+      </c>
+      <c r="D136" s="6" t="inlineStr">
+        <is>
+          <t>신규상장</t>
+        </is>
+      </c>
+      <c r="E136" s="6" t="inlineStr">
+        <is>
+          <t>FY24</t>
+        </is>
+      </c>
+      <c r="F136" s="7" t="inlineStr">
+        <is>
+          <t>2,461</t>
+        </is>
+      </c>
+      <c r="G136" s="7" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="H136" s="7" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I136" s="6" t="inlineStr">
+        <is>
+          <t>절연선 및 케이블 제조업</t>
+        </is>
+      </c>
+      <c r="J136" s="6" t="inlineStr">
+        <is>
+          <t>한국, 미래</t>
+        </is>
+      </c>
+      <c r="K136" s="6" t="inlineStr">
+        <is>
+          <t>심사 철회</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="6" t="inlineStr">
+        <is>
           <t>2026-01-23</t>
         </is>
       </c>
-      <c r="B136" s="6" t="inlineStr">
+      <c r="B137" s="6" t="inlineStr">
         <is>
           <t>에코크레이션</t>
         </is>
       </c>
-      <c r="C136" s="6" t="inlineStr">
+      <c r="C137" s="6" t="inlineStr">
         <is>
           <t>코스닥</t>
         </is>
       </c>
-      <c r="D136" s="6" t="inlineStr">
+      <c r="D137" s="6" t="inlineStr">
         <is>
           <t>신규상장</t>
         </is>
       </c>
-      <c r="E136" s="6" t="inlineStr">
+      <c r="E137" s="6" t="inlineStr">
         <is>
           <t>FY24</t>
         </is>
       </c>
-      <c r="F136" s="7" t="inlineStr">
+      <c r="F137" s="7" t="inlineStr">
         <is>
           <t>18,544</t>
         </is>
       </c>
-      <c r="G136" s="7" t="inlineStr">
+      <c r="G137" s="7" t="inlineStr">
         <is>
           <t>-15,634</t>
         </is>
       </c>
-      <c r="H136" s="7" t="inlineStr">
+      <c r="H137" s="7" t="inlineStr">
         <is>
           <t>4,550</t>
         </is>
       </c>
-      <c r="I136" s="6" t="inlineStr">
+      <c r="I137" s="6" t="inlineStr">
         <is>
           <t>일반 목적용 기계 제조업</t>
         </is>
       </c>
-      <c r="J136" s="6" t="inlineStr">
+      <c r="J137" s="6" t="inlineStr">
         <is>
           <t>키움</t>
         </is>
       </c>
-      <c r="K136" s="6" t="inlineStr">
+      <c r="K137" s="6" t="inlineStr">
         <is>
           <t>심사 철회</t>
         </is>
@@ -7792,7 +7849,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R82"/>
+  <dimension ref="A1:R84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -11230,7 +11287,7 @@
     <row r="48" ht="22" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>■ 공모 진행 (예심 승인법인)  (30건)</t>
+          <t>■ 공모 진행 (예심 승인법인)  (32건)</t>
         </is>
       </c>
       <c r="B48" s="4" t="n"/>
@@ -11406,71 +11463,71 @@
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>한국제17호스팩</t>
+          <t>와이즈플래닛컴퍼니</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>09-07~09-08</t>
-        </is>
-      </c>
-      <c r="C51" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>09-04~09-10</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>10,000~12,000</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>7,000,000</t>
+          <t>1,600,000</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>14,000,000,000</t>
-        </is>
-      </c>
-      <c r="F51" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>19,200,000,000</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>20.04배 (PER)</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="H51" s="6" t="n">
-        <v>1270.51</v>
+        <v>1248.47</v>
       </c>
       <c r="I51" s="6" t="n">
-        <v>2040</v>
+        <v>2323</v>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
-          <t>09-10~09-11</t>
+          <t>09-14~09-15</t>
         </is>
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>8,291.55</t>
+          <t>3,568.86</t>
         </is>
       </c>
       <c r="L51" s="6" t="inlineStr"/>
       <c r="M51" s="6" t="inlineStr"/>
-      <c r="N51" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="N51" s="6" t="inlineStr">
+        <is>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="O51" s="6" t="inlineStr"/>
-      <c r="P51" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P51" s="7" t="inlineStr">
+        <is>
+          <t>494,400,000</t>
         </is>
       </c>
       <c r="Q51" s="6" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
@@ -11482,120 +11539,124 @@
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>브릴스</t>
+          <t>한국제17호스팩</t>
         </is>
       </c>
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>08-31~09-04</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>16,500~19,500</t>
+          <t>09-07~09-08</t>
+        </is>
+      </c>
+      <c r="C52" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>1,200,000</t>
+          <t>7,000,000</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>23,400,000,000</t>
-        </is>
-      </c>
-      <c r="F52" s="6" t="inlineStr">
-        <is>
-          <t>13.44 (PSR)</t>
+          <t>14,000,000,000</t>
+        </is>
+      </c>
+      <c r="F52" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>19,500</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="H52" s="6" t="n">
-        <v>1187.74</v>
+        <v>1270.51</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>2181</v>
+        <v>2040</v>
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
-          <t>09-08~09-09</t>
-        </is>
-      </c>
-      <c r="K52" s="6" t="inlineStr"/>
+          <t>09-10~09-11</t>
+        </is>
+      </c>
+      <c r="K52" s="6" t="inlineStr">
+        <is>
+          <t>8,291.55</t>
+        </is>
+      </c>
       <c r="L52" s="6" t="inlineStr"/>
       <c r="M52" s="6" t="inlineStr"/>
-      <c r="N52" s="6" t="inlineStr">
-        <is>
-          <t>아이비케이투자증권</t>
+      <c r="N52" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="O52" s="6" t="inlineStr"/>
-      <c r="P52" s="7" t="inlineStr">
-        <is>
-          <t>713,790,000</t>
+      <c r="P52" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="Q52" s="6" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
-          <t>발행조건확정</t>
+          <t>청약완료·상장대기</t>
         </is>
       </c>
     </row>
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>와이즈플래닛컴퍼니</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>09-04~09-10</t>
+          <t>08-31~09-04</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>10,000~12,000</t>
+          <t>16,500~19,500</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>1,600,000</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>19,200,000,000</t>
+          <t>23,400,000,000</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>20.04배 (PER)</t>
+          <t>13.44 (PSR)</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>19,500</t>
         </is>
       </c>
       <c r="H53" s="6" t="n">
-        <v>1248.47</v>
+        <v>1187.74</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>2323</v>
+        <v>2181</v>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>09-14~09-15</t>
+          <t>09-08~09-09</t>
         </is>
       </c>
       <c r="K53" s="6" t="inlineStr"/>
@@ -11603,18 +11664,18 @@
       <c r="M53" s="6" t="inlineStr"/>
       <c r="N53" s="6" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>아이비케이투자증권</t>
         </is>
       </c>
       <c r="O53" s="6" t="inlineStr"/>
       <c r="P53" s="7" t="inlineStr">
         <is>
-          <t>494,400,000</t>
+          <t>713,790,000</t>
         </is>
       </c>
       <c r="Q53" s="6" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
@@ -12170,32 +12231,32 @@
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>엠비디</t>
+          <t>크리에이츠</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>09-21~09-29</t>
+          <t>10-12~10-16</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>9,400~11,500</t>
+          <t>15,000~18,000</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>1,400,000</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>18,800,000,000</t>
+          <t>21,000,000,000</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>26.87배 (PER)</t>
+          <t>19.15배 (PER)</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr"/>
@@ -12203,7 +12264,7 @@
       <c r="I62" s="6" t="inlineStr"/>
       <c r="J62" s="6" t="inlineStr">
         <is>
-          <t>10-06~10-07</t>
+          <t>10-20~10-21</t>
         </is>
       </c>
       <c r="K62" s="6" t="inlineStr"/>
@@ -12211,55 +12272,55 @@
       <c r="M62" s="6" t="inlineStr"/>
       <c r="N62" s="6" t="inlineStr">
         <is>
-          <t>하나증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="O62" s="6" t="inlineStr"/>
       <c r="P62" s="7" t="inlineStr">
         <is>
-          <t>968,200,000</t>
+          <t>865,200,000</t>
         </is>
       </c>
       <c r="Q62" s="6" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="R62" s="6" t="inlineStr">
         <is>
-          <t>최초</t>
+          <t>정정</t>
         </is>
       </c>
     </row>
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>엠에스바이오</t>
+          <t>엠비디</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>09-28~10-02</t>
+          <t>09-21~09-29</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>6,800~7,800</t>
+          <t>9,400~11,500</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>27,200,000,000</t>
+          <t>18,800,000,000</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>30.89배 (PER)</t>
+          <t>26.87배 (PER)</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr"/>
@@ -12267,7 +12328,7 @@
       <c r="I63" s="6" t="inlineStr"/>
       <c r="J63" s="6" t="inlineStr">
         <is>
-          <t>10-12~10-13</t>
+          <t>10-06~10-07</t>
         </is>
       </c>
       <c r="K63" s="6" t="inlineStr"/>
@@ -12275,18 +12336,18 @@
       <c r="M63" s="6" t="inlineStr"/>
       <c r="N63" s="6" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>하나증권</t>
         </is>
       </c>
       <c r="O63" s="6" t="inlineStr"/>
       <c r="P63" s="7" t="inlineStr">
         <is>
-          <t>1,120,640,000</t>
+          <t>968,200,000</t>
         </is>
       </c>
       <c r="Q63" s="6" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="R63" s="6" t="inlineStr">
@@ -12298,32 +12359,32 @@
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>티앤이코리아</t>
+          <t>엠에스바이오</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>10-07~10-14</t>
+          <t>09-28~10-02</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>12,600~15,300</t>
+          <t>6,800~7,800</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>2,400,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>30,240,000,000</t>
+          <t>27,200,000,000</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>19.48배 (PER)</t>
+          <t>30.89배 (PER)</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr"/>
@@ -12331,7 +12392,7 @@
       <c r="I64" s="6" t="inlineStr"/>
       <c r="J64" s="6" t="inlineStr">
         <is>
-          <t>10-20~10-21</t>
+          <t>10-12~10-13</t>
         </is>
       </c>
       <c r="K64" s="6" t="inlineStr"/>
@@ -12339,13 +12400,13 @@
       <c r="M64" s="6" t="inlineStr"/>
       <c r="N64" s="6" t="inlineStr">
         <is>
-          <t>신한투자증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="O64" s="6" t="inlineStr"/>
       <c r="P64" s="7" t="inlineStr">
         <is>
-          <t>1,245,888,000</t>
+          <t>1,120,640,000</t>
         </is>
       </c>
       <c r="Q64" s="6" t="inlineStr">
@@ -12362,7 +12423,7 @@
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>유캐스트</t>
+          <t>티앤이코리아</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
@@ -12372,22 +12433,22 @@
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>21,000~26,000</t>
+          <t>12,600~15,300</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>800,000</t>
+          <t>2,400,000</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>16,800,000,000</t>
+          <t>30,240,000,000</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>17.97배 (PER)</t>
+          <t>19.48배 (PER)</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr"/>
@@ -12395,7 +12456,7 @@
       <c r="I65" s="6" t="inlineStr"/>
       <c r="J65" s="6" t="inlineStr">
         <is>
-          <t>10-19~10-20</t>
+          <t>10-20~10-21</t>
         </is>
       </c>
       <c r="K65" s="6" t="inlineStr"/>
@@ -12403,18 +12464,18 @@
       <c r="M65" s="6" t="inlineStr"/>
       <c r="N65" s="6" t="inlineStr">
         <is>
-          <t>유진투자증권</t>
+          <t>신한투자증권</t>
         </is>
       </c>
       <c r="O65" s="6" t="inlineStr"/>
       <c r="P65" s="7" t="inlineStr">
         <is>
-          <t>1,181,280,000</t>
+          <t>1,245,888,000</t>
         </is>
       </c>
       <c r="Q65" s="6" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="R65" s="6" t="inlineStr">
@@ -12426,7 +12487,7 @@
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>다비오</t>
+          <t>유캐스트</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
@@ -12436,22 +12497,22 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>12,300~16,600</t>
+          <t>21,000~26,000</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>1,000,000</t>
+          <t>800,000</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>12,300,000,000</t>
+          <t>16,800,000,000</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>26.70배 (PER)</t>
+          <t>17.97배 (PER)</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr"/>
@@ -12467,18 +12528,18 @@
       <c r="M66" s="6" t="inlineStr"/>
       <c r="N66" s="6" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>유진투자증권</t>
         </is>
       </c>
       <c r="O66" s="6" t="inlineStr"/>
       <c r="P66" s="7" t="inlineStr">
         <is>
-          <t>570,105,000</t>
+          <t>1,181,280,000</t>
         </is>
       </c>
       <c r="Q66" s="6" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="R66" s="6" t="inlineStr">
@@ -12490,32 +12551,32 @@
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>크리에이츠</t>
+          <t>다비오</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>10-12~10-16</t>
+          <t>10-07~10-14</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>15,000~18,000</t>
+          <t>12,300~16,600</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>1,400,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>21,000,000,000</t>
+          <t>12,300,000,000</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>19.15배 (PER)</t>
+          <t>26.70배 (PER)</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr"/>
@@ -12523,7 +12584,7 @@
       <c r="I67" s="6" t="inlineStr"/>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t>10-20~10-21</t>
+          <t>10-19~10-20</t>
         </is>
       </c>
       <c r="K67" s="6" t="inlineStr"/>
@@ -12531,18 +12592,18 @@
       <c r="M67" s="6" t="inlineStr"/>
       <c r="N67" s="6" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="O67" s="6" t="inlineStr"/>
       <c r="P67" s="7" t="inlineStr">
         <is>
-          <t>865,200,000</t>
+          <t>570,105,000</t>
         </is>
       </c>
       <c r="Q67" s="6" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="R67" s="6" t="inlineStr">
@@ -12618,40 +12679,40 @@
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>바로팜</t>
-        </is>
-      </c>
-      <c r="B69" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>16,400~20,200</t>
+          <t>한화플러스제6호스팩</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>10-14~10-15</t>
+        </is>
+      </c>
+      <c r="C69" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>1,780,000</t>
+          <t>6,000,000</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>29,192,000,000</t>
-        </is>
-      </c>
-      <c r="F69" s="6" t="inlineStr">
-        <is>
-          <t>24.95배 (PER)</t>
+          <t>12,000,000,000</t>
+        </is>
+      </c>
+      <c r="F69" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr"/>
       <c r="H69" s="6" t="inlineStr"/>
       <c r="I69" s="6" t="inlineStr"/>
-      <c r="J69" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="J69" s="6" t="inlineStr">
+        <is>
+          <t>10-20~10-21</t>
         </is>
       </c>
       <c r="K69" s="6" t="inlineStr"/>
@@ -12668,9 +12729,9 @@
           <t>수집예정</t>
         </is>
       </c>
-      <c r="Q69" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="Q69" s="6" t="inlineStr">
+        <is>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="R69" s="6" t="inlineStr">
@@ -12682,12 +12743,12 @@
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>디티에스</t>
-        </is>
-      </c>
-      <c r="B70" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>아이엠스팩1호</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>10-19~10-20</t>
         </is>
       </c>
       <c r="C70" s="18" t="inlineStr">
@@ -12695,14 +12756,14 @@
           <t>수집예정</t>
         </is>
       </c>
-      <c r="D70" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="E70" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>5,000,000</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>10,000,000,000</t>
         </is>
       </c>
       <c r="F70" s="18" t="inlineStr">
@@ -12713,9 +12774,9 @@
       <c r="G70" s="6" t="inlineStr"/>
       <c r="H70" s="6" t="inlineStr"/>
       <c r="I70" s="6" t="inlineStr"/>
-      <c r="J70" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="J70" s="6" t="inlineStr">
+        <is>
+          <t>10-26~10-27</t>
         </is>
       </c>
       <c r="K70" s="6" t="inlineStr"/>
@@ -12732,21 +12793,21 @@
           <t>수집예정</t>
         </is>
       </c>
-      <c r="Q70" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="Q70" s="6" t="inlineStr">
+        <is>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="R70" s="6" t="inlineStr">
         <is>
-          <t>신고서 대기</t>
+          <t>최초</t>
         </is>
       </c>
     </row>
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>한화플러스제6호스팩</t>
+          <t>바로팜</t>
         </is>
       </c>
       <c r="B71" s="18" t="inlineStr">
@@ -12754,24 +12815,24 @@
           <t>수집예정</t>
         </is>
       </c>
-      <c r="C71" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="D71" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="E71" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="F71" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>16,400~20,200</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>1,780,000</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>29,192,000,000</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>24.95배 (PER)</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr"/>
@@ -12803,14 +12864,14 @@
       </c>
       <c r="R71" s="6" t="inlineStr">
         <is>
-          <t>신고서 대기</t>
+          <t>최초</t>
         </is>
       </c>
     </row>
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>하나에어로다이내믹스</t>
+          <t>디티에스</t>
         </is>
       </c>
       <c r="B72" s="18" t="inlineStr">
@@ -12874,7 +12935,7 @@
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>에이엔에이치스트럭쳐</t>
+          <t>하나에어로다이내믹스</t>
         </is>
       </c>
       <c r="B73" s="18" t="inlineStr">
@@ -12938,7 +12999,7 @@
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>아이엠스팩1호</t>
+          <t>에이엔에이치스트럭쳐</t>
         </is>
       </c>
       <c r="B74" s="18" t="inlineStr">
@@ -13255,22 +13316,150 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="20" t="inlineStr">
-        <is>
-          <t>※ 상장 완료 = KIND 신규상장 페이지 기준(스팩합병 포함) · 스팩 공모상장은 밴드·밸류에이션 등 해당없음(공모가 2,000원 고정).</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="20" t="inlineStr">
-        <is>
-          <t>※ 기재정정 신고서 내 정정 전·후 병존 → 자동수집은 "정정 후" 값만 취함.</t>
+    <row r="79" ht="30" customHeight="1">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>케이엠에프</t>
+        </is>
+      </c>
+      <c r="B79" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="C79" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="D79" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="E79" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="F79" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr"/>
+      <c r="H79" s="6" t="inlineStr"/>
+      <c r="I79" s="6" t="inlineStr"/>
+      <c r="J79" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="K79" s="6" t="inlineStr"/>
+      <c r="L79" s="6" t="inlineStr"/>
+      <c r="M79" s="6" t="inlineStr"/>
+      <c r="N79" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="O79" s="6" t="inlineStr"/>
+      <c r="P79" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="Q79" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="R79" s="6" t="inlineStr">
+        <is>
+          <t>신고서 대기</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="30" customHeight="1">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>넥스아이</t>
+        </is>
+      </c>
+      <c r="B80" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="C80" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="D80" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="E80" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="F80" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr"/>
+      <c r="H80" s="6" t="inlineStr"/>
+      <c r="I80" s="6" t="inlineStr"/>
+      <c r="J80" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="K80" s="6" t="inlineStr"/>
+      <c r="L80" s="6" t="inlineStr"/>
+      <c r="M80" s="6" t="inlineStr"/>
+      <c r="N80" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="O80" s="6" t="inlineStr"/>
+      <c r="P80" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="Q80" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="R80" s="6" t="inlineStr">
+        <is>
+          <t>신고서 대기</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="20" t="inlineStr">
+        <is>
+          <t>※ 상장 완료 = KIND 신규상장 페이지 기준(스팩합병 포함) · 스팩 공모상장은 밴드·밸류에이션 등 해당없음(공모가 2,000원 고정).</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="20" t="inlineStr">
+        <is>
+          <t>※ 기재정정 신고서 내 정정 전·후 병존 → 자동수집은 "정정 후" 값만 취함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="20" t="inlineStr">
         <is>
           <t>※ 청약경쟁률=일반투자자 청약수량÷최종배정수량 · "MM-DD~"는 종료일 자동수집 예정.</t>
         </is>
@@ -13547,10 +13736,10 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>0</v>

--- a/IPO_analysis.xlsx
+++ b/IPO_analysis.xlsx
@@ -592,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K137"/>
+  <dimension ref="A1:K138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -618,14 +618,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>기준일 2026-09-17 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
+          <t>기준일 2026-09-18 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>■ 심사 신청(진행중)  (44건)</t>
+          <t>■ 심사 신청(진행중)  (45건)</t>
         </is>
       </c>
       <c r="B4" s="4" t="n"/>
@@ -699,12 +699,12 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>노바셀테크놀로지</t>
+          <t>엠아이티</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -724,27 +724,27 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>14,921</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>-4,606</t>
+          <t>1,181</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>-15,458</t>
+          <t>28,026</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>키움</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
@@ -756,12 +756,12 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>(주)태석광학</t>
+          <t>큐로드</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -779,29 +779,17 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F7" s="7" t="inlineStr">
-        <is>
-          <t>79,804</t>
-        </is>
-      </c>
-      <c r="G7" s="7" t="inlineStr">
-        <is>
-          <t>4,721</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>7,228</t>
-        </is>
-      </c>
+      <c r="F7" s="7" t="inlineStr"/>
+      <c r="G7" s="7" t="inlineStr"/>
+      <c r="H7" s="7" t="inlineStr"/>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>생활용품 도매업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>신한, 대신</t>
+          <t>교보</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
@@ -813,12 +801,12 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>엑티브온</t>
+          <t>노바셀테크놀로지</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -828,7 +816,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -836,12 +824,24 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F8" s="7" t="inlineStr"/>
-      <c r="G8" s="7" t="inlineStr"/>
-      <c r="H8" s="7" t="inlineStr"/>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>377</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>-4,606</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
+          <t>-15,458</t>
+        </is>
+      </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>자연과학 및 공학 연구개발업</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
@@ -858,12 +858,12 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>씨앤엠</t>
+          <t>(주)태석광학</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -883,27 +883,27 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>238,489</t>
+          <t>79,804</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>19,869</t>
+          <t>4,721</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>112,262</t>
+          <t>7,228</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>전동기, 발전기 및 전기 변환 · 공급 · 제어 장치 제조업</t>
+          <t>생활용품 도매업</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>신한, 대신</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
@@ -915,22 +915,22 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>무신사</t>
+          <t>엑티브온</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>유가</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -938,29 +938,17 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>1,352,930</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>-10,571</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>243,731</t>
-        </is>
-      </c>
+      <c r="F10" s="7" t="inlineStr"/>
+      <c r="G10" s="7" t="inlineStr"/>
+      <c r="H10" s="7" t="inlineStr"/>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>섬유, 의복, 신발 및 가죽제품 소매업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>한국, 씨티그룹글로벌마켓증권(주), KB, 제이피모간증권회사 서울지점</t>
+          <t>키움</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
@@ -972,12 +960,12 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>마더스제약</t>
+          <t>씨앤엠</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -997,27 +985,27 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>228,830</t>
+          <t>238,489</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>11,204</t>
+          <t>19,869</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>57,394</t>
+          <t>112,262</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>의약품 제조업</t>
+          <t>전동기, 발전기 및 전기 변환 · 공급 · 제어 장치 제조업</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>NH, KB</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
@@ -1029,17 +1017,17 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>이나인페이</t>
+          <t>무신사</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>유가</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
@@ -1054,27 +1042,27 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>64,711</t>
+          <t>1,352,930</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>19,586</t>
+          <t>-10,571</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>79,855</t>
+          <t>243,731</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>섬유, 의복, 신발 및 가죽제품 소매업</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>한국, 씨티그룹글로벌마켓증권(주), KB, 제이피모간증권회사 서울지점</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
@@ -1086,12 +1074,12 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>어피닛</t>
+          <t>마더스제약</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1111,27 +1099,27 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>169,126</t>
+          <t>228,830</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>26,009</t>
+          <t>11,204</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>61,466</t>
+          <t>57,394</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>의약품 제조업</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>미래, 하나</t>
+          <t>NH, KB</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
@@ -1143,12 +1131,12 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>라이드플럭스</t>
+          <t>이나인페이</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -1168,27 +1156,27 @@
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>4,044</t>
+          <t>64,711</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>-31,423</t>
+          <t>19,586</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>-77,243</t>
+          <t>79,855</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>주식회사 우리투자증권, 한국</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
@@ -1200,12 +1188,12 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>신영스팩12호</t>
+          <t>어피닛</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -1223,17 +1211,29 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr"/>
-      <c r="G15" s="7" t="inlineStr"/>
-      <c r="H15" s="7" t="inlineStr"/>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>169,126</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>26,009</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>61,466</t>
+        </is>
+      </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>신영</t>
+          <t>미래, 하나</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
@@ -1245,12 +1245,12 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>우리투자제1호스팩</t>
+          <t>라이드플럭스</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -1268,17 +1268,29 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr"/>
-      <c r="G16" s="7" t="inlineStr"/>
-      <c r="H16" s="7" t="inlineStr"/>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>4,044</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>-31,423</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>-77,243</t>
+        </is>
+      </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>주식회사 우리투자증권</t>
+          <t>주식회사 우리투자증권, 한국</t>
         </is>
       </c>
       <c r="K16" s="6" t="inlineStr">
@@ -1290,17 +1302,17 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>에스텍시스템</t>
+          <t>신영스팩12호</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>유가</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -1313,29 +1325,17 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>975,224</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>24,647</t>
-        </is>
-      </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>237,182</t>
-        </is>
-      </c>
+      <c r="F17" s="7" t="inlineStr"/>
+      <c r="G17" s="7" t="inlineStr"/>
+      <c r="H17" s="7" t="inlineStr"/>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>경비, 경호 및 탐정업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>신영</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
@@ -1347,12 +1347,12 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>범한메카텍</t>
+          <t>우리투자제1호스팩</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -1370,29 +1370,17 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>339,209</t>
-        </is>
-      </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>-18,141</t>
-        </is>
-      </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>265,955</t>
-        </is>
-      </c>
+      <c r="F18" s="7" t="inlineStr"/>
+      <c r="G18" s="7" t="inlineStr"/>
+      <c r="H18" s="7" t="inlineStr"/>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>유진, NH</t>
+          <t>주식회사 우리투자증권</t>
         </is>
       </c>
       <c r="K18" s="6" t="inlineStr">
@@ -1404,17 +1392,17 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>케이티이</t>
+          <t>에스텍시스템</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>유가</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -1429,27 +1417,27 @@
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>173,901</t>
+          <t>975,224</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>14,243</t>
+          <t>24,647</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>94,928</t>
+          <t>237,182</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>전동기, 발전기 및 전기 변환 · 공급 · 제어 장치 제조업</t>
+          <t>경비, 경호 및 탐정업</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
@@ -1461,12 +1449,12 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>데스틴파워</t>
+          <t>범한메카텍</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -1486,27 +1474,27 @@
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>29,851</t>
+          <t>339,209</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>5,852</t>
+          <t>-18,141</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>-30,114</t>
+          <t>265,955</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>전동기, 발전기 및 전기 변환 · 공급 · 제어 장치 제조업</t>
+          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>유진, NH</t>
         </is>
       </c>
       <c r="K20" s="6" t="inlineStr">
@@ -1518,12 +1506,12 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>유림테크</t>
+          <t>케이티이</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1543,27 +1531,27 @@
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>102,586</t>
+          <t>173,901</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>-18,278</t>
+          <t>14,243</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>-4,832</t>
+          <t>94,928</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>자동차 신품 부품 제조업</t>
+          <t>전동기, 발전기 및 전기 변환 · 공급 · 제어 장치 제조업</t>
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
@@ -1575,12 +1563,12 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>솔리스</t>
+          <t>데스틴파워</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1590,7 +1578,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -1598,17 +1586,29 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr"/>
-      <c r="G22" s="7" t="inlineStr"/>
-      <c r="H22" s="7" t="inlineStr"/>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>29,851</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>5,852</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>-30,114</t>
+        </is>
+      </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>전동기, 발전기 및 전기 변환 · 공급 · 제어 장치 제조업</t>
         </is>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>한화</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K22" s="6" t="inlineStr">
@@ -1620,12 +1620,12 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>이노보테라퓨틱스</t>
+          <t>유림테크</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -1645,27 +1645,27 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>102,586</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>-5,429</t>
+          <t>-18,278</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>-53,200</t>
+          <t>-4,832</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>의약품 제조업</t>
+          <t>자동차 신품 부품 제조업</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
@@ -1677,22 +1677,22 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>에스에프씨</t>
+          <t>솔리스</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>유가</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -1700,29 +1700,17 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>160,792</t>
-        </is>
-      </c>
-      <c r="G24" s="7" t="inlineStr">
-        <is>
-          <t>25,509</t>
-        </is>
-      </c>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>243,562</t>
-        </is>
-      </c>
+      <c r="F24" s="7" t="inlineStr"/>
+      <c r="G24" s="7" t="inlineStr"/>
+      <c r="H24" s="7" t="inlineStr"/>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>미래, 한국</t>
+          <t>한화</t>
         </is>
       </c>
       <c r="K24" s="6" t="inlineStr">
@@ -1734,12 +1722,12 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>제논</t>
+          <t>이노보테라퓨틱스</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -1759,27 +1747,27 @@
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>11,744</t>
+          <t>209</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>1,139</t>
+          <t>-5,429</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>-1,220</t>
+          <t>-53,200</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>의약품 제조업</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
@@ -1791,17 +1779,17 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>아델</t>
+          <t>에스에프씨</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>유가</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1816,27 +1804,27 @@
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>62,057</t>
+          <t>160,792</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>-64,210</t>
+          <t>25,509</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>-80,776</t>
+          <t>243,562</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>그외 기타 전문, 과학 및 기술 서비스업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>삼성, 미래</t>
+          <t>미래, 한국</t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr">
@@ -1848,12 +1836,12 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>에버온</t>
+          <t>제논</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -1873,27 +1861,27 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>65,225</t>
+          <t>11,744</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>-3,606</t>
+          <t>1,139</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>54,955</t>
+          <t>-1,220</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>전기업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
@@ -1905,12 +1893,12 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>엔키화이트햇</t>
+          <t>아델</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -1930,27 +1918,27 @@
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>14,176</t>
+          <t>62,057</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>-3,211</t>
+          <t>-64,210</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>8,338</t>
+          <t>-80,776</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>그외 기타 전문, 과학 및 기술 서비스업</t>
         </is>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>신영</t>
+          <t>삼성, 미래</t>
         </is>
       </c>
       <c r="K28" s="6" t="inlineStr">
@@ -1962,12 +1950,12 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>씨아이에스케미칼</t>
+          <t>에버온</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
@@ -1987,27 +1975,27 @@
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>15,985</t>
+          <t>65,225</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>-11,440</t>
+          <t>-3,606</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>23,706</t>
+          <t>54,955</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>기초 화학물질 제조업</t>
+          <t>전기업</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
@@ -2019,12 +2007,12 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>엠디에스코리아</t>
+          <t>엔키화이트햇</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -2044,27 +2032,27 @@
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>97,972</t>
+          <t>14,176</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>6,512</t>
+          <t>-3,211</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>53,818</t>
+          <t>8,338</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>기타 식품 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>신영</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
@@ -2076,12 +2064,12 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>동승</t>
+          <t>씨아이에스케미칼</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -2101,27 +2089,27 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>78,625</t>
+          <t>15,985</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>14,525</t>
+          <t>-11,440</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>5,438</t>
+          <t>23,706</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>부동산 임대 및 공급업</t>
+          <t>기초 화학물질 제조업</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="K31" s="6" t="inlineStr">
@@ -2133,12 +2121,12 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>셀트릭스</t>
+          <t>엠디에스코리아</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -2148,7 +2136,7 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -2158,27 +2146,27 @@
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>16,976</t>
+          <t>97,972</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>4,545</t>
+          <t>6,512</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>2,213</t>
+          <t>53,818</t>
         </is>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>의료용품 및 기타 의약 관련제품 제조업</t>
+          <t>기타 식품 제조업</t>
         </is>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>IBK</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K32" s="6" t="inlineStr">
@@ -2195,7 +2183,7 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>에프엠더블유</t>
+          <t>동승</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -2205,7 +2193,7 @@
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
@@ -2215,27 +2203,27 @@
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>30,282</t>
+          <t>78,625</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>4,762</t>
+          <t>14,525</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>5,438</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>기타 식품 제조업</t>
+          <t>부동산 임대 및 공급업</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>유진</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
@@ -2247,22 +2235,22 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>소노인터내셔널</t>
+          <t>셀트릭스</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>유가</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -2272,27 +2260,27 @@
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>2,093,051</t>
+          <t>16,976</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>-148,064</t>
+          <t>4,545</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>852,372</t>
+          <t>2,213</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>일반 및 생활 숙박시설 운영업</t>
+          <t>의료용품 및 기타 의약 관련제품 제조업</t>
         </is>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>대신, 미래</t>
+          <t>IBK</t>
         </is>
       </c>
       <c r="K34" s="6" t="inlineStr">
@@ -2304,12 +2292,12 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>싸이몬</t>
+          <t>에프엠더블유</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
@@ -2319,7 +2307,7 @@
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
@@ -2329,27 +2317,27 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>48,695</t>
+          <t>30,282</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>15,714</t>
+          <t>4,762</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>61,761</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업</t>
+          <t>기타 식품 제조업</t>
         </is>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>유진</t>
         </is>
       </c>
       <c r="K35" s="6" t="inlineStr">
@@ -2361,17 +2349,17 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>바이다</t>
+          <t>소노인터내셔널</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>유가</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
@@ -2386,27 +2374,27 @@
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>14,432</t>
+          <t>2,093,051</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>-3,951</t>
+          <t>-148,064</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>15,108</t>
+          <t>852,372</t>
         </is>
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>전자부품 제조업</t>
+          <t>일반 및 생활 숙박시설 운영업</t>
         </is>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>대신, 미래</t>
         </is>
       </c>
       <c r="K36" s="6" t="inlineStr">
@@ -2418,12 +2406,12 @@
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>럭스코</t>
+          <t>싸이몬</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -2433,7 +2421,7 @@
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
@@ -2443,27 +2431,27 @@
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>67,976</t>
+          <t>48,695</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>6,893</t>
+          <t>15,714</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>61,761</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>전동기, 발전기 및 전기 변환 · 공급 · 제어 장치 제조업</t>
+          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업</t>
         </is>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>IBK</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
@@ -2475,12 +2463,12 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>아이알큐더스</t>
+          <t>바이다</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -2500,27 +2488,27 @@
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>10,231</t>
+          <t>14,432</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>-986</t>
+          <t>-3,951</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>1,800</t>
+          <t>15,108</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>전자부품 제조업</t>
         </is>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K38" s="6" t="inlineStr">
@@ -2532,12 +2520,12 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>영광</t>
+          <t>럭스코</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -2547,7 +2535,7 @@
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
@@ -2557,27 +2545,27 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>113,133</t>
+          <t>67,976</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>10,328</t>
+          <t>6,893</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>3,052</t>
+          <t>1,000</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
+          <t>전동기, 발전기 및 전기 변환 · 공급 · 제어 장치 제조업</t>
         </is>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>IBK</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr">
@@ -2589,12 +2577,12 @@
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>씨엔티테크</t>
+          <t>아이알큐더스</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -2614,17 +2602,17 @@
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>27,015</t>
+          <t>10,231</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>3,987</t>
+          <t>-986</t>
         </is>
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>2,613</t>
+          <t>1,800</t>
         </is>
       </c>
       <c r="I40" s="6" t="inlineStr">
@@ -2634,7 +2622,7 @@
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>한화, 하나</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="K40" s="6" t="inlineStr">
@@ -2651,7 +2639,7 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>제이앤티지</t>
+          <t>씨엔티테크</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -2671,27 +2659,27 @@
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>72,378</t>
+          <t>27,015</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>9,904</t>
+          <t>3,987</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>6,743</t>
+          <t>2,613</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>전자부품 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>대신, NH</t>
+          <t>한화, 하나</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
@@ -2703,12 +2691,12 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>인터엑스</t>
+          <t>제이앤티지</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -2728,27 +2716,27 @@
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>8,645</t>
+          <t>72,378</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>-20,272</t>
+          <t>9,904</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>4,530</t>
+          <t>6,743</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>전자부품 제조업</t>
         </is>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>대신, NH</t>
         </is>
       </c>
       <c r="K42" s="6" t="inlineStr">
@@ -2760,12 +2748,12 @@
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>삼홍아크튜리온</t>
+          <t>인터엑스</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -2785,27 +2773,27 @@
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>26,162</t>
+          <t>8,645</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>-10,314</t>
+          <t>-20,272</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>6,369</t>
+          <t>4,530</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>삼성, 미래</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
@@ -2817,12 +2805,12 @@
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>넥스트에어로스페이스</t>
+          <t>삼홍아크튜리온</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -2842,27 +2830,27 @@
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>12,084</t>
+          <t>26,162</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>-17,270</t>
+          <t>-10,314</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>6,158</t>
+          <t>6,369</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>유인 항공기, 항공우주선 및 보조장치 제조업</t>
+          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
         </is>
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>삼성, 미래</t>
         </is>
       </c>
       <c r="K44" s="6" t="inlineStr">
@@ -2879,7 +2867,7 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>비앤비코리아</t>
+          <t>넥스트에어로스페이스</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -2899,27 +2887,27 @@
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>141,169</t>
+          <t>12,084</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>21,406</t>
+          <t>-17,270</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>43,932</t>
+          <t>6,158</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>유인 항공기, 항공우주선 및 보조장치 제조업</t>
         </is>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K45" s="6" t="inlineStr">
@@ -2931,12 +2919,12 @@
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>오토핸즈</t>
+          <t>비앤비코리아</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -2946,7 +2934,7 @@
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E46" s="6" t="inlineStr">
@@ -2956,22 +2944,22 @@
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>238,564</t>
+          <t>141,169</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>6,047</t>
+          <t>21,406</t>
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>6,129</t>
+          <t>43,932</t>
         </is>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>자동차 판매업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="J46" s="6" t="inlineStr">
@@ -2988,12 +2976,12 @@
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>아이벡스메디칼시스템즈</t>
+          <t>오토핸즈</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -3003,7 +2991,7 @@
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
@@ -3013,27 +3001,27 @@
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>15,282</t>
+          <t>238,564</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>-7,227</t>
+          <t>6,047</t>
         </is>
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>6,129</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>자동차 판매업</t>
         </is>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K47" s="6" t="inlineStr">
@@ -3045,12 +3033,12 @@
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>옵토닉스</t>
+          <t>아이벡스메디칼시스템즈</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -3070,27 +3058,27 @@
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>25,368</t>
+          <t>15,282</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>1,901</t>
+          <t>-7,227</t>
         </is>
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>744</t>
         </is>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
-          <t>광학렌즈 및 광학요소 제조업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K48" s="6" t="inlineStr">
@@ -3102,188 +3090,188 @@
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
+          <t>2026-04-08</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>옵토닉스</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>신규상장</t>
+        </is>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
+        <is>
+          <t>FY25</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>25,368</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>1,901</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>730</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>광학렌즈 및 광학요소 제조업</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="K49" s="6" t="inlineStr">
+        <is>
+          <t>예심 진행중</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
           <t>2026-02-27</t>
         </is>
       </c>
-      <c r="B49" s="6" t="inlineStr">
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>피지티</t>
         </is>
       </c>
-      <c r="C49" s="6" t="inlineStr">
+      <c r="C50" s="6" t="inlineStr">
         <is>
           <t>코스닥</t>
         </is>
       </c>
-      <c r="D49" s="6" t="inlineStr">
+      <c r="D50" s="6" t="inlineStr">
         <is>
           <t>신규상장</t>
         </is>
       </c>
-      <c r="E49" s="6" t="inlineStr">
+      <c r="E50" s="6" t="inlineStr">
         <is>
           <t>FY25</t>
         </is>
       </c>
-      <c r="F49" s="7" t="inlineStr">
+      <c r="F50" s="7" t="inlineStr">
         <is>
           <t>40,141</t>
         </is>
       </c>
-      <c r="G49" s="7" t="inlineStr">
+      <c r="G50" s="7" t="inlineStr">
         <is>
           <t>-69,722</t>
         </is>
       </c>
-      <c r="H49" s="7" t="inlineStr">
+      <c r="H50" s="7" t="inlineStr">
         <is>
           <t>6,029</t>
         </is>
       </c>
-      <c r="I49" s="6" t="inlineStr">
+      <c r="I50" s="6" t="inlineStr">
         <is>
           <t>기타 화학제품 제조업</t>
         </is>
       </c>
-      <c r="J49" s="6" t="inlineStr">
+      <c r="J50" s="6" t="inlineStr">
         <is>
           <t>한국</t>
         </is>
       </c>
-      <c r="K49" s="6" t="inlineStr">
+      <c r="K50" s="6" t="inlineStr">
         <is>
           <t>예심 진행중</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
         <is>
           <t>■ 심사 승인  (64건)</t>
         </is>
       </c>
-      <c r="B51" s="4" t="n"/>
-      <c r="C51" s="4" t="n"/>
-      <c r="D51" s="4" t="n"/>
-      <c r="E51" s="4" t="n"/>
-      <c r="F51" s="4" t="n"/>
-      <c r="G51" s="4" t="n"/>
-      <c r="H51" s="4" t="n"/>
-      <c r="I51" s="4" t="n"/>
-      <c r="J51" s="4" t="n"/>
-      <c r="K51" s="4" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
+      <c r="B52" s="4" t="n"/>
+      <c r="C52" s="4" t="n"/>
+      <c r="D52" s="4" t="n"/>
+      <c r="E52" s="4" t="n"/>
+      <c r="F52" s="4" t="n"/>
+      <c r="G52" s="4" t="n"/>
+      <c r="H52" s="4" t="n"/>
+      <c r="I52" s="4" t="n"/>
+      <c r="J52" s="4" t="n"/>
+      <c r="K52" s="4" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>일자</t>
         </is>
       </c>
-      <c r="B52" s="5" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>회사명</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>시장</t>
         </is>
       </c>
-      <c r="D52" s="5" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>상장유형</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr">
+      <c r="E53" s="5" t="inlineStr">
         <is>
           <t>기준연도</t>
         </is>
       </c>
-      <c r="F52" s="5" t="inlineStr">
+      <c r="F53" s="5" t="inlineStr">
         <is>
           <t>매출액</t>
         </is>
       </c>
-      <c r="G52" s="5" t="inlineStr">
+      <c r="G53" s="5" t="inlineStr">
         <is>
           <t>순이익</t>
         </is>
       </c>
-      <c r="H52" s="5" t="inlineStr">
+      <c r="H53" s="5" t="inlineStr">
         <is>
           <t>자기자본</t>
         </is>
       </c>
-      <c r="I52" s="5" t="inlineStr">
+      <c r="I53" s="5" t="inlineStr">
         <is>
           <t>업종</t>
         </is>
       </c>
-      <c r="J52" s="5" t="inlineStr">
+      <c r="J53" s="5" t="inlineStr">
         <is>
           <t>대표주관사</t>
         </is>
       </c>
-      <c r="K52" s="5" t="inlineStr">
+      <c r="K53" s="5" t="inlineStr">
         <is>
           <t>현황</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-17</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>케이엠에프</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>코스닥</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>신규상장</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t>FY25</t>
-        </is>
-      </c>
-      <c r="F53" s="7" t="inlineStr">
-        <is>
-          <t>25,751</t>
-        </is>
-      </c>
-      <c r="G53" s="7" t="inlineStr">
-        <is>
-          <t>11,463</t>
-        </is>
-      </c>
-      <c r="H53" s="7" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="I53" s="6" t="inlineStr">
-        <is>
-          <t>기타 식품 제조업</t>
-        </is>
-      </c>
-      <c r="J53" s="6" t="inlineStr">
-        <is>
-          <t>IBK</t>
-        </is>
-      </c>
-      <c r="K53" s="6" t="inlineStr">
-        <is>
-          <t>상장전</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3283,7 @@
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>넥스아이</t>
+          <t>케이엠에프</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
@@ -3315,27 +3303,27 @@
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>5,110</t>
+          <t>25,751</t>
         </is>
       </c>
       <c r="G54" s="7" t="inlineStr">
         <is>
-          <t>-52,331</t>
+          <t>11,463</t>
         </is>
       </c>
       <c r="H54" s="7" t="inlineStr">
         <is>
-          <t>-82,348</t>
+          <t>642</t>
         </is>
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
-          <t>의약품 제조업</t>
+          <t>기타 식품 제조업</t>
         </is>
       </c>
       <c r="J54" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>IBK</t>
         </is>
       </c>
       <c r="K54" s="6" t="inlineStr">
@@ -3347,12 +3335,12 @@
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>영광와이케이엠씨</t>
+          <t>넥스아이</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -3372,27 +3360,27 @@
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>51,609</t>
+          <t>5,110</t>
         </is>
       </c>
       <c r="G55" s="7" t="inlineStr">
         <is>
-          <t>2,708</t>
+          <t>-52,331</t>
         </is>
       </c>
       <c r="H55" s="7" t="inlineStr">
         <is>
-          <t>28,213</t>
+          <t>-82,348</t>
         </is>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
-          <t>기타 금속 가공제품 제조업</t>
+          <t>의약품 제조업</t>
         </is>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K55" s="6" t="inlineStr">
@@ -3409,7 +3397,7 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>동원파츠</t>
+          <t>영광와이케이엠씨</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
@@ -3429,27 +3417,27 @@
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>92,255</t>
+          <t>51,609</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>3,443</t>
+          <t>2,708</t>
         </is>
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>27,535</t>
+          <t>28,213</t>
         </is>
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>기타 금속 가공제품 제조업</t>
         </is>
       </c>
       <c r="J56" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K56" s="6" t="inlineStr">
@@ -3461,12 +3449,12 @@
     <row r="57">
       <c r="A57" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>이에스티</t>
+          <t>동원파츠</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -3486,17 +3474,17 @@
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>33,190</t>
+          <t>92,255</t>
         </is>
       </c>
       <c r="G57" s="7" t="inlineStr">
         <is>
-          <t>2,966</t>
+          <t>3,443</t>
         </is>
       </c>
       <c r="H57" s="7" t="inlineStr">
         <is>
-          <t>4,325</t>
+          <t>27,535</t>
         </is>
       </c>
       <c r="I57" s="6" t="inlineStr">
@@ -3506,7 +3494,7 @@
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K57" s="6" t="inlineStr">
@@ -3523,7 +3511,7 @@
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>에이엘로봇</t>
+          <t>이에스티</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
@@ -3543,22 +3531,22 @@
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>14,985</t>
+          <t>33,190</t>
         </is>
       </c>
       <c r="G58" s="7" t="inlineStr">
         <is>
-          <t>-21,891</t>
+          <t>2,966</t>
         </is>
       </c>
       <c r="H58" s="7" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>4,325</t>
         </is>
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
-          <t>산업용 로봇 제조업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="J58" s="6" t="inlineStr">
@@ -3575,12 +3563,12 @@
     <row r="59">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>아이엠스팩1호</t>
+          <t>에이엘로봇</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
@@ -3598,17 +3586,29 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F59" s="7" t="inlineStr"/>
-      <c r="G59" s="7" t="inlineStr"/>
-      <c r="H59" s="7" t="inlineStr"/>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>14,985</t>
+        </is>
+      </c>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>-21,891</t>
+        </is>
+      </c>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>산업용 로봇 제조업</t>
         </is>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
-          <t>iM증권</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K59" s="6" t="inlineStr">
@@ -3620,12 +3620,12 @@
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>에이엔에이치스트럭쳐</t>
+          <t>아이엠스팩1호</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
@@ -3643,29 +3643,17 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F60" s="7" t="inlineStr">
-        <is>
-          <t>19,784</t>
-        </is>
-      </c>
-      <c r="G60" s="7" t="inlineStr">
-        <is>
-          <t>-4,296</t>
-        </is>
-      </c>
-      <c r="H60" s="7" t="inlineStr">
-        <is>
-          <t>24,561</t>
-        </is>
-      </c>
+      <c r="F60" s="7" t="inlineStr"/>
+      <c r="G60" s="7" t="inlineStr"/>
+      <c r="H60" s="7" t="inlineStr"/>
       <c r="I60" s="6" t="inlineStr">
         <is>
-          <t>건축기술, 엔지니어링 및 관련 기술 서비스업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>iM증권</t>
         </is>
       </c>
       <c r="K60" s="6" t="inlineStr">
@@ -3682,7 +3670,7 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>인텔리빅스</t>
+          <t>에이엔에이치스트럭쳐</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
@@ -3702,27 +3690,27 @@
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>46,644</t>
+          <t>19,784</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>5,357</t>
+          <t>-4,296</t>
         </is>
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>1,048</t>
+          <t>24,561</t>
         </is>
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>건축기술, 엔지니어링 및 관련 기술 서비스업</t>
         </is>
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K61" s="6" t="inlineStr">
@@ -3734,12 +3722,12 @@
     <row r="62">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>하나에어로다이내믹스</t>
+          <t>인텔리빅스</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
@@ -3759,27 +3747,27 @@
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>33,286</t>
+          <t>46,644</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>2,420</t>
+          <t>5,357</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>1,048</t>
         </is>
       </c>
       <c r="I62" s="6" t="inlineStr">
         <is>
-          <t>항공기,우주선 및 부품 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J62" s="6" t="inlineStr">
         <is>
-          <t>IBK</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K62" s="6" t="inlineStr">
@@ -3796,7 +3784,7 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>다비오</t>
+          <t>하나에어로다이내믹스</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
@@ -3816,27 +3804,27 @@
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>9,251</t>
+          <t>33,286</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>-3,473</t>
+          <t>2,420</t>
         </is>
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>890</t>
         </is>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>항공기,우주선 및 부품 제조업</t>
         </is>
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>IBK</t>
         </is>
       </c>
       <c r="K63" s="6" t="inlineStr">
@@ -3848,12 +3836,12 @@
     <row r="64">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>티앤이코리아</t>
+          <t>다비오</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
@@ -3873,27 +3861,27 @@
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>22,339</t>
+          <t>9,251</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>-7,091</t>
+          <t>-3,473</t>
         </is>
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
-          <t>일반 목적용 기계 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J64" s="6" t="inlineStr">
         <is>
-          <t>신한</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K64" s="6" t="inlineStr">
@@ -3910,7 +3898,7 @@
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>유캐스트</t>
+          <t>티앤이코리아</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
@@ -3930,27 +3918,27 @@
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>5,934</t>
+          <t>22,339</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>-3,557</t>
+          <t>-7,091</t>
         </is>
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
-          <t>1,881</t>
+          <t>481</t>
         </is>
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
-          <t>통신 및 방송 장비 제조업</t>
+          <t>일반 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
-          <t>유진</t>
+          <t>신한</t>
         </is>
       </c>
       <c r="K65" s="6" t="inlineStr">
@@ -3967,7 +3955,7 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>엘리스그룹</t>
+          <t>유캐스트</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
@@ -3987,27 +3975,27 @@
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>39,513</t>
+          <t>5,934</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>15,666</t>
+          <t>-3,557</t>
         </is>
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
-          <t>85,400</t>
+          <t>1,881</t>
         </is>
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>통신 및 방송 장비 제조업</t>
         </is>
       </c>
       <c r="J66" s="6" t="inlineStr">
         <is>
-          <t>미래, 삼성</t>
+          <t>유진</t>
         </is>
       </c>
       <c r="K66" s="6" t="inlineStr">
@@ -4019,12 +4007,12 @@
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>엘리스그룹</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
@@ -4034,7 +4022,7 @@
       </c>
       <c r="D67" s="6" t="inlineStr">
         <is>
-          <t>이전상장</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
@@ -4044,27 +4032,27 @@
       </c>
       <c r="F67" s="7" t="inlineStr">
         <is>
-          <t>48,646</t>
+          <t>39,513</t>
         </is>
       </c>
       <c r="G67" s="7" t="inlineStr">
         <is>
-          <t>6,017</t>
+          <t>15,666</t>
         </is>
       </c>
       <c r="H67" s="7" t="inlineStr">
         <is>
-          <t>18,795</t>
+          <t>85,400</t>
         </is>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t>하나</t>
+          <t>미래, 삼성</t>
         </is>
       </c>
       <c r="K67" s="6" t="inlineStr">
@@ -4081,7 +4069,7 @@
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>바로팜</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
@@ -4091,7 +4079,7 @@
       </c>
       <c r="D68" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>이전상장</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
@@ -4101,27 +4089,27 @@
       </c>
       <c r="F68" s="7" t="inlineStr">
         <is>
-          <t>96,724</t>
+          <t>48,646</t>
         </is>
       </c>
       <c r="G68" s="7" t="inlineStr">
         <is>
-          <t>-9,679</t>
+          <t>6,017</t>
         </is>
       </c>
       <c r="H68" s="7" t="inlineStr">
         <is>
-          <t>30,673</t>
+          <t>18,795</t>
         </is>
       </c>
       <c r="I68" s="6" t="inlineStr">
         <is>
-          <t>상품 중개업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="J68" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>하나</t>
         </is>
       </c>
       <c r="K68" s="6" t="inlineStr">
@@ -4138,7 +4126,7 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>크리에이츠</t>
+          <t>바로팜</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
@@ -4158,27 +4146,27 @@
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>76,395</t>
+          <t>96,724</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>23,749</t>
+          <t>-9,679</t>
         </is>
       </c>
       <c r="H69" s="7" t="inlineStr">
         <is>
-          <t>2,335</t>
+          <t>30,673</t>
         </is>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
-          <t>그외 기타 제품 제조업</t>
+          <t>상품 중개업</t>
         </is>
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K69" s="6" t="inlineStr">
@@ -4190,12 +4178,12 @@
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>래블업</t>
+          <t>크리에이츠</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
@@ -4215,27 +4203,27 @@
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>6,712</t>
+          <t>76,395</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>-1,526</t>
+          <t>23,749</t>
         </is>
       </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>2,335</t>
         </is>
       </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
-          <t>데이터베이스 및 온라인정보 제공업</t>
+          <t>그외 기타 제품 제조업</t>
         </is>
       </c>
       <c r="J70" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K70" s="6" t="inlineStr">
@@ -4252,7 +4240,7 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>래블업</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
@@ -4272,27 +4260,27 @@
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>39,319</t>
+          <t>6,712</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>4,739</t>
+          <t>-1,526</t>
         </is>
       </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
-          <t>1,250</t>
+          <t>373</t>
         </is>
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>데이터베이스 및 온라인정보 제공업</t>
         </is>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K71" s="6" t="inlineStr">
@@ -4309,7 +4297,7 @@
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>엠비디</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
@@ -4329,27 +4317,27 @@
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>1,524</t>
+          <t>39,319</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>-2,125</t>
+          <t>4,739</t>
         </is>
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
-          <t>2,753</t>
+          <t>1,250</t>
         </is>
       </c>
       <c r="I72" s="6" t="inlineStr">
         <is>
-          <t>물질 검사, 측정 및 분석기구 제조업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="J72" s="6" t="inlineStr">
         <is>
-          <t>하나</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K72" s="6" t="inlineStr">
@@ -4361,12 +4349,12 @@
     <row r="73">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>에스케이증권제14호기업인수목적</t>
+          <t>엠비디</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
@@ -4386,27 +4374,27 @@
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,524</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-2,125</t>
         </is>
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2,753</t>
         </is>
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>물질 검사, 측정 및 분석기구 제조업</t>
         </is>
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>하나</t>
         </is>
       </c>
       <c r="K73" s="6" t="inlineStr">
@@ -4423,7 +4411,7 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>케이비제34호스팩</t>
+          <t>에스케이증권제14호기업인수목적</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
@@ -4453,7 +4441,7 @@
       </c>
       <c r="H74" s="7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I74" s="6" t="inlineStr">
@@ -4463,7 +4451,7 @@
       </c>
       <c r="J74" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="K74" s="6" t="inlineStr">
@@ -4480,7 +4468,7 @@
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>한국제17호스팩</t>
+          <t>케이비제34호스팩</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
@@ -4510,7 +4498,7 @@
       </c>
       <c r="H75" s="7" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I75" s="6" t="inlineStr">
@@ -4520,12 +4508,12 @@
       </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="K75" s="6" t="inlineStr">
         <is>
-          <t>상장전</t>
+          <t>상장승인(상장예정)</t>
         </is>
       </c>
     </row>
@@ -4537,7 +4525,7 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>한화플러스제6호스팩</t>
+          <t>한국제17호스팩</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
@@ -4567,7 +4555,7 @@
       </c>
       <c r="H76" s="7" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I76" s="6" t="inlineStr">
@@ -4577,24 +4565,24 @@
       </c>
       <c r="J76" s="6" t="inlineStr">
         <is>
-          <t>한화</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K76" s="6" t="inlineStr">
         <is>
-          <t>상장전</t>
+          <t>상장승인(상장예정)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>엔에이치스팩34호</t>
+          <t>한화플러스제6호스팩</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
@@ -4624,34 +4612,34 @@
       </c>
       <c r="H77" s="7" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I77" s="6" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>한화</t>
         </is>
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-09-10)</t>
+          <t>상장전</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>글로벌테크놀로지</t>
+          <t>엔에이치스팩34호</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
@@ -4671,32 +4659,32 @@
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>29,689</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>-25,889</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H78" s="7" t="inlineStr">
         <is>
-          <t>6,402</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I78" s="6" t="inlineStr">
         <is>
-          <t>반도체 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="J78" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K78" s="6" t="inlineStr">
         <is>
-          <t>상장전</t>
+          <t>상장완료 (2026-09-10)</t>
         </is>
       </c>
     </row>
@@ -4708,7 +4696,7 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>글로벌테크놀로지</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
@@ -4723,32 +4711,32 @@
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>FY24</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>48,504</t>
+          <t>29,689</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr">
         <is>
-          <t>3,668</t>
+          <t>-25,889</t>
         </is>
       </c>
       <c r="H79" s="7" t="inlineStr">
         <is>
-          <t>8,448</t>
+          <t>6,402</t>
         </is>
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
-          <t>항공기,우주선 및 부품 제조업</t>
+          <t>반도체 제조업</t>
         </is>
       </c>
       <c r="J79" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K79" s="6" t="inlineStr">
@@ -4765,7 +4753,7 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>디티에스</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
@@ -4785,22 +4773,22 @@
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>142,718</t>
+          <t>48,504</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
-          <t>18,765</t>
+          <t>3,668</t>
         </is>
       </c>
       <c r="H80" s="7" t="inlineStr">
         <is>
-          <t>63,153</t>
+          <t>8,448</t>
         </is>
       </c>
       <c r="I80" s="6" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>항공기,우주선 및 부품 제조업</t>
         </is>
       </c>
       <c r="J80" s="6" t="inlineStr">
@@ -4817,12 +4805,12 @@
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>네오사피엔스</t>
+          <t>디티에스</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
@@ -4837,27 +4825,27 @@
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>FY25</t>
+          <t>FY24</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>10,649</t>
+          <t>142,718</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
         <is>
-          <t>-6,994</t>
+          <t>18,765</t>
         </is>
       </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
-          <t>-39,962</t>
+          <t>63,153</t>
         </is>
       </c>
       <c r="I81" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="J81" s="6" t="inlineStr">
@@ -4867,7 +4855,7 @@
       </c>
       <c r="K81" s="6" t="inlineStr">
         <is>
-          <t>상장승인(상장예정)</t>
+          <t>상장전</t>
         </is>
       </c>
     </row>
@@ -4879,7 +4867,7 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>엠에스바이오</t>
+          <t>네오사피엔스</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
@@ -4899,44 +4887,44 @@
       </c>
       <c r="F82" s="7" t="inlineStr">
         <is>
-          <t>23,787</t>
+          <t>10,649</t>
         </is>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
-          <t>7,288</t>
+          <t>-6,994</t>
         </is>
       </c>
       <c r="H82" s="7" t="inlineStr">
         <is>
-          <t>1,942</t>
+          <t>-39,962</t>
         </is>
       </c>
       <c r="I82" s="6" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J82" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K82" s="6" t="inlineStr">
         <is>
-          <t>상장전</t>
+          <t>상장승인(상장예정)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>기도산업</t>
+          <t>엠에스바이오</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
@@ -4956,32 +4944,32 @@
       </c>
       <c r="F83" s="7" t="inlineStr">
         <is>
-          <t>346,551</t>
+          <t>23,787</t>
         </is>
       </c>
       <c r="G83" s="7" t="inlineStr">
         <is>
-          <t>35,334</t>
+          <t>7,288</t>
         </is>
       </c>
       <c r="H83" s="7" t="inlineStr">
         <is>
-          <t>145,991</t>
+          <t>1,942</t>
         </is>
       </c>
       <c r="I83" s="6" t="inlineStr">
         <is>
-          <t>봉제의복 제조업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="K83" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-08-21)</t>
+          <t>상장전</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4981,7 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>브릴스</t>
+          <t>기도산업</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
@@ -5013,32 +5001,32 @@
       </c>
       <c r="F84" s="7" t="inlineStr">
         <is>
-          <t>23,759</t>
+          <t>346,551</t>
         </is>
       </c>
       <c r="G84" s="7" t="inlineStr">
         <is>
-          <t>1,744</t>
+          <t>35,334</t>
         </is>
       </c>
       <c r="H84" s="7" t="inlineStr">
         <is>
-          <t>4,785</t>
+          <t>145,991</t>
         </is>
       </c>
       <c r="I84" s="6" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>봉제의복 제조업</t>
         </is>
       </c>
       <c r="J84" s="6" t="inlineStr">
         <is>
-          <t>IBK</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K84" s="6" t="inlineStr">
         <is>
-          <t>상장전</t>
+          <t>상장완료 (2026-08-21)</t>
         </is>
       </c>
     </row>
@@ -5050,7 +5038,7 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>와이즈플래닛컴퍼니</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
@@ -5070,27 +5058,27 @@
       </c>
       <c r="F85" s="7" t="inlineStr">
         <is>
-          <t>44,578</t>
+          <t>23,759</t>
         </is>
       </c>
       <c r="G85" s="7" t="inlineStr">
         <is>
-          <t>7,748</t>
+          <t>1,744</t>
         </is>
       </c>
       <c r="H85" s="7" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>4,785</t>
         </is>
       </c>
       <c r="I85" s="6" t="inlineStr">
         <is>
-          <t>광고물 문안, 도안, 설계 등 작성업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="J85" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>IBK</t>
         </is>
       </c>
       <c r="K85" s="6" t="inlineStr">
@@ -5102,12 +5090,12 @@
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>니어스랩</t>
+          <t>와이즈플래닛컴퍼니</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
@@ -5127,32 +5115,32 @@
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
-          <t>6,361</t>
+          <t>44,578</t>
         </is>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
-          <t>-7,287</t>
+          <t>7,748</t>
         </is>
       </c>
       <c r="H86" s="7" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>959</t>
         </is>
       </c>
       <c r="I86" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>광고물 문안, 도안, 설계 등 작성업</t>
         </is>
       </c>
       <c r="J86" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K86" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-08-24)</t>
+          <t>상장전</t>
         </is>
       </c>
     </row>
@@ -5164,7 +5152,7 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>해치텍</t>
+          <t>니어스랩</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
@@ -5184,32 +5172,32 @@
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>14,079</t>
+          <t>6,361</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>-8,009</t>
+          <t>-7,287</t>
         </is>
       </c>
       <c r="H87" s="7" t="inlineStr">
         <is>
-          <t>2,229</t>
+          <t>127</t>
         </is>
       </c>
       <c r="I87" s="6" t="inlineStr">
         <is>
-          <t>반도체 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J87" s="6" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K87" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-08-25)</t>
+          <t>상장완료 (2026-08-24)</t>
         </is>
       </c>
     </row>
@@ -5221,7 +5209,7 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>해치텍</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
@@ -5241,44 +5229,44 @@
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
-          <t>7,936</t>
+          <t>14,079</t>
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>-62,995</t>
+          <t>-8,009</t>
         </is>
       </c>
       <c r="H88" s="7" t="inlineStr">
         <is>
-          <t>8,341</t>
+          <t>2,229</t>
         </is>
       </c>
       <c r="I88" s="6" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>반도체 제조업</t>
         </is>
       </c>
       <c r="J88" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="K88" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-09-04)</t>
+          <t>상장완료 (2026-08-25)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>에이치엘지노믹스</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
@@ -5298,32 +5286,32 @@
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>28,877</t>
+          <t>7,936</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr">
         <is>
-          <t>8,452</t>
+          <t>-62,995</t>
         </is>
       </c>
       <c r="H89" s="7" t="inlineStr">
         <is>
-          <t>83,552</t>
+          <t>8,341</t>
         </is>
       </c>
       <c r="I89" s="6" t="inlineStr">
         <is>
-          <t>기초 의약물질 제조업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="J89" s="6" t="inlineStr">
         <is>
-          <t>KB, IBK</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K89" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-07-24)</t>
+          <t>상장완료 (2026-09-04)</t>
         </is>
       </c>
     </row>
@@ -5335,7 +5323,7 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>딜리셔스</t>
+          <t>에이치엘지노믹스</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
@@ -5355,44 +5343,44 @@
       </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
-          <t>25,149</t>
+          <t>28,877</t>
         </is>
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>-20,419</t>
+          <t>8,452</t>
         </is>
       </c>
       <c r="H90" s="7" t="inlineStr">
         <is>
-          <t>-114,384</t>
+          <t>83,552</t>
         </is>
       </c>
       <c r="I90" s="6" t="inlineStr">
         <is>
-          <t>무점포 소매업</t>
+          <t>기초 의약물질 제조업</t>
         </is>
       </c>
       <c r="J90" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>KB, IBK</t>
         </is>
       </c>
       <c r="K90" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-08-12)</t>
+          <t>상장완료 (2026-07-24)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스</t>
+          <t>딜리셔스</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
@@ -5412,44 +5400,44 @@
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>2,588,400</t>
+          <t>25,149</t>
         </is>
       </c>
       <c r="G91" s="7" t="inlineStr">
         <is>
-          <t>15,755,864</t>
+          <t>-20,419</t>
         </is>
       </c>
       <c r="H91" s="7" t="inlineStr">
         <is>
-          <t>30,841,690</t>
+          <t>-114,384</t>
         </is>
       </c>
       <c r="I91" s="6" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>무점포 소매업</t>
         </is>
       </c>
       <c r="J91" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K91" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-08-18)</t>
+          <t>상장완료 (2026-08-12)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>한국제16호스팩</t>
+          <t>인제니아테라퓨틱스</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
@@ -5467,30 +5455,46 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F92" s="7" t="inlineStr"/>
-      <c r="G92" s="7" t="inlineStr"/>
-      <c r="H92" s="7" t="inlineStr"/>
-      <c r="I92" s="6" t="inlineStr"/>
+      <c r="F92" s="7" t="inlineStr">
+        <is>
+          <t>2,588,400</t>
+        </is>
+      </c>
+      <c r="G92" s="7" t="inlineStr">
+        <is>
+          <t>15,755,864</t>
+        </is>
+      </c>
+      <c r="H92" s="7" t="inlineStr">
+        <is>
+          <t>30,841,690</t>
+        </is>
+      </c>
+      <c r="I92" s="6" t="inlineStr">
+        <is>
+          <t>자연과학 및 공학 연구개발업</t>
+        </is>
+      </c>
       <c r="J92" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K92" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-06-30)</t>
+          <t>상장완료 (2026-08-18)</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>레메디</t>
+          <t>한국제16호스팩</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
@@ -5508,34 +5512,18 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F93" s="7" t="inlineStr">
-        <is>
-          <t>13,441</t>
-        </is>
-      </c>
-      <c r="G93" s="7" t="inlineStr">
-        <is>
-          <t>741</t>
-        </is>
-      </c>
-      <c r="H93" s="7" t="inlineStr">
-        <is>
-          <t>5,870</t>
-        </is>
-      </c>
-      <c r="I93" s="6" t="inlineStr">
-        <is>
-          <t>의료용 기기 제조업</t>
-        </is>
-      </c>
+      <c r="F93" s="7" t="inlineStr"/>
+      <c r="G93" s="7" t="inlineStr"/>
+      <c r="H93" s="7" t="inlineStr"/>
+      <c r="I93" s="6" t="inlineStr"/>
       <c r="J93" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K93" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-07-13)</t>
+          <t>상장완료 (2026-06-30)</t>
         </is>
       </c>
     </row>
@@ -5547,7 +5535,7 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>케이앤에스아이앤씨</t>
+          <t>레메디</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
@@ -5567,44 +5555,44 @@
       </c>
       <c r="F94" s="7" t="inlineStr">
         <is>
-          <t>13,482</t>
+          <t>13,441</t>
         </is>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
-          <t>-2,213</t>
+          <t>741</t>
         </is>
       </c>
       <c r="H94" s="7" t="inlineStr">
         <is>
-          <t>4,273</t>
+          <t>5,870</t>
         </is>
       </c>
       <c r="I94" s="6" t="inlineStr">
         <is>
-          <t>통신 및 방송 장비 제조업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="J94" s="6" t="inlineStr">
         <is>
-          <t>IBK</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="K94" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-08-13)</t>
+          <t>상장완료 (2026-07-13)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>메리츠제2호스팩</t>
+          <t>케이앤에스아이앤씨</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
@@ -5622,30 +5610,46 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F95" s="7" t="inlineStr"/>
-      <c r="G95" s="7" t="inlineStr"/>
-      <c r="H95" s="7" t="inlineStr"/>
-      <c r="I95" s="6" t="inlineStr"/>
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>13,482</t>
+        </is>
+      </c>
+      <c r="G95" s="7" t="inlineStr">
+        <is>
+          <t>-2,213</t>
+        </is>
+      </c>
+      <c r="H95" s="7" t="inlineStr">
+        <is>
+          <t>4,273</t>
+        </is>
+      </c>
+      <c r="I95" s="6" t="inlineStr">
+        <is>
+          <t>통신 및 방송 장비 제조업</t>
+        </is>
+      </c>
       <c r="J95" s="6" t="inlineStr">
         <is>
-          <t>메리츠</t>
+          <t>IBK</t>
         </is>
       </c>
       <c r="K95" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-06-19)</t>
+          <t>상장완료 (2026-08-13)</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>빅웨이브로보틱스</t>
+          <t>메리츠제2호스팩</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
@@ -5660,49 +5664,33 @@
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>FY24</t>
-        </is>
-      </c>
-      <c r="F96" s="7" t="inlineStr">
-        <is>
-          <t>13,851</t>
-        </is>
-      </c>
-      <c r="G96" s="7" t="inlineStr">
-        <is>
-          <t>-5,856</t>
-        </is>
-      </c>
-      <c r="H96" s="7" t="inlineStr">
-        <is>
-          <t>9,470</t>
-        </is>
-      </c>
-      <c r="I96" s="6" t="inlineStr">
-        <is>
-          <t>소프트웨어 개발 및 공급업</t>
-        </is>
-      </c>
+          <t>FY25</t>
+        </is>
+      </c>
+      <c r="F96" s="7" t="inlineStr"/>
+      <c r="G96" s="7" t="inlineStr"/>
+      <c r="H96" s="7" t="inlineStr"/>
+      <c r="I96" s="6" t="inlineStr"/>
       <c r="J96" s="6" t="inlineStr">
         <is>
-          <t>유진, 미래</t>
+          <t>메리츠</t>
         </is>
       </c>
       <c r="K96" s="6" t="inlineStr">
         <is>
-          <t>상장전</t>
+          <t>상장완료 (2026-06-19)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>매드업</t>
+          <t>빅웨이브로보틱스</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
@@ -5722,44 +5710,44 @@
       </c>
       <c r="F97" s="7" t="inlineStr">
         <is>
-          <t>34,989</t>
+          <t>13,851</t>
         </is>
       </c>
       <c r="G97" s="7" t="inlineStr">
         <is>
-          <t>-2,747</t>
+          <t>-5,856</t>
         </is>
       </c>
       <c r="H97" s="7" t="inlineStr">
         <is>
-          <t>-15,766</t>
+          <t>9,470</t>
         </is>
       </c>
       <c r="I97" s="6" t="inlineStr">
         <is>
-          <t>광고</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J97" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>유진, 미래</t>
         </is>
       </c>
       <c r="K97" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-07-01)</t>
+          <t>상장전</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>져스텍</t>
+          <t>매드업</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
@@ -5779,32 +5767,32 @@
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>19,851</t>
+          <t>34,989</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>-2,747</t>
         </is>
       </c>
       <c r="H98" s="7" t="inlineStr">
         <is>
-          <t>10,953</t>
+          <t>-15,766</t>
         </is>
       </c>
       <c r="I98" s="6" t="inlineStr">
         <is>
-          <t>기계</t>
+          <t>광고</t>
         </is>
       </c>
       <c r="J98" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K98" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-06-29)</t>
+          <t>상장완료 (2026-07-01)</t>
         </is>
       </c>
     </row>
@@ -5816,7 +5804,7 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>스트라드비젼</t>
+          <t>져스텍</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
@@ -5836,44 +5824,44 @@
       </c>
       <c r="F99" s="7" t="inlineStr">
         <is>
-          <t>11,539</t>
+          <t>19,851</t>
         </is>
       </c>
       <c r="G99" s="7" t="inlineStr">
         <is>
-          <t>-65,529</t>
+          <t>444</t>
         </is>
       </c>
       <c r="H99" s="7" t="inlineStr">
         <is>
-          <t>-245,151</t>
+          <t>10,953</t>
         </is>
       </c>
       <c r="I99" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어</t>
+          <t>기계</t>
         </is>
       </c>
       <c r="J99" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K99" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-06-30)</t>
+          <t>상장완료 (2026-06-29)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>대신밸런스제20호스팩</t>
+          <t>스트라드비젼</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
@@ -5888,33 +5876,49 @@
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>FY25</t>
-        </is>
-      </c>
-      <c r="F100" s="7" t="inlineStr"/>
-      <c r="G100" s="7" t="inlineStr"/>
-      <c r="H100" s="7" t="inlineStr"/>
-      <c r="I100" s="6" t="inlineStr"/>
+          <t>FY24</t>
+        </is>
+      </c>
+      <c r="F100" s="7" t="inlineStr">
+        <is>
+          <t>11,539</t>
+        </is>
+      </c>
+      <c r="G100" s="7" t="inlineStr">
+        <is>
+          <t>-65,529</t>
+        </is>
+      </c>
+      <c r="H100" s="7" t="inlineStr">
+        <is>
+          <t>-245,151</t>
+        </is>
+      </c>
+      <c r="I100" s="6" t="inlineStr">
+        <is>
+          <t>소프트웨어</t>
+        </is>
+      </c>
       <c r="J100" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-06-05)</t>
+          <t>상장완료 (2026-06-30)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>피스피스스튜디오</t>
+          <t>대신밸런스제20호스팩</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
@@ -5929,37 +5933,21 @@
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>FY24</t>
-        </is>
-      </c>
-      <c r="F101" s="7" t="inlineStr">
-        <is>
-          <t>113,777</t>
-        </is>
-      </c>
-      <c r="G101" s="7" t="inlineStr">
-        <is>
-          <t>17,603</t>
-        </is>
-      </c>
-      <c r="H101" s="7" t="inlineStr">
-        <is>
-          <t>55,861</t>
-        </is>
-      </c>
-      <c r="I101" s="6" t="inlineStr">
-        <is>
-          <t>섬유,의류,신발,호화품</t>
-        </is>
-      </c>
+          <t>FY25</t>
+        </is>
+      </c>
+      <c r="F101" s="7" t="inlineStr"/>
+      <c r="G101" s="7" t="inlineStr"/>
+      <c r="H101" s="7" t="inlineStr"/>
+      <c r="I101" s="6" t="inlineStr"/>
       <c r="J101" s="6" t="inlineStr">
         <is>
-          <t>NH, 미래</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K101" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-06-08)</t>
+          <t>상장완료 (2026-06-05)</t>
         </is>
       </c>
     </row>
@@ -5971,7 +5959,7 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>폴레드</t>
+          <t>피스피스스튜디오</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
@@ -5991,32 +5979,32 @@
       </c>
       <c r="F102" s="7" t="inlineStr">
         <is>
-          <t>52,808</t>
+          <t>113,777</t>
         </is>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>17,603</t>
         </is>
       </c>
       <c r="H102" s="7" t="inlineStr">
         <is>
-          <t>25,416</t>
+          <t>55,861</t>
         </is>
       </c>
       <c r="I102" s="6" t="inlineStr">
         <is>
-          <t>가정용기기와용품</t>
+          <t>섬유,의류,신발,호화품</t>
         </is>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>NH, 미래</t>
         </is>
       </c>
       <c r="K102" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-05-14)</t>
+          <t>상장완료 (2026-06-08)</t>
         </is>
       </c>
     </row>
@@ -6028,7 +6016,7 @@
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>레몬헬스케어</t>
+          <t>폴레드</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
@@ -6048,44 +6036,44 @@
       </c>
       <c r="F103" s="7" t="inlineStr">
         <is>
-          <t>14,877</t>
+          <t>52,808</t>
         </is>
       </c>
       <c r="G103" s="7" t="inlineStr">
         <is>
-          <t>-2,898</t>
+          <t>543</t>
         </is>
       </c>
       <c r="H103" s="7" t="inlineStr">
         <is>
-          <t>-31,162</t>
+          <t>25,416</t>
         </is>
       </c>
       <c r="I103" s="6" t="inlineStr">
         <is>
-          <t>건강관리업체및서비스</t>
+          <t>가정용기기와용품</t>
         </is>
       </c>
       <c r="J103" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K103" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-07-06)</t>
+          <t>상장완료 (2026-05-14)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>마키나락스</t>
+          <t>레몬헬스케어</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
@@ -6105,32 +6093,32 @@
       </c>
       <c r="F104" s="7" t="inlineStr">
         <is>
-          <t>8,294</t>
+          <t>14,877</t>
         </is>
       </c>
       <c r="G104" s="7" t="inlineStr">
         <is>
-          <t>-6,073</t>
+          <t>-2,898</t>
         </is>
       </c>
       <c r="H104" s="7" t="inlineStr">
         <is>
-          <t>2,680</t>
+          <t>-31,162</t>
         </is>
       </c>
       <c r="I104" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어</t>
+          <t>건강관리업체및서비스</t>
         </is>
       </c>
       <c r="J104" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="K104" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-05-20)</t>
+          <t>상장완료 (2026-07-06)</t>
         </is>
       </c>
     </row>
@@ -6142,7 +6130,7 @@
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>채비</t>
+          <t>마키나락스</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
@@ -6162,44 +6150,44 @@
       </c>
       <c r="F105" s="7" t="inlineStr">
         <is>
-          <t>85,082</t>
+          <t>8,294</t>
         </is>
       </c>
       <c r="G105" s="7" t="inlineStr">
         <is>
-          <t>-54,495</t>
+          <t>-6,073</t>
         </is>
       </c>
       <c r="H105" s="7" t="inlineStr">
         <is>
-          <t>96,866</t>
+          <t>2,680</t>
         </is>
       </c>
       <c r="I105" s="6" t="inlineStr">
         <is>
-          <t>전기제품</t>
+          <t>소프트웨어</t>
         </is>
       </c>
       <c r="J105" s="6" t="inlineStr">
         <is>
-          <t>KB, 삼성, 대신, 하나</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K105" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-04-29)</t>
+          <t>상장완료 (2026-05-20)</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>키움히어로제2호스팩</t>
+          <t>채비</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
@@ -6217,30 +6205,46 @@
           <t>FY24</t>
         </is>
       </c>
-      <c r="F106" s="7" t="inlineStr"/>
-      <c r="G106" s="7" t="inlineStr"/>
-      <c r="H106" s="7" t="inlineStr"/>
-      <c r="I106" s="6" t="inlineStr"/>
+      <c r="F106" s="7" t="inlineStr">
+        <is>
+          <t>85,082</t>
+        </is>
+      </c>
+      <c r="G106" s="7" t="inlineStr">
+        <is>
+          <t>-54,495</t>
+        </is>
+      </c>
+      <c r="H106" s="7" t="inlineStr">
+        <is>
+          <t>96,866</t>
+        </is>
+      </c>
+      <c r="I106" s="6" t="inlineStr">
+        <is>
+          <t>전기제품</t>
+        </is>
+      </c>
       <c r="J106" s="6" t="inlineStr">
         <is>
-          <t>키움</t>
+          <t>KB, 삼성, 대신, 하나</t>
         </is>
       </c>
       <c r="K106" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-04-23)</t>
+          <t>상장완료 (2026-04-29)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>세미티에스</t>
+          <t>키움히어로제2호스팩</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
@@ -6250,7 +6254,7 @@
       </c>
       <c r="D107" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E107" s="6" t="inlineStr">
@@ -6258,46 +6262,30 @@
           <t>FY24</t>
         </is>
       </c>
-      <c r="F107" s="7" t="inlineStr">
-        <is>
-          <t>20,808</t>
-        </is>
-      </c>
-      <c r="G107" s="7" t="inlineStr">
-        <is>
-          <t>7,337</t>
-        </is>
-      </c>
-      <c r="H107" s="7" t="inlineStr">
-        <is>
-          <t>26,616</t>
-        </is>
-      </c>
-      <c r="I107" s="6" t="inlineStr">
-        <is>
-          <t>반도체와반도체장비</t>
-        </is>
-      </c>
+      <c r="F107" s="7" t="inlineStr"/>
+      <c r="G107" s="7" t="inlineStr"/>
+      <c r="H107" s="7" t="inlineStr"/>
+      <c r="I107" s="6" t="inlineStr"/>
       <c r="J107" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>키움</t>
         </is>
       </c>
       <c r="K107" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-02-05)</t>
+          <t>상장완료 (2026-04-23)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>교보20호스팩</t>
+          <t>세미티에스</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
@@ -6307,7 +6295,7 @@
       </c>
       <c r="D108" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E108" s="6" t="inlineStr">
@@ -6315,30 +6303,46 @@
           <t>FY24</t>
         </is>
       </c>
-      <c r="F108" s="7" t="inlineStr"/>
-      <c r="G108" s="7" t="inlineStr"/>
-      <c r="H108" s="7" t="inlineStr"/>
-      <c r="I108" s="6" t="inlineStr"/>
+      <c r="F108" s="7" t="inlineStr">
+        <is>
+          <t>20,808</t>
+        </is>
+      </c>
+      <c r="G108" s="7" t="inlineStr">
+        <is>
+          <t>7,337</t>
+        </is>
+      </c>
+      <c r="H108" s="7" t="inlineStr">
+        <is>
+          <t>26,616</t>
+        </is>
+      </c>
+      <c r="I108" s="6" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
       <c r="J108" s="6" t="inlineStr">
         <is>
-          <t>교보</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K108" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-04-02)</t>
+          <t>상장완료 (2026-02-05)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="6" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>케이피항공산업</t>
+          <t>교보20호스팩</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
@@ -6348,7 +6352,7 @@
       </c>
       <c r="D109" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E109" s="6" t="inlineStr">
@@ -6356,34 +6360,18 @@
           <t>FY24</t>
         </is>
       </c>
-      <c r="F109" s="7" t="inlineStr">
-        <is>
-          <t>49,651</t>
-        </is>
-      </c>
-      <c r="G109" s="7" t="inlineStr">
-        <is>
-          <t>3,018</t>
-        </is>
-      </c>
-      <c r="H109" s="7" t="inlineStr">
-        <is>
-          <t>15,901</t>
-        </is>
-      </c>
-      <c r="I109" s="6" t="inlineStr">
-        <is>
-          <t>우주항공과국방</t>
-        </is>
-      </c>
+      <c r="F109" s="7" t="inlineStr"/>
+      <c r="G109" s="7" t="inlineStr"/>
+      <c r="H109" s="7" t="inlineStr"/>
+      <c r="I109" s="6" t="inlineStr"/>
       <c r="J109" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>교보</t>
         </is>
       </c>
       <c r="K109" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-01-29)</t>
+          <t>상장완료 (2026-04-02)</t>
         </is>
       </c>
     </row>
@@ -6395,7 +6383,7 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>한패스</t>
+          <t>케이피항공산업</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
@@ -6405,7 +6393,7 @@
       </c>
       <c r="D110" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E110" s="6" t="inlineStr">
@@ -6415,44 +6403,44 @@
       </c>
       <c r="F110" s="7" t="inlineStr">
         <is>
-          <t>55,297</t>
+          <t>49,651</t>
         </is>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
-          <t>4,403</t>
+          <t>3,018</t>
         </is>
       </c>
       <c r="H110" s="7" t="inlineStr">
         <is>
-          <t>-28,065</t>
+          <t>15,901</t>
         </is>
       </c>
       <c r="I110" s="6" t="inlineStr">
         <is>
-          <t>IT서비스</t>
+          <t>우주항공과국방</t>
         </is>
       </c>
       <c r="J110" s="6" t="inlineStr">
         <is>
-          <t>한국, 대신</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K110" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-03-25)</t>
+          <t>상장완료 (2026-01-29)</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="6" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>신한제18호스팩</t>
+          <t>한패스</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
@@ -6470,30 +6458,46 @@
           <t>FY24</t>
         </is>
       </c>
-      <c r="F111" s="7" t="inlineStr"/>
-      <c r="G111" s="7" t="inlineStr"/>
-      <c r="H111" s="7" t="inlineStr"/>
-      <c r="I111" s="6" t="inlineStr"/>
+      <c r="F111" s="7" t="inlineStr">
+        <is>
+          <t>55,297</t>
+        </is>
+      </c>
+      <c r="G111" s="7" t="inlineStr">
+        <is>
+          <t>4,403</t>
+        </is>
+      </c>
+      <c r="H111" s="7" t="inlineStr">
+        <is>
+          <t>-28,065</t>
+        </is>
+      </c>
+      <c r="I111" s="6" t="inlineStr">
+        <is>
+          <t>IT서비스</t>
+        </is>
+      </c>
       <c r="J111" s="6" t="inlineStr">
         <is>
-          <t>신한</t>
+          <t>한국, 대신</t>
         </is>
       </c>
       <c r="K111" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-04-30)</t>
+          <t>상장완료 (2026-03-25)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>엔에이치스팩33호</t>
+          <t>신한제18호스팩</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
@@ -6517,24 +6521,24 @@
       <c r="I112" s="6" t="inlineStr"/>
       <c r="J112" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>신한</t>
         </is>
       </c>
       <c r="K112" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-03-27)</t>
+          <t>상장완료 (2026-04-30)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="6" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>신한제17호스팩</t>
+          <t>엔에이치스팩33호</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
@@ -6558,24 +6562,24 @@
       <c r="I113" s="6" t="inlineStr"/>
       <c r="J113" s="6" t="inlineStr">
         <is>
-          <t>신한</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K113" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-04-01)</t>
+          <t>상장완료 (2026-03-27)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>아이엠바이오로직스</t>
+          <t>신한제17호스팩</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
@@ -6593,34 +6597,18 @@
           <t>FY24</t>
         </is>
       </c>
-      <c r="F114" s="7" t="inlineStr">
-        <is>
-          <t>27,594</t>
-        </is>
-      </c>
-      <c r="G114" s="7" t="inlineStr">
-        <is>
-          <t>-11,884</t>
-        </is>
-      </c>
-      <c r="H114" s="7" t="inlineStr">
-        <is>
-          <t>-77,202</t>
-        </is>
-      </c>
-      <c r="I114" s="6" t="inlineStr">
-        <is>
-          <t>제약</t>
-        </is>
-      </c>
+      <c r="F114" s="7" t="inlineStr"/>
+      <c r="G114" s="7" t="inlineStr"/>
+      <c r="H114" s="7" t="inlineStr"/>
+      <c r="I114" s="6" t="inlineStr"/>
       <c r="J114" s="6" t="inlineStr">
         <is>
-          <t>한국, 신한</t>
+          <t>신한</t>
         </is>
       </c>
       <c r="K114" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-03-20)</t>
+          <t>상장완료 (2026-04-01)</t>
         </is>
       </c>
     </row>
@@ -6632,7 +6620,7 @@
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>에스팀</t>
+          <t>아이엠바이오로직스</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
@@ -6652,232 +6640,232 @@
       </c>
       <c r="F115" s="7" t="inlineStr">
         <is>
-          <t>35,574</t>
+          <t>27,594</t>
         </is>
       </c>
       <c r="G115" s="7" t="inlineStr">
         <is>
-          <t>1,372</t>
+          <t>-11,884</t>
         </is>
       </c>
       <c r="H115" s="7" t="inlineStr">
         <is>
-          <t>12,331</t>
+          <t>-77,202</t>
         </is>
       </c>
       <c r="I115" s="6" t="inlineStr">
         <is>
-          <t>광고</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="J115" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>한국, 신한</t>
         </is>
       </c>
       <c r="K115" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-03-06)</t>
+          <t>상장완료 (2026-03-20)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
         <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>에스팀</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="inlineStr">
+        <is>
+          <t>신규상장</t>
+        </is>
+      </c>
+      <c r="E116" s="6" t="inlineStr">
+        <is>
+          <t>FY24</t>
+        </is>
+      </c>
+      <c r="F116" s="7" t="inlineStr">
+        <is>
+          <t>35,574</t>
+        </is>
+      </c>
+      <c r="G116" s="7" t="inlineStr">
+        <is>
+          <t>1,372</t>
+        </is>
+      </c>
+      <c r="H116" s="7" t="inlineStr">
+        <is>
+          <t>12,331</t>
+        </is>
+      </c>
+      <c r="I116" s="6" t="inlineStr">
+        <is>
+          <t>광고</t>
+        </is>
+      </c>
+      <c r="J116" s="6" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="K116" s="6" t="inlineStr">
+        <is>
+          <t>상장완료 (2026-03-06)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="6" t="inlineStr">
+        <is>
           <t>2026-01-12</t>
         </is>
       </c>
-      <c r="B116" s="6" t="inlineStr">
+      <c r="B117" s="6" t="inlineStr">
         <is>
           <t>케이뱅크</t>
         </is>
       </c>
-      <c r="C116" s="6" t="inlineStr">
+      <c r="C117" s="6" t="inlineStr">
         <is>
           <t>유가</t>
         </is>
       </c>
-      <c r="D116" s="6" t="inlineStr">
+      <c r="D117" s="6" t="inlineStr">
         <is>
           <t>신규상장</t>
         </is>
       </c>
-      <c r="E116" s="6" t="inlineStr">
+      <c r="E117" s="6" t="inlineStr">
         <is>
           <t>FY24</t>
         </is>
       </c>
-      <c r="F116" s="7" t="inlineStr">
+      <c r="F117" s="7" t="inlineStr">
         <is>
           <t>1,228,501</t>
         </is>
       </c>
-      <c r="G116" s="7" t="inlineStr">
+      <c r="G117" s="7" t="inlineStr">
         <is>
           <t>128,053</t>
         </is>
       </c>
-      <c r="H116" s="7" t="inlineStr">
+      <c r="H117" s="7" t="inlineStr">
         <is>
           <t>1,995,845</t>
         </is>
       </c>
-      <c r="I116" s="6" t="inlineStr">
+      <c r="I117" s="6" t="inlineStr">
         <is>
           <t>은행</t>
         </is>
       </c>
-      <c r="J116" s="6" t="inlineStr">
+      <c r="J117" s="6" t="inlineStr">
         <is>
           <t>NH, 삼성</t>
         </is>
       </c>
-      <c r="K116" s="6" t="inlineStr">
+      <c r="K117" s="6" t="inlineStr">
         <is>
           <t>상장완료 (2026-03-05)</t>
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="3" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
         <is>
           <t>■ 철회·미승인  (18건)</t>
         </is>
       </c>
-      <c r="B118" s="4" t="n"/>
-      <c r="C118" s="4" t="n"/>
-      <c r="D118" s="4" t="n"/>
-      <c r="E118" s="4" t="n"/>
-      <c r="F118" s="4" t="n"/>
-      <c r="G118" s="4" t="n"/>
-      <c r="H118" s="4" t="n"/>
-      <c r="I118" s="4" t="n"/>
-      <c r="J118" s="4" t="n"/>
-      <c r="K118" s="4" t="n"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="5" t="inlineStr">
+      <c r="B119" s="4" t="n"/>
+      <c r="C119" s="4" t="n"/>
+      <c r="D119" s="4" t="n"/>
+      <c r="E119" s="4" t="n"/>
+      <c r="F119" s="4" t="n"/>
+      <c r="G119" s="4" t="n"/>
+      <c r="H119" s="4" t="n"/>
+      <c r="I119" s="4" t="n"/>
+      <c r="J119" s="4" t="n"/>
+      <c r="K119" s="4" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr">
         <is>
           <t>일자</t>
         </is>
       </c>
-      <c r="B119" s="5" t="inlineStr">
+      <c r="B120" s="5" t="inlineStr">
         <is>
           <t>회사명</t>
         </is>
       </c>
-      <c r="C119" s="5" t="inlineStr">
+      <c r="C120" s="5" t="inlineStr">
         <is>
           <t>시장</t>
         </is>
       </c>
-      <c r="D119" s="5" t="inlineStr">
+      <c r="D120" s="5" t="inlineStr">
         <is>
           <t>상장유형</t>
         </is>
       </c>
-      <c r="E119" s="5" t="inlineStr">
+      <c r="E120" s="5" t="inlineStr">
         <is>
           <t>기준연도</t>
         </is>
       </c>
-      <c r="F119" s="5" t="inlineStr">
+      <c r="F120" s="5" t="inlineStr">
         <is>
           <t>매출액</t>
         </is>
       </c>
-      <c r="G119" s="5" t="inlineStr">
+      <c r="G120" s="5" t="inlineStr">
         <is>
           <t>순이익</t>
         </is>
       </c>
-      <c r="H119" s="5" t="inlineStr">
+      <c r="H120" s="5" t="inlineStr">
         <is>
           <t>자기자본</t>
         </is>
       </c>
-      <c r="I119" s="5" t="inlineStr">
+      <c r="I120" s="5" t="inlineStr">
         <is>
           <t>업종</t>
         </is>
       </c>
-      <c r="J119" s="5" t="inlineStr">
+      <c r="J120" s="5" t="inlineStr">
         <is>
           <t>대표주관사</t>
         </is>
       </c>
-      <c r="K119" s="5" t="inlineStr">
+      <c r="K120" s="5" t="inlineStr">
         <is>
           <t>현황</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B120" s="6" t="inlineStr">
-        <is>
-          <t>텔레픽스</t>
-        </is>
-      </c>
-      <c r="C120" s="6" t="inlineStr">
-        <is>
-          <t>코스닥</t>
-        </is>
-      </c>
-      <c r="D120" s="6" t="inlineStr">
-        <is>
-          <t>신규상장</t>
-        </is>
-      </c>
-      <c r="E120" s="6" t="inlineStr">
-        <is>
-          <t>FY25</t>
-        </is>
-      </c>
-      <c r="F120" s="7" t="inlineStr">
-        <is>
-          <t>4,896</t>
-        </is>
-      </c>
-      <c r="G120" s="7" t="inlineStr">
-        <is>
-          <t>-16,214</t>
-        </is>
-      </c>
-      <c r="H120" s="7" t="inlineStr">
-        <is>
-          <t>9,146</t>
-        </is>
-      </c>
-      <c r="I120" s="6" t="inlineStr">
-        <is>
-          <t>소프트웨어 개발 및 공급업</t>
-        </is>
-      </c>
-      <c r="J120" s="6" t="inlineStr">
-        <is>
-          <t>미래</t>
-        </is>
-      </c>
-      <c r="K120" s="6" t="inlineStr">
-        <is>
-          <t>심사 철회</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>씨엠디엘</t>
+          <t>텔레픽스</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
@@ -6887,37 +6875,37 @@
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E121" s="6" t="inlineStr">
         <is>
-          <t>FY24</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="F121" s="7" t="inlineStr">
         <is>
-          <t>39,991</t>
+          <t>4,896</t>
         </is>
       </c>
       <c r="G121" s="7" t="inlineStr">
         <is>
-          <t>3,541</t>
+          <t>-16,214</t>
         </is>
       </c>
       <c r="H121" s="7" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>9,146</t>
         </is>
       </c>
       <c r="I121" s="6" t="inlineStr">
         <is>
-          <t>기타 기초 유기 화학물질 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J121" s="6" t="inlineStr">
         <is>
-          <t>교보</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K121" s="6" t="inlineStr">
@@ -6929,12 +6917,12 @@
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>모비어스</t>
+          <t>씨엠디엘</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
@@ -6944,37 +6932,37 @@
       </c>
       <c r="D122" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E122" s="6" t="inlineStr">
         <is>
-          <t>FY25</t>
+          <t>FY24</t>
         </is>
       </c>
       <c r="F122" s="7" t="inlineStr">
         <is>
-          <t>31,989</t>
+          <t>39,991</t>
         </is>
       </c>
       <c r="G122" s="7" t="inlineStr">
         <is>
-          <t>-45,307</t>
+          <t>3,541</t>
         </is>
       </c>
       <c r="H122" s="7" t="inlineStr">
         <is>
-          <t>-96,707</t>
+          <t>503</t>
         </is>
       </c>
       <c r="I122" s="6" t="inlineStr">
         <is>
-          <t>컴퓨터 프로그래밍, 시스템 통합 및 관리업</t>
+          <t>기타 기초 유기 화학물질 제조업</t>
         </is>
       </c>
       <c r="J122" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>교보</t>
         </is>
       </c>
       <c r="K122" s="6" t="inlineStr">
@@ -6986,12 +6974,12 @@
     <row r="123">
       <c r="A123" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>넥스트젠바이오</t>
+          <t>모비어스</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
@@ -7006,32 +6994,32 @@
       </c>
       <c r="E123" s="6" t="inlineStr">
         <is>
-          <t>FY24</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="F123" s="7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>31,989</t>
         </is>
       </c>
       <c r="G123" s="7" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>-45,307</t>
         </is>
       </c>
       <c r="H123" s="7" t="inlineStr">
         <is>
-          <t>4,792</t>
+          <t>-96,707</t>
         </is>
       </c>
       <c r="I123" s="6" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>컴퓨터 프로그래밍, 시스템 통합 및 관리업</t>
         </is>
       </c>
       <c r="J123" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K123" s="6" t="inlineStr">
@@ -7043,12 +7031,12 @@
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>파워큐브세미</t>
+          <t>넥스트젠바이오</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
@@ -7063,32 +7051,32 @@
       </c>
       <c r="E124" s="6" t="inlineStr">
         <is>
-          <t>FY25</t>
+          <t>FY24</t>
         </is>
       </c>
       <c r="F124" s="7" t="inlineStr">
         <is>
-          <t>10,341</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
-          <t>-10,837</t>
+          <t>69</t>
         </is>
       </c>
       <c r="H124" s="7" t="inlineStr">
         <is>
-          <t>841</t>
+          <t>4,792</t>
         </is>
       </c>
       <c r="I124" s="6" t="inlineStr">
         <is>
-          <t>반도체 제조업</t>
+          <t>자연과학 및 공학 연구개발업</t>
         </is>
       </c>
       <c r="J124" s="6" t="inlineStr">
         <is>
-          <t>하나, BNK</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K124" s="6" t="inlineStr">
@@ -7100,12 +7088,12 @@
     <row r="125">
       <c r="A125" s="6" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B125" s="6" t="inlineStr">
         <is>
-          <t>제이피이노베이션</t>
+          <t>파워큐브세미</t>
         </is>
       </c>
       <c r="C125" s="6" t="inlineStr">
@@ -7125,27 +7113,27 @@
       </c>
       <c r="F125" s="7" t="inlineStr">
         <is>
-          <t>56,324</t>
+          <t>10,341</t>
         </is>
       </c>
       <c r="G125" s="7" t="inlineStr">
         <is>
-          <t>5,588</t>
+          <t>-10,837</t>
         </is>
       </c>
       <c r="H125" s="7" t="inlineStr">
         <is>
-          <t>3,684</t>
+          <t>841</t>
         </is>
       </c>
       <c r="I125" s="6" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>반도체 제조업</t>
         </is>
       </c>
       <c r="J125" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>하나, BNK</t>
         </is>
       </c>
       <c r="K125" s="6" t="inlineStr">
@@ -7157,12 +7145,12 @@
     <row r="126">
       <c r="A126" s="6" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B126" s="6" t="inlineStr">
         <is>
-          <t>케이솔루션</t>
+          <t>제이피이노베이션</t>
         </is>
       </c>
       <c r="C126" s="6" t="inlineStr">
@@ -7172,7 +7160,7 @@
       </c>
       <c r="D126" s="6" t="inlineStr">
         <is>
-          <t>스팩 존속합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E126" s="6" t="inlineStr">
@@ -7182,27 +7170,27 @@
       </c>
       <c r="F126" s="7" t="inlineStr">
         <is>
-          <t>34,565</t>
+          <t>56,324</t>
         </is>
       </c>
       <c r="G126" s="7" t="inlineStr">
         <is>
-          <t>1,158</t>
+          <t>5,588</t>
         </is>
       </c>
       <c r="H126" s="7" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>3,684</t>
         </is>
       </c>
       <c r="I126" s="6" t="inlineStr">
         <is>
-          <t>차체 및 특장차 제조업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="J126" s="6" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K126" s="6" t="inlineStr">
@@ -7214,12 +7202,12 @@
     <row r="127">
       <c r="A127" s="6" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B127" s="6" t="inlineStr">
         <is>
-          <t>디토닉</t>
+          <t>케이솔루션</t>
         </is>
       </c>
       <c r="C127" s="6" t="inlineStr">
@@ -7229,37 +7217,37 @@
       </c>
       <c r="D127" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 존속합병</t>
         </is>
       </c>
       <c r="E127" s="6" t="inlineStr">
         <is>
-          <t>FY24</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="F127" s="7" t="inlineStr">
         <is>
-          <t>31,293</t>
+          <t>34,565</t>
         </is>
       </c>
       <c r="G127" s="7" t="inlineStr">
         <is>
-          <t>-1,633</t>
+          <t>1,158</t>
         </is>
       </c>
       <c r="H127" s="7" t="inlineStr">
         <is>
-          <t>-21,926</t>
+          <t>653</t>
         </is>
       </c>
       <c r="I127" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>차체 및 특장차 제조업</t>
         </is>
       </c>
       <c r="J127" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="K127" s="6" t="inlineStr">
@@ -7271,12 +7259,12 @@
     <row r="128">
       <c r="A128" s="6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B128" s="6" t="inlineStr">
         <is>
-          <t>에스케이팩</t>
+          <t>디토닉</t>
         </is>
       </c>
       <c r="C128" s="6" t="inlineStr">
@@ -7286,7 +7274,7 @@
       </c>
       <c r="D128" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E128" s="6" t="inlineStr">
@@ -7296,27 +7284,27 @@
       </c>
       <c r="F128" s="7" t="inlineStr">
         <is>
-          <t>27,310</t>
+          <t>31,293</t>
         </is>
       </c>
       <c r="G128" s="7" t="inlineStr">
         <is>
-          <t>2,257</t>
+          <t>-1,633</t>
         </is>
       </c>
       <c r="H128" s="7" t="inlineStr">
         <is>
-          <t>3,207</t>
+          <t>-21,926</t>
         </is>
       </c>
       <c r="I128" s="6" t="inlineStr">
         <is>
-          <t>용기 세척, 포장 및 충전기 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J128" s="6" t="inlineStr">
         <is>
-          <t>교보</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K128" s="6" t="inlineStr">
@@ -7328,12 +7316,12 @@
     <row r="129">
       <c r="A129" s="6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>메타넷엑스</t>
+          <t>에스케이팩</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
@@ -7343,7 +7331,7 @@
       </c>
       <c r="D129" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr">
@@ -7353,27 +7341,27 @@
       </c>
       <c r="F129" s="7" t="inlineStr">
         <is>
-          <t>244,130</t>
+          <t>27,310</t>
         </is>
       </c>
       <c r="G129" s="7" t="inlineStr">
         <is>
-          <t>13,455</t>
+          <t>2,257</t>
         </is>
       </c>
       <c r="H129" s="7" t="inlineStr">
         <is>
-          <t>9,995</t>
+          <t>3,207</t>
         </is>
       </c>
       <c r="I129" s="6" t="inlineStr">
         <is>
-          <t>컴퓨터 프로그래밍, 시스템 통합 및 관리업</t>
+          <t>용기 세척, 포장 및 충전기 제조업</t>
         </is>
       </c>
       <c r="J129" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>교보</t>
         </is>
       </c>
       <c r="K129" s="6" t="inlineStr">
@@ -7385,12 +7373,12 @@
     <row r="130">
       <c r="A130" s="6" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>무아스</t>
+          <t>메타넷엑스</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
@@ -7400,7 +7388,7 @@
       </c>
       <c r="D130" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
@@ -7410,27 +7398,27 @@
       </c>
       <c r="F130" s="7" t="inlineStr">
         <is>
-          <t>41,813</t>
+          <t>244,130</t>
         </is>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
-          <t>3,903</t>
+          <t>13,455</t>
         </is>
       </c>
       <c r="H130" s="7" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>9,995</t>
         </is>
       </c>
       <c r="I130" s="6" t="inlineStr">
         <is>
-          <t>가정용 전기기기 제조업</t>
+          <t>컴퓨터 프로그래밍, 시스템 통합 및 관리업</t>
         </is>
       </c>
       <c r="J130" s="6" t="inlineStr">
         <is>
-          <t>신한</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K130" s="6" t="inlineStr">
@@ -7447,7 +7435,7 @@
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>유빅스테라퓨틱스</t>
+          <t>무아스</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
@@ -7457,7 +7445,7 @@
       </c>
       <c r="D131" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
@@ -7467,27 +7455,27 @@
       </c>
       <c r="F131" s="7" t="inlineStr">
         <is>
-          <t>1,071</t>
+          <t>41,813</t>
         </is>
       </c>
       <c r="G131" s="7" t="inlineStr">
         <is>
-          <t>-15,145</t>
+          <t>3,903</t>
         </is>
       </c>
       <c r="H131" s="7" t="inlineStr">
         <is>
-          <t>5,489</t>
+          <t>532</t>
         </is>
       </c>
       <c r="I131" s="6" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>가정용 전기기기 제조업</t>
         </is>
       </c>
       <c r="J131" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>신한</t>
         </is>
       </c>
       <c r="K131" s="6" t="inlineStr">
@@ -7499,12 +7487,12 @@
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>코드잇</t>
+          <t>유빅스테라퓨틱스</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
@@ -7524,27 +7512,27 @@
       </c>
       <c r="F132" s="7" t="inlineStr">
         <is>
-          <t>30,747</t>
+          <t>1,071</t>
         </is>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
-          <t>6,652</t>
+          <t>-15,145</t>
         </is>
       </c>
       <c r="H132" s="7" t="inlineStr">
         <is>
-          <t>2,403</t>
+          <t>5,489</t>
         </is>
       </c>
       <c r="I132" s="6" t="inlineStr">
         <is>
-          <t>교육지원 서비스업</t>
+          <t>자연과학 및 공학 연구개발업</t>
         </is>
       </c>
       <c r="J132" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K132" s="6" t="inlineStr">
@@ -7556,12 +7544,12 @@
     <row r="133">
       <c r="A133" s="6" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>한컴인스페이스</t>
+          <t>코드잇</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
@@ -7581,44 +7569,44 @@
       </c>
       <c r="F133" s="7" t="inlineStr">
         <is>
-          <t>23,492</t>
+          <t>30,747</t>
         </is>
       </c>
       <c r="G133" s="7" t="inlineStr">
         <is>
-          <t>-3,104</t>
+          <t>6,652</t>
         </is>
       </c>
       <c r="H133" s="7" t="inlineStr">
         <is>
-          <t>5,815</t>
+          <t>2,403</t>
         </is>
       </c>
       <c r="I133" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>교육지원 서비스업</t>
         </is>
       </c>
       <c r="J133" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K133" s="6" t="inlineStr">
         <is>
-          <t>심사 미승인</t>
+          <t>심사 철회</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>크몽</t>
+          <t>한컴인스페이스</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
@@ -7638,44 +7626,44 @@
       </c>
       <c r="F134" s="7" t="inlineStr">
         <is>
-          <t>48,572</t>
+          <t>23,492</t>
         </is>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
-          <t>3,988</t>
+          <t>-3,104</t>
         </is>
       </c>
       <c r="H134" s="7" t="inlineStr">
         <is>
-          <t>4,930</t>
+          <t>5,815</t>
         </is>
       </c>
       <c r="I134" s="6" t="inlineStr">
         <is>
-          <t>기타 정보 서비스업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J134" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K134" s="6" t="inlineStr">
         <is>
-          <t>심사 철회</t>
+          <t>심사 미승인</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="6" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>한화플러스제6호스팩</t>
+          <t>크몽</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
@@ -7695,27 +7683,27 @@
       </c>
       <c r="F135" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>48,572</t>
         </is>
       </c>
       <c r="G135" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3,988</t>
         </is>
       </c>
       <c r="H135" s="7" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4,930</t>
         </is>
       </c>
       <c r="I135" s="6" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>기타 정보 서비스업</t>
         </is>
       </c>
       <c r="J135" s="6" t="inlineStr">
         <is>
-          <t>한화</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K135" s="6" t="inlineStr">
@@ -7727,17 +7715,17 @@
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>에식스솔루션즈</t>
+          <t>한화플러스제6호스팩</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr">
         <is>
-          <t>유가</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D136" s="6" t="inlineStr">
@@ -7752,27 +7740,27 @@
       </c>
       <c r="F136" s="7" t="inlineStr">
         <is>
-          <t>2,461</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H136" s="7" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I136" s="6" t="inlineStr">
         <is>
-          <t>절연선 및 케이블 제조업</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="J136" s="6" t="inlineStr">
         <is>
-          <t>한국, 미래</t>
+          <t>한화</t>
         </is>
       </c>
       <c r="K136" s="6" t="inlineStr">
@@ -7784,55 +7772,112 @@
     <row r="137">
       <c r="A137" s="6" t="inlineStr">
         <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B137" s="6" t="inlineStr">
+        <is>
+          <t>에식스솔루션즈</t>
+        </is>
+      </c>
+      <c r="C137" s="6" t="inlineStr">
+        <is>
+          <t>유가</t>
+        </is>
+      </c>
+      <c r="D137" s="6" t="inlineStr">
+        <is>
+          <t>신규상장</t>
+        </is>
+      </c>
+      <c r="E137" s="6" t="inlineStr">
+        <is>
+          <t>FY24</t>
+        </is>
+      </c>
+      <c r="F137" s="7" t="inlineStr">
+        <is>
+          <t>2,461</t>
+        </is>
+      </c>
+      <c r="G137" s="7" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="H137" s="7" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I137" s="6" t="inlineStr">
+        <is>
+          <t>절연선 및 케이블 제조업</t>
+        </is>
+      </c>
+      <c r="J137" s="6" t="inlineStr">
+        <is>
+          <t>한국, 미래</t>
+        </is>
+      </c>
+      <c r="K137" s="6" t="inlineStr">
+        <is>
+          <t>심사 철회</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="6" t="inlineStr">
+        <is>
           <t>2026-01-23</t>
         </is>
       </c>
-      <c r="B137" s="6" t="inlineStr">
+      <c r="B138" s="6" t="inlineStr">
         <is>
           <t>에코크레이션</t>
         </is>
       </c>
-      <c r="C137" s="6" t="inlineStr">
+      <c r="C138" s="6" t="inlineStr">
         <is>
           <t>코스닥</t>
         </is>
       </c>
-      <c r="D137" s="6" t="inlineStr">
+      <c r="D138" s="6" t="inlineStr">
         <is>
           <t>신규상장</t>
         </is>
       </c>
-      <c r="E137" s="6" t="inlineStr">
+      <c r="E138" s="6" t="inlineStr">
         <is>
           <t>FY24</t>
         </is>
       </c>
-      <c r="F137" s="7" t="inlineStr">
+      <c r="F138" s="7" t="inlineStr">
         <is>
           <t>18,544</t>
         </is>
       </c>
-      <c r="G137" s="7" t="inlineStr">
+      <c r="G138" s="7" t="inlineStr">
         <is>
           <t>-15,634</t>
         </is>
       </c>
-      <c r="H137" s="7" t="inlineStr">
+      <c r="H138" s="7" t="inlineStr">
         <is>
           <t>4,550</t>
         </is>
       </c>
-      <c r="I137" s="6" t="inlineStr">
+      <c r="I138" s="6" t="inlineStr">
         <is>
           <t>일반 목적용 기계 제조업</t>
         </is>
       </c>
-      <c r="J137" s="6" t="inlineStr">
+      <c r="J138" s="6" t="inlineStr">
         <is>
           <t>키움</t>
         </is>
       </c>
-      <c r="K137" s="6" t="inlineStr">
+      <c r="K138" s="6" t="inlineStr">
         <is>
           <t>심사 철회</t>
         </is>
@@ -11615,120 +11660,128 @@
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>브릴스</t>
+          <t>빅웨이브로보틱스</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>08-31~09-04</t>
+          <t>09-07~09-11</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>16,500~19,500</t>
+          <t>15,000~18,000</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>1,200,000</t>
+          <t>1,600,000</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>23,400,000,000</t>
+          <t>28,800,000,000</t>
         </is>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>13.44 (PSR)</t>
+          <t>11.15 (PSR)</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>19,500</t>
+          <t>18,000</t>
         </is>
       </c>
       <c r="H53" s="6" t="n">
-        <v>1187.74</v>
+        <v>1109.37</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>2181</v>
+        <v>2255</v>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>09-08~09-09</t>
-        </is>
-      </c>
-      <c r="K53" s="6" t="inlineStr"/>
+          <t>09-15~09-16</t>
+        </is>
+      </c>
+      <c r="K53" s="6" t="inlineStr">
+        <is>
+          <t>2,706.30</t>
+        </is>
+      </c>
       <c r="L53" s="6" t="inlineStr"/>
       <c r="M53" s="6" t="inlineStr"/>
       <c r="N53" s="6" t="inlineStr">
         <is>
-          <t>아이비케이투자증권</t>
-        </is>
-      </c>
-      <c r="O53" s="6" t="inlineStr"/>
+          <t>유진투자증권</t>
+        </is>
+      </c>
+      <c r="O53" s="6" t="inlineStr">
+        <is>
+          <t>미래</t>
+        </is>
+      </c>
       <c r="P53" s="7" t="inlineStr">
         <is>
-          <t>713,790,000</t>
+          <t>378,216,000</t>
         </is>
       </c>
       <c r="Q53" s="6" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>발행조건확정</t>
+          <t>청약완료·상장대기</t>
         </is>
       </c>
     </row>
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>빅웨이브로보틱스</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>09-07~09-11</t>
+          <t>08-31~09-04</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>15,000~18,000</t>
+          <t>16,500~19,500</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>1,600,000</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>28,800,000,000</t>
+          <t>23,400,000,000</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>11.15 (PSR)</t>
+          <t>13.44 (PSR)</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>18,000</t>
+          <t>19,500</t>
         </is>
       </c>
       <c r="H54" s="6" t="n">
-        <v>1109.37</v>
+        <v>1187.74</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>2255</v>
+        <v>2181</v>
       </c>
       <c r="J54" s="6" t="inlineStr">
         <is>
-          <t>09-15~09-16</t>
+          <t>09-08~09-09</t>
         </is>
       </c>
       <c r="K54" s="6" t="inlineStr"/>
@@ -11736,22 +11789,18 @@
       <c r="M54" s="6" t="inlineStr"/>
       <c r="N54" s="6" t="inlineStr">
         <is>
-          <t>유진투자증권</t>
-        </is>
-      </c>
-      <c r="O54" s="6" t="inlineStr">
-        <is>
-          <t>미래</t>
-        </is>
-      </c>
+          <t>아이비케이투자증권</t>
+        </is>
+      </c>
+      <c r="O54" s="6" t="inlineStr"/>
       <c r="P54" s="7" t="inlineStr">
         <is>
-          <t>378,216,000</t>
+          <t>713,790,000</t>
         </is>
       </c>
       <c r="Q54" s="6" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
@@ -12300,12 +12349,12 @@
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>09-21~09-29</t>
+          <t>10-16~10-22</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>9,400~11,500</t>
+          <t>9,600~11,700</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
@@ -12315,7 +12364,7 @@
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>18,800,000,000</t>
+          <t>19,200,000,000</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
@@ -12328,7 +12377,7 @@
       <c r="I63" s="6" t="inlineStr"/>
       <c r="J63" s="6" t="inlineStr">
         <is>
-          <t>10-06~10-07</t>
+          <t>10-28~10-29</t>
         </is>
       </c>
       <c r="K63" s="6" t="inlineStr"/>
@@ -12342,7 +12391,7 @@
       <c r="O63" s="6" t="inlineStr"/>
       <c r="P63" s="7" t="inlineStr">
         <is>
-          <t>968,200,000</t>
+          <t>988,800,000</t>
         </is>
       </c>
       <c r="Q63" s="6" t="inlineStr">
@@ -12352,7 +12401,7 @@
       </c>
       <c r="R63" s="6" t="inlineStr">
         <is>
-          <t>최초</t>
+          <t>정정</t>
         </is>
       </c>
     </row>
@@ -13670,7 +13719,7 @@
         <v>17</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>2</v>
@@ -13736,7 +13785,7 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C14" s="6" t="n">
         <v>9</v>
@@ -13966,7 +14015,7 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>35,414,000,000</t>
+          <t>35,814,000,000</t>
         </is>
       </c>
     </row>

--- a/IPO_analysis.xlsx
+++ b/IPO_analysis.xlsx
@@ -618,7 +618,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>기준일 2026-09-18 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
+          <t>기준일 2026-09-19 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
         </is>
       </c>
     </row>

--- a/IPO_analysis.xlsx
+++ b/IPO_analysis.xlsx
@@ -618,7 +618,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>기준일 2026-09-19 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
+          <t>기준일 2026-09-20 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
         </is>
       </c>
     </row>

--- a/IPO_analysis.xlsx
+++ b/IPO_analysis.xlsx
@@ -618,7 +618,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>기준일 2026-09-22 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
+          <t>기준일 2026-09-23 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
         </is>
       </c>
     </row>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="K84" s="6" t="inlineStr">
         <is>
-          <t>상장전</t>
+          <t>상장승인(상장예정)</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="K91" s="6" t="inlineStr">
         <is>
-          <t>상장승인(상장예정)</t>
+          <t>상장완료 (2026-09-23)</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="K102" s="6" t="inlineStr">
         <is>
-          <t>상장전</t>
+          <t>상장승인(상장예정)</t>
         </is>
       </c>
     </row>
@@ -8395,7 +8395,7 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>■ 상장 완료 (2026)  (43건)</t>
+          <t>■ 상장 완료 (2026)  (44건)</t>
         </is>
       </c>
       <c r="B6" s="4" t="n"/>
@@ -8419,44 +8419,44 @@
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>한국제17호스팩</t>
+          <t>와이즈플래닛컴퍼니</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>09-07~09-08</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>09-04~09-10</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>10,000~12,000</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>7,000,000</t>
+          <t>1,600,000</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>14,000,000,000</t>
-        </is>
-      </c>
-      <c r="F7" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>19,200,000,000</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>20.04배 (PER)</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>1270.51</v>
+        <v>1248.47</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>2040</v>
+        <v>2323</v>
       </c>
       <c r="J7" s="18" t="inlineStr">
         <is>
@@ -8465,29 +8465,29 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>8,291.55</t>
+          <t>3,568.86</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr"/>
       <c r="M7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="N7" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="N7" s="6" t="inlineStr">
+        <is>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="O7" s="6" t="inlineStr"/>
-      <c r="P7" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P7" s="7" t="inlineStr">
+        <is>
+          <t>494,400,000</t>
         </is>
       </c>
       <c r="Q7" s="6" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="R7" s="6" t="inlineStr">
@@ -8499,12 +8499,12 @@
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>KB제34호스팩</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>한국제17호스팩</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>09-07~09-08</t>
         </is>
       </c>
       <c r="C8" s="18" t="inlineStr">
@@ -8527,25 +8527,25 @@
           <t>수집예정</t>
         </is>
       </c>
-      <c r="G8" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>2,000</t>
         </is>
       </c>
       <c r="H8" s="6" t="n">
-        <v>1232.51</v>
+        <v>1270.51</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>2001</v>
+        <v>2040</v>
       </c>
       <c r="J8" s="18" t="inlineStr">
         <is>
           <t>수집예정</t>
         </is>
       </c>
-      <c r="K8" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>8,291.55</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr"/>
@@ -8579,75 +8579,75 @@
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>네오사피엔스</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>09-02~09-08</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>13,800~15,800</t>
+          <t>KB제34호스팩</t>
+        </is>
+      </c>
+      <c r="B9" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>7,000,000</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>20,000,000,000</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>26.76배 (PER)</t>
-        </is>
-      </c>
-      <c r="G9" s="6" t="inlineStr">
-        <is>
-          <t>10,000</t>
+          <t>14,000,000,000</t>
+        </is>
+      </c>
+      <c r="F9" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="G9" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>219.56</v>
+        <v>1232.51</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>1045</v>
+        <v>2001</v>
       </c>
       <c r="J9" s="18" t="inlineStr">
         <is>
           <t>수집예정</t>
         </is>
       </c>
-      <c r="K9" s="6" t="inlineStr">
-        <is>
-          <t>4,885.53</t>
+      <c r="K9" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr"/>
       <c r="M9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="N9" s="6" t="inlineStr">
-        <is>
-          <t>대신증권</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="N9" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="O9" s="6" t="inlineStr"/>
-      <c r="P9" s="7" t="inlineStr">
-        <is>
-          <t>1,080,264,000</t>
+      <c r="P9" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="Q9" s="6" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
@@ -8659,44 +8659,44 @@
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>엔에이치스팩34호</t>
+          <t>네오사피엔스</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>08-24~08-25</t>
-        </is>
-      </c>
-      <c r="C10" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>09-02~09-08</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>13,800~15,800</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>8,500,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>17,000,000,000</t>
-        </is>
-      </c>
-      <c r="F10" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>20,000,000,000</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>26.76배 (PER)</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="H10" s="6" t="n">
-        <v>1160.7</v>
+        <v>219.56</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>2050</v>
+        <v>1045</v>
       </c>
       <c r="J10" s="18" t="inlineStr">
         <is>
@@ -8705,29 +8705,29 @@
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>16,216.08</t>
+          <t>4,885.53</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr"/>
       <c r="M10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="N10" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="N10" s="6" t="inlineStr">
+        <is>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="O10" s="6" t="inlineStr"/>
-      <c r="P10" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P10" s="7" t="inlineStr">
+        <is>
+          <t>1,080,264,000</t>
         </is>
       </c>
       <c r="Q10" s="6" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="R10" s="6" t="inlineStr">
@@ -8739,44 +8739,44 @@
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>엔에이치스팩34호</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>08-14~08-21</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>13,000~16,000</t>
+          <t>08-24~08-25</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>8,500,000</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>20,000,000,000</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>29.52배 (PER)</t>
+          <t>17,000,000,000</t>
+        </is>
+      </c>
+      <c r="F11" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>63.41</v>
+        <v>1160.7</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>246</v>
+        <v>2050</v>
       </c>
       <c r="J11" s="18" t="inlineStr">
         <is>
@@ -8785,29 +8785,29 @@
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>88.20</t>
+          <t>16,216.08</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr"/>
       <c r="M11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="N11" s="6" t="inlineStr">
-        <is>
-          <t>한국투자증권</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="N11" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="O11" s="6" t="inlineStr"/>
-      <c r="P11" s="7" t="inlineStr">
-        <is>
-          <t>1,071,200,000</t>
-        </is>
-      </c>
-      <c r="Q11" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P11" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>50%</t>
         </is>
       </c>
       <c r="R11" s="6" t="inlineStr">
@@ -8819,75 +8819,75 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>해치텍</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>08-03~08-07</t>
+          <t>08-14~08-21</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>23,000~28,000</t>
+          <t>13,000~16,000</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>1,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>23,000,000,000</t>
+          <t>20,000,000,000</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>36.99배 (PER)</t>
+          <t>29.52배 (PER)</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="H12" s="6" t="n">
-        <v>101.91</v>
+        <v>63.41</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>321</v>
+        <v>246</v>
       </c>
       <c r="J12" s="18" t="inlineStr">
         <is>
           <t>수집예정</t>
         </is>
       </c>
-      <c r="K12" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>88.20</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr"/>
       <c r="M12" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
-          <t>DB증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="O12" s="6" t="inlineStr"/>
       <c r="P12" s="7" t="inlineStr">
         <is>
-          <t>1,302,950,000</t>
-        </is>
-      </c>
-      <c r="Q12" s="6" t="inlineStr">
-        <is>
-          <t>5.5%</t>
+          <t>1,071,200,000</t>
+        </is>
+      </c>
+      <c r="Q12" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="R12" s="6" t="inlineStr">
@@ -8899,7 +8899,7 @@
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>니어스랩</t>
+          <t>해치텍</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
@@ -8909,34 +8909,34 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>30,000~41,200</t>
+          <t>23,000~28,000</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>910,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>37,492,000,000</t>
+          <t>23,000,000,000</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>44.41배 (PER)</t>
+          <t>36.99배 (PER)</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>41,200</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>743.49</v>
+        <v>101.91</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>1795</v>
+        <v>321</v>
       </c>
       <c r="J13" s="18" t="inlineStr">
         <is>
@@ -8951,23 +8951,23 @@
       <c r="L13" s="6" t="inlineStr"/>
       <c r="M13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="N13" s="6" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>DB증권</t>
         </is>
       </c>
       <c r="O13" s="6" t="inlineStr"/>
       <c r="P13" s="7" t="inlineStr">
         <is>
-          <t>1,265,355,000</t>
+          <t>1,302,950,000</t>
         </is>
       </c>
       <c r="Q13" s="6" t="inlineStr">
         <is>
-          <t>4.50%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
@@ -8979,44 +8979,44 @@
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>기도산업</t>
+          <t>니어스랩</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>07-31~08-06</t>
+          <t>08-03~08-07</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>24,800~28,400</t>
+          <t>30,000~41,200</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>1,700,000</t>
+          <t>910,000</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>48,280,000,000</t>
+          <t>37,492,000,000</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>10.01배 (PER)</t>
+          <t>44.41배 (PER)</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>28,400</t>
+          <t>41,200</t>
         </is>
       </c>
       <c r="H14" s="6" t="n">
-        <v>213.31</v>
+        <v>743.49</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>637</v>
+        <v>1795</v>
       </c>
       <c r="J14" s="18" t="inlineStr">
         <is>
@@ -9031,23 +9031,23 @@
       <c r="L14" s="6" t="inlineStr"/>
       <c r="M14" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="N14" s="6" t="inlineStr">
         <is>
-          <t>미래에셋증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="O14" s="6" t="inlineStr"/>
       <c r="P14" s="7" t="inlineStr">
         <is>
-          <t>716,720,000</t>
+          <t>1,265,355,000</t>
         </is>
       </c>
       <c r="Q14" s="6" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>4.50%</t>
         </is>
       </c>
       <c r="R14" s="6" t="inlineStr">
@@ -9059,44 +9059,44 @@
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스</t>
+          <t>기도산업</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>07-20~07-24</t>
+          <t>07-31~08-06</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>12,000~14,500</t>
+          <t>24,800~28,400</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>1,700,000</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>60,000,000,000</t>
+          <t>48,280,000,000</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>22.89배 (PER)</t>
+          <t>10.01배 (PER)</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>28,400</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>50.4</v>
+        <v>213.31</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>307</v>
+        <v>637</v>
       </c>
       <c r="J15" s="18" t="inlineStr">
         <is>
@@ -9111,23 +9111,23 @@
       <c r="L15" s="6" t="inlineStr"/>
       <c r="M15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="N15" s="6" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>미래에셋증권</t>
         </is>
       </c>
       <c r="O15" s="6" t="inlineStr"/>
       <c r="P15" s="7" t="inlineStr">
         <is>
-          <t>4,095,000,000</t>
+          <t>716,720,000</t>
         </is>
       </c>
       <c r="Q15" s="6" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
@@ -9139,44 +9139,44 @@
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>케이앤에스아이앤씨</t>
+          <t>인제니아테라퓨틱스</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>07-27~07-31</t>
+          <t>07-20~07-24</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>9,000~11,000</t>
+          <t>12,000~14,500</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>2,400,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>26,400,000,000</t>
+          <t>60,000,000,000</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>42.08배 (PER)</t>
+          <t>22.89배 (PER)</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>11,000</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="H16" s="6" t="n">
-        <v>938.24</v>
+        <v>50.4</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>2024</v>
+        <v>307</v>
       </c>
       <c r="J16" s="18" t="inlineStr">
         <is>
@@ -9191,23 +9191,23 @@
       <c r="L16" s="6" t="inlineStr"/>
       <c r="M16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="N16" s="6" t="inlineStr">
         <is>
-          <t>아이비케이투자증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="O16" s="6" t="inlineStr"/>
       <c r="P16" s="7" t="inlineStr">
         <is>
-          <t>1,500,000,000</t>
+          <t>4,095,000,000</t>
         </is>
       </c>
       <c r="Q16" s="6" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="R16" s="6" t="inlineStr">
@@ -9219,44 +9219,44 @@
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>딜리셔스</t>
+          <t>케이앤에스아이앤씨</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>07-23~07-29</t>
+          <t>07-27~07-31</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>5,000~7,000</t>
+          <t>9,000~11,000</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>2,200,000</t>
+          <t>2,400,000</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>15,400,000,000</t>
+          <t>26,400,000,000</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>23.93배 (PER)</t>
+          <t>42.08배 (PER)</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>7,000</t>
+          <t>11,000</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>184.06</v>
+        <v>938.24</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>441</v>
+        <v>2024</v>
       </c>
       <c r="J17" s="18" t="inlineStr">
         <is>
@@ -9271,23 +9271,23 @@
       <c r="L17" s="6" t="inlineStr"/>
       <c r="M17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="N17" s="6" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>아이비케이투자증권</t>
         </is>
       </c>
       <c r="O17" s="6" t="inlineStr"/>
       <c r="P17" s="7" t="inlineStr">
         <is>
-          <t>566,500,000</t>
+          <t>1,500,000,000</t>
         </is>
       </c>
       <c r="Q17" s="6" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="R17" s="6" t="inlineStr">
@@ -9299,44 +9299,44 @@
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>에이치엘지노믹스</t>
+          <t>딜리셔스</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>07-02~07-08</t>
+          <t>07-23~07-29</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>18,500~21,500</t>
+          <t>5,000~7,000</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>2,565,000</t>
+          <t>2,200,000</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>55,147,500,000</t>
+          <t>15,400,000,000</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>12.85배 (EV/EBITDA)</t>
+          <t>23.93배 (PER)</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>21,500</t>
+          <t>7,000</t>
         </is>
       </c>
       <c r="H18" s="6" t="n">
-        <v>714.52</v>
+        <v>184.06</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>2148</v>
+        <v>441</v>
       </c>
       <c r="J18" s="18" t="inlineStr">
         <is>
@@ -9351,27 +9351,23 @@
       <c r="L18" s="6" t="inlineStr"/>
       <c r="M18" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="N18" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
-        </is>
-      </c>
-      <c r="O18" s="6" t="inlineStr">
-        <is>
-          <t>아이비케이투자증권, IBK투자증권, IBK투자증권, IBK투자증권, IBK투자증권, IBK투자증권㈜, 보통주, IBK투자증권㈜</t>
-        </is>
-      </c>
+          <t>한국투자증권</t>
+        </is>
+      </c>
+      <c r="O18" s="6" t="inlineStr"/>
       <c r="P18" s="7" t="inlineStr">
         <is>
-          <t>1,211</t>
+          <t>566,500,000</t>
         </is>
       </c>
       <c r="Q18" s="6" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="R18" s="6" t="inlineStr">
@@ -9383,63 +9379,59 @@
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>레메디</t>
-        </is>
-      </c>
-      <c r="B19" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>에이치엘지노믹스</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>07-02~07-08</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>17,800~20,700</t>
+          <t>18,500~21,500</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>1,200,000</t>
+          <t>2,565,000</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>24,840,000,000</t>
+          <t>55,147,500,000</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>21.95배 (PER)</t>
+          <t>12.85배 (EV/EBITDA)</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>20,700</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>1,146.41</t>
-        </is>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>2,246</t>
-        </is>
+          <t>21,500</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>714.52</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>2148</v>
       </c>
       <c r="J19" s="18" t="inlineStr">
         <is>
           <t>수집예정</t>
         </is>
       </c>
-      <c r="K19" s="6" t="inlineStr">
-        <is>
-          <t>1,706.71</t>
+      <c r="K19" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr"/>
       <c r="M19" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="N19" s="6" t="inlineStr">
@@ -9447,15 +9439,19 @@
           <t>KB</t>
         </is>
       </c>
-      <c r="O19" s="6" t="inlineStr"/>
+      <c r="O19" s="6" t="inlineStr">
+        <is>
+          <t>아이비케이투자증권, IBK투자증권, IBK투자증권, IBK투자증권, IBK투자증권, IBK투자증권㈜, 보통주, IBK투자증권㈜</t>
+        </is>
+      </c>
       <c r="P19" s="7" t="inlineStr">
         <is>
-          <t>1,279</t>
+          <t>1,211</t>
         </is>
       </c>
       <c r="Q19" s="6" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
@@ -9467,7 +9463,7 @@
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>레몬헬스케어</t>
+          <t>레메디</t>
         </is>
       </c>
       <c r="B20" s="18" t="inlineStr">
@@ -9477,45 +9473,53 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>7,500~10,000</t>
+          <t>17,800~20,700</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>24,840,000,000</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>25.48배 (PER)</t>
-        </is>
-      </c>
-      <c r="G20" s="6" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H20" s="6" t="n">
-        <v>1238</v>
-      </c>
-      <c r="I20" s="6" t="n">
-        <v>2233</v>
-      </c>
-      <c r="J20" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-24~25</t>
-        </is>
-      </c>
-      <c r="K20" s="6" t="n">
-        <v>1510.57</v>
+          <t>21.95배 (PER)</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>20,700</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="inlineStr">
+        <is>
+          <t>1,146.41</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>2,246</t>
+        </is>
+      </c>
+      <c r="J20" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>1,706.71</t>
+        </is>
       </c>
       <c r="L20" s="6" t="inlineStr"/>
       <c r="M20" s="6" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="N20" s="6" t="inlineStr">
@@ -9526,12 +9530,12 @@
       <c r="O20" s="6" t="inlineStr"/>
       <c r="P20" s="7" t="inlineStr">
         <is>
-          <t>824</t>
+          <t>1,279</t>
         </is>
       </c>
       <c r="Q20" s="6" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
@@ -9543,7 +9547,7 @@
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>매드업</t>
+          <t>레몬헬스케어</t>
         </is>
       </c>
       <c r="B21" s="18" t="inlineStr">
@@ -9553,7 +9557,7 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>7,000~8,000</t>
+          <t>7,500~10,000</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
@@ -9563,51 +9567,51 @@
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>16,000</t>
+          <t>20,000</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>24.57배 (PER)</t>
+          <t>25.48배 (PER)</t>
         </is>
       </c>
       <c r="G21" s="6" t="n">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>1396.29</v>
+        <v>1238</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>2392</v>
+        <v>2233</v>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>2026-06-23~24</t>
+          <t>2026-06-24~25</t>
         </is>
       </c>
       <c r="K21" s="6" t="n">
-        <v>3304.76</v>
+        <v>1510.57</v>
       </c>
       <c r="L21" s="6" t="inlineStr"/>
       <c r="M21" s="6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="N21" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="O21" s="6" t="inlineStr"/>
       <c r="P21" s="7" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>824</t>
         </is>
       </c>
       <c r="Q21" s="6" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
@@ -9619,75 +9623,71 @@
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>한국제16호스팩</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
+          <t>매드업</t>
+        </is>
+      </c>
+      <c r="B22" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>7,000~8,000</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>5,500,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>11,000</t>
-        </is>
-      </c>
-      <c r="F22" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
+          <t>16,000</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>24.57배 (PER)</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>8000</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>1364.09</v>
+        <v>1396.29</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>2089</v>
+        <v>2392</v>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>2026-06-22~06-23</t>
-        </is>
-      </c>
-      <c r="K22" s="6" t="inlineStr">
-        <is>
-          <t>1,274.77</t>
-        </is>
+          <t>2026-06-23~24</t>
+        </is>
+      </c>
+      <c r="K22" s="6" t="n">
+        <v>3304.76</v>
       </c>
       <c r="L22" s="6" t="inlineStr"/>
       <c r="M22" s="6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="N22" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="O22" s="6" t="inlineStr"/>
       <c r="P22" s="7" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>742</t>
         </is>
       </c>
       <c r="Q22" s="6" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="R22" s="6" t="inlineStr">
@@ -9699,51 +9699,53 @@
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>스트라드비젼</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>한국제16호스팩</t>
+        </is>
+      </c>
+      <c r="B23" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>12,000~14,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>7,000,000</t>
+          <t>5,500,000</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>84,000</t>
-        </is>
-      </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>37.45배 (PER)</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="n">
-        <v>12000</v>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="F23" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>381.3</v>
+        <v>1364.09</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>1604</v>
+        <v>2089</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>2026-06-18~06-19</t>
+          <t>2026-06-22~06-23</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>45.81</t>
+          <t>1,274.77</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr"/>
@@ -9754,13 +9756,13 @@
       </c>
       <c r="N23" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="O23" s="6" t="inlineStr"/>
       <c r="P23" s="7" t="inlineStr">
         <is>
-          <t>2,575</t>
+          <t>330</t>
         </is>
       </c>
       <c r="Q23" s="6" t="inlineStr">
@@ -9777,7 +9779,7 @@
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>져스텍</t>
+          <t>스트라드비젼</t>
         </is>
       </c>
       <c r="B24" s="18" t="inlineStr">
@@ -9787,32 +9789,32 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>10,500~12,500</t>
+          <t>12,000~14,000</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>1,600,000</t>
+          <t>7,000,000</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>84,000</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>26.82배 (PER)</t>
+          <t>37.45배 (PER)</t>
         </is>
       </c>
       <c r="G24" s="6" t="n">
-        <v>12500</v>
+        <v>12000</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>1294.99</v>
+        <v>381.3</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>2252</v>
+        <v>1604</v>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
@@ -9821,29 +9823,29 @@
       </c>
       <c r="K24" s="6" t="inlineStr">
         <is>
-          <t>2,783.89</t>
+          <t>45.81</t>
         </is>
       </c>
       <c r="L24" s="6" t="inlineStr"/>
       <c r="M24" s="6" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="N24" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="O24" s="6" t="inlineStr"/>
       <c r="P24" s="7" t="inlineStr">
         <is>
-          <t>1,164</t>
+          <t>2,575</t>
         </is>
       </c>
       <c r="Q24" s="6" t="inlineStr">
         <is>
-          <t>5.65%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="R24" s="6" t="inlineStr">
@@ -9855,75 +9857,73 @@
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>메리츠제2호스팩</t>
-        </is>
-      </c>
-      <c r="B25" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
+          <t>져스텍</t>
+        </is>
+      </c>
+      <c r="B25" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>10,500~12,500</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>7,000,000</t>
+          <t>1,600,000</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>14,000</t>
-        </is>
-      </c>
-      <c r="F25" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>26.82배 (PER)</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>12500</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>1087.58</v>
+        <v>1294.99</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>1798</v>
+        <v>2252</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09~06-10</t>
+          <t>2026-06-18~06-19</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>1,338.66</t>
+          <t>2,783.89</t>
         </is>
       </c>
       <c r="L25" s="6" t="inlineStr"/>
       <c r="M25" s="6" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="N25" s="6" t="inlineStr">
         <is>
-          <t>메리츠</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="O25" s="6" t="inlineStr"/>
       <c r="P25" s="7" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>1,164</t>
         </is>
       </c>
       <c r="Q25" s="6" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>5.65%</t>
         </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
@@ -9935,77 +9935,75 @@
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>피스피스스튜디오</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>메리츠제2호스팩</t>
+        </is>
+      </c>
+      <c r="B26" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>19,000~21,500</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>2,272,637</t>
+          <t>7,000,000</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>48,862</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>21.48배 (PER)</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="n">
-        <v>21500</v>
+          <t>14,000</t>
+        </is>
+      </c>
+      <c r="F26" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
       </c>
       <c r="H26" s="6" t="n">
-        <v>847.76</v>
+        <v>1087.58</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>2329</v>
+        <v>1798</v>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>2026-05-26~05-27</t>
+          <t>2026-06-09~06-10</t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>1,191.15</t>
+          <t>1,338.66</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr"/>
       <c r="M26" s="6" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="N26" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
-        </is>
-      </c>
-      <c r="O26" s="6" t="inlineStr">
-        <is>
-          <t>NH</t>
-        </is>
-      </c>
+          <t>메리츠</t>
+        </is>
+      </c>
+      <c r="O26" s="6" t="inlineStr"/>
       <c r="P26" s="7" t="inlineStr">
         <is>
-          <t>1,994</t>
+          <t>245</t>
         </is>
       </c>
       <c r="Q26" s="6" t="inlineStr">
         <is>
-          <t>4.00%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
@@ -10017,75 +10015,77 @@
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>대신밸런스제20호스팩</t>
-        </is>
-      </c>
-      <c r="B27" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
+          <t>피스피스스튜디오</t>
+        </is>
+      </c>
+      <c r="B27" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>19,000~21,500</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>6,500,000</t>
+          <t>2,272,637</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>13,000</t>
-        </is>
-      </c>
-      <c r="F27" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
+          <t>48,862</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>21.48배 (PER)</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>21500</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>1327.13</v>
+        <v>847.76</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>2194</v>
+        <v>2329</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>2026-05-22~05-25</t>
+          <t>2026-05-26~05-27</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>1,486.88</t>
+          <t>1,191.15</t>
         </is>
       </c>
       <c r="L27" s="6" t="inlineStr"/>
       <c r="M27" s="6" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="N27" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
-        </is>
-      </c>
-      <c r="O27" s="6" t="inlineStr"/>
+          <t>미래</t>
+        </is>
+      </c>
+      <c r="O27" s="6" t="inlineStr">
+        <is>
+          <t>NH</t>
+        </is>
+      </c>
       <c r="P27" s="7" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>1,994</t>
         </is>
       </c>
       <c r="Q27" s="6" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>4.00%</t>
         </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
@@ -10097,73 +10097,75 @@
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>마키나락스</t>
-        </is>
-      </c>
-      <c r="B28" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>대신밸런스제20호스팩</t>
+        </is>
+      </c>
+      <c r="B28" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>12,500~15,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>2,635,000</t>
+          <t>6,500,000</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>39,525</t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>40.5배 (PER)</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="n">
-        <v>15000</v>
+          <t>13,000</t>
+        </is>
+      </c>
+      <c r="F28" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
       </c>
       <c r="H28" s="6" t="n">
-        <v>1196.08</v>
+        <v>1327.13</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>2427</v>
+        <v>2194</v>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>2026-05-11~05-12</t>
+          <t>2026-05-22~05-25</t>
         </is>
       </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
-          <t>2,807.79</t>
+          <t>1,486.88</t>
         </is>
       </c>
       <c r="L28" s="6" t="inlineStr"/>
       <c r="M28" s="6" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="N28" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="O28" s="6" t="inlineStr"/>
       <c r="P28" s="7" t="inlineStr">
         <is>
-          <t>2,026</t>
+          <t>390</t>
         </is>
       </c>
       <c r="Q28" s="6" t="inlineStr">
         <is>
-          <t>5.00%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
@@ -10175,7 +10177,7 @@
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>폴레드</t>
+          <t>마키나락스</t>
         </is>
       </c>
       <c r="B29" s="18" t="inlineStr">
@@ -10185,63 +10187,63 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>4,100~5,000</t>
+          <t>12,500~15,000</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>2,600,000</t>
+          <t>2,635,000</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>13,000</t>
+          <t>39,525</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>19.05배 (PER)</t>
+          <t>40.5배 (PER)</t>
         </is>
       </c>
       <c r="G29" s="6" t="n">
-        <v>5000</v>
+        <v>15000</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>1486.66</v>
+        <v>1196.08</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>2372</v>
+        <v>2427</v>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>2026-05-04~05-05</t>
+          <t>2026-05-11~05-12</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>3,169.86</t>
+          <t>2,807.79</t>
         </is>
       </c>
       <c r="L29" s="6" t="inlineStr"/>
       <c r="M29" s="6" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="N29" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="O29" s="6" t="inlineStr"/>
       <c r="P29" s="7" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>2,026</t>
         </is>
       </c>
       <c r="Q29" s="6" t="inlineStr">
         <is>
-          <t>4.03%</t>
+          <t>5.00%</t>
         </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
@@ -10253,7 +10255,7 @@
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>코스모로보틱스</t>
+          <t>폴레드</t>
         </is>
       </c>
       <c r="B30" s="18" t="inlineStr">
@@ -10263,67 +10265,63 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>5,300~6,000</t>
+          <t>4,100~5,000</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>4,170,000</t>
+          <t>2,600,000</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>25,020</t>
+          <t>13,000</t>
         </is>
       </c>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>47.45배 (PER)</t>
+          <t>19.05배 (PER)</t>
         </is>
       </c>
       <c r="G30" s="6" t="n">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>1140.11</v>
+        <v>1486.66</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>2257</v>
+        <v>2372</v>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>2026-04-27~04-28</t>
+          <t>2026-05-04~05-05</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>2,013.80</t>
+          <t>3,169.86</t>
         </is>
       </c>
       <c r="L30" s="6" t="inlineStr"/>
       <c r="M30" s="6" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="N30" s="6" t="inlineStr">
         <is>
-          <t>유진</t>
-        </is>
-      </c>
-      <c r="O30" s="6" t="inlineStr">
-        <is>
           <t>NH</t>
         </is>
       </c>
+      <c r="O30" s="6" t="inlineStr"/>
       <c r="P30" s="7" t="inlineStr">
         <is>
-          <t>1,289</t>
+          <t>540</t>
         </is>
       </c>
       <c r="Q30" s="6" t="inlineStr">
         <is>
-          <t>3.78%</t>
+          <t>4.03%</t>
         </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
@@ -10335,75 +10333,77 @@
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>신한스팩18호</t>
-        </is>
-      </c>
-      <c r="B31" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
+          <t>코스모로보틱스</t>
+        </is>
+      </c>
+      <c r="B31" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>5,300~6,000</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>4,170,000</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>10,000</t>
-        </is>
-      </c>
-      <c r="F31" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
+          <t>25,020</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>47.45배 (PER)</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>6000</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>1388.6</v>
+        <v>1140.11</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>2044</v>
+        <v>2257</v>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>2026-04-20~04-21</t>
+          <t>2026-04-27~04-28</t>
         </is>
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>1,601.36</t>
+          <t>2,013.80</t>
         </is>
       </c>
       <c r="L31" s="6" t="inlineStr"/>
       <c r="M31" s="6" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="N31" s="6" t="inlineStr">
         <is>
-          <t>신한</t>
-        </is>
-      </c>
-      <c r="O31" s="6" t="inlineStr"/>
+          <t>유진</t>
+        </is>
+      </c>
+      <c r="O31" s="6" t="inlineStr">
+        <is>
+          <t>NH</t>
+        </is>
+      </c>
       <c r="P31" s="7" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>1,289</t>
         </is>
       </c>
       <c r="Q31" s="6" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>3.78%</t>
         </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
@@ -10415,42 +10415,44 @@
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>채비</t>
-        </is>
-      </c>
-      <c r="B32" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>신한스팩18호</t>
+        </is>
+      </c>
+      <c r="B32" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>12,300~15,300</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>9,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>110,700</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>24.0배 (EV/EBITDA)</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="n">
-        <v>12300</v>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="F32" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
       </c>
       <c r="H32" s="6" t="n">
-        <v>55.23</v>
+        <v>1388.6</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>751</v>
+        <v>2044</v>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
@@ -10459,33 +10461,29 @@
       </c>
       <c r="K32" s="6" t="inlineStr">
         <is>
-          <t>302.11</t>
+          <t>1,601.36</t>
         </is>
       </c>
       <c r="L32" s="6" t="inlineStr"/>
       <c r="M32" s="6" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="N32" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
-        </is>
-      </c>
-      <c r="O32" s="6" t="inlineStr">
-        <is>
-          <t>삼성</t>
-        </is>
-      </c>
+          <t>신한</t>
+        </is>
+      </c>
+      <c r="O32" s="6" t="inlineStr"/>
       <c r="P32" s="7" t="inlineStr">
         <is>
-          <t>3,384</t>
+          <t>350</t>
         </is>
       </c>
       <c r="Q32" s="6" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="R32" s="6" t="inlineStr">
@@ -10497,75 +10495,77 @@
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>키움히어로스펙2호</t>
-        </is>
-      </c>
-      <c r="B33" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
+          <t>채비</t>
+        </is>
+      </c>
+      <c r="B33" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>12,300~15,300</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>6,000,000</t>
+          <t>9,000,000</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>12,000</t>
-        </is>
-      </c>
-      <c r="F33" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="G33" s="6" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
+          <t>110,700</t>
+        </is>
+      </c>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>24.0배 (EV/EBITDA)</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>12300</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>1271.12</v>
+        <v>55.23</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>2054</v>
+        <v>751</v>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>2026-04-14~04-15</t>
+          <t>2026-04-20~04-21</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>1,727.59</t>
+          <t>302.11</t>
         </is>
       </c>
       <c r="L33" s="6" t="inlineStr"/>
       <c r="M33" s="6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="N33" s="6" t="inlineStr">
         <is>
-          <t>키움</t>
-        </is>
-      </c>
-      <c r="O33" s="6" t="inlineStr"/>
+          <t>KB</t>
+        </is>
+      </c>
+      <c r="O33" s="6" t="inlineStr">
+        <is>
+          <t>삼성</t>
+        </is>
+      </c>
       <c r="P33" s="7" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>3,384</t>
         </is>
       </c>
       <c r="Q33" s="6" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
@@ -10577,7 +10577,7 @@
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>교보스팩20호</t>
+          <t>키움히어로스펙2호</t>
         </is>
       </c>
       <c r="B34" s="19" t="inlineStr">
@@ -10592,12 +10592,12 @@
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>5,400,000</t>
+          <t>6,000,000</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>10,800</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="F34" s="19" t="inlineStr">
@@ -10611,30 +10611,30 @@
         </is>
       </c>
       <c r="H34" s="6" t="n">
-        <v>1196.99</v>
+        <v>1271.12</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>1855</v>
+        <v>2054</v>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>2026-03-23~03-24</t>
+          <t>2026-04-14~04-15</t>
         </is>
       </c>
       <c r="K34" s="6" t="inlineStr">
         <is>
-          <t>747.00</t>
+          <t>1,727.59</t>
         </is>
       </c>
       <c r="L34" s="6" t="inlineStr"/>
       <c r="M34" s="6" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="N34" s="6" t="inlineStr">
         <is>
-          <t>교보</t>
+          <t>키움</t>
         </is>
       </c>
       <c r="O34" s="6" t="inlineStr"/>
@@ -10645,7 +10645,7 @@
       </c>
       <c r="Q34" s="6" t="inlineStr">
         <is>
-          <t>2.78%</t>
+          <t>2.50%</t>
         </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
@@ -10657,42 +10657,44 @@
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>인벤테라</t>
-        </is>
-      </c>
-      <c r="B35" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>교보스팩20호</t>
+        </is>
+      </c>
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>12,100~16,600</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>1,180,000</t>
+          <t>5,400,000</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>19,588</t>
-        </is>
-      </c>
-      <c r="F35" s="6" t="inlineStr">
-        <is>
-          <t>24.34배 (PER)</t>
-        </is>
-      </c>
-      <c r="G35" s="6" t="n">
-        <v>16600</v>
+          <t>10,800</t>
+        </is>
+      </c>
+      <c r="F35" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
       </c>
       <c r="H35" s="6" t="n">
-        <v>1328.82</v>
+        <v>1196.99</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>2309</v>
+        <v>1855</v>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
@@ -10701,7 +10703,7 @@
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>1,913.00</t>
+          <t>747.00</t>
         </is>
       </c>
       <c r="L35" s="6" t="inlineStr"/>
@@ -10712,18 +10714,18 @@
       </c>
       <c r="N35" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>교보</t>
         </is>
       </c>
       <c r="O35" s="6" t="inlineStr"/>
       <c r="P35" s="7" t="inlineStr">
         <is>
-          <t>1,211</t>
+          <t>300</t>
         </is>
       </c>
       <c r="Q35" s="6" t="inlineStr">
         <is>
-          <t>6.00%</t>
+          <t>2.78%</t>
         </is>
       </c>
       <c r="R35" s="6" t="inlineStr">
@@ -10735,75 +10737,73 @@
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>신한스팩17호</t>
-        </is>
-      </c>
-      <c r="B36" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
+          <t>인벤테라</t>
+        </is>
+      </c>
+      <c r="B36" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>12,100~16,600</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>1,180,000</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>10,000</t>
-        </is>
-      </c>
-      <c r="F36" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="G36" s="6" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
+          <t>19,588</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>24.34배 (PER)</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v>16600</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>1343.8</v>
+        <v>1328.82</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>2022</v>
+        <v>2309</v>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>2026-03-19~03-20</t>
+          <t>2026-03-23~03-24</t>
         </is>
       </c>
       <c r="K36" s="6" t="inlineStr">
         <is>
-          <t>1,403.74</t>
+          <t>1,913.00</t>
         </is>
       </c>
       <c r="L36" s="6" t="inlineStr"/>
       <c r="M36" s="6" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="N36" s="6" t="inlineStr">
         <is>
-          <t>신한</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="O36" s="6" t="inlineStr"/>
       <c r="P36" s="7" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>1,211</t>
         </is>
       </c>
       <c r="Q36" s="6" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>6.00%</t>
         </is>
       </c>
       <c r="R36" s="6" t="inlineStr">
@@ -10815,42 +10815,44 @@
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>리센스메디컬</t>
-        </is>
-      </c>
-      <c r="B37" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>신한스팩17호</t>
+        </is>
+      </c>
+      <c r="B37" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>9,000~11,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>1,400,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>15,400</t>
-        </is>
-      </c>
-      <c r="F37" s="6" t="inlineStr">
-        <is>
-          <t>31.33배 (PER)</t>
-        </is>
-      </c>
-      <c r="G37" s="6" t="n">
-        <v>11000</v>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="F37" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
       </c>
       <c r="H37" s="6" t="n">
-        <v>1352.63</v>
+        <v>1343.8</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>2261</v>
+        <v>2022</v>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
@@ -10859,33 +10861,29 @@
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>2,097.68</t>
+          <t>1,403.74</t>
         </is>
       </c>
       <c r="L37" s="6" t="inlineStr"/>
       <c r="M37" s="6" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="N37" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
-        </is>
-      </c>
-      <c r="O37" s="6" t="inlineStr">
-        <is>
-          <t>KB</t>
-        </is>
-      </c>
+          <t>신한</t>
+        </is>
+      </c>
+      <c r="O37" s="6" t="inlineStr"/>
       <c r="P37" s="7" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>350</t>
         </is>
       </c>
       <c r="Q37" s="6" t="inlineStr">
         <is>
-          <t>5.77%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="R37" s="6" t="inlineStr">
@@ -10897,75 +10895,77 @@
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>NH스팩33호</t>
-        </is>
-      </c>
-      <c r="B38" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
+          <t>리센스메디컬</t>
+        </is>
+      </c>
+      <c r="B38" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>9,000~11,000</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>6,350,000</t>
+          <t>1,400,000</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>12,700</t>
-        </is>
-      </c>
-      <c r="F38" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="G38" s="6" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
+          <t>15,400</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>31.33배 (PER)</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="n">
+        <v>11000</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>1228.71</v>
+        <v>1352.63</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>2058</v>
+        <v>2261</v>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>2026-03-17~03-18</t>
+          <t>2026-03-19~03-20</t>
         </is>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
-          <t>569.27</t>
+          <t>2,097.68</t>
         </is>
       </c>
       <c r="L38" s="6" t="inlineStr"/>
       <c r="M38" s="6" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="N38" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
-        </is>
-      </c>
-      <c r="O38" s="6" t="inlineStr"/>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="O38" s="6" t="inlineStr">
+        <is>
+          <t>KB</t>
+        </is>
+      </c>
       <c r="P38" s="7" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>916</t>
         </is>
       </c>
       <c r="Q38" s="6" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>5.77%</t>
         </is>
       </c>
       <c r="R38" s="6" t="inlineStr">
@@ -10977,73 +10977,75 @@
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>메쥬</t>
-        </is>
-      </c>
-      <c r="B39" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>NH스팩33호</t>
+        </is>
+      </c>
+      <c r="B39" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>16,700~21,600</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>1,345,000</t>
+          <t>6,350,000</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>29,052</t>
-        </is>
-      </c>
-      <c r="F39" s="6" t="inlineStr">
-        <is>
-          <t>20.66배 (PER)</t>
-        </is>
-      </c>
-      <c r="G39" s="6" t="n">
-        <v>21600</v>
+          <t>12,700</t>
+        </is>
+      </c>
+      <c r="F39" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
       </c>
       <c r="H39" s="6" t="n">
-        <v>1108.93</v>
+        <v>1228.71</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>2320</v>
+        <v>2058</v>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>2026-03-16~03-17</t>
+          <t>2026-03-17~03-18</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>2,428.25</t>
+          <t>569.27</t>
         </is>
       </c>
       <c r="L39" s="6" t="inlineStr"/>
       <c r="M39" s="6" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="N39" s="6" t="inlineStr">
         <is>
-          <t>신한</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="O39" s="6" t="inlineStr"/>
       <c r="P39" s="7" t="inlineStr">
         <is>
-          <t>1,496</t>
+          <t>381</t>
         </is>
       </c>
       <c r="Q39" s="6" t="inlineStr">
         <is>
-          <t>5.00%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="R39" s="6" t="inlineStr">
@@ -11055,7 +11057,7 @@
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>한패스</t>
+          <t>메쥬</t>
         </is>
       </c>
       <c r="B40" s="18" t="inlineStr">
@@ -11065,32 +11067,32 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>17,000~19,000</t>
+          <t>16,700~21,600</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>1,100,000</t>
+          <t>1,345,000</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>20,900</t>
+          <t>29,052</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>29.09배 (PER)</t>
+          <t>20.66배 (PER)</t>
         </is>
       </c>
       <c r="G40" s="6" t="n">
-        <v>19000</v>
+        <v>21600</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>1172.59</v>
+        <v>1108.93</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>2229</v>
+        <v>2320</v>
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
@@ -11099,29 +11101,29 @@
       </c>
       <c r="K40" s="6" t="inlineStr">
         <is>
-          <t>1,673.04</t>
+          <t>2,428.25</t>
         </is>
       </c>
       <c r="L40" s="6" t="inlineStr"/>
       <c r="M40" s="6" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="N40" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>신한</t>
         </is>
       </c>
       <c r="O40" s="6" t="inlineStr"/>
       <c r="P40" s="7" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>1,496</t>
         </is>
       </c>
       <c r="Q40" s="6" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>5.00%</t>
         </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
@@ -11133,7 +11135,7 @@
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>아이엠바이오로직스</t>
+          <t>한패스</t>
         </is>
       </c>
       <c r="B41" s="18" t="inlineStr">
@@ -11143,47 +11145,47 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>19,000~26,000</t>
+          <t>17,000~19,000</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>1,100,000</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>52,000</t>
+          <t>20,900</t>
         </is>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>21.46배 (PER)</t>
+          <t>29.09배 (PER)</t>
         </is>
       </c>
       <c r="G41" s="6" t="n">
-        <v>26000</v>
+        <v>19000</v>
       </c>
       <c r="H41" s="6" t="n">
-        <v>839.23</v>
+        <v>1172.59</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>2333</v>
+        <v>2229</v>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11~03-12</t>
+          <t>2026-03-16~03-17</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>1,806.00</t>
+          <t>1,673.04</t>
         </is>
       </c>
       <c r="L41" s="6" t="inlineStr"/>
       <c r="M41" s="6" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="N41" s="6" t="inlineStr">
@@ -11194,12 +11196,12 @@
       <c r="O41" s="6" t="inlineStr"/>
       <c r="P41" s="7" t="inlineStr">
         <is>
-          <t>2,650</t>
+          <t>753</t>
         </is>
       </c>
       <c r="Q41" s="6" t="inlineStr">
         <is>
-          <t>5.00%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
@@ -11211,7 +11213,7 @@
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>카나프테라퓨틱스</t>
+          <t>아이엠바이오로직스</t>
         </is>
       </c>
       <c r="B42" s="18" t="inlineStr">
@@ -11221,7 +11223,7 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>16,000~20,000</t>
+          <t>19,000~26,000</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
@@ -11231,37 +11233,37 @@
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>40,000</t>
+          <t>52,000</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>23.59배 (PER)</t>
+          <t>21.46배 (PER)</t>
         </is>
       </c>
       <c r="G42" s="6" t="n">
-        <v>20000</v>
+        <v>26000</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>962.1</v>
+        <v>839.23</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>2327</v>
+        <v>2333</v>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>2026-03-05~03-06</t>
+          <t>2026-03-11~03-12</t>
         </is>
       </c>
       <c r="K42" s="6" t="inlineStr">
         <is>
-          <t>1,899.29</t>
+          <t>1,806.00</t>
         </is>
       </c>
       <c r="L42" s="6" t="inlineStr"/>
       <c r="M42" s="6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="N42" s="6" t="inlineStr">
@@ -11272,7 +11274,7 @@
       <c r="O42" s="6" t="inlineStr"/>
       <c r="P42" s="7" t="inlineStr">
         <is>
-          <t>2,050</t>
+          <t>2,650</t>
         </is>
       </c>
       <c r="Q42" s="6" t="inlineStr">
@@ -11289,7 +11291,7 @@
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>액스비스</t>
+          <t>카나프테라퓨틱스</t>
         </is>
       </c>
       <c r="B43" s="18" t="inlineStr">
@@ -11299,63 +11301,63 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>10,100~11,500</t>
+          <t>16,000~20,000</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>2,300,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>26,450</t>
+          <t>40,000</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>27.60배 (PER)</t>
+          <t>23.59배 (PER)</t>
         </is>
       </c>
       <c r="G43" s="6" t="n">
-        <v>11500</v>
+        <v>20000</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>1124.21</v>
+        <v>962.1</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>2411</v>
+        <v>2327</v>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>2026-02-23~02-24</t>
+          <t>2026-03-05~03-06</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>1,960.87</t>
+          <t>1,899.29</t>
         </is>
       </c>
       <c r="L43" s="6" t="inlineStr"/>
       <c r="M43" s="6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="N43" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="O43" s="6" t="inlineStr"/>
       <c r="P43" s="7" t="inlineStr">
         <is>
-          <t>1,090</t>
+          <t>2,050</t>
         </is>
       </c>
       <c r="Q43" s="6" t="inlineStr">
         <is>
-          <t>4.00%</t>
+          <t>5.00%</t>
         </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
@@ -11367,7 +11369,7 @@
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>에스팀</t>
+          <t>액스비스</t>
         </is>
       </c>
       <c r="B44" s="18" t="inlineStr">
@@ -11377,32 +11379,32 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>7,000~8,500</t>
+          <t>10,100~11,500</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>1,800,000</t>
+          <t>2,300,000</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>15,300</t>
+          <t>26,450</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>17.71배 (EV/EBITDA)</t>
+          <t>27.60배 (PER)</t>
         </is>
       </c>
       <c r="G44" s="6" t="n">
-        <v>8500</v>
+        <v>11500</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>1334.91</v>
+        <v>1124.21</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>2263</v>
+        <v>2411</v>
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
@@ -11411,29 +11413,29 @@
       </c>
       <c r="K44" s="6" t="inlineStr">
         <is>
-          <t>1,334.91</t>
+          <t>1,960.87</t>
         </is>
       </c>
       <c r="L44" s="6" t="inlineStr"/>
       <c r="M44" s="6" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="N44" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="O44" s="6" t="inlineStr"/>
       <c r="P44" s="7" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>1,090</t>
         </is>
       </c>
       <c r="Q44" s="6" t="inlineStr">
         <is>
-          <t>5.00%</t>
+          <t>4.00%</t>
         </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
@@ -11445,7 +11447,7 @@
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>케이뱅크 (유가)</t>
+          <t>에스팀</t>
         </is>
       </c>
       <c r="B45" s="18" t="inlineStr">
@@ -11455,67 +11457,63 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>8,300~9,500</t>
+          <t>7,000~8,500</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>60,000,000</t>
+          <t>1,800,000</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>498,000</t>
+          <t>15,300</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>1.80배 (PBR)</t>
+          <t>17.71배 (EV/EBITDA)</t>
         </is>
       </c>
       <c r="G45" s="6" t="n">
-        <v>8300</v>
+        <v>8500</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>198.53</v>
+        <v>1334.91</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>2007</v>
+        <v>2263</v>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>2026-02-20~23</t>
+          <t>2026-02-23~02-24</t>
         </is>
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>134.59</t>
+          <t>1,334.91</t>
         </is>
       </c>
       <c r="L45" s="6" t="inlineStr"/>
       <c r="M45" s="6" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="N45" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
-        </is>
-      </c>
-      <c r="O45" s="6" t="inlineStr">
-        <is>
-          <t>삼성</t>
-        </is>
-      </c>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="O45" s="6" t="inlineStr"/>
       <c r="P45" s="7" t="inlineStr">
         <is>
-          <t>5,976</t>
+          <t>788</t>
         </is>
       </c>
       <c r="Q45" s="6" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>5.00%</t>
         </is>
       </c>
       <c r="R45" s="6" t="inlineStr">
@@ -11527,63 +11525,57 @@
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>세미티에스</t>
-        </is>
-      </c>
-      <c r="B46" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="C46" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="D46" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="E46" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="F46" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="G46" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="H46" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="I46" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="J46" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="K46" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
+          <t>케이뱅크 (유가)</t>
+        </is>
+      </c>
+      <c r="B46" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>8,300~9,500</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>60,000,000</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>498,000</t>
+        </is>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>1.80배 (PBR)</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="n">
+        <v>8300</v>
+      </c>
+      <c r="H46" s="6" t="n">
+        <v>198.53</v>
+      </c>
+      <c r="I46" s="6" t="n">
+        <v>2007</v>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-20~23</t>
+        </is>
+      </c>
+      <c r="K46" s="6" t="inlineStr">
+        <is>
+          <t>134.59</t>
         </is>
       </c>
       <c r="L46" s="6" t="inlineStr"/>
       <c r="M46" s="6" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="N46" s="6" t="inlineStr">
@@ -11591,77 +11583,87 @@
           <t>NH</t>
         </is>
       </c>
-      <c r="O46" s="6" t="inlineStr"/>
-      <c r="P46" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="Q46" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
+      <c r="O46" s="6" t="inlineStr">
+        <is>
+          <t>삼성</t>
+        </is>
+      </c>
+      <c r="P46" s="7" t="inlineStr">
+        <is>
+          <t>5,976</t>
+        </is>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
-          <t>상장완료(스팩합병)</t>
+          <t>상장완료</t>
         </is>
       </c>
     </row>
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>덕양에너젠</t>
-        </is>
-      </c>
-      <c r="B47" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>8,500~10,000</t>
-        </is>
-      </c>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>7,500,000</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>75,000</t>
-        </is>
-      </c>
-      <c r="F47" s="6" t="inlineStr">
-        <is>
-          <t>30.32배 (EV/EBITDA)</t>
-        </is>
-      </c>
-      <c r="G47" s="6" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H47" s="6" t="n">
-        <v>650.14</v>
-      </c>
-      <c r="I47" s="6" t="n">
-        <v>2324</v>
-      </c>
-      <c r="J47" s="6" t="inlineStr">
-        <is>
-          <t>2026-01-20~01-21</t>
-        </is>
-      </c>
-      <c r="K47" s="6" t="inlineStr">
-        <is>
-          <t>1,354.00</t>
+          <t>세미티에스</t>
+        </is>
+      </c>
+      <c r="B47" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="C47" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="D47" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="E47" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="F47" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="G47" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="H47" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="I47" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="J47" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="K47" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="L47" s="6" t="inlineStr"/>
       <c r="M47" s="6" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="N47" s="6" t="inlineStr">
@@ -11669,87 +11671,77 @@
           <t>NH</t>
         </is>
       </c>
-      <c r="O47" s="6" t="inlineStr">
-        <is>
-          <t>미래</t>
-        </is>
-      </c>
-      <c r="P47" s="7" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
-      </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>2.92%</t>
+      <c r="O47" s="6" t="inlineStr"/>
+      <c r="P47" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="Q47" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
-          <t>상장완료</t>
+          <t>상장완료(스팩합병)</t>
         </is>
       </c>
     </row>
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>케이피항공산업</t>
-        </is>
-      </c>
-      <c r="B48" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="C48" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="D48" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="E48" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="F48" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="G48" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="H48" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="I48" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="J48" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="K48" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
+          <t>덕양에너젠</t>
+        </is>
+      </c>
+      <c r="B48" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>8,500~10,000</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>7,500,000</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>75,000</t>
+        </is>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>30.32배 (EV/EBITDA)</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H48" s="6" t="n">
+        <v>650.14</v>
+      </c>
+      <c r="I48" s="6" t="n">
+        <v>2324</v>
+      </c>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-20~01-21</t>
+        </is>
+      </c>
+      <c r="K48" s="6" t="inlineStr">
+        <is>
+          <t>1,354.00</t>
         </is>
       </c>
       <c r="L48" s="6" t="inlineStr"/>
       <c r="M48" s="6" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="N48" s="6" t="inlineStr">
@@ -11757,27 +11749,31 @@
           <t>NH</t>
         </is>
       </c>
-      <c r="O48" s="6" t="inlineStr"/>
-      <c r="P48" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="Q48" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
+      <c r="O48" s="6" t="inlineStr">
+        <is>
+          <t>미래</t>
+        </is>
+      </c>
+      <c r="P48" s="7" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>2.92%</t>
         </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
-          <t>상장완료(스팩합병)</t>
+          <t>상장완료</t>
         </is>
       </c>
     </row>
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>삼성스팩13호</t>
+          <t>케이피항공산업</t>
         </is>
       </c>
       <c r="B49" s="19" t="inlineStr">
@@ -11785,19 +11781,19 @@
           <t>해당없음</t>
         </is>
       </c>
-      <c r="C49" s="6" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>6,000,000</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>12,000</t>
+      <c r="C49" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="D49" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="E49" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="F49" s="19" t="inlineStr">
@@ -11805,223 +11801,231 @@
           <t>해당없음</t>
         </is>
       </c>
-      <c r="G49" s="6" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
-      </c>
-      <c r="H49" s="6" t="n">
-        <v>1159.11</v>
-      </c>
-      <c r="I49" s="6" t="n">
-        <v>1892</v>
-      </c>
-      <c r="J49" s="6" t="inlineStr">
-        <is>
-          <t>2026-01-12~01-13</t>
-        </is>
-      </c>
-      <c r="K49" s="6" t="inlineStr">
-        <is>
-          <t>1,870.40</t>
+      <c r="G49" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="H49" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="I49" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="J49" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="K49" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="L49" s="6" t="inlineStr"/>
       <c r="M49" s="6" t="inlineStr">
         <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="N49" s="6" t="inlineStr">
+        <is>
+          <t>NH</t>
+        </is>
+      </c>
+      <c r="O49" s="6" t="inlineStr"/>
+      <c r="P49" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="Q49" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>상장완료(스팩합병)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="30" customHeight="1">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>삼성스팩13호</t>
+        </is>
+      </c>
+      <c r="B50" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>6,000,000</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="F50" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="n">
+        <v>1159.11</v>
+      </c>
+      <c r="I50" s="6" t="n">
+        <v>1892</v>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-12~01-13</t>
+        </is>
+      </c>
+      <c r="K50" s="6" t="inlineStr">
+        <is>
+          <t>1,870.40</t>
+        </is>
+      </c>
+      <c r="L50" s="6" t="inlineStr"/>
+      <c r="M50" s="6" t="inlineStr">
+        <is>
           <t>2026-01-21</t>
         </is>
       </c>
-      <c r="N49" s="6" t="inlineStr">
+      <c r="N50" s="6" t="inlineStr">
         <is>
           <t>삼성</t>
         </is>
       </c>
-      <c r="O49" s="6" t="inlineStr"/>
-      <c r="P49" s="7" t="inlineStr">
+      <c r="O50" s="6" t="inlineStr"/>
+      <c r="P50" s="7" t="inlineStr">
         <is>
           <t>360</t>
         </is>
       </c>
-      <c r="Q49" s="6" t="inlineStr">
+      <c r="Q50" s="6" t="inlineStr">
         <is>
           <t>3.00%</t>
         </is>
       </c>
-      <c r="R49" s="6" t="inlineStr">
+      <c r="R50" s="6" t="inlineStr">
         <is>
           <t>상장완료</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>■ 공모 진행 (예심 승인법인)  (33건)</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="n"/>
-      <c r="C51" s="4" t="n"/>
-      <c r="D51" s="4" t="n"/>
-      <c r="E51" s="4" t="n"/>
-      <c r="F51" s="4" t="n"/>
-      <c r="G51" s="4" t="n"/>
-      <c r="H51" s="4" t="n"/>
-      <c r="I51" s="4" t="n"/>
-      <c r="J51" s="4" t="n"/>
-      <c r="K51" s="4" t="n"/>
-      <c r="L51" s="4" t="n"/>
-      <c r="M51" s="4" t="n"/>
-      <c r="N51" s="4" t="n"/>
-      <c r="O51" s="4" t="n"/>
-      <c r="P51" s="4" t="n"/>
-      <c r="Q51" s="4" t="n"/>
-      <c r="R51" s="4" t="n"/>
-    </row>
-    <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>브릴스</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>08-31~09-04</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>16,500~19,500</t>
-        </is>
-      </c>
-      <c r="D52" s="7" t="inlineStr">
-        <is>
-          <t>1,200,000</t>
-        </is>
-      </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>23,400,000,000</t>
-        </is>
-      </c>
-      <c r="F52" s="6" t="inlineStr">
-        <is>
-          <t>13.44 (PSR)</t>
-        </is>
-      </c>
-      <c r="G52" s="6" t="inlineStr">
-        <is>
-          <t>19,500</t>
-        </is>
-      </c>
-      <c r="H52" s="6" t="n">
-        <v>1187.74</v>
-      </c>
-      <c r="I52" s="6" t="n">
-        <v>2181</v>
-      </c>
-      <c r="J52" s="6" t="inlineStr">
-        <is>
-          <t>09-08~09-09</t>
-        </is>
-      </c>
-      <c r="K52" s="6" t="inlineStr">
-        <is>
-          <t>4,418.97</t>
-        </is>
-      </c>
-      <c r="L52" s="6" t="inlineStr"/>
-      <c r="M52" s="6" t="inlineStr"/>
-      <c r="N52" s="6" t="inlineStr">
-        <is>
-          <t>아이비케이투자증권</t>
-        </is>
-      </c>
-      <c r="O52" s="6" t="inlineStr"/>
-      <c r="P52" s="7" t="inlineStr">
-        <is>
-          <t>713,790,000</t>
-        </is>
-      </c>
-      <c r="Q52" s="6" t="inlineStr">
-        <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>청약완료·상장대기</t>
-        </is>
-      </c>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>■ 공모 진행 (예심 승인법인)  (32건)</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="n"/>
+      <c r="C52" s="4" t="n"/>
+      <c r="D52" s="4" t="n"/>
+      <c r="E52" s="4" t="n"/>
+      <c r="F52" s="4" t="n"/>
+      <c r="G52" s="4" t="n"/>
+      <c r="H52" s="4" t="n"/>
+      <c r="I52" s="4" t="n"/>
+      <c r="J52" s="4" t="n"/>
+      <c r="K52" s="4" t="n"/>
+      <c r="L52" s="4" t="n"/>
+      <c r="M52" s="4" t="n"/>
+      <c r="N52" s="4" t="n"/>
+      <c r="O52" s="4" t="n"/>
+      <c r="P52" s="4" t="n"/>
+      <c r="Q52" s="4" t="n"/>
+      <c r="R52" s="4" t="n"/>
     </row>
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>케이비제34호스팩</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>09-04~09-07</t>
-        </is>
-      </c>
-      <c r="C53" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>08-31~09-04</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>16,500~19,500</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>7,000,000</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>14,000,000,000</t>
-        </is>
-      </c>
-      <c r="F53" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>23,400,000,000</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>13.44 (PSR)</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>19,500</t>
         </is>
       </c>
       <c r="H53" s="6" t="n">
-        <v>1232.51</v>
+        <v>1187.74</v>
       </c>
       <c r="I53" s="6" t="n">
-        <v>2001</v>
+        <v>2181</v>
       </c>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>09-10~09-11</t>
+          <t>09-08~09-09</t>
         </is>
       </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>6,777.78</t>
+          <t>4,418.97</t>
         </is>
       </c>
       <c r="L53" s="6" t="inlineStr"/>
       <c r="M53" s="6" t="inlineStr"/>
-      <c r="N53" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="N53" s="6" t="inlineStr">
+        <is>
+          <t>아이비케이투자증권</t>
         </is>
       </c>
       <c r="O53" s="6" t="inlineStr"/>
-      <c r="P53" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P53" s="7" t="inlineStr">
+        <is>
+          <t>713,790,000</t>
         </is>
       </c>
       <c r="Q53" s="6" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
@@ -12033,71 +12037,71 @@
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>와이즈플래닛컴퍼니</t>
+          <t>케이비제34호스팩</t>
         </is>
       </c>
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>09-04~09-10</t>
-        </is>
-      </c>
-      <c r="C54" s="6" t="inlineStr">
-        <is>
-          <t>10,000~12,000</t>
+          <t>09-04~09-07</t>
+        </is>
+      </c>
+      <c r="C54" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>1,600,000</t>
+          <t>7,000,000</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>19,200,000,000</t>
-        </is>
-      </c>
-      <c r="F54" s="6" t="inlineStr">
-        <is>
-          <t>20.04배 (PER)</t>
+          <t>14,000,000,000</t>
+        </is>
+      </c>
+      <c r="F54" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="H54" s="6" t="n">
-        <v>1248.47</v>
+        <v>1232.51</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>2323</v>
+        <v>2001</v>
       </c>
       <c r="J54" s="6" t="inlineStr">
         <is>
-          <t>09-14~09-15</t>
+          <t>09-10~09-11</t>
         </is>
       </c>
       <c r="K54" s="6" t="inlineStr">
         <is>
-          <t>3,568.86</t>
+          <t>6,777.78</t>
         </is>
       </c>
       <c r="L54" s="6" t="inlineStr"/>
       <c r="M54" s="6" t="inlineStr"/>
-      <c r="N54" s="6" t="inlineStr">
-        <is>
-          <t>대신증권</t>
+      <c r="N54" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="O54" s="6" t="inlineStr"/>
-      <c r="P54" s="7" t="inlineStr">
-        <is>
-          <t>494,400,000</t>
+      <c r="P54" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="Q54" s="6" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
@@ -12537,32 +12541,32 @@
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>에스케이증권제14호기업인수목적</t>
+          <t>티앤이코리아</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>10-12~10-13</t>
-        </is>
-      </c>
-      <c r="C61" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>10-07~10-14</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>12,600~15,300</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>6,500,000</t>
+          <t>2,400,000</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>13,000,000,000</t>
-        </is>
-      </c>
-      <c r="F61" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>30,240,000,000</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>19.48배 (PER)</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr"/>
@@ -12570,26 +12574,26 @@
       <c r="I61" s="6" t="inlineStr"/>
       <c r="J61" s="6" t="inlineStr">
         <is>
-          <t>10-15~10-16</t>
+          <t>10-20~10-21</t>
         </is>
       </c>
       <c r="K61" s="6" t="inlineStr"/>
       <c r="L61" s="6" t="inlineStr"/>
       <c r="M61" s="6" t="inlineStr"/>
-      <c r="N61" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="N61" s="6" t="inlineStr">
+        <is>
+          <t>신한투자증권</t>
         </is>
       </c>
       <c r="O61" s="6" t="inlineStr"/>
-      <c r="P61" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P61" s="7" t="inlineStr">
+        <is>
+          <t>1,245,888,000</t>
         </is>
       </c>
       <c r="Q61" s="6" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="R61" s="6" t="inlineStr">
@@ -12601,32 +12605,32 @@
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>크리에이츠</t>
+          <t>에스케이증권제14호기업인수목적</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>10-12~10-16</t>
-        </is>
-      </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>15,000~18,000</t>
+          <t>10-12~10-13</t>
+        </is>
+      </c>
+      <c r="C62" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>1,400,000</t>
+          <t>6,500,000</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>21,000,000,000</t>
-        </is>
-      </c>
-      <c r="F62" s="6" t="inlineStr">
-        <is>
-          <t>19.15배 (PER)</t>
+          <t>13,000,000,000</t>
+        </is>
+      </c>
+      <c r="F62" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr"/>
@@ -12634,26 +12638,26 @@
       <c r="I62" s="6" t="inlineStr"/>
       <c r="J62" s="6" t="inlineStr">
         <is>
-          <t>10-20~10-21</t>
+          <t>10-15~10-16</t>
         </is>
       </c>
       <c r="K62" s="6" t="inlineStr"/>
       <c r="L62" s="6" t="inlineStr"/>
       <c r="M62" s="6" t="inlineStr"/>
-      <c r="N62" s="6" t="inlineStr">
-        <is>
-          <t>삼성증권</t>
+      <c r="N62" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="O62" s="6" t="inlineStr"/>
-      <c r="P62" s="7" t="inlineStr">
-        <is>
-          <t>865,200,000</t>
+      <c r="P62" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="Q62" s="6" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="R62" s="6" t="inlineStr">
@@ -12665,32 +12669,32 @@
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>래블업</t>
+          <t>크리에이츠</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>10-13~10-19</t>
+          <t>10-12~10-16</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>19,000~22,000</t>
+          <t>15,000~18,000</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>2,180,000</t>
+          <t>1,400,000</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>41,420,000,000</t>
+          <t>21,000,000,000</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>33.6배 (PER)</t>
+          <t>19.15배 (PER)</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr"/>
@@ -12698,7 +12702,7 @@
       <c r="I63" s="6" t="inlineStr"/>
       <c r="J63" s="6" t="inlineStr">
         <is>
-          <t>10-22~10-23</t>
+          <t>10-20~10-21</t>
         </is>
       </c>
       <c r="K63" s="6" t="inlineStr"/>
@@ -12706,18 +12710,18 @@
       <c r="M63" s="6" t="inlineStr"/>
       <c r="N63" s="6" t="inlineStr">
         <is>
-          <t>NH투자증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="O63" s="6" t="inlineStr"/>
       <c r="P63" s="7" t="inlineStr">
         <is>
-          <t>1,908,899,000</t>
+          <t>865,200,000</t>
         </is>
       </c>
       <c r="Q63" s="6" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="R63" s="6" t="inlineStr">
@@ -12729,32 +12733,32 @@
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>엠비디</t>
+          <t>래블업</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>10-16~10-22</t>
+          <t>10-13~10-19</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>9,600~11,700</t>
+          <t>19,000~22,000</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>2,180,000</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>19,200,000,000</t>
+          <t>41,420,000,000</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>26.87배 (PER)</t>
+          <t>33.6배 (PER)</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr"/>
@@ -12762,7 +12766,7 @@
       <c r="I64" s="6" t="inlineStr"/>
       <c r="J64" s="6" t="inlineStr">
         <is>
-          <t>10-28~10-29</t>
+          <t>10-22~10-23</t>
         </is>
       </c>
       <c r="K64" s="6" t="inlineStr"/>
@@ -12770,18 +12774,18 @@
       <c r="M64" s="6" t="inlineStr"/>
       <c r="N64" s="6" t="inlineStr">
         <is>
-          <t>하나증권</t>
+          <t>NH투자증권</t>
         </is>
       </c>
       <c r="O64" s="6" t="inlineStr"/>
       <c r="P64" s="7" t="inlineStr">
         <is>
-          <t>988,800,000</t>
+          <t>1,908,899,000</t>
         </is>
       </c>
       <c r="Q64" s="6" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="R64" s="6" t="inlineStr">
@@ -12793,32 +12797,32 @@
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>엠에스바이오</t>
+          <t>엠비디</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>09-28~10-02</t>
+          <t>10-16~10-22</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>6,800~7,800</t>
+          <t>9,600~11,700</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>27,200,000,000</t>
+          <t>19,200,000,000</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>30.89배 (PER)</t>
+          <t>26.87배 (PER)</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr"/>
@@ -12826,7 +12830,7 @@
       <c r="I65" s="6" t="inlineStr"/>
       <c r="J65" s="6" t="inlineStr">
         <is>
-          <t>10-12~10-13</t>
+          <t>10-28~10-29</t>
         </is>
       </c>
       <c r="K65" s="6" t="inlineStr"/>
@@ -12834,55 +12838,55 @@
       <c r="M65" s="6" t="inlineStr"/>
       <c r="N65" s="6" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>하나증권</t>
         </is>
       </c>
       <c r="O65" s="6" t="inlineStr"/>
       <c r="P65" s="7" t="inlineStr">
         <is>
-          <t>1,120,640,000</t>
+          <t>988,800,000</t>
         </is>
       </c>
       <c r="Q65" s="6" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="R65" s="6" t="inlineStr">
         <is>
-          <t>최초</t>
+          <t>정정</t>
         </is>
       </c>
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>티앤이코리아</t>
+          <t>엠에스바이오</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>10-07~10-14</t>
+          <t>09-28~10-02</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>12,600~15,300</t>
+          <t>6,800~7,800</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>2,400,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>30,240,000,000</t>
+          <t>27,200,000,000</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>19.48배 (PER)</t>
+          <t>30.89배 (PER)</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr"/>
@@ -12890,7 +12894,7 @@
       <c r="I66" s="6" t="inlineStr"/>
       <c r="J66" s="6" t="inlineStr">
         <is>
-          <t>10-20~10-21</t>
+          <t>10-12~10-13</t>
         </is>
       </c>
       <c r="K66" s="6" t="inlineStr"/>
@@ -12898,13 +12902,13 @@
       <c r="M66" s="6" t="inlineStr"/>
       <c r="N66" s="6" t="inlineStr">
         <is>
-          <t>신한투자증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="O66" s="6" t="inlineStr"/>
       <c r="P66" s="7" t="inlineStr">
         <is>
-          <t>1,245,888,000</t>
+          <t>1,120,640,000</t>
         </is>
       </c>
       <c r="Q66" s="6" t="inlineStr">
@@ -14371,7 +14375,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F14" s="21">
         <f>IF((C14+D14)=0,"-",C14/(C14+D14))</f>
@@ -14453,11 +14457,11 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>179,730,000,000</t>
+          <t>198,930,000,000</t>
         </is>
       </c>
     </row>

--- a/IPO_analysis.xlsx
+++ b/IPO_analysis.xlsx
@@ -618,7 +618,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>기준일 2026-09-23 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
+          <t>기준일 2026-09-24 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
         </is>
       </c>
     </row>

--- a/IPO_analysis.xlsx
+++ b/IPO_analysis.xlsx
@@ -618,7 +618,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>기준일 2026-09-24 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
+          <t>기준일 2026-09-25 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
         </is>
       </c>
     </row>

--- a/IPO_analysis.xlsx
+++ b/IPO_analysis.xlsx
@@ -618,7 +618,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>기준일 2026-09-25 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
+          <t>기준일 2026-09-26 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
         </is>
       </c>
     </row>

--- a/IPO_analysis.xlsx
+++ b/IPO_analysis.xlsx
@@ -618,7 +618,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>기준일 2026-09-26 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
+          <t>기준일 2026-09-27 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
         </is>
       </c>
     </row>

--- a/IPO_analysis.xlsx
+++ b/IPO_analysis.xlsx
@@ -618,14 +618,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>기준일 2026-09-27 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
+          <t>기준일 2026-09-28 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>■ 심사 신청(진행중)  (47건)</t>
+          <t>■ 심사 신청(진행중)  (44건)</t>
         </is>
       </c>
       <c r="B4" s="4" t="n"/>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>솔리스</t>
+          <t>이노보테라퓨틱스</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -1928,17 +1928,29 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F28" s="7" t="inlineStr"/>
-      <c r="G28" s="7" t="inlineStr"/>
-      <c r="H28" s="7" t="inlineStr"/>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="inlineStr">
+        <is>
+          <t>-5,429</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>-53,200</t>
+        </is>
+      </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>의약품 제조업</t>
         </is>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>한화</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K28" s="6" t="inlineStr">
@@ -1950,17 +1962,17 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>이노보테라퓨틱스</t>
+          <t>에스에프씨</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>유가</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -1975,27 +1987,27 @@
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>160,792</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>-5,429</t>
+          <t>25,509</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>-53,200</t>
+          <t>243,562</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>의약품 제조업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>미래, 한국</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
@@ -2007,17 +2019,17 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>에스에프씨</t>
+          <t>아델</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>유가</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -2032,27 +2044,27 @@
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>160,792</t>
+          <t>62,057</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>25,509</t>
+          <t>-64,210</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>243,562</t>
+          <t>-80,776</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>그외 기타 전문, 과학 및 기술 서비스업</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>미래, 한국</t>
+          <t>삼성, 미래</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
@@ -2064,12 +2076,12 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>아델</t>
+          <t>에버온</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -2089,27 +2101,27 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>62,057</t>
+          <t>65,225</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>-64,210</t>
+          <t>-3,606</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>-80,776</t>
+          <t>54,955</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>그외 기타 전문, 과학 및 기술 서비스업</t>
+          <t>전기업</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>삼성, 미래</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K31" s="6" t="inlineStr">
@@ -2121,12 +2133,12 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>에버온</t>
+          <t>엔키화이트햇</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -2146,27 +2158,27 @@
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>65,225</t>
+          <t>14,176</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>-3,606</t>
+          <t>-3,211</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>54,955</t>
+          <t>8,338</t>
         </is>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>전기업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>신영</t>
         </is>
       </c>
       <c r="K32" s="6" t="inlineStr">
@@ -2178,12 +2190,12 @@
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>엔키화이트햇</t>
+          <t>씨아이에스케미칼</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -2203,27 +2215,27 @@
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>14,176</t>
+          <t>15,985</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>-3,211</t>
+          <t>-11,440</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>8,338</t>
+          <t>23,706</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>기초 화학물질 제조업</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>신영</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
@@ -2235,12 +2247,12 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>씨아이에스케미칼</t>
+          <t>엠디에스코리아</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -2260,27 +2272,27 @@
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>15,985</t>
+          <t>97,972</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>-11,440</t>
+          <t>6,512</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>23,706</t>
+          <t>53,818</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>기초 화학물질 제조업</t>
+          <t>기타 식품 제조업</t>
         </is>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K34" s="6" t="inlineStr">
@@ -2292,12 +2304,12 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>엠디에스코리아</t>
+          <t>동승</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
@@ -2317,27 +2329,27 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>97,972</t>
+          <t>78,625</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>6,512</t>
+          <t>14,525</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>53,818</t>
+          <t>5,438</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>기타 식품 제조업</t>
+          <t>부동산 임대 및 공급업</t>
         </is>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K35" s="6" t="inlineStr">
@@ -2354,7 +2366,7 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>동승</t>
+          <t>에프엠더블유</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
@@ -2364,7 +2376,7 @@
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -2374,27 +2386,27 @@
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>78,625</t>
+          <t>30,282</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>14,525</t>
+          <t>4,762</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>5,438</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>부동산 임대 및 공급업</t>
+          <t>기타 식품 제조업</t>
         </is>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>유진</t>
         </is>
       </c>
       <c r="K36" s="6" t="inlineStr">
@@ -2406,22 +2418,22 @@
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>셀트릭스</t>
+          <t>소노인터내셔널</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>유가</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
@@ -2431,27 +2443,27 @@
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>16,976</t>
+          <t>2,093,051</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>4,545</t>
+          <t>-148,064</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>2,213</t>
+          <t>852,372</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>의료용품 및 기타 의약 관련제품 제조업</t>
+          <t>일반 및 생활 숙박시설 운영업</t>
         </is>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>IBK</t>
+          <t>대신, 미래</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
@@ -2463,12 +2475,12 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>에프엠더블유</t>
+          <t>싸이몬</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -2478,7 +2490,7 @@
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -2488,27 +2500,27 @@
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>30,282</t>
+          <t>48,695</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>4,762</t>
+          <t>15,714</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>61,761</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>기타 식품 제조업</t>
+          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업</t>
         </is>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>유진</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K38" s="6" t="inlineStr">
@@ -2520,17 +2532,17 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>소노인터내셔널</t>
+          <t>바이다</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>유가</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
@@ -2545,27 +2557,27 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>2,093,051</t>
+          <t>14,432</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>-148,064</t>
+          <t>-3,951</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>852,372</t>
+          <t>15,108</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>일반 및 생활 숙박시설 운영업</t>
+          <t>전자부품 제조업</t>
         </is>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>대신, 미래</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr">
@@ -2577,12 +2589,12 @@
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>싸이몬</t>
+          <t>아이알큐더스</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -2602,27 +2614,27 @@
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>48,695</t>
+          <t>10,231</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>15,714</t>
+          <t>-986</t>
         </is>
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>61,761</t>
+          <t>1,800</t>
         </is>
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="K40" s="6" t="inlineStr">
@@ -2634,12 +2646,12 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>바이다</t>
+          <t>씨엔티테크</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -2659,27 +2671,27 @@
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>14,432</t>
+          <t>27,015</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>-3,951</t>
+          <t>3,987</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>15,108</t>
+          <t>2,613</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>전자부품 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>한화, 하나</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
@@ -2691,12 +2703,12 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>럭스코</t>
+          <t>제이앤티지</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -2706,7 +2718,7 @@
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -2716,27 +2728,27 @@
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>67,976</t>
+          <t>72,378</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>6,893</t>
+          <t>9,904</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>6,743</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>전동기, 발전기 및 전기 변환 · 공급 · 제어 장치 제조업</t>
+          <t>전자부품 제조업</t>
         </is>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>IBK</t>
+          <t>대신, NH</t>
         </is>
       </c>
       <c r="K42" s="6" t="inlineStr">
@@ -2748,12 +2760,12 @@
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>아이알큐더스</t>
+          <t>인터엑스</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -2773,17 +2785,17 @@
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>10,231</t>
+          <t>8,645</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>-986</t>
+          <t>-20,272</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>1,800</t>
+          <t>4,530</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
@@ -2793,7 +2805,7 @@
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
@@ -2805,12 +2817,12 @@
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>씨엔티테크</t>
+          <t>삼홍아크튜리온</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -2830,27 +2842,27 @@
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>27,015</t>
+          <t>26,162</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>3,987</t>
+          <t>-10,314</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>2,613</t>
+          <t>6,369</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
         </is>
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>한화, 하나</t>
+          <t>삼성, 미래</t>
         </is>
       </c>
       <c r="K44" s="6" t="inlineStr">
@@ -2862,12 +2874,12 @@
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>제이앤티지</t>
+          <t>넥스트에어로스페이스</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -2887,27 +2899,27 @@
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>72,378</t>
+          <t>12,084</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>9,904</t>
+          <t>-17,270</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>6,743</t>
+          <t>6,158</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>전자부품 제조업</t>
+          <t>유인 항공기, 항공우주선 및 보조장치 제조업</t>
         </is>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>대신, NH</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K45" s="6" t="inlineStr">
@@ -2919,12 +2931,12 @@
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>인터엑스</t>
+          <t>비앤비코리아</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -2944,27 +2956,27 @@
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>8,645</t>
+          <t>141,169</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>-20,272</t>
+          <t>21,406</t>
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>4,530</t>
+          <t>43,932</t>
         </is>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K46" s="6" t="inlineStr">
@@ -2976,12 +2988,12 @@
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>삼홍아크튜리온</t>
+          <t>오토핸즈</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -2991,7 +3003,7 @@
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
@@ -3001,27 +3013,27 @@
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>26,162</t>
+          <t>238,564</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>-10,314</t>
+          <t>6,047</t>
         </is>
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>6,369</t>
+          <t>6,129</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
+          <t>자동차 판매업</t>
         </is>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>삼성, 미래</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K47" s="6" t="inlineStr">
@@ -3033,12 +3045,12 @@
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>넥스트에어로스페이스</t>
+          <t>아이벡스메디칼시스템즈</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -3058,27 +3070,27 @@
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>12,084</t>
+          <t>15,282</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>-17,270</t>
+          <t>-7,227</t>
         </is>
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>6,158</t>
+          <t>744</t>
         </is>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
-          <t>유인 항공기, 항공우주선 및 보조장치 제조업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K48" s="6" t="inlineStr">
@@ -3090,12 +3102,12 @@
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>비앤비코리아</t>
+          <t>피지티</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -3115,17 +3127,17 @@
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>141,169</t>
+          <t>40,141</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>21,406</t>
+          <t>-69,722</t>
         </is>
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>43,932</t>
+          <t>6,029</t>
         </is>
       </c>
       <c r="I49" s="6" t="inlineStr">
@@ -3135,7 +3147,7 @@
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K49" s="6" t="inlineStr">
@@ -3144,248 +3156,236 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>오토핸즈</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>■ 심사 승인  (70건)</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="n"/>
+      <c r="C51" s="4" t="n"/>
+      <c r="D51" s="4" t="n"/>
+      <c r="E51" s="4" t="n"/>
+      <c r="F51" s="4" t="n"/>
+      <c r="G51" s="4" t="n"/>
+      <c r="H51" s="4" t="n"/>
+      <c r="I51" s="4" t="n"/>
+      <c r="J51" s="4" t="n"/>
+      <c r="K51" s="4" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>일자</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>회사명</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>시장</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>상장유형</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>기준연도</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>자기자본</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>업종</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>대표주관사</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>현황</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>셀트릭스</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
         <is>
           <t>코스닥</t>
         </is>
       </c>
-      <c r="D50" s="6" t="inlineStr">
+      <c r="D53" s="6" t="inlineStr">
         <is>
           <t>스팩 소멸합병</t>
         </is>
       </c>
-      <c r="E50" s="6" t="inlineStr">
+      <c r="E53" s="6" t="inlineStr">
         <is>
           <t>FY25</t>
         </is>
       </c>
-      <c r="F50" s="7" t="inlineStr">
-        <is>
-          <t>238,564</t>
-        </is>
-      </c>
-      <c r="G50" s="7" t="inlineStr">
-        <is>
-          <t>6,047</t>
-        </is>
-      </c>
-      <c r="H50" s="7" t="inlineStr">
-        <is>
-          <t>6,129</t>
-        </is>
-      </c>
-      <c r="I50" s="6" t="inlineStr">
-        <is>
-          <t>자동차 판매업</t>
-        </is>
-      </c>
-      <c r="J50" s="6" t="inlineStr">
-        <is>
-          <t>미래</t>
-        </is>
-      </c>
-      <c r="K50" s="6" t="inlineStr">
-        <is>
-          <t>예심 진행중</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>아이벡스메디칼시스템즈</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>16,976</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>4,545</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>2,213</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>의료용품 및 기타 의약 관련제품 제조업</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>IBK</t>
+        </is>
+      </c>
+      <c r="K53" s="6" t="inlineStr">
+        <is>
+          <t>상장전</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>럭스코</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
         <is>
           <t>코스닥</t>
         </is>
       </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>신규상장</t>
-        </is>
-      </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>스팩 소멸합병</t>
+        </is>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
         <is>
           <t>FY25</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>15,282</t>
-        </is>
-      </c>
-      <c r="G51" s="7" t="inlineStr">
-        <is>
-          <t>-7,227</t>
-        </is>
-      </c>
-      <c r="H51" s="7" t="inlineStr">
-        <is>
-          <t>744</t>
-        </is>
-      </c>
-      <c r="I51" s="6" t="inlineStr">
-        <is>
-          <t>의료용 기기 제조업</t>
-        </is>
-      </c>
-      <c r="J51" s="6" t="inlineStr">
-        <is>
-          <t>NH</t>
-        </is>
-      </c>
-      <c r="K51" s="6" t="inlineStr">
-        <is>
-          <t>예심 진행중</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>피지티</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>67,976</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>6,893</t>
+        </is>
+      </c>
+      <c r="H54" s="7" t="inlineStr">
+        <is>
+          <t>1,000</t>
+        </is>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>전동기, 발전기 및 전기 변환 · 공급 · 제어 장치 제조업</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>IBK</t>
+        </is>
+      </c>
+      <c r="K54" s="6" t="inlineStr">
+        <is>
+          <t>상장전</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>솔리스</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
         <is>
           <t>코스닥</t>
         </is>
       </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>신규상장</t>
-        </is>
-      </c>
-      <c r="E52" s="6" t="inlineStr">
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>스팩 소멸합병</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
         <is>
           <t>FY25</t>
         </is>
       </c>
-      <c r="F52" s="7" t="inlineStr">
-        <is>
-          <t>40,141</t>
-        </is>
-      </c>
-      <c r="G52" s="7" t="inlineStr">
-        <is>
-          <t>-69,722</t>
-        </is>
-      </c>
-      <c r="H52" s="7" t="inlineStr">
-        <is>
-          <t>6,029</t>
-        </is>
-      </c>
-      <c r="I52" s="6" t="inlineStr">
-        <is>
-          <t>기타 화학제품 제조업</t>
-        </is>
-      </c>
-      <c r="J52" s="6" t="inlineStr">
-        <is>
-          <t>한국</t>
-        </is>
-      </c>
-      <c r="K52" s="6" t="inlineStr">
-        <is>
-          <t>예심 진행중</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>■ 심사 승인  (67건)</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="n"/>
-      <c r="C54" s="4" t="n"/>
-      <c r="D54" s="4" t="n"/>
-      <c r="E54" s="4" t="n"/>
-      <c r="F54" s="4" t="n"/>
-      <c r="G54" s="4" t="n"/>
-      <c r="H54" s="4" t="n"/>
-      <c r="I54" s="4" t="n"/>
-      <c r="J54" s="4" t="n"/>
-      <c r="K54" s="4" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>일자</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>회사명</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>시장</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>상장유형</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>기준연도</t>
-        </is>
-      </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="inlineStr">
-        <is>
-          <t>순이익</t>
-        </is>
-      </c>
-      <c r="H55" s="5" t="inlineStr">
-        <is>
-          <t>자기자본</t>
-        </is>
-      </c>
-      <c r="I55" s="5" t="inlineStr">
-        <is>
-          <t>업종</t>
-        </is>
-      </c>
-      <c r="J55" s="5" t="inlineStr">
-        <is>
-          <t>대표주관사</t>
-        </is>
-      </c>
-      <c r="K55" s="5" t="inlineStr">
-        <is>
-          <t>현황</t>
+      <c r="F55" s="7" t="inlineStr"/>
+      <c r="G55" s="7" t="inlineStr"/>
+      <c r="H55" s="7" t="inlineStr"/>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>금융 지원 서비스업</t>
+        </is>
+      </c>
+      <c r="J55" s="6" t="inlineStr">
+        <is>
+          <t>한화</t>
+        </is>
+      </c>
+      <c r="K55" s="6" t="inlineStr">
+        <is>
+          <t>상장전</t>
         </is>
       </c>
     </row>
@@ -5083,7 +5083,7 @@
       </c>
       <c r="K85" s="6" t="inlineStr">
         <is>
-          <t>상장전</t>
+          <t>상장승인(상장예정)</t>
         </is>
       </c>
     </row>
@@ -8179,7 +8179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R88"/>
+  <dimension ref="A1:R91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -11937,7 +11937,7 @@
     <row r="52" ht="22" customHeight="1">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>■ 공모 진행 (예심 승인법인)  (32건)</t>
+          <t>■ 공모 진행 (예심 승인법인)  (35건)</t>
         </is>
       </c>
       <c r="B52" s="4" t="n"/>
@@ -12345,7 +12345,7 @@
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
@@ -12355,30 +12355,38 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>10,700~12,300</t>
+          <t>19,500~23,500</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>2,500,000</t>
+          <t>852,000</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>26,750,000,000</t>
+          <t>16,614,000,000</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>26.18배 (PER)</t>
-        </is>
-      </c>
-      <c r="G58" s="6" t="inlineStr"/>
-      <c r="H58" s="6" t="inlineStr"/>
-      <c r="I58" s="6" t="inlineStr"/>
+          <t>17.61배 (PER)</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>19,500</t>
+        </is>
+      </c>
+      <c r="H58" s="6" t="n">
+        <v>1097.62</v>
+      </c>
+      <c r="I58" s="6" t="n">
+        <v>2006</v>
+      </c>
       <c r="J58" s="6" t="inlineStr">
         <is>
-          <t>10-01~10-02</t>
+          <t>10-02~10-06</t>
         </is>
       </c>
       <c r="K58" s="6" t="inlineStr"/>
@@ -12386,30 +12394,30 @@
       <c r="M58" s="6" t="inlineStr"/>
       <c r="N58" s="6" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>하나증권</t>
         </is>
       </c>
       <c r="O58" s="6" t="inlineStr"/>
       <c r="P58" s="7" t="inlineStr">
         <is>
-          <t>826,575,000</t>
+          <t>697,788,000</t>
         </is>
       </c>
       <c r="Q58" s="6" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>정정</t>
+          <t>발행조건확정</t>
         </is>
       </c>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
@@ -12419,22 +12427,22 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>19,500~23,500</t>
+          <t>10,700~12,300</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>852,000</t>
+          <t>2,500,000</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>16,614,000,000</t>
+          <t>26,750,000,000</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>17.61배 (PER)</t>
+          <t>26.18배 (PER)</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr"/>
@@ -12442,7 +12450,7 @@
       <c r="I59" s="6" t="inlineStr"/>
       <c r="J59" s="6" t="inlineStr">
         <is>
-          <t>10-02~10-06</t>
+          <t>10-01~10-02</t>
         </is>
       </c>
       <c r="K59" s="6" t="inlineStr"/>
@@ -12450,18 +12458,18 @@
       <c r="M59" s="6" t="inlineStr"/>
       <c r="N59" s="6" t="inlineStr">
         <is>
-          <t>하나증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="O59" s="6" t="inlineStr"/>
       <c r="P59" s="7" t="inlineStr">
         <is>
-          <t>697,788,000</t>
+          <t>826,575,000</t>
         </is>
       </c>
       <c r="Q59" s="6" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="R59" s="6" t="inlineStr">
@@ -13373,32 +13381,32 @@
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>하나에어로다이내믹스</t>
+          <t>넥스아이</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>11-02~11-06</t>
+          <t>10-22~10-28</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>4,700~5,700</t>
+          <t>10,500~13,000</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>4,400,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>20,680,000,000</t>
+          <t>52,500,000,000</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>17.89배 (EV/EBITDA)</t>
+          <t>19.15배 (PER)</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr"/>
@@ -13406,7 +13414,7 @@
       <c r="I74" s="6" t="inlineStr"/>
       <c r="J74" s="6" t="inlineStr">
         <is>
-          <t>11-10~11-11</t>
+          <t>11-03~11-04</t>
         </is>
       </c>
       <c r="K74" s="6" t="inlineStr"/>
@@ -13414,18 +13422,18 @@
       <c r="M74" s="6" t="inlineStr"/>
       <c r="N74" s="6" t="inlineStr">
         <is>
-          <t>아이비케이투자증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="O74" s="6" t="inlineStr"/>
       <c r="P74" s="7" t="inlineStr">
         <is>
-          <t>850,000,000</t>
-        </is>
-      </c>
-      <c r="Q74" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>2,407,500,000</t>
+        </is>
+      </c>
+      <c r="Q74" s="6" t="inlineStr">
+        <is>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="R74" s="6" t="inlineStr">
@@ -13437,54 +13445,54 @@
     <row r="75" ht="30" customHeight="1">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>바로팜</t>
-        </is>
-      </c>
-      <c r="B75" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>하나에어로다이내믹스</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>11-02~11-06</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>16,400~20,200</t>
+          <t>4,700~5,700</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>1,780,000</t>
+          <t>4,400,000</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>29,192,000,000</t>
+          <t>20,680,000,000</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
         <is>
-          <t>24.95배 (PER)</t>
+          <t>17.89배 (EV/EBITDA)</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr"/>
       <c r="H75" s="6" t="inlineStr"/>
       <c r="I75" s="6" t="inlineStr"/>
-      <c r="J75" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="J75" s="6" t="inlineStr">
+        <is>
+          <t>11-10~11-11</t>
         </is>
       </c>
       <c r="K75" s="6" t="inlineStr"/>
       <c r="L75" s="6" t="inlineStr"/>
       <c r="M75" s="6" t="inlineStr"/>
-      <c r="N75" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="N75" s="6" t="inlineStr">
+        <is>
+          <t>아이비케이투자증권</t>
         </is>
       </c>
       <c r="O75" s="6" t="inlineStr"/>
-      <c r="P75" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P75" s="7" t="inlineStr">
+        <is>
+          <t>850,000,000</t>
         </is>
       </c>
       <c r="Q75" s="18" t="inlineStr">
@@ -13501,7 +13509,7 @@
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>디티에스</t>
+          <t>바로팜</t>
         </is>
       </c>
       <c r="B76" s="18" t="inlineStr">
@@ -13509,24 +13517,24 @@
           <t>수집예정</t>
         </is>
       </c>
-      <c r="C76" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="D76" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="E76" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="F76" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>16,400~20,200</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>1,780,000</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>29,192,000,000</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>24.95배 (PER)</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr"/>
@@ -13558,14 +13566,14 @@
       </c>
       <c r="R76" s="6" t="inlineStr">
         <is>
-          <t>신고서 대기</t>
+          <t>최초</t>
         </is>
       </c>
     </row>
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>에이엔에이치스트럭쳐</t>
+          <t>디티에스</t>
         </is>
       </c>
       <c r="B77" s="18" t="inlineStr">
@@ -13629,7 +13637,7 @@
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>이에스티</t>
+          <t>에이엔에이치스트럭쳐</t>
         </is>
       </c>
       <c r="B78" s="18" t="inlineStr">
@@ -13693,7 +13701,7 @@
     <row r="79" ht="30" customHeight="1">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>영광와이케이엠씨</t>
+          <t>이에스티</t>
         </is>
       </c>
       <c r="B79" s="18" t="inlineStr">
@@ -13757,7 +13765,7 @@
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>동원파츠</t>
+          <t>영광와이케이엠씨</t>
         </is>
       </c>
       <c r="B80" s="18" t="inlineStr">
@@ -13821,7 +13829,7 @@
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>케이엠에프</t>
+          <t>동원파츠</t>
         </is>
       </c>
       <c r="B81" s="18" t="inlineStr">
@@ -13885,7 +13893,7 @@
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>넥스아이</t>
+          <t>케이엠에프</t>
         </is>
       </c>
       <c r="B82" s="18" t="inlineStr">
@@ -14074,22 +14082,214 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="20" t="inlineStr">
+    <row r="85" ht="30" customHeight="1">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>셀트릭스</t>
+        </is>
+      </c>
+      <c r="B85" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="C85" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="D85" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="E85" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="F85" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="G85" s="6" t="inlineStr"/>
+      <c r="H85" s="6" t="inlineStr"/>
+      <c r="I85" s="6" t="inlineStr"/>
+      <c r="J85" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="K85" s="6" t="inlineStr"/>
+      <c r="L85" s="6" t="inlineStr"/>
+      <c r="M85" s="6" t="inlineStr"/>
+      <c r="N85" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="O85" s="6" t="inlineStr"/>
+      <c r="P85" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="Q85" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="R85" s="6" t="inlineStr">
+        <is>
+          <t>신고서 대기</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="30" customHeight="1">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>럭스코</t>
+        </is>
+      </c>
+      <c r="B86" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="C86" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="D86" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="E86" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="F86" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr"/>
+      <c r="H86" s="6" t="inlineStr"/>
+      <c r="I86" s="6" t="inlineStr"/>
+      <c r="J86" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="K86" s="6" t="inlineStr"/>
+      <c r="L86" s="6" t="inlineStr"/>
+      <c r="M86" s="6" t="inlineStr"/>
+      <c r="N86" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="O86" s="6" t="inlineStr"/>
+      <c r="P86" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="Q86" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="R86" s="6" t="inlineStr">
+        <is>
+          <t>신고서 대기</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="30" customHeight="1">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>솔리스</t>
+        </is>
+      </c>
+      <c r="B87" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="C87" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="D87" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="E87" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="F87" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr"/>
+      <c r="H87" s="6" t="inlineStr"/>
+      <c r="I87" s="6" t="inlineStr"/>
+      <c r="J87" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="K87" s="6" t="inlineStr"/>
+      <c r="L87" s="6" t="inlineStr"/>
+      <c r="M87" s="6" t="inlineStr"/>
+      <c r="N87" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="O87" s="6" t="inlineStr"/>
+      <c r="P87" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="Q87" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="R87" s="6" t="inlineStr">
+        <is>
+          <t>신고서 대기</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="20" t="inlineStr">
         <is>
           <t>※ 상장 완료 = KIND 신규상장 페이지 기준(스팩합병 포함) · 스팩 공모상장은 밴드·밸류에이션 등 해당없음(공모가 2,000원 고정).</t>
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="20" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="20" t="inlineStr">
         <is>
           <t>※ 기재정정 신고서 내 정정 전·후 병존 → 자동수집은 "정정 후" 값만 취함.</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="20" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="20" t="inlineStr">
         <is>
           <t>※ 청약경쟁률=일반투자자 청약수량÷최종배정수량 · "MM-DD~"는 종료일 자동수집 예정.</t>
         </is>
@@ -14369,7 +14569,7 @@
         <v>11</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>0</v>
@@ -14468,30 +14668,30 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>미래에셋증권㈜</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>156,428,800,000</t>
+          <t>194,940,000,000</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>미래에셋증권㈜</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>142,440,000,000</t>
+          <t>156,428,800,000</t>
         </is>
       </c>
     </row>

--- a/IPO_analysis.xlsx
+++ b/IPO_analysis.xlsx
@@ -618,7 +618,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>기준일 2026-09-28 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
+          <t>기준일 2026-09-29 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
         </is>
       </c>
     </row>
@@ -5026,7 +5026,7 @@
       </c>
       <c r="K84" s="6" t="inlineStr">
         <is>
-          <t>상장승인(상장예정)</t>
+          <t>상장완료 (2026-09-29)</t>
         </is>
       </c>
     </row>
@@ -5368,7 +5368,7 @@
       </c>
       <c r="K90" s="6" t="inlineStr">
         <is>
-          <t>상장전</t>
+          <t>상장승인(상장예정)</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="K102" s="6" t="inlineStr">
         <is>
-          <t>상장승인(상장예정)</t>
+          <t>상장완료 (2026-09-29)</t>
         </is>
       </c>
     </row>
@@ -8395,7 +8395,7 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>■ 상장 완료 (2026)  (44건)</t>
+          <t>■ 상장 완료 (2026)  (46건)</t>
         </is>
       </c>
       <c r="B6" s="4" t="n"/>
@@ -8419,17 +8419,17 @@
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>와이즈플래닛컴퍼니</t>
+          <t>빅웨이브로보틱스</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>09-04~09-10</t>
+          <t>09-07~09-11</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>10,000~12,000</t>
+          <t>15,000~18,000</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
@@ -8439,24 +8439,24 @@
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>19,200,000,000</t>
+          <t>28,800,000,000</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>20.04배 (PER)</t>
+          <t>11.15 (PSR)</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>18,000</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>1248.47</v>
+        <v>1109.37</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>2323</v>
+        <v>2255</v>
       </c>
       <c r="J7" s="18" t="inlineStr">
         <is>
@@ -8465,24 +8465,28 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>3,568.86</t>
+          <t>2,706.30</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr"/>
       <c r="M7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="N7" s="6" t="inlineStr">
         <is>
-          <t>대신증권</t>
-        </is>
-      </c>
-      <c r="O7" s="6" t="inlineStr"/>
+          <t>유진투자증권</t>
+        </is>
+      </c>
+      <c r="O7" s="6" t="inlineStr">
+        <is>
+          <t>미래</t>
+        </is>
+      </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
-          <t>494,400,000</t>
+          <t>378,216,000</t>
         </is>
       </c>
       <c r="Q7" s="6" t="inlineStr">
@@ -8499,44 +8503,44 @@
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>한국제17호스팩</t>
+          <t>글로벌테크놀로지</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>09-07~09-08</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>09-07~09-11</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>13,000~15,000</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>7,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>14,000,000,000</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>40,000,000,000</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>19.22배 (PER)</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="H8" s="6" t="n">
-        <v>1270.51</v>
+        <v>123.19</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>2040</v>
+        <v>961</v>
       </c>
       <c r="J8" s="18" t="inlineStr">
         <is>
@@ -8545,29 +8549,29 @@
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>8,291.55</t>
+          <t>57.15</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr"/>
       <c r="M8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="N8" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="N8" s="6" t="inlineStr">
+        <is>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="O8" s="6" t="inlineStr"/>
-      <c r="P8" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="Q8" s="6" t="inlineStr">
-        <is>
-          <t>50%</t>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>2,119,999,960</t>
+        </is>
+      </c>
+      <c r="Q8" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="R8" s="6" t="inlineStr">
@@ -8579,75 +8583,75 @@
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>KB제34호스팩</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="C9" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>와이즈플래닛컴퍼니</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>09-04~09-10</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>10,000~12,000</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>7,000,000</t>
+          <t>1,600,000</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>14,000,000,000</t>
-        </is>
-      </c>
-      <c r="F9" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="G9" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>19,200,000,000</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>20.04배 (PER)</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>12,000</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>1232.51</v>
+        <v>1248.47</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>2001</v>
+        <v>2323</v>
       </c>
       <c r="J9" s="18" t="inlineStr">
         <is>
           <t>수집예정</t>
         </is>
       </c>
-      <c r="K9" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>3,568.86</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr"/>
       <c r="M9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="N9" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="N9" s="6" t="inlineStr">
+        <is>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="O9" s="6" t="inlineStr"/>
-      <c r="P9" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P9" s="7" t="inlineStr">
+        <is>
+          <t>494,400,000</t>
         </is>
       </c>
       <c r="Q9" s="6" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
@@ -8659,44 +8663,44 @@
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>네오사피엔스</t>
+          <t>한국제17호스팩</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>09-02~09-08</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>13,800~15,800</t>
+          <t>09-07~09-08</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>7,000,000</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>20,000,000,000</t>
-        </is>
-      </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>26.76배 (PER)</t>
+          <t>14,000,000,000</t>
+        </is>
+      </c>
+      <c r="F10" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="H10" s="6" t="n">
-        <v>219.56</v>
+        <v>1270.51</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>1045</v>
+        <v>2040</v>
       </c>
       <c r="J10" s="18" t="inlineStr">
         <is>
@@ -8705,29 +8709,29 @@
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>4,885.53</t>
+          <t>8,291.55</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr"/>
       <c r="M10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="N10" s="6" t="inlineStr">
-        <is>
-          <t>대신증권</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="N10" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="O10" s="6" t="inlineStr"/>
-      <c r="P10" s="7" t="inlineStr">
-        <is>
-          <t>1,080,264,000</t>
+      <c r="P10" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="Q10" s="6" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="R10" s="6" t="inlineStr">
@@ -8739,12 +8743,12 @@
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>엔에이치스팩34호</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>08-24~08-25</t>
+          <t>KB제34호스팩</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="C11" s="18" t="inlineStr">
@@ -8754,12 +8758,12 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>8,500,000</t>
+          <t>7,000,000</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>17,000,000,000</t>
+          <t>14,000,000,000</t>
         </is>
       </c>
       <c r="F11" s="18" t="inlineStr">
@@ -8767,31 +8771,31 @@
           <t>수집예정</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>2,000</t>
+      <c r="G11" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>1160.7</v>
+        <v>1232.51</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>2050</v>
+        <v>2001</v>
       </c>
       <c r="J11" s="18" t="inlineStr">
         <is>
           <t>수집예정</t>
         </is>
       </c>
-      <c r="K11" s="6" t="inlineStr">
-        <is>
-          <t>16,216.08</t>
+      <c r="K11" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr"/>
       <c r="M11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="N11" s="18" t="inlineStr">
@@ -8819,17 +8823,17 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>네오사피엔스</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>08-14~08-21</t>
+          <t>09-02~09-08</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>13,000~16,000</t>
+          <t>13,800~15,800</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -8844,7 +8848,7 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>29.52배 (PER)</t>
+          <t>26.76배 (PER)</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
@@ -8853,10 +8857,10 @@
         </is>
       </c>
       <c r="H12" s="6" t="n">
-        <v>63.41</v>
+        <v>219.56</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>246</v>
+        <v>1045</v>
       </c>
       <c r="J12" s="18" t="inlineStr">
         <is>
@@ -8865,29 +8869,29 @@
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>88.20</t>
+          <t>4,885.53</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr"/>
       <c r="M12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="O12" s="6" t="inlineStr"/>
       <c r="P12" s="7" t="inlineStr">
         <is>
-          <t>1,071,200,000</t>
-        </is>
-      </c>
-      <c r="Q12" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>1,080,264,000</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="R12" s="6" t="inlineStr">
@@ -8899,75 +8903,75 @@
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>해치텍</t>
+          <t>엔에이치스팩34호</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>08-03~08-07</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>23,000~28,000</t>
+          <t>08-24~08-25</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>1,000,000</t>
+          <t>8,500,000</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>23,000,000,000</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>36.99배 (PER)</t>
+          <t>17,000,000,000</t>
+        </is>
+      </c>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>101.91</v>
+        <v>1160.7</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>321</v>
+        <v>2050</v>
       </c>
       <c r="J13" s="18" t="inlineStr">
         <is>
           <t>수집예정</t>
         </is>
       </c>
-      <c r="K13" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>16,216.08</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr"/>
       <c r="M13" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="N13" s="6" t="inlineStr">
-        <is>
-          <t>DB증권</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="N13" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="O13" s="6" t="inlineStr"/>
-      <c r="P13" s="7" t="inlineStr">
-        <is>
-          <t>1,302,950,000</t>
+      <c r="P13" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="Q13" s="6" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
@@ -8979,75 +8983,75 @@
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>니어스랩</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>08-03~08-07</t>
+          <t>08-14~08-21</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>30,000~41,200</t>
+          <t>13,000~16,000</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>910,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>37,492,000,000</t>
+          <t>20,000,000,000</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>44.41배 (PER)</t>
+          <t>29.52배 (PER)</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>41,200</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="H14" s="6" t="n">
-        <v>743.49</v>
+        <v>63.41</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>1795</v>
+        <v>246</v>
       </c>
       <c r="J14" s="18" t="inlineStr">
         <is>
           <t>수집예정</t>
         </is>
       </c>
-      <c r="K14" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="K14" s="6" t="inlineStr">
+        <is>
+          <t>88.20</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr"/>
       <c r="M14" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="N14" s="6" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="O14" s="6" t="inlineStr"/>
       <c r="P14" s="7" t="inlineStr">
         <is>
-          <t>1,265,355,000</t>
-        </is>
-      </c>
-      <c r="Q14" s="6" t="inlineStr">
-        <is>
-          <t>4.50%</t>
+          <t>1,071,200,000</t>
+        </is>
+      </c>
+      <c r="Q14" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="R14" s="6" t="inlineStr">
@@ -9059,44 +9063,44 @@
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>기도산업</t>
+          <t>해치텍</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>07-31~08-06</t>
+          <t>08-03~08-07</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>24,800~28,400</t>
+          <t>23,000~28,000</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>1,700,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>48,280,000,000</t>
+          <t>23,000,000,000</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
         <is>
-          <t>10.01배 (PER)</t>
+          <t>36.99배 (PER)</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>28,400</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>213.31</v>
+        <v>101.91</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>637</v>
+        <v>321</v>
       </c>
       <c r="J15" s="18" t="inlineStr">
         <is>
@@ -9111,23 +9115,23 @@
       <c r="L15" s="6" t="inlineStr"/>
       <c r="M15" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="N15" s="6" t="inlineStr">
         <is>
-          <t>미래에셋증권</t>
+          <t>DB증권</t>
         </is>
       </c>
       <c r="O15" s="6" t="inlineStr"/>
       <c r="P15" s="7" t="inlineStr">
         <is>
-          <t>716,720,000</t>
+          <t>1,302,950,000</t>
         </is>
       </c>
       <c r="Q15" s="6" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
@@ -9139,44 +9143,44 @@
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스</t>
+          <t>니어스랩</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>07-20~07-24</t>
+          <t>08-03~08-07</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>12,000~14,500</t>
+          <t>30,000~41,200</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>910,000</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>60,000,000,000</t>
+          <t>37,492,000,000</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>22.89배 (PER)</t>
+          <t>44.41배 (PER)</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>41,200</t>
         </is>
       </c>
       <c r="H16" s="6" t="n">
-        <v>50.4</v>
+        <v>743.49</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>307</v>
+        <v>1795</v>
       </c>
       <c r="J16" s="18" t="inlineStr">
         <is>
@@ -9191,7 +9195,7 @@
       <c r="L16" s="6" t="inlineStr"/>
       <c r="M16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="N16" s="6" t="inlineStr">
@@ -9202,12 +9206,12 @@
       <c r="O16" s="6" t="inlineStr"/>
       <c r="P16" s="7" t="inlineStr">
         <is>
-          <t>4,095,000,000</t>
+          <t>1,265,355,000</t>
         </is>
       </c>
       <c r="Q16" s="6" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>4.50%</t>
         </is>
       </c>
       <c r="R16" s="6" t="inlineStr">
@@ -9219,44 +9223,44 @@
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>케이앤에스아이앤씨</t>
+          <t>기도산업</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>07-27~07-31</t>
+          <t>07-31~08-06</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>9,000~11,000</t>
+          <t>24,800~28,400</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>2,400,000</t>
+          <t>1,700,000</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>26,400,000,000</t>
+          <t>48,280,000,000</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>42.08배 (PER)</t>
+          <t>10.01배 (PER)</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>11,000</t>
+          <t>28,400</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>938.24</v>
+        <v>213.31</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>2024</v>
+        <v>637</v>
       </c>
       <c r="J17" s="18" t="inlineStr">
         <is>
@@ -9271,23 +9275,23 @@
       <c r="L17" s="6" t="inlineStr"/>
       <c r="M17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="N17" s="6" t="inlineStr">
         <is>
-          <t>아이비케이투자증권</t>
+          <t>미래에셋증권</t>
         </is>
       </c>
       <c r="O17" s="6" t="inlineStr"/>
       <c r="P17" s="7" t="inlineStr">
         <is>
-          <t>1,500,000,000</t>
+          <t>716,720,000</t>
         </is>
       </c>
       <c r="Q17" s="6" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="R17" s="6" t="inlineStr">
@@ -9299,44 +9303,44 @@
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>딜리셔스</t>
+          <t>인제니아테라퓨틱스</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>07-23~07-29</t>
+          <t>07-20~07-24</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>5,000~7,000</t>
+          <t>12,000~14,500</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>2,200,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>15,400,000,000</t>
+          <t>60,000,000,000</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>23.93배 (PER)</t>
+          <t>22.89배 (PER)</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>7,000</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="H18" s="6" t="n">
-        <v>184.06</v>
+        <v>50.4</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>441</v>
+        <v>307</v>
       </c>
       <c r="J18" s="18" t="inlineStr">
         <is>
@@ -9351,23 +9355,23 @@
       <c r="L18" s="6" t="inlineStr"/>
       <c r="M18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="N18" s="6" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="O18" s="6" t="inlineStr"/>
       <c r="P18" s="7" t="inlineStr">
         <is>
-          <t>566,500,000</t>
+          <t>4,095,000,000</t>
         </is>
       </c>
       <c r="Q18" s="6" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="R18" s="6" t="inlineStr">
@@ -9379,44 +9383,44 @@
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>에이치엘지노믹스</t>
+          <t>케이앤에스아이앤씨</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>07-02~07-08</t>
+          <t>07-27~07-31</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>18,500~21,500</t>
+          <t>9,000~11,000</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>2,565,000</t>
+          <t>2,400,000</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>55,147,500,000</t>
+          <t>26,400,000,000</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>12.85배 (EV/EBITDA)</t>
+          <t>42.08배 (PER)</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>21,500</t>
+          <t>11,000</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>714.52</v>
+        <v>938.24</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>2148</v>
+        <v>2024</v>
       </c>
       <c r="J19" s="18" t="inlineStr">
         <is>
@@ -9431,27 +9435,23 @@
       <c r="L19" s="6" t="inlineStr"/>
       <c r="M19" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="N19" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
-        </is>
-      </c>
-      <c r="O19" s="6" t="inlineStr">
-        <is>
-          <t>아이비케이투자증권, IBK투자증권, IBK투자증권, IBK투자증권, IBK투자증권, IBK투자증권㈜, 보통주, IBK투자증권㈜</t>
-        </is>
-      </c>
+          <t>아이비케이투자증권</t>
+        </is>
+      </c>
+      <c r="O19" s="6" t="inlineStr"/>
       <c r="P19" s="7" t="inlineStr">
         <is>
-          <t>1,211</t>
+          <t>1,500,000,000</t>
         </is>
       </c>
       <c r="Q19" s="6" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
@@ -9463,74 +9463,70 @@
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>레메디</t>
-        </is>
-      </c>
-      <c r="B20" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>딜리셔스</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>07-23~07-29</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>17,800~20,700</t>
+          <t>5,000~7,000</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>1,200,000</t>
+          <t>2,200,000</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>24,840,000,000</t>
+          <t>15,400,000,000</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>21.95배 (PER)</t>
+          <t>23.93배 (PER)</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>20,700</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="inlineStr">
-        <is>
-          <t>1,146.41</t>
-        </is>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>2,246</t>
-        </is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>184.06</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>441</v>
       </c>
       <c r="J20" s="18" t="inlineStr">
         <is>
           <t>수집예정</t>
         </is>
       </c>
-      <c r="K20" s="6" t="inlineStr">
-        <is>
-          <t>1,706.71</t>
+      <c r="K20" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="L20" s="6" t="inlineStr"/>
       <c r="M20" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="N20" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="O20" s="6" t="inlineStr"/>
       <c r="P20" s="7" t="inlineStr">
         <is>
-          <t>1,279</t>
+          <t>566,500,000</t>
         </is>
       </c>
       <c r="Q20" s="6" t="inlineStr">
@@ -9547,55 +9543,59 @@
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>레몬헬스케어</t>
-        </is>
-      </c>
-      <c r="B21" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>에이치엘지노믹스</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>07-02~07-08</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>7,500~10,000</t>
+          <t>18,500~21,500</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>2,565,000</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>55,147,500,000</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>25.48배 (PER)</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="n">
-        <v>10000</v>
+          <t>12.85배 (EV/EBITDA)</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>21,500</t>
+        </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>1238</v>
+        <v>714.52</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>2233</v>
-      </c>
-      <c r="J21" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-24~25</t>
-        </is>
-      </c>
-      <c r="K21" s="6" t="n">
-        <v>1510.57</v>
+        <v>2148</v>
+      </c>
+      <c r="J21" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="K21" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
       </c>
       <c r="L21" s="6" t="inlineStr"/>
       <c r="M21" s="6" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="N21" s="6" t="inlineStr">
@@ -9603,15 +9603,19 @@
           <t>KB</t>
         </is>
       </c>
-      <c r="O21" s="6" t="inlineStr"/>
+      <c r="O21" s="6" t="inlineStr">
+        <is>
+          <t>아이비케이투자증권, IBK투자증권, IBK투자증권, IBK투자증권, IBK투자증권, IBK투자증권㈜, 보통주, IBK투자증권㈜</t>
+        </is>
+      </c>
       <c r="P21" s="7" t="inlineStr">
         <is>
-          <t>824</t>
+          <t>1,211</t>
         </is>
       </c>
       <c r="Q21" s="6" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
@@ -9623,7 +9627,7 @@
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>매드업</t>
+          <t>레메디</t>
         </is>
       </c>
       <c r="B22" s="18" t="inlineStr">
@@ -9633,61 +9637,69 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>7,000~8,000</t>
+          <t>17,800~20,700</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>16,000</t>
+          <t>24,840,000,000</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>24.57배 (PER)</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="n">
-        <v>8000</v>
-      </c>
-      <c r="H22" s="6" t="n">
-        <v>1396.29</v>
-      </c>
-      <c r="I22" s="6" t="n">
-        <v>2392</v>
-      </c>
-      <c r="J22" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-23~24</t>
-        </is>
-      </c>
-      <c r="K22" s="6" t="n">
-        <v>3304.76</v>
+          <t>21.95배 (PER)</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>20,700</t>
+        </is>
+      </c>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t>1,146.41</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>2,246</t>
+        </is>
+      </c>
+      <c r="J22" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>1,706.71</t>
+        </is>
       </c>
       <c r="L22" s="6" t="inlineStr"/>
       <c r="M22" s="6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="N22" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="O22" s="6" t="inlineStr"/>
       <c r="P22" s="7" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>1,279</t>
         </is>
       </c>
       <c r="Q22" s="6" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="R22" s="6" t="inlineStr">
@@ -9699,75 +9711,71 @@
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>한국제16호스팩</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
+          <t>레몬헬스케어</t>
+        </is>
+      </c>
+      <c r="B23" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>7,500~10,000</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>5,500,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>11,000</t>
-        </is>
-      </c>
-      <c r="F23" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>25.48배 (PER)</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>10000</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>1364.09</v>
+        <v>1238</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>2089</v>
+        <v>2233</v>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>2026-06-22~06-23</t>
-        </is>
-      </c>
-      <c r="K23" s="6" t="inlineStr">
-        <is>
-          <t>1,274.77</t>
-        </is>
+          <t>2026-06-24~25</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="n">
+        <v>1510.57</v>
       </c>
       <c r="L23" s="6" t="inlineStr"/>
       <c r="M23" s="6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="N23" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="O23" s="6" t="inlineStr"/>
       <c r="P23" s="7" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>824</t>
         </is>
       </c>
       <c r="Q23" s="6" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="R23" s="6" t="inlineStr">
@@ -9779,7 +9787,7 @@
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>스트라드비젼</t>
+          <t>매드업</t>
         </is>
       </c>
       <c r="B24" s="18" t="inlineStr">
@@ -9789,63 +9797,61 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>12,000~14,000</t>
+          <t>7,000~8,000</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>7,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>84,000</t>
+          <t>16,000</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>37.45배 (PER)</t>
+          <t>24.57배 (PER)</t>
         </is>
       </c>
       <c r="G24" s="6" t="n">
-        <v>12000</v>
+        <v>8000</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>381.3</v>
+        <v>1396.29</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>1604</v>
+        <v>2392</v>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>2026-06-18~06-19</t>
-        </is>
-      </c>
-      <c r="K24" s="6" t="inlineStr">
-        <is>
-          <t>45.81</t>
-        </is>
+          <t>2026-06-23~24</t>
+        </is>
+      </c>
+      <c r="K24" s="6" t="n">
+        <v>3304.76</v>
       </c>
       <c r="L24" s="6" t="inlineStr"/>
       <c r="M24" s="6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="N24" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="O24" s="6" t="inlineStr"/>
       <c r="P24" s="7" t="inlineStr">
         <is>
-          <t>2,575</t>
+          <t>742</t>
         </is>
       </c>
       <c r="Q24" s="6" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="R24" s="6" t="inlineStr">
@@ -9857,73 +9863,75 @@
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>져스텍</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>한국제16호스팩</t>
+        </is>
+      </c>
+      <c r="B25" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>10,500~12,500</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>1,600,000</t>
+          <t>5,500,000</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>20,000</t>
-        </is>
-      </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>26.82배 (PER)</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="n">
-        <v>12500</v>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="F25" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>1294.99</v>
+        <v>1364.09</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>2252</v>
+        <v>2089</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>2026-06-18~06-19</t>
+          <t>2026-06-22~06-23</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>2,783.89</t>
+          <t>1,274.77</t>
         </is>
       </c>
       <c r="L25" s="6" t="inlineStr"/>
       <c r="M25" s="6" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="N25" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="O25" s="6" t="inlineStr"/>
       <c r="P25" s="7" t="inlineStr">
         <is>
-          <t>1,164</t>
+          <t>330</t>
         </is>
       </c>
       <c r="Q25" s="6" t="inlineStr">
         <is>
-          <t>5.65%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
@@ -9935,17 +9943,17 @@
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>메리츠제2호스팩</t>
-        </is>
-      </c>
-      <c r="B26" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
+          <t>스트라드비젼</t>
+        </is>
+      </c>
+      <c r="B26" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>12,000~14,000</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
@@ -9955,55 +9963,53 @@
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>14,000</t>
-        </is>
-      </c>
-      <c r="F26" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
+          <t>84,000</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>37.45배 (PER)</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>12000</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>1087.58</v>
+        <v>381.3</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>1798</v>
+        <v>1604</v>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09~06-10</t>
+          <t>2026-06-18~06-19</t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr">
         <is>
-          <t>1,338.66</t>
+          <t>45.81</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr"/>
       <c r="M26" s="6" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="N26" s="6" t="inlineStr">
         <is>
-          <t>메리츠</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="O26" s="6" t="inlineStr"/>
       <c r="P26" s="7" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>2,575</t>
         </is>
       </c>
       <c r="Q26" s="6" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
@@ -10015,7 +10021,7 @@
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>피스피스스튜디오</t>
+          <t>져스텍</t>
         </is>
       </c>
       <c r="B27" s="18" t="inlineStr">
@@ -10025,67 +10031,63 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>19,000~21,500</t>
+          <t>10,500~12,500</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>2,272,637</t>
+          <t>1,600,000</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>48,862</t>
+          <t>20,000</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>21.48배 (PER)</t>
+          <t>26.82배 (PER)</t>
         </is>
       </c>
       <c r="G27" s="6" t="n">
-        <v>21500</v>
+        <v>12500</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>847.76</v>
+        <v>1294.99</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>2329</v>
+        <v>2252</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>2026-05-26~05-27</t>
+          <t>2026-06-18~06-19</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>1,191.15</t>
+          <t>2,783.89</t>
         </is>
       </c>
       <c r="L27" s="6" t="inlineStr"/>
       <c r="M27" s="6" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="N27" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
-        </is>
-      </c>
-      <c r="O27" s="6" t="inlineStr">
-        <is>
-          <t>NH</t>
-        </is>
-      </c>
+          <t>삼성</t>
+        </is>
+      </c>
+      <c r="O27" s="6" t="inlineStr"/>
       <c r="P27" s="7" t="inlineStr">
         <is>
-          <t>1,994</t>
+          <t>1,164</t>
         </is>
       </c>
       <c r="Q27" s="6" t="inlineStr">
         <is>
-          <t>4.00%</t>
+          <t>5.65%</t>
         </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
@@ -10097,7 +10099,7 @@
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>대신밸런스제20호스팩</t>
+          <t>메리츠제2호스팩</t>
         </is>
       </c>
       <c r="B28" s="19" t="inlineStr">
@@ -10112,12 +10114,12 @@
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>6,500,000</t>
+          <t>7,000,000</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>13,000</t>
+          <t>14,000</t>
         </is>
       </c>
       <c r="F28" s="19" t="inlineStr">
@@ -10131,41 +10133,41 @@
         </is>
       </c>
       <c r="H28" s="6" t="n">
-        <v>1327.13</v>
+        <v>1087.58</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>2194</v>
+        <v>1798</v>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>2026-05-22~05-25</t>
+          <t>2026-06-09~06-10</t>
         </is>
       </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
-          <t>1,486.88</t>
+          <t>1,338.66</t>
         </is>
       </c>
       <c r="L28" s="6" t="inlineStr"/>
       <c r="M28" s="6" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="N28" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>메리츠</t>
         </is>
       </c>
       <c r="O28" s="6" t="inlineStr"/>
       <c r="P28" s="7" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>245</t>
         </is>
       </c>
       <c r="Q28" s="6" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
@@ -10177,7 +10179,7 @@
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>마키나락스</t>
+          <t>피스피스스튜디오</t>
         </is>
       </c>
       <c r="B29" s="18" t="inlineStr">
@@ -10187,47 +10189,47 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>12,500~15,000</t>
+          <t>19,000~21,500</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>2,635,000</t>
+          <t>2,272,637</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>39,525</t>
+          <t>48,862</t>
         </is>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>40.5배 (PER)</t>
+          <t>21.48배 (PER)</t>
         </is>
       </c>
       <c r="G29" s="6" t="n">
-        <v>15000</v>
+        <v>21500</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>1196.08</v>
+        <v>847.76</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>2427</v>
+        <v>2329</v>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>2026-05-11~05-12</t>
+          <t>2026-05-26~05-27</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>2,807.79</t>
+          <t>1,191.15</t>
         </is>
       </c>
       <c r="L29" s="6" t="inlineStr"/>
       <c r="M29" s="6" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="N29" s="6" t="inlineStr">
@@ -10235,15 +10237,19 @@
           <t>미래</t>
         </is>
       </c>
-      <c r="O29" s="6" t="inlineStr"/>
+      <c r="O29" s="6" t="inlineStr">
+        <is>
+          <t>NH</t>
+        </is>
+      </c>
       <c r="P29" s="7" t="inlineStr">
         <is>
-          <t>2,026</t>
+          <t>1,994</t>
         </is>
       </c>
       <c r="Q29" s="6" t="inlineStr">
         <is>
-          <t>5.00%</t>
+          <t>4.00%</t>
         </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
@@ -10255,22 +10261,22 @@
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>폴레드</t>
-        </is>
-      </c>
-      <c r="B30" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>대신밸런스제20호스팩</t>
+        </is>
+      </c>
+      <c r="B30" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>4,100~5,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>2,600,000</t>
+          <t>6,500,000</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
@@ -10278,50 +10284,52 @@
           <t>13,000</t>
         </is>
       </c>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>19.05배 (PER)</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="n">
-        <v>5000</v>
+      <c r="F30" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
       </c>
       <c r="H30" s="6" t="n">
-        <v>1486.66</v>
+        <v>1327.13</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>2372</v>
+        <v>2194</v>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>2026-05-04~05-05</t>
+          <t>2026-05-22~05-25</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>3,169.86</t>
+          <t>1,486.88</t>
         </is>
       </c>
       <c r="L30" s="6" t="inlineStr"/>
       <c r="M30" s="6" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="N30" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="O30" s="6" t="inlineStr"/>
       <c r="P30" s="7" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>390</t>
         </is>
       </c>
       <c r="Q30" s="6" t="inlineStr">
         <is>
-          <t>4.03%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
@@ -10333,7 +10341,7 @@
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>코스모로보틱스</t>
+          <t>마키나락스</t>
         </is>
       </c>
       <c r="B31" s="18" t="inlineStr">
@@ -10343,67 +10351,63 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>5,300~6,000</t>
+          <t>12,500~15,000</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>4,170,000</t>
+          <t>2,635,000</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>25,020</t>
+          <t>39,525</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>47.45배 (PER)</t>
+          <t>40.5배 (PER)</t>
         </is>
       </c>
       <c r="G31" s="6" t="n">
-        <v>6000</v>
+        <v>15000</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>1140.11</v>
+        <v>1196.08</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>2257</v>
+        <v>2427</v>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>2026-04-27~04-28</t>
+          <t>2026-05-11~05-12</t>
         </is>
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>2,013.80</t>
+          <t>2,807.79</t>
         </is>
       </c>
       <c r="L31" s="6" t="inlineStr"/>
       <c r="M31" s="6" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="N31" s="6" t="inlineStr">
         <is>
-          <t>유진</t>
-        </is>
-      </c>
-      <c r="O31" s="6" t="inlineStr">
-        <is>
-          <t>NH</t>
-        </is>
-      </c>
+          <t>미래</t>
+        </is>
+      </c>
+      <c r="O31" s="6" t="inlineStr"/>
       <c r="P31" s="7" t="inlineStr">
         <is>
-          <t>1,289</t>
+          <t>2,026</t>
         </is>
       </c>
       <c r="Q31" s="6" t="inlineStr">
         <is>
-          <t>3.78%</t>
+          <t>5.00%</t>
         </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
@@ -10415,75 +10419,73 @@
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>신한스팩18호</t>
-        </is>
-      </c>
-      <c r="B32" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
+          <t>폴레드</t>
+        </is>
+      </c>
+      <c r="B32" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>4,100~5,000</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>2,600,000</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>10,000</t>
-        </is>
-      </c>
-      <c r="F32" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
+          <t>13,000</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>19.05배 (PER)</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>5000</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>1388.6</v>
+        <v>1486.66</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>2044</v>
+        <v>2372</v>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>2026-04-20~04-21</t>
+          <t>2026-05-04~05-05</t>
         </is>
       </c>
       <c r="K32" s="6" t="inlineStr">
         <is>
-          <t>1,601.36</t>
+          <t>3,169.86</t>
         </is>
       </c>
       <c r="L32" s="6" t="inlineStr"/>
       <c r="M32" s="6" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="N32" s="6" t="inlineStr">
         <is>
-          <t>신한</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="O32" s="6" t="inlineStr"/>
       <c r="P32" s="7" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>540</t>
         </is>
       </c>
       <c r="Q32" s="6" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>4.03%</t>
         </is>
       </c>
       <c r="R32" s="6" t="inlineStr">
@@ -10495,7 +10497,7 @@
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>채비</t>
+          <t>코스모로보틱스</t>
         </is>
       </c>
       <c r="B33" s="18" t="inlineStr">
@@ -10505,67 +10507,67 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>12,300~15,300</t>
+          <t>5,300~6,000</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>9,000,000</t>
+          <t>4,170,000</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>110,700</t>
+          <t>25,020</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>24.0배 (EV/EBITDA)</t>
+          <t>47.45배 (PER)</t>
         </is>
       </c>
       <c r="G33" s="6" t="n">
-        <v>12300</v>
+        <v>6000</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>55.23</v>
+        <v>1140.11</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>751</v>
+        <v>2257</v>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>2026-04-20~04-21</t>
+          <t>2026-04-27~04-28</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>302.11</t>
+          <t>2,013.80</t>
         </is>
       </c>
       <c r="L33" s="6" t="inlineStr"/>
       <c r="M33" s="6" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="N33" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>유진</t>
         </is>
       </c>
       <c r="O33" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="P33" s="7" t="inlineStr">
         <is>
-          <t>3,384</t>
+          <t>1,289</t>
         </is>
       </c>
       <c r="Q33" s="6" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>3.78%</t>
         </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
@@ -10577,7 +10579,7 @@
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>키움히어로스펙2호</t>
+          <t>신한스팩18호</t>
         </is>
       </c>
       <c r="B34" s="19" t="inlineStr">
@@ -10592,12 +10594,12 @@
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>6,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="F34" s="19" t="inlineStr">
@@ -10611,41 +10613,41 @@
         </is>
       </c>
       <c r="H34" s="6" t="n">
-        <v>1271.12</v>
+        <v>1388.6</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>2054</v>
+        <v>2044</v>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>2026-04-14~04-15</t>
+          <t>2026-04-20~04-21</t>
         </is>
       </c>
       <c r="K34" s="6" t="inlineStr">
         <is>
-          <t>1,727.59</t>
+          <t>1,601.36</t>
         </is>
       </c>
       <c r="L34" s="6" t="inlineStr"/>
       <c r="M34" s="6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="N34" s="6" t="inlineStr">
         <is>
-          <t>키움</t>
+          <t>신한</t>
         </is>
       </c>
       <c r="O34" s="6" t="inlineStr"/>
       <c r="P34" s="7" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>350</t>
         </is>
       </c>
       <c r="Q34" s="6" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
@@ -10657,75 +10659,77 @@
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>교보스팩20호</t>
-        </is>
-      </c>
-      <c r="B35" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
+          <t>채비</t>
+        </is>
+      </c>
+      <c r="B35" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>12,300~15,300</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>5,400,000</t>
+          <t>9,000,000</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>10,800</t>
-        </is>
-      </c>
-      <c r="F35" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="G35" s="6" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
+          <t>110,700</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>24.0배 (EV/EBITDA)</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>12300</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>1196.99</v>
+        <v>55.23</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>1855</v>
+        <v>751</v>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>2026-03-23~03-24</t>
+          <t>2026-04-20~04-21</t>
         </is>
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>747.00</t>
+          <t>302.11</t>
         </is>
       </c>
       <c r="L35" s="6" t="inlineStr"/>
       <c r="M35" s="6" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="N35" s="6" t="inlineStr">
         <is>
-          <t>교보</t>
-        </is>
-      </c>
-      <c r="O35" s="6" t="inlineStr"/>
+          <t>KB</t>
+        </is>
+      </c>
+      <c r="O35" s="6" t="inlineStr">
+        <is>
+          <t>삼성</t>
+        </is>
+      </c>
       <c r="P35" s="7" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>3,384</t>
         </is>
       </c>
       <c r="Q35" s="6" t="inlineStr">
         <is>
-          <t>2.78%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="R35" s="6" t="inlineStr">
@@ -10737,73 +10741,75 @@
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>인벤테라</t>
-        </is>
-      </c>
-      <c r="B36" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>키움히어로스펙2호</t>
+        </is>
+      </c>
+      <c r="B36" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>12,100~16,600</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>1,180,000</t>
+          <t>6,000,000</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>19,588</t>
-        </is>
-      </c>
-      <c r="F36" s="6" t="inlineStr">
-        <is>
-          <t>24.34배 (PER)</t>
-        </is>
-      </c>
-      <c r="G36" s="6" t="n">
-        <v>16600</v>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="F36" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
       </c>
       <c r="H36" s="6" t="n">
-        <v>1328.82</v>
+        <v>1271.12</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>2309</v>
+        <v>2054</v>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>2026-03-23~03-24</t>
+          <t>2026-04-14~04-15</t>
         </is>
       </c>
       <c r="K36" s="6" t="inlineStr">
         <is>
-          <t>1,913.00</t>
+          <t>1,727.59</t>
         </is>
       </c>
       <c r="L36" s="6" t="inlineStr"/>
       <c r="M36" s="6" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="N36" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>키움</t>
         </is>
       </c>
       <c r="O36" s="6" t="inlineStr"/>
       <c r="P36" s="7" t="inlineStr">
         <is>
-          <t>1,211</t>
+          <t>300</t>
         </is>
       </c>
       <c r="Q36" s="6" t="inlineStr">
         <is>
-          <t>6.00%</t>
+          <t>2.50%</t>
         </is>
       </c>
       <c r="R36" s="6" t="inlineStr">
@@ -10815,7 +10821,7 @@
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>신한스팩17호</t>
+          <t>교보스팩20호</t>
         </is>
       </c>
       <c r="B37" s="19" t="inlineStr">
@@ -10830,12 +10836,12 @@
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>5,400,000</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>10,800</t>
         </is>
       </c>
       <c r="F37" s="19" t="inlineStr">
@@ -10849,41 +10855,41 @@
         </is>
       </c>
       <c r="H37" s="6" t="n">
-        <v>1343.8</v>
+        <v>1196.99</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>2022</v>
+        <v>1855</v>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>2026-03-19~03-20</t>
+          <t>2026-03-23~03-24</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>1,403.74</t>
+          <t>747.00</t>
         </is>
       </c>
       <c r="L37" s="6" t="inlineStr"/>
       <c r="M37" s="6" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="N37" s="6" t="inlineStr">
         <is>
-          <t>신한</t>
+          <t>교보</t>
         </is>
       </c>
       <c r="O37" s="6" t="inlineStr"/>
       <c r="P37" s="7" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>300</t>
         </is>
       </c>
       <c r="Q37" s="6" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>2.78%</t>
         </is>
       </c>
       <c r="R37" s="6" t="inlineStr">
@@ -10895,7 +10901,7 @@
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>리센스메디컬</t>
+          <t>인벤테라</t>
         </is>
       </c>
       <c r="B38" s="18" t="inlineStr">
@@ -10905,67 +10911,63 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>9,000~11,000</t>
+          <t>12,100~16,600</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>1,400,000</t>
+          <t>1,180,000</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>15,400</t>
+          <t>19,588</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>31.33배 (PER)</t>
+          <t>24.34배 (PER)</t>
         </is>
       </c>
       <c r="G38" s="6" t="n">
-        <v>11000</v>
+        <v>16600</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>1352.63</v>
+        <v>1328.82</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>2261</v>
+        <v>2309</v>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>2026-03-19~03-20</t>
+          <t>2026-03-23~03-24</t>
         </is>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
-          <t>2,097.68</t>
+          <t>1,913.00</t>
         </is>
       </c>
       <c r="L38" s="6" t="inlineStr"/>
       <c r="M38" s="6" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="N38" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
-        </is>
-      </c>
-      <c r="O38" s="6" t="inlineStr">
-        <is>
-          <t>KB</t>
-        </is>
-      </c>
+          <t>NH</t>
+        </is>
+      </c>
+      <c r="O38" s="6" t="inlineStr"/>
       <c r="P38" s="7" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>1,211</t>
         </is>
       </c>
       <c r="Q38" s="6" t="inlineStr">
         <is>
-          <t>5.77%</t>
+          <t>6.00%</t>
         </is>
       </c>
       <c r="R38" s="6" t="inlineStr">
@@ -10977,7 +10979,7 @@
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>NH스팩33호</t>
+          <t>신한스팩17호</t>
         </is>
       </c>
       <c r="B39" s="19" t="inlineStr">
@@ -10992,12 +10994,12 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>6,350,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>12,700</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="F39" s="19" t="inlineStr">
@@ -11011,41 +11013,41 @@
         </is>
       </c>
       <c r="H39" s="6" t="n">
-        <v>1228.71</v>
+        <v>1343.8</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>2058</v>
+        <v>2022</v>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>2026-03-17~03-18</t>
+          <t>2026-03-19~03-20</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>569.27</t>
+          <t>1,403.74</t>
         </is>
       </c>
       <c r="L39" s="6" t="inlineStr"/>
       <c r="M39" s="6" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="N39" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>신한</t>
         </is>
       </c>
       <c r="O39" s="6" t="inlineStr"/>
       <c r="P39" s="7" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>350</t>
         </is>
       </c>
       <c r="Q39" s="6" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="R39" s="6" t="inlineStr">
@@ -11057,7 +11059,7 @@
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>메쥬</t>
+          <t>리센스메디컬</t>
         </is>
       </c>
       <c r="B40" s="18" t="inlineStr">
@@ -11067,63 +11069,67 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>16,700~21,600</t>
+          <t>9,000~11,000</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>1,345,000</t>
+          <t>1,400,000</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>29,052</t>
+          <t>15,400</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>20.66배 (PER)</t>
+          <t>31.33배 (PER)</t>
         </is>
       </c>
       <c r="G40" s="6" t="n">
-        <v>21600</v>
+        <v>11000</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>1108.93</v>
+        <v>1352.63</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>2320</v>
+        <v>2261</v>
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>2026-03-16~03-17</t>
+          <t>2026-03-19~03-20</t>
         </is>
       </c>
       <c r="K40" s="6" t="inlineStr">
         <is>
-          <t>2,428.25</t>
+          <t>2,097.68</t>
         </is>
       </c>
       <c r="L40" s="6" t="inlineStr"/>
       <c r="M40" s="6" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="N40" s="6" t="inlineStr">
         <is>
-          <t>신한</t>
-        </is>
-      </c>
-      <c r="O40" s="6" t="inlineStr"/>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="O40" s="6" t="inlineStr">
+        <is>
+          <t>KB</t>
+        </is>
+      </c>
       <c r="P40" s="7" t="inlineStr">
         <is>
-          <t>1,496</t>
+          <t>916</t>
         </is>
       </c>
       <c r="Q40" s="6" t="inlineStr">
         <is>
-          <t>5.00%</t>
+          <t>5.77%</t>
         </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
@@ -11135,73 +11141,75 @@
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>한패스</t>
-        </is>
-      </c>
-      <c r="B41" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>NH스팩33호</t>
+        </is>
+      </c>
+      <c r="B41" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>17,000~19,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>1,100,000</t>
+          <t>6,350,000</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>20,900</t>
-        </is>
-      </c>
-      <c r="F41" s="6" t="inlineStr">
-        <is>
-          <t>29.09배 (PER)</t>
-        </is>
-      </c>
-      <c r="G41" s="6" t="n">
-        <v>19000</v>
+          <t>12,700</t>
+        </is>
+      </c>
+      <c r="F41" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
       </c>
       <c r="H41" s="6" t="n">
-        <v>1172.59</v>
+        <v>1228.71</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>2229</v>
+        <v>2058</v>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>2026-03-16~03-17</t>
+          <t>2026-03-17~03-18</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>1,673.04</t>
+          <t>569.27</t>
         </is>
       </c>
       <c r="L41" s="6" t="inlineStr"/>
       <c r="M41" s="6" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="N41" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="O41" s="6" t="inlineStr"/>
       <c r="P41" s="7" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>381</t>
         </is>
       </c>
       <c r="Q41" s="6" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
@@ -11213,7 +11221,7 @@
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>아이엠바이오로직스</t>
+          <t>메쥬</t>
         </is>
       </c>
       <c r="B42" s="18" t="inlineStr">
@@ -11223,58 +11231,58 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>19,000~26,000</t>
+          <t>16,700~21,600</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>1,345,000</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>52,000</t>
+          <t>29,052</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>21.46배 (PER)</t>
+          <t>20.66배 (PER)</t>
         </is>
       </c>
       <c r="G42" s="6" t="n">
-        <v>26000</v>
+        <v>21600</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>839.23</v>
+        <v>1108.93</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>2333</v>
+        <v>2320</v>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11~03-12</t>
+          <t>2026-03-16~03-17</t>
         </is>
       </c>
       <c r="K42" s="6" t="inlineStr">
         <is>
-          <t>1,806.00</t>
+          <t>2,428.25</t>
         </is>
       </c>
       <c r="L42" s="6" t="inlineStr"/>
       <c r="M42" s="6" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="N42" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>신한</t>
         </is>
       </c>
       <c r="O42" s="6" t="inlineStr"/>
       <c r="P42" s="7" t="inlineStr">
         <is>
-          <t>2,650</t>
+          <t>1,496</t>
         </is>
       </c>
       <c r="Q42" s="6" t="inlineStr">
@@ -11291,7 +11299,7 @@
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>카나프테라퓨틱스</t>
+          <t>한패스</t>
         </is>
       </c>
       <c r="B43" s="18" t="inlineStr">
@@ -11301,47 +11309,47 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>16,000~20,000</t>
+          <t>17,000~19,000</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>1,100,000</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>40,000</t>
+          <t>20,900</t>
         </is>
       </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>23.59배 (PER)</t>
+          <t>29.09배 (PER)</t>
         </is>
       </c>
       <c r="G43" s="6" t="n">
-        <v>20000</v>
+        <v>19000</v>
       </c>
       <c r="H43" s="6" t="n">
-        <v>962.1</v>
+        <v>1172.59</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>2327</v>
+        <v>2229</v>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>2026-03-05~03-06</t>
+          <t>2026-03-16~03-17</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>1,899.29</t>
+          <t>1,673.04</t>
         </is>
       </c>
       <c r="L43" s="6" t="inlineStr"/>
       <c r="M43" s="6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="N43" s="6" t="inlineStr">
@@ -11352,12 +11360,12 @@
       <c r="O43" s="6" t="inlineStr"/>
       <c r="P43" s="7" t="inlineStr">
         <is>
-          <t>2,050</t>
+          <t>753</t>
         </is>
       </c>
       <c r="Q43" s="6" t="inlineStr">
         <is>
-          <t>5.00%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
@@ -11369,7 +11377,7 @@
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>액스비스</t>
+          <t>아이엠바이오로직스</t>
         </is>
       </c>
       <c r="B44" s="18" t="inlineStr">
@@ -11379,63 +11387,63 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>10,100~11,500</t>
+          <t>19,000~26,000</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>2,300,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>26,450</t>
+          <t>52,000</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>27.60배 (PER)</t>
+          <t>21.46배 (PER)</t>
         </is>
       </c>
       <c r="G44" s="6" t="n">
-        <v>11500</v>
+        <v>26000</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>1124.21</v>
+        <v>839.23</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>2411</v>
+        <v>2333</v>
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>2026-02-23~02-24</t>
+          <t>2026-03-11~03-12</t>
         </is>
       </c>
       <c r="K44" s="6" t="inlineStr">
         <is>
-          <t>1,960.87</t>
+          <t>1,806.00</t>
         </is>
       </c>
       <c r="L44" s="6" t="inlineStr"/>
       <c r="M44" s="6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="N44" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="O44" s="6" t="inlineStr"/>
       <c r="P44" s="7" t="inlineStr">
         <is>
-          <t>1,090</t>
+          <t>2,650</t>
         </is>
       </c>
       <c r="Q44" s="6" t="inlineStr">
         <is>
-          <t>4.00%</t>
+          <t>5.00%</t>
         </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
@@ -11447,7 +11455,7 @@
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>에스팀</t>
+          <t>카나프테라퓨틱스</t>
         </is>
       </c>
       <c r="B45" s="18" t="inlineStr">
@@ -11457,47 +11465,47 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>7,000~8,500</t>
+          <t>16,000~20,000</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>1,800,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>15,300</t>
+          <t>40,000</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>17.71배 (EV/EBITDA)</t>
+          <t>23.59배 (PER)</t>
         </is>
       </c>
       <c r="G45" s="6" t="n">
-        <v>8500</v>
+        <v>20000</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>1334.91</v>
+        <v>962.1</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>2263</v>
+        <v>2327</v>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>2026-02-23~02-24</t>
+          <t>2026-03-05~03-06</t>
         </is>
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>1,334.91</t>
+          <t>1,899.29</t>
         </is>
       </c>
       <c r="L45" s="6" t="inlineStr"/>
       <c r="M45" s="6" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="N45" s="6" t="inlineStr">
@@ -11508,7 +11516,7 @@
       <c r="O45" s="6" t="inlineStr"/>
       <c r="P45" s="7" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>2,050</t>
         </is>
       </c>
       <c r="Q45" s="6" t="inlineStr">
@@ -11525,7 +11533,7 @@
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>케이뱅크 (유가)</t>
+          <t>액스비스</t>
         </is>
       </c>
       <c r="B46" s="18" t="inlineStr">
@@ -11535,67 +11543,63 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>8,300~9,500</t>
+          <t>10,100~11,500</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>60,000,000</t>
+          <t>2,300,000</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>498,000</t>
+          <t>26,450</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>1.80배 (PBR)</t>
+          <t>27.60배 (PER)</t>
         </is>
       </c>
       <c r="G46" s="6" t="n">
-        <v>8300</v>
+        <v>11500</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>198.53</v>
+        <v>1124.21</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>2007</v>
+        <v>2411</v>
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
-          <t>2026-02-20~23</t>
+          <t>2026-02-23~02-24</t>
         </is>
       </c>
       <c r="K46" s="6" t="inlineStr">
         <is>
-          <t>134.59</t>
+          <t>1,960.87</t>
         </is>
       </c>
       <c r="L46" s="6" t="inlineStr"/>
       <c r="M46" s="6" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="N46" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
-        </is>
-      </c>
-      <c r="O46" s="6" t="inlineStr">
-        <is>
-          <t>삼성</t>
-        </is>
-      </c>
+          <t>미래</t>
+        </is>
+      </c>
+      <c r="O46" s="6" t="inlineStr"/>
       <c r="P46" s="7" t="inlineStr">
         <is>
-          <t>5,976</t>
+          <t>1,090</t>
         </is>
       </c>
       <c r="Q46" s="6" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>4.00%</t>
         </is>
       </c>
       <c r="R46" s="6" t="inlineStr">
@@ -11607,91 +11611,85 @@
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>세미티에스</t>
-        </is>
-      </c>
-      <c r="B47" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="C47" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="D47" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="E47" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="F47" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="G47" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="H47" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="I47" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="J47" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="K47" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
+          <t>에스팀</t>
+        </is>
+      </c>
+      <c r="B47" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>7,000~8,500</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>1,800,000</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>15,300</t>
+        </is>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>17.71배 (EV/EBITDA)</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="n">
+        <v>8500</v>
+      </c>
+      <c r="H47" s="6" t="n">
+        <v>1334.91</v>
+      </c>
+      <c r="I47" s="6" t="n">
+        <v>2263</v>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-23~02-24</t>
+        </is>
+      </c>
+      <c r="K47" s="6" t="inlineStr">
+        <is>
+          <t>1,334.91</t>
         </is>
       </c>
       <c r="L47" s="6" t="inlineStr"/>
       <c r="M47" s="6" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="N47" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="O47" s="6" t="inlineStr"/>
-      <c r="P47" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="Q47" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
+      <c r="P47" s="7" t="inlineStr">
+        <is>
+          <t>788</t>
+        </is>
+      </c>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>5.00%</t>
         </is>
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
-          <t>상장완료(스팩합병)</t>
+          <t>상장완료</t>
         </is>
       </c>
     </row>
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>덕양에너젠</t>
+          <t>케이뱅크 (유가)</t>
         </is>
       </c>
       <c r="B48" s="18" t="inlineStr">
@@ -11701,47 +11699,47 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>8,500~10,000</t>
+          <t>8,300~9,500</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>7,500,000</t>
+          <t>60,000,000</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>75,000</t>
+          <t>498,000</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>30.32배 (EV/EBITDA)</t>
+          <t>1.80배 (PBR)</t>
         </is>
       </c>
       <c r="G48" s="6" t="n">
-        <v>10000</v>
+        <v>8300</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>650.14</v>
+        <v>198.53</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>2324</v>
+        <v>2007</v>
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>2026-01-20~01-21</t>
+          <t>2026-02-20~23</t>
         </is>
       </c>
       <c r="K48" s="6" t="inlineStr">
         <is>
-          <t>1,354.00</t>
+          <t>134.59</t>
         </is>
       </c>
       <c r="L48" s="6" t="inlineStr"/>
       <c r="M48" s="6" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="N48" s="6" t="inlineStr">
@@ -11751,17 +11749,17 @@
       </c>
       <c r="O48" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="P48" s="7" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>5,976</t>
         </is>
       </c>
       <c r="Q48" s="6" t="inlineStr">
         <is>
-          <t>2.92%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
@@ -11773,7 +11771,7 @@
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>케이피항공산업</t>
+          <t>세미티에스</t>
         </is>
       </c>
       <c r="B49" s="19" t="inlineStr">
@@ -11829,7 +11827,7 @@
       <c r="L49" s="6" t="inlineStr"/>
       <c r="M49" s="6" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="N49" s="6" t="inlineStr">
@@ -11857,331 +11855,341 @@
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>삼성스팩13호</t>
-        </is>
-      </c>
-      <c r="B50" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
+          <t>덕양에너젠</t>
+        </is>
+      </c>
+      <c r="B50" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>8,500~10,000</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>6,000,000</t>
+          <t>7,500,000</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>12,000</t>
-        </is>
-      </c>
-      <c r="F50" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="G50" s="6" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
+          <t>75,000</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>30.32배 (EV/EBITDA)</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="n">
+        <v>10000</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>1159.11</v>
+        <v>650.14</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>1892</v>
+        <v>2324</v>
       </c>
       <c r="J50" s="6" t="inlineStr">
         <is>
-          <t>2026-01-12~01-13</t>
+          <t>2026-01-20~01-21</t>
         </is>
       </c>
       <c r="K50" s="6" t="inlineStr">
         <is>
-          <t>1,870.40</t>
+          <t>1,354.00</t>
         </is>
       </c>
       <c r="L50" s="6" t="inlineStr"/>
       <c r="M50" s="6" t="inlineStr">
         <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="N50" s="6" t="inlineStr">
+        <is>
+          <t>NH</t>
+        </is>
+      </c>
+      <c r="O50" s="6" t="inlineStr">
+        <is>
+          <t>미래</t>
+        </is>
+      </c>
+      <c r="P50" s="7" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>2.92%</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>상장완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="30" customHeight="1">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>케이피항공산업</t>
+        </is>
+      </c>
+      <c r="B51" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="C51" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="D51" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="E51" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="F51" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="G51" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="H51" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="I51" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="J51" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="K51" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="L51" s="6" t="inlineStr"/>
+      <c r="M51" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="N51" s="6" t="inlineStr">
+        <is>
+          <t>NH</t>
+        </is>
+      </c>
+      <c r="O51" s="6" t="inlineStr"/>
+      <c r="P51" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="Q51" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>상장완료(스팩합병)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>삼성스팩13호</t>
+        </is>
+      </c>
+      <c r="B52" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>6,000,000</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="F52" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="H52" s="6" t="n">
+        <v>1159.11</v>
+      </c>
+      <c r="I52" s="6" t="n">
+        <v>1892</v>
+      </c>
+      <c r="J52" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-12~01-13</t>
+        </is>
+      </c>
+      <c r="K52" s="6" t="inlineStr">
+        <is>
+          <t>1,870.40</t>
+        </is>
+      </c>
+      <c r="L52" s="6" t="inlineStr"/>
+      <c r="M52" s="6" t="inlineStr">
+        <is>
           <t>2026-01-21</t>
         </is>
       </c>
-      <c r="N50" s="6" t="inlineStr">
+      <c r="N52" s="6" t="inlineStr">
         <is>
           <t>삼성</t>
         </is>
       </c>
-      <c r="O50" s="6" t="inlineStr"/>
-      <c r="P50" s="7" t="inlineStr">
+      <c r="O52" s="6" t="inlineStr"/>
+      <c r="P52" s="7" t="inlineStr">
         <is>
           <t>360</t>
         </is>
       </c>
-      <c r="Q50" s="6" t="inlineStr">
+      <c r="Q52" s="6" t="inlineStr">
         <is>
           <t>3.00%</t>
         </is>
       </c>
-      <c r="R50" s="6" t="inlineStr">
+      <c r="R52" s="6" t="inlineStr">
         <is>
           <t>상장완료</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="22" customHeight="1">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>■ 공모 진행 (예심 승인법인)  (35건)</t>
-        </is>
-      </c>
-      <c r="B52" s="4" t="n"/>
-      <c r="C52" s="4" t="n"/>
-      <c r="D52" s="4" t="n"/>
-      <c r="E52" s="4" t="n"/>
-      <c r="F52" s="4" t="n"/>
-      <c r="G52" s="4" t="n"/>
-      <c r="H52" s="4" t="n"/>
-      <c r="I52" s="4" t="n"/>
-      <c r="J52" s="4" t="n"/>
-      <c r="K52" s="4" t="n"/>
-      <c r="L52" s="4" t="n"/>
-      <c r="M52" s="4" t="n"/>
-      <c r="N52" s="4" t="n"/>
-      <c r="O52" s="4" t="n"/>
-      <c r="P52" s="4" t="n"/>
-      <c r="Q52" s="4" t="n"/>
-      <c r="R52" s="4" t="n"/>
-    </row>
-    <row r="53" ht="30" customHeight="1">
-      <c r="A53" s="6" t="inlineStr">
-        <is>
-          <t>브릴스</t>
-        </is>
-      </c>
-      <c r="B53" s="6" t="inlineStr">
-        <is>
-          <t>08-31~09-04</t>
-        </is>
-      </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>16,500~19,500</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>1,200,000</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>23,400,000,000</t>
-        </is>
-      </c>
-      <c r="F53" s="6" t="inlineStr">
-        <is>
-          <t>13.44 (PSR)</t>
-        </is>
-      </c>
-      <c r="G53" s="6" t="inlineStr">
-        <is>
-          <t>19,500</t>
-        </is>
-      </c>
-      <c r="H53" s="6" t="n">
-        <v>1187.74</v>
-      </c>
-      <c r="I53" s="6" t="n">
-        <v>2181</v>
-      </c>
-      <c r="J53" s="6" t="inlineStr">
-        <is>
-          <t>09-08~09-09</t>
-        </is>
-      </c>
-      <c r="K53" s="6" t="inlineStr">
-        <is>
-          <t>4,418.97</t>
-        </is>
-      </c>
-      <c r="L53" s="6" t="inlineStr"/>
-      <c r="M53" s="6" t="inlineStr"/>
-      <c r="N53" s="6" t="inlineStr">
-        <is>
-          <t>아이비케이투자증권</t>
-        </is>
-      </c>
-      <c r="O53" s="6" t="inlineStr"/>
-      <c r="P53" s="7" t="inlineStr">
-        <is>
-          <t>713,790,000</t>
-        </is>
-      </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>청약완료·상장대기</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="6" t="inlineStr">
-        <is>
-          <t>케이비제34호스팩</t>
-        </is>
-      </c>
-      <c r="B54" s="6" t="inlineStr">
-        <is>
-          <t>09-04~09-07</t>
-        </is>
-      </c>
-      <c r="C54" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="D54" s="7" t="inlineStr">
-        <is>
-          <t>7,000,000</t>
-        </is>
-      </c>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t>14,000,000,000</t>
-        </is>
-      </c>
-      <c r="F54" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="G54" s="6" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
-      </c>
-      <c r="H54" s="6" t="n">
-        <v>1232.51</v>
-      </c>
-      <c r="I54" s="6" t="n">
-        <v>2001</v>
-      </c>
-      <c r="J54" s="6" t="inlineStr">
-        <is>
-          <t>09-10~09-11</t>
-        </is>
-      </c>
-      <c r="K54" s="6" t="inlineStr">
-        <is>
-          <t>6,777.78</t>
-        </is>
-      </c>
-      <c r="L54" s="6" t="inlineStr"/>
-      <c r="M54" s="6" t="inlineStr"/>
-      <c r="N54" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="O54" s="6" t="inlineStr"/>
-      <c r="P54" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>청약완료·상장대기</t>
-        </is>
-      </c>
+    <row r="54" ht="22" customHeight="1">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>■ 공모 진행 (예심 승인법인)  (33건)</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="n"/>
+      <c r="C54" s="4" t="n"/>
+      <c r="D54" s="4" t="n"/>
+      <c r="E54" s="4" t="n"/>
+      <c r="F54" s="4" t="n"/>
+      <c r="G54" s="4" t="n"/>
+      <c r="H54" s="4" t="n"/>
+      <c r="I54" s="4" t="n"/>
+      <c r="J54" s="4" t="n"/>
+      <c r="K54" s="4" t="n"/>
+      <c r="L54" s="4" t="n"/>
+      <c r="M54" s="4" t="n"/>
+      <c r="N54" s="4" t="n"/>
+      <c r="O54" s="4" t="n"/>
+      <c r="P54" s="4" t="n"/>
+      <c r="Q54" s="4" t="n"/>
+      <c r="R54" s="4" t="n"/>
     </row>
     <row r="55" ht="30" customHeight="1">
       <c r="A55" s="6" t="inlineStr">
         <is>
-          <t>빅웨이브로보틱스</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>09-07~09-11</t>
+          <t>08-31~09-04</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>15,000~18,000</t>
+          <t>16,500~19,500</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>1,600,000</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>28,800,000,000</t>
+          <t>23,400,000,000</t>
         </is>
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>11.15 (PSR)</t>
+          <t>13.44 (PSR)</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>18,000</t>
+          <t>19,500</t>
         </is>
       </c>
       <c r="H55" s="6" t="n">
-        <v>1109.37</v>
+        <v>1187.74</v>
       </c>
       <c r="I55" s="6" t="n">
-        <v>2255</v>
+        <v>2181</v>
       </c>
       <c r="J55" s="6" t="inlineStr">
         <is>
-          <t>09-15~09-16</t>
+          <t>09-08~09-09</t>
         </is>
       </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
-          <t>2,706.30</t>
+          <t>4,418.97</t>
         </is>
       </c>
       <c r="L55" s="6" t="inlineStr"/>
       <c r="M55" s="6" t="inlineStr"/>
       <c r="N55" s="6" t="inlineStr">
         <is>
-          <t>유진투자증권</t>
-        </is>
-      </c>
-      <c r="O55" s="6" t="inlineStr">
-        <is>
-          <t>미래</t>
-        </is>
-      </c>
+          <t>아이비케이투자증권</t>
+        </is>
+      </c>
+      <c r="O55" s="6" t="inlineStr"/>
       <c r="P55" s="7" t="inlineStr">
         <is>
-          <t>378,216,000</t>
+          <t>713,790,000</t>
         </is>
       </c>
       <c r="Q55" s="6" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
@@ -12193,71 +12201,71 @@
     <row r="56" ht="30" customHeight="1">
       <c r="A56" s="6" t="inlineStr">
         <is>
-          <t>글로벌테크놀로지</t>
+          <t>케이비제34호스팩</t>
         </is>
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>09-07~09-11</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>13,000~15,000</t>
+          <t>09-04~09-07</t>
+        </is>
+      </c>
+      <c r="C56" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>7,000,000</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>40,000,000,000</t>
-        </is>
-      </c>
-      <c r="F56" s="6" t="inlineStr">
-        <is>
-          <t>19.22배 (PER)</t>
+          <t>14,000,000,000</t>
+        </is>
+      </c>
+      <c r="F56" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="H56" s="6" t="n">
-        <v>123.19</v>
+        <v>1232.51</v>
       </c>
       <c r="I56" s="6" t="n">
-        <v>961</v>
+        <v>2001</v>
       </c>
       <c r="J56" s="6" t="inlineStr">
         <is>
-          <t>09-16~09-17</t>
+          <t>09-10~09-11</t>
         </is>
       </c>
       <c r="K56" s="6" t="inlineStr">
         <is>
-          <t>57.15</t>
+          <t>6,777.78</t>
         </is>
       </c>
       <c r="L56" s="6" t="inlineStr"/>
       <c r="M56" s="6" t="inlineStr"/>
-      <c r="N56" s="6" t="inlineStr">
-        <is>
-          <t>한국투자증권</t>
+      <c r="N56" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="O56" s="6" t="inlineStr"/>
-      <c r="P56" s="7" t="inlineStr">
-        <is>
-          <t>2,119,999,960</t>
-        </is>
-      </c>
-      <c r="Q56" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P56" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>50%</t>
         </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
@@ -12345,7 +12353,7 @@
     <row r="58" ht="30" customHeight="1">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
@@ -12355,38 +12363,38 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>19,500~23,500</t>
+          <t>10,700~12,300</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>852,000</t>
+          <t>2,500,000</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>16,614,000,000</t>
+          <t>30,750,000,000</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>17.61배 (PER)</t>
+          <t>26.18배 (PER)</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>19,500</t>
+          <t>12,300</t>
         </is>
       </c>
       <c r="H58" s="6" t="n">
-        <v>1097.62</v>
+        <v>1136.84</v>
       </c>
       <c r="I58" s="6" t="n">
-        <v>2006</v>
+        <v>2405</v>
       </c>
       <c r="J58" s="6" t="inlineStr">
         <is>
-          <t>10-02~10-06</t>
+          <t>10-01~10-02</t>
         </is>
       </c>
       <c r="K58" s="6" t="inlineStr"/>
@@ -12394,18 +12402,18 @@
       <c r="M58" s="6" t="inlineStr"/>
       <c r="N58" s="6" t="inlineStr">
         <is>
-          <t>하나증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="O58" s="6" t="inlineStr"/>
       <c r="P58" s="7" t="inlineStr">
         <is>
-          <t>697,788,000</t>
+          <t>826,575,000</t>
         </is>
       </c>
       <c r="Q58" s="6" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
@@ -12417,7 +12425,7 @@
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
@@ -12427,30 +12435,38 @@
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>10,700~12,300</t>
+          <t>19,500~23,500</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>2,500,000</t>
+          <t>852,000</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>26,750,000,000</t>
+          <t>16,614,000,000</t>
         </is>
       </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>26.18배 (PER)</t>
-        </is>
-      </c>
-      <c r="G59" s="6" t="inlineStr"/>
-      <c r="H59" s="6" t="inlineStr"/>
-      <c r="I59" s="6" t="inlineStr"/>
+          <t>17.61배 (PER)</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>19,500</t>
+        </is>
+      </c>
+      <c r="H59" s="6" t="n">
+        <v>1097.62</v>
+      </c>
+      <c r="I59" s="6" t="n">
+        <v>2006</v>
+      </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
-          <t>10-01~10-02</t>
+          <t>10-02~10-06</t>
         </is>
       </c>
       <c r="K59" s="6" t="inlineStr"/>
@@ -12458,23 +12474,23 @@
       <c r="M59" s="6" t="inlineStr"/>
       <c r="N59" s="6" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>하나증권</t>
         </is>
       </c>
       <c r="O59" s="6" t="inlineStr"/>
       <c r="P59" s="7" t="inlineStr">
         <is>
-          <t>826,575,000</t>
+          <t>697,788,000</t>
         </is>
       </c>
       <c r="Q59" s="6" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
-          <t>정정</t>
+          <t>발행조건확정</t>
         </is>
       </c>
     </row>
@@ -12549,32 +12565,32 @@
     <row r="61" ht="30" customHeight="1">
       <c r="A61" s="6" t="inlineStr">
         <is>
-          <t>티앤이코리아</t>
+          <t>엠에스바이오</t>
         </is>
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>10-07~10-14</t>
+          <t>09-28~10-02</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>12,600~15,300</t>
+          <t>6,800~7,800</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>2,400,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>30,240,000,000</t>
+          <t>27,200,000,000</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>19.48배 (PER)</t>
+          <t>30.89배 (PER)</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr"/>
@@ -12582,7 +12598,7 @@
       <c r="I61" s="6" t="inlineStr"/>
       <c r="J61" s="6" t="inlineStr">
         <is>
-          <t>10-20~10-21</t>
+          <t>10-12~10-13</t>
         </is>
       </c>
       <c r="K61" s="6" t="inlineStr"/>
@@ -12590,13 +12606,13 @@
       <c r="M61" s="6" t="inlineStr"/>
       <c r="N61" s="6" t="inlineStr">
         <is>
-          <t>신한투자증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="O61" s="6" t="inlineStr"/>
       <c r="P61" s="7" t="inlineStr">
         <is>
-          <t>1,245,888,000</t>
+          <t>1,120,640,000</t>
         </is>
       </c>
       <c r="Q61" s="6" t="inlineStr">
@@ -12613,32 +12629,32 @@
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>에스케이증권제14호기업인수목적</t>
+          <t>티앤이코리아</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>10-12~10-13</t>
-        </is>
-      </c>
-      <c r="C62" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>10-07~10-14</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>12,600~15,300</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>6,500,000</t>
+          <t>2,400,000</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>13,000,000,000</t>
-        </is>
-      </c>
-      <c r="F62" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>30,240,000,000</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>19.48배 (PER)</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr"/>
@@ -12646,26 +12662,26 @@
       <c r="I62" s="6" t="inlineStr"/>
       <c r="J62" s="6" t="inlineStr">
         <is>
-          <t>10-15~10-16</t>
+          <t>10-20~10-21</t>
         </is>
       </c>
       <c r="K62" s="6" t="inlineStr"/>
       <c r="L62" s="6" t="inlineStr"/>
       <c r="M62" s="6" t="inlineStr"/>
-      <c r="N62" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="N62" s="6" t="inlineStr">
+        <is>
+          <t>신한투자증권</t>
         </is>
       </c>
       <c r="O62" s="6" t="inlineStr"/>
-      <c r="P62" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P62" s="7" t="inlineStr">
+        <is>
+          <t>1,245,888,000</t>
         </is>
       </c>
       <c r="Q62" s="6" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="R62" s="6" t="inlineStr">
@@ -12677,32 +12693,32 @@
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>크리에이츠</t>
+          <t>에스케이증권제14호기업인수목적</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>10-12~10-16</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>15,000~18,000</t>
+          <t>10-12~10-13</t>
+        </is>
+      </c>
+      <c r="C63" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>1,400,000</t>
+          <t>6,500,000</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>21,000,000,000</t>
-        </is>
-      </c>
-      <c r="F63" s="6" t="inlineStr">
-        <is>
-          <t>19.15배 (PER)</t>
+          <t>13,000,000,000</t>
+        </is>
+      </c>
+      <c r="F63" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr"/>
@@ -12710,26 +12726,26 @@
       <c r="I63" s="6" t="inlineStr"/>
       <c r="J63" s="6" t="inlineStr">
         <is>
-          <t>10-20~10-21</t>
+          <t>10-15~10-16</t>
         </is>
       </c>
       <c r="K63" s="6" t="inlineStr"/>
       <c r="L63" s="6" t="inlineStr"/>
       <c r="M63" s="6" t="inlineStr"/>
-      <c r="N63" s="6" t="inlineStr">
-        <is>
-          <t>삼성증권</t>
+      <c r="N63" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="O63" s="6" t="inlineStr"/>
-      <c r="P63" s="7" t="inlineStr">
-        <is>
-          <t>865,200,000</t>
+      <c r="P63" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="Q63" s="6" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="R63" s="6" t="inlineStr">
@@ -12741,32 +12757,32 @@
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>래블업</t>
+          <t>크리에이츠</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>10-13~10-19</t>
+          <t>10-12~10-16</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>19,000~22,000</t>
+          <t>15,000~18,000</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>2,180,000</t>
+          <t>1,400,000</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>41,420,000,000</t>
+          <t>21,000,000,000</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>33.6배 (PER)</t>
+          <t>19.15배 (PER)</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr"/>
@@ -12774,7 +12790,7 @@
       <c r="I64" s="6" t="inlineStr"/>
       <c r="J64" s="6" t="inlineStr">
         <is>
-          <t>10-22~10-23</t>
+          <t>10-20~10-21</t>
         </is>
       </c>
       <c r="K64" s="6" t="inlineStr"/>
@@ -12782,18 +12798,18 @@
       <c r="M64" s="6" t="inlineStr"/>
       <c r="N64" s="6" t="inlineStr">
         <is>
-          <t>NH투자증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="O64" s="6" t="inlineStr"/>
       <c r="P64" s="7" t="inlineStr">
         <is>
-          <t>1,908,899,000</t>
+          <t>865,200,000</t>
         </is>
       </c>
       <c r="Q64" s="6" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="R64" s="6" t="inlineStr">
@@ -12805,32 +12821,32 @@
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>엠비디</t>
+          <t>래블업</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>10-16~10-22</t>
+          <t>10-13~10-19</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>9,600~11,700</t>
+          <t>19,000~22,000</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>2,180,000</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>19,200,000,000</t>
+          <t>41,420,000,000</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>26.87배 (PER)</t>
+          <t>33.6배 (PER)</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr"/>
@@ -12838,7 +12854,7 @@
       <c r="I65" s="6" t="inlineStr"/>
       <c r="J65" s="6" t="inlineStr">
         <is>
-          <t>10-28~10-29</t>
+          <t>10-22~10-23</t>
         </is>
       </c>
       <c r="K65" s="6" t="inlineStr"/>
@@ -12846,18 +12862,18 @@
       <c r="M65" s="6" t="inlineStr"/>
       <c r="N65" s="6" t="inlineStr">
         <is>
-          <t>하나증권</t>
+          <t>NH투자증권</t>
         </is>
       </c>
       <c r="O65" s="6" t="inlineStr"/>
       <c r="P65" s="7" t="inlineStr">
         <is>
-          <t>988,800,000</t>
+          <t>1,908,899,000</t>
         </is>
       </c>
       <c r="Q65" s="6" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="R65" s="6" t="inlineStr">
@@ -12869,32 +12885,32 @@
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>엠에스바이오</t>
+          <t>엠비디</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>09-28~10-02</t>
+          <t>10-16~10-22</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>6,800~7,800</t>
+          <t>9,600~11,700</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>27,200,000,000</t>
+          <t>19,200,000,000</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>30.89배 (PER)</t>
+          <t>26.87배 (PER)</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr"/>
@@ -12902,7 +12918,7 @@
       <c r="I66" s="6" t="inlineStr"/>
       <c r="J66" s="6" t="inlineStr">
         <is>
-          <t>10-12~10-13</t>
+          <t>10-28~10-29</t>
         </is>
       </c>
       <c r="K66" s="6" t="inlineStr"/>
@@ -12910,23 +12926,23 @@
       <c r="M66" s="6" t="inlineStr"/>
       <c r="N66" s="6" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>하나증권</t>
         </is>
       </c>
       <c r="O66" s="6" t="inlineStr"/>
       <c r="P66" s="7" t="inlineStr">
         <is>
-          <t>1,120,640,000</t>
+          <t>988,800,000</t>
         </is>
       </c>
       <c r="Q66" s="6" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="R66" s="6" t="inlineStr">
         <is>
-          <t>최초</t>
+          <t>정정</t>
         </is>
       </c>
     </row>
@@ -13381,32 +13397,32 @@
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>넥스아이</t>
+          <t>옵토닉스</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>10-22~10-28</t>
+          <t>10-21~10-27</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>10,500~13,000</t>
+          <t>10,000~12,000</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>2,200,000</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>52,500,000,000</t>
+          <t>22,000,000,000</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>19.15배 (PER)</t>
+          <t>25.27배 (EV/EBITDA)</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr"/>
@@ -13414,7 +13430,7 @@
       <c r="I74" s="6" t="inlineStr"/>
       <c r="J74" s="6" t="inlineStr">
         <is>
-          <t>11-03~11-04</t>
+          <t>11-05~11-06</t>
         </is>
       </c>
       <c r="K74" s="6" t="inlineStr"/>
@@ -13428,12 +13444,12 @@
       <c r="O74" s="6" t="inlineStr"/>
       <c r="P74" s="7" t="inlineStr">
         <is>
-          <t>2,407,500,000</t>
+          <t>1,133,000,000</t>
         </is>
       </c>
       <c r="Q74" s="6" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="R74" s="6" t="inlineStr">
@@ -13445,32 +13461,32 @@
     <row r="75" ht="30" customHeight="1">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>하나에어로다이내믹스</t>
+          <t>넥스아이</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>11-02~11-06</t>
+          <t>10-22~10-28</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>4,700~5,700</t>
+          <t>10,500~13,000</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>4,400,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>20,680,000,000</t>
+          <t>52,500,000,000</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
         <is>
-          <t>17.89배 (EV/EBITDA)</t>
+          <t>19.15배 (PER)</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr"/>
@@ -13478,7 +13494,7 @@
       <c r="I75" s="6" t="inlineStr"/>
       <c r="J75" s="6" t="inlineStr">
         <is>
-          <t>11-10~11-11</t>
+          <t>11-03~11-04</t>
         </is>
       </c>
       <c r="K75" s="6" t="inlineStr"/>
@@ -13486,18 +13502,18 @@
       <c r="M75" s="6" t="inlineStr"/>
       <c r="N75" s="6" t="inlineStr">
         <is>
-          <t>아이비케이투자증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="O75" s="6" t="inlineStr"/>
       <c r="P75" s="7" t="inlineStr">
         <is>
-          <t>850,000,000</t>
-        </is>
-      </c>
-      <c r="Q75" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>2,407,500,000</t>
+        </is>
+      </c>
+      <c r="Q75" s="6" t="inlineStr">
+        <is>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="R75" s="6" t="inlineStr">
@@ -13509,54 +13525,54 @@
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>바로팜</t>
-        </is>
-      </c>
-      <c r="B76" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>하나에어로다이내믹스</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="inlineStr">
+        <is>
+          <t>11-02~11-06</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>16,400~20,200</t>
+          <t>4,700~5,700</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>1,780,000</t>
+          <t>4,400,000</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>29,192,000,000</t>
+          <t>20,680,000,000</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
         <is>
-          <t>24.95배 (PER)</t>
+          <t>17.89배 (EV/EBITDA)</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr"/>
       <c r="H76" s="6" t="inlineStr"/>
       <c r="I76" s="6" t="inlineStr"/>
-      <c r="J76" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="J76" s="6" t="inlineStr">
+        <is>
+          <t>11-10~11-11</t>
         </is>
       </c>
       <c r="K76" s="6" t="inlineStr"/>
       <c r="L76" s="6" t="inlineStr"/>
       <c r="M76" s="6" t="inlineStr"/>
-      <c r="N76" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="N76" s="6" t="inlineStr">
+        <is>
+          <t>아이비케이투자증권</t>
         </is>
       </c>
       <c r="O76" s="6" t="inlineStr"/>
-      <c r="P76" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P76" s="7" t="inlineStr">
+        <is>
+          <t>850,000,000</t>
         </is>
       </c>
       <c r="Q76" s="18" t="inlineStr">
@@ -13573,7 +13589,7 @@
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>디티에스</t>
+          <t>바로팜</t>
         </is>
       </c>
       <c r="B77" s="18" t="inlineStr">
@@ -13581,24 +13597,24 @@
           <t>수집예정</t>
         </is>
       </c>
-      <c r="C77" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="D77" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="E77" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="F77" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>16,400~20,200</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>1,780,000</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>29,192,000,000</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>24.95배 (PER)</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr"/>
@@ -13630,14 +13646,14 @@
       </c>
       <c r="R77" s="6" t="inlineStr">
         <is>
-          <t>신고서 대기</t>
+          <t>최초</t>
         </is>
       </c>
     </row>
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>에이엔에이치스트럭쳐</t>
+          <t>셀트릭스</t>
         </is>
       </c>
       <c r="B78" s="18" t="inlineStr">
@@ -13694,14 +13710,14 @@
       </c>
       <c r="R78" s="6" t="inlineStr">
         <is>
-          <t>신고서 대기</t>
+          <t>최초</t>
         </is>
       </c>
     </row>
     <row r="79" ht="30" customHeight="1">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>이에스티</t>
+          <t>솔리스</t>
         </is>
       </c>
       <c r="B79" s="18" t="inlineStr">
@@ -13758,14 +13774,14 @@
       </c>
       <c r="R79" s="6" t="inlineStr">
         <is>
-          <t>신고서 대기</t>
+          <t>최초</t>
         </is>
       </c>
     </row>
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>영광와이케이엠씨</t>
+          <t>디티에스</t>
         </is>
       </c>
       <c r="B80" s="18" t="inlineStr">
@@ -13829,7 +13845,7 @@
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>동원파츠</t>
+          <t>에이엔에이치스트럭쳐</t>
         </is>
       </c>
       <c r="B81" s="18" t="inlineStr">
@@ -13893,7 +13909,7 @@
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>케이엠에프</t>
+          <t>이에스티</t>
         </is>
       </c>
       <c r="B82" s="18" t="inlineStr">
@@ -13957,7 +13973,7 @@
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>옵토닉스</t>
+          <t>영광와이케이엠씨</t>
         </is>
       </c>
       <c r="B83" s="18" t="inlineStr">
@@ -14021,7 +14037,7 @@
     <row r="84" ht="30" customHeight="1">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>제논</t>
+          <t>동원파츠</t>
         </is>
       </c>
       <c r="B84" s="18" t="inlineStr">
@@ -14085,7 +14101,7 @@
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>셀트릭스</t>
+          <t>케이엠에프</t>
         </is>
       </c>
       <c r="B85" s="18" t="inlineStr">
@@ -14149,7 +14165,7 @@
     <row r="86" ht="30" customHeight="1">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>럭스코</t>
+          <t>제논</t>
         </is>
       </c>
       <c r="B86" s="18" t="inlineStr">
@@ -14213,7 +14229,7 @@
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>솔리스</t>
+          <t>럭스코</t>
         </is>
       </c>
       <c r="B87" s="18" t="inlineStr">
@@ -14575,7 +14591,7 @@
         <v>0</v>
       </c>
       <c r="E14" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F14" s="21">
         <f>IF((C14+D14)=0,"-",C14/(C14+D14))</f>
@@ -14638,45 +14654,45 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>215,984,000,000</t>
+          <t>256,940,000,000</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>198,930,000,000</t>
+          <t>215,984,000,000</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>194,940,000,000</t>
+          <t>202,930,000,000</t>
         </is>
       </c>
     </row>
@@ -14743,22 +14759,22 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>DB증권</t>
+          <t>유진투자증권</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>46,000,000,000</t>
+          <t>74,400,000,000</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>유진투자증권</t>
+          <t>DB증권</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
@@ -14766,7 +14782,7 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>45,600,000,000</t>
+          <t>46,000,000,000</t>
         </is>
       </c>
     </row>

--- a/IPO_analysis.xlsx
+++ b/IPO_analysis.xlsx
@@ -618,7 +618,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>기준일 2026-09-30 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
+          <t>기준일 2026-10-01 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
         </is>
       </c>
     </row>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="K92" s="6" t="inlineStr">
         <is>
-          <t>상장승인(상장예정)</t>
+          <t>상장완료 (2026-10-01)</t>
         </is>
       </c>
     </row>
@@ -8509,7 +8509,7 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>■ 상장 완료 (2026)  (47건)</t>
+          <t>■ 상장 완료 (2026)  (48건)</t>
         </is>
       </c>
       <c r="B6" s="4" t="n"/>
@@ -8533,44 +8533,44 @@
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>09-08~09-14</t>
+          <t>08-31~09-04</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>12,400~14,600</t>
+          <t>16,500~19,500</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>43,800,000,000</t>
+          <t>23,400,000,000</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>32.57배 (PER)</t>
+          <t>13.44 (PSR)</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>14,600</t>
+          <t>19,500</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>868.64</v>
+        <v>1187.74</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>2269</v>
+        <v>2181</v>
       </c>
       <c r="J7" s="18" t="inlineStr">
         <is>
@@ -8579,29 +8579,29 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>1,878.06</t>
+          <t>4,418.97</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr"/>
       <c r="M7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="N7" s="6" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>아이비케이투자증권</t>
         </is>
       </c>
       <c r="O7" s="6" t="inlineStr"/>
       <c r="P7" s="7" t="inlineStr">
         <is>
-          <t>1,413,399,926</t>
+          <t>713,790,000</t>
         </is>
       </c>
       <c r="Q7" s="6" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="R7" s="6" t="inlineStr">
@@ -8613,44 +8613,44 @@
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>빅웨이브로보틱스</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>09-07~09-11</t>
+          <t>09-08~09-14</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>15,000~18,000</t>
+          <t>12,400~14,600</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>1,600,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>28,800,000,000</t>
+          <t>43,800,000,000</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>11.15 (PSR)</t>
+          <t>32.57배 (PER)</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>18,000</t>
+          <t>14,600</t>
         </is>
       </c>
       <c r="H8" s="6" t="n">
-        <v>1109.37</v>
+        <v>868.64</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>2255</v>
+        <v>2269</v>
       </c>
       <c r="J8" s="18" t="inlineStr">
         <is>
@@ -8659,33 +8659,29 @@
       </c>
       <c r="K8" s="6" t="inlineStr">
         <is>
-          <t>2,706.30</t>
+          <t>1,878.06</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr"/>
       <c r="M8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="N8" s="6" t="inlineStr">
         <is>
-          <t>유진투자증권</t>
-        </is>
-      </c>
-      <c r="O8" s="6" t="inlineStr">
-        <is>
-          <t>미래</t>
-        </is>
-      </c>
+          <t>대신증권</t>
+        </is>
+      </c>
+      <c r="O8" s="6" t="inlineStr"/>
       <c r="P8" s="7" t="inlineStr">
         <is>
-          <t>378,216,000</t>
+          <t>1,413,399,926</t>
         </is>
       </c>
       <c r="Q8" s="6" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="R8" s="6" t="inlineStr">
@@ -8697,7 +8693,7 @@
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>글로벌테크놀로지</t>
+          <t>빅웨이브로보틱스</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
@@ -8707,34 +8703,34 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>13,000~15,000</t>
+          <t>15,000~18,000</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>1,600,000</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>40,000,000,000</t>
+          <t>28,800,000,000</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>19.22배 (PER)</t>
+          <t>11.15 (PSR)</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>18,000</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>123.19</v>
+        <v>1109.37</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>961</v>
+        <v>2255</v>
       </c>
       <c r="J9" s="18" t="inlineStr">
         <is>
@@ -8743,7 +8739,7 @@
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>57.15</t>
+          <t>2,706.30</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr"/>
@@ -8754,18 +8750,22 @@
       </c>
       <c r="N9" s="6" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
-        </is>
-      </c>
-      <c r="O9" s="6" t="inlineStr"/>
+          <t>유진투자증권</t>
+        </is>
+      </c>
+      <c r="O9" s="6" t="inlineStr">
+        <is>
+          <t>미래</t>
+        </is>
+      </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
-          <t>2,119,999,960</t>
-        </is>
-      </c>
-      <c r="Q9" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>378,216,000</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
@@ -8777,44 +8777,44 @@
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>와이즈플래닛컴퍼니</t>
+          <t>글로벌테크놀로지</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>09-04~09-10</t>
+          <t>09-07~09-11</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>10,000~12,000</t>
+          <t>13,000~15,000</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>1,600,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>19,200,000,000</t>
+          <t>40,000,000,000</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>20.04배 (PER)</t>
+          <t>19.22배 (PER)</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="H10" s="6" t="n">
-        <v>1248.47</v>
+        <v>123.19</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>2323</v>
+        <v>961</v>
       </c>
       <c r="J10" s="18" t="inlineStr">
         <is>
@@ -8823,29 +8823,29 @@
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>3,568.86</t>
+          <t>57.15</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr"/>
       <c r="M10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="O10" s="6" t="inlineStr"/>
       <c r="P10" s="7" t="inlineStr">
         <is>
-          <t>494,400,000</t>
-        </is>
-      </c>
-      <c r="Q10" s="6" t="inlineStr">
-        <is>
-          <t>3.0%</t>
+          <t>2,119,999,960</t>
+        </is>
+      </c>
+      <c r="Q10" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="R10" s="6" t="inlineStr">
@@ -8857,44 +8857,44 @@
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>한국제17호스팩</t>
+          <t>와이즈플래닛컴퍼니</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>09-07~09-08</t>
-        </is>
-      </c>
-      <c r="C11" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>09-04~09-10</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>10,000~12,000</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>7,000,000</t>
+          <t>1,600,000</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>14,000,000,000</t>
-        </is>
-      </c>
-      <c r="F11" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>19,200,000,000</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>20.04배 (PER)</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>1270.51</v>
+        <v>1248.47</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>2040</v>
+        <v>2323</v>
       </c>
       <c r="J11" s="18" t="inlineStr">
         <is>
@@ -8903,29 +8903,29 @@
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>8,291.55</t>
+          <t>3,568.86</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr"/>
       <c r="M11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="N11" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="N11" s="6" t="inlineStr">
+        <is>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="O11" s="6" t="inlineStr"/>
-      <c r="P11" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P11" s="7" t="inlineStr">
+        <is>
+          <t>494,400,000</t>
         </is>
       </c>
       <c r="Q11" s="6" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="R11" s="6" t="inlineStr">
@@ -8937,12 +8937,12 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>KB제34호스팩</t>
-        </is>
-      </c>
-      <c r="B12" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>한국제17호스팩</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>09-07~09-08</t>
         </is>
       </c>
       <c r="C12" s="18" t="inlineStr">
@@ -8965,25 +8965,25 @@
           <t>수집예정</t>
         </is>
       </c>
-      <c r="G12" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>2,000</t>
         </is>
       </c>
       <c r="H12" s="6" t="n">
-        <v>1232.51</v>
+        <v>1270.51</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>2001</v>
+        <v>2040</v>
       </c>
       <c r="J12" s="18" t="inlineStr">
         <is>
           <t>수집예정</t>
         </is>
       </c>
-      <c r="K12" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="K12" s="6" t="inlineStr">
+        <is>
+          <t>8,291.55</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr"/>
@@ -9017,75 +9017,75 @@
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>네오사피엔스</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>09-02~09-08</t>
-        </is>
-      </c>
-      <c r="C13" s="6" t="inlineStr">
-        <is>
-          <t>13,800~15,800</t>
+          <t>KB제34호스팩</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>7,000,000</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>20,000,000,000</t>
-        </is>
-      </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>26.76배 (PER)</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
-        <is>
-          <t>10,000</t>
+          <t>14,000,000,000</t>
+        </is>
+      </c>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="G13" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>219.56</v>
+        <v>1232.51</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>1045</v>
+        <v>2001</v>
       </c>
       <c r="J13" s="18" t="inlineStr">
         <is>
           <t>수집예정</t>
         </is>
       </c>
-      <c r="K13" s="6" t="inlineStr">
-        <is>
-          <t>4,885.53</t>
+      <c r="K13" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr"/>
       <c r="M13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="N13" s="6" t="inlineStr">
-        <is>
-          <t>대신증권</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="N13" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="O13" s="6" t="inlineStr"/>
-      <c r="P13" s="7" t="inlineStr">
-        <is>
-          <t>1,080,264,000</t>
+      <c r="P13" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="Q13" s="6" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
@@ -9097,44 +9097,44 @@
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>엔에이치스팩34호</t>
+          <t>네오사피엔스</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>08-24~08-25</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>09-02~09-08</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>13,800~15,800</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>8,500,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>17,000,000,000</t>
-        </is>
-      </c>
-      <c r="F14" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>20,000,000,000</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>26.76배 (PER)</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="H14" s="6" t="n">
-        <v>1160.7</v>
+        <v>219.56</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>2050</v>
+        <v>1045</v>
       </c>
       <c r="J14" s="18" t="inlineStr">
         <is>
@@ -9143,29 +9143,29 @@
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>16,216.08</t>
+          <t>4,885.53</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr"/>
       <c r="M14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="N14" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="N14" s="6" t="inlineStr">
+        <is>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="O14" s="6" t="inlineStr"/>
-      <c r="P14" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>1,080,264,000</t>
         </is>
       </c>
       <c r="Q14" s="6" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="R14" s="6" t="inlineStr">
@@ -9177,44 +9177,44 @@
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>엔에이치스팩34호</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>08-14~08-21</t>
-        </is>
-      </c>
-      <c r="C15" s="6" t="inlineStr">
-        <is>
-          <t>13,000~16,000</t>
+          <t>08-24~08-25</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>8,500,000</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>20,000,000,000</t>
-        </is>
-      </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>29.52배 (PER)</t>
+          <t>17,000,000,000</t>
+        </is>
+      </c>
+      <c r="F15" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>63.41</v>
+        <v>1160.7</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>246</v>
+        <v>2050</v>
       </c>
       <c r="J15" s="18" t="inlineStr">
         <is>
@@ -9223,29 +9223,29 @@
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>88.20</t>
+          <t>16,216.08</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr"/>
       <c r="M15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="N15" s="6" t="inlineStr">
-        <is>
-          <t>한국투자증권</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="N15" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="O15" s="6" t="inlineStr"/>
-      <c r="P15" s="7" t="inlineStr">
-        <is>
-          <t>1,071,200,000</t>
-        </is>
-      </c>
-      <c r="Q15" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P15" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>50%</t>
         </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
@@ -9257,75 +9257,75 @@
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>해치텍</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>08-03~08-07</t>
+          <t>08-14~08-21</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>23,000~28,000</t>
+          <t>13,000~16,000</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>1,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>23,000,000,000</t>
+          <t>20,000,000,000</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>36.99배 (PER)</t>
+          <t>29.52배 (PER)</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="H16" s="6" t="n">
-        <v>101.91</v>
+        <v>63.41</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>321</v>
+        <v>246</v>
       </c>
       <c r="J16" s="18" t="inlineStr">
         <is>
           <t>수집예정</t>
         </is>
       </c>
-      <c r="K16" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>88.20</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr"/>
       <c r="M16" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="N16" s="6" t="inlineStr">
         <is>
-          <t>DB증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="O16" s="6" t="inlineStr"/>
       <c r="P16" s="7" t="inlineStr">
         <is>
-          <t>1,302,950,000</t>
-        </is>
-      </c>
-      <c r="Q16" s="6" t="inlineStr">
-        <is>
-          <t>5.5%</t>
+          <t>1,071,200,000</t>
+        </is>
+      </c>
+      <c r="Q16" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="R16" s="6" t="inlineStr">
@@ -9337,7 +9337,7 @@
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>니어스랩</t>
+          <t>해치텍</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
@@ -9347,34 +9347,34 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>30,000~41,200</t>
+          <t>23,000~28,000</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>910,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>37,492,000,000</t>
+          <t>23,000,000,000</t>
         </is>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>44.41배 (PER)</t>
+          <t>36.99배 (PER)</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>41,200</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>743.49</v>
+        <v>101.91</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>1795</v>
+        <v>321</v>
       </c>
       <c r="J17" s="18" t="inlineStr">
         <is>
@@ -9389,23 +9389,23 @@
       <c r="L17" s="6" t="inlineStr"/>
       <c r="M17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="N17" s="6" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>DB증권</t>
         </is>
       </c>
       <c r="O17" s="6" t="inlineStr"/>
       <c r="P17" s="7" t="inlineStr">
         <is>
-          <t>1,265,355,000</t>
+          <t>1,302,950,000</t>
         </is>
       </c>
       <c r="Q17" s="6" t="inlineStr">
         <is>
-          <t>4.50%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="R17" s="6" t="inlineStr">
@@ -9417,44 +9417,44 @@
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>기도산업</t>
+          <t>니어스랩</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>07-31~08-06</t>
+          <t>08-03~08-07</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>24,800~28,400</t>
+          <t>30,000~41,200</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>1,700,000</t>
+          <t>910,000</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>48,280,000,000</t>
+          <t>37,492,000,000</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>10.01배 (PER)</t>
+          <t>44.41배 (PER)</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>28,400</t>
+          <t>41,200</t>
         </is>
       </c>
       <c r="H18" s="6" t="n">
-        <v>213.31</v>
+        <v>743.49</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>637</v>
+        <v>1795</v>
       </c>
       <c r="J18" s="18" t="inlineStr">
         <is>
@@ -9469,23 +9469,23 @@
       <c r="L18" s="6" t="inlineStr"/>
       <c r="M18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="N18" s="6" t="inlineStr">
         <is>
-          <t>미래에셋증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="O18" s="6" t="inlineStr"/>
       <c r="P18" s="7" t="inlineStr">
         <is>
-          <t>716,720,000</t>
+          <t>1,265,355,000</t>
         </is>
       </c>
       <c r="Q18" s="6" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>4.50%</t>
         </is>
       </c>
       <c r="R18" s="6" t="inlineStr">
@@ -9497,44 +9497,44 @@
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스</t>
+          <t>기도산업</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>07-20~07-24</t>
+          <t>07-31~08-06</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>12,000~14,500</t>
+          <t>24,800~28,400</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>1,700,000</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>60,000,000,000</t>
+          <t>48,280,000,000</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>22.89배 (PER)</t>
+          <t>10.01배 (PER)</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>28,400</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>50.4</v>
+        <v>213.31</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>307</v>
+        <v>637</v>
       </c>
       <c r="J19" s="18" t="inlineStr">
         <is>
@@ -9549,23 +9549,23 @@
       <c r="L19" s="6" t="inlineStr"/>
       <c r="M19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="N19" s="6" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>미래에셋증권</t>
         </is>
       </c>
       <c r="O19" s="6" t="inlineStr"/>
       <c r="P19" s="7" t="inlineStr">
         <is>
-          <t>4,095,000,000</t>
+          <t>716,720,000</t>
         </is>
       </c>
       <c r="Q19" s="6" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
@@ -9577,44 +9577,44 @@
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>케이앤에스아이앤씨</t>
+          <t>인제니아테라퓨틱스</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>07-27~07-31</t>
+          <t>07-20~07-24</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>9,000~11,000</t>
+          <t>12,000~14,500</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>2,400,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>26,400,000,000</t>
+          <t>60,000,000,000</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>42.08배 (PER)</t>
+          <t>22.89배 (PER)</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>11,000</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="H20" s="6" t="n">
-        <v>938.24</v>
+        <v>50.4</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>2024</v>
+        <v>307</v>
       </c>
       <c r="J20" s="18" t="inlineStr">
         <is>
@@ -9629,23 +9629,23 @@
       <c r="L20" s="6" t="inlineStr"/>
       <c r="M20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="N20" s="6" t="inlineStr">
         <is>
-          <t>아이비케이투자증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="O20" s="6" t="inlineStr"/>
       <c r="P20" s="7" t="inlineStr">
         <is>
-          <t>1,500,000,000</t>
+          <t>4,095,000,000</t>
         </is>
       </c>
       <c r="Q20" s="6" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
@@ -9657,44 +9657,44 @@
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>딜리셔스</t>
+          <t>케이앤에스아이앤씨</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>07-23~07-29</t>
+          <t>07-27~07-31</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>5,000~7,000</t>
+          <t>9,000~11,000</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>2,200,000</t>
+          <t>2,400,000</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>15,400,000,000</t>
+          <t>26,400,000,000</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>23.93배 (PER)</t>
+          <t>42.08배 (PER)</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>7,000</t>
+          <t>11,000</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>184.06</v>
+        <v>938.24</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>441</v>
+        <v>2024</v>
       </c>
       <c r="J21" s="18" t="inlineStr">
         <is>
@@ -9709,23 +9709,23 @@
       <c r="L21" s="6" t="inlineStr"/>
       <c r="M21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="N21" s="6" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>아이비케이투자증권</t>
         </is>
       </c>
       <c r="O21" s="6" t="inlineStr"/>
       <c r="P21" s="7" t="inlineStr">
         <is>
-          <t>566,500,000</t>
+          <t>1,500,000,000</t>
         </is>
       </c>
       <c r="Q21" s="6" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
@@ -9737,44 +9737,44 @@
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>에이치엘지노믹스</t>
+          <t>딜리셔스</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>07-02~07-08</t>
+          <t>07-23~07-29</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>18,500~21,500</t>
+          <t>5,000~7,000</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>2,565,000</t>
+          <t>2,200,000</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>55,147,500,000</t>
+          <t>15,400,000,000</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>12.85배 (EV/EBITDA)</t>
+          <t>23.93배 (PER)</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>21,500</t>
+          <t>7,000</t>
         </is>
       </c>
       <c r="H22" s="6" t="n">
-        <v>714.52</v>
+        <v>184.06</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>2148</v>
+        <v>441</v>
       </c>
       <c r="J22" s="18" t="inlineStr">
         <is>
@@ -9789,27 +9789,23 @@
       <c r="L22" s="6" t="inlineStr"/>
       <c r="M22" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="N22" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
-        </is>
-      </c>
-      <c r="O22" s="6" t="inlineStr">
-        <is>
-          <t>아이비케이투자증권, IBK투자증권, IBK투자증권, IBK투자증권, IBK투자증권, IBK투자증권㈜, 보통주, IBK투자증권㈜</t>
-        </is>
-      </c>
+          <t>한국투자증권</t>
+        </is>
+      </c>
+      <c r="O22" s="6" t="inlineStr"/>
       <c r="P22" s="7" t="inlineStr">
         <is>
-          <t>1,211</t>
+          <t>566,500,000</t>
         </is>
       </c>
       <c r="Q22" s="6" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="R22" s="6" t="inlineStr">
@@ -9821,63 +9817,59 @@
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>레메디</t>
-        </is>
-      </c>
-      <c r="B23" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>에이치엘지노믹스</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>07-02~07-08</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>17,800~20,700</t>
+          <t>18,500~21,500</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>1,200,000</t>
+          <t>2,565,000</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>24,840,000,000</t>
+          <t>55,147,500,000</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>21.95배 (PER)</t>
+          <t>12.85배 (EV/EBITDA)</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>20,700</t>
-        </is>
-      </c>
-      <c r="H23" s="6" t="inlineStr">
-        <is>
-          <t>1,146.41</t>
-        </is>
-      </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>2,246</t>
-        </is>
+          <t>21,500</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>714.52</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>2148</v>
       </c>
       <c r="J23" s="18" t="inlineStr">
         <is>
           <t>수집예정</t>
         </is>
       </c>
-      <c r="K23" s="6" t="inlineStr">
-        <is>
-          <t>1,706.71</t>
+      <c r="K23" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="L23" s="6" t="inlineStr"/>
       <c r="M23" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="N23" s="6" t="inlineStr">
@@ -9885,15 +9877,19 @@
           <t>KB</t>
         </is>
       </c>
-      <c r="O23" s="6" t="inlineStr"/>
+      <c r="O23" s="6" t="inlineStr">
+        <is>
+          <t>아이비케이투자증권, IBK투자증권, IBK투자증권, IBK투자증권, IBK투자증권, IBK투자증권㈜, 보통주, IBK투자증권㈜</t>
+        </is>
+      </c>
       <c r="P23" s="7" t="inlineStr">
         <is>
-          <t>1,279</t>
+          <t>1,211</t>
         </is>
       </c>
       <c r="Q23" s="6" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="R23" s="6" t="inlineStr">
@@ -9905,7 +9901,7 @@
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>레몬헬스케어</t>
+          <t>레메디</t>
         </is>
       </c>
       <c r="B24" s="18" t="inlineStr">
@@ -9915,45 +9911,53 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>7,500~10,000</t>
+          <t>17,800~20,700</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>24,840,000,000</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>25.48배 (PER)</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H24" s="6" t="n">
-        <v>1238</v>
-      </c>
-      <c r="I24" s="6" t="n">
-        <v>2233</v>
-      </c>
-      <c r="J24" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-24~25</t>
-        </is>
-      </c>
-      <c r="K24" s="6" t="n">
-        <v>1510.57</v>
+          <t>21.95배 (PER)</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>20,700</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t>1,146.41</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>2,246</t>
+        </is>
+      </c>
+      <c r="J24" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="K24" s="6" t="inlineStr">
+        <is>
+          <t>1,706.71</t>
+        </is>
       </c>
       <c r="L24" s="6" t="inlineStr"/>
       <c r="M24" s="6" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="N24" s="6" t="inlineStr">
@@ -9964,12 +9968,12 @@
       <c r="O24" s="6" t="inlineStr"/>
       <c r="P24" s="7" t="inlineStr">
         <is>
-          <t>824</t>
+          <t>1,279</t>
         </is>
       </c>
       <c r="Q24" s="6" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="R24" s="6" t="inlineStr">
@@ -9981,7 +9985,7 @@
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>매드업</t>
+          <t>레몬헬스케어</t>
         </is>
       </c>
       <c r="B25" s="18" t="inlineStr">
@@ -9991,7 +9995,7 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>7,000~8,000</t>
+          <t>7,500~10,000</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
@@ -10001,51 +10005,51 @@
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>16,000</t>
+          <t>20,000</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>24.57배 (PER)</t>
+          <t>25.48배 (PER)</t>
         </is>
       </c>
       <c r="G25" s="6" t="n">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>1396.29</v>
+        <v>1238</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>2392</v>
+        <v>2233</v>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>2026-06-23~24</t>
+          <t>2026-06-24~25</t>
         </is>
       </c>
       <c r="K25" s="6" t="n">
-        <v>3304.76</v>
+        <v>1510.57</v>
       </c>
       <c r="L25" s="6" t="inlineStr"/>
       <c r="M25" s="6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="N25" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="O25" s="6" t="inlineStr"/>
       <c r="P25" s="7" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>824</t>
         </is>
       </c>
       <c r="Q25" s="6" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
@@ -10057,75 +10061,71 @@
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>한국제16호스팩</t>
-        </is>
-      </c>
-      <c r="B26" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
+          <t>매드업</t>
+        </is>
+      </c>
+      <c r="B26" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>7,000~8,000</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>5,500,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>11,000</t>
-        </is>
-      </c>
-      <c r="F26" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
+          <t>16,000</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>24.57배 (PER)</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>8000</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>1364.09</v>
+        <v>1396.29</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>2089</v>
+        <v>2392</v>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>2026-06-22~06-23</t>
-        </is>
-      </c>
-      <c r="K26" s="6" t="inlineStr">
-        <is>
-          <t>1,274.77</t>
-        </is>
+          <t>2026-06-23~24</t>
+        </is>
+      </c>
+      <c r="K26" s="6" t="n">
+        <v>3304.76</v>
       </c>
       <c r="L26" s="6" t="inlineStr"/>
       <c r="M26" s="6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="N26" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="O26" s="6" t="inlineStr"/>
       <c r="P26" s="7" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>742</t>
         </is>
       </c>
       <c r="Q26" s="6" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
@@ -10137,51 +10137,53 @@
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>스트라드비젼</t>
-        </is>
-      </c>
-      <c r="B27" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>한국제16호스팩</t>
+        </is>
+      </c>
+      <c r="B27" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>12,000~14,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>7,000,000</t>
+          <t>5,500,000</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>84,000</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>37.45배 (PER)</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="n">
-        <v>12000</v>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="F27" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>381.3</v>
+        <v>1364.09</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>1604</v>
+        <v>2089</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>2026-06-18~06-19</t>
+          <t>2026-06-22~06-23</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>45.81</t>
+          <t>1,274.77</t>
         </is>
       </c>
       <c r="L27" s="6" t="inlineStr"/>
@@ -10192,13 +10194,13 @@
       </c>
       <c r="N27" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="O27" s="6" t="inlineStr"/>
       <c r="P27" s="7" t="inlineStr">
         <is>
-          <t>2,575</t>
+          <t>330</t>
         </is>
       </c>
       <c r="Q27" s="6" t="inlineStr">
@@ -10215,7 +10217,7 @@
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>져스텍</t>
+          <t>스트라드비젼</t>
         </is>
       </c>
       <c r="B28" s="18" t="inlineStr">
@@ -10225,32 +10227,32 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>10,500~12,500</t>
+          <t>12,000~14,000</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>1,600,000</t>
+          <t>7,000,000</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>84,000</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>26.82배 (PER)</t>
+          <t>37.45배 (PER)</t>
         </is>
       </c>
       <c r="G28" s="6" t="n">
-        <v>12500</v>
+        <v>12000</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>1294.99</v>
+        <v>381.3</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>2252</v>
+        <v>1604</v>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
@@ -10259,29 +10261,29 @@
       </c>
       <c r="K28" s="6" t="inlineStr">
         <is>
-          <t>2,783.89</t>
+          <t>45.81</t>
         </is>
       </c>
       <c r="L28" s="6" t="inlineStr"/>
       <c r="M28" s="6" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="N28" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="O28" s="6" t="inlineStr"/>
       <c r="P28" s="7" t="inlineStr">
         <is>
-          <t>1,164</t>
+          <t>2,575</t>
         </is>
       </c>
       <c r="Q28" s="6" t="inlineStr">
         <is>
-          <t>5.65%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
@@ -10293,75 +10295,73 @@
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>메리츠제2호스팩</t>
-        </is>
-      </c>
-      <c r="B29" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
+          <t>져스텍</t>
+        </is>
+      </c>
+      <c r="B29" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>10,500~12,500</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>7,000,000</t>
+          <t>1,600,000</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>14,000</t>
-        </is>
-      </c>
-      <c r="F29" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>26.82배 (PER)</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>12500</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>1087.58</v>
+        <v>1294.99</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>1798</v>
+        <v>2252</v>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09~06-10</t>
+          <t>2026-06-18~06-19</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>1,338.66</t>
+          <t>2,783.89</t>
         </is>
       </c>
       <c r="L29" s="6" t="inlineStr"/>
       <c r="M29" s="6" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="N29" s="6" t="inlineStr">
         <is>
-          <t>메리츠</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="O29" s="6" t="inlineStr"/>
       <c r="P29" s="7" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>1,164</t>
         </is>
       </c>
       <c r="Q29" s="6" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>5.65%</t>
         </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
@@ -10373,77 +10373,75 @@
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>피스피스스튜디오</t>
-        </is>
-      </c>
-      <c r="B30" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>메리츠제2호스팩</t>
+        </is>
+      </c>
+      <c r="B30" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>19,000~21,500</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>2,272,637</t>
+          <t>7,000,000</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>48,862</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>21.48배 (PER)</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="n">
-        <v>21500</v>
+          <t>14,000</t>
+        </is>
+      </c>
+      <c r="F30" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
       </c>
       <c r="H30" s="6" t="n">
-        <v>847.76</v>
+        <v>1087.58</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>2329</v>
+        <v>1798</v>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>2026-05-26~05-27</t>
+          <t>2026-06-09~06-10</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>1,191.15</t>
+          <t>1,338.66</t>
         </is>
       </c>
       <c r="L30" s="6" t="inlineStr"/>
       <c r="M30" s="6" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="N30" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
-        </is>
-      </c>
-      <c r="O30" s="6" t="inlineStr">
-        <is>
-          <t>NH</t>
-        </is>
-      </c>
+          <t>메리츠</t>
+        </is>
+      </c>
+      <c r="O30" s="6" t="inlineStr"/>
       <c r="P30" s="7" t="inlineStr">
         <is>
-          <t>1,994</t>
+          <t>245</t>
         </is>
       </c>
       <c r="Q30" s="6" t="inlineStr">
         <is>
-          <t>4.00%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
@@ -10455,75 +10453,77 @@
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>대신밸런스제20호스팩</t>
-        </is>
-      </c>
-      <c r="B31" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
+          <t>피스피스스튜디오</t>
+        </is>
+      </c>
+      <c r="B31" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>19,000~21,500</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>6,500,000</t>
+          <t>2,272,637</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>13,000</t>
-        </is>
-      </c>
-      <c r="F31" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
+          <t>48,862</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>21.48배 (PER)</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>21500</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>1327.13</v>
+        <v>847.76</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>2194</v>
+        <v>2329</v>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>2026-05-22~05-25</t>
+          <t>2026-05-26~05-27</t>
         </is>
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>1,486.88</t>
+          <t>1,191.15</t>
         </is>
       </c>
       <c r="L31" s="6" t="inlineStr"/>
       <c r="M31" s="6" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="N31" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
-        </is>
-      </c>
-      <c r="O31" s="6" t="inlineStr"/>
+          <t>미래</t>
+        </is>
+      </c>
+      <c r="O31" s="6" t="inlineStr">
+        <is>
+          <t>NH</t>
+        </is>
+      </c>
       <c r="P31" s="7" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>1,994</t>
         </is>
       </c>
       <c r="Q31" s="6" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>4.00%</t>
         </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
@@ -10535,73 +10535,75 @@
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>마키나락스</t>
-        </is>
-      </c>
-      <c r="B32" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>대신밸런스제20호스팩</t>
+        </is>
+      </c>
+      <c r="B32" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>12,500~15,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>2,635,000</t>
+          <t>6,500,000</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>39,525</t>
-        </is>
-      </c>
-      <c r="F32" s="6" t="inlineStr">
-        <is>
-          <t>40.5배 (PER)</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="n">
-        <v>15000</v>
+          <t>13,000</t>
+        </is>
+      </c>
+      <c r="F32" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
       </c>
       <c r="H32" s="6" t="n">
-        <v>1196.08</v>
+        <v>1327.13</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>2427</v>
+        <v>2194</v>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>2026-05-11~05-12</t>
+          <t>2026-05-22~05-25</t>
         </is>
       </c>
       <c r="K32" s="6" t="inlineStr">
         <is>
-          <t>2,807.79</t>
+          <t>1,486.88</t>
         </is>
       </c>
       <c r="L32" s="6" t="inlineStr"/>
       <c r="M32" s="6" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="N32" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="O32" s="6" t="inlineStr"/>
       <c r="P32" s="7" t="inlineStr">
         <is>
-          <t>2,026</t>
+          <t>390</t>
         </is>
       </c>
       <c r="Q32" s="6" t="inlineStr">
         <is>
-          <t>5.00%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="R32" s="6" t="inlineStr">
@@ -10613,7 +10615,7 @@
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>폴레드</t>
+          <t>마키나락스</t>
         </is>
       </c>
       <c r="B33" s="18" t="inlineStr">
@@ -10623,63 +10625,63 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>4,100~5,000</t>
+          <t>12,500~15,000</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>2,600,000</t>
+          <t>2,635,000</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>13,000</t>
+          <t>39,525</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>19.05배 (PER)</t>
+          <t>40.5배 (PER)</t>
         </is>
       </c>
       <c r="G33" s="6" t="n">
-        <v>5000</v>
+        <v>15000</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>1486.66</v>
+        <v>1196.08</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>2372</v>
+        <v>2427</v>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>2026-05-04~05-05</t>
+          <t>2026-05-11~05-12</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>3,169.86</t>
+          <t>2,807.79</t>
         </is>
       </c>
       <c r="L33" s="6" t="inlineStr"/>
       <c r="M33" s="6" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="N33" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="O33" s="6" t="inlineStr"/>
       <c r="P33" s="7" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>2,026</t>
         </is>
       </c>
       <c r="Q33" s="6" t="inlineStr">
         <is>
-          <t>4.03%</t>
+          <t>5.00%</t>
         </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
@@ -10691,7 +10693,7 @@
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>코스모로보틱스</t>
+          <t>폴레드</t>
         </is>
       </c>
       <c r="B34" s="18" t="inlineStr">
@@ -10701,67 +10703,63 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>5,300~6,000</t>
+          <t>4,100~5,000</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>4,170,000</t>
+          <t>2,600,000</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>25,020</t>
+          <t>13,000</t>
         </is>
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>47.45배 (PER)</t>
+          <t>19.05배 (PER)</t>
         </is>
       </c>
       <c r="G34" s="6" t="n">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>1140.11</v>
+        <v>1486.66</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>2257</v>
+        <v>2372</v>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>2026-04-27~04-28</t>
+          <t>2026-05-04~05-05</t>
         </is>
       </c>
       <c r="K34" s="6" t="inlineStr">
         <is>
-          <t>2,013.80</t>
+          <t>3,169.86</t>
         </is>
       </c>
       <c r="L34" s="6" t="inlineStr"/>
       <c r="M34" s="6" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="N34" s="6" t="inlineStr">
         <is>
-          <t>유진</t>
-        </is>
-      </c>
-      <c r="O34" s="6" t="inlineStr">
-        <is>
           <t>NH</t>
         </is>
       </c>
+      <c r="O34" s="6" t="inlineStr"/>
       <c r="P34" s="7" t="inlineStr">
         <is>
-          <t>1,289</t>
+          <t>540</t>
         </is>
       </c>
       <c r="Q34" s="6" t="inlineStr">
         <is>
-          <t>3.78%</t>
+          <t>4.03%</t>
         </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
@@ -10773,75 +10771,77 @@
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>신한스팩18호</t>
-        </is>
-      </c>
-      <c r="B35" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
+          <t>코스모로보틱스</t>
+        </is>
+      </c>
+      <c r="B35" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>5,300~6,000</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>4,170,000</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>10,000</t>
-        </is>
-      </c>
-      <c r="F35" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="G35" s="6" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
+          <t>25,020</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>47.45배 (PER)</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>6000</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>1388.6</v>
+        <v>1140.11</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>2044</v>
+        <v>2257</v>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>2026-04-20~04-21</t>
+          <t>2026-04-27~04-28</t>
         </is>
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>1,601.36</t>
+          <t>2,013.80</t>
         </is>
       </c>
       <c r="L35" s="6" t="inlineStr"/>
       <c r="M35" s="6" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="N35" s="6" t="inlineStr">
         <is>
-          <t>신한</t>
-        </is>
-      </c>
-      <c r="O35" s="6" t="inlineStr"/>
+          <t>유진</t>
+        </is>
+      </c>
+      <c r="O35" s="6" t="inlineStr">
+        <is>
+          <t>NH</t>
+        </is>
+      </c>
       <c r="P35" s="7" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>1,289</t>
         </is>
       </c>
       <c r="Q35" s="6" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>3.78%</t>
         </is>
       </c>
       <c r="R35" s="6" t="inlineStr">
@@ -10853,42 +10853,44 @@
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>채비</t>
-        </is>
-      </c>
-      <c r="B36" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>신한스팩18호</t>
+        </is>
+      </c>
+      <c r="B36" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>12,300~15,300</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>9,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>110,700</t>
-        </is>
-      </c>
-      <c r="F36" s="6" t="inlineStr">
-        <is>
-          <t>24.0배 (EV/EBITDA)</t>
-        </is>
-      </c>
-      <c r="G36" s="6" t="n">
-        <v>12300</v>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="F36" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
       </c>
       <c r="H36" s="6" t="n">
-        <v>55.23</v>
+        <v>1388.6</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>751</v>
+        <v>2044</v>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
@@ -10897,33 +10899,29 @@
       </c>
       <c r="K36" s="6" t="inlineStr">
         <is>
-          <t>302.11</t>
+          <t>1,601.36</t>
         </is>
       </c>
       <c r="L36" s="6" t="inlineStr"/>
       <c r="M36" s="6" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="N36" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
-        </is>
-      </c>
-      <c r="O36" s="6" t="inlineStr">
-        <is>
-          <t>삼성</t>
-        </is>
-      </c>
+          <t>신한</t>
+        </is>
+      </c>
+      <c r="O36" s="6" t="inlineStr"/>
       <c r="P36" s="7" t="inlineStr">
         <is>
-          <t>3,384</t>
+          <t>350</t>
         </is>
       </c>
       <c r="Q36" s="6" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="R36" s="6" t="inlineStr">
@@ -10935,75 +10933,77 @@
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>키움히어로스펙2호</t>
-        </is>
-      </c>
-      <c r="B37" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
+          <t>채비</t>
+        </is>
+      </c>
+      <c r="B37" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>12,300~15,300</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>6,000,000</t>
+          <t>9,000,000</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>12,000</t>
-        </is>
-      </c>
-      <c r="F37" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="G37" s="6" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
+          <t>110,700</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>24.0배 (EV/EBITDA)</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>12300</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>1271.12</v>
+        <v>55.23</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>2054</v>
+        <v>751</v>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>2026-04-14~04-15</t>
+          <t>2026-04-20~04-21</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>1,727.59</t>
+          <t>302.11</t>
         </is>
       </c>
       <c r="L37" s="6" t="inlineStr"/>
       <c r="M37" s="6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="N37" s="6" t="inlineStr">
         <is>
-          <t>키움</t>
-        </is>
-      </c>
-      <c r="O37" s="6" t="inlineStr"/>
+          <t>KB</t>
+        </is>
+      </c>
+      <c r="O37" s="6" t="inlineStr">
+        <is>
+          <t>삼성</t>
+        </is>
+      </c>
       <c r="P37" s="7" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>3,384</t>
         </is>
       </c>
       <c r="Q37" s="6" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="R37" s="6" t="inlineStr">
@@ -11015,7 +11015,7 @@
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>교보스팩20호</t>
+          <t>키움히어로스펙2호</t>
         </is>
       </c>
       <c r="B38" s="19" t="inlineStr">
@@ -11030,12 +11030,12 @@
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>5,400,000</t>
+          <t>6,000,000</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>10,800</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="F38" s="19" t="inlineStr">
@@ -11049,30 +11049,30 @@
         </is>
       </c>
       <c r="H38" s="6" t="n">
-        <v>1196.99</v>
+        <v>1271.12</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>1855</v>
+        <v>2054</v>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>2026-03-23~03-24</t>
+          <t>2026-04-14~04-15</t>
         </is>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
-          <t>747.00</t>
+          <t>1,727.59</t>
         </is>
       </c>
       <c r="L38" s="6" t="inlineStr"/>
       <c r="M38" s="6" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="N38" s="6" t="inlineStr">
         <is>
-          <t>교보</t>
+          <t>키움</t>
         </is>
       </c>
       <c r="O38" s="6" t="inlineStr"/>
@@ -11083,7 +11083,7 @@
       </c>
       <c r="Q38" s="6" t="inlineStr">
         <is>
-          <t>2.78%</t>
+          <t>2.50%</t>
         </is>
       </c>
       <c r="R38" s="6" t="inlineStr">
@@ -11095,42 +11095,44 @@
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>인벤테라</t>
-        </is>
-      </c>
-      <c r="B39" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>교보스팩20호</t>
+        </is>
+      </c>
+      <c r="B39" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>12,100~16,600</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>1,180,000</t>
+          <t>5,400,000</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>19,588</t>
-        </is>
-      </c>
-      <c r="F39" s="6" t="inlineStr">
-        <is>
-          <t>24.34배 (PER)</t>
-        </is>
-      </c>
-      <c r="G39" s="6" t="n">
-        <v>16600</v>
+          <t>10,800</t>
+        </is>
+      </c>
+      <c r="F39" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
       </c>
       <c r="H39" s="6" t="n">
-        <v>1328.82</v>
+        <v>1196.99</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>2309</v>
+        <v>1855</v>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
@@ -11139,7 +11141,7 @@
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>1,913.00</t>
+          <t>747.00</t>
         </is>
       </c>
       <c r="L39" s="6" t="inlineStr"/>
@@ -11150,18 +11152,18 @@
       </c>
       <c r="N39" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>교보</t>
         </is>
       </c>
       <c r="O39" s="6" t="inlineStr"/>
       <c r="P39" s="7" t="inlineStr">
         <is>
-          <t>1,211</t>
+          <t>300</t>
         </is>
       </c>
       <c r="Q39" s="6" t="inlineStr">
         <is>
-          <t>6.00%</t>
+          <t>2.78%</t>
         </is>
       </c>
       <c r="R39" s="6" t="inlineStr">
@@ -11173,75 +11175,73 @@
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>신한스팩17호</t>
-        </is>
-      </c>
-      <c r="B40" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
+          <t>인벤테라</t>
+        </is>
+      </c>
+      <c r="B40" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>12,100~16,600</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>1,180,000</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>10,000</t>
-        </is>
-      </c>
-      <c r="F40" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="G40" s="6" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
+          <t>19,588</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>24.34배 (PER)</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="n">
+        <v>16600</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>1343.8</v>
+        <v>1328.82</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>2022</v>
+        <v>2309</v>
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>2026-03-19~03-20</t>
+          <t>2026-03-23~03-24</t>
         </is>
       </c>
       <c r="K40" s="6" t="inlineStr">
         <is>
-          <t>1,403.74</t>
+          <t>1,913.00</t>
         </is>
       </c>
       <c r="L40" s="6" t="inlineStr"/>
       <c r="M40" s="6" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="N40" s="6" t="inlineStr">
         <is>
-          <t>신한</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="O40" s="6" t="inlineStr"/>
       <c r="P40" s="7" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>1,211</t>
         </is>
       </c>
       <c r="Q40" s="6" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>6.00%</t>
         </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
@@ -11253,42 +11253,44 @@
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>리센스메디컬</t>
-        </is>
-      </c>
-      <c r="B41" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>신한스팩17호</t>
+        </is>
+      </c>
+      <c r="B41" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>9,000~11,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>1,400,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>15,400</t>
-        </is>
-      </c>
-      <c r="F41" s="6" t="inlineStr">
-        <is>
-          <t>31.33배 (PER)</t>
-        </is>
-      </c>
-      <c r="G41" s="6" t="n">
-        <v>11000</v>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="F41" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
       </c>
       <c r="H41" s="6" t="n">
-        <v>1352.63</v>
+        <v>1343.8</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>2261</v>
+        <v>2022</v>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
@@ -11297,33 +11299,29 @@
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>2,097.68</t>
+          <t>1,403.74</t>
         </is>
       </c>
       <c r="L41" s="6" t="inlineStr"/>
       <c r="M41" s="6" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="N41" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
-        </is>
-      </c>
-      <c r="O41" s="6" t="inlineStr">
-        <is>
-          <t>KB</t>
-        </is>
-      </c>
+          <t>신한</t>
+        </is>
+      </c>
+      <c r="O41" s="6" t="inlineStr"/>
       <c r="P41" s="7" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>350</t>
         </is>
       </c>
       <c r="Q41" s="6" t="inlineStr">
         <is>
-          <t>5.77%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
@@ -11335,75 +11333,77 @@
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>NH스팩33호</t>
-        </is>
-      </c>
-      <c r="B42" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
+          <t>리센스메디컬</t>
+        </is>
+      </c>
+      <c r="B42" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>9,000~11,000</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>6,350,000</t>
+          <t>1,400,000</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>12,700</t>
-        </is>
-      </c>
-      <c r="F42" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="G42" s="6" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
+          <t>15,400</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>31.33배 (PER)</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>11000</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>1228.71</v>
+        <v>1352.63</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>2058</v>
+        <v>2261</v>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>2026-03-17~03-18</t>
+          <t>2026-03-19~03-20</t>
         </is>
       </c>
       <c r="K42" s="6" t="inlineStr">
         <is>
-          <t>569.27</t>
+          <t>2,097.68</t>
         </is>
       </c>
       <c r="L42" s="6" t="inlineStr"/>
       <c r="M42" s="6" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="N42" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
-        </is>
-      </c>
-      <c r="O42" s="6" t="inlineStr"/>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="O42" s="6" t="inlineStr">
+        <is>
+          <t>KB</t>
+        </is>
+      </c>
       <c r="P42" s="7" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>916</t>
         </is>
       </c>
       <c r="Q42" s="6" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>5.77%</t>
         </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
@@ -11415,73 +11415,75 @@
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>메쥬</t>
-        </is>
-      </c>
-      <c r="B43" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>NH스팩33호</t>
+        </is>
+      </c>
+      <c r="B43" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>16,700~21,600</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>1,345,000</t>
+          <t>6,350,000</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>29,052</t>
-        </is>
-      </c>
-      <c r="F43" s="6" t="inlineStr">
-        <is>
-          <t>20.66배 (PER)</t>
-        </is>
-      </c>
-      <c r="G43" s="6" t="n">
-        <v>21600</v>
+          <t>12,700</t>
+        </is>
+      </c>
+      <c r="F43" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
       </c>
       <c r="H43" s="6" t="n">
-        <v>1108.93</v>
+        <v>1228.71</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>2320</v>
+        <v>2058</v>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>2026-03-16~03-17</t>
+          <t>2026-03-17~03-18</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>2,428.25</t>
+          <t>569.27</t>
         </is>
       </c>
       <c r="L43" s="6" t="inlineStr"/>
       <c r="M43" s="6" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="N43" s="6" t="inlineStr">
         <is>
-          <t>신한</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="O43" s="6" t="inlineStr"/>
       <c r="P43" s="7" t="inlineStr">
         <is>
-          <t>1,496</t>
+          <t>381</t>
         </is>
       </c>
       <c r="Q43" s="6" t="inlineStr">
         <is>
-          <t>5.00%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
@@ -11493,7 +11495,7 @@
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>한패스</t>
+          <t>메쥬</t>
         </is>
       </c>
       <c r="B44" s="18" t="inlineStr">
@@ -11503,32 +11505,32 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>17,000~19,000</t>
+          <t>16,700~21,600</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>1,100,000</t>
+          <t>1,345,000</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>20,900</t>
+          <t>29,052</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>29.09배 (PER)</t>
+          <t>20.66배 (PER)</t>
         </is>
       </c>
       <c r="G44" s="6" t="n">
-        <v>19000</v>
+        <v>21600</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>1172.59</v>
+        <v>1108.93</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>2229</v>
+        <v>2320</v>
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
@@ -11537,29 +11539,29 @@
       </c>
       <c r="K44" s="6" t="inlineStr">
         <is>
-          <t>1,673.04</t>
+          <t>2,428.25</t>
         </is>
       </c>
       <c r="L44" s="6" t="inlineStr"/>
       <c r="M44" s="6" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="N44" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>신한</t>
         </is>
       </c>
       <c r="O44" s="6" t="inlineStr"/>
       <c r="P44" s="7" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>1,496</t>
         </is>
       </c>
       <c r="Q44" s="6" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>5.00%</t>
         </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
@@ -11571,7 +11573,7 @@
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>아이엠바이오로직스</t>
+          <t>한패스</t>
         </is>
       </c>
       <c r="B45" s="18" t="inlineStr">
@@ -11581,47 +11583,47 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>19,000~26,000</t>
+          <t>17,000~19,000</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>1,100,000</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>52,000</t>
+          <t>20,900</t>
         </is>
       </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>21.46배 (PER)</t>
+          <t>29.09배 (PER)</t>
         </is>
       </c>
       <c r="G45" s="6" t="n">
-        <v>26000</v>
+        <v>19000</v>
       </c>
       <c r="H45" s="6" t="n">
-        <v>839.23</v>
+        <v>1172.59</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>2333</v>
+        <v>2229</v>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11~03-12</t>
+          <t>2026-03-16~03-17</t>
         </is>
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>1,806.00</t>
+          <t>1,673.04</t>
         </is>
       </c>
       <c r="L45" s="6" t="inlineStr"/>
       <c r="M45" s="6" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="N45" s="6" t="inlineStr">
@@ -11632,12 +11634,12 @@
       <c r="O45" s="6" t="inlineStr"/>
       <c r="P45" s="7" t="inlineStr">
         <is>
-          <t>2,650</t>
+          <t>753</t>
         </is>
       </c>
       <c r="Q45" s="6" t="inlineStr">
         <is>
-          <t>5.00%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="R45" s="6" t="inlineStr">
@@ -11649,7 +11651,7 @@
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>카나프테라퓨틱스</t>
+          <t>아이엠바이오로직스</t>
         </is>
       </c>
       <c r="B46" s="18" t="inlineStr">
@@ -11659,7 +11661,7 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>16,000~20,000</t>
+          <t>19,000~26,000</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
@@ -11669,37 +11671,37 @@
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>40,000</t>
+          <t>52,000</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>23.59배 (PER)</t>
+          <t>21.46배 (PER)</t>
         </is>
       </c>
       <c r="G46" s="6" t="n">
-        <v>20000</v>
+        <v>26000</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>962.1</v>
+        <v>839.23</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>2327</v>
+        <v>2333</v>
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
-          <t>2026-03-05~03-06</t>
+          <t>2026-03-11~03-12</t>
         </is>
       </c>
       <c r="K46" s="6" t="inlineStr">
         <is>
-          <t>1,899.29</t>
+          <t>1,806.00</t>
         </is>
       </c>
       <c r="L46" s="6" t="inlineStr"/>
       <c r="M46" s="6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="N46" s="6" t="inlineStr">
@@ -11710,7 +11712,7 @@
       <c r="O46" s="6" t="inlineStr"/>
       <c r="P46" s="7" t="inlineStr">
         <is>
-          <t>2,050</t>
+          <t>2,650</t>
         </is>
       </c>
       <c r="Q46" s="6" t="inlineStr">
@@ -11727,7 +11729,7 @@
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>액스비스</t>
+          <t>카나프테라퓨틱스</t>
         </is>
       </c>
       <c r="B47" s="18" t="inlineStr">
@@ -11737,63 +11739,63 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>10,100~11,500</t>
+          <t>16,000~20,000</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>2,300,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>26,450</t>
+          <t>40,000</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>27.60배 (PER)</t>
+          <t>23.59배 (PER)</t>
         </is>
       </c>
       <c r="G47" s="6" t="n">
-        <v>11500</v>
+        <v>20000</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>1124.21</v>
+        <v>962.1</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>2411</v>
+        <v>2327</v>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>2026-02-23~02-24</t>
+          <t>2026-03-05~03-06</t>
         </is>
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>1,960.87</t>
+          <t>1,899.29</t>
         </is>
       </c>
       <c r="L47" s="6" t="inlineStr"/>
       <c r="M47" s="6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="N47" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="O47" s="6" t="inlineStr"/>
       <c r="P47" s="7" t="inlineStr">
         <is>
-          <t>1,090</t>
+          <t>2,050</t>
         </is>
       </c>
       <c r="Q47" s="6" t="inlineStr">
         <is>
-          <t>4.00%</t>
+          <t>5.00%</t>
         </is>
       </c>
       <c r="R47" s="6" t="inlineStr">
@@ -11805,7 +11807,7 @@
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>에스팀</t>
+          <t>액스비스</t>
         </is>
       </c>
       <c r="B48" s="18" t="inlineStr">
@@ -11815,32 +11817,32 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>7,000~8,500</t>
+          <t>10,100~11,500</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>1,800,000</t>
+          <t>2,300,000</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>15,300</t>
+          <t>26,450</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>17.71배 (EV/EBITDA)</t>
+          <t>27.60배 (PER)</t>
         </is>
       </c>
       <c r="G48" s="6" t="n">
-        <v>8500</v>
+        <v>11500</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>1334.91</v>
+        <v>1124.21</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>2263</v>
+        <v>2411</v>
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
@@ -11849,29 +11851,29 @@
       </c>
       <c r="K48" s="6" t="inlineStr">
         <is>
-          <t>1,334.91</t>
+          <t>1,960.87</t>
         </is>
       </c>
       <c r="L48" s="6" t="inlineStr"/>
       <c r="M48" s="6" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="N48" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="O48" s="6" t="inlineStr"/>
       <c r="P48" s="7" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>1,090</t>
         </is>
       </c>
       <c r="Q48" s="6" t="inlineStr">
         <is>
-          <t>5.00%</t>
+          <t>4.00%</t>
         </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
@@ -11883,7 +11885,7 @@
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>케이뱅크 (유가)</t>
+          <t>에스팀</t>
         </is>
       </c>
       <c r="B49" s="18" t="inlineStr">
@@ -11893,67 +11895,63 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>8,300~9,500</t>
+          <t>7,000~8,500</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>60,000,000</t>
+          <t>1,800,000</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>498,000</t>
+          <t>15,300</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>1.80배 (PBR)</t>
+          <t>17.71배 (EV/EBITDA)</t>
         </is>
       </c>
       <c r="G49" s="6" t="n">
-        <v>8300</v>
+        <v>8500</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>198.53</v>
+        <v>1334.91</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>2007</v>
+        <v>2263</v>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>2026-02-20~23</t>
+          <t>2026-02-23~02-24</t>
         </is>
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>134.59</t>
+          <t>1,334.91</t>
         </is>
       </c>
       <c r="L49" s="6" t="inlineStr"/>
       <c r="M49" s="6" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="N49" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
-        </is>
-      </c>
-      <c r="O49" s="6" t="inlineStr">
-        <is>
-          <t>삼성</t>
-        </is>
-      </c>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="O49" s="6" t="inlineStr"/>
       <c r="P49" s="7" t="inlineStr">
         <is>
-          <t>5,976</t>
+          <t>788</t>
         </is>
       </c>
       <c r="Q49" s="6" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>5.00%</t>
         </is>
       </c>
       <c r="R49" s="6" t="inlineStr">
@@ -11965,63 +11963,57 @@
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>세미티에스</t>
-        </is>
-      </c>
-      <c r="B50" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="C50" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="D50" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="E50" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="F50" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="G50" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="H50" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="I50" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="J50" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="K50" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
+          <t>케이뱅크 (유가)</t>
+        </is>
+      </c>
+      <c r="B50" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>8,300~9,500</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>60,000,000</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>498,000</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
+        <is>
+          <t>1.80배 (PBR)</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="n">
+        <v>8300</v>
+      </c>
+      <c r="H50" s="6" t="n">
+        <v>198.53</v>
+      </c>
+      <c r="I50" s="6" t="n">
+        <v>2007</v>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-20~23</t>
+        </is>
+      </c>
+      <c r="K50" s="6" t="inlineStr">
+        <is>
+          <t>134.59</t>
         </is>
       </c>
       <c r="L50" s="6" t="inlineStr"/>
       <c r="M50" s="6" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="N50" s="6" t="inlineStr">
@@ -12029,77 +12021,87 @@
           <t>NH</t>
         </is>
       </c>
-      <c r="O50" s="6" t="inlineStr"/>
-      <c r="P50" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="Q50" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
+      <c r="O50" s="6" t="inlineStr">
+        <is>
+          <t>삼성</t>
+        </is>
+      </c>
+      <c r="P50" s="7" t="inlineStr">
+        <is>
+          <t>5,976</t>
+        </is>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
-          <t>상장완료(스팩합병)</t>
+          <t>상장완료</t>
         </is>
       </c>
     </row>
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>덕양에너젠</t>
-        </is>
-      </c>
-      <c r="B51" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
-        <is>
-          <t>8,500~10,000</t>
-        </is>
-      </c>
-      <c r="D51" s="7" t="inlineStr">
-        <is>
-          <t>7,500,000</t>
-        </is>
-      </c>
-      <c r="E51" s="7" t="inlineStr">
-        <is>
-          <t>75,000</t>
-        </is>
-      </c>
-      <c r="F51" s="6" t="inlineStr">
-        <is>
-          <t>30.32배 (EV/EBITDA)</t>
-        </is>
-      </c>
-      <c r="G51" s="6" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H51" s="6" t="n">
-        <v>650.14</v>
-      </c>
-      <c r="I51" s="6" t="n">
-        <v>2324</v>
-      </c>
-      <c r="J51" s="6" t="inlineStr">
-        <is>
-          <t>2026-01-20~01-21</t>
-        </is>
-      </c>
-      <c r="K51" s="6" t="inlineStr">
-        <is>
-          <t>1,354.00</t>
+          <t>세미티에스</t>
+        </is>
+      </c>
+      <c r="B51" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="C51" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="D51" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="E51" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="F51" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="G51" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="H51" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="I51" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="J51" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="K51" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="L51" s="6" t="inlineStr"/>
       <c r="M51" s="6" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="N51" s="6" t="inlineStr">
@@ -12107,87 +12109,77 @@
           <t>NH</t>
         </is>
       </c>
-      <c r="O51" s="6" t="inlineStr">
-        <is>
-          <t>미래</t>
-        </is>
-      </c>
-      <c r="P51" s="7" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
-      </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>2.92%</t>
+      <c r="O51" s="6" t="inlineStr"/>
+      <c r="P51" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="Q51" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
-          <t>상장완료</t>
+          <t>상장완료(스팩합병)</t>
         </is>
       </c>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>케이피항공산업</t>
-        </is>
-      </c>
-      <c r="B52" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="C52" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="D52" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="E52" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="F52" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="G52" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="H52" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="I52" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="J52" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="K52" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
+          <t>덕양에너젠</t>
+        </is>
+      </c>
+      <c r="B52" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>8,500~10,000</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>7,500,000</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>75,000</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>30.32배 (EV/EBITDA)</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="n">
+        <v>10000</v>
+      </c>
+      <c r="H52" s="6" t="n">
+        <v>650.14</v>
+      </c>
+      <c r="I52" s="6" t="n">
+        <v>2324</v>
+      </c>
+      <c r="J52" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-20~01-21</t>
+        </is>
+      </c>
+      <c r="K52" s="6" t="inlineStr">
+        <is>
+          <t>1,354.00</t>
         </is>
       </c>
       <c r="L52" s="6" t="inlineStr"/>
       <c r="M52" s="6" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="N52" s="6" t="inlineStr">
@@ -12195,27 +12187,31 @@
           <t>NH</t>
         </is>
       </c>
-      <c r="O52" s="6" t="inlineStr"/>
-      <c r="P52" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="Q52" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
+      <c r="O52" s="6" t="inlineStr">
+        <is>
+          <t>미래</t>
+        </is>
+      </c>
+      <c r="P52" s="7" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>2.92%</t>
         </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
-          <t>상장완료(스팩합병)</t>
+          <t>상장완료</t>
         </is>
       </c>
     </row>
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>삼성스팩13호</t>
+          <t>케이피항공산업</t>
         </is>
       </c>
       <c r="B53" s="19" t="inlineStr">
@@ -12223,19 +12219,19 @@
           <t>해당없음</t>
         </is>
       </c>
-      <c r="C53" s="6" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
-      </c>
-      <c r="D53" s="7" t="inlineStr">
-        <is>
-          <t>6,000,000</t>
-        </is>
-      </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>12,000</t>
+      <c r="C53" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="D53" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="E53" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="F53" s="19" t="inlineStr">
@@ -12243,154 +12239,162 @@
           <t>해당없음</t>
         </is>
       </c>
-      <c r="G53" s="6" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
-      </c>
-      <c r="H53" s="6" t="n">
-        <v>1159.11</v>
-      </c>
-      <c r="I53" s="6" t="n">
-        <v>1892</v>
-      </c>
-      <c r="J53" s="6" t="inlineStr">
-        <is>
-          <t>2026-01-12~01-13</t>
-        </is>
-      </c>
-      <c r="K53" s="6" t="inlineStr">
-        <is>
-          <t>1,870.40</t>
+      <c r="G53" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="H53" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="I53" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="J53" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="K53" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="L53" s="6" t="inlineStr"/>
       <c r="M53" s="6" t="inlineStr">
         <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="N53" s="6" t="inlineStr">
+        <is>
+          <t>NH</t>
+        </is>
+      </c>
+      <c r="O53" s="6" t="inlineStr"/>
+      <c r="P53" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="Q53" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>상장완료(스팩합병)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="30" customHeight="1">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>삼성스팩13호</t>
+        </is>
+      </c>
+      <c r="B54" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>6,000,000</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="F54" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="H54" s="6" t="n">
+        <v>1159.11</v>
+      </c>
+      <c r="I54" s="6" t="n">
+        <v>1892</v>
+      </c>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-12~01-13</t>
+        </is>
+      </c>
+      <c r="K54" s="6" t="inlineStr">
+        <is>
+          <t>1,870.40</t>
+        </is>
+      </c>
+      <c r="L54" s="6" t="inlineStr"/>
+      <c r="M54" s="6" t="inlineStr">
+        <is>
           <t>2026-01-21</t>
         </is>
       </c>
-      <c r="N53" s="6" t="inlineStr">
+      <c r="N54" s="6" t="inlineStr">
         <is>
           <t>삼성</t>
         </is>
       </c>
-      <c r="O53" s="6" t="inlineStr"/>
-      <c r="P53" s="7" t="inlineStr">
+      <c r="O54" s="6" t="inlineStr"/>
+      <c r="P54" s="7" t="inlineStr">
         <is>
           <t>360</t>
         </is>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
+      <c r="Q54" s="6" t="inlineStr">
         <is>
           <t>3.00%</t>
         </is>
       </c>
-      <c r="R53" s="6" t="inlineStr">
+      <c r="R54" s="6" t="inlineStr">
         <is>
           <t>상장완료</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="22" customHeight="1">
-      <c r="A55" s="3" t="inlineStr">
-        <is>
-          <t>■ 공모 진행 (예심 승인법인)  (32건)</t>
-        </is>
-      </c>
-      <c r="B55" s="4" t="n"/>
-      <c r="C55" s="4" t="n"/>
-      <c r="D55" s="4" t="n"/>
-      <c r="E55" s="4" t="n"/>
-      <c r="F55" s="4" t="n"/>
-      <c r="G55" s="4" t="n"/>
-      <c r="H55" s="4" t="n"/>
-      <c r="I55" s="4" t="n"/>
-      <c r="J55" s="4" t="n"/>
-      <c r="K55" s="4" t="n"/>
-      <c r="L55" s="4" t="n"/>
-      <c r="M55" s="4" t="n"/>
-      <c r="N55" s="4" t="n"/>
-      <c r="O55" s="4" t="n"/>
-      <c r="P55" s="4" t="n"/>
-      <c r="Q55" s="4" t="n"/>
-      <c r="R55" s="4" t="n"/>
-    </row>
-    <row r="56" ht="30" customHeight="1">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>브릴스</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>08-31~09-04</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>16,500~19,500</t>
-        </is>
-      </c>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>1,200,000</t>
-        </is>
-      </c>
-      <c r="E56" s="7" t="inlineStr">
-        <is>
-          <t>23,400,000,000</t>
-        </is>
-      </c>
-      <c r="F56" s="6" t="inlineStr">
-        <is>
-          <t>13.44 (PSR)</t>
-        </is>
-      </c>
-      <c r="G56" s="6" t="inlineStr">
-        <is>
-          <t>19,500</t>
-        </is>
-      </c>
-      <c r="H56" s="6" t="n">
-        <v>1187.74</v>
-      </c>
-      <c r="I56" s="6" t="n">
-        <v>2181</v>
-      </c>
-      <c r="J56" s="6" t="inlineStr">
-        <is>
-          <t>09-08~09-09</t>
-        </is>
-      </c>
-      <c r="K56" s="6" t="inlineStr">
-        <is>
-          <t>4,418.97</t>
-        </is>
-      </c>
-      <c r="L56" s="6" t="inlineStr"/>
-      <c r="M56" s="6" t="inlineStr"/>
-      <c r="N56" s="6" t="inlineStr">
-        <is>
-          <t>아이비케이투자증권</t>
-        </is>
-      </c>
-      <c r="O56" s="6" t="inlineStr"/>
-      <c r="P56" s="7" t="inlineStr">
-        <is>
-          <t>713,790,000</t>
-        </is>
-      </c>
-      <c r="Q56" s="6" t="inlineStr">
-        <is>
-          <t>3.5%</t>
-        </is>
-      </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>청약완료·상장대기</t>
-        </is>
-      </c>
+    <row r="56" ht="22" customHeight="1">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>■ 공모 진행 (예심 승인법인)  (31건)</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="n"/>
+      <c r="C56" s="4" t="n"/>
+      <c r="D56" s="4" t="n"/>
+      <c r="E56" s="4" t="n"/>
+      <c r="F56" s="4" t="n"/>
+      <c r="G56" s="4" t="n"/>
+      <c r="H56" s="4" t="n"/>
+      <c r="I56" s="4" t="n"/>
+      <c r="J56" s="4" t="n"/>
+      <c r="K56" s="4" t="n"/>
+      <c r="L56" s="4" t="n"/>
+      <c r="M56" s="4" t="n"/>
+      <c r="N56" s="4" t="n"/>
+      <c r="O56" s="4" t="n"/>
+      <c r="P56" s="4" t="n"/>
+      <c r="Q56" s="4" t="n"/>
+      <c r="R56" s="4" t="n"/>
     </row>
     <row r="57" ht="30" customHeight="1">
       <c r="A57" s="6" t="inlineStr">
@@ -12811,32 +12815,32 @@
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>에스케이증권제14호기업인수목적</t>
+          <t>유캐스트</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>10-12~10-13</t>
-        </is>
-      </c>
-      <c r="C63" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>10-07~10-14</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>21,000~26,000</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>6,500,000</t>
+          <t>800,000</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>13,000,000,000</t>
-        </is>
-      </c>
-      <c r="F63" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>16,800,000,000</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
+        <is>
+          <t>17.97배 (PER)</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr"/>
@@ -12844,26 +12848,26 @@
       <c r="I63" s="6" t="inlineStr"/>
       <c r="J63" s="6" t="inlineStr">
         <is>
-          <t>10-15~10-16</t>
+          <t>10-19~10-20</t>
         </is>
       </c>
       <c r="K63" s="6" t="inlineStr"/>
       <c r="L63" s="6" t="inlineStr"/>
       <c r="M63" s="6" t="inlineStr"/>
-      <c r="N63" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="N63" s="6" t="inlineStr">
+        <is>
+          <t>유진투자증권</t>
         </is>
       </c>
       <c r="O63" s="6" t="inlineStr"/>
-      <c r="P63" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P63" s="7" t="inlineStr">
+        <is>
+          <t>1,181,280,000</t>
         </is>
       </c>
       <c r="Q63" s="6" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="R63" s="6" t="inlineStr">
@@ -12875,32 +12879,32 @@
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>크리에이츠</t>
+          <t>에스케이증권제14호기업인수목적</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>10-12~10-16</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>15,000~18,000</t>
+          <t>10-12~10-13</t>
+        </is>
+      </c>
+      <c r="C64" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>1,400,000</t>
+          <t>6,500,000</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>21,000,000,000</t>
-        </is>
-      </c>
-      <c r="F64" s="6" t="inlineStr">
-        <is>
-          <t>19.15배 (PER)</t>
+          <t>13,000,000,000</t>
+        </is>
+      </c>
+      <c r="F64" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr"/>
@@ -12908,26 +12912,26 @@
       <c r="I64" s="6" t="inlineStr"/>
       <c r="J64" s="6" t="inlineStr">
         <is>
-          <t>10-20~10-21</t>
+          <t>10-15~10-16</t>
         </is>
       </c>
       <c r="K64" s="6" t="inlineStr"/>
       <c r="L64" s="6" t="inlineStr"/>
       <c r="M64" s="6" t="inlineStr"/>
-      <c r="N64" s="6" t="inlineStr">
-        <is>
-          <t>삼성증권</t>
+      <c r="N64" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="O64" s="6" t="inlineStr"/>
-      <c r="P64" s="7" t="inlineStr">
-        <is>
-          <t>865,200,000</t>
+      <c r="P64" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="Q64" s="6" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="R64" s="6" t="inlineStr">
@@ -12939,32 +12943,32 @@
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>래블업</t>
+          <t>크리에이츠</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>10-13~10-19</t>
+          <t>10-12~10-16</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>19,000~22,000</t>
+          <t>15,000~18,000</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>2,180,000</t>
+          <t>1,400,000</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>41,420,000,000</t>
+          <t>21,000,000,000</t>
         </is>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>33.6배 (PER)</t>
+          <t>19.15배 (PER)</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr"/>
@@ -12972,7 +12976,7 @@
       <c r="I65" s="6" t="inlineStr"/>
       <c r="J65" s="6" t="inlineStr">
         <is>
-          <t>10-22~10-23</t>
+          <t>10-20~10-21</t>
         </is>
       </c>
       <c r="K65" s="6" t="inlineStr"/>
@@ -12980,18 +12984,18 @@
       <c r="M65" s="6" t="inlineStr"/>
       <c r="N65" s="6" t="inlineStr">
         <is>
-          <t>NH투자증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="O65" s="6" t="inlineStr"/>
       <c r="P65" s="7" t="inlineStr">
         <is>
-          <t>1,908,899,000</t>
+          <t>865,200,000</t>
         </is>
       </c>
       <c r="Q65" s="6" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="R65" s="6" t="inlineStr">
@@ -13003,32 +13007,32 @@
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>엠비디</t>
+          <t>래블업</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>10-16~10-22</t>
+          <t>10-13~10-19</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>9,600~11,700</t>
+          <t>19,000~22,000</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>2,180,000</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>19,200,000,000</t>
+          <t>41,420,000,000</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>26.87배 (PER)</t>
+          <t>33.6배 (PER)</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr"/>
@@ -13036,7 +13040,7 @@
       <c r="I66" s="6" t="inlineStr"/>
       <c r="J66" s="6" t="inlineStr">
         <is>
-          <t>10-28~10-29</t>
+          <t>10-22~10-23</t>
         </is>
       </c>
       <c r="K66" s="6" t="inlineStr"/>
@@ -13044,18 +13048,18 @@
       <c r="M66" s="6" t="inlineStr"/>
       <c r="N66" s="6" t="inlineStr">
         <is>
-          <t>하나증권</t>
+          <t>NH투자증권</t>
         </is>
       </c>
       <c r="O66" s="6" t="inlineStr"/>
       <c r="P66" s="7" t="inlineStr">
         <is>
-          <t>988,800,000</t>
+          <t>1,908,899,000</t>
         </is>
       </c>
       <c r="Q66" s="6" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="R66" s="6" t="inlineStr">
@@ -13067,32 +13071,32 @@
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>유캐스트</t>
+          <t>엠비디</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>10-07~10-14</t>
+          <t>10-16~10-22</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>21,000~26,000</t>
+          <t>9,600~11,700</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>800,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>16,800,000,000</t>
+          <t>19,200,000,000</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>17.97배 (PER)</t>
+          <t>26.87배 (PER)</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr"/>
@@ -13100,7 +13104,7 @@
       <c r="I67" s="6" t="inlineStr"/>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t>10-19~10-20</t>
+          <t>10-28~10-29</t>
         </is>
       </c>
       <c r="K67" s="6" t="inlineStr"/>
@@ -13108,119 +13112,119 @@
       <c r="M67" s="6" t="inlineStr"/>
       <c r="N67" s="6" t="inlineStr">
         <is>
-          <t>유진투자증권</t>
+          <t>하나증권</t>
         </is>
       </c>
       <c r="O67" s="6" t="inlineStr"/>
       <c r="P67" s="7" t="inlineStr">
         <is>
-          <t>1,181,280,000</t>
+          <t>988,800,000</t>
         </is>
       </c>
       <c r="Q67" s="6" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="R67" s="6" t="inlineStr">
         <is>
-          <t>최초</t>
+          <t>정정</t>
         </is>
       </c>
     </row>
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>다비오</t>
-        </is>
-      </c>
-      <c r="B68" s="6" t="inlineStr">
-        <is>
-          <t>10-07~10-14</t>
+          <t>바로팜</t>
+        </is>
+      </c>
+      <c r="B68" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>12,300~16,600</t>
+          <t>16,400~20,200</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>1,000,000</t>
+          <t>1,780,000</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>12,300,000,000</t>
+          <t>29,192,000,000</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>26.70배 (PER)</t>
+          <t>24.95배 (PER)</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr"/>
       <c r="H68" s="6" t="inlineStr"/>
       <c r="I68" s="6" t="inlineStr"/>
-      <c r="J68" s="6" t="inlineStr">
-        <is>
-          <t>10-19~10-20</t>
+      <c r="J68" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="K68" s="6" t="inlineStr"/>
       <c r="L68" s="6" t="inlineStr"/>
       <c r="M68" s="6" t="inlineStr"/>
-      <c r="N68" s="6" t="inlineStr">
-        <is>
-          <t>대신증권</t>
+      <c r="N68" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="O68" s="6" t="inlineStr"/>
-      <c r="P68" s="7" t="inlineStr">
-        <is>
-          <t>570,105,000</t>
-        </is>
-      </c>
-      <c r="Q68" s="6" t="inlineStr">
-        <is>
-          <t>4.5%</t>
+      <c r="P68" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="Q68" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="R68" s="6" t="inlineStr">
         <is>
-          <t>최초</t>
+          <t>정정</t>
         </is>
       </c>
     </row>
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>인텔리빅스</t>
+          <t>다비오</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>10-12~10-16</t>
+          <t>10-07~10-14</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>7,600~9,000</t>
+          <t>12,300~16,600</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>2,500,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>19,000,000,000</t>
+          <t>12,300,000,000</t>
         </is>
       </c>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>22.02배 (PER)</t>
+          <t>26.70배 (PER)</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr"/>
@@ -13228,7 +13232,7 @@
       <c r="I69" s="6" t="inlineStr"/>
       <c r="J69" s="6" t="inlineStr">
         <is>
-          <t>10-21~10-22</t>
+          <t>10-19~10-20</t>
         </is>
       </c>
       <c r="K69" s="6" t="inlineStr"/>
@@ -13236,18 +13240,18 @@
       <c r="M69" s="6" t="inlineStr"/>
       <c r="N69" s="6" t="inlineStr">
         <is>
-          <t>미래에셋증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="O69" s="6" t="inlineStr"/>
       <c r="P69" s="7" t="inlineStr">
         <is>
-          <t>782,800,000</t>
+          <t>570,105,000</t>
         </is>
       </c>
       <c r="Q69" s="6" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="R69" s="6" t="inlineStr">
@@ -13259,32 +13263,32 @@
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>영광</t>
+          <t>인텔리빅스</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>10-13~10-19</t>
+          <t>10-12~10-16</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>14,000~17,000</t>
+          <t>7,600~9,000</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>2,260,000</t>
+          <t>2,500,000</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>31,640,000,000</t>
+          <t>19,000,000,000</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>11.98배 (EV/EBITDA)</t>
+          <t>22.02배 (PER)</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr"/>
@@ -13292,7 +13296,7 @@
       <c r="I70" s="6" t="inlineStr"/>
       <c r="J70" s="6" t="inlineStr">
         <is>
-          <t>10-22~10-23</t>
+          <t>10-21~10-22</t>
         </is>
       </c>
       <c r="K70" s="6" t="inlineStr"/>
@@ -13300,18 +13304,18 @@
       <c r="M70" s="6" t="inlineStr"/>
       <c r="N70" s="6" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>미래에셋증권</t>
         </is>
       </c>
       <c r="O70" s="6" t="inlineStr"/>
       <c r="P70" s="7" t="inlineStr">
         <is>
-          <t>977,676,000</t>
-        </is>
-      </c>
-      <c r="Q70" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>782,800,000</t>
+        </is>
+      </c>
+      <c r="Q70" s="6" t="inlineStr">
+        <is>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="R70" s="6" t="inlineStr">
@@ -13323,32 +13327,32 @@
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>한화플러스제6호스팩</t>
+          <t>영광</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>10-14~10-15</t>
-        </is>
-      </c>
-      <c r="C71" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>10-13~10-19</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>14,000~17,000</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>6,000,000</t>
+          <t>2,260,000</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>12,000,000,000</t>
-        </is>
-      </c>
-      <c r="F71" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>31,640,000,000</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>11.98배 (EV/EBITDA)</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr"/>
@@ -13356,26 +13360,26 @@
       <c r="I71" s="6" t="inlineStr"/>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>10-20~10-21</t>
+          <t>10-22~10-23</t>
         </is>
       </c>
       <c r="K71" s="6" t="inlineStr"/>
       <c r="L71" s="6" t="inlineStr"/>
       <c r="M71" s="6" t="inlineStr"/>
-      <c r="N71" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="N71" s="6" t="inlineStr">
+        <is>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="O71" s="6" t="inlineStr"/>
-      <c r="P71" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="Q71" s="6" t="inlineStr">
-        <is>
-          <t>3.50%</t>
+      <c r="P71" s="7" t="inlineStr">
+        <is>
+          <t>977,676,000</t>
+        </is>
+      </c>
+      <c r="Q71" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="R71" s="6" t="inlineStr">
@@ -13387,32 +13391,32 @@
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>에이엘로봇</t>
+          <t>한화플러스제6호스팩</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>10-15~10-21</t>
-        </is>
-      </c>
-      <c r="C72" s="6" t="inlineStr">
-        <is>
-          <t>15,700~17,600</t>
+          <t>10-14~10-15</t>
+        </is>
+      </c>
+      <c r="C72" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>2,400,000</t>
+          <t>6,000,000</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>37,680,000,000</t>
-        </is>
-      </c>
-      <c r="F72" s="6" t="inlineStr">
-        <is>
-          <t>37.17배 (PER)</t>
+          <t>12,000,000,000</t>
+        </is>
+      </c>
+      <c r="F72" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr"/>
@@ -13420,26 +13424,26 @@
       <c r="I72" s="6" t="inlineStr"/>
       <c r="J72" s="6" t="inlineStr">
         <is>
-          <t>10-26~10-27</t>
+          <t>10-20~10-21</t>
         </is>
       </c>
       <c r="K72" s="6" t="inlineStr"/>
       <c r="L72" s="6" t="inlineStr"/>
       <c r="M72" s="6" t="inlineStr"/>
-      <c r="N72" s="6" t="inlineStr">
-        <is>
-          <t>대신증권</t>
+      <c r="N72" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="O72" s="6" t="inlineStr"/>
-      <c r="P72" s="7" t="inlineStr">
-        <is>
-          <t>1,160,399,874</t>
+      <c r="P72" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="Q72" s="6" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="R72" s="6" t="inlineStr">
@@ -13451,32 +13455,32 @@
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>아이엠스팩1호</t>
+          <t>에이엘로봇</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>10-19~10-20</t>
-        </is>
-      </c>
-      <c r="C73" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>10-15~10-21</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>15,700~17,600</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>2,400,000</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>10,000,000,000</t>
-        </is>
-      </c>
-      <c r="F73" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>37,680,000,000</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>37.17배 (PER)</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr"/>
@@ -13490,20 +13494,20 @@
       <c r="K73" s="6" t="inlineStr"/>
       <c r="L73" s="6" t="inlineStr"/>
       <c r="M73" s="6" t="inlineStr"/>
-      <c r="N73" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="N73" s="6" t="inlineStr">
+        <is>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="O73" s="6" t="inlineStr"/>
-      <c r="P73" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P73" s="7" t="inlineStr">
+        <is>
+          <t>1,160,399,874</t>
         </is>
       </c>
       <c r="Q73" s="6" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="R73" s="6" t="inlineStr">
@@ -13515,32 +13519,32 @@
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>옵토닉스</t>
+          <t>아이엠스팩1호</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>10-21~10-27</t>
-        </is>
-      </c>
-      <c r="C74" s="6" t="inlineStr">
-        <is>
-          <t>10,000~12,000</t>
+          <t>10-19~10-20</t>
+        </is>
+      </c>
+      <c r="C74" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>2,200,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>22,000,000,000</t>
-        </is>
-      </c>
-      <c r="F74" s="6" t="inlineStr">
-        <is>
-          <t>25.27배 (EV/EBITDA)</t>
+          <t>10,000,000,000</t>
+        </is>
+      </c>
+      <c r="F74" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr"/>
@@ -13548,26 +13552,26 @@
       <c r="I74" s="6" t="inlineStr"/>
       <c r="J74" s="6" t="inlineStr">
         <is>
-          <t>11-05~11-06</t>
+          <t>10-26~10-27</t>
         </is>
       </c>
       <c r="K74" s="6" t="inlineStr"/>
       <c r="L74" s="6" t="inlineStr"/>
       <c r="M74" s="6" t="inlineStr"/>
-      <c r="N74" s="6" t="inlineStr">
-        <is>
-          <t>한국투자증권</t>
+      <c r="N74" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="O74" s="6" t="inlineStr"/>
-      <c r="P74" s="7" t="inlineStr">
-        <is>
-          <t>1,133,000,000</t>
+      <c r="P74" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="Q74" s="6" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="R74" s="6" t="inlineStr">
@@ -13579,32 +13583,32 @@
     <row r="75" ht="30" customHeight="1">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>넥스아이</t>
+          <t>옵토닉스</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>10-22~10-28</t>
+          <t>10-21~10-27</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>10,500~13,000</t>
+          <t>10,000~12,000</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>2,200,000</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>52,500,000,000</t>
+          <t>22,000,000,000</t>
         </is>
       </c>
       <c r="F75" s="6" t="inlineStr">
         <is>
-          <t>19.15배 (PER)</t>
+          <t>25.27배 (EV/EBITDA)</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr"/>
@@ -13612,7 +13616,7 @@
       <c r="I75" s="6" t="inlineStr"/>
       <c r="J75" s="6" t="inlineStr">
         <is>
-          <t>11-03~11-04</t>
+          <t>11-05~11-06</t>
         </is>
       </c>
       <c r="K75" s="6" t="inlineStr"/>
@@ -13626,12 +13630,12 @@
       <c r="O75" s="6" t="inlineStr"/>
       <c r="P75" s="7" t="inlineStr">
         <is>
-          <t>2,407,500,000</t>
+          <t>1,133,000,000</t>
         </is>
       </c>
       <c r="Q75" s="6" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="R75" s="6" t="inlineStr">
@@ -13643,32 +13647,32 @@
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>하나에어로다이내믹스</t>
+          <t>동원파츠</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>11-02~11-06</t>
+          <t>10-22~10-28</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>4,700~5,700</t>
+          <t>23,000~26,500</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>4,400,000</t>
+          <t>2,030,000</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>20,680,000,000</t>
+          <t>46,690,000,000</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
         <is>
-          <t>17.89배 (EV/EBITDA)</t>
+          <t>22.91배 (PER)</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr"/>
@@ -13676,7 +13680,7 @@
       <c r="I76" s="6" t="inlineStr"/>
       <c r="J76" s="6" t="inlineStr">
         <is>
-          <t>11-10~11-11</t>
+          <t>11-02~11-03</t>
         </is>
       </c>
       <c r="K76" s="6" t="inlineStr"/>
@@ -13684,18 +13688,18 @@
       <c r="M76" s="6" t="inlineStr"/>
       <c r="N76" s="6" t="inlineStr">
         <is>
-          <t>아이비케이투자증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="O76" s="6" t="inlineStr"/>
       <c r="P76" s="7" t="inlineStr">
         <is>
-          <t>850,000,000</t>
-        </is>
-      </c>
-      <c r="Q76" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>1,430,699,820</t>
+        </is>
+      </c>
+      <c r="Q76" s="6" t="inlineStr">
+        <is>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="R76" s="6" t="inlineStr">
@@ -13707,59 +13711,59 @@
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>바로팜</t>
-        </is>
-      </c>
-      <c r="B77" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>넥스아이</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>10-22~10-28</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>16,400~20,200</t>
+          <t>10,500~13,000</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>1,780,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>29,192,000,000</t>
+          <t>52,500,000,000</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>24.95배 (PER)</t>
+          <t>19.15배 (PER)</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr"/>
       <c r="H77" s="6" t="inlineStr"/>
       <c r="I77" s="6" t="inlineStr"/>
-      <c r="J77" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="J77" s="6" t="inlineStr">
+        <is>
+          <t>11-03~11-04</t>
         </is>
       </c>
       <c r="K77" s="6" t="inlineStr"/>
       <c r="L77" s="6" t="inlineStr"/>
       <c r="M77" s="6" t="inlineStr"/>
-      <c r="N77" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="N77" s="6" t="inlineStr">
+        <is>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="O77" s="6" t="inlineStr"/>
-      <c r="P77" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="Q77" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P77" s="7" t="inlineStr">
+        <is>
+          <t>2,407,500,000</t>
+        </is>
+      </c>
+      <c r="Q77" s="6" t="inlineStr">
+        <is>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="R77" s="6" t="inlineStr">
@@ -13771,54 +13775,54 @@
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>셀트릭스</t>
-        </is>
-      </c>
-      <c r="B78" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="C78" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="D78" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="E78" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="F78" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>하나에어로다이내믹스</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="inlineStr">
+        <is>
+          <t>11-02~11-06</t>
+        </is>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>4,700~5,700</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>4,400,000</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>20,680,000,000</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>17.89배 (EV/EBITDA)</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr"/>
       <c r="H78" s="6" t="inlineStr"/>
       <c r="I78" s="6" t="inlineStr"/>
-      <c r="J78" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="J78" s="6" t="inlineStr">
+        <is>
+          <t>11-10~11-11</t>
         </is>
       </c>
       <c r="K78" s="6" t="inlineStr"/>
       <c r="L78" s="6" t="inlineStr"/>
       <c r="M78" s="6" t="inlineStr"/>
-      <c r="N78" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="N78" s="6" t="inlineStr">
+        <is>
+          <t>아이비케이투자증권</t>
         </is>
       </c>
       <c r="O78" s="6" t="inlineStr"/>
-      <c r="P78" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P78" s="7" t="inlineStr">
+        <is>
+          <t>850,000,000</t>
         </is>
       </c>
       <c r="Q78" s="18" t="inlineStr">
@@ -13835,7 +13839,7 @@
     <row r="79" ht="30" customHeight="1">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>솔리스</t>
+          <t>셀트릭스</t>
         </is>
       </c>
       <c r="B79" s="18" t="inlineStr">
@@ -13899,7 +13903,7 @@
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>디티에스</t>
+          <t>솔리스</t>
         </is>
       </c>
       <c r="B80" s="18" t="inlineStr">
@@ -13956,14 +13960,14 @@
       </c>
       <c r="R80" s="6" t="inlineStr">
         <is>
-          <t>신고서 대기</t>
+          <t>최초</t>
         </is>
       </c>
     </row>
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>에이엔에이치스트럭쳐</t>
+          <t>디티에스</t>
         </is>
       </c>
       <c r="B81" s="18" t="inlineStr">
@@ -14027,7 +14031,7 @@
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>이에스티</t>
+          <t>에이엔에이치스트럭쳐</t>
         </is>
       </c>
       <c r="B82" s="18" t="inlineStr">
@@ -14091,7 +14095,7 @@
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>영광와이케이엠씨</t>
+          <t>이에스티</t>
         </is>
       </c>
       <c r="B83" s="18" t="inlineStr">
@@ -14155,7 +14159,7 @@
     <row r="84" ht="30" customHeight="1">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>동원파츠</t>
+          <t>영광와이케이엠씨</t>
         </is>
       </c>
       <c r="B84" s="18" t="inlineStr">
@@ -14440,7 +14444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -14717,145 +14721,153 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="22" t="inlineStr">
-        <is>
-          <t>합계</t>
-        </is>
-      </c>
-      <c r="B15" s="22">
-        <f>SUM(B6:B14)</f>
-        <v/>
-      </c>
-      <c r="C15" s="22">
-        <f>SUM(C6:C14)</f>
-        <v/>
-      </c>
-      <c r="D15" s="22">
-        <f>SUM(D6:D14)</f>
-        <v/>
-      </c>
-      <c r="E15" s="22">
-        <f>SUM(E6:E14)</f>
-        <v/>
-      </c>
-      <c r="F15" s="23">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F15" s="21">
         <f>IF((C15+D15)=0,"-",C15/(C15+D15))</f>
         <v/>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="22" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="B16" s="22">
+        <f>SUM(B6:B15)</f>
+        <v/>
+      </c>
+      <c r="C16" s="22">
+        <f>SUM(C6:C15)</f>
+        <v/>
+      </c>
+      <c r="D16" s="22">
+        <f>SUM(D6:D15)</f>
+        <v/>
+      </c>
+      <c r="E16" s="22">
+        <f>SUM(E6:E15)</f>
+        <v/>
+      </c>
+      <c r="F16" s="23">
+        <f>IF((C16+D16)=0,"-",C16/(C16+D16))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>② 주관사별 점유율 (공모 확보분)</t>
         </is>
       </c>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>대표주관사</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>건수</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>공모금액(백만원)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>한국투자증권</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>256,940,000,000</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>246,730,000,000</t>
+          <t>262,674,000,000</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>215,984,000,000</t>
+          <t>256,940,000,000</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>미래에셋증권㈜</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>156,428,800,000</t>
+          <t>246,730,000,000</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>미래에셋증권㈜</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>135,135,239,540</t>
+          <t>156,428,800,000</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>미래에셋증권</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>115,560,000,000</t>
+          <t>135,135,239,540</t>
         </is>
       </c>
     </row>
@@ -14866,18 +14878,18 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>96,880,000,000</t>
+          <t>120,280,000,000</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>유진투자증권</t>
+          <t>미래에셋증권</t>
         </is>
       </c>
       <c r="B26" s="6" t="n">
@@ -14885,74 +14897,74 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>74,400,000,000</t>
+          <t>115,560,000,000</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>DB증권</t>
+          <t>유진투자증권</t>
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>46,000,000,000</t>
+          <t>74,400,000,000</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>NH투자증권</t>
+          <t>DB증권</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>41,420,000,000</t>
+          <t>46,000,000,000</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>하나증권</t>
+          <t>NH투자증권</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>35,814,000,000</t>
+          <t>41,420,000,000</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>신한투자증권</t>
+          <t>하나증권</t>
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>30,240,000,000</t>
+          <t>35,814,000,000</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>신한투자증권</t>
         </is>
       </c>
       <c r="B31" s="6" t="n">
@@ -14960,104 +14972,104 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>27,200,000,000</t>
+          <t>30,240,000,000</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>618,288</t>
+          <t>27,200,000,000</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>154,600</t>
+          <t>618,288</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>130,837</t>
+          <t>154,600</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>신한</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>49,052</t>
+          <t>130,837</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>신한</t>
         </is>
       </c>
       <c r="B36" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>49,052</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>유진</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>25,020</t>
+          <t>32,000</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>메리츠</t>
+          <t>유진</t>
         </is>
       </c>
       <c r="B38" s="6" t="n">
@@ -15065,14 +15077,14 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>14,000</t>
+          <t>25,020</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>메리츠</t>
         </is>
       </c>
       <c r="B39" s="6" t="n">
@@ -15080,14 +15092,14 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>13,000</t>
+          <t>14,000</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>키움</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="B40" s="6" t="n">
@@ -15095,20 +15107,35 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>13,000</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>교보</t>
+          <t>키움</t>
         </is>
       </c>
       <c r="B41" s="6" t="n">
         <v>1</v>
       </c>
       <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>교보</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>10,800</t>
         </is>

--- a/IPO_analysis.xlsx
+++ b/IPO_analysis.xlsx
@@ -592,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K145"/>
+  <dimension ref="A1:K146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -618,14 +618,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>기준일 2026-10-01 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
+          <t>기준일 2026-10-02 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>■ 심사 신청(진행중)  (46건)</t>
+          <t>■ 심사 신청(진행중)  (47건)</t>
         </is>
       </c>
       <c r="B4" s="4" t="n"/>
@@ -699,12 +699,12 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>키노톤</t>
+          <t>뱅크샐러드</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -724,27 +724,27 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>46,943</t>
+          <t>25,994</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>4,222</t>
+          <t>-59,792</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>19,112</t>
+          <t>28,335</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>건축기술, 엔지니어링 및 관련 기술 서비스업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>티에스모스트</t>
+          <t>키노톤</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -781,27 +781,27 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>156,198</t>
+          <t>46,943</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>5,666</t>
+          <t>4,222</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>25,181</t>
+          <t>19,112</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>자동차 신품 부품 제조업</t>
+          <t>건축기술, 엔지니어링 및 관련 기술 서비스업</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>신한</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
@@ -813,12 +813,12 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>셀렉트스타</t>
+          <t>티에스모스트</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -838,27 +838,27 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>11,616</t>
+          <t>156,198</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>-9,883</t>
+          <t>5,666</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>-34,511</t>
+          <t>25,181</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>자동차 신품 부품 제조업</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>신한</t>
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr">
@@ -870,12 +870,12 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>서북</t>
+          <t>셀렉트스타</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -895,27 +895,27 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>60,439</t>
+          <t>11,616</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>-8,764</t>
+          <t>-9,883</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>4,485</t>
+          <t>-34,511</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>사진장비 및 광학기기 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>에이스엔지니어링</t>
+          <t>서북</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -952,27 +952,27 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>307,911</t>
+          <t>60,439</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>-101,468</t>
+          <t>-8,764</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>83,159</t>
+          <t>4,485</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>전동기, 발전기 및 전기 변환 · 공급 · 제어 장치 제조업</t>
+          <t>사진장비 및 광학기기 제조업</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>대신, 미래, 키움</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>플렉스시스템</t>
+          <t>에이스엔지니어링</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -1009,27 +1009,27 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>10,894</t>
+          <t>307,911</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>-2,342</t>
+          <t>-101,468</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>3,014</t>
+          <t>83,159</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업; 광학기기 제외</t>
+          <t>전동기, 발전기 및 전기 변환 · 공급 · 제어 장치 제조업</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>대신, 미래, 키움</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
@@ -1041,12 +1041,12 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>엠아이티</t>
+          <t>플렉스시스템</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -1066,27 +1066,27 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>14,921</t>
+          <t>10,894</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>1,181</t>
+          <t>-2,342</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>28,026</t>
+          <t>3,014</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업; 광학기기 제외</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>큐로드</t>
+          <t>엠아이티</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
@@ -1121,17 +1121,29 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F13" s="7" t="inlineStr"/>
-      <c r="G13" s="7" t="inlineStr"/>
-      <c r="H13" s="7" t="inlineStr"/>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>14,921</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>1,181</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>28,026</t>
+        </is>
+      </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>교보</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
@@ -1143,12 +1155,12 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>노바셀테크놀로지</t>
+          <t>큐로드</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -1158,7 +1170,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -1166,29 +1178,17 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
-      </c>
-      <c r="G14" s="7" t="inlineStr">
-        <is>
-          <t>-4,606</t>
-        </is>
-      </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>-15,458</t>
-        </is>
-      </c>
+      <c r="F14" s="7" t="inlineStr"/>
+      <c r="G14" s="7" t="inlineStr"/>
+      <c r="H14" s="7" t="inlineStr"/>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>키움</t>
+          <t>교보</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
@@ -1200,12 +1200,12 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>(주)태석광학</t>
+          <t>노바셀테크놀로지</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -1225,27 +1225,27 @@
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>79,804</t>
+          <t>377</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
         <is>
-          <t>4,721</t>
+          <t>-4,606</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
         <is>
-          <t>7,228</t>
+          <t>-15,458</t>
         </is>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>생활용품 도매업</t>
+          <t>자연과학 및 공학 연구개발업</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>신한, 대신</t>
+          <t>키움</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
@@ -1257,12 +1257,12 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>엑티브온</t>
+          <t>(주)태석광학</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -1280,17 +1280,29 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr"/>
-      <c r="G16" s="7" t="inlineStr"/>
-      <c r="H16" s="7" t="inlineStr"/>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>79,804</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>4,721</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>7,228</t>
+        </is>
+      </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>생활용품 도매업</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>키움</t>
+          <t>신한, 대신</t>
         </is>
       </c>
       <c r="K16" s="6" t="inlineStr">
@@ -1302,12 +1314,12 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>씨앤엠</t>
+          <t>엑티브온</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -1317,7 +1329,7 @@
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
@@ -1325,29 +1337,17 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
-        <is>
-          <t>238,489</t>
-        </is>
-      </c>
-      <c r="G17" s="7" t="inlineStr">
-        <is>
-          <t>19,869</t>
-        </is>
-      </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>112,262</t>
-        </is>
-      </c>
+      <c r="F17" s="7" t="inlineStr"/>
+      <c r="G17" s="7" t="inlineStr"/>
+      <c r="H17" s="7" t="inlineStr"/>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>전동기, 발전기 및 전기 변환 · 공급 · 제어 장치 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>키움</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
@@ -1359,17 +1359,17 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>무신사</t>
+          <t>씨앤엠</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>유가</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -1384,27 +1384,27 @@
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>1,352,930</t>
+          <t>238,489</t>
         </is>
       </c>
       <c r="G18" s="7" t="inlineStr">
         <is>
-          <t>-10,571</t>
+          <t>19,869</t>
         </is>
       </c>
       <c r="H18" s="7" t="inlineStr">
         <is>
-          <t>243,731</t>
+          <t>112,262</t>
         </is>
       </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>섬유, 의복, 신발 및 가죽제품 소매업</t>
+          <t>전동기, 발전기 및 전기 변환 · 공급 · 제어 장치 제조업</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>한국, 씨티그룹글로벌마켓증권(주), KB, 제이피모간증권회사 서울지점</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K18" s="6" t="inlineStr">
@@ -1416,17 +1416,17 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>마더스제약</t>
+          <t>무신사</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>유가</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -1441,27 +1441,27 @@
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>228,830</t>
+          <t>1,352,930</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>11,204</t>
+          <t>-10,571</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>57,394</t>
+          <t>243,731</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>의약품 제조업</t>
+          <t>섬유, 의복, 신발 및 가죽제품 소매업</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>NH, KB</t>
+          <t>한국, 씨티그룹글로벌마켓증권(주), KB, 제이피모간증권회사 서울지점</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>이나인페이</t>
+          <t>마더스제약</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -1498,27 +1498,27 @@
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>64,711</t>
+          <t>228,830</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>19,586</t>
+          <t>11,204</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>79,855</t>
+          <t>57,394</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>의약품 제조업</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>NH, KB</t>
         </is>
       </c>
       <c r="K20" s="6" t="inlineStr">
@@ -1530,12 +1530,12 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>어피닛</t>
+          <t>이나인페이</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1555,27 +1555,27 @@
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>169,126</t>
+          <t>64,711</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>26,009</t>
+          <t>19,586</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>61,466</t>
+          <t>79,855</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>미래, 하나</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>라이드플럭스</t>
+          <t>어피닛</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1612,17 +1612,17 @@
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>4,044</t>
+          <t>169,126</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>-31,423</t>
+          <t>26,009</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>-77,243</t>
+          <t>61,466</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>주식회사 우리투자증권, 한국</t>
+          <t>미래, 하나</t>
         </is>
       </c>
       <c r="K22" s="6" t="inlineStr">
@@ -1644,12 +1644,12 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>신영스팩12호</t>
+          <t>라이드플럭스</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -1667,17 +1667,29 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr"/>
-      <c r="G23" s="7" t="inlineStr"/>
-      <c r="H23" s="7" t="inlineStr"/>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>4,044</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>-31,423</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>-77,243</t>
+        </is>
+      </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>신영</t>
+          <t>주식회사 우리투자증권, 한국</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
@@ -1689,12 +1701,12 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>우리투자제1호스팩</t>
+          <t>신영스팩12호</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -1717,12 +1729,12 @@
       <c r="H24" s="7" t="inlineStr"/>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>주식회사 우리투자증권</t>
+          <t>신영</t>
         </is>
       </c>
       <c r="K24" s="6" t="inlineStr">
@@ -1734,17 +1746,17 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>에스텍시스템</t>
+          <t>우리투자제1호스팩</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>유가</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -1757,29 +1769,17 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>975,224</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>24,647</t>
-        </is>
-      </c>
-      <c r="H25" s="7" t="inlineStr">
-        <is>
-          <t>237,182</t>
-        </is>
-      </c>
+      <c r="F25" s="7" t="inlineStr"/>
+      <c r="G25" s="7" t="inlineStr"/>
+      <c r="H25" s="7" t="inlineStr"/>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>경비, 경호 및 탐정업</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>주식회사 우리투자증권</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
@@ -1791,17 +1791,17 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>범한메카텍</t>
+          <t>에스텍시스템</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>유가</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1816,27 +1816,27 @@
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>339,209</t>
+          <t>975,224</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>-18,141</t>
+          <t>24,647</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>265,955</t>
+          <t>237,182</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
+          <t>경비, 경호 및 탐정업</t>
         </is>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>유진, NH</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr">
@@ -1853,7 +1853,7 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>케이티이</t>
+          <t>범한메카텍</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -1873,27 +1873,27 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>173,901</t>
+          <t>339,209</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>14,243</t>
+          <t>-18,141</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>94,928</t>
+          <t>265,955</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>전동기, 발전기 및 전기 변환 · 공급 · 제어 장치 제조업</t>
+          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>유진, NH</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
@@ -1905,12 +1905,12 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>데스틴파워</t>
+          <t>케이티이</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -1930,17 +1930,17 @@
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>29,851</t>
+          <t>173,901</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>5,852</t>
+          <t>14,243</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>-30,114</t>
+          <t>94,928</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K28" s="6" t="inlineStr">
@@ -1967,7 +1967,7 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>유림테크</t>
+          <t>데스틴파워</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
@@ -1987,27 +1987,27 @@
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>102,586</t>
+          <t>29,851</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>-18,278</t>
+          <t>5,852</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>-4,832</t>
+          <t>-30,114</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>자동차 신품 부품 제조업</t>
+          <t>전동기, 발전기 및 전기 변환 · 공급 · 제어 장치 제조업</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
@@ -2019,12 +2019,12 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>이노보테라퓨틱스</t>
+          <t>유림테크</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -2044,27 +2044,27 @@
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>102,586</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>-5,429</t>
+          <t>-18,278</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>-53,200</t>
+          <t>-4,832</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>의약품 제조업</t>
+          <t>자동차 신품 부품 제조업</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
@@ -2076,17 +2076,17 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>에스에프씨</t>
+          <t>이노보테라퓨틱스</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>유가</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -2101,27 +2101,27 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>160,792</t>
+          <t>209</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>25,509</t>
+          <t>-5,429</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>243,562</t>
+          <t>-53,200</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>의약품 제조업</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>미래, 한국</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K31" s="6" t="inlineStr">
@@ -2133,17 +2133,17 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>아델</t>
+          <t>에스에프씨</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>유가</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -2158,27 +2158,27 @@
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>62,057</t>
+          <t>160,792</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>-64,210</t>
+          <t>25,509</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>-80,776</t>
+          <t>243,562</t>
         </is>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>그외 기타 전문, 과학 및 기술 서비스업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>삼성, 미래</t>
+          <t>미래, 한국</t>
         </is>
       </c>
       <c r="K32" s="6" t="inlineStr">
@@ -2190,12 +2190,12 @@
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>에버온</t>
+          <t>아델</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -2215,27 +2215,27 @@
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>65,225</t>
+          <t>62,057</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>-3,606</t>
+          <t>-64,210</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>54,955</t>
+          <t>-80,776</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>전기업</t>
+          <t>그외 기타 전문, 과학 및 기술 서비스업</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>삼성, 미래</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
@@ -2247,12 +2247,12 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>엔키화이트햇</t>
+          <t>에버온</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -2272,27 +2272,27 @@
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>14,176</t>
+          <t>65,225</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>-3,211</t>
+          <t>-3,606</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>8,338</t>
+          <t>54,955</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>전기업</t>
         </is>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>신영</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K34" s="6" t="inlineStr">
@@ -2304,12 +2304,12 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>씨아이에스케미칼</t>
+          <t>엔키화이트햇</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
@@ -2329,27 +2329,27 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>15,985</t>
+          <t>14,176</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>-11,440</t>
+          <t>-3,211</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>23,706</t>
+          <t>8,338</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>기초 화학물질 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>신영</t>
         </is>
       </c>
       <c r="K35" s="6" t="inlineStr">
@@ -2361,12 +2361,12 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>엠디에스코리아</t>
+          <t>씨아이에스케미칼</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
@@ -2386,27 +2386,27 @@
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>97,972</t>
+          <t>15,985</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>6,512</t>
+          <t>-11,440</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>53,818</t>
+          <t>23,706</t>
         </is>
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>기타 식품 제조업</t>
+          <t>기초 화학물질 제조업</t>
         </is>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="K36" s="6" t="inlineStr">
@@ -2418,12 +2418,12 @@
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>동승</t>
+          <t>엠디에스코리아</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -2443,27 +2443,27 @@
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>78,625</t>
+          <t>97,972</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>14,525</t>
+          <t>6,512</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>5,438</t>
+          <t>53,818</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>부동산 임대 및 공급업</t>
+          <t>기타 식품 제조업</t>
         </is>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>에프엠더블유</t>
+          <t>동승</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -2500,27 +2500,27 @@
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>30,282</t>
+          <t>78,625</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>4,762</t>
+          <t>14,525</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>5,438</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>기타 식품 제조업</t>
+          <t>부동산 임대 및 공급업</t>
         </is>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>유진</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K38" s="6" t="inlineStr">
@@ -2532,22 +2532,22 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>소노인터내셔널</t>
+          <t>에프엠더블유</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>유가</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
@@ -2557,27 +2557,27 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>2,093,051</t>
+          <t>30,282</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>-148,064</t>
+          <t>4,762</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>852,372</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>일반 및 생활 숙박시설 운영업</t>
+          <t>기타 식품 제조업</t>
         </is>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>대신, 미래</t>
+          <t>유진</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr">
@@ -2589,17 +2589,17 @@
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>싸이몬</t>
+          <t>소노인터내셔널</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>유가</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
@@ -2614,27 +2614,27 @@
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>48,695</t>
+          <t>2,093,051</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>15,714</t>
+          <t>-148,064</t>
         </is>
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>61,761</t>
+          <t>852,372</t>
         </is>
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업</t>
+          <t>일반 및 생활 숙박시설 운영업</t>
         </is>
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>대신, 미래</t>
         </is>
       </c>
       <c r="K40" s="6" t="inlineStr">
@@ -2646,12 +2646,12 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>바이다</t>
+          <t>싸이몬</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -2671,27 +2671,27 @@
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>14,432</t>
+          <t>48,695</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>-3,951</t>
+          <t>15,714</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>15,108</t>
+          <t>61,761</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>전자부품 제조업</t>
+          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업</t>
         </is>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
@@ -2703,12 +2703,12 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>아이알큐더스</t>
+          <t>바이다</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -2728,27 +2728,27 @@
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>10,231</t>
+          <t>14,432</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>-986</t>
+          <t>-3,951</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>1,800</t>
+          <t>15,108</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>전자부품 제조업</t>
         </is>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K42" s="6" t="inlineStr">
@@ -2760,12 +2760,12 @@
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>씨엔티테크</t>
+          <t>아이알큐더스</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -2785,17 +2785,17 @@
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>27,015</t>
+          <t>10,231</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>3,987</t>
+          <t>-986</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>2,613</t>
+          <t>1,800</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>한화, 하나</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
@@ -2822,7 +2822,7 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>제이앤티지</t>
+          <t>씨엔티테크</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -2842,27 +2842,27 @@
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>72,378</t>
+          <t>27,015</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>9,904</t>
+          <t>3,987</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>6,743</t>
+          <t>2,613</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>전자부품 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>대신, NH</t>
+          <t>한화, 하나</t>
         </is>
       </c>
       <c r="K44" s="6" t="inlineStr">
@@ -2874,12 +2874,12 @@
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>인터엑스</t>
+          <t>제이앤티지</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -2899,27 +2899,27 @@
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>8,645</t>
+          <t>72,378</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>-20,272</t>
+          <t>9,904</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>4,530</t>
+          <t>6,743</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>전자부품 제조업</t>
         </is>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>대신, NH</t>
         </is>
       </c>
       <c r="K45" s="6" t="inlineStr">
@@ -2931,12 +2931,12 @@
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>삼홍아크튜리온</t>
+          <t>인터엑스</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -2956,27 +2956,27 @@
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>26,162</t>
+          <t>8,645</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>-10,314</t>
+          <t>-20,272</t>
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>6,369</t>
+          <t>4,530</t>
         </is>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
-          <t>삼성, 미래</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K46" s="6" t="inlineStr">
@@ -2988,12 +2988,12 @@
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>넥스트에어로스페이스</t>
+          <t>삼홍아크튜리온</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -3013,27 +3013,27 @@
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>12,084</t>
+          <t>26,162</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>-17,270</t>
+          <t>-10,314</t>
         </is>
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>6,158</t>
+          <t>6,369</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>유인 항공기, 항공우주선 및 보조장치 제조업</t>
+          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
         </is>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>삼성, 미래</t>
         </is>
       </c>
       <c r="K47" s="6" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>비앤비코리아</t>
+          <t>넥스트에어로스페이스</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -3070,27 +3070,27 @@
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>141,169</t>
+          <t>12,084</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>21,406</t>
+          <t>-17,270</t>
         </is>
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>43,932</t>
+          <t>6,158</t>
         </is>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>유인 항공기, 항공우주선 및 보조장치 제조업</t>
         </is>
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K48" s="6" t="inlineStr">
@@ -3102,12 +3102,12 @@
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>오토핸즈</t>
+          <t>비앤비코리아</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -3117,7 +3117,7 @@
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
@@ -3127,22 +3127,22 @@
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>238,564</t>
+          <t>141,169</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>6,047</t>
+          <t>21,406</t>
         </is>
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>6,129</t>
+          <t>43,932</t>
         </is>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>자동차 판매업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="J49" s="6" t="inlineStr">
@@ -3159,12 +3159,12 @@
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>아이벡스메디칼시스템즈</t>
+          <t>오토핸즈</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
@@ -3184,27 +3184,27 @@
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>15,282</t>
+          <t>238,564</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>-7,227</t>
+          <t>6,047</t>
         </is>
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>6,129</t>
         </is>
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>자동차 판매업</t>
         </is>
       </c>
       <c r="J50" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K50" s="6" t="inlineStr">
@@ -3216,188 +3216,188 @@
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>아이벡스메디칼시스템즈</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>신규상장</t>
+        </is>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>FY25</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>15,282</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>-7,227</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>744</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>의료용 기기 제조업</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>NH</t>
+        </is>
+      </c>
+      <c r="K51" s="6" t="inlineStr">
+        <is>
+          <t>예심 진행중</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
           <t>2026-02-27</t>
         </is>
       </c>
-      <c r="B51" s="6" t="inlineStr">
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>피지티</t>
         </is>
       </c>
-      <c r="C51" s="6" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr">
         <is>
           <t>코스닥</t>
         </is>
       </c>
-      <c r="D51" s="6" t="inlineStr">
+      <c r="D52" s="6" t="inlineStr">
         <is>
           <t>신규상장</t>
         </is>
       </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="E52" s="6" t="inlineStr">
         <is>
           <t>FY25</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr">
+      <c r="F52" s="7" t="inlineStr">
         <is>
           <t>40,141</t>
         </is>
       </c>
-      <c r="G51" s="7" t="inlineStr">
+      <c r="G52" s="7" t="inlineStr">
         <is>
           <t>-69,722</t>
         </is>
       </c>
-      <c r="H51" s="7" t="inlineStr">
+      <c r="H52" s="7" t="inlineStr">
         <is>
           <t>6,029</t>
         </is>
       </c>
-      <c r="I51" s="6" t="inlineStr">
+      <c r="I52" s="6" t="inlineStr">
         <is>
           <t>기타 화학제품 제조업</t>
         </is>
       </c>
-      <c r="J51" s="6" t="inlineStr">
+      <c r="J52" s="6" t="inlineStr">
         <is>
           <t>한국</t>
         </is>
       </c>
-      <c r="K51" s="6" t="inlineStr">
+      <c r="K52" s="6" t="inlineStr">
         <is>
           <t>예심 진행중</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>■ 심사 승인  (70건)</t>
         </is>
       </c>
-      <c r="B53" s="4" t="n"/>
-      <c r="C53" s="4" t="n"/>
-      <c r="D53" s="4" t="n"/>
-      <c r="E53" s="4" t="n"/>
-      <c r="F53" s="4" t="n"/>
-      <c r="G53" s="4" t="n"/>
-      <c r="H53" s="4" t="n"/>
-      <c r="I53" s="4" t="n"/>
-      <c r="J53" s="4" t="n"/>
-      <c r="K53" s="4" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="B54" s="4" t="n"/>
+      <c r="C54" s="4" t="n"/>
+      <c r="D54" s="4" t="n"/>
+      <c r="E54" s="4" t="n"/>
+      <c r="F54" s="4" t="n"/>
+      <c r="G54" s="4" t="n"/>
+      <c r="H54" s="4" t="n"/>
+      <c r="I54" s="4" t="n"/>
+      <c r="J54" s="4" t="n"/>
+      <c r="K54" s="4" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>일자</t>
         </is>
       </c>
-      <c r="B54" s="5" t="inlineStr">
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>회사명</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
         <is>
           <t>시장</t>
         </is>
       </c>
-      <c r="D54" s="5" t="inlineStr">
+      <c r="D55" s="5" t="inlineStr">
         <is>
           <t>상장유형</t>
         </is>
       </c>
-      <c r="E54" s="5" t="inlineStr">
+      <c r="E55" s="5" t="inlineStr">
         <is>
           <t>기준연도</t>
         </is>
       </c>
-      <c r="F54" s="5" t="inlineStr">
+      <c r="F55" s="5" t="inlineStr">
         <is>
           <t>매출액</t>
         </is>
       </c>
-      <c r="G54" s="5" t="inlineStr">
+      <c r="G55" s="5" t="inlineStr">
         <is>
           <t>순이익</t>
         </is>
       </c>
-      <c r="H54" s="5" t="inlineStr">
+      <c r="H55" s="5" t="inlineStr">
         <is>
           <t>자기자본</t>
         </is>
       </c>
-      <c r="I54" s="5" t="inlineStr">
+      <c r="I55" s="5" t="inlineStr">
         <is>
           <t>업종</t>
         </is>
       </c>
-      <c r="J54" s="5" t="inlineStr">
+      <c r="J55" s="5" t="inlineStr">
         <is>
           <t>대표주관사</t>
         </is>
       </c>
-      <c r="K54" s="5" t="inlineStr">
+      <c r="K55" s="5" t="inlineStr">
         <is>
           <t>현황</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="6" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B55" s="6" t="inlineStr">
-        <is>
-          <t>셀트릭스</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>코스닥</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>스팩 소멸합병</t>
-        </is>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>FY25</t>
-        </is>
-      </c>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>16,976</t>
-        </is>
-      </c>
-      <c r="G55" s="7" t="inlineStr">
-        <is>
-          <t>4,545</t>
-        </is>
-      </c>
-      <c r="H55" s="7" t="inlineStr">
-        <is>
-          <t>2,213</t>
-        </is>
-      </c>
-      <c r="I55" s="6" t="inlineStr">
-        <is>
-          <t>의료용품 및 기타 의약 관련제품 제조업</t>
-        </is>
-      </c>
-      <c r="J55" s="6" t="inlineStr">
-        <is>
-          <t>IBK</t>
-        </is>
-      </c>
-      <c r="K55" s="6" t="inlineStr">
-        <is>
-          <t>상장전</t>
         </is>
       </c>
     </row>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>럭스코</t>
+          <t>셀트릭스</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
@@ -3429,22 +3429,22 @@
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>67,976</t>
+          <t>16,976</t>
         </is>
       </c>
       <c r="G56" s="7" t="inlineStr">
         <is>
-          <t>6,893</t>
+          <t>4,545</t>
         </is>
       </c>
       <c r="H56" s="7" t="inlineStr">
         <is>
-          <t>1,000</t>
+          <t>2,213</t>
         </is>
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
-          <t>전동기, 발전기 및 전기 변환 · 공급 · 제어 장치 제조업</t>
+          <t>의료용품 및 기타 의약 관련제품 제조업</t>
         </is>
       </c>
       <c r="J56" s="6" t="inlineStr">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>솔리스</t>
+          <t>럭스코</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
@@ -3484,17 +3484,29 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F57" s="7" t="inlineStr"/>
-      <c r="G57" s="7" t="inlineStr"/>
-      <c r="H57" s="7" t="inlineStr"/>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>67,976</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>6,893</t>
+        </is>
+      </c>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>1,000</t>
+        </is>
+      </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>전동기, 발전기 및 전기 변환 · 공급 · 제어 장치 제조업</t>
         </is>
       </c>
       <c r="J57" s="6" t="inlineStr">
         <is>
-          <t>한화</t>
+          <t>IBK</t>
         </is>
       </c>
       <c r="K57" s="6" t="inlineStr">
@@ -3506,12 +3518,12 @@
     <row r="58">
       <c r="A58" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>옵토닉스</t>
+          <t>솔리스</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
@@ -3521,7 +3533,7 @@
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
@@ -3529,29 +3541,17 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F58" s="7" t="inlineStr">
-        <is>
-          <t>25,368</t>
-        </is>
-      </c>
-      <c r="G58" s="7" t="inlineStr">
-        <is>
-          <t>1,901</t>
-        </is>
-      </c>
-      <c r="H58" s="7" t="inlineStr">
-        <is>
-          <t>730</t>
-        </is>
-      </c>
+      <c r="F58" s="7" t="inlineStr"/>
+      <c r="G58" s="7" t="inlineStr"/>
+      <c r="H58" s="7" t="inlineStr"/>
       <c r="I58" s="6" t="inlineStr">
         <is>
-          <t>광학렌즈 및 광학요소 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="J58" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>한화</t>
         </is>
       </c>
       <c r="K58" s="6" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>제논</t>
+          <t>옵토닉스</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
@@ -3588,27 +3588,27 @@
       </c>
       <c r="F59" s="7" t="inlineStr">
         <is>
-          <t>11,744</t>
+          <t>25,368</t>
         </is>
       </c>
       <c r="G59" s="7" t="inlineStr">
         <is>
-          <t>1,139</t>
+          <t>1,901</t>
         </is>
       </c>
       <c r="H59" s="7" t="inlineStr">
         <is>
-          <t>-1,220</t>
+          <t>730</t>
         </is>
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>광학렌즈 및 광학요소 제조업</t>
         </is>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K59" s="6" t="inlineStr">
@@ -3620,12 +3620,12 @@
     <row r="60">
       <c r="A60" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>영광</t>
+          <t>제논</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
@@ -3645,27 +3645,27 @@
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>113,133</t>
+          <t>11,744</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr">
         <is>
-          <t>10,328</t>
+          <t>1,139</t>
         </is>
       </c>
       <c r="H60" s="7" t="inlineStr">
         <is>
-          <t>3,052</t>
+          <t>-1,220</t>
         </is>
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
-          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K60" s="6" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>케이엠에프</t>
+          <t>영광</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
@@ -3702,27 +3702,27 @@
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>25,751</t>
+          <t>113,133</t>
         </is>
       </c>
       <c r="G61" s="7" t="inlineStr">
         <is>
-          <t>11,463</t>
+          <t>10,328</t>
         </is>
       </c>
       <c r="H61" s="7" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>3,052</t>
         </is>
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
-          <t>기타 식품 제조업</t>
+          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
         </is>
       </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
-          <t>IBK</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K61" s="6" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>넥스아이</t>
+          <t>케이엠에프</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
@@ -3759,27 +3759,27 @@
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>5,110</t>
+          <t>25,751</t>
         </is>
       </c>
       <c r="G62" s="7" t="inlineStr">
         <is>
-          <t>-52,331</t>
+          <t>11,463</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr">
         <is>
-          <t>-82,348</t>
+          <t>642</t>
         </is>
       </c>
       <c r="I62" s="6" t="inlineStr">
         <is>
-          <t>의약품 제조업</t>
+          <t>기타 식품 제조업</t>
         </is>
       </c>
       <c r="J62" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>IBK</t>
         </is>
       </c>
       <c r="K62" s="6" t="inlineStr">
@@ -3791,12 +3791,12 @@
     <row r="63">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>영광와이케이엠씨</t>
+          <t>넥스아이</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
@@ -3816,27 +3816,27 @@
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>51,609</t>
+          <t>5,110</t>
         </is>
       </c>
       <c r="G63" s="7" t="inlineStr">
         <is>
-          <t>2,708</t>
+          <t>-52,331</t>
         </is>
       </c>
       <c r="H63" s="7" t="inlineStr">
         <is>
-          <t>28,213</t>
+          <t>-82,348</t>
         </is>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
-          <t>기타 금속 가공제품 제조업</t>
+          <t>의약품 제조업</t>
         </is>
       </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K63" s="6" t="inlineStr">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>동원파츠</t>
+          <t>영광와이케이엠씨</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
@@ -3873,27 +3873,27 @@
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>92,255</t>
+          <t>51,609</t>
         </is>
       </c>
       <c r="G64" s="7" t="inlineStr">
         <is>
-          <t>3,443</t>
+          <t>2,708</t>
         </is>
       </c>
       <c r="H64" s="7" t="inlineStr">
         <is>
-          <t>27,535</t>
+          <t>28,213</t>
         </is>
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>기타 금속 가공제품 제조업</t>
         </is>
       </c>
       <c r="J64" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K64" s="6" t="inlineStr">
@@ -3905,12 +3905,12 @@
     <row r="65">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>이에스티</t>
+          <t>동원파츠</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
@@ -3930,17 +3930,17 @@
       </c>
       <c r="F65" s="7" t="inlineStr">
         <is>
-          <t>33,190</t>
+          <t>92,255</t>
         </is>
       </c>
       <c r="G65" s="7" t="inlineStr">
         <is>
-          <t>2,966</t>
+          <t>3,443</t>
         </is>
       </c>
       <c r="H65" s="7" t="inlineStr">
         <is>
-          <t>4,325</t>
+          <t>27,535</t>
         </is>
       </c>
       <c r="I65" s="6" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K65" s="6" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>에이엘로봇</t>
+          <t>이에스티</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
@@ -3987,22 +3987,22 @@
       </c>
       <c r="F66" s="7" t="inlineStr">
         <is>
-          <t>14,985</t>
+          <t>33,190</t>
         </is>
       </c>
       <c r="G66" s="7" t="inlineStr">
         <is>
-          <t>-21,891</t>
+          <t>2,966</t>
         </is>
       </c>
       <c r="H66" s="7" t="inlineStr">
         <is>
-          <t>129</t>
+          <t>4,325</t>
         </is>
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
-          <t>산업용 로봇 제조업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="J66" s="6" t="inlineStr">
@@ -4019,12 +4019,12 @@
     <row r="67">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>아이엠스팩1호</t>
+          <t>에이엘로봇</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
@@ -4042,17 +4042,29 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F67" s="7" t="inlineStr"/>
-      <c r="G67" s="7" t="inlineStr"/>
-      <c r="H67" s="7" t="inlineStr"/>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>14,985</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>-21,891</t>
+        </is>
+      </c>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>산업용 로봇 제조업</t>
         </is>
       </c>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t>iM증권</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K67" s="6" t="inlineStr">
@@ -4064,12 +4076,12 @@
     <row r="68">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>에이엔에이치스트럭쳐</t>
+          <t>아이엠스팩1호</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
@@ -4087,29 +4099,17 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F68" s="7" t="inlineStr">
-        <is>
-          <t>19,784</t>
-        </is>
-      </c>
-      <c r="G68" s="7" t="inlineStr">
-        <is>
-          <t>-4,296</t>
-        </is>
-      </c>
-      <c r="H68" s="7" t="inlineStr">
-        <is>
-          <t>24,561</t>
-        </is>
-      </c>
+      <c r="F68" s="7" t="inlineStr"/>
+      <c r="G68" s="7" t="inlineStr"/>
+      <c r="H68" s="7" t="inlineStr"/>
       <c r="I68" s="6" t="inlineStr">
         <is>
-          <t>건축기술, 엔지니어링 및 관련 기술 서비스업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="J68" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>iM증권</t>
         </is>
       </c>
       <c r="K68" s="6" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>인텔리빅스</t>
+          <t>에이엔에이치스트럭쳐</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
@@ -4146,27 +4146,27 @@
       </c>
       <c r="F69" s="7" t="inlineStr">
         <is>
-          <t>46,644</t>
+          <t>19,784</t>
         </is>
       </c>
       <c r="G69" s="7" t="inlineStr">
         <is>
-          <t>5,357</t>
+          <t>-4,296</t>
         </is>
       </c>
       <c r="H69" s="7" t="inlineStr">
         <is>
-          <t>1,048</t>
+          <t>24,561</t>
         </is>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>건축기술, 엔지니어링 및 관련 기술 서비스업</t>
         </is>
       </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K69" s="6" t="inlineStr">
@@ -4178,12 +4178,12 @@
     <row r="70">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>하나에어로다이내믹스</t>
+          <t>인텔리빅스</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
@@ -4203,27 +4203,27 @@
       </c>
       <c r="F70" s="7" t="inlineStr">
         <is>
-          <t>33,286</t>
+          <t>46,644</t>
         </is>
       </c>
       <c r="G70" s="7" t="inlineStr">
         <is>
-          <t>2,420</t>
+          <t>5,357</t>
         </is>
       </c>
       <c r="H70" s="7" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>1,048</t>
         </is>
       </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
-          <t>항공기,우주선 및 부품 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J70" s="6" t="inlineStr">
         <is>
-          <t>IBK</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K70" s="6" t="inlineStr">
@@ -4240,7 +4240,7 @@
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>다비오</t>
+          <t>하나에어로다이내믹스</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
@@ -4260,27 +4260,27 @@
       </c>
       <c r="F71" s="7" t="inlineStr">
         <is>
-          <t>9,251</t>
+          <t>33,286</t>
         </is>
       </c>
       <c r="G71" s="7" t="inlineStr">
         <is>
-          <t>-3,473</t>
+          <t>2,420</t>
         </is>
       </c>
       <c r="H71" s="7" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>890</t>
         </is>
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>항공기,우주선 및 부품 제조업</t>
         </is>
       </c>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>IBK</t>
         </is>
       </c>
       <c r="K71" s="6" t="inlineStr">
@@ -4292,12 +4292,12 @@
     <row r="72">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>티앤이코리아</t>
+          <t>다비오</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
@@ -4317,27 +4317,27 @@
       </c>
       <c r="F72" s="7" t="inlineStr">
         <is>
-          <t>22,339</t>
+          <t>9,251</t>
         </is>
       </c>
       <c r="G72" s="7" t="inlineStr">
         <is>
-          <t>-7,091</t>
+          <t>-3,473</t>
         </is>
       </c>
       <c r="H72" s="7" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>300</t>
         </is>
       </c>
       <c r="I72" s="6" t="inlineStr">
         <is>
-          <t>일반 목적용 기계 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J72" s="6" t="inlineStr">
         <is>
-          <t>신한</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K72" s="6" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>유캐스트</t>
+          <t>티앤이코리아</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
@@ -4374,27 +4374,27 @@
       </c>
       <c r="F73" s="7" t="inlineStr">
         <is>
-          <t>5,934</t>
+          <t>22,339</t>
         </is>
       </c>
       <c r="G73" s="7" t="inlineStr">
         <is>
-          <t>-3,557</t>
+          <t>-7,091</t>
         </is>
       </c>
       <c r="H73" s="7" t="inlineStr">
         <is>
-          <t>1,881</t>
+          <t>481</t>
         </is>
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
-          <t>통신 및 방송 장비 제조업</t>
+          <t>일반 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
-          <t>유진</t>
+          <t>신한</t>
         </is>
       </c>
       <c r="K73" s="6" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>엘리스그룹</t>
+          <t>유캐스트</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
@@ -4431,27 +4431,27 @@
       </c>
       <c r="F74" s="7" t="inlineStr">
         <is>
-          <t>39,513</t>
+          <t>5,934</t>
         </is>
       </c>
       <c r="G74" s="7" t="inlineStr">
         <is>
-          <t>15,666</t>
+          <t>-3,557</t>
         </is>
       </c>
       <c r="H74" s="7" t="inlineStr">
         <is>
-          <t>85,400</t>
+          <t>1,881</t>
         </is>
       </c>
       <c r="I74" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>통신 및 방송 장비 제조업</t>
         </is>
       </c>
       <c r="J74" s="6" t="inlineStr">
         <is>
-          <t>미래, 삼성</t>
+          <t>유진</t>
         </is>
       </c>
       <c r="K74" s="6" t="inlineStr">
@@ -4463,12 +4463,12 @@
     <row r="75">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>엘리스그룹</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
@@ -4478,7 +4478,7 @@
       </c>
       <c r="D75" s="6" t="inlineStr">
         <is>
-          <t>이전상장</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
@@ -4488,27 +4488,27 @@
       </c>
       <c r="F75" s="7" t="inlineStr">
         <is>
-          <t>48,646</t>
+          <t>39,513</t>
         </is>
       </c>
       <c r="G75" s="7" t="inlineStr">
         <is>
-          <t>6,017</t>
+          <t>15,666</t>
         </is>
       </c>
       <c r="H75" s="7" t="inlineStr">
         <is>
-          <t>18,795</t>
+          <t>85,400</t>
         </is>
       </c>
       <c r="I75" s="6" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
-          <t>하나</t>
+          <t>미래, 삼성</t>
         </is>
       </c>
       <c r="K75" s="6" t="inlineStr">
@@ -4525,7 +4525,7 @@
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>바로팜</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>이전상장</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
@@ -4545,27 +4545,27 @@
       </c>
       <c r="F76" s="7" t="inlineStr">
         <is>
-          <t>96,724</t>
+          <t>48,646</t>
         </is>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>-9,679</t>
+          <t>6,017</t>
         </is>
       </c>
       <c r="H76" s="7" t="inlineStr">
         <is>
-          <t>30,673</t>
+          <t>18,795</t>
         </is>
       </c>
       <c r="I76" s="6" t="inlineStr">
         <is>
-          <t>상품 중개업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="J76" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>하나</t>
         </is>
       </c>
       <c r="K76" s="6" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>크리에이츠</t>
+          <t>바로팜</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
@@ -4602,27 +4602,27 @@
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>76,395</t>
+          <t>96,724</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>23,749</t>
+          <t>-9,679</t>
         </is>
       </c>
       <c r="H77" s="7" t="inlineStr">
         <is>
-          <t>2,335</t>
+          <t>30,673</t>
         </is>
       </c>
       <c r="I77" s="6" t="inlineStr">
         <is>
-          <t>그외 기타 제품 제조업</t>
+          <t>상품 중개업</t>
         </is>
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K77" s="6" t="inlineStr">
@@ -4634,12 +4634,12 @@
     <row r="78">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>래블업</t>
+          <t>크리에이츠</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
@@ -4659,27 +4659,27 @@
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>6,712</t>
+          <t>76,395</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>-1,526</t>
+          <t>23,749</t>
         </is>
       </c>
       <c r="H78" s="7" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>2,335</t>
         </is>
       </c>
       <c r="I78" s="6" t="inlineStr">
         <is>
-          <t>데이터베이스 및 온라인정보 제공업</t>
+          <t>그외 기타 제품 제조업</t>
         </is>
       </c>
       <c r="J78" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K78" s="6" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>래블업</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
@@ -4716,27 +4716,27 @@
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>39,319</t>
+          <t>6,712</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr">
         <is>
-          <t>4,739</t>
+          <t>-1,526</t>
         </is>
       </c>
       <c r="H79" s="7" t="inlineStr">
         <is>
-          <t>1,250</t>
+          <t>373</t>
         </is>
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>데이터베이스 및 온라인정보 제공업</t>
         </is>
       </c>
       <c r="J79" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K79" s="6" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>엠비디</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
@@ -4773,27 +4773,27 @@
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>1,524</t>
+          <t>39,319</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
-          <t>-2,125</t>
+          <t>4,739</t>
         </is>
       </c>
       <c r="H80" s="7" t="inlineStr">
         <is>
-          <t>2,753</t>
+          <t>1,250</t>
         </is>
       </c>
       <c r="I80" s="6" t="inlineStr">
         <is>
-          <t>물질 검사, 측정 및 분석기구 제조업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="J80" s="6" t="inlineStr">
         <is>
-          <t>하나</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K80" s="6" t="inlineStr">
@@ -4805,12 +4805,12 @@
     <row r="81">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>에스케이증권제14호기업인수목적</t>
+          <t>엠비디</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
@@ -4830,27 +4830,27 @@
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,524</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-2,125</t>
         </is>
       </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2,753</t>
         </is>
       </c>
       <c r="I81" s="6" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>물질 검사, 측정 및 분석기구 제조업</t>
         </is>
       </c>
       <c r="J81" s="6" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>하나</t>
         </is>
       </c>
       <c r="K81" s="6" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>케이비제34호스팩</t>
+          <t>에스케이증권제14호기업인수목적</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="H82" s="7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I82" s="6" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="J82" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="K82" s="6" t="inlineStr">
         <is>
-          <t>상장승인(상장예정)</t>
+          <t>상장전</t>
         </is>
       </c>
     </row>
@@ -4924,7 +4924,7 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>한국제17호스팩</t>
+          <t>케이비제34호스팩</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="H83" s="7" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I83" s="6" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="K83" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-09-22)</t>
+          <t>상장승인(상장예정)</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>한화플러스제6호스팩</t>
+          <t>한국제17호스팩</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="H84" s="7" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I84" s="6" t="inlineStr">
@@ -5021,24 +5021,24 @@
       </c>
       <c r="J84" s="6" t="inlineStr">
         <is>
-          <t>한화</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K84" s="6" t="inlineStr">
         <is>
-          <t>상장전</t>
+          <t>상장완료 (2026-09-22)</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>엔에이치스팩34호</t>
+          <t>한화플러스제6호스팩</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
@@ -5068,34 +5068,34 @@
       </c>
       <c r="H85" s="7" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I85" s="6" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="J85" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>한화</t>
         </is>
       </c>
       <c r="K85" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-09-10)</t>
+          <t>상장전</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>글로벌테크놀로지</t>
+          <t>엔에이치스팩34호</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
@@ -5115,32 +5115,32 @@
       </c>
       <c r="F86" s="7" t="inlineStr">
         <is>
-          <t>29,689</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G86" s="7" t="inlineStr">
         <is>
-          <t>-25,889</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H86" s="7" t="inlineStr">
         <is>
-          <t>6,402</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I86" s="6" t="inlineStr">
         <is>
-          <t>반도체 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="J86" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K86" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-09-29)</t>
+          <t>상장완료 (2026-09-10)</t>
         </is>
       </c>
     </row>
@@ -5152,7 +5152,7 @@
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>글로벌테크놀로지</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
@@ -5167,37 +5167,37 @@
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>FY24</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>48,504</t>
+          <t>29,689</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>3,668</t>
+          <t>-25,889</t>
         </is>
       </c>
       <c r="H87" s="7" t="inlineStr">
         <is>
-          <t>8,448</t>
+          <t>6,402</t>
         </is>
       </c>
       <c r="I87" s="6" t="inlineStr">
         <is>
-          <t>항공기,우주선 및 부품 제조업</t>
+          <t>반도체 제조업</t>
         </is>
       </c>
       <c r="J87" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K87" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-09-30)</t>
+          <t>상장완료 (2026-09-29)</t>
         </is>
       </c>
     </row>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>디티에스</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
@@ -5229,22 +5229,22 @@
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
-          <t>142,718</t>
+          <t>48,504</t>
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>18,765</t>
+          <t>3,668</t>
         </is>
       </c>
       <c r="H88" s="7" t="inlineStr">
         <is>
-          <t>63,153</t>
+          <t>8,448</t>
         </is>
       </c>
       <c r="I88" s="6" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>항공기,우주선 및 부품 제조업</t>
         </is>
       </c>
       <c r="J88" s="6" t="inlineStr">
@@ -5254,19 +5254,19 @@
       </c>
       <c r="K88" s="6" t="inlineStr">
         <is>
-          <t>상장전</t>
+          <t>상장완료 (2026-09-30)</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>네오사피엔스</t>
+          <t>디티에스</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
@@ -5281,27 +5281,27 @@
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>FY25</t>
+          <t>FY24</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>10,649</t>
+          <t>142,718</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr">
         <is>
-          <t>-6,994</t>
+          <t>18,765</t>
         </is>
       </c>
       <c r="H89" s="7" t="inlineStr">
         <is>
-          <t>-39,962</t>
+          <t>63,153</t>
         </is>
       </c>
       <c r="I89" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="J89" s="6" t="inlineStr">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="K89" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-09-21)</t>
+          <t>상장전</t>
         </is>
       </c>
     </row>
@@ -5323,7 +5323,7 @@
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>엠에스바이오</t>
+          <t>네오사피엔스</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
@@ -5343,44 +5343,44 @@
       </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
-          <t>23,787</t>
+          <t>10,649</t>
         </is>
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>7,288</t>
+          <t>-6,994</t>
         </is>
       </c>
       <c r="H90" s="7" t="inlineStr">
         <is>
-          <t>1,942</t>
+          <t>-39,962</t>
         </is>
       </c>
       <c r="I90" s="6" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J90" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K90" s="6" t="inlineStr">
         <is>
-          <t>상장전</t>
+          <t>상장완료 (2026-09-21)</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>기도산업</t>
+          <t>엠에스바이오</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
@@ -5400,32 +5400,32 @@
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>346,551</t>
+          <t>23,787</t>
         </is>
       </c>
       <c r="G91" s="7" t="inlineStr">
         <is>
-          <t>35,334</t>
+          <t>7,288</t>
         </is>
       </c>
       <c r="H91" s="7" t="inlineStr">
         <is>
-          <t>145,991</t>
+          <t>1,942</t>
         </is>
       </c>
       <c r="I91" s="6" t="inlineStr">
         <is>
-          <t>봉제의복 제조업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="J91" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="K91" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-08-21)</t>
+          <t>상장전</t>
         </is>
       </c>
     </row>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>브릴스</t>
+          <t>기도산업</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
@@ -5457,32 +5457,32 @@
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>23,759</t>
+          <t>346,551</t>
         </is>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
-          <t>1,744</t>
+          <t>35,334</t>
         </is>
       </c>
       <c r="H92" s="7" t="inlineStr">
         <is>
-          <t>4,785</t>
+          <t>145,991</t>
         </is>
       </c>
       <c r="I92" s="6" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>봉제의복 제조업</t>
         </is>
       </c>
       <c r="J92" s="6" t="inlineStr">
         <is>
-          <t>IBK</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K92" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-10-01)</t>
+          <t>상장완료 (2026-08-21)</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>와이즈플래닛컴퍼니</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
@@ -5514,44 +5514,44 @@
       </c>
       <c r="F93" s="7" t="inlineStr">
         <is>
-          <t>44,578</t>
+          <t>23,759</t>
         </is>
       </c>
       <c r="G93" s="7" t="inlineStr">
         <is>
-          <t>7,748</t>
+          <t>1,744</t>
         </is>
       </c>
       <c r="H93" s="7" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>4,785</t>
         </is>
       </c>
       <c r="I93" s="6" t="inlineStr">
         <is>
-          <t>광고물 문안, 도안, 설계 등 작성업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="J93" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>IBK</t>
         </is>
       </c>
       <c r="K93" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-09-23)</t>
+          <t>상장완료 (2026-10-01)</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>니어스랩</t>
+          <t>와이즈플래닛컴퍼니</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
@@ -5571,32 +5571,32 @@
       </c>
       <c r="F94" s="7" t="inlineStr">
         <is>
-          <t>6,361</t>
+          <t>44,578</t>
         </is>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
-          <t>-7,287</t>
+          <t>7,748</t>
         </is>
       </c>
       <c r="H94" s="7" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>959</t>
         </is>
       </c>
       <c r="I94" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>광고물 문안, 도안, 설계 등 작성업</t>
         </is>
       </c>
       <c r="J94" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K94" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-08-24)</t>
+          <t>상장완료 (2026-09-23)</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>해치텍</t>
+          <t>니어스랩</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
@@ -5628,32 +5628,32 @@
       </c>
       <c r="F95" s="7" t="inlineStr">
         <is>
-          <t>14,079</t>
+          <t>6,361</t>
         </is>
       </c>
       <c r="G95" s="7" t="inlineStr">
         <is>
-          <t>-8,009</t>
+          <t>-7,287</t>
         </is>
       </c>
       <c r="H95" s="7" t="inlineStr">
         <is>
-          <t>2,229</t>
+          <t>127</t>
         </is>
       </c>
       <c r="I95" s="6" t="inlineStr">
         <is>
-          <t>반도체 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J95" s="6" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K95" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-08-25)</t>
+          <t>상장완료 (2026-08-24)</t>
         </is>
       </c>
     </row>
@@ -5665,7 +5665,7 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>해치텍</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
@@ -5685,44 +5685,44 @@
       </c>
       <c r="F96" s="7" t="inlineStr">
         <is>
-          <t>7,936</t>
+          <t>14,079</t>
         </is>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>-62,995</t>
+          <t>-8,009</t>
         </is>
       </c>
       <c r="H96" s="7" t="inlineStr">
         <is>
-          <t>8,341</t>
+          <t>2,229</t>
         </is>
       </c>
       <c r="I96" s="6" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>반도체 제조업</t>
         </is>
       </c>
       <c r="J96" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="K96" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-09-04)</t>
+          <t>상장완료 (2026-08-25)</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>에이치엘지노믹스</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
@@ -5742,32 +5742,32 @@
       </c>
       <c r="F97" s="7" t="inlineStr">
         <is>
-          <t>28,877</t>
+          <t>7,936</t>
         </is>
       </c>
       <c r="G97" s="7" t="inlineStr">
         <is>
-          <t>8,452</t>
+          <t>-62,995</t>
         </is>
       </c>
       <c r="H97" s="7" t="inlineStr">
         <is>
-          <t>83,552</t>
+          <t>8,341</t>
         </is>
       </c>
       <c r="I97" s="6" t="inlineStr">
         <is>
-          <t>기초 의약물질 제조업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="J97" s="6" t="inlineStr">
         <is>
-          <t>KB, IBK</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K97" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-07-24)</t>
+          <t>상장완료 (2026-09-04)</t>
         </is>
       </c>
     </row>
@@ -5779,7 +5779,7 @@
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>딜리셔스</t>
+          <t>에이치엘지노믹스</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
@@ -5799,44 +5799,44 @@
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>25,149</t>
+          <t>28,877</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>-20,419</t>
+          <t>8,452</t>
         </is>
       </c>
       <c r="H98" s="7" t="inlineStr">
         <is>
-          <t>-114,384</t>
+          <t>83,552</t>
         </is>
       </c>
       <c r="I98" s="6" t="inlineStr">
         <is>
-          <t>무점포 소매업</t>
+          <t>기초 의약물질 제조업</t>
         </is>
       </c>
       <c r="J98" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>KB, IBK</t>
         </is>
       </c>
       <c r="K98" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-08-12)</t>
+          <t>상장완료 (2026-07-24)</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스</t>
+          <t>딜리셔스</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
@@ -5856,44 +5856,44 @@
       </c>
       <c r="F99" s="7" t="inlineStr">
         <is>
-          <t>2,588,400</t>
+          <t>25,149</t>
         </is>
       </c>
       <c r="G99" s="7" t="inlineStr">
         <is>
-          <t>15,755,864</t>
+          <t>-20,419</t>
         </is>
       </c>
       <c r="H99" s="7" t="inlineStr">
         <is>
-          <t>30,841,690</t>
+          <t>-114,384</t>
         </is>
       </c>
       <c r="I99" s="6" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>무점포 소매업</t>
         </is>
       </c>
       <c r="J99" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K99" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-08-18)</t>
+          <t>상장완료 (2026-08-12)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>한국제16호스팩</t>
+          <t>인제니아테라퓨틱스</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
@@ -5911,30 +5911,46 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F100" s="7" t="inlineStr"/>
-      <c r="G100" s="7" t="inlineStr"/>
-      <c r="H100" s="7" t="inlineStr"/>
-      <c r="I100" s="6" t="inlineStr"/>
+      <c r="F100" s="7" t="inlineStr">
+        <is>
+          <t>2,588,400</t>
+        </is>
+      </c>
+      <c r="G100" s="7" t="inlineStr">
+        <is>
+          <t>15,755,864</t>
+        </is>
+      </c>
+      <c r="H100" s="7" t="inlineStr">
+        <is>
+          <t>30,841,690</t>
+        </is>
+      </c>
+      <c r="I100" s="6" t="inlineStr">
+        <is>
+          <t>자연과학 및 공학 연구개발업</t>
+        </is>
+      </c>
       <c r="J100" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-06-30)</t>
+          <t>상장완료 (2026-08-18)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>레메디</t>
+          <t>한국제16호스팩</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
@@ -5952,34 +5968,18 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F101" s="7" t="inlineStr">
-        <is>
-          <t>13,441</t>
-        </is>
-      </c>
-      <c r="G101" s="7" t="inlineStr">
-        <is>
-          <t>741</t>
-        </is>
-      </c>
-      <c r="H101" s="7" t="inlineStr">
-        <is>
-          <t>5,870</t>
-        </is>
-      </c>
-      <c r="I101" s="6" t="inlineStr">
-        <is>
-          <t>의료용 기기 제조업</t>
-        </is>
-      </c>
+      <c r="F101" s="7" t="inlineStr"/>
+      <c r="G101" s="7" t="inlineStr"/>
+      <c r="H101" s="7" t="inlineStr"/>
+      <c r="I101" s="6" t="inlineStr"/>
       <c r="J101" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K101" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-07-13)</t>
+          <t>상장완료 (2026-06-30)</t>
         </is>
       </c>
     </row>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>케이앤에스아이앤씨</t>
+          <t>레메디</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
@@ -6011,44 +6011,44 @@
       </c>
       <c r="F102" s="7" t="inlineStr">
         <is>
-          <t>13,482</t>
+          <t>13,441</t>
         </is>
       </c>
       <c r="G102" s="7" t="inlineStr">
         <is>
-          <t>-2,213</t>
+          <t>741</t>
         </is>
       </c>
       <c r="H102" s="7" t="inlineStr">
         <is>
-          <t>4,273</t>
+          <t>5,870</t>
         </is>
       </c>
       <c r="I102" s="6" t="inlineStr">
         <is>
-          <t>통신 및 방송 장비 제조업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="J102" s="6" t="inlineStr">
         <is>
-          <t>IBK</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="K102" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-08-13)</t>
+          <t>상장완료 (2026-07-13)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>메리츠제2호스팩</t>
+          <t>케이앤에스아이앤씨</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
@@ -6066,30 +6066,46 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F103" s="7" t="inlineStr"/>
-      <c r="G103" s="7" t="inlineStr"/>
-      <c r="H103" s="7" t="inlineStr"/>
-      <c r="I103" s="6" t="inlineStr"/>
+      <c r="F103" s="7" t="inlineStr">
+        <is>
+          <t>13,482</t>
+        </is>
+      </c>
+      <c r="G103" s="7" t="inlineStr">
+        <is>
+          <t>-2,213</t>
+        </is>
+      </c>
+      <c r="H103" s="7" t="inlineStr">
+        <is>
+          <t>4,273</t>
+        </is>
+      </c>
+      <c r="I103" s="6" t="inlineStr">
+        <is>
+          <t>통신 및 방송 장비 제조업</t>
+        </is>
+      </c>
       <c r="J103" s="6" t="inlineStr">
         <is>
-          <t>메리츠</t>
+          <t>IBK</t>
         </is>
       </c>
       <c r="K103" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-06-19)</t>
+          <t>상장완료 (2026-08-13)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>빅웨이브로보틱스</t>
+          <t>메리츠제2호스팩</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
@@ -6104,49 +6120,33 @@
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>FY24</t>
-        </is>
-      </c>
-      <c r="F104" s="7" t="inlineStr">
-        <is>
-          <t>13,851</t>
-        </is>
-      </c>
-      <c r="G104" s="7" t="inlineStr">
-        <is>
-          <t>-5,856</t>
-        </is>
-      </c>
-      <c r="H104" s="7" t="inlineStr">
-        <is>
-          <t>9,470</t>
-        </is>
-      </c>
-      <c r="I104" s="6" t="inlineStr">
-        <is>
-          <t>소프트웨어 개발 및 공급업</t>
-        </is>
-      </c>
+          <t>FY25</t>
+        </is>
+      </c>
+      <c r="F104" s="7" t="inlineStr"/>
+      <c r="G104" s="7" t="inlineStr"/>
+      <c r="H104" s="7" t="inlineStr"/>
+      <c r="I104" s="6" t="inlineStr"/>
       <c r="J104" s="6" t="inlineStr">
         <is>
-          <t>유진, 미래</t>
+          <t>메리츠</t>
         </is>
       </c>
       <c r="K104" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-09-29)</t>
+          <t>상장완료 (2026-06-19)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>매드업</t>
+          <t>빅웨이브로보틱스</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
@@ -6166,44 +6166,44 @@
       </c>
       <c r="F105" s="7" t="inlineStr">
         <is>
-          <t>34,989</t>
+          <t>13,851</t>
         </is>
       </c>
       <c r="G105" s="7" t="inlineStr">
         <is>
-          <t>-2,747</t>
+          <t>-5,856</t>
         </is>
       </c>
       <c r="H105" s="7" t="inlineStr">
         <is>
-          <t>-15,766</t>
+          <t>9,470</t>
         </is>
       </c>
       <c r="I105" s="6" t="inlineStr">
         <is>
-          <t>광고</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J105" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>유진, 미래</t>
         </is>
       </c>
       <c r="K105" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-07-01)</t>
+          <t>상장완료 (2026-09-29)</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>져스텍</t>
+          <t>매드업</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="F106" s="7" t="inlineStr">
         <is>
-          <t>19,851</t>
+          <t>34,989</t>
         </is>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>-2,747</t>
         </is>
       </c>
       <c r="H106" s="7" t="inlineStr">
         <is>
-          <t>10,953</t>
+          <t>-15,766</t>
         </is>
       </c>
       <c r="I106" s="6" t="inlineStr">
         <is>
-          <t>기계</t>
+          <t>광고</t>
         </is>
       </c>
       <c r="J106" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K106" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-06-29)</t>
+          <t>상장완료 (2026-07-01)</t>
         </is>
       </c>
     </row>
@@ -6260,7 +6260,7 @@
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>스트라드비젼</t>
+          <t>져스텍</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
@@ -6280,44 +6280,44 @@
       </c>
       <c r="F107" s="7" t="inlineStr">
         <is>
-          <t>11,539</t>
+          <t>19,851</t>
         </is>
       </c>
       <c r="G107" s="7" t="inlineStr">
         <is>
-          <t>-65,529</t>
+          <t>444</t>
         </is>
       </c>
       <c r="H107" s="7" t="inlineStr">
         <is>
-          <t>-245,151</t>
+          <t>10,953</t>
         </is>
       </c>
       <c r="I107" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어</t>
+          <t>기계</t>
         </is>
       </c>
       <c r="J107" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K107" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-06-30)</t>
+          <t>상장완료 (2026-06-29)</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="6" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>대신밸런스제20호스팩</t>
+          <t>스트라드비젼</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
@@ -6332,33 +6332,49 @@
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t>FY25</t>
-        </is>
-      </c>
-      <c r="F108" s="7" t="inlineStr"/>
-      <c r="G108" s="7" t="inlineStr"/>
-      <c r="H108" s="7" t="inlineStr"/>
-      <c r="I108" s="6" t="inlineStr"/>
+          <t>FY24</t>
+        </is>
+      </c>
+      <c r="F108" s="7" t="inlineStr">
+        <is>
+          <t>11,539</t>
+        </is>
+      </c>
+      <c r="G108" s="7" t="inlineStr">
+        <is>
+          <t>-65,529</t>
+        </is>
+      </c>
+      <c r="H108" s="7" t="inlineStr">
+        <is>
+          <t>-245,151</t>
+        </is>
+      </c>
+      <c r="I108" s="6" t="inlineStr">
+        <is>
+          <t>소프트웨어</t>
+        </is>
+      </c>
       <c r="J108" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="K108" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-06-05)</t>
+          <t>상장완료 (2026-06-30)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="6" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>피스피스스튜디오</t>
+          <t>대신밸런스제20호스팩</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
@@ -6373,37 +6389,21 @@
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>FY24</t>
-        </is>
-      </c>
-      <c r="F109" s="7" t="inlineStr">
-        <is>
-          <t>113,777</t>
-        </is>
-      </c>
-      <c r="G109" s="7" t="inlineStr">
-        <is>
-          <t>17,603</t>
-        </is>
-      </c>
-      <c r="H109" s="7" t="inlineStr">
-        <is>
-          <t>55,861</t>
-        </is>
-      </c>
-      <c r="I109" s="6" t="inlineStr">
-        <is>
-          <t>섬유,의류,신발,호화품</t>
-        </is>
-      </c>
+          <t>FY25</t>
+        </is>
+      </c>
+      <c r="F109" s="7" t="inlineStr"/>
+      <c r="G109" s="7" t="inlineStr"/>
+      <c r="H109" s="7" t="inlineStr"/>
+      <c r="I109" s="6" t="inlineStr"/>
       <c r="J109" s="6" t="inlineStr">
         <is>
-          <t>NH, 미래</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K109" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-06-08)</t>
+          <t>상장완료 (2026-06-05)</t>
         </is>
       </c>
     </row>
@@ -6415,7 +6415,7 @@
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>폴레드</t>
+          <t>피스피스스튜디오</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
@@ -6435,32 +6435,32 @@
       </c>
       <c r="F110" s="7" t="inlineStr">
         <is>
-          <t>52,808</t>
+          <t>113,777</t>
         </is>
       </c>
       <c r="G110" s="7" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>17,603</t>
         </is>
       </c>
       <c r="H110" s="7" t="inlineStr">
         <is>
-          <t>25,416</t>
+          <t>55,861</t>
         </is>
       </c>
       <c r="I110" s="6" t="inlineStr">
         <is>
-          <t>가정용기기와용품</t>
+          <t>섬유,의류,신발,호화품</t>
         </is>
       </c>
       <c r="J110" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>NH, 미래</t>
         </is>
       </c>
       <c r="K110" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-05-14)</t>
+          <t>상장완료 (2026-06-08)</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>레몬헬스케어</t>
+          <t>폴레드</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
@@ -6492,44 +6492,44 @@
       </c>
       <c r="F111" s="7" t="inlineStr">
         <is>
-          <t>14,877</t>
+          <t>52,808</t>
         </is>
       </c>
       <c r="G111" s="7" t="inlineStr">
         <is>
-          <t>-2,898</t>
+          <t>543</t>
         </is>
       </c>
       <c r="H111" s="7" t="inlineStr">
         <is>
-          <t>-31,162</t>
+          <t>25,416</t>
         </is>
       </c>
       <c r="I111" s="6" t="inlineStr">
         <is>
-          <t>건강관리업체및서비스</t>
+          <t>가정용기기와용품</t>
         </is>
       </c>
       <c r="J111" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K111" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-07-06)</t>
+          <t>상장완료 (2026-05-14)</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="6" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>마키나락스</t>
+          <t>레몬헬스케어</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
@@ -6549,32 +6549,32 @@
       </c>
       <c r="F112" s="7" t="inlineStr">
         <is>
-          <t>8,294</t>
+          <t>14,877</t>
         </is>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
-          <t>-6,073</t>
+          <t>-2,898</t>
         </is>
       </c>
       <c r="H112" s="7" t="inlineStr">
         <is>
-          <t>2,680</t>
+          <t>-31,162</t>
         </is>
       </c>
       <c r="I112" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어</t>
+          <t>건강관리업체및서비스</t>
         </is>
       </c>
       <c r="J112" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="K112" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-05-20)</t>
+          <t>상장완료 (2026-07-06)</t>
         </is>
       </c>
     </row>
@@ -6586,7 +6586,7 @@
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>채비</t>
+          <t>마키나락스</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
@@ -6606,44 +6606,44 @@
       </c>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>85,082</t>
+          <t>8,294</t>
         </is>
       </c>
       <c r="G113" s="7" t="inlineStr">
         <is>
-          <t>-54,495</t>
+          <t>-6,073</t>
         </is>
       </c>
       <c r="H113" s="7" t="inlineStr">
         <is>
-          <t>96,866</t>
+          <t>2,680</t>
         </is>
       </c>
       <c r="I113" s="6" t="inlineStr">
         <is>
-          <t>전기제품</t>
+          <t>소프트웨어</t>
         </is>
       </c>
       <c r="J113" s="6" t="inlineStr">
         <is>
-          <t>KB, 삼성, 대신, 하나</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K113" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-04-29)</t>
+          <t>상장완료 (2026-05-20)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="6" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>키움히어로제2호스팩</t>
+          <t>채비</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
@@ -6661,30 +6661,46 @@
           <t>FY24</t>
         </is>
       </c>
-      <c r="F114" s="7" t="inlineStr"/>
-      <c r="G114" s="7" t="inlineStr"/>
-      <c r="H114" s="7" t="inlineStr"/>
-      <c r="I114" s="6" t="inlineStr"/>
+      <c r="F114" s="7" t="inlineStr">
+        <is>
+          <t>85,082</t>
+        </is>
+      </c>
+      <c r="G114" s="7" t="inlineStr">
+        <is>
+          <t>-54,495</t>
+        </is>
+      </c>
+      <c r="H114" s="7" t="inlineStr">
+        <is>
+          <t>96,866</t>
+        </is>
+      </c>
+      <c r="I114" s="6" t="inlineStr">
+        <is>
+          <t>전기제품</t>
+        </is>
+      </c>
       <c r="J114" s="6" t="inlineStr">
         <is>
-          <t>키움</t>
+          <t>KB, 삼성, 대신, 하나</t>
         </is>
       </c>
       <c r="K114" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-04-23)</t>
+          <t>상장완료 (2026-04-29)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="6" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>세미티에스</t>
+          <t>키움히어로제2호스팩</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
@@ -6694,7 +6710,7 @@
       </c>
       <c r="D115" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E115" s="6" t="inlineStr">
@@ -6702,46 +6718,30 @@
           <t>FY24</t>
         </is>
       </c>
-      <c r="F115" s="7" t="inlineStr">
-        <is>
-          <t>20,808</t>
-        </is>
-      </c>
-      <c r="G115" s="7" t="inlineStr">
-        <is>
-          <t>7,337</t>
-        </is>
-      </c>
-      <c r="H115" s="7" t="inlineStr">
-        <is>
-          <t>26,616</t>
-        </is>
-      </c>
-      <c r="I115" s="6" t="inlineStr">
-        <is>
-          <t>반도체와반도체장비</t>
-        </is>
-      </c>
+      <c r="F115" s="7" t="inlineStr"/>
+      <c r="G115" s="7" t="inlineStr"/>
+      <c r="H115" s="7" t="inlineStr"/>
+      <c r="I115" s="6" t="inlineStr"/>
       <c r="J115" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>키움</t>
         </is>
       </c>
       <c r="K115" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-02-05)</t>
+          <t>상장완료 (2026-04-23)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>교보20호스팩</t>
+          <t>세미티에스</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
@@ -6759,30 +6759,46 @@
           <t>FY24</t>
         </is>
       </c>
-      <c r="F116" s="7" t="inlineStr"/>
-      <c r="G116" s="7" t="inlineStr"/>
-      <c r="H116" s="7" t="inlineStr"/>
-      <c r="I116" s="6" t="inlineStr"/>
+      <c r="F116" s="7" t="inlineStr">
+        <is>
+          <t>20,808</t>
+        </is>
+      </c>
+      <c r="G116" s="7" t="inlineStr">
+        <is>
+          <t>7,337</t>
+        </is>
+      </c>
+      <c r="H116" s="7" t="inlineStr">
+        <is>
+          <t>26,616</t>
+        </is>
+      </c>
+      <c r="I116" s="6" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
       <c r="J116" s="6" t="inlineStr">
         <is>
-          <t>교보</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K116" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-04-02)</t>
+          <t>상장완료 (2026-02-05)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="6" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>케이피항공산업</t>
+          <t>교보20호스팩</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
@@ -6792,7 +6808,7 @@
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
@@ -6800,34 +6816,18 @@
           <t>FY24</t>
         </is>
       </c>
-      <c r="F117" s="7" t="inlineStr">
-        <is>
-          <t>49,651</t>
-        </is>
-      </c>
-      <c r="G117" s="7" t="inlineStr">
-        <is>
-          <t>3,018</t>
-        </is>
-      </c>
-      <c r="H117" s="7" t="inlineStr">
-        <is>
-          <t>15,901</t>
-        </is>
-      </c>
-      <c r="I117" s="6" t="inlineStr">
-        <is>
-          <t>우주항공과국방</t>
-        </is>
-      </c>
+      <c r="F117" s="7" t="inlineStr"/>
+      <c r="G117" s="7" t="inlineStr"/>
+      <c r="H117" s="7" t="inlineStr"/>
+      <c r="I117" s="6" t="inlineStr"/>
       <c r="J117" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>교보</t>
         </is>
       </c>
       <c r="K117" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-01-29)</t>
+          <t>상장완료 (2026-04-02)</t>
         </is>
       </c>
     </row>
@@ -6839,7 +6839,7 @@
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>한패스</t>
+          <t>케이피항공산업</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
@@ -6859,44 +6859,44 @@
       </c>
       <c r="F118" s="7" t="inlineStr">
         <is>
-          <t>55,297</t>
+          <t>49,651</t>
         </is>
       </c>
       <c r="G118" s="7" t="inlineStr">
         <is>
-          <t>4,403</t>
+          <t>3,018</t>
         </is>
       </c>
       <c r="H118" s="7" t="inlineStr">
         <is>
-          <t>-28,065</t>
+          <t>15,901</t>
         </is>
       </c>
       <c r="I118" s="6" t="inlineStr">
         <is>
-          <t>IT서비스</t>
+          <t>우주항공과국방</t>
         </is>
       </c>
       <c r="J118" s="6" t="inlineStr">
         <is>
-          <t>한국, 대신</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K118" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-03-25)</t>
+          <t>상장완료 (2026-01-29)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="6" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>신한제18호스팩</t>
+          <t>한패스</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
@@ -6914,30 +6914,46 @@
           <t>FY24</t>
         </is>
       </c>
-      <c r="F119" s="7" t="inlineStr"/>
-      <c r="G119" s="7" t="inlineStr"/>
-      <c r="H119" s="7" t="inlineStr"/>
-      <c r="I119" s="6" t="inlineStr"/>
+      <c r="F119" s="7" t="inlineStr">
+        <is>
+          <t>55,297</t>
+        </is>
+      </c>
+      <c r="G119" s="7" t="inlineStr">
+        <is>
+          <t>4,403</t>
+        </is>
+      </c>
+      <c r="H119" s="7" t="inlineStr">
+        <is>
+          <t>-28,065</t>
+        </is>
+      </c>
+      <c r="I119" s="6" t="inlineStr">
+        <is>
+          <t>IT서비스</t>
+        </is>
+      </c>
       <c r="J119" s="6" t="inlineStr">
         <is>
-          <t>신한</t>
+          <t>한국, 대신</t>
         </is>
       </c>
       <c r="K119" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-04-30)</t>
+          <t>상장완료 (2026-03-25)</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>엔에이치스팩33호</t>
+          <t>신한제18호스팩</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
@@ -6961,24 +6977,24 @@
       <c r="I120" s="6" t="inlineStr"/>
       <c r="J120" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>신한</t>
         </is>
       </c>
       <c r="K120" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-03-27)</t>
+          <t>상장완료 (2026-04-30)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="6" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>신한제17호스팩</t>
+          <t>엔에이치스팩33호</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
@@ -7002,24 +7018,24 @@
       <c r="I121" s="6" t="inlineStr"/>
       <c r="J121" s="6" t="inlineStr">
         <is>
-          <t>신한</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K121" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-04-01)</t>
+          <t>상장완료 (2026-03-27)</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>아이엠바이오로직스</t>
+          <t>신한제17호스팩</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
@@ -7037,34 +7053,18 @@
           <t>FY24</t>
         </is>
       </c>
-      <c r="F122" s="7" t="inlineStr">
-        <is>
-          <t>27,594</t>
-        </is>
-      </c>
-      <c r="G122" s="7" t="inlineStr">
-        <is>
-          <t>-11,884</t>
-        </is>
-      </c>
-      <c r="H122" s="7" t="inlineStr">
-        <is>
-          <t>-77,202</t>
-        </is>
-      </c>
-      <c r="I122" s="6" t="inlineStr">
-        <is>
-          <t>제약</t>
-        </is>
-      </c>
+      <c r="F122" s="7" t="inlineStr"/>
+      <c r="G122" s="7" t="inlineStr"/>
+      <c r="H122" s="7" t="inlineStr"/>
+      <c r="I122" s="6" t="inlineStr"/>
       <c r="J122" s="6" t="inlineStr">
         <is>
-          <t>한국, 신한</t>
+          <t>신한</t>
         </is>
       </c>
       <c r="K122" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-03-20)</t>
+          <t>상장완료 (2026-04-01)</t>
         </is>
       </c>
     </row>
@@ -7076,7 +7076,7 @@
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>에스팀</t>
+          <t>아이엠바이오로직스</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
@@ -7096,232 +7096,232 @@
       </c>
       <c r="F123" s="7" t="inlineStr">
         <is>
-          <t>35,574</t>
+          <t>27,594</t>
         </is>
       </c>
       <c r="G123" s="7" t="inlineStr">
         <is>
-          <t>1,372</t>
+          <t>-11,884</t>
         </is>
       </c>
       <c r="H123" s="7" t="inlineStr">
         <is>
-          <t>12,331</t>
+          <t>-77,202</t>
         </is>
       </c>
       <c r="I123" s="6" t="inlineStr">
         <is>
-          <t>광고</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="J123" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>한국, 신한</t>
         </is>
       </c>
       <c r="K123" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-03-06)</t>
+          <t>상장완료 (2026-03-20)</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="6" t="inlineStr">
         <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>에스팀</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="inlineStr">
+        <is>
+          <t>신규상장</t>
+        </is>
+      </c>
+      <c r="E124" s="6" t="inlineStr">
+        <is>
+          <t>FY24</t>
+        </is>
+      </c>
+      <c r="F124" s="7" t="inlineStr">
+        <is>
+          <t>35,574</t>
+        </is>
+      </c>
+      <c r="G124" s="7" t="inlineStr">
+        <is>
+          <t>1,372</t>
+        </is>
+      </c>
+      <c r="H124" s="7" t="inlineStr">
+        <is>
+          <t>12,331</t>
+        </is>
+      </c>
+      <c r="I124" s="6" t="inlineStr">
+        <is>
+          <t>광고</t>
+        </is>
+      </c>
+      <c r="J124" s="6" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="K124" s="6" t="inlineStr">
+        <is>
+          <t>상장완료 (2026-03-06)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="6" t="inlineStr">
+        <is>
           <t>2026-01-12</t>
         </is>
       </c>
-      <c r="B124" s="6" t="inlineStr">
+      <c r="B125" s="6" t="inlineStr">
         <is>
           <t>케이뱅크</t>
         </is>
       </c>
-      <c r="C124" s="6" t="inlineStr">
+      <c r="C125" s="6" t="inlineStr">
         <is>
           <t>유가</t>
         </is>
       </c>
-      <c r="D124" s="6" t="inlineStr">
+      <c r="D125" s="6" t="inlineStr">
         <is>
           <t>신규상장</t>
         </is>
       </c>
-      <c r="E124" s="6" t="inlineStr">
+      <c r="E125" s="6" t="inlineStr">
         <is>
           <t>FY24</t>
         </is>
       </c>
-      <c r="F124" s="7" t="inlineStr">
+      <c r="F125" s="7" t="inlineStr">
         <is>
           <t>1,228,501</t>
         </is>
       </c>
-      <c r="G124" s="7" t="inlineStr">
+      <c r="G125" s="7" t="inlineStr">
         <is>
           <t>128,053</t>
         </is>
       </c>
-      <c r="H124" s="7" t="inlineStr">
+      <c r="H125" s="7" t="inlineStr">
         <is>
           <t>1,995,845</t>
         </is>
       </c>
-      <c r="I124" s="6" t="inlineStr">
+      <c r="I125" s="6" t="inlineStr">
         <is>
           <t>은행</t>
         </is>
       </c>
-      <c r="J124" s="6" t="inlineStr">
+      <c r="J125" s="6" t="inlineStr">
         <is>
           <t>NH, 삼성</t>
         </is>
       </c>
-      <c r="K124" s="6" t="inlineStr">
+      <c r="K125" s="6" t="inlineStr">
         <is>
           <t>상장완료 (2026-03-05)</t>
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="3" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
         <is>
           <t>■ 철회·미승인  (18건)</t>
         </is>
       </c>
-      <c r="B126" s="4" t="n"/>
-      <c r="C126" s="4" t="n"/>
-      <c r="D126" s="4" t="n"/>
-      <c r="E126" s="4" t="n"/>
-      <c r="F126" s="4" t="n"/>
-      <c r="G126" s="4" t="n"/>
-      <c r="H126" s="4" t="n"/>
-      <c r="I126" s="4" t="n"/>
-      <c r="J126" s="4" t="n"/>
-      <c r="K126" s="4" t="n"/>
-    </row>
-    <row r="127">
-      <c r="A127" s="5" t="inlineStr">
+      <c r="B127" s="4" t="n"/>
+      <c r="C127" s="4" t="n"/>
+      <c r="D127" s="4" t="n"/>
+      <c r="E127" s="4" t="n"/>
+      <c r="F127" s="4" t="n"/>
+      <c r="G127" s="4" t="n"/>
+      <c r="H127" s="4" t="n"/>
+      <c r="I127" s="4" t="n"/>
+      <c r="J127" s="4" t="n"/>
+      <c r="K127" s="4" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
         <is>
           <t>일자</t>
         </is>
       </c>
-      <c r="B127" s="5" t="inlineStr">
+      <c r="B128" s="5" t="inlineStr">
         <is>
           <t>회사명</t>
         </is>
       </c>
-      <c r="C127" s="5" t="inlineStr">
+      <c r="C128" s="5" t="inlineStr">
         <is>
           <t>시장</t>
         </is>
       </c>
-      <c r="D127" s="5" t="inlineStr">
+      <c r="D128" s="5" t="inlineStr">
         <is>
           <t>상장유형</t>
         </is>
       </c>
-      <c r="E127" s="5" t="inlineStr">
+      <c r="E128" s="5" t="inlineStr">
         <is>
           <t>기준연도</t>
         </is>
       </c>
-      <c r="F127" s="5" t="inlineStr">
+      <c r="F128" s="5" t="inlineStr">
         <is>
           <t>매출액</t>
         </is>
       </c>
-      <c r="G127" s="5" t="inlineStr">
+      <c r="G128" s="5" t="inlineStr">
         <is>
           <t>순이익</t>
         </is>
       </c>
-      <c r="H127" s="5" t="inlineStr">
+      <c r="H128" s="5" t="inlineStr">
         <is>
           <t>자기자본</t>
         </is>
       </c>
-      <c r="I127" s="5" t="inlineStr">
+      <c r="I128" s="5" t="inlineStr">
         <is>
           <t>업종</t>
         </is>
       </c>
-      <c r="J127" s="5" t="inlineStr">
+      <c r="J128" s="5" t="inlineStr">
         <is>
           <t>대표주관사</t>
         </is>
       </c>
-      <c r="K127" s="5" t="inlineStr">
+      <c r="K128" s="5" t="inlineStr">
         <is>
           <t>현황</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="6" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="B128" s="6" t="inlineStr">
-        <is>
-          <t>텔레픽스</t>
-        </is>
-      </c>
-      <c r="C128" s="6" t="inlineStr">
-        <is>
-          <t>코스닥</t>
-        </is>
-      </c>
-      <c r="D128" s="6" t="inlineStr">
-        <is>
-          <t>신규상장</t>
-        </is>
-      </c>
-      <c r="E128" s="6" t="inlineStr">
-        <is>
-          <t>FY25</t>
-        </is>
-      </c>
-      <c r="F128" s="7" t="inlineStr">
-        <is>
-          <t>4,896</t>
-        </is>
-      </c>
-      <c r="G128" s="7" t="inlineStr">
-        <is>
-          <t>-16,214</t>
-        </is>
-      </c>
-      <c r="H128" s="7" t="inlineStr">
-        <is>
-          <t>9,146</t>
-        </is>
-      </c>
-      <c r="I128" s="6" t="inlineStr">
-        <is>
-          <t>소프트웨어 개발 및 공급업</t>
-        </is>
-      </c>
-      <c r="J128" s="6" t="inlineStr">
-        <is>
-          <t>미래</t>
-        </is>
-      </c>
-      <c r="K128" s="6" t="inlineStr">
-        <is>
-          <t>심사 철회</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>씨엠디엘</t>
+          <t>텔레픽스</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
@@ -7331,37 +7331,37 @@
       </c>
       <c r="D129" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E129" s="6" t="inlineStr">
         <is>
-          <t>FY24</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="F129" s="7" t="inlineStr">
         <is>
-          <t>39,991</t>
+          <t>4,896</t>
         </is>
       </c>
       <c r="G129" s="7" t="inlineStr">
         <is>
-          <t>3,541</t>
+          <t>-16,214</t>
         </is>
       </c>
       <c r="H129" s="7" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>9,146</t>
         </is>
       </c>
       <c r="I129" s="6" t="inlineStr">
         <is>
-          <t>기타 기초 유기 화학물질 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J129" s="6" t="inlineStr">
         <is>
-          <t>교보</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K129" s="6" t="inlineStr">
@@ -7373,12 +7373,12 @@
     <row r="130">
       <c r="A130" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>모비어스</t>
+          <t>씨엠디엘</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
@@ -7388,37 +7388,37 @@
       </c>
       <c r="D130" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
         <is>
-          <t>FY25</t>
+          <t>FY24</t>
         </is>
       </c>
       <c r="F130" s="7" t="inlineStr">
         <is>
-          <t>31,989</t>
+          <t>39,991</t>
         </is>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
-          <t>-45,307</t>
+          <t>3,541</t>
         </is>
       </c>
       <c r="H130" s="7" t="inlineStr">
         <is>
-          <t>-96,707</t>
+          <t>503</t>
         </is>
       </c>
       <c r="I130" s="6" t="inlineStr">
         <is>
-          <t>컴퓨터 프로그래밍, 시스템 통합 및 관리업</t>
+          <t>기타 기초 유기 화학물질 제조업</t>
         </is>
       </c>
       <c r="J130" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>교보</t>
         </is>
       </c>
       <c r="K130" s="6" t="inlineStr">
@@ -7430,12 +7430,12 @@
     <row r="131">
       <c r="A131" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>넥스트젠바이오</t>
+          <t>모비어스</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
@@ -7450,32 +7450,32 @@
       </c>
       <c r="E131" s="6" t="inlineStr">
         <is>
-          <t>FY24</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="F131" s="7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>31,989</t>
         </is>
       </c>
       <c r="G131" s="7" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>-45,307</t>
         </is>
       </c>
       <c r="H131" s="7" t="inlineStr">
         <is>
-          <t>4,792</t>
+          <t>-96,707</t>
         </is>
       </c>
       <c r="I131" s="6" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>컴퓨터 프로그래밍, 시스템 통합 및 관리업</t>
         </is>
       </c>
       <c r="J131" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K131" s="6" t="inlineStr">
@@ -7487,12 +7487,12 @@
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>파워큐브세미</t>
+          <t>넥스트젠바이오</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
@@ -7507,32 +7507,32 @@
       </c>
       <c r="E132" s="6" t="inlineStr">
         <is>
-          <t>FY25</t>
+          <t>FY24</t>
         </is>
       </c>
       <c r="F132" s="7" t="inlineStr">
         <is>
-          <t>10,341</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
-          <t>-10,837</t>
+          <t>69</t>
         </is>
       </c>
       <c r="H132" s="7" t="inlineStr">
         <is>
-          <t>841</t>
+          <t>4,792</t>
         </is>
       </c>
       <c r="I132" s="6" t="inlineStr">
         <is>
-          <t>반도체 제조업</t>
+          <t>자연과학 및 공학 연구개발업</t>
         </is>
       </c>
       <c r="J132" s="6" t="inlineStr">
         <is>
-          <t>하나, BNK</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K132" s="6" t="inlineStr">
@@ -7544,12 +7544,12 @@
     <row r="133">
       <c r="A133" s="6" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>제이피이노베이션</t>
+          <t>파워큐브세미</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
@@ -7569,27 +7569,27 @@
       </c>
       <c r="F133" s="7" t="inlineStr">
         <is>
-          <t>56,324</t>
+          <t>10,341</t>
         </is>
       </c>
       <c r="G133" s="7" t="inlineStr">
         <is>
-          <t>5,588</t>
+          <t>-10,837</t>
         </is>
       </c>
       <c r="H133" s="7" t="inlineStr">
         <is>
-          <t>3,684</t>
+          <t>841</t>
         </is>
       </c>
       <c r="I133" s="6" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>반도체 제조업</t>
         </is>
       </c>
       <c r="J133" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>하나, BNK</t>
         </is>
       </c>
       <c r="K133" s="6" t="inlineStr">
@@ -7601,12 +7601,12 @@
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>케이솔루션</t>
+          <t>제이피이노베이션</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="D134" s="6" t="inlineStr">
         <is>
-          <t>스팩 존속합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E134" s="6" t="inlineStr">
@@ -7626,27 +7626,27 @@
       </c>
       <c r="F134" s="7" t="inlineStr">
         <is>
-          <t>34,565</t>
+          <t>56,324</t>
         </is>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
-          <t>1,158</t>
+          <t>5,588</t>
         </is>
       </c>
       <c r="H134" s="7" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>3,684</t>
         </is>
       </c>
       <c r="I134" s="6" t="inlineStr">
         <is>
-          <t>차체 및 특장차 제조업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="J134" s="6" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K134" s="6" t="inlineStr">
@@ -7658,12 +7658,12 @@
     <row r="135">
       <c r="A135" s="6" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>디토닉</t>
+          <t>케이솔루션</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
@@ -7673,37 +7673,37 @@
       </c>
       <c r="D135" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 존속합병</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t>FY24</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="F135" s="7" t="inlineStr">
         <is>
-          <t>31,293</t>
+          <t>34,565</t>
         </is>
       </c>
       <c r="G135" s="7" t="inlineStr">
         <is>
-          <t>-1,633</t>
+          <t>1,158</t>
         </is>
       </c>
       <c r="H135" s="7" t="inlineStr">
         <is>
-          <t>-21,926</t>
+          <t>653</t>
         </is>
       </c>
       <c r="I135" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>차체 및 특장차 제조업</t>
         </is>
       </c>
       <c r="J135" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="K135" s="6" t="inlineStr">
@@ -7715,12 +7715,12 @@
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>에스케이팩</t>
+          <t>디토닉</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="D136" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
@@ -7740,27 +7740,27 @@
       </c>
       <c r="F136" s="7" t="inlineStr">
         <is>
-          <t>27,310</t>
+          <t>31,293</t>
         </is>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
-          <t>2,257</t>
+          <t>-1,633</t>
         </is>
       </c>
       <c r="H136" s="7" t="inlineStr">
         <is>
-          <t>3,207</t>
+          <t>-21,926</t>
         </is>
       </c>
       <c r="I136" s="6" t="inlineStr">
         <is>
-          <t>용기 세척, 포장 및 충전기 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J136" s="6" t="inlineStr">
         <is>
-          <t>교보</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K136" s="6" t="inlineStr">
@@ -7772,12 +7772,12 @@
     <row r="137">
       <c r="A137" s="6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>메타넷엑스</t>
+          <t>에스케이팩</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
@@ -7787,7 +7787,7 @@
       </c>
       <c r="D137" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
@@ -7797,27 +7797,27 @@
       </c>
       <c r="F137" s="7" t="inlineStr">
         <is>
-          <t>244,130</t>
+          <t>27,310</t>
         </is>
       </c>
       <c r="G137" s="7" t="inlineStr">
         <is>
-          <t>13,455</t>
+          <t>2,257</t>
         </is>
       </c>
       <c r="H137" s="7" t="inlineStr">
         <is>
-          <t>9,995</t>
+          <t>3,207</t>
         </is>
       </c>
       <c r="I137" s="6" t="inlineStr">
         <is>
-          <t>컴퓨터 프로그래밍, 시스템 통합 및 관리업</t>
+          <t>용기 세척, 포장 및 충전기 제조업</t>
         </is>
       </c>
       <c r="J137" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>교보</t>
         </is>
       </c>
       <c r="K137" s="6" t="inlineStr">
@@ -7829,12 +7829,12 @@
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>무아스</t>
+          <t>메타넷엑스</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="D138" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
@@ -7854,27 +7854,27 @@
       </c>
       <c r="F138" s="7" t="inlineStr">
         <is>
-          <t>41,813</t>
+          <t>244,130</t>
         </is>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
-          <t>3,903</t>
+          <t>13,455</t>
         </is>
       </c>
       <c r="H138" s="7" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>9,995</t>
         </is>
       </c>
       <c r="I138" s="6" t="inlineStr">
         <is>
-          <t>가정용 전기기기 제조업</t>
+          <t>컴퓨터 프로그래밍, 시스템 통합 및 관리업</t>
         </is>
       </c>
       <c r="J138" s="6" t="inlineStr">
         <is>
-          <t>신한</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K138" s="6" t="inlineStr">
@@ -7891,7 +7891,7 @@
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>유빅스테라퓨틱스</t>
+          <t>무아스</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="D139" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E139" s="6" t="inlineStr">
@@ -7911,27 +7911,27 @@
       </c>
       <c r="F139" s="7" t="inlineStr">
         <is>
-          <t>1,071</t>
+          <t>41,813</t>
         </is>
       </c>
       <c r="G139" s="7" t="inlineStr">
         <is>
-          <t>-15,145</t>
+          <t>3,903</t>
         </is>
       </c>
       <c r="H139" s="7" t="inlineStr">
         <is>
-          <t>5,489</t>
+          <t>532</t>
         </is>
       </c>
       <c r="I139" s="6" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>가정용 전기기기 제조업</t>
         </is>
       </c>
       <c r="J139" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>신한</t>
         </is>
       </c>
       <c r="K139" s="6" t="inlineStr">
@@ -7943,12 +7943,12 @@
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>코드잇</t>
+          <t>유빅스테라퓨틱스</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr">
@@ -7968,27 +7968,27 @@
       </c>
       <c r="F140" s="7" t="inlineStr">
         <is>
-          <t>30,747</t>
+          <t>1,071</t>
         </is>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
-          <t>6,652</t>
+          <t>-15,145</t>
         </is>
       </c>
       <c r="H140" s="7" t="inlineStr">
         <is>
-          <t>2,403</t>
+          <t>5,489</t>
         </is>
       </c>
       <c r="I140" s="6" t="inlineStr">
         <is>
-          <t>교육지원 서비스업</t>
+          <t>자연과학 및 공학 연구개발업</t>
         </is>
       </c>
       <c r="J140" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K140" s="6" t="inlineStr">
@@ -8000,12 +8000,12 @@
     <row r="141">
       <c r="A141" s="6" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>한컴인스페이스</t>
+          <t>코드잇</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
@@ -8025,44 +8025,44 @@
       </c>
       <c r="F141" s="7" t="inlineStr">
         <is>
-          <t>23,492</t>
+          <t>30,747</t>
         </is>
       </c>
       <c r="G141" s="7" t="inlineStr">
         <is>
-          <t>-3,104</t>
+          <t>6,652</t>
         </is>
       </c>
       <c r="H141" s="7" t="inlineStr">
         <is>
-          <t>5,815</t>
+          <t>2,403</t>
         </is>
       </c>
       <c r="I141" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>교육지원 서비스업</t>
         </is>
       </c>
       <c r="J141" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K141" s="6" t="inlineStr">
         <is>
-          <t>심사 미승인</t>
+          <t>심사 철회</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="6" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>크몽</t>
+          <t>한컴인스페이스</t>
         </is>
       </c>
       <c r="C142" s="6" t="inlineStr">
@@ -8082,44 +8082,44 @@
       </c>
       <c r="F142" s="7" t="inlineStr">
         <is>
-          <t>48,572</t>
+          <t>23,492</t>
         </is>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
-          <t>3,988</t>
+          <t>-3,104</t>
         </is>
       </c>
       <c r="H142" s="7" t="inlineStr">
         <is>
-          <t>4,930</t>
+          <t>5,815</t>
         </is>
       </c>
       <c r="I142" s="6" t="inlineStr">
         <is>
-          <t>기타 정보 서비스업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J142" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K142" s="6" t="inlineStr">
         <is>
-          <t>심사 철회</t>
+          <t>심사 미승인</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="6" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>한화플러스제6호스팩</t>
+          <t>크몽</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
@@ -8139,27 +8139,27 @@
       </c>
       <c r="F143" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>48,572</t>
         </is>
       </c>
       <c r="G143" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3,988</t>
         </is>
       </c>
       <c r="H143" s="7" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4,930</t>
         </is>
       </c>
       <c r="I143" s="6" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>기타 정보 서비스업</t>
         </is>
       </c>
       <c r="J143" s="6" t="inlineStr">
         <is>
-          <t>한화</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K143" s="6" t="inlineStr">
@@ -8171,17 +8171,17 @@
     <row r="144">
       <c r="A144" s="6" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>에식스솔루션즈</t>
+          <t>한화플러스제6호스팩</t>
         </is>
       </c>
       <c r="C144" s="6" t="inlineStr">
         <is>
-          <t>유가</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D144" s="6" t="inlineStr">
@@ -8196,27 +8196,27 @@
       </c>
       <c r="F144" s="7" t="inlineStr">
         <is>
-          <t>2,461</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H144" s="7" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I144" s="6" t="inlineStr">
         <is>
-          <t>절연선 및 케이블 제조업</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="J144" s="6" t="inlineStr">
         <is>
-          <t>한국, 미래</t>
+          <t>한화</t>
         </is>
       </c>
       <c r="K144" s="6" t="inlineStr">
@@ -8228,55 +8228,112 @@
     <row r="145">
       <c r="A145" s="6" t="inlineStr">
         <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B145" s="6" t="inlineStr">
+        <is>
+          <t>에식스솔루션즈</t>
+        </is>
+      </c>
+      <c r="C145" s="6" t="inlineStr">
+        <is>
+          <t>유가</t>
+        </is>
+      </c>
+      <c r="D145" s="6" t="inlineStr">
+        <is>
+          <t>신규상장</t>
+        </is>
+      </c>
+      <c r="E145" s="6" t="inlineStr">
+        <is>
+          <t>FY24</t>
+        </is>
+      </c>
+      <c r="F145" s="7" t="inlineStr">
+        <is>
+          <t>2,461</t>
+        </is>
+      </c>
+      <c r="G145" s="7" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="H145" s="7" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I145" s="6" t="inlineStr">
+        <is>
+          <t>절연선 및 케이블 제조업</t>
+        </is>
+      </c>
+      <c r="J145" s="6" t="inlineStr">
+        <is>
+          <t>한국, 미래</t>
+        </is>
+      </c>
+      <c r="K145" s="6" t="inlineStr">
+        <is>
+          <t>심사 철회</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="6" t="inlineStr">
+        <is>
           <t>2026-01-23</t>
         </is>
       </c>
-      <c r="B145" s="6" t="inlineStr">
+      <c r="B146" s="6" t="inlineStr">
         <is>
           <t>에코크레이션</t>
         </is>
       </c>
-      <c r="C145" s="6" t="inlineStr">
+      <c r="C146" s="6" t="inlineStr">
         <is>
           <t>코스닥</t>
         </is>
       </c>
-      <c r="D145" s="6" t="inlineStr">
+      <c r="D146" s="6" t="inlineStr">
         <is>
           <t>신규상장</t>
         </is>
       </c>
-      <c r="E145" s="6" t="inlineStr">
+      <c r="E146" s="6" t="inlineStr">
         <is>
           <t>FY24</t>
         </is>
       </c>
-      <c r="F145" s="7" t="inlineStr">
+      <c r="F146" s="7" t="inlineStr">
         <is>
           <t>18,544</t>
         </is>
       </c>
-      <c r="G145" s="7" t="inlineStr">
+      <c r="G146" s="7" t="inlineStr">
         <is>
           <t>-15,634</t>
         </is>
       </c>
-      <c r="H145" s="7" t="inlineStr">
+      <c r="H146" s="7" t="inlineStr">
         <is>
           <t>4,550</t>
         </is>
       </c>
-      <c r="I145" s="6" t="inlineStr">
+      <c r="I146" s="6" t="inlineStr">
         <is>
           <t>일반 목적용 기계 제조업</t>
         </is>
       </c>
-      <c r="J145" s="6" t="inlineStr">
+      <c r="J146" s="6" t="inlineStr">
         <is>
           <t>키움</t>
         </is>
       </c>
-      <c r="K145" s="6" t="inlineStr">
+      <c r="K146" s="6" t="inlineStr">
         <is>
           <t>심사 철회</t>
         </is>
@@ -13199,96 +13256,96 @@
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>다비오</t>
-        </is>
-      </c>
-      <c r="B69" s="6" t="inlineStr">
-        <is>
-          <t>10-07~10-14</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>12,300~16,600</t>
-        </is>
-      </c>
-      <c r="D69" s="7" t="inlineStr">
-        <is>
-          <t>1,000,000</t>
-        </is>
-      </c>
-      <c r="E69" s="7" t="inlineStr">
-        <is>
-          <t>12,300,000,000</t>
-        </is>
-      </c>
-      <c r="F69" s="6" t="inlineStr">
-        <is>
-          <t>26.70배 (PER)</t>
+          <t>셀트릭스</t>
+        </is>
+      </c>
+      <c r="B69" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="C69" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="D69" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="E69" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="F69" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr"/>
       <c r="H69" s="6" t="inlineStr"/>
       <c r="I69" s="6" t="inlineStr"/>
-      <c r="J69" s="6" t="inlineStr">
-        <is>
-          <t>10-19~10-20</t>
+      <c r="J69" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="K69" s="6" t="inlineStr"/>
       <c r="L69" s="6" t="inlineStr"/>
       <c r="M69" s="6" t="inlineStr"/>
-      <c r="N69" s="6" t="inlineStr">
-        <is>
-          <t>대신증권</t>
+      <c r="N69" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="O69" s="6" t="inlineStr"/>
-      <c r="P69" s="7" t="inlineStr">
-        <is>
-          <t>570,105,000</t>
-        </is>
-      </c>
-      <c r="Q69" s="6" t="inlineStr">
-        <is>
-          <t>4.5%</t>
+      <c r="P69" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="Q69" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="R69" s="6" t="inlineStr">
         <is>
-          <t>최초</t>
+          <t>정정</t>
         </is>
       </c>
     </row>
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>인텔리빅스</t>
+          <t>다비오</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>10-12~10-16</t>
+          <t>10-07~10-14</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>7,600~9,000</t>
+          <t>12,300~16,600</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>2,500,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>19,000,000,000</t>
+          <t>12,300,000,000</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>22.02배 (PER)</t>
+          <t>26.70배 (PER)</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr"/>
@@ -13296,7 +13353,7 @@
       <c r="I70" s="6" t="inlineStr"/>
       <c r="J70" s="6" t="inlineStr">
         <is>
-          <t>10-21~10-22</t>
+          <t>10-19~10-20</t>
         </is>
       </c>
       <c r="K70" s="6" t="inlineStr"/>
@@ -13304,18 +13361,18 @@
       <c r="M70" s="6" t="inlineStr"/>
       <c r="N70" s="6" t="inlineStr">
         <is>
-          <t>미래에셋증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="O70" s="6" t="inlineStr"/>
       <c r="P70" s="7" t="inlineStr">
         <is>
-          <t>782,800,000</t>
+          <t>570,105,000</t>
         </is>
       </c>
       <c r="Q70" s="6" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="R70" s="6" t="inlineStr">
@@ -13327,32 +13384,32 @@
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>영광</t>
+          <t>인텔리빅스</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>10-13~10-19</t>
+          <t>10-12~10-16</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>14,000~17,000</t>
+          <t>7,600~9,000</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>2,260,000</t>
+          <t>2,500,000</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>31,640,000,000</t>
+          <t>19,000,000,000</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>11.98배 (EV/EBITDA)</t>
+          <t>22.02배 (PER)</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr"/>
@@ -13360,7 +13417,7 @@
       <c r="I71" s="6" t="inlineStr"/>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>10-22~10-23</t>
+          <t>10-21~10-22</t>
         </is>
       </c>
       <c r="K71" s="6" t="inlineStr"/>
@@ -13368,18 +13425,18 @@
       <c r="M71" s="6" t="inlineStr"/>
       <c r="N71" s="6" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>미래에셋증권</t>
         </is>
       </c>
       <c r="O71" s="6" t="inlineStr"/>
       <c r="P71" s="7" t="inlineStr">
         <is>
-          <t>977,676,000</t>
-        </is>
-      </c>
-      <c r="Q71" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>782,800,000</t>
+        </is>
+      </c>
+      <c r="Q71" s="6" t="inlineStr">
+        <is>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="R71" s="6" t="inlineStr">
@@ -13391,32 +13448,32 @@
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>한화플러스제6호스팩</t>
+          <t>영광</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>10-14~10-15</t>
-        </is>
-      </c>
-      <c r="C72" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>10-13~10-19</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>14,000~17,000</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>6,000,000</t>
+          <t>2,260,000</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>12,000,000,000</t>
-        </is>
-      </c>
-      <c r="F72" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>31,640,000,000</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>11.98배 (EV/EBITDA)</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr"/>
@@ -13424,26 +13481,26 @@
       <c r="I72" s="6" t="inlineStr"/>
       <c r="J72" s="6" t="inlineStr">
         <is>
-          <t>10-20~10-21</t>
+          <t>10-22~10-23</t>
         </is>
       </c>
       <c r="K72" s="6" t="inlineStr"/>
       <c r="L72" s="6" t="inlineStr"/>
       <c r="M72" s="6" t="inlineStr"/>
-      <c r="N72" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="N72" s="6" t="inlineStr">
+        <is>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="O72" s="6" t="inlineStr"/>
-      <c r="P72" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="Q72" s="6" t="inlineStr">
-        <is>
-          <t>3.50%</t>
+      <c r="P72" s="7" t="inlineStr">
+        <is>
+          <t>977,676,000</t>
+        </is>
+      </c>
+      <c r="Q72" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="R72" s="6" t="inlineStr">
@@ -13455,32 +13512,32 @@
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>에이엘로봇</t>
+          <t>한화플러스제6호스팩</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>10-15~10-21</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>15,700~17,600</t>
+          <t>10-14~10-15</t>
+        </is>
+      </c>
+      <c r="C73" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>2,400,000</t>
+          <t>6,000,000</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>37,680,000,000</t>
-        </is>
-      </c>
-      <c r="F73" s="6" t="inlineStr">
-        <is>
-          <t>37.17배 (PER)</t>
+          <t>12,000,000,000</t>
+        </is>
+      </c>
+      <c r="F73" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr"/>
@@ -13488,26 +13545,26 @@
       <c r="I73" s="6" t="inlineStr"/>
       <c r="J73" s="6" t="inlineStr">
         <is>
-          <t>10-26~10-27</t>
+          <t>10-20~10-21</t>
         </is>
       </c>
       <c r="K73" s="6" t="inlineStr"/>
       <c r="L73" s="6" t="inlineStr"/>
       <c r="M73" s="6" t="inlineStr"/>
-      <c r="N73" s="6" t="inlineStr">
-        <is>
-          <t>대신증권</t>
+      <c r="N73" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="O73" s="6" t="inlineStr"/>
-      <c r="P73" s="7" t="inlineStr">
-        <is>
-          <t>1,160,399,874</t>
+      <c r="P73" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="Q73" s="6" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="R73" s="6" t="inlineStr">
@@ -13519,32 +13576,32 @@
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>아이엠스팩1호</t>
+          <t>에이엘로봇</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>10-19~10-20</t>
-        </is>
-      </c>
-      <c r="C74" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>10-15~10-21</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>15,700~17,600</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>2,400,000</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>10,000,000,000</t>
-        </is>
-      </c>
-      <c r="F74" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>37,680,000,000</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>37.17배 (PER)</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr"/>
@@ -13558,20 +13615,20 @@
       <c r="K74" s="6" t="inlineStr"/>
       <c r="L74" s="6" t="inlineStr"/>
       <c r="M74" s="6" t="inlineStr"/>
-      <c r="N74" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="N74" s="6" t="inlineStr">
+        <is>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="O74" s="6" t="inlineStr"/>
-      <c r="P74" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P74" s="7" t="inlineStr">
+        <is>
+          <t>1,160,399,874</t>
         </is>
       </c>
       <c r="Q74" s="6" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="R74" s="6" t="inlineStr">
@@ -13583,32 +13640,32 @@
     <row r="75" ht="30" customHeight="1">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>옵토닉스</t>
+          <t>아이엠스팩1호</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>10-21~10-27</t>
-        </is>
-      </c>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>10,000~12,000</t>
+          <t>10-19~10-20</t>
+        </is>
+      </c>
+      <c r="C75" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>2,200,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>22,000,000,000</t>
-        </is>
-      </c>
-      <c r="F75" s="6" t="inlineStr">
-        <is>
-          <t>25.27배 (EV/EBITDA)</t>
+          <t>10,000,000,000</t>
+        </is>
+      </c>
+      <c r="F75" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr"/>
@@ -13616,26 +13673,26 @@
       <c r="I75" s="6" t="inlineStr"/>
       <c r="J75" s="6" t="inlineStr">
         <is>
-          <t>11-05~11-06</t>
+          <t>10-26~10-27</t>
         </is>
       </c>
       <c r="K75" s="6" t="inlineStr"/>
       <c r="L75" s="6" t="inlineStr"/>
       <c r="M75" s="6" t="inlineStr"/>
-      <c r="N75" s="6" t="inlineStr">
-        <is>
-          <t>한국투자증권</t>
+      <c r="N75" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="O75" s="6" t="inlineStr"/>
-      <c r="P75" s="7" t="inlineStr">
-        <is>
-          <t>1,133,000,000</t>
+      <c r="P75" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="Q75" s="6" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="R75" s="6" t="inlineStr">
@@ -13647,32 +13704,32 @@
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>동원파츠</t>
+          <t>옵토닉스</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>10-22~10-28</t>
+          <t>10-21~10-27</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>23,000~26,500</t>
+          <t>10,000~12,000</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>2,030,000</t>
+          <t>2,200,000</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>46,690,000,000</t>
+          <t>22,000,000,000</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
         <is>
-          <t>22.91배 (PER)</t>
+          <t>25.27배 (EV/EBITDA)</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr"/>
@@ -13680,7 +13737,7 @@
       <c r="I76" s="6" t="inlineStr"/>
       <c r="J76" s="6" t="inlineStr">
         <is>
-          <t>11-02~11-03</t>
+          <t>11-05~11-06</t>
         </is>
       </c>
       <c r="K76" s="6" t="inlineStr"/>
@@ -13688,18 +13745,18 @@
       <c r="M76" s="6" t="inlineStr"/>
       <c r="N76" s="6" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="O76" s="6" t="inlineStr"/>
       <c r="P76" s="7" t="inlineStr">
         <is>
-          <t>1,430,699,820</t>
+          <t>1,133,000,000</t>
         </is>
       </c>
       <c r="Q76" s="6" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="R76" s="6" t="inlineStr">
@@ -13711,7 +13768,7 @@
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>넥스아이</t>
+          <t>동원파츠</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
@@ -13721,22 +13778,22 @@
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>10,500~13,000</t>
+          <t>23,000~26,500</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>2,030,000</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>52,500,000,000</t>
+          <t>46,690,000,000</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>19.15배 (PER)</t>
+          <t>22.91배 (PER)</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr"/>
@@ -13744,7 +13801,7 @@
       <c r="I77" s="6" t="inlineStr"/>
       <c r="J77" s="6" t="inlineStr">
         <is>
-          <t>11-03~11-04</t>
+          <t>11-02~11-03</t>
         </is>
       </c>
       <c r="K77" s="6" t="inlineStr"/>
@@ -13752,18 +13809,18 @@
       <c r="M77" s="6" t="inlineStr"/>
       <c r="N77" s="6" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="O77" s="6" t="inlineStr"/>
       <c r="P77" s="7" t="inlineStr">
         <is>
-          <t>2,407,500,000</t>
+          <t>1,430,699,820</t>
         </is>
       </c>
       <c r="Q77" s="6" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="R77" s="6" t="inlineStr">
@@ -13775,32 +13832,32 @@
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>하나에어로다이내믹스</t>
+          <t>넥스아이</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>11-02~11-06</t>
+          <t>10-22~10-28</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>4,700~5,700</t>
+          <t>10,500~13,000</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>4,400,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>20,680,000,000</t>
+          <t>52,500,000,000</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr">
         <is>
-          <t>17.89배 (EV/EBITDA)</t>
+          <t>19.15배 (PER)</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr"/>
@@ -13808,7 +13865,7 @@
       <c r="I78" s="6" t="inlineStr"/>
       <c r="J78" s="6" t="inlineStr">
         <is>
-          <t>11-10~11-11</t>
+          <t>11-03~11-04</t>
         </is>
       </c>
       <c r="K78" s="6" t="inlineStr"/>
@@ -13816,18 +13873,18 @@
       <c r="M78" s="6" t="inlineStr"/>
       <c r="N78" s="6" t="inlineStr">
         <is>
-          <t>아이비케이투자증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="O78" s="6" t="inlineStr"/>
       <c r="P78" s="7" t="inlineStr">
         <is>
-          <t>850,000,000</t>
-        </is>
-      </c>
-      <c r="Q78" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>2,407,500,000</t>
+        </is>
+      </c>
+      <c r="Q78" s="6" t="inlineStr">
+        <is>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="R78" s="6" t="inlineStr">
@@ -13839,54 +13896,54 @@
     <row r="79" ht="30" customHeight="1">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>셀트릭스</t>
-        </is>
-      </c>
-      <c r="B79" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="C79" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="D79" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="E79" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="F79" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>하나에어로다이내믹스</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>11-02~11-06</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>4,700~5,700</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="inlineStr">
+        <is>
+          <t>4,400,000</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>20,680,000,000</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>17.89배 (EV/EBITDA)</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr"/>
       <c r="H79" s="6" t="inlineStr"/>
       <c r="I79" s="6" t="inlineStr"/>
-      <c r="J79" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="J79" s="6" t="inlineStr">
+        <is>
+          <t>11-10~11-11</t>
         </is>
       </c>
       <c r="K79" s="6" t="inlineStr"/>
       <c r="L79" s="6" t="inlineStr"/>
       <c r="M79" s="6" t="inlineStr"/>
-      <c r="N79" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="N79" s="6" t="inlineStr">
+        <is>
+          <t>아이비케이투자증권</t>
         </is>
       </c>
       <c r="O79" s="6" t="inlineStr"/>
-      <c r="P79" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P79" s="7" t="inlineStr">
+        <is>
+          <t>850,000,000</t>
         </is>
       </c>
       <c r="Q79" s="18" t="inlineStr">
@@ -13903,59 +13960,59 @@
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>솔리스</t>
-        </is>
-      </c>
-      <c r="B80" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="C80" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="D80" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="E80" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="F80" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>케이엠에프</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>11-16~11-20</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>15,000~17,800</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>2,000,000</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>30,000,000,000</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>18.53배 (PER)</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr"/>
       <c r="H80" s="6" t="inlineStr"/>
       <c r="I80" s="6" t="inlineStr"/>
-      <c r="J80" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="J80" s="6" t="inlineStr">
+        <is>
+          <t>11-24~11-25</t>
         </is>
       </c>
       <c r="K80" s="6" t="inlineStr"/>
       <c r="L80" s="6" t="inlineStr"/>
       <c r="M80" s="6" t="inlineStr"/>
-      <c r="N80" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="N80" s="6" t="inlineStr">
+        <is>
+          <t>아이비케이투자증권</t>
         </is>
       </c>
       <c r="O80" s="6" t="inlineStr"/>
-      <c r="P80" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="Q80" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P80" s="7" t="inlineStr">
+        <is>
+          <t>927,000,000</t>
+        </is>
+      </c>
+      <c r="Q80" s="6" t="inlineStr">
+        <is>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="R80" s="6" t="inlineStr">
@@ -13967,7 +14024,7 @@
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>디티에스</t>
+          <t>솔리스</t>
         </is>
       </c>
       <c r="B81" s="18" t="inlineStr">
@@ -14024,14 +14081,14 @@
       </c>
       <c r="R81" s="6" t="inlineStr">
         <is>
-          <t>신고서 대기</t>
+          <t>최초</t>
         </is>
       </c>
     </row>
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>에이엔에이치스트럭쳐</t>
+          <t>디티에스</t>
         </is>
       </c>
       <c r="B82" s="18" t="inlineStr">
@@ -14095,7 +14152,7 @@
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>이에스티</t>
+          <t>에이엔에이치스트럭쳐</t>
         </is>
       </c>
       <c r="B83" s="18" t="inlineStr">
@@ -14159,7 +14216,7 @@
     <row r="84" ht="30" customHeight="1">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>영광와이케이엠씨</t>
+          <t>이에스티</t>
         </is>
       </c>
       <c r="B84" s="18" t="inlineStr">
@@ -14223,7 +14280,7 @@
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>케이엠에프</t>
+          <t>영광와이케이엠씨</t>
         </is>
       </c>
       <c r="B85" s="18" t="inlineStr">
@@ -14727,7 +14784,7 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>0</v>
@@ -14859,30 +14916,30 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>아이비케이투자증권</t>
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>135,135,239,540</t>
+          <t>150,280,000,000</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>아이비케이투자증권</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>120,280,000,000</t>
+          <t>135,135,239,540</t>
         </is>
       </c>
     </row>

--- a/IPO_analysis.xlsx
+++ b/IPO_analysis.xlsx
@@ -618,7 +618,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>기준일 2026-10-02 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
+          <t>기준일 2026-10-03 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
         </is>
       </c>
     </row>

--- a/IPO_analysis.xlsx
+++ b/IPO_analysis.xlsx
@@ -618,7 +618,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>기준일 2026-10-03 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
+          <t>기준일 2026-10-04 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
         </is>
       </c>
     </row>

--- a/IPO_analysis.xlsx
+++ b/IPO_analysis.xlsx
@@ -618,7 +618,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>기준일 2026-10-04 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
+          <t>기준일 2026-10-05 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
         </is>
       </c>
     </row>

--- a/IPO_analysis.xlsx
+++ b/IPO_analysis.xlsx
@@ -618,14 +618,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>기준일 2026-10-05 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
+          <t>기준일 2026-10-06 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>■ 심사 신청(진행중)  (47건)</t>
+          <t>■ 심사 신청(진행중)  (46건)</t>
         </is>
       </c>
       <c r="B4" s="4" t="n"/>
@@ -1746,17 +1746,17 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>우리투자제1호스팩</t>
+          <t>에스텍시스템</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>유가</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -1769,17 +1769,29 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr"/>
-      <c r="G25" s="7" t="inlineStr"/>
-      <c r="H25" s="7" t="inlineStr"/>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>975,224</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>24,647</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>237,182</t>
+        </is>
+      </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>경비, 경호 및 탐정업</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>주식회사 우리투자증권</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
@@ -1791,17 +1803,17 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>에스텍시스템</t>
+          <t>범한메카텍</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>유가</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
@@ -1816,27 +1828,27 @@
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>975,224</t>
+          <t>339,209</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>24,647</t>
+          <t>-18,141</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>237,182</t>
+          <t>265,955</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>경비, 경호 및 탐정업</t>
+          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
         </is>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>유진, NH</t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr">
@@ -1853,7 +1865,7 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>범한메카텍</t>
+          <t>케이티이</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -1873,27 +1885,27 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>339,209</t>
+          <t>173,901</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>-18,141</t>
+          <t>14,243</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>265,955</t>
+          <t>94,928</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
+          <t>전동기, 발전기 및 전기 변환 · 공급 · 제어 장치 제조업</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>유진, NH</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
@@ -1905,12 +1917,12 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>케이티이</t>
+          <t>데스틴파워</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -1930,17 +1942,17 @@
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>173,901</t>
+          <t>29,851</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>14,243</t>
+          <t>5,852</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>94,928</t>
+          <t>-30,114</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
@@ -1950,7 +1962,7 @@
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K28" s="6" t="inlineStr">
@@ -1967,7 +1979,7 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>데스틴파워</t>
+          <t>유림테크</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
@@ -1987,27 +1999,27 @@
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>29,851</t>
+          <t>102,586</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>5,852</t>
+          <t>-18,278</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>-30,114</t>
+          <t>-4,832</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>전동기, 발전기 및 전기 변환 · 공급 · 제어 장치 제조업</t>
+          <t>자동차 신품 부품 제조업</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
@@ -2019,12 +2031,12 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>유림테크</t>
+          <t>이노보테라퓨틱스</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -2044,27 +2056,27 @@
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>102,586</t>
+          <t>209</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>-18,278</t>
+          <t>-5,429</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>-4,832</t>
+          <t>-53,200</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>자동차 신품 부품 제조업</t>
+          <t>의약품 제조업</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
@@ -2076,17 +2088,17 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>이노보테라퓨틱스</t>
+          <t>에스에프씨</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>유가</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -2101,27 +2113,27 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>160,792</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>-5,429</t>
+          <t>25,509</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>-53,200</t>
+          <t>243,562</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>의약품 제조업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>미래, 한국</t>
         </is>
       </c>
       <c r="K31" s="6" t="inlineStr">
@@ -2133,17 +2145,17 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>에스에프씨</t>
+          <t>아델</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>유가</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
@@ -2158,27 +2170,27 @@
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>160,792</t>
+          <t>62,057</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>25,509</t>
+          <t>-64,210</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>243,562</t>
+          <t>-80,776</t>
         </is>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>그외 기타 전문, 과학 및 기술 서비스업</t>
         </is>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>미래, 한국</t>
+          <t>삼성, 미래</t>
         </is>
       </c>
       <c r="K32" s="6" t="inlineStr">
@@ -2190,12 +2202,12 @@
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>아델</t>
+          <t>에버온</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -2215,27 +2227,27 @@
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>62,057</t>
+          <t>65,225</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>-64,210</t>
+          <t>-3,606</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>-80,776</t>
+          <t>54,955</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>그외 기타 전문, 과학 및 기술 서비스업</t>
+          <t>전기업</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>삼성, 미래</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
@@ -2247,12 +2259,12 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>에버온</t>
+          <t>엔키화이트햇</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -2272,27 +2284,27 @@
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>65,225</t>
+          <t>14,176</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>-3,606</t>
+          <t>-3,211</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>54,955</t>
+          <t>8,338</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>전기업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>신영</t>
         </is>
       </c>
       <c r="K34" s="6" t="inlineStr">
@@ -2304,12 +2316,12 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>엔키화이트햇</t>
+          <t>씨아이에스케미칼</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
@@ -2329,27 +2341,27 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>14,176</t>
+          <t>15,985</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>-3,211</t>
+          <t>-11,440</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>8,338</t>
+          <t>23,706</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>기초 화학물질 제조업</t>
         </is>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>신영</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="K35" s="6" t="inlineStr">
@@ -2361,12 +2373,12 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>씨아이에스케미칼</t>
+          <t>엠디에스코리아</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
@@ -2386,27 +2398,27 @@
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>15,985</t>
+          <t>97,972</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>-11,440</t>
+          <t>6,512</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>23,706</t>
+          <t>53,818</t>
         </is>
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>기초 화학물질 제조업</t>
+          <t>기타 식품 제조업</t>
         </is>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K36" s="6" t="inlineStr">
@@ -2418,12 +2430,12 @@
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>엠디에스코리아</t>
+          <t>동승</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -2443,27 +2455,27 @@
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>97,972</t>
+          <t>78,625</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>6,512</t>
+          <t>14,525</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>53,818</t>
+          <t>5,438</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>기타 식품 제조업</t>
+          <t>부동산 임대 및 공급업</t>
         </is>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
@@ -2480,7 +2492,7 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>동승</t>
+          <t>에프엠더블유</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -2490,7 +2502,7 @@
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -2500,27 +2512,27 @@
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>78,625</t>
+          <t>30,282</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>14,525</t>
+          <t>4,762</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>5,438</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>부동산 임대 및 공급업</t>
+          <t>기타 식품 제조업</t>
         </is>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>유진</t>
         </is>
       </c>
       <c r="K38" s="6" t="inlineStr">
@@ -2532,22 +2544,22 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>에프엠더블유</t>
+          <t>소노인터내셔널</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>유가</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
@@ -2557,27 +2569,27 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>30,282</t>
+          <t>2,093,051</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>4,762</t>
+          <t>-148,064</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>852,372</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>기타 식품 제조업</t>
+          <t>일반 및 생활 숙박시설 운영업</t>
         </is>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>유진</t>
+          <t>대신, 미래</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr">
@@ -2589,17 +2601,17 @@
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>소노인터내셔널</t>
+          <t>싸이몬</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>유가</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
@@ -2614,27 +2626,27 @@
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>2,093,051</t>
+          <t>48,695</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>-148,064</t>
+          <t>15,714</t>
         </is>
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>852,372</t>
+          <t>61,761</t>
         </is>
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>일반 및 생활 숙박시설 운영업</t>
+          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업</t>
         </is>
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>대신, 미래</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K40" s="6" t="inlineStr">
@@ -2646,12 +2658,12 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>싸이몬</t>
+          <t>바이다</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -2671,27 +2683,27 @@
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>48,695</t>
+          <t>14,432</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>15,714</t>
+          <t>-3,951</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>61,761</t>
+          <t>15,108</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업</t>
+          <t>전자부품 제조업</t>
         </is>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
@@ -2703,12 +2715,12 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>바이다</t>
+          <t>아이알큐더스</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -2728,27 +2740,27 @@
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>14,432</t>
+          <t>10,231</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>-3,951</t>
+          <t>-986</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>15,108</t>
+          <t>1,800</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>전자부품 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="K42" s="6" t="inlineStr">
@@ -2760,12 +2772,12 @@
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>아이알큐더스</t>
+          <t>씨엔티테크</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -2785,17 +2797,17 @@
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>10,231</t>
+          <t>27,015</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>-986</t>
+          <t>3,987</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>1,800</t>
+          <t>2,613</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
@@ -2805,7 +2817,7 @@
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>한화, 하나</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
@@ -2822,7 +2834,7 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>씨엔티테크</t>
+          <t>제이앤티지</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -2842,27 +2854,27 @@
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>27,015</t>
+          <t>72,378</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>3,987</t>
+          <t>9,904</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>2,613</t>
+          <t>6,743</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>전자부품 제조업</t>
         </is>
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>한화, 하나</t>
+          <t>대신, NH</t>
         </is>
       </c>
       <c r="K44" s="6" t="inlineStr">
@@ -2874,12 +2886,12 @@
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>제이앤티지</t>
+          <t>인터엑스</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -2899,27 +2911,27 @@
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>72,378</t>
+          <t>8,645</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>9,904</t>
+          <t>-20,272</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>6,743</t>
+          <t>4,530</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>전자부품 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>대신, NH</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K45" s="6" t="inlineStr">
@@ -2931,12 +2943,12 @@
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>인터엑스</t>
+          <t>삼홍아크튜리온</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -2956,27 +2968,27 @@
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>8,645</t>
+          <t>26,162</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>-20,272</t>
+          <t>-10,314</t>
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>4,530</t>
+          <t>6,369</t>
         </is>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
         </is>
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>삼성, 미래</t>
         </is>
       </c>
       <c r="K46" s="6" t="inlineStr">
@@ -2988,12 +3000,12 @@
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>삼홍아크튜리온</t>
+          <t>넥스트에어로스페이스</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -3013,27 +3025,27 @@
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>26,162</t>
+          <t>12,084</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>-10,314</t>
+          <t>-17,270</t>
         </is>
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>6,369</t>
+          <t>6,158</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
+          <t>유인 항공기, 항공우주선 및 보조장치 제조업</t>
         </is>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>삼성, 미래</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K47" s="6" t="inlineStr">
@@ -3050,7 +3062,7 @@
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>넥스트에어로스페이스</t>
+          <t>비앤비코리아</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -3070,27 +3082,27 @@
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>12,084</t>
+          <t>141,169</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>-17,270</t>
+          <t>21,406</t>
         </is>
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>6,158</t>
+          <t>43,932</t>
         </is>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
-          <t>유인 항공기, 항공우주선 및 보조장치 제조업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K48" s="6" t="inlineStr">
@@ -3102,12 +3114,12 @@
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>비앤비코리아</t>
+          <t>오토핸즈</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -3117,7 +3129,7 @@
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
@@ -3127,22 +3139,22 @@
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>141,169</t>
+          <t>238,564</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>21,406</t>
+          <t>6,047</t>
         </is>
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>43,932</t>
+          <t>6,129</t>
         </is>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>자동차 판매업</t>
         </is>
       </c>
       <c r="J49" s="6" t="inlineStr">
@@ -3159,12 +3171,12 @@
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>오토핸즈</t>
+          <t>아이벡스메디칼시스템즈</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -3174,7 +3186,7 @@
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
@@ -3184,27 +3196,27 @@
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>238,564</t>
+          <t>15,282</t>
         </is>
       </c>
       <c r="G50" s="7" t="inlineStr">
         <is>
-          <t>6,047</t>
+          <t>-7,227</t>
         </is>
       </c>
       <c r="H50" s="7" t="inlineStr">
         <is>
-          <t>6,129</t>
+          <t>744</t>
         </is>
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
-          <t>자동차 판매업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="J50" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K50" s="6" t="inlineStr">
@@ -3216,12 +3228,12 @@
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>아이벡스메디칼시스템즈</t>
+          <t>피지티</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
@@ -3241,27 +3253,27 @@
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>15,282</t>
+          <t>40,141</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr">
         <is>
-          <t>-7,227</t>
+          <t>-69,722</t>
         </is>
       </c>
       <c r="H51" s="7" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>6,029</t>
         </is>
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K51" s="6" t="inlineStr">
@@ -3270,134 +3282,122 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="inlineStr">
-        <is>
-          <t>피지티</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>■ 심사 승인  (71건)</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="n"/>
+      <c r="C53" s="4" t="n"/>
+      <c r="D53" s="4" t="n"/>
+      <c r="E53" s="4" t="n"/>
+      <c r="F53" s="4" t="n"/>
+      <c r="G53" s="4" t="n"/>
+      <c r="H53" s="4" t="n"/>
+      <c r="I53" s="4" t="n"/>
+      <c r="J53" s="4" t="n"/>
+      <c r="K53" s="4" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>일자</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>회사명</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>시장</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr">
+        <is>
+          <t>상장유형</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>기준연도</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>자기자본</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>업종</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>대표주관사</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="inlineStr">
+        <is>
+          <t>현황</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>우리투자제1호스팩</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
         <is>
           <t>코스닥</t>
         </is>
       </c>
-      <c r="D52" s="6" t="inlineStr">
+      <c r="D55" s="6" t="inlineStr">
         <is>
           <t>신규상장</t>
         </is>
       </c>
-      <c r="E52" s="6" t="inlineStr">
+      <c r="E55" s="6" t="inlineStr">
         <is>
           <t>FY25</t>
         </is>
       </c>
-      <c r="F52" s="7" t="inlineStr">
-        <is>
-          <t>40,141</t>
-        </is>
-      </c>
-      <c r="G52" s="7" t="inlineStr">
-        <is>
-          <t>-69,722</t>
-        </is>
-      </c>
-      <c r="H52" s="7" t="inlineStr">
-        <is>
-          <t>6,029</t>
-        </is>
-      </c>
-      <c r="I52" s="6" t="inlineStr">
-        <is>
-          <t>기타 화학제품 제조업</t>
-        </is>
-      </c>
-      <c r="J52" s="6" t="inlineStr">
-        <is>
-          <t>한국</t>
-        </is>
-      </c>
-      <c r="K52" s="6" t="inlineStr">
-        <is>
-          <t>예심 진행중</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>■ 심사 승인  (70건)</t>
-        </is>
-      </c>
-      <c r="B54" s="4" t="n"/>
-      <c r="C54" s="4" t="n"/>
-      <c r="D54" s="4" t="n"/>
-      <c r="E54" s="4" t="n"/>
-      <c r="F54" s="4" t="n"/>
-      <c r="G54" s="4" t="n"/>
-      <c r="H54" s="4" t="n"/>
-      <c r="I54" s="4" t="n"/>
-      <c r="J54" s="4" t="n"/>
-      <c r="K54" s="4" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="5" t="inlineStr">
-        <is>
-          <t>일자</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>회사명</t>
-        </is>
-      </c>
-      <c r="C55" s="5" t="inlineStr">
-        <is>
-          <t>시장</t>
-        </is>
-      </c>
-      <c r="D55" s="5" t="inlineStr">
-        <is>
-          <t>상장유형</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>기준연도</t>
-        </is>
-      </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="inlineStr">
-        <is>
-          <t>순이익</t>
-        </is>
-      </c>
-      <c r="H55" s="5" t="inlineStr">
-        <is>
-          <t>자기자본</t>
-        </is>
-      </c>
-      <c r="I55" s="5" t="inlineStr">
-        <is>
-          <t>업종</t>
-        </is>
-      </c>
-      <c r="J55" s="5" t="inlineStr">
-        <is>
-          <t>대표주관사</t>
-        </is>
-      </c>
-      <c r="K55" s="5" t="inlineStr">
-        <is>
-          <t>현황</t>
+      <c r="F55" s="7" t="inlineStr"/>
+      <c r="G55" s="7" t="inlineStr"/>
+      <c r="H55" s="7" t="inlineStr"/>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>기타 금융업</t>
+        </is>
+      </c>
+      <c r="J55" s="6" t="inlineStr">
+        <is>
+          <t>주식회사 우리투자증권</t>
+        </is>
+      </c>
+      <c r="K55" s="6" t="inlineStr">
+        <is>
+          <t>상장전</t>
         </is>
       </c>
     </row>
@@ -8350,7 +8350,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R91"/>
+  <dimension ref="A1:R92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -12432,7 +12432,7 @@
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>■ 공모 진행 (예심 승인법인)  (31건)</t>
+          <t>■ 공모 진행 (예심 승인법인)  (32건)</t>
         </is>
       </c>
       <c r="B56" s="4" t="n"/>
@@ -12696,7 +12696,7 @@
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>156,428,800,000</t>
+          <t>201,091,000,000</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
@@ -12704,9 +12704,17 @@
           <t>27.13배 (EV/EBITDA)</t>
         </is>
       </c>
-      <c r="G60" s="6" t="inlineStr"/>
-      <c r="H60" s="6" t="inlineStr"/>
-      <c r="I60" s="6" t="inlineStr"/>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>90,500</t>
+        </is>
+      </c>
+      <c r="H60" s="6" t="n">
+        <v>388.84</v>
+      </c>
+      <c r="I60" s="6" t="n">
+        <v>2367</v>
+      </c>
       <c r="J60" s="6" t="inlineStr">
         <is>
           <t>10-07~10-08</t>
@@ -12737,7 +12745,7 @@
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
-          <t>정정</t>
+          <t>발행조건확정</t>
         </is>
       </c>
     </row>
@@ -12936,32 +12944,32 @@
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>에스케이증권제14호기업인수목적</t>
+          <t>다비오</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>10-12~10-13</t>
-        </is>
-      </c>
-      <c r="C64" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>10-07~10-14</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>12,300~16,600</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>6,500,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>13,000,000,000</t>
-        </is>
-      </c>
-      <c r="F64" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>12,300,000,000</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>26.70배 (PER)</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr"/>
@@ -12969,26 +12977,26 @@
       <c r="I64" s="6" t="inlineStr"/>
       <c r="J64" s="6" t="inlineStr">
         <is>
-          <t>10-15~10-16</t>
+          <t>10-19~10-20</t>
         </is>
       </c>
       <c r="K64" s="6" t="inlineStr"/>
       <c r="L64" s="6" t="inlineStr"/>
       <c r="M64" s="6" t="inlineStr"/>
-      <c r="N64" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="N64" s="6" t="inlineStr">
+        <is>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="O64" s="6" t="inlineStr"/>
-      <c r="P64" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P64" s="7" t="inlineStr">
+        <is>
+          <t>570,105,000</t>
         </is>
       </c>
       <c r="Q64" s="6" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="R64" s="6" t="inlineStr">
@@ -13000,32 +13008,32 @@
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>크리에이츠</t>
+          <t>에스케이증권제14호기업인수목적</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>10-12~10-16</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>15,000~18,000</t>
+          <t>10-12~10-13</t>
+        </is>
+      </c>
+      <c r="C65" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>1,400,000</t>
+          <t>6,500,000</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>21,000,000,000</t>
-        </is>
-      </c>
-      <c r="F65" s="6" t="inlineStr">
-        <is>
-          <t>19.15배 (PER)</t>
+          <t>13,000,000,000</t>
+        </is>
+      </c>
+      <c r="F65" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr"/>
@@ -13033,26 +13041,26 @@
       <c r="I65" s="6" t="inlineStr"/>
       <c r="J65" s="6" t="inlineStr">
         <is>
-          <t>10-20~10-21</t>
+          <t>10-15~10-16</t>
         </is>
       </c>
       <c r="K65" s="6" t="inlineStr"/>
       <c r="L65" s="6" t="inlineStr"/>
       <c r="M65" s="6" t="inlineStr"/>
-      <c r="N65" s="6" t="inlineStr">
-        <is>
-          <t>삼성증권</t>
+      <c r="N65" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="O65" s="6" t="inlineStr"/>
-      <c r="P65" s="7" t="inlineStr">
-        <is>
-          <t>865,200,000</t>
+      <c r="P65" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="Q65" s="6" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="R65" s="6" t="inlineStr">
@@ -13064,32 +13072,32 @@
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>래블업</t>
+          <t>크리에이츠</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>10-13~10-19</t>
+          <t>10-12~10-16</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>19,000~22,000</t>
+          <t>15,000~18,000</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>2,180,000</t>
+          <t>1,400,000</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>41,420,000,000</t>
+          <t>21,000,000,000</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>33.6배 (PER)</t>
+          <t>19.15배 (PER)</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr"/>
@@ -13097,7 +13105,7 @@
       <c r="I66" s="6" t="inlineStr"/>
       <c r="J66" s="6" t="inlineStr">
         <is>
-          <t>10-22~10-23</t>
+          <t>10-20~10-21</t>
         </is>
       </c>
       <c r="K66" s="6" t="inlineStr"/>
@@ -13105,18 +13113,18 @@
       <c r="M66" s="6" t="inlineStr"/>
       <c r="N66" s="6" t="inlineStr">
         <is>
-          <t>NH투자증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="O66" s="6" t="inlineStr"/>
       <c r="P66" s="7" t="inlineStr">
         <is>
-          <t>1,908,899,000</t>
+          <t>865,200,000</t>
         </is>
       </c>
       <c r="Q66" s="6" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="R66" s="6" t="inlineStr">
@@ -13128,32 +13136,32 @@
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>엠비디</t>
+          <t>래블업</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>10-16~10-22</t>
+          <t>10-13~10-19</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>9,600~11,700</t>
+          <t>19,000~22,000</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>2,180,000</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>19,200,000,000</t>
+          <t>41,420,000,000</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>26.87배 (PER)</t>
+          <t>33.6배 (PER)</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr"/>
@@ -13161,7 +13169,7 @@
       <c r="I67" s="6" t="inlineStr"/>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t>10-28~10-29</t>
+          <t>10-22~10-23</t>
         </is>
       </c>
       <c r="K67" s="6" t="inlineStr"/>
@@ -13169,18 +13177,18 @@
       <c r="M67" s="6" t="inlineStr"/>
       <c r="N67" s="6" t="inlineStr">
         <is>
-          <t>하나증권</t>
+          <t>NH투자증권</t>
         </is>
       </c>
       <c r="O67" s="6" t="inlineStr"/>
       <c r="P67" s="7" t="inlineStr">
         <is>
-          <t>988,800,000</t>
+          <t>1,908,899,000</t>
         </is>
       </c>
       <c r="Q67" s="6" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="R67" s="6" t="inlineStr">
@@ -13192,40 +13200,40 @@
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>바로팜</t>
-        </is>
-      </c>
-      <c r="B68" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>16,400~20,200</t>
+          <t>한화플러스제6호스팩</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>10-14~10-15</t>
+        </is>
+      </c>
+      <c r="C68" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>1,780,000</t>
+          <t>6,000,000</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>29,192,000,000</t>
-        </is>
-      </c>
-      <c r="F68" s="6" t="inlineStr">
-        <is>
-          <t>24.95배 (PER)</t>
+          <t>12,000,000,000</t>
+        </is>
+      </c>
+      <c r="F68" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr"/>
       <c r="H68" s="6" t="inlineStr"/>
       <c r="I68" s="6" t="inlineStr"/>
-      <c r="J68" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="J68" s="6" t="inlineStr">
+        <is>
+          <t>10-20~10-21</t>
         </is>
       </c>
       <c r="K68" s="6" t="inlineStr"/>
@@ -13242,9 +13250,9 @@
           <t>수집예정</t>
         </is>
       </c>
-      <c r="Q68" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="Q68" s="6" t="inlineStr">
+        <is>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="R68" s="6" t="inlineStr">
@@ -13256,59 +13264,59 @@
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>셀트릭스</t>
-        </is>
-      </c>
-      <c r="B69" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="C69" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="D69" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="E69" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="F69" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>엠비디</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="inlineStr">
+        <is>
+          <t>10-16~10-22</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>9,600~11,700</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>2,000,000</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>19,200,000,000</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>26.87배 (PER)</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr"/>
       <c r="H69" s="6" t="inlineStr"/>
       <c r="I69" s="6" t="inlineStr"/>
-      <c r="J69" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="J69" s="6" t="inlineStr">
+        <is>
+          <t>10-28~10-29</t>
         </is>
       </c>
       <c r="K69" s="6" t="inlineStr"/>
       <c r="L69" s="6" t="inlineStr"/>
       <c r="M69" s="6" t="inlineStr"/>
-      <c r="N69" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="N69" s="6" t="inlineStr">
+        <is>
+          <t>하나증권</t>
         </is>
       </c>
       <c r="O69" s="6" t="inlineStr"/>
-      <c r="P69" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="Q69" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P69" s="7" t="inlineStr">
+        <is>
+          <t>988,800,000</t>
+        </is>
+      </c>
+      <c r="Q69" s="6" t="inlineStr">
+        <is>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="R69" s="6" t="inlineStr">
@@ -13320,160 +13328,160 @@
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>다비오</t>
-        </is>
-      </c>
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>10-07~10-14</t>
+          <t>바로팜</t>
+        </is>
+      </c>
+      <c r="B70" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>12,300~16,600</t>
+          <t>16,400~20,200</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>1,000,000</t>
+          <t>1,780,000</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>12,300,000,000</t>
+          <t>29,192,000,000</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>26.70배 (PER)</t>
+          <t>24.95배 (PER)</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr"/>
       <c r="H70" s="6" t="inlineStr"/>
       <c r="I70" s="6" t="inlineStr"/>
-      <c r="J70" s="6" t="inlineStr">
-        <is>
-          <t>10-19~10-20</t>
+      <c r="J70" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="K70" s="6" t="inlineStr"/>
       <c r="L70" s="6" t="inlineStr"/>
       <c r="M70" s="6" t="inlineStr"/>
-      <c r="N70" s="6" t="inlineStr">
-        <is>
-          <t>대신증권</t>
+      <c r="N70" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="O70" s="6" t="inlineStr"/>
-      <c r="P70" s="7" t="inlineStr">
-        <is>
-          <t>570,105,000</t>
-        </is>
-      </c>
-      <c r="Q70" s="6" t="inlineStr">
-        <is>
-          <t>4.5%</t>
+      <c r="P70" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="Q70" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="R70" s="6" t="inlineStr">
         <is>
-          <t>최초</t>
+          <t>정정</t>
         </is>
       </c>
     </row>
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>인텔리빅스</t>
-        </is>
-      </c>
-      <c r="B71" s="6" t="inlineStr">
-        <is>
-          <t>10-12~10-16</t>
-        </is>
-      </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>7,600~9,000</t>
-        </is>
-      </c>
-      <c r="D71" s="7" t="inlineStr">
-        <is>
-          <t>2,500,000</t>
-        </is>
-      </c>
-      <c r="E71" s="7" t="inlineStr">
-        <is>
-          <t>19,000,000,000</t>
-        </is>
-      </c>
-      <c r="F71" s="6" t="inlineStr">
-        <is>
-          <t>22.02배 (PER)</t>
+          <t>셀트릭스</t>
+        </is>
+      </c>
+      <c r="B71" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="C71" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="D71" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="E71" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="F71" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr"/>
       <c r="H71" s="6" t="inlineStr"/>
       <c r="I71" s="6" t="inlineStr"/>
-      <c r="J71" s="6" t="inlineStr">
-        <is>
-          <t>10-21~10-22</t>
+      <c r="J71" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="K71" s="6" t="inlineStr"/>
       <c r="L71" s="6" t="inlineStr"/>
       <c r="M71" s="6" t="inlineStr"/>
-      <c r="N71" s="6" t="inlineStr">
-        <is>
-          <t>미래에셋증권</t>
+      <c r="N71" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="O71" s="6" t="inlineStr"/>
-      <c r="P71" s="7" t="inlineStr">
-        <is>
-          <t>782,800,000</t>
-        </is>
-      </c>
-      <c r="Q71" s="6" t="inlineStr">
-        <is>
-          <t>4.0%</t>
+      <c r="P71" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="Q71" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="R71" s="6" t="inlineStr">
         <is>
-          <t>최초</t>
+          <t>정정</t>
         </is>
       </c>
     </row>
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>영광</t>
+          <t>인텔리빅스</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>10-13~10-19</t>
+          <t>10-12~10-16</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>14,000~17,000</t>
+          <t>7,600~9,000</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>2,260,000</t>
+          <t>2,500,000</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>31,640,000,000</t>
+          <t>19,000,000,000</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>11.98배 (EV/EBITDA)</t>
+          <t>22.02배 (PER)</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr"/>
@@ -13481,7 +13489,7 @@
       <c r="I72" s="6" t="inlineStr"/>
       <c r="J72" s="6" t="inlineStr">
         <is>
-          <t>10-22~10-23</t>
+          <t>10-21~10-22</t>
         </is>
       </c>
       <c r="K72" s="6" t="inlineStr"/>
@@ -13489,18 +13497,18 @@
       <c r="M72" s="6" t="inlineStr"/>
       <c r="N72" s="6" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>미래에셋증권</t>
         </is>
       </c>
       <c r="O72" s="6" t="inlineStr"/>
       <c r="P72" s="7" t="inlineStr">
         <is>
-          <t>977,676,000</t>
-        </is>
-      </c>
-      <c r="Q72" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>782,800,000</t>
+        </is>
+      </c>
+      <c r="Q72" s="6" t="inlineStr">
+        <is>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="R72" s="6" t="inlineStr">
@@ -13512,32 +13520,32 @@
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>한화플러스제6호스팩</t>
+          <t>영광</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>10-14~10-15</t>
-        </is>
-      </c>
-      <c r="C73" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>10-13~10-19</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>14,000~17,000</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>6,000,000</t>
+          <t>2,260,000</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>12,000,000,000</t>
-        </is>
-      </c>
-      <c r="F73" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>31,640,000,000</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>11.98배 (EV/EBITDA)</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr"/>
@@ -13545,26 +13553,26 @@
       <c r="I73" s="6" t="inlineStr"/>
       <c r="J73" s="6" t="inlineStr">
         <is>
-          <t>10-20~10-21</t>
+          <t>10-22~10-23</t>
         </is>
       </c>
       <c r="K73" s="6" t="inlineStr"/>
       <c r="L73" s="6" t="inlineStr"/>
       <c r="M73" s="6" t="inlineStr"/>
-      <c r="N73" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="N73" s="6" t="inlineStr">
+        <is>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="O73" s="6" t="inlineStr"/>
-      <c r="P73" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="Q73" s="6" t="inlineStr">
-        <is>
-          <t>3.50%</t>
+      <c r="P73" s="7" t="inlineStr">
+        <is>
+          <t>977,676,000</t>
+        </is>
+      </c>
+      <c r="Q73" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="R73" s="6" t="inlineStr">
@@ -14024,7 +14032,7 @@
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>솔리스</t>
+          <t>럭스코</t>
         </is>
       </c>
       <c r="B81" s="18" t="inlineStr">
@@ -14088,7 +14096,7 @@
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>디티에스</t>
+          <t>솔리스</t>
         </is>
       </c>
       <c r="B82" s="18" t="inlineStr">
@@ -14145,14 +14153,14 @@
       </c>
       <c r="R82" s="6" t="inlineStr">
         <is>
-          <t>신고서 대기</t>
+          <t>최초</t>
         </is>
       </c>
     </row>
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>에이엔에이치스트럭쳐</t>
+          <t>디티에스</t>
         </is>
       </c>
       <c r="B83" s="18" t="inlineStr">
@@ -14216,7 +14224,7 @@
     <row r="84" ht="30" customHeight="1">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>이에스티</t>
+          <t>에이엔에이치스트럭쳐</t>
         </is>
       </c>
       <c r="B84" s="18" t="inlineStr">
@@ -14280,7 +14288,7 @@
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>영광와이케이엠씨</t>
+          <t>이에스티</t>
         </is>
       </c>
       <c r="B85" s="18" t="inlineStr">
@@ -14344,7 +14352,7 @@
     <row r="86" ht="30" customHeight="1">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>제논</t>
+          <t>영광와이케이엠씨</t>
         </is>
       </c>
       <c r="B86" s="18" t="inlineStr">
@@ -14408,7 +14416,7 @@
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>럭스코</t>
+          <t>제논</t>
         </is>
       </c>
       <c r="B87" s="18" t="inlineStr">
@@ -14469,22 +14477,86 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="20" t="inlineStr">
-        <is>
-          <t>※ 상장 완료 = KIND 신규상장 페이지 기준(스팩합병 포함) · 스팩 공모상장은 밴드·밸류에이션 등 해당없음(공모가 2,000원 고정).</t>
+    <row r="88" ht="30" customHeight="1">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>우리투자제1호스팩</t>
+        </is>
+      </c>
+      <c r="B88" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="C88" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="D88" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="E88" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="F88" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr"/>
+      <c r="H88" s="6" t="inlineStr"/>
+      <c r="I88" s="6" t="inlineStr"/>
+      <c r="J88" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="K88" s="6" t="inlineStr"/>
+      <c r="L88" s="6" t="inlineStr"/>
+      <c r="M88" s="6" t="inlineStr"/>
+      <c r="N88" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="O88" s="6" t="inlineStr"/>
+      <c r="P88" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="Q88" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="R88" s="6" t="inlineStr">
+        <is>
+          <t>신고서 대기</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="20" t="inlineStr">
         <is>
-          <t>※ 기재정정 신고서 내 정정 전·후 병존 → 자동수집은 "정정 후" 값만 취함.</t>
+          <t>※ 상장 완료 = KIND 신규상장 페이지 기준(스팩합병 포함) · 스팩 공모상장은 밴드·밸류에이션 등 해당없음(공모가 2,000원 고정).</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="20" t="inlineStr">
+        <is>
+          <t>※ 기재정정 신고서 내 정정 전·후 병존 → 자동수집은 "정정 후" 값만 취함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="20" t="inlineStr">
         <is>
           <t>※ 청약경쟁률=일반투자자 청약수량÷최종배정수량 · "MM-DD~"는 종료일 자동수집 예정.</t>
         </is>
@@ -14787,7 +14859,7 @@
         <v>1</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D15" s="6" t="n">
         <v>0</v>
@@ -14909,7 +14981,7 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>156,428,800,000</t>
+          <t>201,091,000,000</t>
         </is>
       </c>
     </row>

--- a/IPO_analysis.xlsx
+++ b/IPO_analysis.xlsx
@@ -592,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K146"/>
+  <dimension ref="A1:K147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -618,14 +618,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>기준일 2026-10-06 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
+          <t>기준일 2026-10-07 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>■ 심사 신청(진행중)  (46건)</t>
+          <t>■ 심사 신청(진행중)  (44건)</t>
         </is>
       </c>
       <c r="B4" s="4" t="n"/>
@@ -699,12 +699,12 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>뱅크샐러드</t>
+          <t>베르티스</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -724,27 +724,27 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>25,994</t>
+          <t>5,119</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>-59,792</t>
+          <t>-12,903</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>28,335</t>
+          <t>-16,364</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>의료용품 및 기타 의약 관련제품 제조업</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
@@ -756,12 +756,12 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>키노톤</t>
+          <t>뱅크샐러드</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -781,27 +781,27 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>46,943</t>
+          <t>25,994</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>4,222</t>
+          <t>-59,792</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>19,112</t>
+          <t>28,335</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>건축기술, 엔지니어링 및 관련 기술 서비스업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>티에스모스트</t>
+          <t>키노톤</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -838,27 +838,27 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>156,198</t>
+          <t>46,943</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>5,666</t>
+          <t>4,222</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>25,181</t>
+          <t>19,112</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>자동차 신품 부품 제조업</t>
+          <t>건축기술, 엔지니어링 및 관련 기술 서비스업</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>신한</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr">
@@ -870,12 +870,12 @@
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>셀렉트스타</t>
+          <t>티에스모스트</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -895,27 +895,27 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>11,616</t>
+          <t>156,198</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>-9,883</t>
+          <t>5,666</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>-34,511</t>
+          <t>25,181</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>자동차 신품 부품 제조업</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>신한</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
@@ -927,12 +927,12 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>서북</t>
+          <t>셀렉트스타</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -952,27 +952,27 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>60,439</t>
+          <t>11,616</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>-8,764</t>
+          <t>-9,883</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>4,485</t>
+          <t>-34,511</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>사진장비 및 광학기기 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>에이스엔지니어링</t>
+          <t>서북</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -1009,27 +1009,27 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>307,911</t>
+          <t>60,439</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>-101,468</t>
+          <t>-8,764</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>83,159</t>
+          <t>4,485</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>전동기, 발전기 및 전기 변환 · 공급 · 제어 장치 제조업</t>
+          <t>사진장비 및 광학기기 제조업</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>대신, 미래, 키움</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>플렉스시스템</t>
+          <t>에이스엔지니어링</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -1066,27 +1066,27 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>10,894</t>
+          <t>307,911</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>-2,342</t>
+          <t>-101,468</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>3,014</t>
+          <t>83,159</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업; 광학기기 제외</t>
+          <t>전동기, 발전기 및 전기 변환 · 공급 · 제어 장치 제조업</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>대신, 미래, 키움</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
@@ -1098,12 +1098,12 @@
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>엠아이티</t>
+          <t>플렉스시스템</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1123,27 +1123,27 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>14,921</t>
+          <t>10,894</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>1,181</t>
+          <t>-2,342</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>28,026</t>
+          <t>3,014</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업; 광학기기 제외</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>큐로드</t>
+          <t>엠아이티</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -1178,17 +1178,29 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F14" s="7" t="inlineStr"/>
-      <c r="G14" s="7" t="inlineStr"/>
-      <c r="H14" s="7" t="inlineStr"/>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>14,921</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>1,181</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>28,026</t>
+        </is>
+      </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>교보</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
@@ -1200,12 +1212,12 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>노바셀테크놀로지</t>
+          <t>큐로드</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -1215,7 +1227,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -1223,29 +1235,17 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>-4,606</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>-15,458</t>
-        </is>
-      </c>
+      <c r="F15" s="7" t="inlineStr"/>
+      <c r="G15" s="7" t="inlineStr"/>
+      <c r="H15" s="7" t="inlineStr"/>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>키움</t>
+          <t>교보</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
@@ -1257,12 +1257,12 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>(주)태석광학</t>
+          <t>노바셀테크놀로지</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -1282,27 +1282,27 @@
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>79,804</t>
+          <t>377</t>
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr">
         <is>
-          <t>4,721</t>
+          <t>-4,606</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
         <is>
-          <t>7,228</t>
+          <t>-15,458</t>
         </is>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>생활용품 도매업</t>
+          <t>자연과학 및 공학 연구개발업</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>신한, 대신</t>
+          <t>키움</t>
         </is>
       </c>
       <c r="K16" s="6" t="inlineStr">
@@ -1314,12 +1314,12 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>엑티브온</t>
+          <t>(주)태석광학</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E17" s="6" t="inlineStr">
@@ -1337,17 +1337,29 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr"/>
-      <c r="G17" s="7" t="inlineStr"/>
-      <c r="H17" s="7" t="inlineStr"/>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>79,804</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>4,721</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>7,228</t>
+        </is>
+      </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>생활용품 도매업</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>키움</t>
+          <t>신한, 대신</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
@@ -1359,12 +1371,12 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>씨앤엠</t>
+          <t>엑티브온</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -1374,7 +1386,7 @@
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -1382,29 +1394,17 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>238,489</t>
-        </is>
-      </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>19,869</t>
-        </is>
-      </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>112,262</t>
-        </is>
-      </c>
+      <c r="F18" s="7" t="inlineStr"/>
+      <c r="G18" s="7" t="inlineStr"/>
+      <c r="H18" s="7" t="inlineStr"/>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>전동기, 발전기 및 전기 변환 · 공급 · 제어 장치 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>키움</t>
         </is>
       </c>
       <c r="K18" s="6" t="inlineStr">
@@ -1416,17 +1416,17 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>무신사</t>
+          <t>씨앤엠</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>유가</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
@@ -1441,27 +1441,27 @@
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>1,352,930</t>
+          <t>238,489</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
         <is>
-          <t>-10,571</t>
+          <t>19,869</t>
         </is>
       </c>
       <c r="H19" s="7" t="inlineStr">
         <is>
-          <t>243,731</t>
+          <t>112,262</t>
         </is>
       </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>섬유, 의복, 신발 및 가죽제품 소매업</t>
+          <t>전동기, 발전기 및 전기 변환 · 공급 · 제어 장치 제조업</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>한국, 씨티그룹글로벌마켓증권(주), KB, 제이피모간증권회사 서울지점</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
@@ -1473,17 +1473,17 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>마더스제약</t>
+          <t>무신사</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>유가</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1498,27 +1498,27 @@
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>228,830</t>
+          <t>1,352,930</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>11,204</t>
+          <t>-10,571</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>57,394</t>
+          <t>243,731</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>의약품 제조업</t>
+          <t>섬유, 의복, 신발 및 가죽제품 소매업</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>NH, KB</t>
+          <t>한국, 씨티그룹글로벌마켓증권(주), KB, 제이피모간증권회사 서울지점</t>
         </is>
       </c>
       <c r="K20" s="6" t="inlineStr">
@@ -2259,12 +2259,12 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>엔키화이트햇</t>
+          <t>씨아이에스케미칼</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -2284,27 +2284,27 @@
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>14,176</t>
+          <t>15,985</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>-3,211</t>
+          <t>-11,440</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>8,338</t>
+          <t>23,706</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>기초 화학물질 제조업</t>
         </is>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>신영</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="K34" s="6" t="inlineStr">
@@ -2316,12 +2316,12 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>씨아이에스케미칼</t>
+          <t>엠디에스코리아</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
@@ -2341,27 +2341,27 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>15,985</t>
+          <t>97,972</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>-11,440</t>
+          <t>6,512</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>23,706</t>
+          <t>53,818</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>기초 화학물질 제조업</t>
+          <t>기타 식품 제조업</t>
         </is>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K35" s="6" t="inlineStr">
@@ -2373,12 +2373,12 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>엠디에스코리아</t>
+          <t>동승</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
@@ -2398,27 +2398,27 @@
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>97,972</t>
+          <t>78,625</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>6,512</t>
+          <t>14,525</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>53,818</t>
+          <t>5,438</t>
         </is>
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>기타 식품 제조업</t>
+          <t>부동산 임대 및 공급업</t>
         </is>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K36" s="6" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>동승</t>
+          <t>에프엠더블유</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
@@ -2455,27 +2455,27 @@
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>78,625</t>
+          <t>30,282</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>14,525</t>
+          <t>4,762</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>5,438</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>부동산 임대 및 공급업</t>
+          <t>기타 식품 제조업</t>
         </is>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>유진</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
@@ -2487,22 +2487,22 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>에프엠더블유</t>
+          <t>소노인터내셔널</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>유가</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
@@ -2512,27 +2512,27 @@
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>30,282</t>
+          <t>2,093,051</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>4,762</t>
+          <t>-148,064</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>852,372</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>기타 식품 제조업</t>
+          <t>일반 및 생활 숙박시설 운영업</t>
         </is>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>유진</t>
+          <t>대신, 미래</t>
         </is>
       </c>
       <c r="K38" s="6" t="inlineStr">
@@ -2544,17 +2544,17 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>소노인터내셔널</t>
+          <t>싸이몬</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>유가</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
@@ -2569,27 +2569,27 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>2,093,051</t>
+          <t>48,695</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>-148,064</t>
+          <t>15,714</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>852,372</t>
+          <t>61,761</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>일반 및 생활 숙박시설 운영업</t>
+          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업</t>
         </is>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>대신, 미래</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr">
@@ -2601,12 +2601,12 @@
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>싸이몬</t>
+          <t>바이다</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -2626,27 +2626,27 @@
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>48,695</t>
+          <t>14,432</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>15,714</t>
+          <t>-3,951</t>
         </is>
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>61,761</t>
+          <t>15,108</t>
         </is>
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업</t>
+          <t>전자부품 제조업</t>
         </is>
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K40" s="6" t="inlineStr">
@@ -2658,12 +2658,12 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>바이다</t>
+          <t>아이알큐더스</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -2683,27 +2683,27 @@
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>14,432</t>
+          <t>10,231</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>-3,951</t>
+          <t>-986</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>15,108</t>
+          <t>1,800</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>전자부품 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
@@ -2715,12 +2715,12 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>아이알큐더스</t>
+          <t>씨엔티테크</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -2740,17 +2740,17 @@
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>10,231</t>
+          <t>27,015</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>-986</t>
+          <t>3,987</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>1,800</t>
+          <t>2,613</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>한화, 하나</t>
         </is>
       </c>
       <c r="K42" s="6" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>씨엔티테크</t>
+          <t>제이앤티지</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -2797,27 +2797,27 @@
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>27,015</t>
+          <t>72,378</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>3,987</t>
+          <t>9,904</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>2,613</t>
+          <t>6,743</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>전자부품 제조업</t>
         </is>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>한화, 하나</t>
+          <t>대신, NH</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
@@ -2829,12 +2829,12 @@
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>제이앤티지</t>
+          <t>인터엑스</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -2854,27 +2854,27 @@
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>72,378</t>
+          <t>8,645</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>9,904</t>
+          <t>-20,272</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>6,743</t>
+          <t>4,530</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>전자부품 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>대신, NH</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K44" s="6" t="inlineStr">
@@ -2886,12 +2886,12 @@
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>인터엑스</t>
+          <t>삼홍아크튜리온</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -2911,27 +2911,27 @@
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>8,645</t>
+          <t>26,162</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>-20,272</t>
+          <t>-10,314</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>4,530</t>
+          <t>6,369</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
         </is>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>삼성, 미래</t>
         </is>
       </c>
       <c r="K45" s="6" t="inlineStr">
@@ -2943,12 +2943,12 @@
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>삼홍아크튜리온</t>
+          <t>비앤비코리아</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -2968,27 +2968,27 @@
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>26,162</t>
+          <t>141,169</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>-10,314</t>
+          <t>21,406</t>
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>6,369</t>
+          <t>43,932</t>
         </is>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
-          <t>삼성, 미래</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K46" s="6" t="inlineStr">
@@ -3000,12 +3000,12 @@
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>넥스트에어로스페이스</t>
+          <t>오토핸즈</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
@@ -3025,27 +3025,27 @@
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>12,084</t>
+          <t>238,564</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
         <is>
-          <t>-17,270</t>
+          <t>6,047</t>
         </is>
       </c>
       <c r="H47" s="7" t="inlineStr">
         <is>
-          <t>6,158</t>
+          <t>6,129</t>
         </is>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>유인 항공기, 항공우주선 및 보조장치 제조업</t>
+          <t>자동차 판매업</t>
         </is>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K47" s="6" t="inlineStr">
@@ -3057,12 +3057,12 @@
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>비앤비코리아</t>
+          <t>아이벡스메디칼시스템즈</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -3082,27 +3082,27 @@
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>141,169</t>
+          <t>15,282</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
         <is>
-          <t>21,406</t>
+          <t>-7,227</t>
         </is>
       </c>
       <c r="H48" s="7" t="inlineStr">
         <is>
-          <t>43,932</t>
+          <t>744</t>
         </is>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K48" s="6" t="inlineStr">
@@ -3114,12 +3114,12 @@
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>오토핸즈</t>
+          <t>피지티</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
@@ -3139,27 +3139,27 @@
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>238,564</t>
+          <t>40,141</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
         <is>
-          <t>6,047</t>
+          <t>-69,722</t>
         </is>
       </c>
       <c r="H49" s="7" t="inlineStr">
         <is>
-          <t>6,129</t>
+          <t>6,029</t>
         </is>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>자동차 판매업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K49" s="6" t="inlineStr">
@@ -3168,191 +3168,191 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="B50" s="6" t="inlineStr">
-        <is>
-          <t>아이벡스메디칼시스템즈</t>
-        </is>
-      </c>
-      <c r="C50" s="6" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>■ 심사 승인  (73건)</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="n"/>
+      <c r="C51" s="4" t="n"/>
+      <c r="D51" s="4" t="n"/>
+      <c r="E51" s="4" t="n"/>
+      <c r="F51" s="4" t="n"/>
+      <c r="G51" s="4" t="n"/>
+      <c r="H51" s="4" t="n"/>
+      <c r="I51" s="4" t="n"/>
+      <c r="J51" s="4" t="n"/>
+      <c r="K51" s="4" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>일자</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>회사명</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>시장</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>상장유형</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>기준연도</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>자기자본</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>업종</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>대표주관사</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>현황</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>엔키화이트햇</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
         <is>
           <t>코스닥</t>
         </is>
       </c>
-      <c r="D50" s="6" t="inlineStr">
+      <c r="D53" s="6" t="inlineStr">
         <is>
           <t>신규상장</t>
         </is>
       </c>
-      <c r="E50" s="6" t="inlineStr">
+      <c r="E53" s="6" t="inlineStr">
         <is>
           <t>FY25</t>
         </is>
       </c>
-      <c r="F50" s="7" t="inlineStr">
-        <is>
-          <t>15,282</t>
-        </is>
-      </c>
-      <c r="G50" s="7" t="inlineStr">
-        <is>
-          <t>-7,227</t>
-        </is>
-      </c>
-      <c r="H50" s="7" t="inlineStr">
-        <is>
-          <t>744</t>
-        </is>
-      </c>
-      <c r="I50" s="6" t="inlineStr">
-        <is>
-          <t>의료용 기기 제조업</t>
-        </is>
-      </c>
-      <c r="J50" s="6" t="inlineStr">
-        <is>
-          <t>NH</t>
-        </is>
-      </c>
-      <c r="K50" s="6" t="inlineStr">
-        <is>
-          <t>예심 진행중</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="B51" s="6" t="inlineStr">
-        <is>
-          <t>피지티</t>
-        </is>
-      </c>
-      <c r="C51" s="6" t="inlineStr">
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>14,176</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>-3,211</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>8,338</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr">
+        <is>
+          <t>신영</t>
+        </is>
+      </c>
+      <c r="K53" s="6" t="inlineStr">
+        <is>
+          <t>상장전</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="inlineStr">
+        <is>
+          <t>마더스제약</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
         <is>
           <t>코스닥</t>
         </is>
       </c>
-      <c r="D51" s="6" t="inlineStr">
+      <c r="D54" s="6" t="inlineStr">
         <is>
           <t>신규상장</t>
         </is>
       </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="E54" s="6" t="inlineStr">
         <is>
           <t>FY25</t>
         </is>
       </c>
-      <c r="F51" s="7" t="inlineStr">
-        <is>
-          <t>40,141</t>
-        </is>
-      </c>
-      <c r="G51" s="7" t="inlineStr">
-        <is>
-          <t>-69,722</t>
-        </is>
-      </c>
-      <c r="H51" s="7" t="inlineStr">
-        <is>
-          <t>6,029</t>
-        </is>
-      </c>
-      <c r="I51" s="6" t="inlineStr">
-        <is>
-          <t>기타 화학제품 제조업</t>
-        </is>
-      </c>
-      <c r="J51" s="6" t="inlineStr">
-        <is>
-          <t>한국</t>
-        </is>
-      </c>
-      <c r="K51" s="6" t="inlineStr">
-        <is>
-          <t>예심 진행중</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>■ 심사 승인  (71건)</t>
-        </is>
-      </c>
-      <c r="B53" s="4" t="n"/>
-      <c r="C53" s="4" t="n"/>
-      <c r="D53" s="4" t="n"/>
-      <c r="E53" s="4" t="n"/>
-      <c r="F53" s="4" t="n"/>
-      <c r="G53" s="4" t="n"/>
-      <c r="H53" s="4" t="n"/>
-      <c r="I53" s="4" t="n"/>
-      <c r="J53" s="4" t="n"/>
-      <c r="K53" s="4" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>일자</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>회사명</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>시장</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>상장유형</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>기준연도</t>
-        </is>
-      </c>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="G54" s="5" t="inlineStr">
-        <is>
-          <t>순이익</t>
-        </is>
-      </c>
-      <c r="H54" s="5" t="inlineStr">
-        <is>
-          <t>자기자본</t>
-        </is>
-      </c>
-      <c r="I54" s="5" t="inlineStr">
-        <is>
-          <t>업종</t>
-        </is>
-      </c>
-      <c r="J54" s="5" t="inlineStr">
-        <is>
-          <t>대표주관사</t>
-        </is>
-      </c>
-      <c r="K54" s="5" t="inlineStr">
-        <is>
-          <t>현황</t>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>228,830</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>11,204</t>
+        </is>
+      </c>
+      <c r="H54" s="7" t="inlineStr">
+        <is>
+          <t>57,394</t>
+        </is>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>의약품 제조업</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>NH, KB</t>
+        </is>
+      </c>
+      <c r="K54" s="6" t="inlineStr">
+        <is>
+          <t>상장전</t>
         </is>
       </c>
     </row>
@@ -7242,7 +7242,7 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>■ 철회·미승인  (18건)</t>
+          <t>■ 철회·미승인  (19건)</t>
         </is>
       </c>
       <c r="B127" s="4" t="n"/>
@@ -7316,12 +7316,12 @@
     <row r="129">
       <c r="A129" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>텔레픽스</t>
+          <t>넥스트에어로스페이스</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
@@ -7341,27 +7341,27 @@
       </c>
       <c r="F129" s="7" t="inlineStr">
         <is>
-          <t>4,896</t>
+          <t>12,084</t>
         </is>
       </c>
       <c r="G129" s="7" t="inlineStr">
         <is>
-          <t>-16,214</t>
+          <t>-17,270</t>
         </is>
       </c>
       <c r="H129" s="7" t="inlineStr">
         <is>
-          <t>9,146</t>
+          <t>6,158</t>
         </is>
       </c>
       <c r="I129" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>유인 항공기, 항공우주선 및 보조장치 제조업</t>
         </is>
       </c>
       <c r="J129" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K129" s="6" t="inlineStr">
@@ -7373,12 +7373,12 @@
     <row r="130">
       <c r="A130" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>씨엠디엘</t>
+          <t>텔레픽스</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
@@ -7388,37 +7388,37 @@
       </c>
       <c r="D130" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E130" s="6" t="inlineStr">
         <is>
-          <t>FY24</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="F130" s="7" t="inlineStr">
         <is>
-          <t>39,991</t>
+          <t>4,896</t>
         </is>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
-          <t>3,541</t>
+          <t>-16,214</t>
         </is>
       </c>
       <c r="H130" s="7" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>9,146</t>
         </is>
       </c>
       <c r="I130" s="6" t="inlineStr">
         <is>
-          <t>기타 기초 유기 화학물질 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J130" s="6" t="inlineStr">
         <is>
-          <t>교보</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K130" s="6" t="inlineStr">
@@ -7430,12 +7430,12 @@
     <row r="131">
       <c r="A131" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>모비어스</t>
+          <t>씨엠디엘</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
@@ -7445,37 +7445,37 @@
       </c>
       <c r="D131" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
         <is>
-          <t>FY25</t>
+          <t>FY24</t>
         </is>
       </c>
       <c r="F131" s="7" t="inlineStr">
         <is>
-          <t>31,989</t>
+          <t>39,991</t>
         </is>
       </c>
       <c r="G131" s="7" t="inlineStr">
         <is>
-          <t>-45,307</t>
+          <t>3,541</t>
         </is>
       </c>
       <c r="H131" s="7" t="inlineStr">
         <is>
-          <t>-96,707</t>
+          <t>503</t>
         </is>
       </c>
       <c r="I131" s="6" t="inlineStr">
         <is>
-          <t>컴퓨터 프로그래밍, 시스템 통합 및 관리업</t>
+          <t>기타 기초 유기 화학물질 제조업</t>
         </is>
       </c>
       <c r="J131" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>교보</t>
         </is>
       </c>
       <c r="K131" s="6" t="inlineStr">
@@ -7487,12 +7487,12 @@
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>넥스트젠바이오</t>
+          <t>모비어스</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
@@ -7507,32 +7507,32 @@
       </c>
       <c r="E132" s="6" t="inlineStr">
         <is>
-          <t>FY24</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="F132" s="7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>31,989</t>
         </is>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>-45,307</t>
         </is>
       </c>
       <c r="H132" s="7" t="inlineStr">
         <is>
-          <t>4,792</t>
+          <t>-96,707</t>
         </is>
       </c>
       <c r="I132" s="6" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>컴퓨터 프로그래밍, 시스템 통합 및 관리업</t>
         </is>
       </c>
       <c r="J132" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K132" s="6" t="inlineStr">
@@ -7544,12 +7544,12 @@
     <row r="133">
       <c r="A133" s="6" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>파워큐브세미</t>
+          <t>넥스트젠바이오</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
@@ -7564,32 +7564,32 @@
       </c>
       <c r="E133" s="6" t="inlineStr">
         <is>
-          <t>FY25</t>
+          <t>FY24</t>
         </is>
       </c>
       <c r="F133" s="7" t="inlineStr">
         <is>
-          <t>10,341</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G133" s="7" t="inlineStr">
         <is>
-          <t>-10,837</t>
+          <t>69</t>
         </is>
       </c>
       <c r="H133" s="7" t="inlineStr">
         <is>
-          <t>841</t>
+          <t>4,792</t>
         </is>
       </c>
       <c r="I133" s="6" t="inlineStr">
         <is>
-          <t>반도체 제조업</t>
+          <t>자연과학 및 공학 연구개발업</t>
         </is>
       </c>
       <c r="J133" s="6" t="inlineStr">
         <is>
-          <t>하나, BNK</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K133" s="6" t="inlineStr">
@@ -7601,12 +7601,12 @@
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>제이피이노베이션</t>
+          <t>파워큐브세미</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
@@ -7626,27 +7626,27 @@
       </c>
       <c r="F134" s="7" t="inlineStr">
         <is>
-          <t>56,324</t>
+          <t>10,341</t>
         </is>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
-          <t>5,588</t>
+          <t>-10,837</t>
         </is>
       </c>
       <c r="H134" s="7" t="inlineStr">
         <is>
-          <t>3,684</t>
+          <t>841</t>
         </is>
       </c>
       <c r="I134" s="6" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>반도체 제조업</t>
         </is>
       </c>
       <c r="J134" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>하나, BNK</t>
         </is>
       </c>
       <c r="K134" s="6" t="inlineStr">
@@ -7658,12 +7658,12 @@
     <row r="135">
       <c r="A135" s="6" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>케이솔루션</t>
+          <t>제이피이노베이션</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
@@ -7673,7 +7673,7 @@
       </c>
       <c r="D135" s="6" t="inlineStr">
         <is>
-          <t>스팩 존속합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E135" s="6" t="inlineStr">
@@ -7683,27 +7683,27 @@
       </c>
       <c r="F135" s="7" t="inlineStr">
         <is>
-          <t>34,565</t>
+          <t>56,324</t>
         </is>
       </c>
       <c r="G135" s="7" t="inlineStr">
         <is>
-          <t>1,158</t>
+          <t>5,588</t>
         </is>
       </c>
       <c r="H135" s="7" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>3,684</t>
         </is>
       </c>
       <c r="I135" s="6" t="inlineStr">
         <is>
-          <t>차체 및 특장차 제조업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="J135" s="6" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K135" s="6" t="inlineStr">
@@ -7715,12 +7715,12 @@
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>디토닉</t>
+          <t>케이솔루션</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr">
@@ -7730,37 +7730,37 @@
       </c>
       <c r="D136" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 존속합병</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
         <is>
-          <t>FY24</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="F136" s="7" t="inlineStr">
         <is>
-          <t>31,293</t>
+          <t>34,565</t>
         </is>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
-          <t>-1,633</t>
+          <t>1,158</t>
         </is>
       </c>
       <c r="H136" s="7" t="inlineStr">
         <is>
-          <t>-21,926</t>
+          <t>653</t>
         </is>
       </c>
       <c r="I136" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>차체 및 특장차 제조업</t>
         </is>
       </c>
       <c r="J136" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="K136" s="6" t="inlineStr">
@@ -7772,12 +7772,12 @@
     <row r="137">
       <c r="A137" s="6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>에스케이팩</t>
+          <t>디토닉</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
@@ -7787,7 +7787,7 @@
       </c>
       <c r="D137" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
@@ -7797,27 +7797,27 @@
       </c>
       <c r="F137" s="7" t="inlineStr">
         <is>
-          <t>27,310</t>
+          <t>31,293</t>
         </is>
       </c>
       <c r="G137" s="7" t="inlineStr">
         <is>
-          <t>2,257</t>
+          <t>-1,633</t>
         </is>
       </c>
       <c r="H137" s="7" t="inlineStr">
         <is>
-          <t>3,207</t>
+          <t>-21,926</t>
         </is>
       </c>
       <c r="I137" s="6" t="inlineStr">
         <is>
-          <t>용기 세척, 포장 및 충전기 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J137" s="6" t="inlineStr">
         <is>
-          <t>교보</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K137" s="6" t="inlineStr">
@@ -7829,12 +7829,12 @@
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>메타넷엑스</t>
+          <t>에스케이팩</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="D138" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
@@ -7854,27 +7854,27 @@
       </c>
       <c r="F138" s="7" t="inlineStr">
         <is>
-          <t>244,130</t>
+          <t>27,310</t>
         </is>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
-          <t>13,455</t>
+          <t>2,257</t>
         </is>
       </c>
       <c r="H138" s="7" t="inlineStr">
         <is>
-          <t>9,995</t>
+          <t>3,207</t>
         </is>
       </c>
       <c r="I138" s="6" t="inlineStr">
         <is>
-          <t>컴퓨터 프로그래밍, 시스템 통합 및 관리업</t>
+          <t>용기 세척, 포장 및 충전기 제조업</t>
         </is>
       </c>
       <c r="J138" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>교보</t>
         </is>
       </c>
       <c r="K138" s="6" t="inlineStr">
@@ -7886,12 +7886,12 @@
     <row r="139">
       <c r="A139" s="6" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>무아스</t>
+          <t>메타넷엑스</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="D139" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E139" s="6" t="inlineStr">
@@ -7911,27 +7911,27 @@
       </c>
       <c r="F139" s="7" t="inlineStr">
         <is>
-          <t>41,813</t>
+          <t>244,130</t>
         </is>
       </c>
       <c r="G139" s="7" t="inlineStr">
         <is>
-          <t>3,903</t>
+          <t>13,455</t>
         </is>
       </c>
       <c r="H139" s="7" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>9,995</t>
         </is>
       </c>
       <c r="I139" s="6" t="inlineStr">
         <is>
-          <t>가정용 전기기기 제조업</t>
+          <t>컴퓨터 프로그래밍, 시스템 통합 및 관리업</t>
         </is>
       </c>
       <c r="J139" s="6" t="inlineStr">
         <is>
-          <t>신한</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K139" s="6" t="inlineStr">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>유빅스테라퓨틱스</t>
+          <t>무아스</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="D140" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
@@ -7968,27 +7968,27 @@
       </c>
       <c r="F140" s="7" t="inlineStr">
         <is>
-          <t>1,071</t>
+          <t>41,813</t>
         </is>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
-          <t>-15,145</t>
+          <t>3,903</t>
         </is>
       </c>
       <c r="H140" s="7" t="inlineStr">
         <is>
-          <t>5,489</t>
+          <t>532</t>
         </is>
       </c>
       <c r="I140" s="6" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>가정용 전기기기 제조업</t>
         </is>
       </c>
       <c r="J140" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>신한</t>
         </is>
       </c>
       <c r="K140" s="6" t="inlineStr">
@@ -8000,12 +8000,12 @@
     <row r="141">
       <c r="A141" s="6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>코드잇</t>
+          <t>유빅스테라퓨틱스</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
@@ -8025,27 +8025,27 @@
       </c>
       <c r="F141" s="7" t="inlineStr">
         <is>
-          <t>30,747</t>
+          <t>1,071</t>
         </is>
       </c>
       <c r="G141" s="7" t="inlineStr">
         <is>
-          <t>6,652</t>
+          <t>-15,145</t>
         </is>
       </c>
       <c r="H141" s="7" t="inlineStr">
         <is>
-          <t>2,403</t>
+          <t>5,489</t>
         </is>
       </c>
       <c r="I141" s="6" t="inlineStr">
         <is>
-          <t>교육지원 서비스업</t>
+          <t>자연과학 및 공학 연구개발업</t>
         </is>
       </c>
       <c r="J141" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K141" s="6" t="inlineStr">
@@ -8057,12 +8057,12 @@
     <row r="142">
       <c r="A142" s="6" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>한컴인스페이스</t>
+          <t>코드잇</t>
         </is>
       </c>
       <c r="C142" s="6" t="inlineStr">
@@ -8082,44 +8082,44 @@
       </c>
       <c r="F142" s="7" t="inlineStr">
         <is>
-          <t>23,492</t>
+          <t>30,747</t>
         </is>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
-          <t>-3,104</t>
+          <t>6,652</t>
         </is>
       </c>
       <c r="H142" s="7" t="inlineStr">
         <is>
-          <t>5,815</t>
+          <t>2,403</t>
         </is>
       </c>
       <c r="I142" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>교육지원 서비스업</t>
         </is>
       </c>
       <c r="J142" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K142" s="6" t="inlineStr">
         <is>
-          <t>심사 미승인</t>
+          <t>심사 철회</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="6" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>크몽</t>
+          <t>한컴인스페이스</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
@@ -8139,44 +8139,44 @@
       </c>
       <c r="F143" s="7" t="inlineStr">
         <is>
-          <t>48,572</t>
+          <t>23,492</t>
         </is>
       </c>
       <c r="G143" s="7" t="inlineStr">
         <is>
-          <t>3,988</t>
+          <t>-3,104</t>
         </is>
       </c>
       <c r="H143" s="7" t="inlineStr">
         <is>
-          <t>4,930</t>
+          <t>5,815</t>
         </is>
       </c>
       <c r="I143" s="6" t="inlineStr">
         <is>
-          <t>기타 정보 서비스업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J143" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K143" s="6" t="inlineStr">
         <is>
-          <t>심사 철회</t>
+          <t>심사 미승인</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="6" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>한화플러스제6호스팩</t>
+          <t>크몽</t>
         </is>
       </c>
       <c r="C144" s="6" t="inlineStr">
@@ -8196,27 +8196,27 @@
       </c>
       <c r="F144" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>48,572</t>
         </is>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3,988</t>
         </is>
       </c>
       <c r="H144" s="7" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4,930</t>
         </is>
       </c>
       <c r="I144" s="6" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>기타 정보 서비스업</t>
         </is>
       </c>
       <c r="J144" s="6" t="inlineStr">
         <is>
-          <t>한화</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K144" s="6" t="inlineStr">
@@ -8228,17 +8228,17 @@
     <row r="145">
       <c r="A145" s="6" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>에식스솔루션즈</t>
+          <t>한화플러스제6호스팩</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
         <is>
-          <t>유가</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D145" s="6" t="inlineStr">
@@ -8253,27 +8253,27 @@
       </c>
       <c r="F145" s="7" t="inlineStr">
         <is>
-          <t>2,461</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G145" s="7" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H145" s="7" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I145" s="6" t="inlineStr">
         <is>
-          <t>절연선 및 케이블 제조업</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="J145" s="6" t="inlineStr">
         <is>
-          <t>한국, 미래</t>
+          <t>한화</t>
         </is>
       </c>
       <c r="K145" s="6" t="inlineStr">
@@ -8285,55 +8285,112 @@
     <row r="146">
       <c r="A146" s="6" t="inlineStr">
         <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B146" s="6" t="inlineStr">
+        <is>
+          <t>에식스솔루션즈</t>
+        </is>
+      </c>
+      <c r="C146" s="6" t="inlineStr">
+        <is>
+          <t>유가</t>
+        </is>
+      </c>
+      <c r="D146" s="6" t="inlineStr">
+        <is>
+          <t>신규상장</t>
+        </is>
+      </c>
+      <c r="E146" s="6" t="inlineStr">
+        <is>
+          <t>FY24</t>
+        </is>
+      </c>
+      <c r="F146" s="7" t="inlineStr">
+        <is>
+          <t>2,461</t>
+        </is>
+      </c>
+      <c r="G146" s="7" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="H146" s="7" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I146" s="6" t="inlineStr">
+        <is>
+          <t>절연선 및 케이블 제조업</t>
+        </is>
+      </c>
+      <c r="J146" s="6" t="inlineStr">
+        <is>
+          <t>한국, 미래</t>
+        </is>
+      </c>
+      <c r="K146" s="6" t="inlineStr">
+        <is>
+          <t>심사 철회</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="6" t="inlineStr">
+        <is>
           <t>2026-01-23</t>
         </is>
       </c>
-      <c r="B146" s="6" t="inlineStr">
+      <c r="B147" s="6" t="inlineStr">
         <is>
           <t>에코크레이션</t>
         </is>
       </c>
-      <c r="C146" s="6" t="inlineStr">
+      <c r="C147" s="6" t="inlineStr">
         <is>
           <t>코스닥</t>
         </is>
       </c>
-      <c r="D146" s="6" t="inlineStr">
+      <c r="D147" s="6" t="inlineStr">
         <is>
           <t>신규상장</t>
         </is>
       </c>
-      <c r="E146" s="6" t="inlineStr">
+      <c r="E147" s="6" t="inlineStr">
         <is>
           <t>FY24</t>
         </is>
       </c>
-      <c r="F146" s="7" t="inlineStr">
+      <c r="F147" s="7" t="inlineStr">
         <is>
           <t>18,544</t>
         </is>
       </c>
-      <c r="G146" s="7" t="inlineStr">
+      <c r="G147" s="7" t="inlineStr">
         <is>
           <t>-15,634</t>
         </is>
       </c>
-      <c r="H146" s="7" t="inlineStr">
+      <c r="H147" s="7" t="inlineStr">
         <is>
           <t>4,550</t>
         </is>
       </c>
-      <c r="I146" s="6" t="inlineStr">
+      <c r="I147" s="6" t="inlineStr">
         <is>
           <t>일반 목적용 기계 제조업</t>
         </is>
       </c>
-      <c r="J146" s="6" t="inlineStr">
+      <c r="J147" s="6" t="inlineStr">
         <is>
           <t>키움</t>
         </is>
       </c>
-      <c r="K146" s="6" t="inlineStr">
+      <c r="K147" s="6" t="inlineStr">
         <is>
           <t>심사 철회</t>
         </is>
@@ -8350,7 +8407,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R92"/>
+  <dimension ref="A1:R94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -12432,7 +12489,7 @@
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>■ 공모 진행 (예심 승인법인)  (32건)</t>
+          <t>■ 공모 진행 (예심 승인법인)  (34건)</t>
         </is>
       </c>
       <c r="B56" s="4" t="n"/>
@@ -12576,7 +12633,11 @@
           <t>10-01~10-02</t>
         </is>
       </c>
-      <c r="K58" s="6" t="inlineStr"/>
+      <c r="K58" s="6" t="inlineStr">
+        <is>
+          <t>4,284.98</t>
+        </is>
+      </c>
       <c r="L58" s="6" t="inlineStr"/>
       <c r="M58" s="6" t="inlineStr"/>
       <c r="N58" s="6" t="inlineStr">
@@ -12597,7 +12658,7 @@
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>발행조건확정</t>
+          <t>청약완료·상장대기</t>
         </is>
       </c>
     </row>
@@ -12772,7 +12833,7 @@
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>27,200,000,000</t>
+          <t>31,200,000,000</t>
         </is>
       </c>
       <c r="F61" s="6" t="inlineStr">
@@ -12780,9 +12841,17 @@
           <t>30.89배 (PER)</t>
         </is>
       </c>
-      <c r="G61" s="6" t="inlineStr"/>
-      <c r="H61" s="6" t="inlineStr"/>
-      <c r="I61" s="6" t="inlineStr"/>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>7,800</t>
+        </is>
+      </c>
+      <c r="H61" s="6" t="n">
+        <v>1096.56</v>
+      </c>
+      <c r="I61" s="6" t="n">
+        <v>2269</v>
+      </c>
       <c r="J61" s="6" t="inlineStr">
         <is>
           <t>10-12~10-13</t>
@@ -12809,7 +12878,7 @@
       </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
-          <t>정정</t>
+          <t>발행조건확정</t>
         </is>
       </c>
     </row>
@@ -13456,96 +13525,96 @@
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>인텔리빅스</t>
-        </is>
-      </c>
-      <c r="B72" s="6" t="inlineStr">
-        <is>
-          <t>10-12~10-16</t>
-        </is>
-      </c>
-      <c r="C72" s="6" t="inlineStr">
-        <is>
-          <t>7,600~9,000</t>
-        </is>
-      </c>
-      <c r="D72" s="7" t="inlineStr">
-        <is>
-          <t>2,500,000</t>
-        </is>
-      </c>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t>19,000,000,000</t>
-        </is>
-      </c>
-      <c r="F72" s="6" t="inlineStr">
-        <is>
-          <t>22.02배 (PER)</t>
+          <t>솔리스</t>
+        </is>
+      </c>
+      <c r="B72" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="C72" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="D72" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="E72" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="F72" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr"/>
       <c r="H72" s="6" t="inlineStr"/>
       <c r="I72" s="6" t="inlineStr"/>
-      <c r="J72" s="6" t="inlineStr">
-        <is>
-          <t>10-21~10-22</t>
+      <c r="J72" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="K72" s="6" t="inlineStr"/>
       <c r="L72" s="6" t="inlineStr"/>
       <c r="M72" s="6" t="inlineStr"/>
-      <c r="N72" s="6" t="inlineStr">
-        <is>
-          <t>미래에셋증권</t>
+      <c r="N72" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="O72" s="6" t="inlineStr"/>
-      <c r="P72" s="7" t="inlineStr">
-        <is>
-          <t>782,800,000</t>
-        </is>
-      </c>
-      <c r="Q72" s="6" t="inlineStr">
-        <is>
-          <t>4.0%</t>
+      <c r="P72" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="Q72" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="R72" s="6" t="inlineStr">
         <is>
-          <t>최초</t>
+          <t>정정</t>
         </is>
       </c>
     </row>
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>영광</t>
+          <t>인텔리빅스</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>10-13~10-19</t>
+          <t>10-12~10-16</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>14,000~17,000</t>
+          <t>7,600~9,000</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>2,260,000</t>
+          <t>2,500,000</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>31,640,000,000</t>
+          <t>19,000,000,000</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>11.98배 (EV/EBITDA)</t>
+          <t>22.02배 (PER)</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr"/>
@@ -13553,7 +13622,7 @@
       <c r="I73" s="6" t="inlineStr"/>
       <c r="J73" s="6" t="inlineStr">
         <is>
-          <t>10-22~10-23</t>
+          <t>10-21~10-22</t>
         </is>
       </c>
       <c r="K73" s="6" t="inlineStr"/>
@@ -13561,18 +13630,18 @@
       <c r="M73" s="6" t="inlineStr"/>
       <c r="N73" s="6" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>미래에셋증권</t>
         </is>
       </c>
       <c r="O73" s="6" t="inlineStr"/>
       <c r="P73" s="7" t="inlineStr">
         <is>
-          <t>977,676,000</t>
-        </is>
-      </c>
-      <c r="Q73" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>782,800,000</t>
+        </is>
+      </c>
+      <c r="Q73" s="6" t="inlineStr">
+        <is>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="R73" s="6" t="inlineStr">
@@ -13584,32 +13653,32 @@
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>에이엘로봇</t>
+          <t>영광</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>10-15~10-21</t>
+          <t>10-13~10-19</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>15,700~17,600</t>
+          <t>14,000~17,000</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>2,400,000</t>
+          <t>2,260,000</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>37,680,000,000</t>
+          <t>31,640,000,000</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>37.17배 (PER)</t>
+          <t>11.98배 (EV/EBITDA)</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr"/>
@@ -13617,7 +13686,7 @@
       <c r="I74" s="6" t="inlineStr"/>
       <c r="J74" s="6" t="inlineStr">
         <is>
-          <t>10-26~10-27</t>
+          <t>10-22~10-23</t>
         </is>
       </c>
       <c r="K74" s="6" t="inlineStr"/>
@@ -13625,18 +13694,18 @@
       <c r="M74" s="6" t="inlineStr"/>
       <c r="N74" s="6" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="O74" s="6" t="inlineStr"/>
       <c r="P74" s="7" t="inlineStr">
         <is>
-          <t>1,160,399,874</t>
-        </is>
-      </c>
-      <c r="Q74" s="6" t="inlineStr">
-        <is>
-          <t>3.0%</t>
+          <t>977,676,000</t>
+        </is>
+      </c>
+      <c r="Q74" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="R74" s="6" t="inlineStr">
@@ -13648,32 +13717,32 @@
     <row r="75" ht="30" customHeight="1">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>아이엠스팩1호</t>
+          <t>에이엘로봇</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>10-19~10-20</t>
-        </is>
-      </c>
-      <c r="C75" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>10-15~10-21</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>15,700~17,600</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>2,400,000</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>10,000,000,000</t>
-        </is>
-      </c>
-      <c r="F75" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>37,680,000,000</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>37.17배 (PER)</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr"/>
@@ -13687,20 +13756,20 @@
       <c r="K75" s="6" t="inlineStr"/>
       <c r="L75" s="6" t="inlineStr"/>
       <c r="M75" s="6" t="inlineStr"/>
-      <c r="N75" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="N75" s="6" t="inlineStr">
+        <is>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="O75" s="6" t="inlineStr"/>
-      <c r="P75" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P75" s="7" t="inlineStr">
+        <is>
+          <t>1,160,399,874</t>
         </is>
       </c>
       <c r="Q75" s="6" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="R75" s="6" t="inlineStr">
@@ -13712,32 +13781,32 @@
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>옵토닉스</t>
+          <t>아이엠스팩1호</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>10-21~10-27</t>
-        </is>
-      </c>
-      <c r="C76" s="6" t="inlineStr">
-        <is>
-          <t>10,000~12,000</t>
+          <t>10-19~10-20</t>
+        </is>
+      </c>
+      <c r="C76" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>2,200,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>22,000,000,000</t>
-        </is>
-      </c>
-      <c r="F76" s="6" t="inlineStr">
-        <is>
-          <t>25.27배 (EV/EBITDA)</t>
+          <t>10,000,000,000</t>
+        </is>
+      </c>
+      <c r="F76" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr"/>
@@ -13745,26 +13814,26 @@
       <c r="I76" s="6" t="inlineStr"/>
       <c r="J76" s="6" t="inlineStr">
         <is>
-          <t>11-05~11-06</t>
+          <t>10-26~10-27</t>
         </is>
       </c>
       <c r="K76" s="6" t="inlineStr"/>
       <c r="L76" s="6" t="inlineStr"/>
       <c r="M76" s="6" t="inlineStr"/>
-      <c r="N76" s="6" t="inlineStr">
-        <is>
-          <t>한국투자증권</t>
+      <c r="N76" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="O76" s="6" t="inlineStr"/>
-      <c r="P76" s="7" t="inlineStr">
-        <is>
-          <t>1,133,000,000</t>
+      <c r="P76" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="Q76" s="6" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="R76" s="6" t="inlineStr">
@@ -13776,32 +13845,32 @@
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>동원파츠</t>
+          <t>옵토닉스</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>10-22~10-28</t>
+          <t>10-21~10-27</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>23,000~26,500</t>
+          <t>10,000~12,000</t>
         </is>
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>2,030,000</t>
+          <t>2,200,000</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>46,690,000,000</t>
+          <t>22,000,000,000</t>
         </is>
       </c>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>22.91배 (PER)</t>
+          <t>25.27배 (EV/EBITDA)</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr"/>
@@ -13809,7 +13878,7 @@
       <c r="I77" s="6" t="inlineStr"/>
       <c r="J77" s="6" t="inlineStr">
         <is>
-          <t>11-02~11-03</t>
+          <t>11-05~11-06</t>
         </is>
       </c>
       <c r="K77" s="6" t="inlineStr"/>
@@ -13817,18 +13886,18 @@
       <c r="M77" s="6" t="inlineStr"/>
       <c r="N77" s="6" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="O77" s="6" t="inlineStr"/>
       <c r="P77" s="7" t="inlineStr">
         <is>
-          <t>1,430,699,820</t>
+          <t>1,133,000,000</t>
         </is>
       </c>
       <c r="Q77" s="6" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="R77" s="6" t="inlineStr">
@@ -13840,7 +13909,7 @@
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>넥스아이</t>
+          <t>동원파츠</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
@@ -13850,22 +13919,22 @@
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>10,500~13,000</t>
+          <t>23,000~26,500</t>
         </is>
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>2,030,000</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>52,500,000,000</t>
+          <t>46,690,000,000</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr">
         <is>
-          <t>19.15배 (PER)</t>
+          <t>22.91배 (PER)</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr"/>
@@ -13873,7 +13942,7 @@
       <c r="I78" s="6" t="inlineStr"/>
       <c r="J78" s="6" t="inlineStr">
         <is>
-          <t>11-03~11-04</t>
+          <t>11-02~11-03</t>
         </is>
       </c>
       <c r="K78" s="6" t="inlineStr"/>
@@ -13881,18 +13950,18 @@
       <c r="M78" s="6" t="inlineStr"/>
       <c r="N78" s="6" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="O78" s="6" t="inlineStr"/>
       <c r="P78" s="7" t="inlineStr">
         <is>
-          <t>2,407,500,000</t>
+          <t>1,430,699,820</t>
         </is>
       </c>
       <c r="Q78" s="6" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="R78" s="6" t="inlineStr">
@@ -13904,32 +13973,32 @@
     <row r="79" ht="30" customHeight="1">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>하나에어로다이내믹스</t>
+          <t>넥스아이</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>11-02~11-06</t>
+          <t>10-22~10-28</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>4,700~5,700</t>
+          <t>10,500~13,000</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>4,400,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>20,680,000,000</t>
+          <t>52,500,000,000</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>17.89배 (EV/EBITDA)</t>
+          <t>19.15배 (PER)</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr"/>
@@ -13937,7 +14006,7 @@
       <c r="I79" s="6" t="inlineStr"/>
       <c r="J79" s="6" t="inlineStr">
         <is>
-          <t>11-10~11-11</t>
+          <t>11-03~11-04</t>
         </is>
       </c>
       <c r="K79" s="6" t="inlineStr"/>
@@ -13945,18 +14014,18 @@
       <c r="M79" s="6" t="inlineStr"/>
       <c r="N79" s="6" t="inlineStr">
         <is>
-          <t>아이비케이투자증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="O79" s="6" t="inlineStr"/>
       <c r="P79" s="7" t="inlineStr">
         <is>
-          <t>850,000,000</t>
-        </is>
-      </c>
-      <c r="Q79" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>2,407,500,000</t>
+        </is>
+      </c>
+      <c r="Q79" s="6" t="inlineStr">
+        <is>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="R79" s="6" t="inlineStr">
@@ -13968,32 +14037,32 @@
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>케이엠에프</t>
+          <t>제논</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>11-16~11-20</t>
+          <t>10-26~10-30</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>15,000~17,800</t>
+          <t>9,700~12,200</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>2,200,000</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>30,000,000,000</t>
+          <t>21,340,000,000</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr">
         <is>
-          <t>18.53배 (PER)</t>
+          <t>36.49배 (PER)</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr"/>
@@ -14001,7 +14070,7 @@
       <c r="I80" s="6" t="inlineStr"/>
       <c r="J80" s="6" t="inlineStr">
         <is>
-          <t>11-24~11-25</t>
+          <t>11-04~11-05</t>
         </is>
       </c>
       <c r="K80" s="6" t="inlineStr"/>
@@ -14009,18 +14078,18 @@
       <c r="M80" s="6" t="inlineStr"/>
       <c r="N80" s="6" t="inlineStr">
         <is>
-          <t>아이비케이투자증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="O80" s="6" t="inlineStr"/>
       <c r="P80" s="7" t="inlineStr">
         <is>
-          <t>927,000,000</t>
+          <t>835,247,600</t>
         </is>
       </c>
       <c r="Q80" s="6" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>3.80%</t>
         </is>
       </c>
       <c r="R80" s="6" t="inlineStr">
@@ -14032,54 +14101,54 @@
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>럭스코</t>
-        </is>
-      </c>
-      <c r="B81" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="C81" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="D81" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="E81" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="F81" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>하나에어로다이내믹스</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>11-02~11-06</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>4,700~5,700</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>4,400,000</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>20,680,000,000</t>
+        </is>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
+        <is>
+          <t>17.89배 (EV/EBITDA)</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr"/>
       <c r="H81" s="6" t="inlineStr"/>
       <c r="I81" s="6" t="inlineStr"/>
-      <c r="J81" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="J81" s="6" t="inlineStr">
+        <is>
+          <t>11-10~11-11</t>
         </is>
       </c>
       <c r="K81" s="6" t="inlineStr"/>
       <c r="L81" s="6" t="inlineStr"/>
       <c r="M81" s="6" t="inlineStr"/>
-      <c r="N81" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="N81" s="6" t="inlineStr">
+        <is>
+          <t>아이비케이투자증권</t>
         </is>
       </c>
       <c r="O81" s="6" t="inlineStr"/>
-      <c r="P81" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P81" s="7" t="inlineStr">
+        <is>
+          <t>850,000,000</t>
         </is>
       </c>
       <c r="Q81" s="18" t="inlineStr">
@@ -14096,59 +14165,59 @@
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>솔리스</t>
-        </is>
-      </c>
-      <c r="B82" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="C82" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="D82" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="E82" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="F82" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>케이엠에프</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="inlineStr">
+        <is>
+          <t>11-16~11-20</t>
+        </is>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>15,000~17,800</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>2,000,000</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>30,000,000,000</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>18.53배 (PER)</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr"/>
       <c r="H82" s="6" t="inlineStr"/>
       <c r="I82" s="6" t="inlineStr"/>
-      <c r="J82" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="J82" s="6" t="inlineStr">
+        <is>
+          <t>11-24~11-25</t>
         </is>
       </c>
       <c r="K82" s="6" t="inlineStr"/>
       <c r="L82" s="6" t="inlineStr"/>
       <c r="M82" s="6" t="inlineStr"/>
-      <c r="N82" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="N82" s="6" t="inlineStr">
+        <is>
+          <t>아이비케이투자증권</t>
         </is>
       </c>
       <c r="O82" s="6" t="inlineStr"/>
-      <c r="P82" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="Q82" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P82" s="7" t="inlineStr">
+        <is>
+          <t>927,000,000</t>
+        </is>
+      </c>
+      <c r="Q82" s="6" t="inlineStr">
+        <is>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="R82" s="6" t="inlineStr">
@@ -14160,7 +14229,7 @@
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>디티에스</t>
+          <t>럭스코</t>
         </is>
       </c>
       <c r="B83" s="18" t="inlineStr">
@@ -14217,14 +14286,14 @@
       </c>
       <c r="R83" s="6" t="inlineStr">
         <is>
-          <t>신고서 대기</t>
+          <t>최초</t>
         </is>
       </c>
     </row>
     <row r="84" ht="30" customHeight="1">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>에이엔에이치스트럭쳐</t>
+          <t>디티에스</t>
         </is>
       </c>
       <c r="B84" s="18" t="inlineStr">
@@ -14288,7 +14357,7 @@
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>이에스티</t>
+          <t>에이엔에이치스트럭쳐</t>
         </is>
       </c>
       <c r="B85" s="18" t="inlineStr">
@@ -14352,7 +14421,7 @@
     <row r="86" ht="30" customHeight="1">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>영광와이케이엠씨</t>
+          <t>이에스티</t>
         </is>
       </c>
       <c r="B86" s="18" t="inlineStr">
@@ -14416,7 +14485,7 @@
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>제논</t>
+          <t>영광와이케이엠씨</t>
         </is>
       </c>
       <c r="B87" s="18" t="inlineStr">
@@ -14541,22 +14610,150 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="20" t="inlineStr">
-        <is>
-          <t>※ 상장 완료 = KIND 신규상장 페이지 기준(스팩합병 포함) · 스팩 공모상장은 밴드·밸류에이션 등 해당없음(공모가 2,000원 고정).</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="20" t="inlineStr">
-        <is>
-          <t>※ 기재정정 신고서 내 정정 전·후 병존 → 자동수집은 "정정 후" 값만 취함.</t>
+    <row r="89" ht="30" customHeight="1">
+      <c r="A89" s="6" t="inlineStr">
+        <is>
+          <t>엔키화이트햇</t>
+        </is>
+      </c>
+      <c r="B89" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="C89" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="D89" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="E89" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="F89" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="inlineStr"/>
+      <c r="H89" s="6" t="inlineStr"/>
+      <c r="I89" s="6" t="inlineStr"/>
+      <c r="J89" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="K89" s="6" t="inlineStr"/>
+      <c r="L89" s="6" t="inlineStr"/>
+      <c r="M89" s="6" t="inlineStr"/>
+      <c r="N89" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="O89" s="6" t="inlineStr"/>
+      <c r="P89" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="Q89" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="R89" s="6" t="inlineStr">
+        <is>
+          <t>신고서 대기</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="30" customHeight="1">
+      <c r="A90" s="6" t="inlineStr">
+        <is>
+          <t>마더스제약</t>
+        </is>
+      </c>
+      <c r="B90" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="C90" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="D90" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="E90" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="F90" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr"/>
+      <c r="H90" s="6" t="inlineStr"/>
+      <c r="I90" s="6" t="inlineStr"/>
+      <c r="J90" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="K90" s="6" t="inlineStr"/>
+      <c r="L90" s="6" t="inlineStr"/>
+      <c r="M90" s="6" t="inlineStr"/>
+      <c r="N90" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="O90" s="6" t="inlineStr"/>
+      <c r="P90" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="Q90" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="R90" s="6" t="inlineStr">
+        <is>
+          <t>신고서 대기</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="20" t="inlineStr">
+        <is>
+          <t>※ 상장 완료 = KIND 신규상장 페이지 기준(스팩합병 포함) · 스팩 공모상장은 밴드·밸류에이션 등 해당없음(공모가 2,000원 고정).</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="20" t="inlineStr">
+        <is>
+          <t>※ 기재정정 신고서 내 정정 전·후 병존 → 자동수집은 "정정 후" 값만 취함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="20" t="inlineStr">
         <is>
           <t>※ 청약경쟁률=일반투자자 청약수량÷최종배정수량 · "MM-DD~"는 종료일 자동수집 예정.</t>
         </is>
@@ -14747,7 +14944,7 @@
         <v>4</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" s="6" t="n">
         <v>3</v>
@@ -14856,10 +15053,10 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D15" s="6" t="n">
         <v>0</v>
@@ -14932,11 +15129,11 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>262,674,000,000</t>
+          <t>284,014,000,000</t>
         </is>
       </c>
     </row>
@@ -15093,7 +15290,7 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>신한투자증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="B31" s="6" t="n">
@@ -15101,14 +15298,14 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>30,240,000,000</t>
+          <t>31,200,000,000</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>신한투자증권</t>
         </is>
       </c>
       <c r="B32" s="6" t="n">
@@ -15116,7 +15313,7 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>27,200,000,000</t>
+          <t>30,240,000,000</t>
         </is>
       </c>
     </row>

--- a/IPO_analysis.xlsx
+++ b/IPO_analysis.xlsx
@@ -592,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K147"/>
+  <dimension ref="A1:K148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -618,14 +618,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>기준일 2026-10-07 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
+          <t>기준일 2026-10-08 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>■ 심사 신청(진행중)  (44건)</t>
+          <t>■ 심사 신청(진행중)  (41건)</t>
         </is>
       </c>
       <c r="B4" s="4" t="n"/>
@@ -699,12 +699,12 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>베르티스</t>
+          <t>세미솔루션</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
@@ -724,27 +724,27 @@
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>5,119</t>
+          <t>16,266</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
-          <t>-12,903</t>
+          <t>791</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>-16,364</t>
+          <t>9,629</t>
         </is>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>의료용품 및 기타 의약 관련제품 제조업</t>
+          <t>반도체 제조업</t>
         </is>
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
@@ -756,12 +756,12 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>뱅크샐러드</t>
+          <t>베르티스</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
@@ -781,27 +781,27 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>25,994</t>
+          <t>5,119</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
         <is>
-          <t>-59,792</t>
+          <t>-12,903</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>28,335</t>
+          <t>-16,364</t>
         </is>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>의료용품 및 기타 의약 관련제품 제조업</t>
         </is>
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
@@ -813,12 +813,12 @@
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>키노톤</t>
+          <t>뱅크샐러드</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -838,27 +838,27 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>46,943</t>
+          <t>25,994</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
         <is>
-          <t>4,222</t>
+          <t>-59,792</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>19,112</t>
+          <t>28,335</t>
         </is>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>건축기술, 엔지니어링 및 관련 기술 서비스업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>티에스모스트</t>
+          <t>키노톤</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
@@ -895,27 +895,27 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>156,198</t>
+          <t>46,943</t>
         </is>
       </c>
       <c r="G9" s="7" t="inlineStr">
         <is>
-          <t>5,666</t>
+          <t>4,222</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>25,181</t>
+          <t>19,112</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>자동차 신품 부품 제조업</t>
+          <t>건축기술, 엔지니어링 및 관련 기술 서비스업</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>신한</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
@@ -927,12 +927,12 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>셀렉트스타</t>
+          <t>티에스모스트</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
@@ -952,27 +952,27 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>11,616</t>
+          <t>156,198</t>
         </is>
       </c>
       <c r="G10" s="7" t="inlineStr">
         <is>
-          <t>-9,883</t>
+          <t>5,666</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>-34,511</t>
+          <t>25,181</t>
         </is>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>자동차 신품 부품 제조업</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>신한</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
@@ -984,12 +984,12 @@
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>서북</t>
+          <t>셀렉트스타</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
@@ -1009,27 +1009,27 @@
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>60,439</t>
+          <t>11,616</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
         <is>
-          <t>-8,764</t>
+          <t>-9,883</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
         <is>
-          <t>4,485</t>
+          <t>-34,511</t>
         </is>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>사진장비 및 광학기기 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>에이스엔지니어링</t>
+          <t>서북</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
@@ -1066,27 +1066,27 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>307,911</t>
+          <t>60,439</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
         <is>
-          <t>-101,468</t>
+          <t>-8,764</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>83,159</t>
+          <t>4,485</t>
         </is>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>전동기, 발전기 및 전기 변환 · 공급 · 제어 장치 제조업</t>
+          <t>사진장비 및 광학기기 제조업</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>대신, 미래, 키움</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>플렉스시스템</t>
+          <t>에이스엔지니어링</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
@@ -1123,27 +1123,27 @@
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>10,894</t>
+          <t>307,911</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
         <is>
-          <t>-2,342</t>
+          <t>-101,468</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
-          <t>3,014</t>
+          <t>83,159</t>
         </is>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업; 광학기기 제외</t>
+          <t>전동기, 발전기 및 전기 변환 · 공급 · 제어 장치 제조업</t>
         </is>
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>대신, 미래, 키움</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
@@ -1155,12 +1155,12 @@
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>엠아이티</t>
+          <t>플렉스시스템</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -1180,27 +1180,27 @@
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>14,921</t>
+          <t>10,894</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
         <is>
-          <t>1,181</t>
+          <t>-2,342</t>
         </is>
       </c>
       <c r="H14" s="7" t="inlineStr">
         <is>
-          <t>28,026</t>
+          <t>3,014</t>
         </is>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업; 광학기기 제외</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>큐로드</t>
+          <t>엠아이티</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
@@ -1235,17 +1235,29 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F15" s="7" t="inlineStr"/>
-      <c r="G15" s="7" t="inlineStr"/>
-      <c r="H15" s="7" t="inlineStr"/>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>14,921</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>1,181</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>28,026</t>
+        </is>
+      </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>교보</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
@@ -1257,12 +1269,12 @@
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>노바셀테크놀로지</t>
+          <t>큐로드</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -1272,7 +1284,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -1280,29 +1292,17 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>377</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>-4,606</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>-15,458</t>
-        </is>
-      </c>
+      <c r="F16" s="7" t="inlineStr"/>
+      <c r="G16" s="7" t="inlineStr"/>
+      <c r="H16" s="7" t="inlineStr"/>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>키움</t>
+          <t>교보</t>
         </is>
       </c>
       <c r="K16" s="6" t="inlineStr">
@@ -1314,12 +1314,12 @@
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>(주)태석광학</t>
+          <t>노바셀테크놀로지</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
@@ -1339,27 +1339,27 @@
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>79,804</t>
+          <t>377</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
         <is>
-          <t>4,721</t>
+          <t>-4,606</t>
         </is>
       </c>
       <c r="H17" s="7" t="inlineStr">
         <is>
-          <t>7,228</t>
+          <t>-15,458</t>
         </is>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
-          <t>생활용품 도매업</t>
+          <t>자연과학 및 공학 연구개발업</t>
         </is>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>신한, 대신</t>
+          <t>키움</t>
         </is>
       </c>
       <c r="K17" s="6" t="inlineStr">
@@ -1371,12 +1371,12 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>엑티브온</t>
+          <t>(주)태석광학</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -1394,17 +1394,29 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr"/>
-      <c r="G18" s="7" t="inlineStr"/>
-      <c r="H18" s="7" t="inlineStr"/>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>79,804</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>4,721</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>7,228</t>
+        </is>
+      </c>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>생활용품 도매업</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>키움</t>
+          <t>신한, 대신</t>
         </is>
       </c>
       <c r="K18" s="6" t="inlineStr">
@@ -1416,12 +1428,12 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>씨앤엠</t>
+          <t>엑티브온</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
@@ -1431,7 +1443,7 @@
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -1439,29 +1451,17 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>238,489</t>
-        </is>
-      </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>19,869</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>112,262</t>
-        </is>
-      </c>
+      <c r="F19" s="7" t="inlineStr"/>
+      <c r="G19" s="7" t="inlineStr"/>
+      <c r="H19" s="7" t="inlineStr"/>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>전동기, 발전기 및 전기 변환 · 공급 · 제어 장치 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>키움</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
@@ -1746,17 +1746,17 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>에스텍시스템</t>
+          <t>범한메카텍</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>유가</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -1771,27 +1771,27 @@
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>975,224</t>
+          <t>339,209</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>24,647</t>
+          <t>-18,141</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>237,182</t>
+          <t>265,955</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>경비, 경호 및 탐정업</t>
+          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>유진, NH</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
@@ -1803,12 +1803,12 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>범한메카텍</t>
+          <t>데스틴파워</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -1828,27 +1828,27 @@
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>339,209</t>
+          <t>29,851</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>-18,141</t>
+          <t>5,852</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>265,955</t>
+          <t>-30,114</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
+          <t>전동기, 발전기 및 전기 변환 · 공급 · 제어 장치 제조업</t>
         </is>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>유진, NH</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr">
@@ -1860,12 +1860,12 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>케이티이</t>
+          <t>유림테크</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -1885,27 +1885,27 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>173,901</t>
+          <t>102,586</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>14,243</t>
+          <t>-18,278</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>94,928</t>
+          <t>-4,832</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>전동기, 발전기 및 전기 변환 · 공급 · 제어 장치 제조업</t>
+          <t>자동차 신품 부품 제조업</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
@@ -1917,12 +1917,12 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>데스틴파워</t>
+          <t>이노보테라퓨틱스</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -1942,22 +1942,22 @@
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>29,851</t>
+          <t>209</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>5,852</t>
+          <t>-5,429</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>-30,114</t>
+          <t>-53,200</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>전동기, 발전기 및 전기 변환 · 공급 · 제어 장치 제조업</t>
+          <t>의약품 제조업</t>
         </is>
       </c>
       <c r="J28" s="6" t="inlineStr">
@@ -1974,17 +1974,17 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>유림테크</t>
+          <t>에스에프씨</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>유가</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -1999,27 +1999,27 @@
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>102,586</t>
+          <t>160,792</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>-18,278</t>
+          <t>25,509</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>-4,832</t>
+          <t>243,562</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>자동차 신품 부품 제조업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>미래, 한국</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
@@ -2031,12 +2031,12 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>이노보테라퓨틱스</t>
+          <t>에버온</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -2056,27 +2056,27 @@
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>65,225</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>-5,429</t>
+          <t>-3,606</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>-53,200</t>
+          <t>54,955</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>의약품 제조업</t>
+          <t>전기업</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
@@ -2088,17 +2088,17 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>에스에프씨</t>
+          <t>씨아이에스케미칼</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>유가</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -2113,27 +2113,27 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>160,792</t>
+          <t>15,985</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>25,509</t>
+          <t>-11,440</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>243,562</t>
+          <t>23,706</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>기초 화학물질 제조업</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>미래, 한국</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="K31" s="6" t="inlineStr">
@@ -2145,12 +2145,12 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>아델</t>
+          <t>엠디에스코리아</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -2170,27 +2170,27 @@
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>62,057</t>
+          <t>97,972</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>-64,210</t>
+          <t>6,512</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>-80,776</t>
+          <t>53,818</t>
         </is>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>그외 기타 전문, 과학 및 기술 서비스업</t>
+          <t>기타 식품 제조업</t>
         </is>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>삼성, 미래</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K32" s="6" t="inlineStr">
@@ -2202,12 +2202,12 @@
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>에버온</t>
+          <t>동승</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -2227,27 +2227,27 @@
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>65,225</t>
+          <t>78,625</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>-3,606</t>
+          <t>14,525</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>54,955</t>
+          <t>5,438</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>전기업</t>
+          <t>부동산 임대 및 공급업</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
@@ -2259,12 +2259,12 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>씨아이에스케미칼</t>
+          <t>에프엠더블유</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -2284,27 +2284,27 @@
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>15,985</t>
+          <t>30,282</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>-11,440</t>
+          <t>4,762</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>23,706</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>기초 화학물질 제조업</t>
+          <t>기타 식품 제조업</t>
         </is>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>유진</t>
         </is>
       </c>
       <c r="K34" s="6" t="inlineStr">
@@ -2316,17 +2316,17 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>엠디에스코리아</t>
+          <t>소노인터내셔널</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>유가</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -2341,27 +2341,27 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>97,972</t>
+          <t>2,093,051</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>6,512</t>
+          <t>-148,064</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>53,818</t>
+          <t>852,372</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>기타 식품 제조업</t>
+          <t>일반 및 생활 숙박시설 운영업</t>
         </is>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>대신, 미래</t>
         </is>
       </c>
       <c r="K35" s="6" t="inlineStr">
@@ -2373,12 +2373,12 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>동승</t>
+          <t>싸이몬</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
@@ -2398,27 +2398,27 @@
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>78,625</t>
+          <t>48,695</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>14,525</t>
+          <t>15,714</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>5,438</t>
+          <t>61,761</t>
         </is>
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>부동산 임대 및 공급업</t>
+          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업</t>
         </is>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K36" s="6" t="inlineStr">
@@ -2430,12 +2430,12 @@
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>에프엠더블유</t>
+          <t>바이다</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
@@ -2455,27 +2455,27 @@
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>30,282</t>
+          <t>14,432</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>4,762</t>
+          <t>-3,951</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>15,108</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>기타 식품 제조업</t>
+          <t>전자부품 제조업</t>
         </is>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>유진</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
@@ -2487,17 +2487,17 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>소노인터내셔널</t>
+          <t>아이알큐더스</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>유가</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
@@ -2512,27 +2512,27 @@
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>2,093,051</t>
+          <t>10,231</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>-148,064</t>
+          <t>-986</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>852,372</t>
+          <t>1,800</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>일반 및 생활 숙박시설 운영업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>대신, 미래</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="K38" s="6" t="inlineStr">
@@ -2544,12 +2544,12 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>싸이몬</t>
+          <t>씨엔티테크</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -2569,27 +2569,27 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>48,695</t>
+          <t>27,015</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>15,714</t>
+          <t>3,987</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>61,761</t>
+          <t>2,613</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>한화, 하나</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr">
@@ -2601,12 +2601,12 @@
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>바이다</t>
+          <t>제이앤티지</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -2626,17 +2626,17 @@
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>14,432</t>
+          <t>72,378</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>-3,951</t>
+          <t>9,904</t>
         </is>
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>15,108</t>
+          <t>6,743</t>
         </is>
       </c>
       <c r="I40" s="6" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>대신, NH</t>
         </is>
       </c>
       <c r="K40" s="6" t="inlineStr">
@@ -2658,12 +2658,12 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>아이알큐더스</t>
+          <t>인터엑스</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -2683,17 +2683,17 @@
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>10,231</t>
+          <t>8,645</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>-986</t>
+          <t>-20,272</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>1,800</t>
+          <t>4,530</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
@@ -2715,12 +2715,12 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>씨엔티테크</t>
+          <t>삼홍아크튜리온</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -2740,27 +2740,27 @@
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>27,015</t>
+          <t>26,162</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>3,987</t>
+          <t>-10,314</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>2,613</t>
+          <t>6,369</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
         </is>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>한화, 하나</t>
+          <t>삼성, 미래</t>
         </is>
       </c>
       <c r="K42" s="6" t="inlineStr">
@@ -2772,12 +2772,12 @@
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>제이앤티지</t>
+          <t>비앤비코리아</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -2797,27 +2797,27 @@
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>72,378</t>
+          <t>141,169</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>9,904</t>
+          <t>21,406</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>6,743</t>
+          <t>43,932</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>전자부품 제조업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>대신, NH</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
@@ -2829,12 +2829,12 @@
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>인터엑스</t>
+          <t>오토핸즈</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
@@ -2854,27 +2854,27 @@
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>8,645</t>
+          <t>238,564</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>-20,272</t>
+          <t>6,047</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>4,530</t>
+          <t>6,129</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>자동차 판매업</t>
         </is>
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K44" s="6" t="inlineStr">
@@ -2886,12 +2886,12 @@
     <row r="45">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>삼홍아크튜리온</t>
+          <t>아이벡스메디칼시스템즈</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
@@ -2911,27 +2911,27 @@
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>26,162</t>
+          <t>15,282</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
         <is>
-          <t>-10,314</t>
+          <t>-7,227</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
         <is>
-          <t>6,369</t>
+          <t>744</t>
         </is>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
-          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>삼성, 미래</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K45" s="6" t="inlineStr">
@@ -2943,12 +2943,12 @@
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>비앤비코리아</t>
+          <t>피지티</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -2968,17 +2968,17 @@
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>141,169</t>
+          <t>40,141</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
         <is>
-          <t>21,406</t>
+          <t>-69,722</t>
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr">
         <is>
-          <t>43,932</t>
+          <t>6,029</t>
         </is>
       </c>
       <c r="I46" s="6" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K46" s="6" t="inlineStr">
@@ -2997,248 +2997,248 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>오토핸즈</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>■ 심사 승인  (76건)</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="n"/>
+      <c r="C48" s="4" t="n"/>
+      <c r="D48" s="4" t="n"/>
+      <c r="E48" s="4" t="n"/>
+      <c r="F48" s="4" t="n"/>
+      <c r="G48" s="4" t="n"/>
+      <c r="H48" s="4" t="n"/>
+      <c r="I48" s="4" t="n"/>
+      <c r="J48" s="4" t="n"/>
+      <c r="K48" s="4" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>일자</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>회사명</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>시장</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>상장유형</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>기준연도</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>자기자본</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>업종</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>대표주관사</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>현황</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>아델</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
         <is>
           <t>코스닥</t>
         </is>
       </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>스팩 소멸합병</t>
-        </is>
-      </c>
-      <c r="E47" s="6" t="inlineStr">
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>신규상장</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
         <is>
           <t>FY25</t>
         </is>
       </c>
-      <c r="F47" s="7" t="inlineStr">
-        <is>
-          <t>238,564</t>
-        </is>
-      </c>
-      <c r="G47" s="7" t="inlineStr">
-        <is>
-          <t>6,047</t>
-        </is>
-      </c>
-      <c r="H47" s="7" t="inlineStr">
-        <is>
-          <t>6,129</t>
-        </is>
-      </c>
-      <c r="I47" s="6" t="inlineStr">
-        <is>
-          <t>자동차 판매업</t>
-        </is>
-      </c>
-      <c r="J47" s="6" t="inlineStr">
-        <is>
-          <t>미래</t>
-        </is>
-      </c>
-      <c r="K47" s="6" t="inlineStr">
-        <is>
-          <t>예심 진행중</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>아이벡스메디칼시스템즈</t>
-        </is>
-      </c>
-      <c r="C48" s="6" t="inlineStr">
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>62,057</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>-64,210</t>
+        </is>
+      </c>
+      <c r="H50" s="7" t="inlineStr">
+        <is>
+          <t>-80,776</t>
+        </is>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>그외 기타 전문, 과학 및 기술 서비스업</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>삼성, 미래</t>
+        </is>
+      </c>
+      <c r="K50" s="6" t="inlineStr">
+        <is>
+          <t>상장전</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="inlineStr">
+        <is>
+          <t>케이티이</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
         <is>
           <t>코스닥</t>
         </is>
       </c>
-      <c r="D48" s="6" t="inlineStr">
+      <c r="D51" s="6" t="inlineStr">
         <is>
           <t>신규상장</t>
         </is>
       </c>
-      <c r="E48" s="6" t="inlineStr">
+      <c r="E51" s="6" t="inlineStr">
         <is>
           <t>FY25</t>
         </is>
       </c>
-      <c r="F48" s="7" t="inlineStr">
-        <is>
-          <t>15,282</t>
-        </is>
-      </c>
-      <c r="G48" s="7" t="inlineStr">
-        <is>
-          <t>-7,227</t>
-        </is>
-      </c>
-      <c r="H48" s="7" t="inlineStr">
-        <is>
-          <t>744</t>
-        </is>
-      </c>
-      <c r="I48" s="6" t="inlineStr">
-        <is>
-          <t>의료용 기기 제조업</t>
-        </is>
-      </c>
-      <c r="J48" s="6" t="inlineStr">
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>173,901</t>
+        </is>
+      </c>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>14,243</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>94,928</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>전동기, 발전기 및 전기 변환 · 공급 · 제어 장치 제조업</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="inlineStr">
         <is>
           <t>NH</t>
         </is>
       </c>
-      <c r="K48" s="6" t="inlineStr">
-        <is>
-          <t>예심 진행중</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="inlineStr">
-        <is>
-          <t>피지티</t>
-        </is>
-      </c>
-      <c r="C49" s="6" t="inlineStr">
+      <c r="K51" s="6" t="inlineStr">
+        <is>
+          <t>상장전</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>씨앤엠</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
         <is>
           <t>코스닥</t>
         </is>
       </c>
-      <c r="D49" s="6" t="inlineStr">
+      <c r="D52" s="6" t="inlineStr">
         <is>
           <t>신규상장</t>
         </is>
       </c>
-      <c r="E49" s="6" t="inlineStr">
+      <c r="E52" s="6" t="inlineStr">
         <is>
           <t>FY25</t>
         </is>
       </c>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
-          <t>40,141</t>
-        </is>
-      </c>
-      <c r="G49" s="7" t="inlineStr">
-        <is>
-          <t>-69,722</t>
-        </is>
-      </c>
-      <c r="H49" s="7" t="inlineStr">
-        <is>
-          <t>6,029</t>
-        </is>
-      </c>
-      <c r="I49" s="6" t="inlineStr">
-        <is>
-          <t>기타 화학제품 제조업</t>
-        </is>
-      </c>
-      <c r="J49" s="6" t="inlineStr">
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>238,489</t>
+        </is>
+      </c>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>19,869</t>
+        </is>
+      </c>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>112,262</t>
+        </is>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>전동기, 발전기 및 전기 변환 · 공급 · 제어 장치 제조업</t>
+        </is>
+      </c>
+      <c r="J52" s="6" t="inlineStr">
         <is>
           <t>한국</t>
         </is>
       </c>
-      <c r="K49" s="6" t="inlineStr">
-        <is>
-          <t>예심 진행중</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="3" t="inlineStr">
-        <is>
-          <t>■ 심사 승인  (73건)</t>
-        </is>
-      </c>
-      <c r="B51" s="4" t="n"/>
-      <c r="C51" s="4" t="n"/>
-      <c r="D51" s="4" t="n"/>
-      <c r="E51" s="4" t="n"/>
-      <c r="F51" s="4" t="n"/>
-      <c r="G51" s="4" t="n"/>
-      <c r="H51" s="4" t="n"/>
-      <c r="I51" s="4" t="n"/>
-      <c r="J51" s="4" t="n"/>
-      <c r="K51" s="4" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>일자</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t>회사명</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>시장</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>상장유형</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>기준연도</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="inlineStr">
-        <is>
-          <t>순이익</t>
-        </is>
-      </c>
-      <c r="H52" s="5" t="inlineStr">
-        <is>
-          <t>자기자본</t>
-        </is>
-      </c>
-      <c r="I52" s="5" t="inlineStr">
-        <is>
-          <t>업종</t>
-        </is>
-      </c>
-      <c r="J52" s="5" t="inlineStr">
-        <is>
-          <t>대표주관사</t>
-        </is>
-      </c>
-      <c r="K52" s="5" t="inlineStr">
-        <is>
-          <t>현황</t>
+      <c r="K52" s="6" t="inlineStr">
+        <is>
+          <t>상장전</t>
         </is>
       </c>
     </row>
@@ -7242,7 +7242,7 @@
     <row r="127">
       <c r="A127" s="3" t="inlineStr">
         <is>
-          <t>■ 철회·미승인  (19건)</t>
+          <t>■ 철회·미승인  (20건)</t>
         </is>
       </c>
       <c r="B127" s="4" t="n"/>
@@ -7316,17 +7316,17 @@
     <row r="129">
       <c r="A129" s="6" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B129" s="6" t="inlineStr">
         <is>
-          <t>넥스트에어로스페이스</t>
+          <t>에스텍시스템</t>
         </is>
       </c>
       <c r="C129" s="6" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>유가</t>
         </is>
       </c>
       <c r="D129" s="6" t="inlineStr">
@@ -7341,27 +7341,27 @@
       </c>
       <c r="F129" s="7" t="inlineStr">
         <is>
-          <t>12,084</t>
+          <t>975,224</t>
         </is>
       </c>
       <c r="G129" s="7" t="inlineStr">
         <is>
-          <t>-17,270</t>
+          <t>24,647</t>
         </is>
       </c>
       <c r="H129" s="7" t="inlineStr">
         <is>
-          <t>6,158</t>
+          <t>237,182</t>
         </is>
       </c>
       <c r="I129" s="6" t="inlineStr">
         <is>
-          <t>유인 항공기, 항공우주선 및 보조장치 제조업</t>
+          <t>경비, 경호 및 탐정업</t>
         </is>
       </c>
       <c r="J129" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K129" s="6" t="inlineStr">
@@ -7373,12 +7373,12 @@
     <row r="130">
       <c r="A130" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>텔레픽스</t>
+          <t>넥스트에어로스페이스</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
@@ -7398,27 +7398,27 @@
       </c>
       <c r="F130" s="7" t="inlineStr">
         <is>
-          <t>4,896</t>
+          <t>12,084</t>
         </is>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
-          <t>-16,214</t>
+          <t>-17,270</t>
         </is>
       </c>
       <c r="H130" s="7" t="inlineStr">
         <is>
-          <t>9,146</t>
+          <t>6,158</t>
         </is>
       </c>
       <c r="I130" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>유인 항공기, 항공우주선 및 보조장치 제조업</t>
         </is>
       </c>
       <c r="J130" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K130" s="6" t="inlineStr">
@@ -7430,12 +7430,12 @@
     <row r="131">
       <c r="A131" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>씨엠디엘</t>
+          <t>텔레픽스</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
@@ -7445,37 +7445,37 @@
       </c>
       <c r="D131" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E131" s="6" t="inlineStr">
         <is>
-          <t>FY24</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="F131" s="7" t="inlineStr">
         <is>
-          <t>39,991</t>
+          <t>4,896</t>
         </is>
       </c>
       <c r="G131" s="7" t="inlineStr">
         <is>
-          <t>3,541</t>
+          <t>-16,214</t>
         </is>
       </c>
       <c r="H131" s="7" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>9,146</t>
         </is>
       </c>
       <c r="I131" s="6" t="inlineStr">
         <is>
-          <t>기타 기초 유기 화학물질 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J131" s="6" t="inlineStr">
         <is>
-          <t>교보</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K131" s="6" t="inlineStr">
@@ -7487,12 +7487,12 @@
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>모비어스</t>
+          <t>씨엠디엘</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
@@ -7502,37 +7502,37 @@
       </c>
       <c r="D132" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
         <is>
-          <t>FY25</t>
+          <t>FY24</t>
         </is>
       </c>
       <c r="F132" s="7" t="inlineStr">
         <is>
-          <t>31,989</t>
+          <t>39,991</t>
         </is>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
-          <t>-45,307</t>
+          <t>3,541</t>
         </is>
       </c>
       <c r="H132" s="7" t="inlineStr">
         <is>
-          <t>-96,707</t>
+          <t>503</t>
         </is>
       </c>
       <c r="I132" s="6" t="inlineStr">
         <is>
-          <t>컴퓨터 프로그래밍, 시스템 통합 및 관리업</t>
+          <t>기타 기초 유기 화학물질 제조업</t>
         </is>
       </c>
       <c r="J132" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>교보</t>
         </is>
       </c>
       <c r="K132" s="6" t="inlineStr">
@@ -7544,12 +7544,12 @@
     <row r="133">
       <c r="A133" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>넥스트젠바이오</t>
+          <t>모비어스</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
@@ -7564,32 +7564,32 @@
       </c>
       <c r="E133" s="6" t="inlineStr">
         <is>
-          <t>FY24</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="F133" s="7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>31,989</t>
         </is>
       </c>
       <c r="G133" s="7" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>-45,307</t>
         </is>
       </c>
       <c r="H133" s="7" t="inlineStr">
         <is>
-          <t>4,792</t>
+          <t>-96,707</t>
         </is>
       </c>
       <c r="I133" s="6" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>컴퓨터 프로그래밍, 시스템 통합 및 관리업</t>
         </is>
       </c>
       <c r="J133" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K133" s="6" t="inlineStr">
@@ -7601,12 +7601,12 @@
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>파워큐브세미</t>
+          <t>넥스트젠바이오</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
@@ -7621,32 +7621,32 @@
       </c>
       <c r="E134" s="6" t="inlineStr">
         <is>
-          <t>FY25</t>
+          <t>FY24</t>
         </is>
       </c>
       <c r="F134" s="7" t="inlineStr">
         <is>
-          <t>10,341</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
-          <t>-10,837</t>
+          <t>69</t>
         </is>
       </c>
       <c r="H134" s="7" t="inlineStr">
         <is>
-          <t>841</t>
+          <t>4,792</t>
         </is>
       </c>
       <c r="I134" s="6" t="inlineStr">
         <is>
-          <t>반도체 제조업</t>
+          <t>자연과학 및 공학 연구개발업</t>
         </is>
       </c>
       <c r="J134" s="6" t="inlineStr">
         <is>
-          <t>하나, BNK</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K134" s="6" t="inlineStr">
@@ -7658,12 +7658,12 @@
     <row r="135">
       <c r="A135" s="6" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>제이피이노베이션</t>
+          <t>파워큐브세미</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
@@ -7683,27 +7683,27 @@
       </c>
       <c r="F135" s="7" t="inlineStr">
         <is>
-          <t>56,324</t>
+          <t>10,341</t>
         </is>
       </c>
       <c r="G135" s="7" t="inlineStr">
         <is>
-          <t>5,588</t>
+          <t>-10,837</t>
         </is>
       </c>
       <c r="H135" s="7" t="inlineStr">
         <is>
-          <t>3,684</t>
+          <t>841</t>
         </is>
       </c>
       <c r="I135" s="6" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>반도체 제조업</t>
         </is>
       </c>
       <c r="J135" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>하나, BNK</t>
         </is>
       </c>
       <c r="K135" s="6" t="inlineStr">
@@ -7715,12 +7715,12 @@
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>케이솔루션</t>
+          <t>제이피이노베이션</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="D136" s="6" t="inlineStr">
         <is>
-          <t>스팩 존속합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E136" s="6" t="inlineStr">
@@ -7740,27 +7740,27 @@
       </c>
       <c r="F136" s="7" t="inlineStr">
         <is>
-          <t>34,565</t>
+          <t>56,324</t>
         </is>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
-          <t>1,158</t>
+          <t>5,588</t>
         </is>
       </c>
       <c r="H136" s="7" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>3,684</t>
         </is>
       </c>
       <c r="I136" s="6" t="inlineStr">
         <is>
-          <t>차체 및 특장차 제조업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="J136" s="6" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K136" s="6" t="inlineStr">
@@ -7772,12 +7772,12 @@
     <row r="137">
       <c r="A137" s="6" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>디토닉</t>
+          <t>케이솔루션</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
@@ -7787,37 +7787,37 @@
       </c>
       <c r="D137" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 존속합병</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
         <is>
-          <t>FY24</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="F137" s="7" t="inlineStr">
         <is>
-          <t>31,293</t>
+          <t>34,565</t>
         </is>
       </c>
       <c r="G137" s="7" t="inlineStr">
         <is>
-          <t>-1,633</t>
+          <t>1,158</t>
         </is>
       </c>
       <c r="H137" s="7" t="inlineStr">
         <is>
-          <t>-21,926</t>
+          <t>653</t>
         </is>
       </c>
       <c r="I137" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>차체 및 특장차 제조업</t>
         </is>
       </c>
       <c r="J137" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="K137" s="6" t="inlineStr">
@@ -7829,12 +7829,12 @@
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>에스케이팩</t>
+          <t>디토닉</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="D138" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
@@ -7854,27 +7854,27 @@
       </c>
       <c r="F138" s="7" t="inlineStr">
         <is>
-          <t>27,310</t>
+          <t>31,293</t>
         </is>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
-          <t>2,257</t>
+          <t>-1,633</t>
         </is>
       </c>
       <c r="H138" s="7" t="inlineStr">
         <is>
-          <t>3,207</t>
+          <t>-21,926</t>
         </is>
       </c>
       <c r="I138" s="6" t="inlineStr">
         <is>
-          <t>용기 세척, 포장 및 충전기 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J138" s="6" t="inlineStr">
         <is>
-          <t>교보</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K138" s="6" t="inlineStr">
@@ -7886,12 +7886,12 @@
     <row r="139">
       <c r="A139" s="6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>메타넷엑스</t>
+          <t>에스케이팩</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="D139" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E139" s="6" t="inlineStr">
@@ -7911,27 +7911,27 @@
       </c>
       <c r="F139" s="7" t="inlineStr">
         <is>
-          <t>244,130</t>
+          <t>27,310</t>
         </is>
       </c>
       <c r="G139" s="7" t="inlineStr">
         <is>
-          <t>13,455</t>
+          <t>2,257</t>
         </is>
       </c>
       <c r="H139" s="7" t="inlineStr">
         <is>
-          <t>9,995</t>
+          <t>3,207</t>
         </is>
       </c>
       <c r="I139" s="6" t="inlineStr">
         <is>
-          <t>컴퓨터 프로그래밍, 시스템 통합 및 관리업</t>
+          <t>용기 세척, 포장 및 충전기 제조업</t>
         </is>
       </c>
       <c r="J139" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>교보</t>
         </is>
       </c>
       <c r="K139" s="6" t="inlineStr">
@@ -7943,12 +7943,12 @@
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>무아스</t>
+          <t>메타넷엑스</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="D140" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
@@ -7968,27 +7968,27 @@
       </c>
       <c r="F140" s="7" t="inlineStr">
         <is>
-          <t>41,813</t>
+          <t>244,130</t>
         </is>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
-          <t>3,903</t>
+          <t>13,455</t>
         </is>
       </c>
       <c r="H140" s="7" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>9,995</t>
         </is>
       </c>
       <c r="I140" s="6" t="inlineStr">
         <is>
-          <t>가정용 전기기기 제조업</t>
+          <t>컴퓨터 프로그래밍, 시스템 통합 및 관리업</t>
         </is>
       </c>
       <c r="J140" s="6" t="inlineStr">
         <is>
-          <t>신한</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K140" s="6" t="inlineStr">
@@ -8005,7 +8005,7 @@
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>유빅스테라퓨틱스</t>
+          <t>무아스</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="D141" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E141" s="6" t="inlineStr">
@@ -8025,27 +8025,27 @@
       </c>
       <c r="F141" s="7" t="inlineStr">
         <is>
-          <t>1,071</t>
+          <t>41,813</t>
         </is>
       </c>
       <c r="G141" s="7" t="inlineStr">
         <is>
-          <t>-15,145</t>
+          <t>3,903</t>
         </is>
       </c>
       <c r="H141" s="7" t="inlineStr">
         <is>
-          <t>5,489</t>
+          <t>532</t>
         </is>
       </c>
       <c r="I141" s="6" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>가정용 전기기기 제조업</t>
         </is>
       </c>
       <c r="J141" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>신한</t>
         </is>
       </c>
       <c r="K141" s="6" t="inlineStr">
@@ -8057,12 +8057,12 @@
     <row r="142">
       <c r="A142" s="6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>코드잇</t>
+          <t>유빅스테라퓨틱스</t>
         </is>
       </c>
       <c r="C142" s="6" t="inlineStr">
@@ -8082,27 +8082,27 @@
       </c>
       <c r="F142" s="7" t="inlineStr">
         <is>
-          <t>30,747</t>
+          <t>1,071</t>
         </is>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
-          <t>6,652</t>
+          <t>-15,145</t>
         </is>
       </c>
       <c r="H142" s="7" t="inlineStr">
         <is>
-          <t>2,403</t>
+          <t>5,489</t>
         </is>
       </c>
       <c r="I142" s="6" t="inlineStr">
         <is>
-          <t>교육지원 서비스업</t>
+          <t>자연과학 및 공학 연구개발업</t>
         </is>
       </c>
       <c r="J142" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K142" s="6" t="inlineStr">
@@ -8114,12 +8114,12 @@
     <row r="143">
       <c r="A143" s="6" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>한컴인스페이스</t>
+          <t>코드잇</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
@@ -8139,44 +8139,44 @@
       </c>
       <c r="F143" s="7" t="inlineStr">
         <is>
-          <t>23,492</t>
+          <t>30,747</t>
         </is>
       </c>
       <c r="G143" s="7" t="inlineStr">
         <is>
-          <t>-3,104</t>
+          <t>6,652</t>
         </is>
       </c>
       <c r="H143" s="7" t="inlineStr">
         <is>
-          <t>5,815</t>
+          <t>2,403</t>
         </is>
       </c>
       <c r="I143" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>교육지원 서비스업</t>
         </is>
       </c>
       <c r="J143" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K143" s="6" t="inlineStr">
         <is>
-          <t>심사 미승인</t>
+          <t>심사 철회</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="6" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>크몽</t>
+          <t>한컴인스페이스</t>
         </is>
       </c>
       <c r="C144" s="6" t="inlineStr">
@@ -8196,44 +8196,44 @@
       </c>
       <c r="F144" s="7" t="inlineStr">
         <is>
-          <t>48,572</t>
+          <t>23,492</t>
         </is>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
-          <t>3,988</t>
+          <t>-3,104</t>
         </is>
       </c>
       <c r="H144" s="7" t="inlineStr">
         <is>
-          <t>4,930</t>
+          <t>5,815</t>
         </is>
       </c>
       <c r="I144" s="6" t="inlineStr">
         <is>
-          <t>기타 정보 서비스업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J144" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K144" s="6" t="inlineStr">
         <is>
-          <t>심사 철회</t>
+          <t>심사 미승인</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="6" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>한화플러스제6호스팩</t>
+          <t>크몽</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
@@ -8253,27 +8253,27 @@
       </c>
       <c r="F145" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>48,572</t>
         </is>
       </c>
       <c r="G145" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3,988</t>
         </is>
       </c>
       <c r="H145" s="7" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4,930</t>
         </is>
       </c>
       <c r="I145" s="6" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>기타 정보 서비스업</t>
         </is>
       </c>
       <c r="J145" s="6" t="inlineStr">
         <is>
-          <t>한화</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K145" s="6" t="inlineStr">
@@ -8285,17 +8285,17 @@
     <row r="146">
       <c r="A146" s="6" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>에식스솔루션즈</t>
+          <t>한화플러스제6호스팩</t>
         </is>
       </c>
       <c r="C146" s="6" t="inlineStr">
         <is>
-          <t>유가</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D146" s="6" t="inlineStr">
@@ -8310,27 +8310,27 @@
       </c>
       <c r="F146" s="7" t="inlineStr">
         <is>
-          <t>2,461</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H146" s="7" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I146" s="6" t="inlineStr">
         <is>
-          <t>절연선 및 케이블 제조업</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="J146" s="6" t="inlineStr">
         <is>
-          <t>한국, 미래</t>
+          <t>한화</t>
         </is>
       </c>
       <c r="K146" s="6" t="inlineStr">
@@ -8342,55 +8342,112 @@
     <row r="147">
       <c r="A147" s="6" t="inlineStr">
         <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B147" s="6" t="inlineStr">
+        <is>
+          <t>에식스솔루션즈</t>
+        </is>
+      </c>
+      <c r="C147" s="6" t="inlineStr">
+        <is>
+          <t>유가</t>
+        </is>
+      </c>
+      <c r="D147" s="6" t="inlineStr">
+        <is>
+          <t>신규상장</t>
+        </is>
+      </c>
+      <c r="E147" s="6" t="inlineStr">
+        <is>
+          <t>FY24</t>
+        </is>
+      </c>
+      <c r="F147" s="7" t="inlineStr">
+        <is>
+          <t>2,461</t>
+        </is>
+      </c>
+      <c r="G147" s="7" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="H147" s="7" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I147" s="6" t="inlineStr">
+        <is>
+          <t>절연선 및 케이블 제조업</t>
+        </is>
+      </c>
+      <c r="J147" s="6" t="inlineStr">
+        <is>
+          <t>한국, 미래</t>
+        </is>
+      </c>
+      <c r="K147" s="6" t="inlineStr">
+        <is>
+          <t>심사 철회</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="6" t="inlineStr">
+        <is>
           <t>2026-01-23</t>
         </is>
       </c>
-      <c r="B147" s="6" t="inlineStr">
+      <c r="B148" s="6" t="inlineStr">
         <is>
           <t>에코크레이션</t>
         </is>
       </c>
-      <c r="C147" s="6" t="inlineStr">
+      <c r="C148" s="6" t="inlineStr">
         <is>
           <t>코스닥</t>
         </is>
       </c>
-      <c r="D147" s="6" t="inlineStr">
+      <c r="D148" s="6" t="inlineStr">
         <is>
           <t>신규상장</t>
         </is>
       </c>
-      <c r="E147" s="6" t="inlineStr">
+      <c r="E148" s="6" t="inlineStr">
         <is>
           <t>FY24</t>
         </is>
       </c>
-      <c r="F147" s="7" t="inlineStr">
+      <c r="F148" s="7" t="inlineStr">
         <is>
           <t>18,544</t>
         </is>
       </c>
-      <c r="G147" s="7" t="inlineStr">
+      <c r="G148" s="7" t="inlineStr">
         <is>
           <t>-15,634</t>
         </is>
       </c>
-      <c r="H147" s="7" t="inlineStr">
+      <c r="H148" s="7" t="inlineStr">
         <is>
           <t>4,550</t>
         </is>
       </c>
-      <c r="I147" s="6" t="inlineStr">
+      <c r="I148" s="6" t="inlineStr">
         <is>
           <t>일반 목적용 기계 제조업</t>
         </is>
       </c>
-      <c r="J147" s="6" t="inlineStr">
+      <c r="J148" s="6" t="inlineStr">
         <is>
           <t>키움</t>
         </is>
       </c>
-      <c r="K147" s="6" t="inlineStr">
+      <c r="K148" s="6" t="inlineStr">
         <is>
           <t>심사 철회</t>
         </is>
@@ -8407,7 +8464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R94"/>
+  <dimension ref="A1:R97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -12489,7 +12546,7 @@
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>■ 공모 진행 (예심 승인법인)  (34건)</t>
+          <t>■ 공모 진행 (예심 승인법인)  (37건)</t>
         </is>
       </c>
       <c r="B56" s="4" t="n"/>
@@ -12730,7 +12787,7 @@
       </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
-          <t>발행조건확정</t>
+          <t>청약완료·상장대기</t>
         </is>
       </c>
     </row>
@@ -13205,32 +13262,32 @@
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>래블업</t>
+          <t>인텔리빅스</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>10-13~10-19</t>
+          <t>10-12~10-16</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>19,000~22,000</t>
+          <t>7,600~9,000</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>2,180,000</t>
+          <t>2,500,000</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>41,420,000,000</t>
+          <t>19,000,000,000</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>33.6배 (PER)</t>
+          <t>22.02배 (PER)</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr"/>
@@ -13238,7 +13295,7 @@
       <c r="I67" s="6" t="inlineStr"/>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t>10-22~10-23</t>
+          <t>10-21~10-22</t>
         </is>
       </c>
       <c r="K67" s="6" t="inlineStr"/>
@@ -13246,18 +13303,18 @@
       <c r="M67" s="6" t="inlineStr"/>
       <c r="N67" s="6" t="inlineStr">
         <is>
-          <t>NH투자증권</t>
+          <t>미래에셋증권</t>
         </is>
       </c>
       <c r="O67" s="6" t="inlineStr"/>
       <c r="P67" s="7" t="inlineStr">
         <is>
-          <t>1,908,899,000</t>
+          <t>782,800,000</t>
         </is>
       </c>
       <c r="Q67" s="6" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="R67" s="6" t="inlineStr">
@@ -13269,32 +13326,32 @@
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>한화플러스제6호스팩</t>
+          <t>래블업</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>10-14~10-15</t>
-        </is>
-      </c>
-      <c r="C68" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>10-13~10-19</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>19,000~22,000</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>6,000,000</t>
+          <t>2,180,000</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>12,000,000,000</t>
-        </is>
-      </c>
-      <c r="F68" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>41,420,000,000</t>
+        </is>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>33.6배 (PER)</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr"/>
@@ -13302,26 +13359,26 @@
       <c r="I68" s="6" t="inlineStr"/>
       <c r="J68" s="6" t="inlineStr">
         <is>
-          <t>10-20~10-21</t>
+          <t>10-22~10-23</t>
         </is>
       </c>
       <c r="K68" s="6" t="inlineStr"/>
       <c r="L68" s="6" t="inlineStr"/>
       <c r="M68" s="6" t="inlineStr"/>
-      <c r="N68" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="N68" s="6" t="inlineStr">
+        <is>
+          <t>NH투자증권</t>
         </is>
       </c>
       <c r="O68" s="6" t="inlineStr"/>
-      <c r="P68" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P68" s="7" t="inlineStr">
+        <is>
+          <t>1,908,899,000</t>
         </is>
       </c>
       <c r="Q68" s="6" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="R68" s="6" t="inlineStr">
@@ -13333,32 +13390,32 @@
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>엠비디</t>
+          <t>한화플러스제6호스팩</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>10-16~10-22</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>9,600~11,700</t>
+          <t>10-14~10-15</t>
+        </is>
+      </c>
+      <c r="C69" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>6,000,000</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>19,200,000,000</t>
-        </is>
-      </c>
-      <c r="F69" s="6" t="inlineStr">
-        <is>
-          <t>26.87배 (PER)</t>
+          <t>12,000,000,000</t>
+        </is>
+      </c>
+      <c r="F69" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr"/>
@@ -13366,26 +13423,26 @@
       <c r="I69" s="6" t="inlineStr"/>
       <c r="J69" s="6" t="inlineStr">
         <is>
-          <t>10-28~10-29</t>
+          <t>10-20~10-21</t>
         </is>
       </c>
       <c r="K69" s="6" t="inlineStr"/>
       <c r="L69" s="6" t="inlineStr"/>
       <c r="M69" s="6" t="inlineStr"/>
-      <c r="N69" s="6" t="inlineStr">
-        <is>
-          <t>하나증권</t>
+      <c r="N69" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="O69" s="6" t="inlineStr"/>
-      <c r="P69" s="7" t="inlineStr">
-        <is>
-          <t>988,800,000</t>
+      <c r="P69" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="Q69" s="6" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="R69" s="6" t="inlineStr">
@@ -13397,59 +13454,59 @@
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>바로팜</t>
-        </is>
-      </c>
-      <c r="B70" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>엠비디</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>10-16~10-22</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>16,400~20,200</t>
+          <t>9,600~11,700</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>1,780,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>29,192,000,000</t>
+          <t>19,200,000,000</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>24.95배 (PER)</t>
+          <t>26.87배 (PER)</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr"/>
       <c r="H70" s="6" t="inlineStr"/>
       <c r="I70" s="6" t="inlineStr"/>
-      <c r="J70" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="J70" s="6" t="inlineStr">
+        <is>
+          <t>10-28~10-29</t>
         </is>
       </c>
       <c r="K70" s="6" t="inlineStr"/>
       <c r="L70" s="6" t="inlineStr"/>
       <c r="M70" s="6" t="inlineStr"/>
-      <c r="N70" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="N70" s="6" t="inlineStr">
+        <is>
+          <t>하나증권</t>
         </is>
       </c>
       <c r="O70" s="6" t="inlineStr"/>
-      <c r="P70" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="Q70" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P70" s="7" t="inlineStr">
+        <is>
+          <t>988,800,000</t>
+        </is>
+      </c>
+      <c r="Q70" s="6" t="inlineStr">
+        <is>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="R70" s="6" t="inlineStr">
@@ -13461,7 +13518,7 @@
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>셀트릭스</t>
+          <t>바로팜</t>
         </is>
       </c>
       <c r="B71" s="18" t="inlineStr">
@@ -13469,24 +13526,24 @@
           <t>수집예정</t>
         </is>
       </c>
-      <c r="C71" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="D71" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="E71" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="F71" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>16,400~20,200</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>1,780,000</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>29,192,000,000</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>24.95배 (PER)</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr"/>
@@ -13525,7 +13582,7 @@
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>솔리스</t>
+          <t>셀트릭스</t>
         </is>
       </c>
       <c r="B72" s="18" t="inlineStr">
@@ -13589,64 +13646,64 @@
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>인텔리빅스</t>
-        </is>
-      </c>
-      <c r="B73" s="6" t="inlineStr">
-        <is>
-          <t>10-12~10-16</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>7,600~9,000</t>
-        </is>
-      </c>
-      <c r="D73" s="7" t="inlineStr">
-        <is>
-          <t>2,500,000</t>
-        </is>
-      </c>
-      <c r="E73" s="7" t="inlineStr">
-        <is>
-          <t>19,000,000,000</t>
-        </is>
-      </c>
-      <c r="F73" s="6" t="inlineStr">
-        <is>
-          <t>22.02배 (PER)</t>
+          <t>솔리스</t>
+        </is>
+      </c>
+      <c r="B73" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="C73" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="D73" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="E73" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="F73" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr"/>
       <c r="H73" s="6" t="inlineStr"/>
       <c r="I73" s="6" t="inlineStr"/>
-      <c r="J73" s="6" t="inlineStr">
-        <is>
-          <t>10-21~10-22</t>
+      <c r="J73" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="K73" s="6" t="inlineStr"/>
       <c r="L73" s="6" t="inlineStr"/>
       <c r="M73" s="6" t="inlineStr"/>
-      <c r="N73" s="6" t="inlineStr">
-        <is>
-          <t>미래에셋증권</t>
+      <c r="N73" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="O73" s="6" t="inlineStr"/>
-      <c r="P73" s="7" t="inlineStr">
-        <is>
-          <t>782,800,000</t>
-        </is>
-      </c>
-      <c r="Q73" s="6" t="inlineStr">
-        <is>
-          <t>4.0%</t>
+      <c r="P73" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="Q73" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="R73" s="6" t="inlineStr">
         <is>
-          <t>최초</t>
+          <t>정정</t>
         </is>
       </c>
     </row>
@@ -14229,7 +14286,7 @@
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>럭스코</t>
+          <t>영광와이케이엠씨</t>
         </is>
       </c>
       <c r="B83" s="18" t="inlineStr">
@@ -14293,7 +14350,7 @@
     <row r="84" ht="30" customHeight="1">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>디티에스</t>
+          <t>럭스코</t>
         </is>
       </c>
       <c r="B84" s="18" t="inlineStr">
@@ -14350,14 +14407,14 @@
       </c>
       <c r="R84" s="6" t="inlineStr">
         <is>
-          <t>신고서 대기</t>
+          <t>최초</t>
         </is>
       </c>
     </row>
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>에이엔에이치스트럭쳐</t>
+          <t>엔키화이트햇</t>
         </is>
       </c>
       <c r="B85" s="18" t="inlineStr">
@@ -14414,14 +14471,14 @@
       </c>
       <c r="R85" s="6" t="inlineStr">
         <is>
-          <t>신고서 대기</t>
+          <t>최초</t>
         </is>
       </c>
     </row>
     <row r="86" ht="30" customHeight="1">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>이에스티</t>
+          <t>아델</t>
         </is>
       </c>
       <c r="B86" s="18" t="inlineStr">
@@ -14478,14 +14535,14 @@
       </c>
       <c r="R86" s="6" t="inlineStr">
         <is>
-          <t>신고서 대기</t>
+          <t>corp_code 미확보(수동확인)</t>
         </is>
       </c>
     </row>
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>영광와이케이엠씨</t>
+          <t>케이티이</t>
         </is>
       </c>
       <c r="B87" s="18" t="inlineStr">
@@ -14542,14 +14599,14 @@
       </c>
       <c r="R87" s="6" t="inlineStr">
         <is>
-          <t>신고서 대기</t>
+          <t>corp_code 미확보(수동확인)</t>
         </is>
       </c>
     </row>
     <row r="88" ht="30" customHeight="1">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>우리투자제1호스팩</t>
+          <t>씨앤엠</t>
         </is>
       </c>
       <c r="B88" s="18" t="inlineStr">
@@ -14606,14 +14663,14 @@
       </c>
       <c r="R88" s="6" t="inlineStr">
         <is>
-          <t>신고서 대기</t>
+          <t>corp_code 미확보(수동확인)</t>
         </is>
       </c>
     </row>
     <row r="89" ht="30" customHeight="1">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>엔키화이트햇</t>
+          <t>디티에스</t>
         </is>
       </c>
       <c r="B89" s="18" t="inlineStr">
@@ -14677,7 +14734,7 @@
     <row r="90" ht="30" customHeight="1">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>마더스제약</t>
+          <t>에이엔에이치스트럭쳐</t>
         </is>
       </c>
       <c r="B90" s="18" t="inlineStr">
@@ -14738,22 +14795,214 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="20" t="inlineStr">
+    <row r="91" ht="30" customHeight="1">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>이에스티</t>
+        </is>
+      </c>
+      <c r="B91" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="C91" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="D91" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="E91" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="F91" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="inlineStr"/>
+      <c r="H91" s="6" t="inlineStr"/>
+      <c r="I91" s="6" t="inlineStr"/>
+      <c r="J91" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="K91" s="6" t="inlineStr"/>
+      <c r="L91" s="6" t="inlineStr"/>
+      <c r="M91" s="6" t="inlineStr"/>
+      <c r="N91" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="O91" s="6" t="inlineStr"/>
+      <c r="P91" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="Q91" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="R91" s="6" t="inlineStr">
+        <is>
+          <t>신고서 대기</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="30" customHeight="1">
+      <c r="A92" s="6" t="inlineStr">
+        <is>
+          <t>우리투자제1호스팩</t>
+        </is>
+      </c>
+      <c r="B92" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="C92" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="D92" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="E92" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="F92" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr"/>
+      <c r="H92" s="6" t="inlineStr"/>
+      <c r="I92" s="6" t="inlineStr"/>
+      <c r="J92" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="K92" s="6" t="inlineStr"/>
+      <c r="L92" s="6" t="inlineStr"/>
+      <c r="M92" s="6" t="inlineStr"/>
+      <c r="N92" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="O92" s="6" t="inlineStr"/>
+      <c r="P92" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="Q92" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="R92" s="6" t="inlineStr">
+        <is>
+          <t>신고서 대기</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="30" customHeight="1">
+      <c r="A93" s="6" t="inlineStr">
+        <is>
+          <t>마더스제약</t>
+        </is>
+      </c>
+      <c r="B93" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="C93" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="D93" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="E93" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="F93" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="G93" s="6" t="inlineStr"/>
+      <c r="H93" s="6" t="inlineStr"/>
+      <c r="I93" s="6" t="inlineStr"/>
+      <c r="J93" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="K93" s="6" t="inlineStr"/>
+      <c r="L93" s="6" t="inlineStr"/>
+      <c r="M93" s="6" t="inlineStr"/>
+      <c r="N93" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="O93" s="6" t="inlineStr"/>
+      <c r="P93" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="Q93" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="R93" s="6" t="inlineStr">
+        <is>
+          <t>신고서 대기</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="20" t="inlineStr">
         <is>
           <t>※ 상장 완료 = KIND 신규상장 페이지 기준(스팩합병 포함) · 스팩 공모상장은 밴드·밸류에이션 등 해당없음(공모가 2,000원 고정).</t>
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="20" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="20" t="inlineStr">
         <is>
           <t>※ 기재정정 신고서 내 정정 전·후 병존 → 자동수집은 "정정 후" 값만 취함.</t>
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="20" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="20" t="inlineStr">
         <is>
           <t>※ 청약경쟁률=일반투자자 청약수량÷최종배정수량 · "MM-DD~"는 종료일 자동수집 예정.</t>
         </is>
@@ -15053,13 +15302,13 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="6" t="n">
         <v>1</v>

--- a/IPO_analysis.xlsx
+++ b/IPO_analysis.xlsx
@@ -13390,32 +13390,32 @@
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>한화플러스제6호스팩</t>
+          <t>영광</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>10-14~10-15</t>
-        </is>
-      </c>
-      <c r="C69" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>10-13~10-19</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>14,000~17,000</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>6,000,000</t>
+          <t>2,260,000</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>12,000,000,000</t>
-        </is>
-      </c>
-      <c r="F69" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>31,640,000,000</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>11.98배 (EV/EBITDA)</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr"/>
@@ -13423,26 +13423,26 @@
       <c r="I69" s="6" t="inlineStr"/>
       <c r="J69" s="6" t="inlineStr">
         <is>
-          <t>10-20~10-21</t>
+          <t>10-22~10-23</t>
         </is>
       </c>
       <c r="K69" s="6" t="inlineStr"/>
       <c r="L69" s="6" t="inlineStr"/>
       <c r="M69" s="6" t="inlineStr"/>
-      <c r="N69" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="N69" s="6" t="inlineStr">
+        <is>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="O69" s="6" t="inlineStr"/>
-      <c r="P69" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="Q69" s="6" t="inlineStr">
-        <is>
-          <t>3.50%</t>
+      <c r="P69" s="7" t="inlineStr">
+        <is>
+          <t>977,676,000</t>
+        </is>
+      </c>
+      <c r="Q69" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="R69" s="6" t="inlineStr">
@@ -13454,32 +13454,32 @@
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>엠비디</t>
+          <t>한화플러스제6호스팩</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>10-16~10-22</t>
-        </is>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>9,600~11,700</t>
+          <t>10-14~10-15</t>
+        </is>
+      </c>
+      <c r="C70" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>6,000,000</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>19,200,000,000</t>
-        </is>
-      </c>
-      <c r="F70" s="6" t="inlineStr">
-        <is>
-          <t>26.87배 (PER)</t>
+          <t>12,000,000,000</t>
+        </is>
+      </c>
+      <c r="F70" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr"/>
@@ -13487,26 +13487,26 @@
       <c r="I70" s="6" t="inlineStr"/>
       <c r="J70" s="6" t="inlineStr">
         <is>
-          <t>10-28~10-29</t>
+          <t>10-20~10-21</t>
         </is>
       </c>
       <c r="K70" s="6" t="inlineStr"/>
       <c r="L70" s="6" t="inlineStr"/>
       <c r="M70" s="6" t="inlineStr"/>
-      <c r="N70" s="6" t="inlineStr">
-        <is>
-          <t>하나증권</t>
+      <c r="N70" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="O70" s="6" t="inlineStr"/>
-      <c r="P70" s="7" t="inlineStr">
-        <is>
-          <t>988,800,000</t>
+      <c r="P70" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="Q70" s="6" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="R70" s="6" t="inlineStr">
@@ -13518,59 +13518,59 @@
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>바로팜</t>
-        </is>
-      </c>
-      <c r="B71" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>엠비디</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>10-16~10-22</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>16,400~20,200</t>
+          <t>9,600~11,700</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>1,780,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>29,192,000,000</t>
+          <t>19,200,000,000</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>24.95배 (PER)</t>
+          <t>26.87배 (PER)</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr"/>
       <c r="H71" s="6" t="inlineStr"/>
       <c r="I71" s="6" t="inlineStr"/>
-      <c r="J71" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="J71" s="6" t="inlineStr">
+        <is>
+          <t>10-28~10-29</t>
         </is>
       </c>
       <c r="K71" s="6" t="inlineStr"/>
       <c r="L71" s="6" t="inlineStr"/>
       <c r="M71" s="6" t="inlineStr"/>
-      <c r="N71" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="N71" s="6" t="inlineStr">
+        <is>
+          <t>하나증권</t>
         </is>
       </c>
       <c r="O71" s="6" t="inlineStr"/>
-      <c r="P71" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="Q71" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P71" s="7" t="inlineStr">
+        <is>
+          <t>988,800,000</t>
+        </is>
+      </c>
+      <c r="Q71" s="6" t="inlineStr">
+        <is>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="R71" s="6" t="inlineStr">
@@ -13582,12 +13582,12 @@
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>셀트릭스</t>
-        </is>
-      </c>
-      <c r="B72" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>아이엠스팩1호</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="inlineStr">
+        <is>
+          <t>10-19~10-20</t>
         </is>
       </c>
       <c r="C72" s="18" t="inlineStr">
@@ -13595,14 +13595,14 @@
           <t>수집예정</t>
         </is>
       </c>
-      <c r="D72" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="E72" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>5,000,000</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>10,000,000,000</t>
         </is>
       </c>
       <c r="F72" s="18" t="inlineStr">
@@ -13613,9 +13613,9 @@
       <c r="G72" s="6" t="inlineStr"/>
       <c r="H72" s="6" t="inlineStr"/>
       <c r="I72" s="6" t="inlineStr"/>
-      <c r="J72" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="J72" s="6" t="inlineStr">
+        <is>
+          <t>10-26~10-27</t>
         </is>
       </c>
       <c r="K72" s="6" t="inlineStr"/>
@@ -13632,9 +13632,9 @@
           <t>수집예정</t>
         </is>
       </c>
-      <c r="Q72" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="Q72" s="6" t="inlineStr">
+        <is>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="R72" s="6" t="inlineStr">
@@ -13646,7 +13646,7 @@
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>솔리스</t>
+          <t>바로팜</t>
         </is>
       </c>
       <c r="B73" s="18" t="inlineStr">
@@ -13654,24 +13654,24 @@
           <t>수집예정</t>
         </is>
       </c>
-      <c r="C73" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="D73" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="E73" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="F73" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>16,400~20,200</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>1,780,000</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>29,192,000,000</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>24.95배 (PER)</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr"/>
@@ -13710,54 +13710,54 @@
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>영광</t>
-        </is>
-      </c>
-      <c r="B74" s="6" t="inlineStr">
-        <is>
-          <t>10-13~10-19</t>
-        </is>
-      </c>
-      <c r="C74" s="6" t="inlineStr">
-        <is>
-          <t>14,000~17,000</t>
-        </is>
-      </c>
-      <c r="D74" s="7" t="inlineStr">
-        <is>
-          <t>2,260,000</t>
-        </is>
-      </c>
-      <c r="E74" s="7" t="inlineStr">
-        <is>
-          <t>31,640,000,000</t>
-        </is>
-      </c>
-      <c r="F74" s="6" t="inlineStr">
-        <is>
-          <t>11.98배 (EV/EBITDA)</t>
+          <t>셀트릭스</t>
+        </is>
+      </c>
+      <c r="B74" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="C74" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="D74" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="E74" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="F74" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr"/>
       <c r="H74" s="6" t="inlineStr"/>
       <c r="I74" s="6" t="inlineStr"/>
-      <c r="J74" s="6" t="inlineStr">
-        <is>
-          <t>10-22~10-23</t>
+      <c r="J74" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="K74" s="6" t="inlineStr"/>
       <c r="L74" s="6" t="inlineStr"/>
       <c r="M74" s="6" t="inlineStr"/>
-      <c r="N74" s="6" t="inlineStr">
-        <is>
-          <t>한국투자증권</t>
+      <c r="N74" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="O74" s="6" t="inlineStr"/>
-      <c r="P74" s="7" t="inlineStr">
-        <is>
-          <t>977,676,000</t>
+      <c r="P74" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="Q74" s="18" t="inlineStr">
@@ -13767,103 +13767,103 @@
       </c>
       <c r="R74" s="6" t="inlineStr">
         <is>
-          <t>최초</t>
+          <t>정정</t>
         </is>
       </c>
     </row>
     <row r="75" ht="30" customHeight="1">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>에이엘로봇</t>
-        </is>
-      </c>
-      <c r="B75" s="6" t="inlineStr">
-        <is>
-          <t>10-15~10-21</t>
-        </is>
-      </c>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>15,700~17,600</t>
-        </is>
-      </c>
-      <c r="D75" s="7" t="inlineStr">
-        <is>
-          <t>2,400,000</t>
-        </is>
-      </c>
-      <c r="E75" s="7" t="inlineStr">
-        <is>
-          <t>37,680,000,000</t>
-        </is>
-      </c>
-      <c r="F75" s="6" t="inlineStr">
-        <is>
-          <t>37.17배 (PER)</t>
+          <t>솔리스</t>
+        </is>
+      </c>
+      <c r="B75" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="C75" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="D75" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="E75" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="F75" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr"/>
       <c r="H75" s="6" t="inlineStr"/>
       <c r="I75" s="6" t="inlineStr"/>
-      <c r="J75" s="6" t="inlineStr">
-        <is>
-          <t>10-26~10-27</t>
+      <c r="J75" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="K75" s="6" t="inlineStr"/>
       <c r="L75" s="6" t="inlineStr"/>
       <c r="M75" s="6" t="inlineStr"/>
-      <c r="N75" s="6" t="inlineStr">
-        <is>
-          <t>대신증권</t>
+      <c r="N75" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="O75" s="6" t="inlineStr"/>
-      <c r="P75" s="7" t="inlineStr">
-        <is>
-          <t>1,160,399,874</t>
-        </is>
-      </c>
-      <c r="Q75" s="6" t="inlineStr">
-        <is>
-          <t>3.0%</t>
+      <c r="P75" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="Q75" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="R75" s="6" t="inlineStr">
         <is>
-          <t>최초</t>
+          <t>정정</t>
         </is>
       </c>
     </row>
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>아이엠스팩1호</t>
+          <t>에이엘로봇</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>10-19~10-20</t>
-        </is>
-      </c>
-      <c r="C76" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>10-15~10-21</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>15,700~17,600</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>2,400,000</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>10,000,000,000</t>
-        </is>
-      </c>
-      <c r="F76" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>37,680,000,000</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>37.17배 (PER)</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr"/>
@@ -13877,20 +13877,20 @@
       <c r="K76" s="6" t="inlineStr"/>
       <c r="L76" s="6" t="inlineStr"/>
       <c r="M76" s="6" t="inlineStr"/>
-      <c r="N76" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="N76" s="6" t="inlineStr">
+        <is>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="O76" s="6" t="inlineStr"/>
-      <c r="P76" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P76" s="7" t="inlineStr">
+        <is>
+          <t>1,160,399,874</t>
         </is>
       </c>
       <c r="Q76" s="6" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="R76" s="6" t="inlineStr">

--- a/IPO_analysis.xlsx
+++ b/IPO_analysis.xlsx
@@ -618,7 +618,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>기준일 2026-10-08 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
+          <t>기준일 2026-10-09 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
         </is>
       </c>
     </row>

--- a/IPO_analysis.xlsx
+++ b/IPO_analysis.xlsx
@@ -618,7 +618,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>기준일 2026-10-09 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
+          <t>기준일 2026-10-10 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
         </is>
       </c>
     </row>

--- a/IPO_analysis.xlsx
+++ b/IPO_analysis.xlsx
@@ -618,7 +618,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>기준일 2026-10-10 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
+          <t>기준일 2026-10-11 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
         </is>
       </c>
     </row>
@@ -13070,32 +13070,32 @@
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>다비오</t>
+          <t>에스케이증권제14호기업인수목적</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>10-07~10-14</t>
-        </is>
-      </c>
-      <c r="C64" s="6" t="inlineStr">
-        <is>
-          <t>12,300~16,600</t>
+          <t>10-12~10-13</t>
+        </is>
+      </c>
+      <c r="C64" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>1,000,000</t>
+          <t>6,500,000</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>12,300,000,000</t>
-        </is>
-      </c>
-      <c r="F64" s="6" t="inlineStr">
-        <is>
-          <t>26.70배 (PER)</t>
+          <t>13,000,000,000</t>
+        </is>
+      </c>
+      <c r="F64" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr"/>
@@ -13103,26 +13103,26 @@
       <c r="I64" s="6" t="inlineStr"/>
       <c r="J64" s="6" t="inlineStr">
         <is>
-          <t>10-19~10-20</t>
+          <t>10-15~10-16</t>
         </is>
       </c>
       <c r="K64" s="6" t="inlineStr"/>
       <c r="L64" s="6" t="inlineStr"/>
       <c r="M64" s="6" t="inlineStr"/>
-      <c r="N64" s="6" t="inlineStr">
-        <is>
-          <t>대신증권</t>
+      <c r="N64" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="O64" s="6" t="inlineStr"/>
-      <c r="P64" s="7" t="inlineStr">
-        <is>
-          <t>570,105,000</t>
+      <c r="P64" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="Q64" s="6" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="R64" s="6" t="inlineStr">
@@ -13134,32 +13134,32 @@
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>에스케이증권제14호기업인수목적</t>
+          <t>크리에이츠</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>10-12~10-13</t>
-        </is>
-      </c>
-      <c r="C65" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>10-12~10-16</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>15,000~18,000</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>6,500,000</t>
+          <t>1,400,000</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>13,000,000,000</t>
-        </is>
-      </c>
-      <c r="F65" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>21,000,000,000</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>19.15배 (PER)</t>
         </is>
       </c>
       <c r="G65" s="6" t="inlineStr"/>
@@ -13167,26 +13167,26 @@
       <c r="I65" s="6" t="inlineStr"/>
       <c r="J65" s="6" t="inlineStr">
         <is>
-          <t>10-15~10-16</t>
+          <t>10-20~10-21</t>
         </is>
       </c>
       <c r="K65" s="6" t="inlineStr"/>
       <c r="L65" s="6" t="inlineStr"/>
       <c r="M65" s="6" t="inlineStr"/>
-      <c r="N65" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="N65" s="6" t="inlineStr">
+        <is>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="O65" s="6" t="inlineStr"/>
-      <c r="P65" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P65" s="7" t="inlineStr">
+        <is>
+          <t>865,200,000</t>
         </is>
       </c>
       <c r="Q65" s="6" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="R65" s="6" t="inlineStr">
@@ -13198,7 +13198,7 @@
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>크리에이츠</t>
+          <t>인텔리빅스</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
@@ -13208,22 +13208,22 @@
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>15,000~18,000</t>
+          <t>7,600~9,000</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>1,400,000</t>
+          <t>2,500,000</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>21,000,000,000</t>
+          <t>19,000,000,000</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>19.15배 (PER)</t>
+          <t>22.02배 (PER)</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr"/>
@@ -13231,7 +13231,7 @@
       <c r="I66" s="6" t="inlineStr"/>
       <c r="J66" s="6" t="inlineStr">
         <is>
-          <t>10-20~10-21</t>
+          <t>10-21~10-22</t>
         </is>
       </c>
       <c r="K66" s="6" t="inlineStr"/>
@@ -13239,13 +13239,13 @@
       <c r="M66" s="6" t="inlineStr"/>
       <c r="N66" s="6" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>미래에셋증권</t>
         </is>
       </c>
       <c r="O66" s="6" t="inlineStr"/>
       <c r="P66" s="7" t="inlineStr">
         <is>
-          <t>865,200,000</t>
+          <t>782,800,000</t>
         </is>
       </c>
       <c r="Q66" s="6" t="inlineStr">
@@ -13262,32 +13262,32 @@
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>인텔리빅스</t>
+          <t>래블업</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>10-12~10-16</t>
+          <t>10-13~10-19</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>7,600~9,000</t>
+          <t>19,000~22,000</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>2,500,000</t>
+          <t>2,180,000</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>19,000,000,000</t>
+          <t>41,420,000,000</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>22.02배 (PER)</t>
+          <t>33.6배 (PER)</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr"/>
@@ -13295,7 +13295,7 @@
       <c r="I67" s="6" t="inlineStr"/>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t>10-21~10-22</t>
+          <t>10-22~10-23</t>
         </is>
       </c>
       <c r="K67" s="6" t="inlineStr"/>
@@ -13303,18 +13303,18 @@
       <c r="M67" s="6" t="inlineStr"/>
       <c r="N67" s="6" t="inlineStr">
         <is>
-          <t>미래에셋증권</t>
+          <t>NH투자증권</t>
         </is>
       </c>
       <c r="O67" s="6" t="inlineStr"/>
       <c r="P67" s="7" t="inlineStr">
         <is>
-          <t>782,800,000</t>
+          <t>1,908,899,000</t>
         </is>
       </c>
       <c r="Q67" s="6" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="R67" s="6" t="inlineStr">
@@ -13326,7 +13326,7 @@
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>래블업</t>
+          <t>영광</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
@@ -13336,22 +13336,22 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>19,000~22,000</t>
+          <t>14,000~17,000</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>2,180,000</t>
+          <t>2,260,000</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>41,420,000,000</t>
+          <t>31,640,000,000</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>33.6배 (PER)</t>
+          <t>11.98배 (EV/EBITDA)</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr"/>
@@ -13367,18 +13367,18 @@
       <c r="M68" s="6" t="inlineStr"/>
       <c r="N68" s="6" t="inlineStr">
         <is>
-          <t>NH투자증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="O68" s="6" t="inlineStr"/>
       <c r="P68" s="7" t="inlineStr">
         <is>
-          <t>1,908,899,000</t>
-        </is>
-      </c>
-      <c r="Q68" s="6" t="inlineStr">
-        <is>
-          <t>4.5%</t>
+          <t>977,676,000</t>
+        </is>
+      </c>
+      <c r="Q68" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="R68" s="6" t="inlineStr">
@@ -13390,32 +13390,32 @@
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>영광</t>
+          <t>한화플러스제6호스팩</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>10-13~10-19</t>
-        </is>
-      </c>
-      <c r="C69" s="6" t="inlineStr">
-        <is>
-          <t>14,000~17,000</t>
+          <t>10-14~10-15</t>
+        </is>
+      </c>
+      <c r="C69" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>2,260,000</t>
+          <t>6,000,000</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>31,640,000,000</t>
-        </is>
-      </c>
-      <c r="F69" s="6" t="inlineStr">
-        <is>
-          <t>11.98배 (EV/EBITDA)</t>
+          <t>12,000,000,000</t>
+        </is>
+      </c>
+      <c r="F69" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr"/>
@@ -13423,26 +13423,26 @@
       <c r="I69" s="6" t="inlineStr"/>
       <c r="J69" s="6" t="inlineStr">
         <is>
-          <t>10-22~10-23</t>
+          <t>10-20~10-21</t>
         </is>
       </c>
       <c r="K69" s="6" t="inlineStr"/>
       <c r="L69" s="6" t="inlineStr"/>
       <c r="M69" s="6" t="inlineStr"/>
-      <c r="N69" s="6" t="inlineStr">
-        <is>
-          <t>한국투자증권</t>
+      <c r="N69" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="O69" s="6" t="inlineStr"/>
-      <c r="P69" s="7" t="inlineStr">
-        <is>
-          <t>977,676,000</t>
-        </is>
-      </c>
-      <c r="Q69" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P69" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="Q69" s="6" t="inlineStr">
+        <is>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="R69" s="6" t="inlineStr">
@@ -13454,32 +13454,32 @@
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>한화플러스제6호스팩</t>
+          <t>엠비디</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>10-14~10-15</t>
-        </is>
-      </c>
-      <c r="C70" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>10-16~10-22</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>9,600~11,700</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>6,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>12,000,000,000</t>
-        </is>
-      </c>
-      <c r="F70" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>19,200,000,000</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>26.87배 (PER)</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr"/>
@@ -13487,26 +13487,26 @@
       <c r="I70" s="6" t="inlineStr"/>
       <c r="J70" s="6" t="inlineStr">
         <is>
-          <t>10-20~10-21</t>
+          <t>10-28~10-29</t>
         </is>
       </c>
       <c r="K70" s="6" t="inlineStr"/>
       <c r="L70" s="6" t="inlineStr"/>
       <c r="M70" s="6" t="inlineStr"/>
-      <c r="N70" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="N70" s="6" t="inlineStr">
+        <is>
+          <t>하나증권</t>
         </is>
       </c>
       <c r="O70" s="6" t="inlineStr"/>
-      <c r="P70" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P70" s="7" t="inlineStr">
+        <is>
+          <t>988,800,000</t>
         </is>
       </c>
       <c r="Q70" s="6" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="R70" s="6" t="inlineStr">
@@ -13518,32 +13518,32 @@
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>엠비디</t>
+          <t>아이엠스팩1호</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>10-16~10-22</t>
-        </is>
-      </c>
-      <c r="C71" s="6" t="inlineStr">
-        <is>
-          <t>9,600~11,700</t>
+          <t>10-19~10-20</t>
+        </is>
+      </c>
+      <c r="C71" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>19,200,000,000</t>
-        </is>
-      </c>
-      <c r="F71" s="6" t="inlineStr">
-        <is>
-          <t>26.87배 (PER)</t>
+          <t>10,000,000,000</t>
+        </is>
+      </c>
+      <c r="F71" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr"/>
@@ -13551,26 +13551,26 @@
       <c r="I71" s="6" t="inlineStr"/>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>10-28~10-29</t>
+          <t>10-26~10-27</t>
         </is>
       </c>
       <c r="K71" s="6" t="inlineStr"/>
       <c r="L71" s="6" t="inlineStr"/>
       <c r="M71" s="6" t="inlineStr"/>
-      <c r="N71" s="6" t="inlineStr">
-        <is>
-          <t>하나증권</t>
+      <c r="N71" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="O71" s="6" t="inlineStr"/>
-      <c r="P71" s="7" t="inlineStr">
-        <is>
-          <t>988,800,000</t>
+      <c r="P71" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="Q71" s="6" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="R71" s="6" t="inlineStr">
@@ -13582,32 +13582,32 @@
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>아이엠스팩1호</t>
+          <t>다비오</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>10-19~10-20</t>
-        </is>
-      </c>
-      <c r="C72" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>11-02~11-06</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>12,300~16,600</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>10,000,000,000</t>
-        </is>
-      </c>
-      <c r="F72" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>12,300,000,000</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>26.70배 (PER)</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr"/>
@@ -13615,26 +13615,26 @@
       <c r="I72" s="6" t="inlineStr"/>
       <c r="J72" s="6" t="inlineStr">
         <is>
-          <t>10-26~10-27</t>
+          <t>11-10~11-11</t>
         </is>
       </c>
       <c r="K72" s="6" t="inlineStr"/>
       <c r="L72" s="6" t="inlineStr"/>
       <c r="M72" s="6" t="inlineStr"/>
-      <c r="N72" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="N72" s="6" t="inlineStr">
+        <is>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="O72" s="6" t="inlineStr"/>
-      <c r="P72" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P72" s="7" t="inlineStr">
+        <is>
+          <t>570,105,000</t>
         </is>
       </c>
       <c r="Q72" s="6" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="R72" s="6" t="inlineStr">
@@ -14158,32 +14158,32 @@
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>하나에어로다이내믹스</t>
+          <t>영광와이케이엠씨</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>11-02~11-06</t>
+          <t>10-27~11-02</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>4,700~5,700</t>
+          <t>9,400~11,000</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>4,400,000</t>
+          <t>2,300,000</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>20,680,000,000</t>
+          <t>21,620,000,000</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>17.89배 (EV/EBITDA)</t>
+          <t>22.91배 (PER)</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr"/>
@@ -14191,7 +14191,7 @@
       <c r="I81" s="6" t="inlineStr"/>
       <c r="J81" s="6" t="inlineStr">
         <is>
-          <t>11-10~11-11</t>
+          <t>11-04~11-05</t>
         </is>
       </c>
       <c r="K81" s="6" t="inlineStr"/>
@@ -14199,18 +14199,18 @@
       <c r="M81" s="6" t="inlineStr"/>
       <c r="N81" s="6" t="inlineStr">
         <is>
-          <t>아이비케이투자증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="O81" s="6" t="inlineStr"/>
       <c r="P81" s="7" t="inlineStr">
         <is>
-          <t>850,000,000</t>
-        </is>
-      </c>
-      <c r="Q81" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>1,002,087,000</t>
+        </is>
+      </c>
+      <c r="Q81" s="6" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="R81" s="6" t="inlineStr">
@@ -14222,32 +14222,32 @@
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>케이엠에프</t>
+          <t>하나에어로다이내믹스</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>11-16~11-20</t>
+          <t>11-02~11-06</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>15,000~17,800</t>
+          <t>4,700~5,700</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>4,400,000</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>30,000,000,000</t>
+          <t>20,680,000,000</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr">
         <is>
-          <t>18.53배 (PER)</t>
+          <t>17.89배 (EV/EBITDA)</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr"/>
@@ -14255,7 +14255,7 @@
       <c r="I82" s="6" t="inlineStr"/>
       <c r="J82" s="6" t="inlineStr">
         <is>
-          <t>11-24~11-25</t>
+          <t>11-10~11-11</t>
         </is>
       </c>
       <c r="K82" s="6" t="inlineStr"/>
@@ -14269,12 +14269,12 @@
       <c r="O82" s="6" t="inlineStr"/>
       <c r="P82" s="7" t="inlineStr">
         <is>
-          <t>927,000,000</t>
-        </is>
-      </c>
-      <c r="Q82" s="6" t="inlineStr">
-        <is>
-          <t>3.0%</t>
+          <t>850,000,000</t>
+        </is>
+      </c>
+      <c r="Q82" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="R82" s="6" t="inlineStr">
@@ -14286,59 +14286,59 @@
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>영광와이케이엠씨</t>
-        </is>
-      </c>
-      <c r="B83" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="C83" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="D83" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="E83" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="F83" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>엔키화이트햇</t>
+        </is>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>11-03~11-09</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>13,000~16,500</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>1,700,000</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>22,100,000,000</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>24.86배 (PER)</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr"/>
       <c r="H83" s="6" t="inlineStr"/>
       <c r="I83" s="6" t="inlineStr"/>
-      <c r="J83" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="J83" s="6" t="inlineStr">
+        <is>
+          <t>11-12~11-13</t>
         </is>
       </c>
       <c r="K83" s="6" t="inlineStr"/>
       <c r="L83" s="6" t="inlineStr"/>
       <c r="M83" s="6" t="inlineStr"/>
-      <c r="N83" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="N83" s="6" t="inlineStr">
+        <is>
+          <t>신영증권</t>
         </is>
       </c>
       <c r="O83" s="6" t="inlineStr"/>
-      <c r="P83" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="Q83" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P83" s="7" t="inlineStr">
+        <is>
+          <t>1,138,150,000</t>
+        </is>
+      </c>
+      <c r="Q83" s="6" t="inlineStr">
+        <is>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="R83" s="6" t="inlineStr">
@@ -14350,59 +14350,59 @@
     <row r="84" ht="30" customHeight="1">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>럭스코</t>
-        </is>
-      </c>
-      <c r="B84" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="C84" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="D84" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="E84" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="F84" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>케이엠에프</t>
+        </is>
+      </c>
+      <c r="B84" s="6" t="inlineStr">
+        <is>
+          <t>11-16~11-20</t>
+        </is>
+      </c>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>15,000~17,800</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>2,000,000</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>30,000,000,000</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>18.53배 (PER)</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr"/>
       <c r="H84" s="6" t="inlineStr"/>
       <c r="I84" s="6" t="inlineStr"/>
-      <c r="J84" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="J84" s="6" t="inlineStr">
+        <is>
+          <t>11-24~11-25</t>
         </is>
       </c>
       <c r="K84" s="6" t="inlineStr"/>
       <c r="L84" s="6" t="inlineStr"/>
       <c r="M84" s="6" t="inlineStr"/>
-      <c r="N84" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="N84" s="6" t="inlineStr">
+        <is>
+          <t>아이비케이투자증권</t>
         </is>
       </c>
       <c r="O84" s="6" t="inlineStr"/>
-      <c r="P84" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="Q84" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P84" s="7" t="inlineStr">
+        <is>
+          <t>927,000,000</t>
+        </is>
+      </c>
+      <c r="Q84" s="6" t="inlineStr">
+        <is>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="R84" s="6" t="inlineStr">
@@ -14414,7 +14414,7 @@
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>엔키화이트햇</t>
+          <t>럭스코</t>
         </is>
       </c>
       <c r="B85" s="18" t="inlineStr">
@@ -14478,7 +14478,7 @@
     <row r="86" ht="30" customHeight="1">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>아델</t>
+          <t>디티에스</t>
         </is>
       </c>
       <c r="B86" s="18" t="inlineStr">
@@ -14535,14 +14535,14 @@
       </c>
       <c r="R86" s="6" t="inlineStr">
         <is>
-          <t>corp_code 미확보(수동확인)</t>
+          <t>신고서 대기</t>
         </is>
       </c>
     </row>
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>케이티이</t>
+          <t>에이엔에이치스트럭쳐</t>
         </is>
       </c>
       <c r="B87" s="18" t="inlineStr">
@@ -14599,14 +14599,14 @@
       </c>
       <c r="R87" s="6" t="inlineStr">
         <is>
-          <t>corp_code 미확보(수동확인)</t>
+          <t>신고서 대기</t>
         </is>
       </c>
     </row>
     <row r="88" ht="30" customHeight="1">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>씨앤엠</t>
+          <t>이에스티</t>
         </is>
       </c>
       <c r="B88" s="18" t="inlineStr">
@@ -14663,14 +14663,14 @@
       </c>
       <c r="R88" s="6" t="inlineStr">
         <is>
-          <t>corp_code 미확보(수동확인)</t>
+          <t>신고서 대기</t>
         </is>
       </c>
     </row>
     <row r="89" ht="30" customHeight="1">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>디티에스</t>
+          <t>우리투자제1호스팩</t>
         </is>
       </c>
       <c r="B89" s="18" t="inlineStr">
@@ -14734,7 +14734,7 @@
     <row r="90" ht="30" customHeight="1">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>에이엔에이치스트럭쳐</t>
+          <t>마더스제약</t>
         </is>
       </c>
       <c r="B90" s="18" t="inlineStr">
@@ -14798,7 +14798,7 @@
     <row r="91" ht="30" customHeight="1">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>이에스티</t>
+          <t>아델</t>
         </is>
       </c>
       <c r="B91" s="18" t="inlineStr">
@@ -14862,7 +14862,7 @@
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>우리투자제1호스팩</t>
+          <t>케이티이</t>
         </is>
       </c>
       <c r="B92" s="18" t="inlineStr">
@@ -14926,7 +14926,7 @@
     <row r="93" ht="30" customHeight="1">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>마더스제약</t>
+          <t>씨앤엠</t>
         </is>
       </c>
       <c r="B93" s="18" t="inlineStr">
@@ -15019,7 +15019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15389,22 +15389,22 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>256,940,000,000</t>
+          <t>268,350,000,000</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
@@ -15412,7 +15412,7 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>246,730,000,000</t>
+          <t>256,940,000,000</t>
         </is>
       </c>
     </row>
@@ -15569,97 +15569,97 @@
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>신영증권</t>
         </is>
       </c>
       <c r="B33" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>618,288</t>
+          <t>22,100,000,000</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>154,600</t>
+          <t>618,288</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>130,837</t>
+          <t>154,600</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>신한</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="B36" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>49,052</t>
+          <t>130,837</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>신한</t>
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>49,052</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>유진</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="B38" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>25,020</t>
+          <t>32,000</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>메리츠</t>
+          <t>유진</t>
         </is>
       </c>
       <c r="B39" s="6" t="n">
@@ -15667,14 +15667,14 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>14,000</t>
+          <t>25,020</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>메리츠</t>
         </is>
       </c>
       <c r="B40" s="6" t="n">
@@ -15682,14 +15682,14 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>13,000</t>
+          <t>14,000</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>키움</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="B41" s="6" t="n">
@@ -15697,20 +15697,35 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>13,000</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>교보</t>
+          <t>키움</t>
         </is>
       </c>
       <c r="B42" s="6" t="n">
         <v>1</v>
       </c>
       <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>교보</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
         <is>
           <t>10,800</t>
         </is>

--- a/IPO_analysis.xlsx
+++ b/IPO_analysis.xlsx
@@ -618,14 +618,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>기준일 2026-10-11 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
+          <t>기준일 2026-10-12 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>■ 심사 신청(진행중)  (41건)</t>
+          <t>■ 심사 신청(진행중)  (39건)</t>
         </is>
       </c>
       <c r="B4" s="4" t="n"/>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>데스틴파워</t>
+          <t>유림테크</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -1828,27 +1828,27 @@
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>29,851</t>
+          <t>102,586</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>5,852</t>
+          <t>-18,278</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>-30,114</t>
+          <t>-4,832</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>전동기, 발전기 및 전기 변환 · 공급 · 제어 장치 제조업</t>
+          <t>자동차 신품 부품 제조업</t>
         </is>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr">
@@ -1860,12 +1860,12 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>유림테크</t>
+          <t>이노보테라퓨틱스</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -1885,27 +1885,27 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>102,586</t>
+          <t>209</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>-18,278</t>
+          <t>-5,429</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>-4,832</t>
+          <t>-53,200</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>자동차 신품 부품 제조업</t>
+          <t>의약품 제조업</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
@@ -1917,17 +1917,17 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>이노보테라퓨틱스</t>
+          <t>에스에프씨</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>유가</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
@@ -1942,27 +1942,27 @@
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>160,792</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>-5,429</t>
+          <t>25,509</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>-53,200</t>
+          <t>243,562</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>의약품 제조업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>미래, 한국</t>
         </is>
       </c>
       <c r="K28" s="6" t="inlineStr">
@@ -1974,17 +1974,17 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>에스에프씨</t>
+          <t>에버온</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>유가</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -1999,27 +1999,27 @@
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>160,792</t>
+          <t>65,225</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>25,509</t>
+          <t>-3,606</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>243,562</t>
+          <t>54,955</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>전기업</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>미래, 한국</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
@@ -2031,12 +2031,12 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>에버온</t>
+          <t>씨아이에스케미칼</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -2056,27 +2056,27 @@
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>65,225</t>
+          <t>15,985</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>-3,606</t>
+          <t>-11,440</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>54,955</t>
+          <t>23,706</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>전기업</t>
+          <t>기초 화학물질 제조업</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
@@ -2088,12 +2088,12 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>씨아이에스케미칼</t>
+          <t>엠디에스코리아</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -2113,27 +2113,27 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>15,985</t>
+          <t>97,972</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>-11,440</t>
+          <t>6,512</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>23,706</t>
+          <t>53,818</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>기초 화학물질 제조업</t>
+          <t>기타 식품 제조업</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K31" s="6" t="inlineStr">
@@ -2145,12 +2145,12 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>엠디에스코리아</t>
+          <t>동승</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -2170,27 +2170,27 @@
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>97,972</t>
+          <t>78,625</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>6,512</t>
+          <t>14,525</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>53,818</t>
+          <t>5,438</t>
         </is>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>기타 식품 제조업</t>
+          <t>부동산 임대 및 공급업</t>
         </is>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K32" s="6" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>동승</t>
+          <t>에프엠더블유</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
@@ -2227,27 +2227,27 @@
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>78,625</t>
+          <t>30,282</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>14,525</t>
+          <t>4,762</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>5,438</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>부동산 임대 및 공급업</t>
+          <t>기타 식품 제조업</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>유진</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
@@ -2259,22 +2259,22 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>에프엠더블유</t>
+          <t>소노인터내셔널</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>유가</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -2284,27 +2284,27 @@
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>30,282</t>
+          <t>2,093,051</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>4,762</t>
+          <t>-148,064</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>852,372</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>기타 식품 제조업</t>
+          <t>일반 및 생활 숙박시설 운영업</t>
         </is>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>유진</t>
+          <t>대신, 미래</t>
         </is>
       </c>
       <c r="K34" s="6" t="inlineStr">
@@ -2316,17 +2316,17 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>소노인터내셔널</t>
+          <t>싸이몬</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>유가</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
@@ -2341,27 +2341,27 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>2,093,051</t>
+          <t>48,695</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>-148,064</t>
+          <t>15,714</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>852,372</t>
+          <t>61,761</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>일반 및 생활 숙박시설 운영업</t>
+          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업</t>
         </is>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>대신, 미래</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K35" s="6" t="inlineStr">
@@ -2373,12 +2373,12 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>싸이몬</t>
+          <t>바이다</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
@@ -2398,27 +2398,27 @@
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>48,695</t>
+          <t>14,432</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>15,714</t>
+          <t>-3,951</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>61,761</t>
+          <t>15,108</t>
         </is>
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업</t>
+          <t>전자부품 제조업</t>
         </is>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K36" s="6" t="inlineStr">
@@ -2430,12 +2430,12 @@
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>바이다</t>
+          <t>아이알큐더스</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -2455,27 +2455,27 @@
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>14,432</t>
+          <t>10,231</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>-3,951</t>
+          <t>-986</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>15,108</t>
+          <t>1,800</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>전자부품 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
@@ -2487,12 +2487,12 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>아이알큐더스</t>
+          <t>씨엔티테크</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -2512,17 +2512,17 @@
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>10,231</t>
+          <t>27,015</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>-986</t>
+          <t>3,987</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>1,800</t>
+          <t>2,613</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>한화, 하나</t>
         </is>
       </c>
       <c r="K38" s="6" t="inlineStr">
@@ -2544,12 +2544,12 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>씨엔티테크</t>
+          <t>인터엑스</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -2569,17 +2569,17 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>27,015</t>
+          <t>8,645</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>3,987</t>
+          <t>-20,272</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>2,613</t>
+          <t>4,530</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>한화, 하나</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr">
@@ -2601,12 +2601,12 @@
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>제이앤티지</t>
+          <t>삼홍아크튜리온</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -2626,27 +2626,27 @@
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>72,378</t>
+          <t>26,162</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>9,904</t>
+          <t>-10,314</t>
         </is>
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>6,743</t>
+          <t>6,369</t>
         </is>
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>전자부품 제조업</t>
+          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
         </is>
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>대신, NH</t>
+          <t>삼성, 미래</t>
         </is>
       </c>
       <c r="K40" s="6" t="inlineStr">
@@ -2658,12 +2658,12 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>인터엑스</t>
+          <t>비앤비코리아</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -2683,27 +2683,27 @@
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>8,645</t>
+          <t>141,169</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>-20,272</t>
+          <t>21,406</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>4,530</t>
+          <t>43,932</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
@@ -2715,12 +2715,12 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>삼홍아크튜리온</t>
+          <t>오토핸즈</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -2740,27 +2740,27 @@
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>26,162</t>
+          <t>238,564</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>-10,314</t>
+          <t>6,047</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>6,369</t>
+          <t>6,129</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
+          <t>자동차 판매업</t>
         </is>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>삼성, 미래</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K42" s="6" t="inlineStr">
@@ -2772,12 +2772,12 @@
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>비앤비코리아</t>
+          <t>아이벡스메디칼시스템즈</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -2797,27 +2797,27 @@
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>141,169</t>
+          <t>15,282</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>21,406</t>
+          <t>-7,227</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>43,932</t>
+          <t>744</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
@@ -2829,12 +2829,12 @@
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>오토핸즈</t>
+          <t>피지티</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
@@ -2854,27 +2854,27 @@
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>238,564</t>
+          <t>40,141</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>6,047</t>
+          <t>-69,722</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>6,129</t>
+          <t>6,029</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>자동차 판매업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K44" s="6" t="inlineStr">
@@ -2883,191 +2883,191 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>아이벡스메디칼시스템즈</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>■ 심사 승인  (78건)</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="n"/>
+      <c r="C46" s="4" t="n"/>
+      <c r="D46" s="4" t="n"/>
+      <c r="E46" s="4" t="n"/>
+      <c r="F46" s="4" t="n"/>
+      <c r="G46" s="4" t="n"/>
+      <c r="H46" s="4" t="n"/>
+      <c r="I46" s="4" t="n"/>
+      <c r="J46" s="4" t="n"/>
+      <c r="K46" s="4" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>일자</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>회사명</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>시장</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>상장유형</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>기준연도</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>자기자본</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>업종</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>대표주관사</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>현황</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>제이앤티지</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
         <is>
           <t>코스닥</t>
         </is>
       </c>
-      <c r="D45" s="6" t="inlineStr">
+      <c r="D48" s="6" t="inlineStr">
         <is>
           <t>신규상장</t>
         </is>
       </c>
-      <c r="E45" s="6" t="inlineStr">
+      <c r="E48" s="6" t="inlineStr">
         <is>
           <t>FY25</t>
         </is>
       </c>
-      <c r="F45" s="7" t="inlineStr">
-        <is>
-          <t>15,282</t>
-        </is>
-      </c>
-      <c r="G45" s="7" t="inlineStr">
-        <is>
-          <t>-7,227</t>
-        </is>
-      </c>
-      <c r="H45" s="7" t="inlineStr">
-        <is>
-          <t>744</t>
-        </is>
-      </c>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>의료용 기기 제조업</t>
-        </is>
-      </c>
-      <c r="J45" s="6" t="inlineStr">
-        <is>
-          <t>NH</t>
-        </is>
-      </c>
-      <c r="K45" s="6" t="inlineStr">
-        <is>
-          <t>예심 진행중</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
-        <is>
-          <t>피지티</t>
-        </is>
-      </c>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>72,378</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>9,904</t>
+        </is>
+      </c>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>6,743</t>
+        </is>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>전자부품 제조업</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>대신, NH</t>
+        </is>
+      </c>
+      <c r="K48" s="6" t="inlineStr">
+        <is>
+          <t>상장전</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>데스틴파워</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>코스닥</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t>신규상장</t>
         </is>
       </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="E49" s="6" t="inlineStr">
         <is>
           <t>FY25</t>
         </is>
       </c>
-      <c r="F46" s="7" t="inlineStr">
-        <is>
-          <t>40,141</t>
-        </is>
-      </c>
-      <c r="G46" s="7" t="inlineStr">
-        <is>
-          <t>-69,722</t>
-        </is>
-      </c>
-      <c r="H46" s="7" t="inlineStr">
-        <is>
-          <t>6,029</t>
-        </is>
-      </c>
-      <c r="I46" s="6" t="inlineStr">
-        <is>
-          <t>기타 화학제품 제조업</t>
-        </is>
-      </c>
-      <c r="J46" s="6" t="inlineStr">
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>29,851</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="inlineStr">
+        <is>
+          <t>5,852</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>-30,114</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>전동기, 발전기 및 전기 변환 · 공급 · 제어 장치 제조업</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
         <is>
           <t>한국</t>
         </is>
       </c>
-      <c r="K46" s="6" t="inlineStr">
-        <is>
-          <t>예심 진행중</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>■ 심사 승인  (76건)</t>
-        </is>
-      </c>
-      <c r="B48" s="4" t="n"/>
-      <c r="C48" s="4" t="n"/>
-      <c r="D48" s="4" t="n"/>
-      <c r="E48" s="4" t="n"/>
-      <c r="F48" s="4" t="n"/>
-      <c r="G48" s="4" t="n"/>
-      <c r="H48" s="4" t="n"/>
-      <c r="I48" s="4" t="n"/>
-      <c r="J48" s="4" t="n"/>
-      <c r="K48" s="4" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>일자</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>회사명</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
-        <is>
-          <t>시장</t>
-        </is>
-      </c>
-      <c r="D49" s="5" t="inlineStr">
-        <is>
-          <t>상장유형</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>기준연도</t>
-        </is>
-      </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="G49" s="5" t="inlineStr">
-        <is>
-          <t>순이익</t>
-        </is>
-      </c>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
-          <t>자기자본</t>
-        </is>
-      </c>
-      <c r="I49" s="5" t="inlineStr">
-        <is>
-          <t>업종</t>
-        </is>
-      </c>
-      <c r="J49" s="5" t="inlineStr">
-        <is>
-          <t>대표주관사</t>
-        </is>
-      </c>
-      <c r="K49" s="5" t="inlineStr">
-        <is>
-          <t>현황</t>
+      <c r="K49" s="6" t="inlineStr">
+        <is>
+          <t>상장전</t>
         </is>
       </c>
     </row>
@@ -8464,7 +8464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R97"/>
+  <dimension ref="A1:R99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -12546,7 +12546,7 @@
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>■ 공모 진행 (예심 승인법인)  (37건)</t>
+          <t>■ 공모 진행 (예심 승인법인)  (39건)</t>
         </is>
       </c>
       <c r="B56" s="4" t="n"/>
@@ -13582,32 +13582,32 @@
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>다비오</t>
+          <t>에이엘로봇</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>11-02~11-06</t>
+          <t>10-28~11-03</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>12,300~16,600</t>
+          <t>15,700~17,600</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>1,000,000</t>
+          <t>2,400,000</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>12,300,000,000</t>
+          <t>37,680,000,000</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>26.70배 (PER)</t>
+          <t>37.17배 (PER)</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr"/>
@@ -13615,7 +13615,7 @@
       <c r="I72" s="6" t="inlineStr"/>
       <c r="J72" s="6" t="inlineStr">
         <is>
-          <t>11-10~11-11</t>
+          <t>11-06~11-09</t>
         </is>
       </c>
       <c r="K72" s="6" t="inlineStr"/>
@@ -13629,12 +13629,12 @@
       <c r="O72" s="6" t="inlineStr"/>
       <c r="P72" s="7" t="inlineStr">
         <is>
-          <t>570,105,000</t>
+          <t>1,160,399,874</t>
         </is>
       </c>
       <c r="Q72" s="6" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="R72" s="6" t="inlineStr">
@@ -13646,59 +13646,59 @@
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>바로팜</t>
-        </is>
-      </c>
-      <c r="B73" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>다비오</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>11-02~11-06</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>16,400~20,200</t>
+          <t>12,300~16,600</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>1,780,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>29,192,000,000</t>
+          <t>12,300,000,000</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>24.95배 (PER)</t>
+          <t>26.70배 (PER)</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr"/>
       <c r="H73" s="6" t="inlineStr"/>
       <c r="I73" s="6" t="inlineStr"/>
-      <c r="J73" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="J73" s="6" t="inlineStr">
+        <is>
+          <t>11-10~11-11</t>
         </is>
       </c>
       <c r="K73" s="6" t="inlineStr"/>
       <c r="L73" s="6" t="inlineStr"/>
       <c r="M73" s="6" t="inlineStr"/>
-      <c r="N73" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="N73" s="6" t="inlineStr">
+        <is>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="O73" s="6" t="inlineStr"/>
-      <c r="P73" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="Q73" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P73" s="7" t="inlineStr">
+        <is>
+          <t>570,105,000</t>
+        </is>
+      </c>
+      <c r="Q73" s="6" t="inlineStr">
+        <is>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="R73" s="6" t="inlineStr">
@@ -13710,7 +13710,7 @@
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>셀트릭스</t>
+          <t>바로팜</t>
         </is>
       </c>
       <c r="B74" s="18" t="inlineStr">
@@ -13718,24 +13718,24 @@
           <t>수집예정</t>
         </is>
       </c>
-      <c r="C74" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="D74" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="E74" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="F74" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>16,400~20,200</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>1,780,000</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>29,192,000,000</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>24.95배 (PER)</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr"/>
@@ -13774,7 +13774,7 @@
     <row r="75" ht="30" customHeight="1">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>솔리스</t>
+          <t>셀트릭스</t>
         </is>
       </c>
       <c r="B75" s="18" t="inlineStr">
@@ -13838,64 +13838,64 @@
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>에이엘로봇</t>
-        </is>
-      </c>
-      <c r="B76" s="6" t="inlineStr">
-        <is>
-          <t>10-15~10-21</t>
-        </is>
-      </c>
-      <c r="C76" s="6" t="inlineStr">
-        <is>
-          <t>15,700~17,600</t>
-        </is>
-      </c>
-      <c r="D76" s="7" t="inlineStr">
-        <is>
-          <t>2,400,000</t>
-        </is>
-      </c>
-      <c r="E76" s="7" t="inlineStr">
-        <is>
-          <t>37,680,000,000</t>
-        </is>
-      </c>
-      <c r="F76" s="6" t="inlineStr">
-        <is>
-          <t>37.17배 (PER)</t>
+          <t>솔리스</t>
+        </is>
+      </c>
+      <c r="B76" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="C76" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="D76" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="E76" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="F76" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr"/>
       <c r="H76" s="6" t="inlineStr"/>
       <c r="I76" s="6" t="inlineStr"/>
-      <c r="J76" s="6" t="inlineStr">
-        <is>
-          <t>10-26~10-27</t>
+      <c r="J76" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="K76" s="6" t="inlineStr"/>
       <c r="L76" s="6" t="inlineStr"/>
       <c r="M76" s="6" t="inlineStr"/>
-      <c r="N76" s="6" t="inlineStr">
-        <is>
-          <t>대신증권</t>
+      <c r="N76" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="O76" s="6" t="inlineStr"/>
-      <c r="P76" s="7" t="inlineStr">
-        <is>
-          <t>1,160,399,874</t>
-        </is>
-      </c>
-      <c r="Q76" s="6" t="inlineStr">
-        <is>
-          <t>3.0%</t>
+      <c r="P76" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="Q76" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="R76" s="6" t="inlineStr">
         <is>
-          <t>최초</t>
+          <t>정정</t>
         </is>
       </c>
     </row>
@@ -14350,32 +14350,32 @@
     <row r="84" ht="30" customHeight="1">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>케이엠에프</t>
+          <t>아델</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>11-16~11-20</t>
+          <t>11-12~11-18</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>15,000~17,800</t>
+          <t>18,000~25,000</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>2,170,000</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>30,000,000,000</t>
+          <t>39,060,000,000</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr">
         <is>
-          <t>18.53배 (PER)</t>
+          <t>20.91배 (PER)</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr"/>
@@ -14383,7 +14383,7 @@
       <c r="I84" s="6" t="inlineStr"/>
       <c r="J84" s="6" t="inlineStr">
         <is>
-          <t>11-24~11-25</t>
+          <t>11-23~11-24</t>
         </is>
       </c>
       <c r="K84" s="6" t="inlineStr"/>
@@ -14391,18 +14391,18 @@
       <c r="M84" s="6" t="inlineStr"/>
       <c r="N84" s="6" t="inlineStr">
         <is>
-          <t>아이비케이투자증권</t>
+          <t>삼성증권㈜</t>
         </is>
       </c>
       <c r="O84" s="6" t="inlineStr"/>
       <c r="P84" s="7" t="inlineStr">
         <is>
-          <t>927,000,000</t>
+          <t>1,041,559,920</t>
         </is>
       </c>
       <c r="Q84" s="6" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="R84" s="6" t="inlineStr">
@@ -14414,59 +14414,59 @@
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>럭스코</t>
-        </is>
-      </c>
-      <c r="B85" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="C85" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="D85" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="E85" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="F85" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>케이엠에프</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>11-16~11-20</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>15,000~17,800</t>
+        </is>
+      </c>
+      <c r="D85" s="7" t="inlineStr">
+        <is>
+          <t>2,000,000</t>
+        </is>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
+        <is>
+          <t>30,000,000,000</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>18.53배 (PER)</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr"/>
       <c r="H85" s="6" t="inlineStr"/>
       <c r="I85" s="6" t="inlineStr"/>
-      <c r="J85" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="J85" s="6" t="inlineStr">
+        <is>
+          <t>11-24~11-25</t>
         </is>
       </c>
       <c r="K85" s="6" t="inlineStr"/>
       <c r="L85" s="6" t="inlineStr"/>
       <c r="M85" s="6" t="inlineStr"/>
-      <c r="N85" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="N85" s="6" t="inlineStr">
+        <is>
+          <t>아이비케이투자증권</t>
         </is>
       </c>
       <c r="O85" s="6" t="inlineStr"/>
-      <c r="P85" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="Q85" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P85" s="7" t="inlineStr">
+        <is>
+          <t>927,000,000</t>
+        </is>
+      </c>
+      <c r="Q85" s="6" t="inlineStr">
+        <is>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="R85" s="6" t="inlineStr">
@@ -14478,7 +14478,7 @@
     <row r="86" ht="30" customHeight="1">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>디티에스</t>
+          <t>럭스코</t>
         </is>
       </c>
       <c r="B86" s="18" t="inlineStr">
@@ -14535,14 +14535,14 @@
       </c>
       <c r="R86" s="6" t="inlineStr">
         <is>
-          <t>신고서 대기</t>
+          <t>최초</t>
         </is>
       </c>
     </row>
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>에이엔에이치스트럭쳐</t>
+          <t>디티에스</t>
         </is>
       </c>
       <c r="B87" s="18" t="inlineStr">
@@ -14606,7 +14606,7 @@
     <row r="88" ht="30" customHeight="1">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>이에스티</t>
+          <t>에이엔에이치스트럭쳐</t>
         </is>
       </c>
       <c r="B88" s="18" t="inlineStr">
@@ -14670,7 +14670,7 @@
     <row r="89" ht="30" customHeight="1">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>우리투자제1호스팩</t>
+          <t>이에스티</t>
         </is>
       </c>
       <c r="B89" s="18" t="inlineStr">
@@ -14734,7 +14734,7 @@
     <row r="90" ht="30" customHeight="1">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>마더스제약</t>
+          <t>우리투자제1호스팩</t>
         </is>
       </c>
       <c r="B90" s="18" t="inlineStr">
@@ -14798,7 +14798,7 @@
     <row r="91" ht="30" customHeight="1">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>아델</t>
+          <t>마더스제약</t>
         </is>
       </c>
       <c r="B91" s="18" t="inlineStr">
@@ -14987,22 +14987,150 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="20" t="inlineStr">
-        <is>
-          <t>※ 상장 완료 = KIND 신규상장 페이지 기준(스팩합병 포함) · 스팩 공모상장은 밴드·밸류에이션 등 해당없음(공모가 2,000원 고정).</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="20" t="inlineStr">
-        <is>
-          <t>※ 기재정정 신고서 내 정정 전·후 병존 → 자동수집은 "정정 후" 값만 취함.</t>
+    <row r="94" ht="30" customHeight="1">
+      <c r="A94" s="6" t="inlineStr">
+        <is>
+          <t>제이앤티지</t>
+        </is>
+      </c>
+      <c r="B94" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="C94" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="D94" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="E94" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="F94" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr"/>
+      <c r="H94" s="6" t="inlineStr"/>
+      <c r="I94" s="6" t="inlineStr"/>
+      <c r="J94" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="K94" s="6" t="inlineStr"/>
+      <c r="L94" s="6" t="inlineStr"/>
+      <c r="M94" s="6" t="inlineStr"/>
+      <c r="N94" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="O94" s="6" t="inlineStr"/>
+      <c r="P94" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="Q94" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="R94" s="6" t="inlineStr">
+        <is>
+          <t>신고서 대기</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="30" customHeight="1">
+      <c r="A95" s="6" t="inlineStr">
+        <is>
+          <t>데스틴파워</t>
+        </is>
+      </c>
+      <c r="B95" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="C95" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="D95" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="E95" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="F95" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="G95" s="6" t="inlineStr"/>
+      <c r="H95" s="6" t="inlineStr"/>
+      <c r="I95" s="6" t="inlineStr"/>
+      <c r="J95" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="K95" s="6" t="inlineStr"/>
+      <c r="L95" s="6" t="inlineStr"/>
+      <c r="M95" s="6" t="inlineStr"/>
+      <c r="N95" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="O95" s="6" t="inlineStr"/>
+      <c r="P95" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="Q95" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="R95" s="6" t="inlineStr">
+        <is>
+          <t>신고서 대기</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="20" t="inlineStr">
+        <is>
+          <t>※ 상장 완료 = KIND 신규상장 페이지 기준(스팩합병 포함) · 스팩 공모상장은 밴드·밸류에이션 등 해당없음(공모가 2,000원 고정).</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="20" t="inlineStr">
+        <is>
+          <t>※ 기재정정 신고서 내 정정 전·후 병존 → 자동수집은 "정정 후" 값만 취함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="20" t="inlineStr">
         <is>
           <t>※ 청약경쟁률=일반투자자 청약수량÷최종배정수량 · "MM-DD~"는 종료일 자동수집 예정.</t>
         </is>
@@ -15019,7 +15147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -15305,7 +15433,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D15" s="6" t="n">
         <v>1</v>
@@ -15524,37 +15652,37 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>하나증권</t>
+          <t>삼성증권㈜</t>
         </is>
       </c>
       <c r="B30" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>35,814,000,000</t>
+          <t>39,060,000,000</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>하나증권</t>
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>31,200,000,000</t>
+          <t>35,814,000,000</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>신한투자증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="B32" s="6" t="n">
@@ -15562,14 +15690,14 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>30,240,000,000</t>
+          <t>31,200,000,000</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>신영증권</t>
+          <t>신한투자증권</t>
         </is>
       </c>
       <c r="B33" s="6" t="n">
@@ -15577,104 +15705,104 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>22,100,000,000</t>
+          <t>30,240,000,000</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>신영증권</t>
         </is>
       </c>
       <c r="B34" s="6" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>618,288</t>
+          <t>22,100,000,000</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>154,600</t>
+          <t>618,288</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="B36" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>130,837</t>
+          <t>154,600</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>신한</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>49,052</t>
+          <t>130,837</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>신한</t>
         </is>
       </c>
       <c r="B38" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>49,052</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>유진</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="B39" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>25,020</t>
+          <t>32,000</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>메리츠</t>
+          <t>유진</t>
         </is>
       </c>
       <c r="B40" s="6" t="n">
@@ -15682,14 +15810,14 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>14,000</t>
+          <t>25,020</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>메리츠</t>
         </is>
       </c>
       <c r="B41" s="6" t="n">
@@ -15697,14 +15825,14 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>13,000</t>
+          <t>14,000</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>키움</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="B42" s="6" t="n">
@@ -15712,20 +15840,35 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>13,000</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>교보</t>
+          <t>키움</t>
         </is>
       </c>
       <c r="B43" s="6" t="n">
         <v>1</v>
       </c>
       <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>교보</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
         <is>
           <t>10,800</t>
         </is>

--- a/IPO_analysis.xlsx
+++ b/IPO_analysis.xlsx
@@ -592,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K148"/>
+  <dimension ref="A1:K149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -618,14 +618,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>기준일 2026-10-12 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
+          <t>기준일 2026-10-13 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>■ 심사 신청(진행중)  (39건)</t>
+          <t>■ 심사 신청(진행중)  (38건)</t>
         </is>
       </c>
       <c r="B4" s="4" t="n"/>
@@ -1371,12 +1371,12 @@
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>(주)태석광학</t>
+          <t>엑티브온</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -1394,29 +1394,17 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>79,804</t>
-        </is>
-      </c>
-      <c r="G18" s="7" t="inlineStr">
-        <is>
-          <t>4,721</t>
-        </is>
-      </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>7,228</t>
-        </is>
-      </c>
+      <c r="F18" s="7" t="inlineStr"/>
+      <c r="G18" s="7" t="inlineStr"/>
+      <c r="H18" s="7" t="inlineStr"/>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>생활용품 도매업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>신한, 대신</t>
+          <t>키움</t>
         </is>
       </c>
       <c r="K18" s="6" t="inlineStr">
@@ -1428,22 +1416,22 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>엑티브온</t>
+          <t>무신사</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>유가</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E19" s="6" t="inlineStr">
@@ -1451,17 +1439,29 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr"/>
-      <c r="G19" s="7" t="inlineStr"/>
-      <c r="H19" s="7" t="inlineStr"/>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>1,352,930</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>-10,571</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>243,731</t>
+        </is>
+      </c>
       <c r="I19" s="6" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>섬유, 의복, 신발 및 가죽제품 소매업</t>
         </is>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
-          <t>키움</t>
+          <t>한국, 씨티그룹글로벌마켓증권(주), KB, 제이피모간증권회사 서울지점</t>
         </is>
       </c>
       <c r="K19" s="6" t="inlineStr">
@@ -1473,17 +1473,17 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>무신사</t>
+          <t>이나인페이</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>유가</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
@@ -1498,27 +1498,27 @@
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>1,352,930</t>
+          <t>64,711</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>-10,571</t>
+          <t>19,586</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>243,731</t>
+          <t>79,855</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>섬유, 의복, 신발 및 가죽제품 소매업</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>한국, 씨티그룹글로벌마켓증권(주), KB, 제이피모간증권회사 서울지점</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K20" s="6" t="inlineStr">
@@ -1530,12 +1530,12 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>이나인페이</t>
+          <t>어피닛</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1555,27 +1555,27 @@
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>64,711</t>
+          <t>169,126</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>19,586</t>
+          <t>26,009</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>79,855</t>
+          <t>61,466</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>미래, 하나</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>어피닛</t>
+          <t>라이드플럭스</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1612,17 +1612,17 @@
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>169,126</t>
+          <t>4,044</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
         <is>
-          <t>26,009</t>
+          <t>-31,423</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
         <is>
-          <t>61,466</t>
+          <t>-77,243</t>
         </is>
       </c>
       <c r="I22" s="6" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>미래, 하나</t>
+          <t>주식회사 우리투자증권, 한국</t>
         </is>
       </c>
       <c r="K22" s="6" t="inlineStr">
@@ -1644,12 +1644,12 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>라이드플럭스</t>
+          <t>신영스팩12호</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -1667,29 +1667,17 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr">
-        <is>
-          <t>4,044</t>
-        </is>
-      </c>
-      <c r="G23" s="7" t="inlineStr">
-        <is>
-          <t>-31,423</t>
-        </is>
-      </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>-77,243</t>
-        </is>
-      </c>
+      <c r="F23" s="7" t="inlineStr"/>
+      <c r="G23" s="7" t="inlineStr"/>
+      <c r="H23" s="7" t="inlineStr"/>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>주식회사 우리투자증권, 한국</t>
+          <t>신영</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
@@ -1701,12 +1689,12 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>신영스팩12호</t>
+          <t>범한메카텍</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -1724,17 +1712,29 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr"/>
-      <c r="G24" s="7" t="inlineStr"/>
-      <c r="H24" s="7" t="inlineStr"/>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>339,209</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>-18,141</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>265,955</t>
+        </is>
+      </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
         </is>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>신영</t>
+          <t>유진, NH</t>
         </is>
       </c>
       <c r="K24" s="6" t="inlineStr">
@@ -1746,12 +1746,12 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>범한메카텍</t>
+          <t>유림테크</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -1771,27 +1771,27 @@
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>339,209</t>
+          <t>102,586</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>-18,141</t>
+          <t>-18,278</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>265,955</t>
+          <t>-4,832</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
+          <t>자동차 신품 부품 제조업</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>유진, NH</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
@@ -1803,12 +1803,12 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>유림테크</t>
+          <t>이노보테라퓨틱스</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -1828,27 +1828,27 @@
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>102,586</t>
+          <t>209</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>-18,278</t>
+          <t>-5,429</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>-4,832</t>
+          <t>-53,200</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>자동차 신품 부품 제조업</t>
+          <t>의약품 제조업</t>
         </is>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr">
@@ -1860,17 +1860,17 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>이노보테라퓨틱스</t>
+          <t>에스에프씨</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>유가</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -1885,27 +1885,27 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>160,792</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>-5,429</t>
+          <t>25,509</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>-53,200</t>
+          <t>243,562</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>의약품 제조업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>미래, 한국</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
@@ -1917,17 +1917,17 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>에스에프씨</t>
+          <t>에버온</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>유가</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
@@ -1942,27 +1942,27 @@
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>160,792</t>
+          <t>65,225</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>25,509</t>
+          <t>-3,606</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>243,562</t>
+          <t>54,955</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>전기업</t>
         </is>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>미래, 한국</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K28" s="6" t="inlineStr">
@@ -1974,12 +1974,12 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>에버온</t>
+          <t>씨아이에스케미칼</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
@@ -1999,27 +1999,27 @@
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>65,225</t>
+          <t>15,985</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>-3,606</t>
+          <t>-11,440</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>54,955</t>
+          <t>23,706</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>전기업</t>
+          <t>기초 화학물질 제조업</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
@@ -2031,12 +2031,12 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>씨아이에스케미칼</t>
+          <t>엠디에스코리아</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -2056,27 +2056,27 @@
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>15,985</t>
+          <t>97,972</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>-11,440</t>
+          <t>6,512</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>23,706</t>
+          <t>53,818</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>기초 화학물질 제조업</t>
+          <t>기타 식품 제조업</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
@@ -2088,12 +2088,12 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>엠디에스코리아</t>
+          <t>동승</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -2113,27 +2113,27 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>97,972</t>
+          <t>78,625</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>6,512</t>
+          <t>14,525</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>53,818</t>
+          <t>5,438</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>기타 식품 제조업</t>
+          <t>부동산 임대 및 공급업</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K31" s="6" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>동승</t>
+          <t>에프엠더블유</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -2170,27 +2170,27 @@
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>78,625</t>
+          <t>30,282</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>14,525</t>
+          <t>4,762</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>5,438</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>부동산 임대 및 공급업</t>
+          <t>기타 식품 제조업</t>
         </is>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>유진</t>
         </is>
       </c>
       <c r="K32" s="6" t="inlineStr">
@@ -2202,22 +2202,22 @@
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>에프엠더블유</t>
+          <t>소노인터내셔널</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>유가</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
@@ -2227,27 +2227,27 @@
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>30,282</t>
+          <t>2,093,051</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>4,762</t>
+          <t>-148,064</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>852,372</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>기타 식품 제조업</t>
+          <t>일반 및 생활 숙박시설 운영업</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>유진</t>
+          <t>대신, 미래</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
@@ -2259,17 +2259,17 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>소노인터내셔널</t>
+          <t>싸이몬</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>유가</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -2284,27 +2284,27 @@
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>2,093,051</t>
+          <t>48,695</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>-148,064</t>
+          <t>15,714</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>852,372</t>
+          <t>61,761</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>일반 및 생활 숙박시설 운영업</t>
+          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업</t>
         </is>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>대신, 미래</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K34" s="6" t="inlineStr">
@@ -2316,12 +2316,12 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>싸이몬</t>
+          <t>바이다</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
@@ -2341,27 +2341,27 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>48,695</t>
+          <t>14,432</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>15,714</t>
+          <t>-3,951</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>61,761</t>
+          <t>15,108</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업</t>
+          <t>전자부품 제조업</t>
         </is>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K35" s="6" t="inlineStr">
@@ -2373,12 +2373,12 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>바이다</t>
+          <t>아이알큐더스</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
@@ -2398,27 +2398,27 @@
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>14,432</t>
+          <t>10,231</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>-3,951</t>
+          <t>-986</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>15,108</t>
+          <t>1,800</t>
         </is>
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>전자부품 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="K36" s="6" t="inlineStr">
@@ -2430,12 +2430,12 @@
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>아이알큐더스</t>
+          <t>씨엔티테크</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -2455,17 +2455,17 @@
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>10,231</t>
+          <t>27,015</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>-986</t>
+          <t>3,987</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>1,800</t>
+          <t>2,613</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
@@ -2475,7 +2475,7 @@
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>한화, 하나</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
@@ -2487,12 +2487,12 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>씨엔티테크</t>
+          <t>인터엑스</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -2512,17 +2512,17 @@
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>27,015</t>
+          <t>8,645</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>3,987</t>
+          <t>-20,272</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>2,613</t>
+          <t>4,530</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>한화, 하나</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K38" s="6" t="inlineStr">
@@ -2544,12 +2544,12 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>인터엑스</t>
+          <t>삼홍아크튜리온</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -2569,27 +2569,27 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>8,645</t>
+          <t>26,162</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>-20,272</t>
+          <t>-10,314</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>4,530</t>
+          <t>6,369</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
         </is>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>삼성, 미래</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr">
@@ -2601,12 +2601,12 @@
     <row r="40">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>삼홍아크튜리온</t>
+          <t>비앤비코리아</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
@@ -2626,27 +2626,27 @@
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>26,162</t>
+          <t>141,169</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
         <is>
-          <t>-10,314</t>
+          <t>21,406</t>
         </is>
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>6,369</t>
+          <t>43,932</t>
         </is>
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>삼성, 미래</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K40" s="6" t="inlineStr">
@@ -2658,12 +2658,12 @@
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>비앤비코리아</t>
+          <t>오토핸즈</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
@@ -2683,22 +2683,22 @@
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>141,169</t>
+          <t>238,564</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
         <is>
-          <t>21,406</t>
+          <t>6,047</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
         <is>
-          <t>43,932</t>
+          <t>6,129</t>
         </is>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>자동차 판매업</t>
         </is>
       </c>
       <c r="J41" s="6" t="inlineStr">
@@ -2715,12 +2715,12 @@
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>오토핸즈</t>
+          <t>아이벡스메디칼시스템즈</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
@@ -2740,27 +2740,27 @@
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>238,564</t>
+          <t>15,282</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
         <is>
-          <t>6,047</t>
+          <t>-7,227</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
-          <t>6,129</t>
+          <t>744</t>
         </is>
       </c>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>자동차 판매업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K42" s="6" t="inlineStr">
@@ -2772,12 +2772,12 @@
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>아이벡스메디칼시스템즈</t>
+          <t>피지티</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -2797,27 +2797,27 @@
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>15,282</t>
+          <t>40,141</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>-7,227</t>
+          <t>-69,722</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>6,029</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
@@ -2826,134 +2826,134 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>피지티</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>■ 심사 승인  (80건)</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="n"/>
+      <c r="C45" s="4" t="n"/>
+      <c r="D45" s="4" t="n"/>
+      <c r="E45" s="4" t="n"/>
+      <c r="F45" s="4" t="n"/>
+      <c r="G45" s="4" t="n"/>
+      <c r="H45" s="4" t="n"/>
+      <c r="I45" s="4" t="n"/>
+      <c r="J45" s="4" t="n"/>
+      <c r="K45" s="4" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>일자</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>회사명</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>시장</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>상장유형</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>기준연도</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>자기자본</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>업종</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>대표주관사</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>현황</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>(주)태석광학</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
         <is>
           <t>코스닥</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t>신규상장</t>
         </is>
       </c>
-      <c r="E44" s="6" t="inlineStr">
+      <c r="E47" s="6" t="inlineStr">
         <is>
           <t>FY25</t>
         </is>
       </c>
-      <c r="F44" s="7" t="inlineStr">
-        <is>
-          <t>40,141</t>
-        </is>
-      </c>
-      <c r="G44" s="7" t="inlineStr">
-        <is>
-          <t>-69,722</t>
-        </is>
-      </c>
-      <c r="H44" s="7" t="inlineStr">
-        <is>
-          <t>6,029</t>
-        </is>
-      </c>
-      <c r="I44" s="6" t="inlineStr">
-        <is>
-          <t>기타 화학제품 제조업</t>
-        </is>
-      </c>
-      <c r="J44" s="6" t="inlineStr">
-        <is>
-          <t>한국</t>
-        </is>
-      </c>
-      <c r="K44" s="6" t="inlineStr">
-        <is>
-          <t>예심 진행중</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>■ 심사 승인  (78건)</t>
-        </is>
-      </c>
-      <c r="B46" s="4" t="n"/>
-      <c r="C46" s="4" t="n"/>
-      <c r="D46" s="4" t="n"/>
-      <c r="E46" s="4" t="n"/>
-      <c r="F46" s="4" t="n"/>
-      <c r="G46" s="4" t="n"/>
-      <c r="H46" s="4" t="n"/>
-      <c r="I46" s="4" t="n"/>
-      <c r="J46" s="4" t="n"/>
-      <c r="K46" s="4" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>일자</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>회사명</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>시장</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>상장유형</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="inlineStr">
-        <is>
-          <t>기준연도</t>
-        </is>
-      </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="G47" s="5" t="inlineStr">
-        <is>
-          <t>순이익</t>
-        </is>
-      </c>
-      <c r="H47" s="5" t="inlineStr">
-        <is>
-          <t>자기자본</t>
-        </is>
-      </c>
-      <c r="I47" s="5" t="inlineStr">
-        <is>
-          <t>업종</t>
-        </is>
-      </c>
-      <c r="J47" s="5" t="inlineStr">
-        <is>
-          <t>대표주관사</t>
-        </is>
-      </c>
-      <c r="K47" s="5" t="inlineStr">
-        <is>
-          <t>현황</t>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>79,804</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>4,721</t>
+        </is>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>7,228</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>생활용품 도매업</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>신한, 대신</t>
+        </is>
+      </c>
+      <c r="K47" s="6" t="inlineStr">
+        <is>
+          <t>상장전</t>
         </is>
       </c>
     </row>
@@ -4520,12 +4520,12 @@
     <row r="76">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>엘리스</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="D76" s="6" t="inlineStr">
         <is>
-          <t>이전상장</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
@@ -4545,27 +4545,27 @@
       </c>
       <c r="F76" s="7" t="inlineStr">
         <is>
-          <t>48,646</t>
+          <t>39,513</t>
         </is>
       </c>
       <c r="G76" s="7" t="inlineStr">
         <is>
-          <t>6,017</t>
+          <t>15,666</t>
         </is>
       </c>
       <c r="H76" s="7" t="inlineStr">
         <is>
-          <t>18,795</t>
+          <t>85,400</t>
         </is>
       </c>
       <c r="I76" s="6" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J76" s="6" t="inlineStr">
         <is>
-          <t>하나</t>
+          <t>미래, 삼성</t>
         </is>
       </c>
       <c r="K76" s="6" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>바로팜</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
@@ -4592,7 +4592,7 @@
       </c>
       <c r="D77" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>이전상장</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
@@ -4602,32 +4602,32 @@
       </c>
       <c r="F77" s="7" t="inlineStr">
         <is>
-          <t>96,724</t>
+          <t>48,646</t>
         </is>
       </c>
       <c r="G77" s="7" t="inlineStr">
         <is>
-          <t>-9,679</t>
+          <t>6,017</t>
         </is>
       </c>
       <c r="H77" s="7" t="inlineStr">
         <is>
-          <t>30,673</t>
+          <t>18,795</t>
         </is>
       </c>
       <c r="I77" s="6" t="inlineStr">
         <is>
-          <t>상품 중개업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="J77" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>하나</t>
         </is>
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
-          <t>상장전</t>
+          <t>상장승인(상장예정)</t>
         </is>
       </c>
     </row>
@@ -4639,7 +4639,7 @@
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>크리에이츠</t>
+          <t>바로팜</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
@@ -4659,27 +4659,27 @@
       </c>
       <c r="F78" s="7" t="inlineStr">
         <is>
-          <t>76,395</t>
+          <t>96,724</t>
         </is>
       </c>
       <c r="G78" s="7" t="inlineStr">
         <is>
-          <t>23,749</t>
+          <t>-9,679</t>
         </is>
       </c>
       <c r="H78" s="7" t="inlineStr">
         <is>
-          <t>2,335</t>
+          <t>30,673</t>
         </is>
       </c>
       <c r="I78" s="6" t="inlineStr">
         <is>
-          <t>그외 기타 제품 제조업</t>
+          <t>상품 중개업</t>
         </is>
       </c>
       <c r="J78" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K78" s="6" t="inlineStr">
@@ -4691,12 +4691,12 @@
     <row r="79">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>래블업</t>
+          <t>크리에이츠</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
@@ -4716,27 +4716,27 @@
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>6,712</t>
+          <t>76,395</t>
         </is>
       </c>
       <c r="G79" s="7" t="inlineStr">
         <is>
-          <t>-1,526</t>
+          <t>23,749</t>
         </is>
       </c>
       <c r="H79" s="7" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>2,335</t>
         </is>
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
-          <t>데이터베이스 및 온라인정보 제공업</t>
+          <t>그외 기타 제품 제조업</t>
         </is>
       </c>
       <c r="J79" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K79" s="6" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>멜콘</t>
+          <t>래블업</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
@@ -4773,27 +4773,27 @@
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>39,319</t>
+          <t>6,712</t>
         </is>
       </c>
       <c r="G80" s="7" t="inlineStr">
         <is>
-          <t>4,739</t>
+          <t>-1,526</t>
         </is>
       </c>
       <c r="H80" s="7" t="inlineStr">
         <is>
-          <t>1,250</t>
+          <t>373</t>
         </is>
       </c>
       <c r="I80" s="6" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>데이터베이스 및 온라인정보 제공업</t>
         </is>
       </c>
       <c r="J80" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K80" s="6" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>엠비디</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
@@ -4830,44 +4830,44 @@
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>1,524</t>
+          <t>39,319</t>
         </is>
       </c>
       <c r="G81" s="7" t="inlineStr">
         <is>
-          <t>-2,125</t>
+          <t>4,739</t>
         </is>
       </c>
       <c r="H81" s="7" t="inlineStr">
         <is>
-          <t>2,753</t>
+          <t>1,250</t>
         </is>
       </c>
       <c r="I81" s="6" t="inlineStr">
         <is>
-          <t>물질 검사, 측정 및 분석기구 제조업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="J81" s="6" t="inlineStr">
         <is>
-          <t>하나</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K81" s="6" t="inlineStr">
         <is>
-          <t>상장전</t>
+          <t>상장승인(상장예정)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>에스케이증권제14호기업인수목적</t>
+          <t>엠비디</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
@@ -4887,27 +4887,27 @@
       </c>
       <c r="F82" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1,524</t>
         </is>
       </c>
       <c r="G82" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>-2,125</t>
         </is>
       </c>
       <c r="H82" s="7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>2,753</t>
         </is>
       </c>
       <c r="I82" s="6" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>물질 검사, 측정 및 분석기구 제조업</t>
         </is>
       </c>
       <c r="J82" s="6" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>하나</t>
         </is>
       </c>
       <c r="K82" s="6" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>케이비제34호스팩</t>
+          <t>에스케이증권제14호기업인수목적</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
@@ -4954,7 +4954,7 @@
       </c>
       <c r="H83" s="7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>17</t>
         </is>
       </c>
       <c r="I83" s="6" t="inlineStr">
@@ -4964,12 +4964,12 @@
       </c>
       <c r="J83" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="K83" s="6" t="inlineStr">
         <is>
-          <t>상장승인(상장예정)</t>
+          <t>상장전</t>
         </is>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>한국제17호스팩</t>
+          <t>케이비제34호스팩</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="H84" s="7" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>21</t>
         </is>
       </c>
       <c r="I84" s="6" t="inlineStr">
@@ -5021,12 +5021,12 @@
       </c>
       <c r="J84" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="K84" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-09-22)</t>
+          <t>상장승인(상장예정)</t>
         </is>
       </c>
     </row>
@@ -5038,7 +5038,7 @@
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>한화플러스제6호스팩</t>
+          <t>한국제17호스팩</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="H85" s="7" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>170</t>
         </is>
       </c>
       <c r="I85" s="6" t="inlineStr">
@@ -5078,24 +5078,24 @@
       </c>
       <c r="J85" s="6" t="inlineStr">
         <is>
-          <t>한화</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K85" s="6" t="inlineStr">
         <is>
-          <t>상장전</t>
+          <t>상장완료 (2026-09-22)</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>엔에이치스팩34호</t>
+          <t>한화플러스제6호스팩</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
@@ -5125,34 +5125,34 @@
       </c>
       <c r="H86" s="7" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I86" s="6" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="J86" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>한화</t>
         </is>
       </c>
       <c r="K86" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-09-10)</t>
+          <t>상장전</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>글로벌테크놀로지</t>
+          <t>엔에이치스팩34호</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
@@ -5172,32 +5172,32 @@
       </c>
       <c r="F87" s="7" t="inlineStr">
         <is>
-          <t>29,689</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G87" s="7" t="inlineStr">
         <is>
-          <t>-25,889</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H87" s="7" t="inlineStr">
         <is>
-          <t>6,402</t>
+          <t>55</t>
         </is>
       </c>
       <c r="I87" s="6" t="inlineStr">
         <is>
-          <t>반도체 제조업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="J87" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K87" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-09-29)</t>
+          <t>상장완료 (2026-09-10)</t>
         </is>
       </c>
     </row>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>글로벌테크놀로지</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
@@ -5224,37 +5224,37 @@
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>FY24</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="F88" s="7" t="inlineStr">
         <is>
-          <t>48,504</t>
+          <t>29,689</t>
         </is>
       </c>
       <c r="G88" s="7" t="inlineStr">
         <is>
-          <t>3,668</t>
+          <t>-25,889</t>
         </is>
       </c>
       <c r="H88" s="7" t="inlineStr">
         <is>
-          <t>8,448</t>
+          <t>6,402</t>
         </is>
       </c>
       <c r="I88" s="6" t="inlineStr">
         <is>
-          <t>항공기,우주선 및 부품 제조업</t>
+          <t>반도체 제조업</t>
         </is>
       </c>
       <c r="J88" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K88" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-09-30)</t>
+          <t>상장완료 (2026-09-29)</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>디티에스</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
@@ -5286,22 +5286,22 @@
       </c>
       <c r="F89" s="7" t="inlineStr">
         <is>
-          <t>142,718</t>
+          <t>48,504</t>
         </is>
       </c>
       <c r="G89" s="7" t="inlineStr">
         <is>
-          <t>18,765</t>
+          <t>3,668</t>
         </is>
       </c>
       <c r="H89" s="7" t="inlineStr">
         <is>
-          <t>63,153</t>
+          <t>8,448</t>
         </is>
       </c>
       <c r="I89" s="6" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>항공기,우주선 및 부품 제조업</t>
         </is>
       </c>
       <c r="J89" s="6" t="inlineStr">
@@ -5311,19 +5311,19 @@
       </c>
       <c r="K89" s="6" t="inlineStr">
         <is>
-          <t>상장전</t>
+          <t>상장완료 (2026-09-30)</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>네오사피엔스</t>
+          <t>디티에스</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
@@ -5338,27 +5338,27 @@
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>FY25</t>
+          <t>FY24</t>
         </is>
       </c>
       <c r="F90" s="7" t="inlineStr">
         <is>
-          <t>10,649</t>
+          <t>142,718</t>
         </is>
       </c>
       <c r="G90" s="7" t="inlineStr">
         <is>
-          <t>-6,994</t>
+          <t>18,765</t>
         </is>
       </c>
       <c r="H90" s="7" t="inlineStr">
         <is>
-          <t>-39,962</t>
+          <t>63,153</t>
         </is>
       </c>
       <c r="I90" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="J90" s="6" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="K90" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-09-21)</t>
+          <t>상장전</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>엠에스바이오</t>
+          <t>네오사피엔스</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
@@ -5400,44 +5400,44 @@
       </c>
       <c r="F91" s="7" t="inlineStr">
         <is>
-          <t>23,787</t>
+          <t>10,649</t>
         </is>
       </c>
       <c r="G91" s="7" t="inlineStr">
         <is>
-          <t>7,288</t>
+          <t>-6,994</t>
         </is>
       </c>
       <c r="H91" s="7" t="inlineStr">
         <is>
-          <t>1,942</t>
+          <t>-39,962</t>
         </is>
       </c>
       <c r="I91" s="6" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J91" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K91" s="6" t="inlineStr">
         <is>
-          <t>상장전</t>
+          <t>상장완료 (2026-09-21)</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>기도산업</t>
+          <t>엠에스바이오</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
@@ -5457,32 +5457,32 @@
       </c>
       <c r="F92" s="7" t="inlineStr">
         <is>
-          <t>346,551</t>
+          <t>23,787</t>
         </is>
       </c>
       <c r="G92" s="7" t="inlineStr">
         <is>
-          <t>35,334</t>
+          <t>7,288</t>
         </is>
       </c>
       <c r="H92" s="7" t="inlineStr">
         <is>
-          <t>145,991</t>
+          <t>1,942</t>
         </is>
       </c>
       <c r="I92" s="6" t="inlineStr">
         <is>
-          <t>봉제의복 제조업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="J92" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="K92" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-08-21)</t>
+          <t>상장전</t>
         </is>
       </c>
     </row>
@@ -5494,7 +5494,7 @@
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>브릴스</t>
+          <t>기도산업</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
@@ -5514,32 +5514,32 @@
       </c>
       <c r="F93" s="7" t="inlineStr">
         <is>
-          <t>23,759</t>
+          <t>346,551</t>
         </is>
       </c>
       <c r="G93" s="7" t="inlineStr">
         <is>
-          <t>1,744</t>
+          <t>35,334</t>
         </is>
       </c>
       <c r="H93" s="7" t="inlineStr">
         <is>
-          <t>4,785</t>
+          <t>145,991</t>
         </is>
       </c>
       <c r="I93" s="6" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>봉제의복 제조업</t>
         </is>
       </c>
       <c r="J93" s="6" t="inlineStr">
         <is>
-          <t>IBK</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K93" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-10-01)</t>
+          <t>상장완료 (2026-08-21)</t>
         </is>
       </c>
     </row>
@@ -5551,7 +5551,7 @@
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>와이즈플래닛컴퍼니</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
@@ -5571,44 +5571,44 @@
       </c>
       <c r="F94" s="7" t="inlineStr">
         <is>
-          <t>44,578</t>
+          <t>23,759</t>
         </is>
       </c>
       <c r="G94" s="7" t="inlineStr">
         <is>
-          <t>7,748</t>
+          <t>1,744</t>
         </is>
       </c>
       <c r="H94" s="7" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>4,785</t>
         </is>
       </c>
       <c r="I94" s="6" t="inlineStr">
         <is>
-          <t>광고물 문안, 도안, 설계 등 작성업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="J94" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>IBK</t>
         </is>
       </c>
       <c r="K94" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-09-23)</t>
+          <t>상장완료 (2026-10-01)</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>니어스랩</t>
+          <t>와이즈플래닛컴퍼니</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
@@ -5628,32 +5628,32 @@
       </c>
       <c r="F95" s="7" t="inlineStr">
         <is>
-          <t>6,361</t>
+          <t>44,578</t>
         </is>
       </c>
       <c r="G95" s="7" t="inlineStr">
         <is>
-          <t>-7,287</t>
+          <t>7,748</t>
         </is>
       </c>
       <c r="H95" s="7" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>959</t>
         </is>
       </c>
       <c r="I95" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>광고물 문안, 도안, 설계 등 작성업</t>
         </is>
       </c>
       <c r="J95" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K95" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-08-24)</t>
+          <t>상장완료 (2026-09-23)</t>
         </is>
       </c>
     </row>
@@ -5665,7 +5665,7 @@
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>해치텍</t>
+          <t>니어스랩</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="F96" s="7" t="inlineStr">
         <is>
-          <t>14,079</t>
+          <t>6,361</t>
         </is>
       </c>
       <c r="G96" s="7" t="inlineStr">
         <is>
-          <t>-8,009</t>
+          <t>-7,287</t>
         </is>
       </c>
       <c r="H96" s="7" t="inlineStr">
         <is>
-          <t>2,229</t>
+          <t>127</t>
         </is>
       </c>
       <c r="I96" s="6" t="inlineStr">
         <is>
-          <t>반도체 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J96" s="6" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K96" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-08-25)</t>
+          <t>상장완료 (2026-08-24)</t>
         </is>
       </c>
     </row>
@@ -5722,7 +5722,7 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>해치텍</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
@@ -5742,44 +5742,44 @@
       </c>
       <c r="F97" s="7" t="inlineStr">
         <is>
-          <t>7,936</t>
+          <t>14,079</t>
         </is>
       </c>
       <c r="G97" s="7" t="inlineStr">
         <is>
-          <t>-62,995</t>
+          <t>-8,009</t>
         </is>
       </c>
       <c r="H97" s="7" t="inlineStr">
         <is>
-          <t>8,341</t>
+          <t>2,229</t>
         </is>
       </c>
       <c r="I97" s="6" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>반도체 제조업</t>
         </is>
       </c>
       <c r="J97" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="K97" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-09-04)</t>
+          <t>상장완료 (2026-08-25)</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>에이치엘지노믹스</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
@@ -5799,32 +5799,32 @@
       </c>
       <c r="F98" s="7" t="inlineStr">
         <is>
-          <t>28,877</t>
+          <t>7,936</t>
         </is>
       </c>
       <c r="G98" s="7" t="inlineStr">
         <is>
-          <t>8,452</t>
+          <t>-62,995</t>
         </is>
       </c>
       <c r="H98" s="7" t="inlineStr">
         <is>
-          <t>83,552</t>
+          <t>8,341</t>
         </is>
       </c>
       <c r="I98" s="6" t="inlineStr">
         <is>
-          <t>기초 의약물질 제조업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="J98" s="6" t="inlineStr">
         <is>
-          <t>KB, IBK</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K98" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-07-24)</t>
+          <t>상장완료 (2026-09-04)</t>
         </is>
       </c>
     </row>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>딜리셔스</t>
+          <t>에이치엘지노믹스</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
@@ -5856,44 +5856,44 @@
       </c>
       <c r="F99" s="7" t="inlineStr">
         <is>
-          <t>25,149</t>
+          <t>28,877</t>
         </is>
       </c>
       <c r="G99" s="7" t="inlineStr">
         <is>
-          <t>-20,419</t>
+          <t>8,452</t>
         </is>
       </c>
       <c r="H99" s="7" t="inlineStr">
         <is>
-          <t>-114,384</t>
+          <t>83,552</t>
         </is>
       </c>
       <c r="I99" s="6" t="inlineStr">
         <is>
-          <t>무점포 소매업</t>
+          <t>기초 의약물질 제조업</t>
         </is>
       </c>
       <c r="J99" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>KB, IBK</t>
         </is>
       </c>
       <c r="K99" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-08-12)</t>
+          <t>상장완료 (2026-07-24)</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스</t>
+          <t>딜리셔스</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
@@ -5913,44 +5913,44 @@
       </c>
       <c r="F100" s="7" t="inlineStr">
         <is>
-          <t>2,588,400</t>
+          <t>25,149</t>
         </is>
       </c>
       <c r="G100" s="7" t="inlineStr">
         <is>
-          <t>15,755,864</t>
+          <t>-20,419</t>
         </is>
       </c>
       <c r="H100" s="7" t="inlineStr">
         <is>
-          <t>30,841,690</t>
+          <t>-114,384</t>
         </is>
       </c>
       <c r="I100" s="6" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>무점포 소매업</t>
         </is>
       </c>
       <c r="J100" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K100" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-08-18)</t>
+          <t>상장완료 (2026-08-12)</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>한국제16호스팩</t>
+          <t>인제니아테라퓨틱스</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
@@ -5968,30 +5968,46 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F101" s="7" t="inlineStr"/>
-      <c r="G101" s="7" t="inlineStr"/>
-      <c r="H101" s="7" t="inlineStr"/>
-      <c r="I101" s="6" t="inlineStr"/>
+      <c r="F101" s="7" t="inlineStr">
+        <is>
+          <t>2,588,400</t>
+        </is>
+      </c>
+      <c r="G101" s="7" t="inlineStr">
+        <is>
+          <t>15,755,864</t>
+        </is>
+      </c>
+      <c r="H101" s="7" t="inlineStr">
+        <is>
+          <t>30,841,690</t>
+        </is>
+      </c>
+      <c r="I101" s="6" t="inlineStr">
+        <is>
+          <t>자연과학 및 공학 연구개발업</t>
+        </is>
+      </c>
       <c r="J101" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K101" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-06-30)</t>
+          <t>상장완료 (2026-08-18)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>레메디</t>
+          <t>한국제16호스팩</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
@@ -6009,34 +6025,18 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F102" s="7" t="inlineStr">
-        <is>
-          <t>13,441</t>
-        </is>
-      </c>
-      <c r="G102" s="7" t="inlineStr">
-        <is>
-          <t>741</t>
-        </is>
-      </c>
-      <c r="H102" s="7" t="inlineStr">
-        <is>
-          <t>5,870</t>
-        </is>
-      </c>
-      <c r="I102" s="6" t="inlineStr">
-        <is>
-          <t>의료용 기기 제조업</t>
-        </is>
-      </c>
+      <c r="F102" s="7" t="inlineStr"/>
+      <c r="G102" s="7" t="inlineStr"/>
+      <c r="H102" s="7" t="inlineStr"/>
+      <c r="I102" s="6" t="inlineStr"/>
       <c r="J102" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K102" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-07-13)</t>
+          <t>상장완료 (2026-06-30)</t>
         </is>
       </c>
     </row>
@@ -6048,7 +6048,7 @@
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>케이앤에스아이앤씨</t>
+          <t>레메디</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
@@ -6068,44 +6068,44 @@
       </c>
       <c r="F103" s="7" t="inlineStr">
         <is>
-          <t>13,482</t>
+          <t>13,441</t>
         </is>
       </c>
       <c r="G103" s="7" t="inlineStr">
         <is>
-          <t>-2,213</t>
+          <t>741</t>
         </is>
       </c>
       <c r="H103" s="7" t="inlineStr">
         <is>
-          <t>4,273</t>
+          <t>5,870</t>
         </is>
       </c>
       <c r="I103" s="6" t="inlineStr">
         <is>
-          <t>통신 및 방송 장비 제조업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="J103" s="6" t="inlineStr">
         <is>
-          <t>IBK</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="K103" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-08-13)</t>
+          <t>상장완료 (2026-07-13)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="6" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>메리츠제2호스팩</t>
+          <t>케이앤에스아이앤씨</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
@@ -6123,30 +6123,46 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F104" s="7" t="inlineStr"/>
-      <c r="G104" s="7" t="inlineStr"/>
-      <c r="H104" s="7" t="inlineStr"/>
-      <c r="I104" s="6" t="inlineStr"/>
+      <c r="F104" s="7" t="inlineStr">
+        <is>
+          <t>13,482</t>
+        </is>
+      </c>
+      <c r="G104" s="7" t="inlineStr">
+        <is>
+          <t>-2,213</t>
+        </is>
+      </c>
+      <c r="H104" s="7" t="inlineStr">
+        <is>
+          <t>4,273</t>
+        </is>
+      </c>
+      <c r="I104" s="6" t="inlineStr">
+        <is>
+          <t>통신 및 방송 장비 제조업</t>
+        </is>
+      </c>
       <c r="J104" s="6" t="inlineStr">
         <is>
-          <t>메리츠</t>
+          <t>IBK</t>
         </is>
       </c>
       <c r="K104" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-06-19)</t>
+          <t>상장완료 (2026-08-13)</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>빅웨이브로보틱스</t>
+          <t>메리츠제2호스팩</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
@@ -6161,49 +6177,33 @@
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>FY24</t>
-        </is>
-      </c>
-      <c r="F105" s="7" t="inlineStr">
-        <is>
-          <t>13,851</t>
-        </is>
-      </c>
-      <c r="G105" s="7" t="inlineStr">
-        <is>
-          <t>-5,856</t>
-        </is>
-      </c>
-      <c r="H105" s="7" t="inlineStr">
-        <is>
-          <t>9,470</t>
-        </is>
-      </c>
-      <c r="I105" s="6" t="inlineStr">
-        <is>
-          <t>소프트웨어 개발 및 공급업</t>
-        </is>
-      </c>
+          <t>FY25</t>
+        </is>
+      </c>
+      <c r="F105" s="7" t="inlineStr"/>
+      <c r="G105" s="7" t="inlineStr"/>
+      <c r="H105" s="7" t="inlineStr"/>
+      <c r="I105" s="6" t="inlineStr"/>
       <c r="J105" s="6" t="inlineStr">
         <is>
-          <t>유진, 미래</t>
+          <t>메리츠</t>
         </is>
       </c>
       <c r="K105" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-09-29)</t>
+          <t>상장완료 (2026-06-19)</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="6" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>매드업</t>
+          <t>빅웨이브로보틱스</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
@@ -6223,44 +6223,44 @@
       </c>
       <c r="F106" s="7" t="inlineStr">
         <is>
-          <t>34,989</t>
+          <t>13,851</t>
         </is>
       </c>
       <c r="G106" s="7" t="inlineStr">
         <is>
-          <t>-2,747</t>
+          <t>-5,856</t>
         </is>
       </c>
       <c r="H106" s="7" t="inlineStr">
         <is>
-          <t>-15,766</t>
+          <t>9,470</t>
         </is>
       </c>
       <c r="I106" s="6" t="inlineStr">
         <is>
-          <t>광고</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J106" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>유진, 미래</t>
         </is>
       </c>
       <c r="K106" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-07-01)</t>
+          <t>상장완료 (2026-09-29)</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="6" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>져스텍</t>
+          <t>매드업</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
@@ -6280,32 +6280,32 @@
       </c>
       <c r="F107" s="7" t="inlineStr">
         <is>
-          <t>19,851</t>
+          <t>34,989</t>
         </is>
       </c>
       <c r="G107" s="7" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>-2,747</t>
         </is>
       </c>
       <c r="H107" s="7" t="inlineStr">
         <is>
-          <t>10,953</t>
+          <t>-15,766</t>
         </is>
       </c>
       <c r="I107" s="6" t="inlineStr">
         <is>
-          <t>기계</t>
+          <t>광고</t>
         </is>
       </c>
       <c r="J107" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K107" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-06-29)</t>
+          <t>상장완료 (2026-07-01)</t>
         </is>
       </c>
     </row>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>스트라드비젼</t>
+          <t>져스텍</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
@@ -6337,44 +6337,44 @@
       </c>
       <c r="F108" s="7" t="inlineStr">
         <is>
-          <t>11,539</t>
+          <t>19,851</t>
         </is>
       </c>
       <c r="G108" s="7" t="inlineStr">
         <is>
-          <t>-65,529</t>
+          <t>444</t>
         </is>
       </c>
       <c r="H108" s="7" t="inlineStr">
         <is>
-          <t>-245,151</t>
+          <t>10,953</t>
         </is>
       </c>
       <c r="I108" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어</t>
+          <t>기계</t>
         </is>
       </c>
       <c r="J108" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K108" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-06-30)</t>
+          <t>상장완료 (2026-06-29)</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="6" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>대신밸런스제20호스팩</t>
+          <t>스트라드비젼</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
@@ -6389,33 +6389,49 @@
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>FY25</t>
-        </is>
-      </c>
-      <c r="F109" s="7" t="inlineStr"/>
-      <c r="G109" s="7" t="inlineStr"/>
-      <c r="H109" s="7" t="inlineStr"/>
-      <c r="I109" s="6" t="inlineStr"/>
+          <t>FY24</t>
+        </is>
+      </c>
+      <c r="F109" s="7" t="inlineStr">
+        <is>
+          <t>11,539</t>
+        </is>
+      </c>
+      <c r="G109" s="7" t="inlineStr">
+        <is>
+          <t>-65,529</t>
+        </is>
+      </c>
+      <c r="H109" s="7" t="inlineStr">
+        <is>
+          <t>-245,151</t>
+        </is>
+      </c>
+      <c r="I109" s="6" t="inlineStr">
+        <is>
+          <t>소프트웨어</t>
+        </is>
+      </c>
       <c r="J109" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="K109" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-06-05)</t>
+          <t>상장완료 (2026-06-30)</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="6" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>피스피스스튜디오</t>
+          <t>대신밸런스제20호스팩</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
@@ -6430,37 +6446,21 @@
       </c>
       <c r="E110" s="6" t="inlineStr">
         <is>
-          <t>FY24</t>
-        </is>
-      </c>
-      <c r="F110" s="7" t="inlineStr">
-        <is>
-          <t>113,777</t>
-        </is>
-      </c>
-      <c r="G110" s="7" t="inlineStr">
-        <is>
-          <t>17,603</t>
-        </is>
-      </c>
-      <c r="H110" s="7" t="inlineStr">
-        <is>
-          <t>55,861</t>
-        </is>
-      </c>
-      <c r="I110" s="6" t="inlineStr">
-        <is>
-          <t>섬유,의류,신발,호화품</t>
-        </is>
-      </c>
+          <t>FY25</t>
+        </is>
+      </c>
+      <c r="F110" s="7" t="inlineStr"/>
+      <c r="G110" s="7" t="inlineStr"/>
+      <c r="H110" s="7" t="inlineStr"/>
+      <c r="I110" s="6" t="inlineStr"/>
       <c r="J110" s="6" t="inlineStr">
         <is>
-          <t>NH, 미래</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K110" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-06-08)</t>
+          <t>상장완료 (2026-06-05)</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>폴레드</t>
+          <t>피스피스스튜디오</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
@@ -6492,32 +6492,32 @@
       </c>
       <c r="F111" s="7" t="inlineStr">
         <is>
-          <t>52,808</t>
+          <t>113,777</t>
         </is>
       </c>
       <c r="G111" s="7" t="inlineStr">
         <is>
-          <t>543</t>
+          <t>17,603</t>
         </is>
       </c>
       <c r="H111" s="7" t="inlineStr">
         <is>
-          <t>25,416</t>
+          <t>55,861</t>
         </is>
       </c>
       <c r="I111" s="6" t="inlineStr">
         <is>
-          <t>가정용기기와용품</t>
+          <t>섬유,의류,신발,호화품</t>
         </is>
       </c>
       <c r="J111" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>NH, 미래</t>
         </is>
       </c>
       <c r="K111" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-05-14)</t>
+          <t>상장완료 (2026-06-08)</t>
         </is>
       </c>
     </row>
@@ -6529,7 +6529,7 @@
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>레몬헬스케어</t>
+          <t>폴레드</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
@@ -6549,44 +6549,44 @@
       </c>
       <c r="F112" s="7" t="inlineStr">
         <is>
-          <t>14,877</t>
+          <t>52,808</t>
         </is>
       </c>
       <c r="G112" s="7" t="inlineStr">
         <is>
-          <t>-2,898</t>
+          <t>543</t>
         </is>
       </c>
       <c r="H112" s="7" t="inlineStr">
         <is>
-          <t>-31,162</t>
+          <t>25,416</t>
         </is>
       </c>
       <c r="I112" s="6" t="inlineStr">
         <is>
-          <t>건강관리업체및서비스</t>
+          <t>가정용기기와용품</t>
         </is>
       </c>
       <c r="J112" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K112" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-07-06)</t>
+          <t>상장완료 (2026-05-14)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="6" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>마키나락스</t>
+          <t>레몬헬스케어</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
@@ -6606,32 +6606,32 @@
       </c>
       <c r="F113" s="7" t="inlineStr">
         <is>
-          <t>8,294</t>
+          <t>14,877</t>
         </is>
       </c>
       <c r="G113" s="7" t="inlineStr">
         <is>
-          <t>-6,073</t>
+          <t>-2,898</t>
         </is>
       </c>
       <c r="H113" s="7" t="inlineStr">
         <is>
-          <t>2,680</t>
+          <t>-31,162</t>
         </is>
       </c>
       <c r="I113" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어</t>
+          <t>건강관리업체및서비스</t>
         </is>
       </c>
       <c r="J113" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="K113" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-05-20)</t>
+          <t>상장완료 (2026-07-06)</t>
         </is>
       </c>
     </row>
@@ -6643,7 +6643,7 @@
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>채비</t>
+          <t>마키나락스</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
@@ -6663,44 +6663,44 @@
       </c>
       <c r="F114" s="7" t="inlineStr">
         <is>
-          <t>85,082</t>
+          <t>8,294</t>
         </is>
       </c>
       <c r="G114" s="7" t="inlineStr">
         <is>
-          <t>-54,495</t>
+          <t>-6,073</t>
         </is>
       </c>
       <c r="H114" s="7" t="inlineStr">
         <is>
-          <t>96,866</t>
+          <t>2,680</t>
         </is>
       </c>
       <c r="I114" s="6" t="inlineStr">
         <is>
-          <t>전기제품</t>
+          <t>소프트웨어</t>
         </is>
       </c>
       <c r="J114" s="6" t="inlineStr">
         <is>
-          <t>KB, 삼성, 대신, 하나</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K114" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-04-29)</t>
+          <t>상장완료 (2026-05-20)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="6" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>키움히어로제2호스팩</t>
+          <t>채비</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
@@ -6718,30 +6718,46 @@
           <t>FY24</t>
         </is>
       </c>
-      <c r="F115" s="7" t="inlineStr"/>
-      <c r="G115" s="7" t="inlineStr"/>
-      <c r="H115" s="7" t="inlineStr"/>
-      <c r="I115" s="6" t="inlineStr"/>
+      <c r="F115" s="7" t="inlineStr">
+        <is>
+          <t>85,082</t>
+        </is>
+      </c>
+      <c r="G115" s="7" t="inlineStr">
+        <is>
+          <t>-54,495</t>
+        </is>
+      </c>
+      <c r="H115" s="7" t="inlineStr">
+        <is>
+          <t>96,866</t>
+        </is>
+      </c>
+      <c r="I115" s="6" t="inlineStr">
+        <is>
+          <t>전기제품</t>
+        </is>
+      </c>
       <c r="J115" s="6" t="inlineStr">
         <is>
-          <t>키움</t>
+          <t>KB, 삼성, 대신, 하나</t>
         </is>
       </c>
       <c r="K115" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-04-23)</t>
+          <t>상장완료 (2026-04-29)</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="6" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>세미티에스</t>
+          <t>키움히어로제2호스팩</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
@@ -6751,7 +6767,7 @@
       </c>
       <c r="D116" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E116" s="6" t="inlineStr">
@@ -6759,46 +6775,30 @@
           <t>FY24</t>
         </is>
       </c>
-      <c r="F116" s="7" t="inlineStr">
-        <is>
-          <t>20,808</t>
-        </is>
-      </c>
-      <c r="G116" s="7" t="inlineStr">
-        <is>
-          <t>7,337</t>
-        </is>
-      </c>
-      <c r="H116" s="7" t="inlineStr">
-        <is>
-          <t>26,616</t>
-        </is>
-      </c>
-      <c r="I116" s="6" t="inlineStr">
-        <is>
-          <t>반도체와반도체장비</t>
-        </is>
-      </c>
+      <c r="F116" s="7" t="inlineStr"/>
+      <c r="G116" s="7" t="inlineStr"/>
+      <c r="H116" s="7" t="inlineStr"/>
+      <c r="I116" s="6" t="inlineStr"/>
       <c r="J116" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>키움</t>
         </is>
       </c>
       <c r="K116" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-02-05)</t>
+          <t>상장완료 (2026-04-23)</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="6" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>교보20호스팩</t>
+          <t>세미티에스</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
@@ -6808,7 +6808,7 @@
       </c>
       <c r="D117" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E117" s="6" t="inlineStr">
@@ -6816,30 +6816,46 @@
           <t>FY24</t>
         </is>
       </c>
-      <c r="F117" s="7" t="inlineStr"/>
-      <c r="G117" s="7" t="inlineStr"/>
-      <c r="H117" s="7" t="inlineStr"/>
-      <c r="I117" s="6" t="inlineStr"/>
+      <c r="F117" s="7" t="inlineStr">
+        <is>
+          <t>20,808</t>
+        </is>
+      </c>
+      <c r="G117" s="7" t="inlineStr">
+        <is>
+          <t>7,337</t>
+        </is>
+      </c>
+      <c r="H117" s="7" t="inlineStr">
+        <is>
+          <t>26,616</t>
+        </is>
+      </c>
+      <c r="I117" s="6" t="inlineStr">
+        <is>
+          <t>반도체와반도체장비</t>
+        </is>
+      </c>
       <c r="J117" s="6" t="inlineStr">
         <is>
-          <t>교보</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K117" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-04-02)</t>
+          <t>상장완료 (2026-02-05)</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="6" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>케이피항공산업</t>
+          <t>교보20호스팩</t>
         </is>
       </c>
       <c r="C118" s="6" t="inlineStr">
@@ -6849,7 +6865,7 @@
       </c>
       <c r="D118" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E118" s="6" t="inlineStr">
@@ -6857,34 +6873,18 @@
           <t>FY24</t>
         </is>
       </c>
-      <c r="F118" s="7" t="inlineStr">
-        <is>
-          <t>49,651</t>
-        </is>
-      </c>
-      <c r="G118" s="7" t="inlineStr">
-        <is>
-          <t>3,018</t>
-        </is>
-      </c>
-      <c r="H118" s="7" t="inlineStr">
-        <is>
-          <t>15,901</t>
-        </is>
-      </c>
-      <c r="I118" s="6" t="inlineStr">
-        <is>
-          <t>우주항공과국방</t>
-        </is>
-      </c>
+      <c r="F118" s="7" t="inlineStr"/>
+      <c r="G118" s="7" t="inlineStr"/>
+      <c r="H118" s="7" t="inlineStr"/>
+      <c r="I118" s="6" t="inlineStr"/>
       <c r="J118" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>교보</t>
         </is>
       </c>
       <c r="K118" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-01-29)</t>
+          <t>상장완료 (2026-04-02)</t>
         </is>
       </c>
     </row>
@@ -6896,7 +6896,7 @@
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>한패스</t>
+          <t>케이피항공산업</t>
         </is>
       </c>
       <c r="C119" s="6" t="inlineStr">
@@ -6906,7 +6906,7 @@
       </c>
       <c r="D119" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E119" s="6" t="inlineStr">
@@ -6916,44 +6916,44 @@
       </c>
       <c r="F119" s="7" t="inlineStr">
         <is>
-          <t>55,297</t>
+          <t>49,651</t>
         </is>
       </c>
       <c r="G119" s="7" t="inlineStr">
         <is>
-          <t>4,403</t>
+          <t>3,018</t>
         </is>
       </c>
       <c r="H119" s="7" t="inlineStr">
         <is>
-          <t>-28,065</t>
+          <t>15,901</t>
         </is>
       </c>
       <c r="I119" s="6" t="inlineStr">
         <is>
-          <t>IT서비스</t>
+          <t>우주항공과국방</t>
         </is>
       </c>
       <c r="J119" s="6" t="inlineStr">
         <is>
-          <t>한국, 대신</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K119" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-03-25)</t>
+          <t>상장완료 (2026-01-29)</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="6" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>신한제18호스팩</t>
+          <t>한패스</t>
         </is>
       </c>
       <c r="C120" s="6" t="inlineStr">
@@ -6971,30 +6971,46 @@
           <t>FY24</t>
         </is>
       </c>
-      <c r="F120" s="7" t="inlineStr"/>
-      <c r="G120" s="7" t="inlineStr"/>
-      <c r="H120" s="7" t="inlineStr"/>
-      <c r="I120" s="6" t="inlineStr"/>
+      <c r="F120" s="7" t="inlineStr">
+        <is>
+          <t>55,297</t>
+        </is>
+      </c>
+      <c r="G120" s="7" t="inlineStr">
+        <is>
+          <t>4,403</t>
+        </is>
+      </c>
+      <c r="H120" s="7" t="inlineStr">
+        <is>
+          <t>-28,065</t>
+        </is>
+      </c>
+      <c r="I120" s="6" t="inlineStr">
+        <is>
+          <t>IT서비스</t>
+        </is>
+      </c>
       <c r="J120" s="6" t="inlineStr">
         <is>
-          <t>신한</t>
+          <t>한국, 대신</t>
         </is>
       </c>
       <c r="K120" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-04-30)</t>
+          <t>상장완료 (2026-03-25)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="6" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>엔에이치스팩33호</t>
+          <t>신한제18호스팩</t>
         </is>
       </c>
       <c r="C121" s="6" t="inlineStr">
@@ -7018,24 +7034,24 @@
       <c r="I121" s="6" t="inlineStr"/>
       <c r="J121" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>신한</t>
         </is>
       </c>
       <c r="K121" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-03-27)</t>
+          <t>상장완료 (2026-04-30)</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="6" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>신한제17호스팩</t>
+          <t>엔에이치스팩33호</t>
         </is>
       </c>
       <c r="C122" s="6" t="inlineStr">
@@ -7059,24 +7075,24 @@
       <c r="I122" s="6" t="inlineStr"/>
       <c r="J122" s="6" t="inlineStr">
         <is>
-          <t>신한</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K122" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-04-01)</t>
+          <t>상장완료 (2026-03-27)</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="6" t="inlineStr">
         <is>
-          <t>2026-01-16</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>아이엠바이오로직스</t>
+          <t>신한제17호스팩</t>
         </is>
       </c>
       <c r="C123" s="6" t="inlineStr">
@@ -7094,34 +7110,18 @@
           <t>FY24</t>
         </is>
       </c>
-      <c r="F123" s="7" t="inlineStr">
-        <is>
-          <t>27,594</t>
-        </is>
-      </c>
-      <c r="G123" s="7" t="inlineStr">
-        <is>
-          <t>-11,884</t>
-        </is>
-      </c>
-      <c r="H123" s="7" t="inlineStr">
-        <is>
-          <t>-77,202</t>
-        </is>
-      </c>
-      <c r="I123" s="6" t="inlineStr">
-        <is>
-          <t>제약</t>
-        </is>
-      </c>
+      <c r="F123" s="7" t="inlineStr"/>
+      <c r="G123" s="7" t="inlineStr"/>
+      <c r="H123" s="7" t="inlineStr"/>
+      <c r="I123" s="6" t="inlineStr"/>
       <c r="J123" s="6" t="inlineStr">
         <is>
-          <t>한국, 신한</t>
+          <t>신한</t>
         </is>
       </c>
       <c r="K123" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-03-20)</t>
+          <t>상장완료 (2026-04-01)</t>
         </is>
       </c>
     </row>
@@ -7133,7 +7133,7 @@
       </c>
       <c r="B124" s="6" t="inlineStr">
         <is>
-          <t>에스팀</t>
+          <t>아이엠바이오로직스</t>
         </is>
       </c>
       <c r="C124" s="6" t="inlineStr">
@@ -7153,237 +7153,237 @@
       </c>
       <c r="F124" s="7" t="inlineStr">
         <is>
-          <t>35,574</t>
+          <t>27,594</t>
         </is>
       </c>
       <c r="G124" s="7" t="inlineStr">
         <is>
-          <t>1,372</t>
+          <t>-11,884</t>
         </is>
       </c>
       <c r="H124" s="7" t="inlineStr">
         <is>
-          <t>12,331</t>
+          <t>-77,202</t>
         </is>
       </c>
       <c r="I124" s="6" t="inlineStr">
         <is>
-          <t>광고</t>
+          <t>제약</t>
         </is>
       </c>
       <c r="J124" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>한국, 신한</t>
         </is>
       </c>
       <c r="K124" s="6" t="inlineStr">
         <is>
-          <t>상장완료 (2026-03-06)</t>
+          <t>상장완료 (2026-03-20)</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="6" t="inlineStr">
         <is>
+          <t>2026-01-16</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>에스팀</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="D125" s="6" t="inlineStr">
+        <is>
+          <t>신규상장</t>
+        </is>
+      </c>
+      <c r="E125" s="6" t="inlineStr">
+        <is>
+          <t>FY24</t>
+        </is>
+      </c>
+      <c r="F125" s="7" t="inlineStr">
+        <is>
+          <t>35,574</t>
+        </is>
+      </c>
+      <c r="G125" s="7" t="inlineStr">
+        <is>
+          <t>1,372</t>
+        </is>
+      </c>
+      <c r="H125" s="7" t="inlineStr">
+        <is>
+          <t>12,331</t>
+        </is>
+      </c>
+      <c r="I125" s="6" t="inlineStr">
+        <is>
+          <t>광고</t>
+        </is>
+      </c>
+      <c r="J125" s="6" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="K125" s="6" t="inlineStr">
+        <is>
+          <t>상장완료 (2026-03-06)</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="6" t="inlineStr">
+        <is>
           <t>2026-01-12</t>
         </is>
       </c>
-      <c r="B125" s="6" t="inlineStr">
+      <c r="B126" s="6" t="inlineStr">
         <is>
           <t>케이뱅크</t>
         </is>
       </c>
-      <c r="C125" s="6" t="inlineStr">
+      <c r="C126" s="6" t="inlineStr">
         <is>
           <t>유가</t>
         </is>
       </c>
-      <c r="D125" s="6" t="inlineStr">
+      <c r="D126" s="6" t="inlineStr">
         <is>
           <t>신규상장</t>
         </is>
       </c>
-      <c r="E125" s="6" t="inlineStr">
+      <c r="E126" s="6" t="inlineStr">
         <is>
           <t>FY24</t>
         </is>
       </c>
-      <c r="F125" s="7" t="inlineStr">
+      <c r="F126" s="7" t="inlineStr">
         <is>
           <t>1,228,501</t>
         </is>
       </c>
-      <c r="G125" s="7" t="inlineStr">
+      <c r="G126" s="7" t="inlineStr">
         <is>
           <t>128,053</t>
         </is>
       </c>
-      <c r="H125" s="7" t="inlineStr">
+      <c r="H126" s="7" t="inlineStr">
         <is>
           <t>1,995,845</t>
         </is>
       </c>
-      <c r="I125" s="6" t="inlineStr">
+      <c r="I126" s="6" t="inlineStr">
         <is>
           <t>은행</t>
         </is>
       </c>
-      <c r="J125" s="6" t="inlineStr">
+      <c r="J126" s="6" t="inlineStr">
         <is>
           <t>NH, 삼성</t>
         </is>
       </c>
-      <c r="K125" s="6" t="inlineStr">
+      <c r="K126" s="6" t="inlineStr">
         <is>
           <t>상장완료 (2026-03-05)</t>
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="3" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="3" t="inlineStr">
         <is>
           <t>■ 철회·미승인  (20건)</t>
         </is>
       </c>
-      <c r="B127" s="4" t="n"/>
-      <c r="C127" s="4" t="n"/>
-      <c r="D127" s="4" t="n"/>
-      <c r="E127" s="4" t="n"/>
-      <c r="F127" s="4" t="n"/>
-      <c r="G127" s="4" t="n"/>
-      <c r="H127" s="4" t="n"/>
-      <c r="I127" s="4" t="n"/>
-      <c r="J127" s="4" t="n"/>
-      <c r="K127" s="4" t="n"/>
-    </row>
-    <row r="128">
-      <c r="A128" s="5" t="inlineStr">
+      <c r="B128" s="4" t="n"/>
+      <c r="C128" s="4" t="n"/>
+      <c r="D128" s="4" t="n"/>
+      <c r="E128" s="4" t="n"/>
+      <c r="F128" s="4" t="n"/>
+      <c r="G128" s="4" t="n"/>
+      <c r="H128" s="4" t="n"/>
+      <c r="I128" s="4" t="n"/>
+      <c r="J128" s="4" t="n"/>
+      <c r="K128" s="4" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
         <is>
           <t>일자</t>
         </is>
       </c>
-      <c r="B128" s="5" t="inlineStr">
+      <c r="B129" s="5" t="inlineStr">
         <is>
           <t>회사명</t>
         </is>
       </c>
-      <c r="C128" s="5" t="inlineStr">
+      <c r="C129" s="5" t="inlineStr">
         <is>
           <t>시장</t>
         </is>
       </c>
-      <c r="D128" s="5" t="inlineStr">
+      <c r="D129" s="5" t="inlineStr">
         <is>
           <t>상장유형</t>
         </is>
       </c>
-      <c r="E128" s="5" t="inlineStr">
+      <c r="E129" s="5" t="inlineStr">
         <is>
           <t>기준연도</t>
         </is>
       </c>
-      <c r="F128" s="5" t="inlineStr">
+      <c r="F129" s="5" t="inlineStr">
         <is>
           <t>매출액</t>
         </is>
       </c>
-      <c r="G128" s="5" t="inlineStr">
+      <c r="G129" s="5" t="inlineStr">
         <is>
           <t>순이익</t>
         </is>
       </c>
-      <c r="H128" s="5" t="inlineStr">
+      <c r="H129" s="5" t="inlineStr">
         <is>
           <t>자기자본</t>
         </is>
       </c>
-      <c r="I128" s="5" t="inlineStr">
+      <c r="I129" s="5" t="inlineStr">
         <is>
           <t>업종</t>
         </is>
       </c>
-      <c r="J128" s="5" t="inlineStr">
+      <c r="J129" s="5" t="inlineStr">
         <is>
           <t>대표주관사</t>
         </is>
       </c>
-      <c r="K128" s="5" t="inlineStr">
+      <c r="K129" s="5" t="inlineStr">
         <is>
           <t>현황</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="6" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="B129" s="6" t="inlineStr">
-        <is>
-          <t>에스텍시스템</t>
-        </is>
-      </c>
-      <c r="C129" s="6" t="inlineStr">
-        <is>
-          <t>유가</t>
-        </is>
-      </c>
-      <c r="D129" s="6" t="inlineStr">
-        <is>
-          <t>신규상장</t>
-        </is>
-      </c>
-      <c r="E129" s="6" t="inlineStr">
-        <is>
-          <t>FY25</t>
-        </is>
-      </c>
-      <c r="F129" s="7" t="inlineStr">
-        <is>
-          <t>975,224</t>
-        </is>
-      </c>
-      <c r="G129" s="7" t="inlineStr">
-        <is>
-          <t>24,647</t>
-        </is>
-      </c>
-      <c r="H129" s="7" t="inlineStr">
-        <is>
-          <t>237,182</t>
-        </is>
-      </c>
-      <c r="I129" s="6" t="inlineStr">
-        <is>
-          <t>경비, 경호 및 탐정업</t>
-        </is>
-      </c>
-      <c r="J129" s="6" t="inlineStr">
-        <is>
-          <t>미래</t>
-        </is>
-      </c>
-      <c r="K129" s="6" t="inlineStr">
-        <is>
-          <t>심사 철회</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="6" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B130" s="6" t="inlineStr">
         <is>
-          <t>넥스트에어로스페이스</t>
+          <t>에스텍시스템</t>
         </is>
       </c>
       <c r="C130" s="6" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>유가</t>
         </is>
       </c>
       <c r="D130" s="6" t="inlineStr">
@@ -7398,27 +7398,27 @@
       </c>
       <c r="F130" s="7" t="inlineStr">
         <is>
-          <t>12,084</t>
+          <t>975,224</t>
         </is>
       </c>
       <c r="G130" s="7" t="inlineStr">
         <is>
-          <t>-17,270</t>
+          <t>24,647</t>
         </is>
       </c>
       <c r="H130" s="7" t="inlineStr">
         <is>
-          <t>6,158</t>
+          <t>237,182</t>
         </is>
       </c>
       <c r="I130" s="6" t="inlineStr">
         <is>
-          <t>유인 항공기, 항공우주선 및 보조장치 제조업</t>
+          <t>경비, 경호 및 탐정업</t>
         </is>
       </c>
       <c r="J130" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K130" s="6" t="inlineStr">
@@ -7430,12 +7430,12 @@
     <row r="131">
       <c r="A131" s="6" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B131" s="6" t="inlineStr">
         <is>
-          <t>텔레픽스</t>
+          <t>넥스트에어로스페이스</t>
         </is>
       </c>
       <c r="C131" s="6" t="inlineStr">
@@ -7455,27 +7455,27 @@
       </c>
       <c r="F131" s="7" t="inlineStr">
         <is>
-          <t>4,896</t>
+          <t>12,084</t>
         </is>
       </c>
       <c r="G131" s="7" t="inlineStr">
         <is>
-          <t>-16,214</t>
+          <t>-17,270</t>
         </is>
       </c>
       <c r="H131" s="7" t="inlineStr">
         <is>
-          <t>9,146</t>
+          <t>6,158</t>
         </is>
       </c>
       <c r="I131" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>유인 항공기, 항공우주선 및 보조장치 제조업</t>
         </is>
       </c>
       <c r="J131" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K131" s="6" t="inlineStr">
@@ -7487,12 +7487,12 @@
     <row r="132">
       <c r="A132" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B132" s="6" t="inlineStr">
         <is>
-          <t>씨엠디엘</t>
+          <t>텔레픽스</t>
         </is>
       </c>
       <c r="C132" s="6" t="inlineStr">
@@ -7502,37 +7502,37 @@
       </c>
       <c r="D132" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E132" s="6" t="inlineStr">
         <is>
-          <t>FY24</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="F132" s="7" t="inlineStr">
         <is>
-          <t>39,991</t>
+          <t>4,896</t>
         </is>
       </c>
       <c r="G132" s="7" t="inlineStr">
         <is>
-          <t>3,541</t>
+          <t>-16,214</t>
         </is>
       </c>
       <c r="H132" s="7" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>9,146</t>
         </is>
       </c>
       <c r="I132" s="6" t="inlineStr">
         <is>
-          <t>기타 기초 유기 화학물질 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J132" s="6" t="inlineStr">
         <is>
-          <t>교보</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K132" s="6" t="inlineStr">
@@ -7544,12 +7544,12 @@
     <row r="133">
       <c r="A133" s="6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B133" s="6" t="inlineStr">
         <is>
-          <t>모비어스</t>
+          <t>씨엠디엘</t>
         </is>
       </c>
       <c r="C133" s="6" t="inlineStr">
@@ -7559,37 +7559,37 @@
       </c>
       <c r="D133" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E133" s="6" t="inlineStr">
         <is>
-          <t>FY25</t>
+          <t>FY24</t>
         </is>
       </c>
       <c r="F133" s="7" t="inlineStr">
         <is>
-          <t>31,989</t>
+          <t>39,991</t>
         </is>
       </c>
       <c r="G133" s="7" t="inlineStr">
         <is>
-          <t>-45,307</t>
+          <t>3,541</t>
         </is>
       </c>
       <c r="H133" s="7" t="inlineStr">
         <is>
-          <t>-96,707</t>
+          <t>503</t>
         </is>
       </c>
       <c r="I133" s="6" t="inlineStr">
         <is>
-          <t>컴퓨터 프로그래밍, 시스템 통합 및 관리업</t>
+          <t>기타 기초 유기 화학물질 제조업</t>
         </is>
       </c>
       <c r="J133" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>교보</t>
         </is>
       </c>
       <c r="K133" s="6" t="inlineStr">
@@ -7601,12 +7601,12 @@
     <row r="134">
       <c r="A134" s="6" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B134" s="6" t="inlineStr">
         <is>
-          <t>넥스트젠바이오</t>
+          <t>모비어스</t>
         </is>
       </c>
       <c r="C134" s="6" t="inlineStr">
@@ -7621,32 +7621,32 @@
       </c>
       <c r="E134" s="6" t="inlineStr">
         <is>
-          <t>FY24</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="F134" s="7" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>31,989</t>
         </is>
       </c>
       <c r="G134" s="7" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>-45,307</t>
         </is>
       </c>
       <c r="H134" s="7" t="inlineStr">
         <is>
-          <t>4,792</t>
+          <t>-96,707</t>
         </is>
       </c>
       <c r="I134" s="6" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>컴퓨터 프로그래밍, 시스템 통합 및 관리업</t>
         </is>
       </c>
       <c r="J134" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K134" s="6" t="inlineStr">
@@ -7658,12 +7658,12 @@
     <row r="135">
       <c r="A135" s="6" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="B135" s="6" t="inlineStr">
         <is>
-          <t>파워큐브세미</t>
+          <t>넥스트젠바이오</t>
         </is>
       </c>
       <c r="C135" s="6" t="inlineStr">
@@ -7678,32 +7678,32 @@
       </c>
       <c r="E135" s="6" t="inlineStr">
         <is>
-          <t>FY25</t>
+          <t>FY24</t>
         </is>
       </c>
       <c r="F135" s="7" t="inlineStr">
         <is>
-          <t>10,341</t>
+          <t>100</t>
         </is>
       </c>
       <c r="G135" s="7" t="inlineStr">
         <is>
-          <t>-10,837</t>
+          <t>69</t>
         </is>
       </c>
       <c r="H135" s="7" t="inlineStr">
         <is>
-          <t>841</t>
+          <t>4,792</t>
         </is>
       </c>
       <c r="I135" s="6" t="inlineStr">
         <is>
-          <t>반도체 제조업</t>
+          <t>자연과학 및 공학 연구개발업</t>
         </is>
       </c>
       <c r="J135" s="6" t="inlineStr">
         <is>
-          <t>하나, BNK</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K135" s="6" t="inlineStr">
@@ -7715,12 +7715,12 @@
     <row r="136">
       <c r="A136" s="6" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B136" s="6" t="inlineStr">
         <is>
-          <t>제이피이노베이션</t>
+          <t>파워큐브세미</t>
         </is>
       </c>
       <c r="C136" s="6" t="inlineStr">
@@ -7740,27 +7740,27 @@
       </c>
       <c r="F136" s="7" t="inlineStr">
         <is>
-          <t>56,324</t>
+          <t>10,341</t>
         </is>
       </c>
       <c r="G136" s="7" t="inlineStr">
         <is>
-          <t>5,588</t>
+          <t>-10,837</t>
         </is>
       </c>
       <c r="H136" s="7" t="inlineStr">
         <is>
-          <t>3,684</t>
+          <t>841</t>
         </is>
       </c>
       <c r="I136" s="6" t="inlineStr">
         <is>
-          <t>특수 목적용 기계 제조업</t>
+          <t>반도체 제조업</t>
         </is>
       </c>
       <c r="J136" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>하나, BNK</t>
         </is>
       </c>
       <c r="K136" s="6" t="inlineStr">
@@ -7772,12 +7772,12 @@
     <row r="137">
       <c r="A137" s="6" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-05-29</t>
         </is>
       </c>
       <c r="B137" s="6" t="inlineStr">
         <is>
-          <t>케이솔루션</t>
+          <t>제이피이노베이션</t>
         </is>
       </c>
       <c r="C137" s="6" t="inlineStr">
@@ -7787,7 +7787,7 @@
       </c>
       <c r="D137" s="6" t="inlineStr">
         <is>
-          <t>스팩 존속합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E137" s="6" t="inlineStr">
@@ -7797,27 +7797,27 @@
       </c>
       <c r="F137" s="7" t="inlineStr">
         <is>
-          <t>34,565</t>
+          <t>56,324</t>
         </is>
       </c>
       <c r="G137" s="7" t="inlineStr">
         <is>
-          <t>1,158</t>
+          <t>5,588</t>
         </is>
       </c>
       <c r="H137" s="7" t="inlineStr">
         <is>
-          <t>653</t>
+          <t>3,684</t>
         </is>
       </c>
       <c r="I137" s="6" t="inlineStr">
         <is>
-          <t>차체 및 특장차 제조업</t>
+          <t>특수 목적용 기계 제조업</t>
         </is>
       </c>
       <c r="J137" s="6" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K137" s="6" t="inlineStr">
@@ -7829,12 +7829,12 @@
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="B138" s="6" t="inlineStr">
         <is>
-          <t>디토닉</t>
+          <t>케이솔루션</t>
         </is>
       </c>
       <c r="C138" s="6" t="inlineStr">
@@ -7844,37 +7844,37 @@
       </c>
       <c r="D138" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 존속합병</t>
         </is>
       </c>
       <c r="E138" s="6" t="inlineStr">
         <is>
-          <t>FY24</t>
+          <t>FY25</t>
         </is>
       </c>
       <c r="F138" s="7" t="inlineStr">
         <is>
-          <t>31,293</t>
+          <t>34,565</t>
         </is>
       </c>
       <c r="G138" s="7" t="inlineStr">
         <is>
-          <t>-1,633</t>
+          <t>1,158</t>
         </is>
       </c>
       <c r="H138" s="7" t="inlineStr">
         <is>
-          <t>-21,926</t>
+          <t>653</t>
         </is>
       </c>
       <c r="I138" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>차체 및 특장차 제조업</t>
         </is>
       </c>
       <c r="J138" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="K138" s="6" t="inlineStr">
@@ -7886,12 +7886,12 @@
     <row r="139">
       <c r="A139" s="6" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="B139" s="6" t="inlineStr">
         <is>
-          <t>에스케이팩</t>
+          <t>디토닉</t>
         </is>
       </c>
       <c r="C139" s="6" t="inlineStr">
@@ -7901,7 +7901,7 @@
       </c>
       <c r="D139" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E139" s="6" t="inlineStr">
@@ -7911,27 +7911,27 @@
       </c>
       <c r="F139" s="7" t="inlineStr">
         <is>
-          <t>27,310</t>
+          <t>31,293</t>
         </is>
       </c>
       <c r="G139" s="7" t="inlineStr">
         <is>
-          <t>2,257</t>
+          <t>-1,633</t>
         </is>
       </c>
       <c r="H139" s="7" t="inlineStr">
         <is>
-          <t>3,207</t>
+          <t>-21,926</t>
         </is>
       </c>
       <c r="I139" s="6" t="inlineStr">
         <is>
-          <t>용기 세척, 포장 및 충전기 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J139" s="6" t="inlineStr">
         <is>
-          <t>교보</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K139" s="6" t="inlineStr">
@@ -7943,12 +7943,12 @@
     <row r="140">
       <c r="A140" s="6" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="B140" s="6" t="inlineStr">
         <is>
-          <t>메타넷엑스</t>
+          <t>에스케이팩</t>
         </is>
       </c>
       <c r="C140" s="6" t="inlineStr">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="D140" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E140" s="6" t="inlineStr">
@@ -7968,27 +7968,27 @@
       </c>
       <c r="F140" s="7" t="inlineStr">
         <is>
-          <t>244,130</t>
+          <t>27,310</t>
         </is>
       </c>
       <c r="G140" s="7" t="inlineStr">
         <is>
-          <t>13,455</t>
+          <t>2,257</t>
         </is>
       </c>
       <c r="H140" s="7" t="inlineStr">
         <is>
-          <t>9,995</t>
+          <t>3,207</t>
         </is>
       </c>
       <c r="I140" s="6" t="inlineStr">
         <is>
-          <t>컴퓨터 프로그래밍, 시스템 통합 및 관리업</t>
+          <t>용기 세척, 포장 및 충전기 제조업</t>
         </is>
       </c>
       <c r="J140" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>교보</t>
         </is>
       </c>
       <c r="K140" s="6" t="inlineStr">
@@ -8000,12 +8000,12 @@
     <row r="141">
       <c r="A141" s="6" t="inlineStr">
         <is>
-          <t>2026-03-17</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B141" s="6" t="inlineStr">
         <is>
-          <t>무아스</t>
+          <t>메타넷엑스</t>
         </is>
       </c>
       <c r="C141" s="6" t="inlineStr">
@@ -8015,7 +8015,7 @@
       </c>
       <c r="D141" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E141" s="6" t="inlineStr">
@@ -8025,27 +8025,27 @@
       </c>
       <c r="F141" s="7" t="inlineStr">
         <is>
-          <t>41,813</t>
+          <t>244,130</t>
         </is>
       </c>
       <c r="G141" s="7" t="inlineStr">
         <is>
-          <t>3,903</t>
+          <t>13,455</t>
         </is>
       </c>
       <c r="H141" s="7" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>9,995</t>
         </is>
       </c>
       <c r="I141" s="6" t="inlineStr">
         <is>
-          <t>가정용 전기기기 제조업</t>
+          <t>컴퓨터 프로그래밍, 시스템 통합 및 관리업</t>
         </is>
       </c>
       <c r="J141" s="6" t="inlineStr">
         <is>
-          <t>신한</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K141" s="6" t="inlineStr">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="B142" s="6" t="inlineStr">
         <is>
-          <t>유빅스테라퓨틱스</t>
+          <t>무아스</t>
         </is>
       </c>
       <c r="C142" s="6" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="D142" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E142" s="6" t="inlineStr">
@@ -8082,27 +8082,27 @@
       </c>
       <c r="F142" s="7" t="inlineStr">
         <is>
-          <t>1,071</t>
+          <t>41,813</t>
         </is>
       </c>
       <c r="G142" s="7" t="inlineStr">
         <is>
-          <t>-15,145</t>
+          <t>3,903</t>
         </is>
       </c>
       <c r="H142" s="7" t="inlineStr">
         <is>
-          <t>5,489</t>
+          <t>532</t>
         </is>
       </c>
       <c r="I142" s="6" t="inlineStr">
         <is>
-          <t>자연과학 및 공학 연구개발업</t>
+          <t>가정용 전기기기 제조업</t>
         </is>
       </c>
       <c r="J142" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>신한</t>
         </is>
       </c>
       <c r="K142" s="6" t="inlineStr">
@@ -8114,12 +8114,12 @@
     <row r="143">
       <c r="A143" s="6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="B143" s="6" t="inlineStr">
         <is>
-          <t>코드잇</t>
+          <t>유빅스테라퓨틱스</t>
         </is>
       </c>
       <c r="C143" s="6" t="inlineStr">
@@ -8139,27 +8139,27 @@
       </c>
       <c r="F143" s="7" t="inlineStr">
         <is>
-          <t>30,747</t>
+          <t>1,071</t>
         </is>
       </c>
       <c r="G143" s="7" t="inlineStr">
         <is>
-          <t>6,652</t>
+          <t>-15,145</t>
         </is>
       </c>
       <c r="H143" s="7" t="inlineStr">
         <is>
-          <t>2,403</t>
+          <t>5,489</t>
         </is>
       </c>
       <c r="I143" s="6" t="inlineStr">
         <is>
-          <t>교육지원 서비스업</t>
+          <t>자연과학 및 공학 연구개발업</t>
         </is>
       </c>
       <c r="J143" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K143" s="6" t="inlineStr">
@@ -8171,12 +8171,12 @@
     <row r="144">
       <c r="A144" s="6" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B144" s="6" t="inlineStr">
         <is>
-          <t>한컴인스페이스</t>
+          <t>코드잇</t>
         </is>
       </c>
       <c r="C144" s="6" t="inlineStr">
@@ -8196,44 +8196,44 @@
       </c>
       <c r="F144" s="7" t="inlineStr">
         <is>
-          <t>23,492</t>
+          <t>30,747</t>
         </is>
       </c>
       <c r="G144" s="7" t="inlineStr">
         <is>
-          <t>-3,104</t>
+          <t>6,652</t>
         </is>
       </c>
       <c r="H144" s="7" t="inlineStr">
         <is>
-          <t>5,815</t>
+          <t>2,403</t>
         </is>
       </c>
       <c r="I144" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>교육지원 서비스업</t>
         </is>
       </c>
       <c r="J144" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K144" s="6" t="inlineStr">
         <is>
-          <t>심사 미승인</t>
+          <t>심사 철회</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="6" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="B145" s="6" t="inlineStr">
         <is>
-          <t>크몽</t>
+          <t>한컴인스페이스</t>
         </is>
       </c>
       <c r="C145" s="6" t="inlineStr">
@@ -8253,44 +8253,44 @@
       </c>
       <c r="F145" s="7" t="inlineStr">
         <is>
-          <t>48,572</t>
+          <t>23,492</t>
         </is>
       </c>
       <c r="G145" s="7" t="inlineStr">
         <is>
-          <t>3,988</t>
+          <t>-3,104</t>
         </is>
       </c>
       <c r="H145" s="7" t="inlineStr">
         <is>
-          <t>4,930</t>
+          <t>5,815</t>
         </is>
       </c>
       <c r="I145" s="6" t="inlineStr">
         <is>
-          <t>기타 정보 서비스업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J145" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K145" s="6" t="inlineStr">
         <is>
-          <t>심사 철회</t>
+          <t>심사 미승인</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="6" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="B146" s="6" t="inlineStr">
         <is>
-          <t>한화플러스제6호스팩</t>
+          <t>크몽</t>
         </is>
       </c>
       <c r="C146" s="6" t="inlineStr">
@@ -8310,27 +8310,27 @@
       </c>
       <c r="F146" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>48,572</t>
         </is>
       </c>
       <c r="G146" s="7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3,988</t>
         </is>
       </c>
       <c r="H146" s="7" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4,930</t>
         </is>
       </c>
       <c r="I146" s="6" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>기타 정보 서비스업</t>
         </is>
       </c>
       <c r="J146" s="6" t="inlineStr">
         <is>
-          <t>한화</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="K146" s="6" t="inlineStr">
@@ -8342,17 +8342,17 @@
     <row r="147">
       <c r="A147" s="6" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="B147" s="6" t="inlineStr">
         <is>
-          <t>에식스솔루션즈</t>
+          <t>한화플러스제6호스팩</t>
         </is>
       </c>
       <c r="C147" s="6" t="inlineStr">
         <is>
-          <t>유가</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D147" s="6" t="inlineStr">
@@ -8367,27 +8367,27 @@
       </c>
       <c r="F147" s="7" t="inlineStr">
         <is>
-          <t>2,461</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G147" s="7" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H147" s="7" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>41</t>
         </is>
       </c>
       <c r="I147" s="6" t="inlineStr">
         <is>
-          <t>절연선 및 케이블 제조업</t>
+          <t>기타 금융업</t>
         </is>
       </c>
       <c r="J147" s="6" t="inlineStr">
         <is>
-          <t>한국, 미래</t>
+          <t>한화</t>
         </is>
       </c>
       <c r="K147" s="6" t="inlineStr">
@@ -8399,55 +8399,112 @@
     <row r="148">
       <c r="A148" s="6" t="inlineStr">
         <is>
+          <t>2026-01-26</t>
+        </is>
+      </c>
+      <c r="B148" s="6" t="inlineStr">
+        <is>
+          <t>에식스솔루션즈</t>
+        </is>
+      </c>
+      <c r="C148" s="6" t="inlineStr">
+        <is>
+          <t>유가</t>
+        </is>
+      </c>
+      <c r="D148" s="6" t="inlineStr">
+        <is>
+          <t>신규상장</t>
+        </is>
+      </c>
+      <c r="E148" s="6" t="inlineStr">
+        <is>
+          <t>FY24</t>
+        </is>
+      </c>
+      <c r="F148" s="7" t="inlineStr">
+        <is>
+          <t>2,461</t>
+        </is>
+      </c>
+      <c r="G148" s="7" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="H148" s="7" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="I148" s="6" t="inlineStr">
+        <is>
+          <t>절연선 및 케이블 제조업</t>
+        </is>
+      </c>
+      <c r="J148" s="6" t="inlineStr">
+        <is>
+          <t>한국, 미래</t>
+        </is>
+      </c>
+      <c r="K148" s="6" t="inlineStr">
+        <is>
+          <t>심사 철회</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="6" t="inlineStr">
+        <is>
           <t>2026-01-23</t>
         </is>
       </c>
-      <c r="B148" s="6" t="inlineStr">
+      <c r="B149" s="6" t="inlineStr">
         <is>
           <t>에코크레이션</t>
         </is>
       </c>
-      <c r="C148" s="6" t="inlineStr">
+      <c r="C149" s="6" t="inlineStr">
         <is>
           <t>코스닥</t>
         </is>
       </c>
-      <c r="D148" s="6" t="inlineStr">
+      <c r="D149" s="6" t="inlineStr">
         <is>
           <t>신규상장</t>
         </is>
       </c>
-      <c r="E148" s="6" t="inlineStr">
+      <c r="E149" s="6" t="inlineStr">
         <is>
           <t>FY24</t>
         </is>
       </c>
-      <c r="F148" s="7" t="inlineStr">
+      <c r="F149" s="7" t="inlineStr">
         <is>
           <t>18,544</t>
         </is>
       </c>
-      <c r="G148" s="7" t="inlineStr">
+      <c r="G149" s="7" t="inlineStr">
         <is>
           <t>-15,634</t>
         </is>
       </c>
-      <c r="H148" s="7" t="inlineStr">
+      <c r="H149" s="7" t="inlineStr">
         <is>
           <t>4,550</t>
         </is>
       </c>
-      <c r="I148" s="6" t="inlineStr">
+      <c r="I149" s="6" t="inlineStr">
         <is>
           <t>일반 목적용 기계 제조업</t>
         </is>
       </c>
-      <c r="J148" s="6" t="inlineStr">
+      <c r="J149" s="6" t="inlineStr">
         <is>
           <t>키움</t>
         </is>
       </c>
-      <c r="K148" s="6" t="inlineStr">
+      <c r="K149" s="6" t="inlineStr">
         <is>
           <t>심사 철회</t>
         </is>
@@ -8464,7 +8521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R99"/>
+  <dimension ref="A1:R101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -12546,7 +12603,7 @@
     <row r="56" ht="22" customHeight="1">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>■ 공모 진행 (예심 승인법인)  (39건)</t>
+          <t>■ 공모 진행 (예심 승인법인)  (41건)</t>
         </is>
       </c>
       <c r="B56" s="4" t="n"/>
@@ -12838,7 +12895,11 @@
           <t>10-07~10-08</t>
         </is>
       </c>
-      <c r="K60" s="6" t="inlineStr"/>
+      <c r="K60" s="6" t="inlineStr">
+        <is>
+          <t>810.15</t>
+        </is>
+      </c>
       <c r="L60" s="6" t="inlineStr"/>
       <c r="M60" s="6" t="inlineStr"/>
       <c r="N60" s="6" t="inlineStr">
@@ -12863,7 +12924,7 @@
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
-          <t>발행조건확정</t>
+          <t>청약완료·상장대기</t>
         </is>
       </c>
     </row>
@@ -14542,7 +14603,7 @@
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>디티에스</t>
+          <t>(주)태석광학</t>
         </is>
       </c>
       <c r="B87" s="18" t="inlineStr">
@@ -14599,14 +14660,14 @@
       </c>
       <c r="R87" s="6" t="inlineStr">
         <is>
-          <t>신고서 대기</t>
+          <t>corp_code 미확보(수동확인)</t>
         </is>
       </c>
     </row>
     <row r="88" ht="30" customHeight="1">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>에이엔에이치스트럭쳐</t>
+          <t>디티에스</t>
         </is>
       </c>
       <c r="B88" s="18" t="inlineStr">
@@ -14670,7 +14731,7 @@
     <row r="89" ht="30" customHeight="1">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>이에스티</t>
+          <t>에이엔에이치스트럭쳐</t>
         </is>
       </c>
       <c r="B89" s="18" t="inlineStr">
@@ -14734,7 +14795,7 @@
     <row r="90" ht="30" customHeight="1">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>우리투자제1호스팩</t>
+          <t>이에스티</t>
         </is>
       </c>
       <c r="B90" s="18" t="inlineStr">
@@ -14798,7 +14859,7 @@
     <row r="91" ht="30" customHeight="1">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>마더스제약</t>
+          <t>우리투자제1호스팩</t>
         </is>
       </c>
       <c r="B91" s="18" t="inlineStr">
@@ -14862,7 +14923,7 @@
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>케이티이</t>
+          <t>마더스제약</t>
         </is>
       </c>
       <c r="B92" s="18" t="inlineStr">
@@ -14926,7 +14987,7 @@
     <row r="93" ht="30" customHeight="1">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>씨앤엠</t>
+          <t>케이티이</t>
         </is>
       </c>
       <c r="B93" s="18" t="inlineStr">
@@ -14990,7 +15051,7 @@
     <row r="94" ht="30" customHeight="1">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>제이앤티지</t>
+          <t>씨앤엠</t>
         </is>
       </c>
       <c r="B94" s="18" t="inlineStr">
@@ -15054,7 +15115,7 @@
     <row r="95" ht="30" customHeight="1">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>데스틴파워</t>
+          <t>제이앤티지</t>
         </is>
       </c>
       <c r="B95" s="18" t="inlineStr">
@@ -15115,22 +15176,150 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="20" t="inlineStr">
-        <is>
-          <t>※ 상장 완료 = KIND 신규상장 페이지 기준(스팩합병 포함) · 스팩 공모상장은 밴드·밸류에이션 등 해당없음(공모가 2,000원 고정).</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="20" t="inlineStr">
-        <is>
-          <t>※ 기재정정 신고서 내 정정 전·후 병존 → 자동수집은 "정정 후" 값만 취함.</t>
+    <row r="96" ht="30" customHeight="1">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>데스틴파워</t>
+        </is>
+      </c>
+      <c r="B96" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="C96" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="D96" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="E96" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="F96" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr"/>
+      <c r="H96" s="6" t="inlineStr"/>
+      <c r="I96" s="6" t="inlineStr"/>
+      <c r="J96" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="K96" s="6" t="inlineStr"/>
+      <c r="L96" s="6" t="inlineStr"/>
+      <c r="M96" s="6" t="inlineStr"/>
+      <c r="N96" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="O96" s="6" t="inlineStr"/>
+      <c r="P96" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="Q96" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="R96" s="6" t="inlineStr">
+        <is>
+          <t>신고서 대기</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="30" customHeight="1">
+      <c r="A97" s="6" t="inlineStr">
+        <is>
+          <t>엘리스</t>
+        </is>
+      </c>
+      <c r="B97" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="C97" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="D97" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="E97" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="F97" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="G97" s="6" t="inlineStr"/>
+      <c r="H97" s="6" t="inlineStr"/>
+      <c r="I97" s="6" t="inlineStr"/>
+      <c r="J97" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="K97" s="6" t="inlineStr"/>
+      <c r="L97" s="6" t="inlineStr"/>
+      <c r="M97" s="6" t="inlineStr"/>
+      <c r="N97" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="O97" s="6" t="inlineStr"/>
+      <c r="P97" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="Q97" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="R97" s="6" t="inlineStr">
+        <is>
+          <t>신고서 대기</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="20" t="inlineStr">
+        <is>
+          <t>※ 상장 완료 = KIND 신규상장 페이지 기준(스팩합병 포함) · 스팩 공모상장은 밴드·밸류에이션 등 해당없음(공모가 2,000원 고정).</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="20" t="inlineStr">
+        <is>
+          <t>※ 기재정정 신고서 내 정정 전·후 병존 → 자동수집은 "정정 후" 값만 취함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="20" t="inlineStr">
         <is>
           <t>※ 청약경쟁률=일반투자자 청약수량÷최종배정수량 · "MM-DD~"는 종료일 자동수집 예정.</t>
         </is>
@@ -15315,7 +15504,7 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" s="6" t="n">
         <v>4</v>
@@ -15387,7 +15576,7 @@
         <v>10</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>1</v>
@@ -15433,7 +15622,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" s="6" t="n">
         <v>1</v>

--- a/IPO_analysis.xlsx
+++ b/IPO_analysis.xlsx
@@ -618,7 +618,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>기준일 2026-10-13 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
+          <t>기준일 2026-10-14 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
         </is>
       </c>
     </row>
@@ -13003,71 +13003,79 @@
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>티앤이코리아</t>
+          <t>에스케이증권제14호기업인수목적</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>10-07~10-14</t>
-        </is>
-      </c>
-      <c r="C62" s="6" t="inlineStr">
-        <is>
-          <t>12,600~15,300</t>
+          <t>10-12~10-13</t>
+        </is>
+      </c>
+      <c r="C62" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>2,400,000</t>
+          <t>6,500,000</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>30,240,000,000</t>
-        </is>
-      </c>
-      <c r="F62" s="6" t="inlineStr">
-        <is>
-          <t>19.48배 (PER)</t>
-        </is>
-      </c>
-      <c r="G62" s="6" t="inlineStr"/>
-      <c r="H62" s="6" t="inlineStr"/>
-      <c r="I62" s="6" t="inlineStr"/>
+          <t>13,000,000,000</t>
+        </is>
+      </c>
+      <c r="F62" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="H62" s="6" t="n">
+        <v>1228.38</v>
+      </c>
+      <c r="I62" s="6" t="n">
+        <v>1945</v>
+      </c>
       <c r="J62" s="6" t="inlineStr">
         <is>
-          <t>10-20~10-21</t>
+          <t>10-15~10-16</t>
         </is>
       </c>
       <c r="K62" s="6" t="inlineStr"/>
       <c r="L62" s="6" t="inlineStr"/>
       <c r="M62" s="6" t="inlineStr"/>
-      <c r="N62" s="6" t="inlineStr">
-        <is>
-          <t>신한투자증권</t>
+      <c r="N62" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="O62" s="6" t="inlineStr"/>
-      <c r="P62" s="7" t="inlineStr">
-        <is>
-          <t>1,245,888,000</t>
+      <c r="P62" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="Q62" s="6" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="R62" s="6" t="inlineStr">
         <is>
-          <t>정정</t>
+          <t>발행조건확정</t>
         </is>
       </c>
     </row>
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>유캐스트</t>
+          <t>티앤이코리아</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
@@ -13077,22 +13085,22 @@
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>21,000~26,000</t>
+          <t>12,600~15,300</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>800,000</t>
+          <t>2,400,000</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>16,800,000,000</t>
+          <t>30,240,000,000</t>
         </is>
       </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>17.97배 (PER)</t>
+          <t>19.48배 (PER)</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr"/>
@@ -13100,7 +13108,7 @@
       <c r="I63" s="6" t="inlineStr"/>
       <c r="J63" s="6" t="inlineStr">
         <is>
-          <t>10-19~10-20</t>
+          <t>10-20~10-21</t>
         </is>
       </c>
       <c r="K63" s="6" t="inlineStr"/>
@@ -13108,18 +13116,18 @@
       <c r="M63" s="6" t="inlineStr"/>
       <c r="N63" s="6" t="inlineStr">
         <is>
-          <t>유진투자증권</t>
+          <t>신한투자증권</t>
         </is>
       </c>
       <c r="O63" s="6" t="inlineStr"/>
       <c r="P63" s="7" t="inlineStr">
         <is>
-          <t>1,181,280,000</t>
+          <t>1,245,888,000</t>
         </is>
       </c>
       <c r="Q63" s="6" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="R63" s="6" t="inlineStr">
@@ -13131,32 +13139,32 @@
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>에스케이증권제14호기업인수목적</t>
+          <t>유캐스트</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>10-12~10-13</t>
-        </is>
-      </c>
-      <c r="C64" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>10-07~10-14</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>21,000~26,000</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>6,500,000</t>
+          <t>800,000</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>13,000,000,000</t>
-        </is>
-      </c>
-      <c r="F64" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>16,800,000,000</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>17.97배 (PER)</t>
         </is>
       </c>
       <c r="G64" s="6" t="inlineStr"/>
@@ -13164,26 +13172,26 @@
       <c r="I64" s="6" t="inlineStr"/>
       <c r="J64" s="6" t="inlineStr">
         <is>
-          <t>10-15~10-16</t>
+          <t>10-19~10-20</t>
         </is>
       </c>
       <c r="K64" s="6" t="inlineStr"/>
       <c r="L64" s="6" t="inlineStr"/>
       <c r="M64" s="6" t="inlineStr"/>
-      <c r="N64" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="N64" s="6" t="inlineStr">
+        <is>
+          <t>유진투자증권</t>
         </is>
       </c>
       <c r="O64" s="6" t="inlineStr"/>
-      <c r="P64" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P64" s="7" t="inlineStr">
+        <is>
+          <t>1,181,280,000</t>
         </is>
       </c>
       <c r="Q64" s="6" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="R64" s="6" t="inlineStr">

--- a/IPO_analysis.xlsx
+++ b/IPO_analysis.xlsx
@@ -618,14 +618,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>기준일 2026-10-14 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
+          <t>기준일 2026-10-15 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>■ 심사 신청(진행중)  (38건)</t>
+          <t>■ 심사 신청(진행중)  (34건)</t>
         </is>
       </c>
       <c r="B4" s="4" t="n"/>
@@ -1473,12 +1473,12 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>이나인페이</t>
+          <t>어피닛</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -1498,27 +1498,27 @@
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>64,711</t>
+          <t>169,126</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
         <is>
-          <t>19,586</t>
+          <t>26,009</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
         <is>
-          <t>79,855</t>
+          <t>61,466</t>
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>기타 금융업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>미래, 하나</t>
         </is>
       </c>
       <c r="K20" s="6" t="inlineStr">
@@ -1530,12 +1530,12 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>어피닛</t>
+          <t>라이드플럭스</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>169,126</t>
+          <t>4,044</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
         <is>
-          <t>26,009</t>
+          <t>-31,423</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
         <is>
-          <t>61,466</t>
+          <t>-77,243</t>
         </is>
       </c>
       <c r="I21" s="6" t="inlineStr">
@@ -1575,7 +1575,7 @@
       </c>
       <c r="J21" s="6" t="inlineStr">
         <is>
-          <t>미래, 하나</t>
+          <t>주식회사 우리투자증권, 한국</t>
         </is>
       </c>
       <c r="K21" s="6" t="inlineStr">
@@ -1587,12 +1587,12 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>라이드플럭스</t>
+          <t>신영스팩12호</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1610,29 +1610,17 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>4,044</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>-31,423</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>-77,243</t>
-        </is>
-      </c>
+      <c r="F22" s="7" t="inlineStr"/>
+      <c r="G22" s="7" t="inlineStr"/>
+      <c r="H22" s="7" t="inlineStr"/>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>금융 지원 서비스업</t>
         </is>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>주식회사 우리투자증권, 한국</t>
+          <t>신영</t>
         </is>
       </c>
       <c r="K22" s="6" t="inlineStr">
@@ -1644,12 +1632,12 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>신영스팩12호</t>
+          <t>범한메카텍</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -1667,17 +1655,29 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr"/>
-      <c r="G23" s="7" t="inlineStr"/>
-      <c r="H23" s="7" t="inlineStr"/>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>339,209</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="inlineStr">
+        <is>
+          <t>-18,141</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>265,955</t>
+        </is>
+      </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>신영</t>
+          <t>유진, NH</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
@@ -1689,12 +1689,12 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>범한메카텍</t>
+          <t>유림테크</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -1714,27 +1714,27 @@
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>339,209</t>
+          <t>102,586</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>-18,141</t>
+          <t>-18,278</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>265,955</t>
+          <t>-4,832</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
+          <t>자동차 신품 부품 제조업</t>
         </is>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>유진, NH</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K24" s="6" t="inlineStr">
@@ -1746,17 +1746,17 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>유림테크</t>
+          <t>에스에프씨</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>유가</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -1771,27 +1771,27 @@
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>102,586</t>
+          <t>160,792</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>-18,278</t>
+          <t>25,509</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>-4,832</t>
+          <t>243,562</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>자동차 신품 부품 제조업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>미래, 한국</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
@@ -1803,12 +1803,12 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>이노보테라퓨틱스</t>
+          <t>에버온</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -1828,27 +1828,27 @@
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>65,225</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>-5,429</t>
+          <t>-3,606</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>-53,200</t>
+          <t>54,955</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>의약품 제조업</t>
+          <t>전기업</t>
         </is>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr">
@@ -1860,17 +1860,17 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>에스에프씨</t>
+          <t>엠디에스코리아</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>유가</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
@@ -1885,27 +1885,27 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>160,792</t>
+          <t>97,972</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>25,509</t>
+          <t>6,512</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>243,562</t>
+          <t>53,818</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>기타 식품 제조업</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>미래, 한국</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
@@ -1917,12 +1917,12 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>에버온</t>
+          <t>동승</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -1942,27 +1942,27 @@
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>65,225</t>
+          <t>78,625</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>-3,606</t>
+          <t>14,525</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>54,955</t>
+          <t>5,438</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>전기업</t>
+          <t>부동산 임대 및 공급업</t>
         </is>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K28" s="6" t="inlineStr">
@@ -1974,12 +1974,12 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>씨아이에스케미칼</t>
+          <t>에프엠더블유</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -1999,27 +1999,27 @@
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>15,985</t>
+          <t>30,282</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>-11,440</t>
+          <t>4,762</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>23,706</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>기초 화학물질 제조업</t>
+          <t>기타 식품 제조업</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>유진</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>엠디에스코리아</t>
+          <t>소노인터내셔널</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>유가</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -2056,27 +2056,27 @@
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>97,972</t>
+          <t>2,093,051</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>6,512</t>
+          <t>-148,064</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>53,818</t>
+          <t>852,372</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>기타 식품 제조업</t>
+          <t>일반 및 생활 숙박시설 운영업</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>대신, 미래</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
@@ -2088,12 +2088,12 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>동승</t>
+          <t>싸이몬</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -2113,27 +2113,27 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>78,625</t>
+          <t>48,695</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>14,525</t>
+          <t>15,714</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>5,438</t>
+          <t>61,761</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>부동산 임대 및 공급업</t>
+          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K31" s="6" t="inlineStr">
@@ -2145,12 +2145,12 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>에프엠더블유</t>
+          <t>바이다</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -2170,27 +2170,27 @@
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>30,282</t>
+          <t>14,432</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>4,762</t>
+          <t>-3,951</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>15,108</t>
         </is>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>기타 식품 제조업</t>
+          <t>전자부품 제조업</t>
         </is>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>유진</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K32" s="6" t="inlineStr">
@@ -2202,17 +2202,17 @@
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>소노인터내셔널</t>
+          <t>아이알큐더스</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>유가</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
@@ -2227,27 +2227,27 @@
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>2,093,051</t>
+          <t>10,231</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>-148,064</t>
+          <t>-986</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>852,372</t>
+          <t>1,800</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>일반 및 생활 숙박시설 운영업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>대신, 미래</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
@@ -2259,12 +2259,12 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>싸이몬</t>
+          <t>씨엔티테크</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -2284,27 +2284,27 @@
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>48,695</t>
+          <t>27,015</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>15,714</t>
+          <t>3,987</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>61,761</t>
+          <t>2,613</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>한화, 하나</t>
         </is>
       </c>
       <c r="K34" s="6" t="inlineStr">
@@ -2316,12 +2316,12 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>바이다</t>
+          <t>삼홍아크튜리온</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
@@ -2341,27 +2341,27 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>14,432</t>
+          <t>26,162</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>-3,951</t>
+          <t>-10,314</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>15,108</t>
+          <t>6,369</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>전자부품 제조업</t>
+          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
         </is>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>삼성, 미래</t>
         </is>
       </c>
       <c r="K35" s="6" t="inlineStr">
@@ -2373,12 +2373,12 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>아이알큐더스</t>
+          <t>비앤비코리아</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
@@ -2398,27 +2398,27 @@
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>10,231</t>
+          <t>141,169</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>-986</t>
+          <t>21,406</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>1,800</t>
+          <t>43,932</t>
         </is>
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K36" s="6" t="inlineStr">
@@ -2430,12 +2430,12 @@
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>씨엔티테크</t>
+          <t>오토핸즈</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
@@ -2455,27 +2455,27 @@
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>27,015</t>
+          <t>238,564</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>3,987</t>
+          <t>6,047</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>2,613</t>
+          <t>6,129</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>자동차 판매업</t>
         </is>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>한화, 하나</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
@@ -2487,12 +2487,12 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>2026-05-29</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>인터엑스</t>
+          <t>아이벡스메디칼시스템즈</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -2512,27 +2512,27 @@
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>8,645</t>
+          <t>15,282</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>-20,272</t>
+          <t>-7,227</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>4,530</t>
+          <t>744</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K38" s="6" t="inlineStr">
@@ -2544,12 +2544,12 @@
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>삼홍아크튜리온</t>
+          <t>피지티</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
@@ -2569,27 +2569,27 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>26,162</t>
+          <t>40,141</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
         <is>
-          <t>-10,314</t>
+          <t>-69,722</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr">
         <is>
-          <t>6,369</t>
+          <t>6,029</t>
         </is>
       </c>
       <c r="I39" s="6" t="inlineStr">
         <is>
-          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>삼성, 미래</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr">
@@ -2598,186 +2598,89 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>비앤비코리아</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>코스닥</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="inlineStr">
-        <is>
-          <t>신규상장</t>
-        </is>
-      </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>FY25</t>
-        </is>
-      </c>
-      <c r="F40" s="7" t="inlineStr">
-        <is>
-          <t>141,169</t>
-        </is>
-      </c>
-      <c r="G40" s="7" t="inlineStr">
-        <is>
-          <t>21,406</t>
-        </is>
-      </c>
-      <c r="H40" s="7" t="inlineStr">
-        <is>
-          <t>43,932</t>
-        </is>
-      </c>
-      <c r="I40" s="6" t="inlineStr">
-        <is>
-          <t>기타 화학제품 제조업</t>
-        </is>
-      </c>
-      <c r="J40" s="6" t="inlineStr">
-        <is>
-          <t>미래</t>
-        </is>
-      </c>
-      <c r="K40" s="6" t="inlineStr">
-        <is>
-          <t>예심 진행중</t>
-        </is>
-      </c>
-    </row>
     <row r="41">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>오토핸즈</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>코스닥</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>스팩 소멸합병</t>
-        </is>
-      </c>
-      <c r="E41" s="6" t="inlineStr">
-        <is>
-          <t>FY25</t>
-        </is>
-      </c>
-      <c r="F41" s="7" t="inlineStr">
-        <is>
-          <t>238,564</t>
-        </is>
-      </c>
-      <c r="G41" s="7" t="inlineStr">
-        <is>
-          <t>6,047</t>
-        </is>
-      </c>
-      <c r="H41" s="7" t="inlineStr">
-        <is>
-          <t>6,129</t>
-        </is>
-      </c>
-      <c r="I41" s="6" t="inlineStr">
-        <is>
-          <t>자동차 판매업</t>
-        </is>
-      </c>
-      <c r="J41" s="6" t="inlineStr">
-        <is>
-          <t>미래</t>
-        </is>
-      </c>
-      <c r="K41" s="6" t="inlineStr">
-        <is>
-          <t>예심 진행중</t>
-        </is>
-      </c>
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>■ 심사 승인  (84건)</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="n"/>
+      <c r="C41" s="4" t="n"/>
+      <c r="D41" s="4" t="n"/>
+      <c r="E41" s="4" t="n"/>
+      <c r="F41" s="4" t="n"/>
+      <c r="G41" s="4" t="n"/>
+      <c r="H41" s="4" t="n"/>
+      <c r="I41" s="4" t="n"/>
+      <c r="J41" s="4" t="n"/>
+      <c r="K41" s="4" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>아이벡스메디칼시스템즈</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>코스닥</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>신규상장</t>
-        </is>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
-        <is>
-          <t>FY25</t>
-        </is>
-      </c>
-      <c r="F42" s="7" t="inlineStr">
-        <is>
-          <t>15,282</t>
-        </is>
-      </c>
-      <c r="G42" s="7" t="inlineStr">
-        <is>
-          <t>-7,227</t>
-        </is>
-      </c>
-      <c r="H42" s="7" t="inlineStr">
-        <is>
-          <t>744</t>
-        </is>
-      </c>
-      <c r="I42" s="6" t="inlineStr">
-        <is>
-          <t>의료용 기기 제조업</t>
-        </is>
-      </c>
-      <c r="J42" s="6" t="inlineStr">
-        <is>
-          <t>NH</t>
-        </is>
-      </c>
-      <c r="K42" s="6" t="inlineStr">
-        <is>
-          <t>예심 진행중</t>
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>일자</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>회사명</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>시장</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>상장유형</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>기준연도</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>자기자본</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>업종</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>대표주관사</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>현황</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>피지티</t>
+          <t>인터엑스</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -2797,22 +2700,22 @@
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>40,141</t>
+          <t>8,645</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>-69,722</t>
+          <t>-20,272</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>6,029</t>
+          <t>4,530</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J43" s="6" t="inlineStr">
@@ -2822,81 +2725,178 @@
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>예심 진행중</t>
+          <t>상장전</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>씨아이에스케미칼</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>신규상장</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
+        <is>
+          <t>FY25</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>15,985</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>-11,440</t>
+        </is>
+      </c>
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>23,706</t>
+        </is>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>기초 화학물질 제조업</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>KB</t>
+        </is>
+      </c>
+      <c r="K44" s="6" t="inlineStr">
+        <is>
+          <t>상장전</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>■ 심사 승인  (80건)</t>
-        </is>
-      </c>
-      <c r="B45" s="4" t="n"/>
-      <c r="C45" s="4" t="n"/>
-      <c r="D45" s="4" t="n"/>
-      <c r="E45" s="4" t="n"/>
-      <c r="F45" s="4" t="n"/>
-      <c r="G45" s="4" t="n"/>
-      <c r="H45" s="4" t="n"/>
-      <c r="I45" s="4" t="n"/>
-      <c r="J45" s="4" t="n"/>
-      <c r="K45" s="4" t="n"/>
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>이노보테라퓨틱스</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>신규상장</t>
+        </is>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
+        <is>
+          <t>FY25</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="inlineStr">
+        <is>
+          <t>-5,429</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>-53,200</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>의약품 제조업</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="K45" s="6" t="inlineStr">
+        <is>
+          <t>상장전</t>
+        </is>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>일자</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>회사명</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>시장</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>상장유형</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>기준연도</t>
-        </is>
-      </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="inlineStr">
-        <is>
-          <t>순이익</t>
-        </is>
-      </c>
-      <c r="H46" s="5" t="inlineStr">
-        <is>
-          <t>자기자본</t>
-        </is>
-      </c>
-      <c r="I46" s="5" t="inlineStr">
-        <is>
-          <t>업종</t>
-        </is>
-      </c>
-      <c r="J46" s="5" t="inlineStr">
-        <is>
-          <t>대표주관사</t>
-        </is>
-      </c>
-      <c r="K46" s="5" t="inlineStr">
-        <is>
-          <t>현황</t>
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>이나인페이</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>코스닥</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>신규상장</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>FY25</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>64,711</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>19,586</t>
+        </is>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>79,855</t>
+        </is>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>기타 금융업</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="K46" s="6" t="inlineStr">
+        <is>
+          <t>상장전</t>
         </is>
       </c>
     </row>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
-          <t>상장승인(상장예정)</t>
+          <t>상장완료 (2026-10-15)</t>
         </is>
       </c>
     </row>
@@ -4855,7 +4855,7 @@
       </c>
       <c r="K81" s="6" t="inlineStr">
         <is>
-          <t>상장승인(상장예정)</t>
+          <t>상장완료 (2026-10-15)</t>
         </is>
       </c>
     </row>
@@ -8521,7 +8521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R101"/>
+  <dimension ref="A1:R105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -8737,7 +8737,7 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>■ 상장 완료 (2026)  (48건)</t>
+          <t>■ 상장 완료 (2026)  (50건)</t>
         </is>
       </c>
       <c r="B6" s="4" t="n"/>
@@ -8761,44 +8761,44 @@
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>브릴스</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>08-31~09-04</t>
+          <t>09-16~09-22</t>
         </is>
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>16,500~19,500</t>
+          <t>10,700~12,300</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>1,200,000</t>
+          <t>2,500,000</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>23,400,000,000</t>
+          <t>30,750,000,000</t>
         </is>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>13.44 (PSR)</t>
+          <t>26.18배 (PER)</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>19,500</t>
+          <t>12,300</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>1187.74</v>
+        <v>1136.84</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>2181</v>
+        <v>2405</v>
       </c>
       <c r="J7" s="18" t="inlineStr">
         <is>
@@ -8807,29 +8807,29 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>4,418.97</t>
+          <t>4,284.98</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr"/>
       <c r="M7" s="6" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="N7" s="6" t="inlineStr">
         <is>
-          <t>아이비케이투자증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="O7" s="6" t="inlineStr"/>
       <c r="P7" s="7" t="inlineStr">
         <is>
-          <t>713,790,000</t>
+          <t>826,575,000</t>
         </is>
       </c>
       <c r="Q7" s="6" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="R7" s="6" t="inlineStr">
@@ -8841,75 +8841,79 @@
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>09-08~09-14</t>
+          <t>09-16~09-22</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>12,400~14,600</t>
+          <t>19,500~23,500</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>852,000</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>43,800,000,000</t>
+          <t>16,614,000,000</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>32.57배 (PER)</t>
+          <t>17.61배 (PER)</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>14,600</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>868.64</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>2269</v>
+          <t>19,500</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>1097.62</t>
+        </is>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
       </c>
       <c r="J8" s="18" t="inlineStr">
         <is>
           <t>수집예정</t>
         </is>
       </c>
-      <c r="K8" s="6" t="inlineStr">
-        <is>
-          <t>1,878.06</t>
+      <c r="K8" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr"/>
       <c r="M8" s="6" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="N8" s="6" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>하나증권</t>
         </is>
       </c>
       <c r="O8" s="6" t="inlineStr"/>
       <c r="P8" s="7" t="inlineStr">
         <is>
-          <t>1,413,399,926</t>
+          <t>697,788,000</t>
         </is>
       </c>
       <c r="Q8" s="6" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="R8" s="6" t="inlineStr">
@@ -8921,44 +8925,44 @@
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>빅웨이브로보틱스</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>09-07~09-11</t>
+          <t>08-31~09-04</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>15,000~18,000</t>
+          <t>16,500~19,500</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>1,600,000</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>28,800,000,000</t>
+          <t>23,400,000,000</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>11.15 (PSR)</t>
+          <t>13.44 (PSR)</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>18,000</t>
+          <t>19,500</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>1109.37</v>
+        <v>1187.74</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>2255</v>
+        <v>2181</v>
       </c>
       <c r="J9" s="18" t="inlineStr">
         <is>
@@ -8967,33 +8971,29 @@
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>2,706.30</t>
+          <t>4,418.97</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr"/>
       <c r="M9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="N9" s="6" t="inlineStr">
         <is>
-          <t>유진투자증권</t>
-        </is>
-      </c>
-      <c r="O9" s="6" t="inlineStr">
-        <is>
-          <t>미래</t>
-        </is>
-      </c>
+          <t>아이비케이투자증권</t>
+        </is>
+      </c>
+      <c r="O9" s="6" t="inlineStr"/>
       <c r="P9" s="7" t="inlineStr">
         <is>
-          <t>378,216,000</t>
+          <t>713,790,000</t>
         </is>
       </c>
       <c r="Q9" s="6" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
@@ -9005,44 +9005,44 @@
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>글로벌테크놀로지</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>09-07~09-11</t>
+          <t>09-08~09-14</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>13,000~15,000</t>
+          <t>12,400~14,600</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>40,000,000,000</t>
+          <t>43,800,000,000</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>19.22배 (PER)</t>
+          <t>32.57배 (PER)</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>14,600</t>
         </is>
       </c>
       <c r="H10" s="6" t="n">
-        <v>123.19</v>
+        <v>868.64</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>961</v>
+        <v>2269</v>
       </c>
       <c r="J10" s="18" t="inlineStr">
         <is>
@@ -9051,29 +9051,29 @@
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>57.15</t>
+          <t>1,878.06</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr"/>
       <c r="M10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="O10" s="6" t="inlineStr"/>
       <c r="P10" s="7" t="inlineStr">
         <is>
-          <t>2,119,999,960</t>
-        </is>
-      </c>
-      <c r="Q10" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>1,413,399,926</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="R10" s="6" t="inlineStr">
@@ -9085,17 +9085,17 @@
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>와이즈플래닛컴퍼니</t>
+          <t>빅웨이브로보틱스</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>09-04~09-10</t>
+          <t>09-07~09-11</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>10,000~12,000</t>
+          <t>15,000~18,000</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
@@ -9105,24 +9105,24 @@
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>19,200,000,000</t>
+          <t>28,800,000,000</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>20.04배 (PER)</t>
+          <t>11.15 (PSR)</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>18,000</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>1248.47</v>
+        <v>1109.37</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>2323</v>
+        <v>2255</v>
       </c>
       <c r="J11" s="18" t="inlineStr">
         <is>
@@ -9131,24 +9131,28 @@
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>3,568.86</t>
+          <t>2,706.30</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr"/>
       <c r="M11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="N11" s="6" t="inlineStr">
         <is>
-          <t>대신증권</t>
-        </is>
-      </c>
-      <c r="O11" s="6" t="inlineStr"/>
+          <t>유진투자증권</t>
+        </is>
+      </c>
+      <c r="O11" s="6" t="inlineStr">
+        <is>
+          <t>미래</t>
+        </is>
+      </c>
       <c r="P11" s="7" t="inlineStr">
         <is>
-          <t>494,400,000</t>
+          <t>378,216,000</t>
         </is>
       </c>
       <c r="Q11" s="6" t="inlineStr">
@@ -9165,44 +9169,44 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>한국제17호스팩</t>
+          <t>글로벌테크놀로지</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>09-07~09-08</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>09-07~09-11</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>13,000~15,000</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>7,000,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>14,000,000,000</t>
-        </is>
-      </c>
-      <c r="F12" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>40,000,000,000</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>19.22배 (PER)</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="H12" s="6" t="n">
-        <v>1270.51</v>
+        <v>123.19</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>2040</v>
+        <v>961</v>
       </c>
       <c r="J12" s="18" t="inlineStr">
         <is>
@@ -9211,29 +9215,29 @@
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>8,291.55</t>
+          <t>57.15</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr"/>
       <c r="M12" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="N12" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="N12" s="6" t="inlineStr">
+        <is>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="O12" s="6" t="inlineStr"/>
-      <c r="P12" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="Q12" s="6" t="inlineStr">
-        <is>
-          <t>50%</t>
+      <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>2,119,999,960</t>
+        </is>
+      </c>
+      <c r="Q12" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="R12" s="6" t="inlineStr">
@@ -9245,75 +9249,75 @@
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>KB제34호스팩</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>와이즈플래닛컴퍼니</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>09-04~09-10</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>10,000~12,000</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>7,000,000</t>
+          <t>1,600,000</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>14,000,000,000</t>
-        </is>
-      </c>
-      <c r="F13" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="G13" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>19,200,000,000</t>
+        </is>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>20.04배 (PER)</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>12,000</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>1232.51</v>
+        <v>1248.47</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>2001</v>
+        <v>2323</v>
       </c>
       <c r="J13" s="18" t="inlineStr">
         <is>
           <t>수집예정</t>
         </is>
       </c>
-      <c r="K13" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="K13" s="6" t="inlineStr">
+        <is>
+          <t>3,568.86</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr"/>
       <c r="M13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="N13" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="N13" s="6" t="inlineStr">
+        <is>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="O13" s="6" t="inlineStr"/>
-      <c r="P13" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P13" s="7" t="inlineStr">
+        <is>
+          <t>494,400,000</t>
         </is>
       </c>
       <c r="Q13" s="6" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
@@ -9325,44 +9329,44 @@
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>네오사피엔스</t>
+          <t>한국제17호스팩</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>09-02~09-08</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="inlineStr">
-        <is>
-          <t>13,800~15,800</t>
+          <t>09-07~09-08</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>7,000,000</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>20,000,000,000</t>
-        </is>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>26.76배 (PER)</t>
+          <t>14,000,000,000</t>
+        </is>
+      </c>
+      <c r="F14" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="H14" s="6" t="n">
-        <v>219.56</v>
+        <v>1270.51</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>1045</v>
+        <v>2040</v>
       </c>
       <c r="J14" s="18" t="inlineStr">
         <is>
@@ -9371,29 +9375,29 @@
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>4,885.53</t>
+          <t>8,291.55</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr"/>
       <c r="M14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="N14" s="6" t="inlineStr">
-        <is>
-          <t>대신증권</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="N14" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="O14" s="6" t="inlineStr"/>
-      <c r="P14" s="7" t="inlineStr">
-        <is>
-          <t>1,080,264,000</t>
+      <c r="P14" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="Q14" s="6" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="R14" s="6" t="inlineStr">
@@ -9405,12 +9409,12 @@
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>엔에이치스팩34호</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>08-24~08-25</t>
+          <t>KB제34호스팩</t>
+        </is>
+      </c>
+      <c r="B15" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="C15" s="18" t="inlineStr">
@@ -9420,12 +9424,12 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>8,500,000</t>
+          <t>7,000,000</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>17,000,000,000</t>
+          <t>14,000,000,000</t>
         </is>
       </c>
       <c r="F15" s="18" t="inlineStr">
@@ -9433,31 +9437,31 @@
           <t>수집예정</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>2,000</t>
+      <c r="G15" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>1160.7</v>
+        <v>1232.51</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>2050</v>
+        <v>2001</v>
       </c>
       <c r="J15" s="18" t="inlineStr">
         <is>
           <t>수집예정</t>
         </is>
       </c>
-      <c r="K15" s="6" t="inlineStr">
-        <is>
-          <t>16,216.08</t>
+      <c r="K15" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr"/>
       <c r="M15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="N15" s="18" t="inlineStr">
@@ -9485,17 +9489,17 @@
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>네오사피엔스</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>08-14~08-21</t>
+          <t>09-02~09-08</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>13,000~16,000</t>
+          <t>13,800~15,800</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
@@ -9510,7 +9514,7 @@
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>29.52배 (PER)</t>
+          <t>26.76배 (PER)</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
@@ -9519,10 +9523,10 @@
         </is>
       </c>
       <c r="H16" s="6" t="n">
-        <v>63.41</v>
+        <v>219.56</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>246</v>
+        <v>1045</v>
       </c>
       <c r="J16" s="18" t="inlineStr">
         <is>
@@ -9531,29 +9535,29 @@
       </c>
       <c r="K16" s="6" t="inlineStr">
         <is>
-          <t>88.20</t>
+          <t>4,885.53</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr"/>
       <c r="M16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="N16" s="6" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="O16" s="6" t="inlineStr"/>
       <c r="P16" s="7" t="inlineStr">
         <is>
-          <t>1,071,200,000</t>
-        </is>
-      </c>
-      <c r="Q16" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>1,080,264,000</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="R16" s="6" t="inlineStr">
@@ -9565,75 +9569,75 @@
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>해치텍</t>
+          <t>엔에이치스팩34호</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>08-03~08-07</t>
-        </is>
-      </c>
-      <c r="C17" s="6" t="inlineStr">
-        <is>
-          <t>23,000~28,000</t>
+          <t>08-24~08-25</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>1,000,000</t>
+          <t>8,500,000</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>23,000,000,000</t>
-        </is>
-      </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>36.99배 (PER)</t>
+          <t>17,000,000,000</t>
+        </is>
+      </c>
+      <c r="F17" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>101.91</v>
+        <v>1160.7</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>321</v>
+        <v>2050</v>
       </c>
       <c r="J17" s="18" t="inlineStr">
         <is>
           <t>수집예정</t>
         </is>
       </c>
-      <c r="K17" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>16,216.08</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr"/>
       <c r="M17" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="N17" s="6" t="inlineStr">
-        <is>
-          <t>DB증권</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="N17" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="O17" s="6" t="inlineStr"/>
-      <c r="P17" s="7" t="inlineStr">
-        <is>
-          <t>1,302,950,000</t>
+      <c r="P17" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="Q17" s="6" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="R17" s="6" t="inlineStr">
@@ -9645,75 +9649,75 @@
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>니어스랩</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>08-03~08-07</t>
+          <t>08-14~08-21</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>30,000~41,200</t>
+          <t>13,000~16,000</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>910,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>37,492,000,000</t>
+          <t>20,000,000,000</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>44.41배 (PER)</t>
+          <t>29.52배 (PER)</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>41,200</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="H18" s="6" t="n">
-        <v>743.49</v>
+        <v>63.41</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>1795</v>
+        <v>246</v>
       </c>
       <c r="J18" s="18" t="inlineStr">
         <is>
           <t>수집예정</t>
         </is>
       </c>
-      <c r="K18" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="K18" s="6" t="inlineStr">
+        <is>
+          <t>88.20</t>
         </is>
       </c>
       <c r="L18" s="6" t="inlineStr"/>
       <c r="M18" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="N18" s="6" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="O18" s="6" t="inlineStr"/>
       <c r="P18" s="7" t="inlineStr">
         <is>
-          <t>1,265,355,000</t>
-        </is>
-      </c>
-      <c r="Q18" s="6" t="inlineStr">
-        <is>
-          <t>4.50%</t>
+          <t>1,071,200,000</t>
+        </is>
+      </c>
+      <c r="Q18" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="R18" s="6" t="inlineStr">
@@ -9725,44 +9729,44 @@
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>기도산업</t>
+          <t>해치텍</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>07-31~08-06</t>
+          <t>08-03~08-07</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>24,800~28,400</t>
+          <t>23,000~28,000</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>1,700,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>48,280,000,000</t>
+          <t>23,000,000,000</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>10.01배 (PER)</t>
+          <t>36.99배 (PER)</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>28,400</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>213.31</v>
+        <v>101.91</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>637</v>
+        <v>321</v>
       </c>
       <c r="J19" s="18" t="inlineStr">
         <is>
@@ -9777,23 +9781,23 @@
       <c r="L19" s="6" t="inlineStr"/>
       <c r="M19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="N19" s="6" t="inlineStr">
         <is>
-          <t>미래에셋증권</t>
+          <t>DB증권</t>
         </is>
       </c>
       <c r="O19" s="6" t="inlineStr"/>
       <c r="P19" s="7" t="inlineStr">
         <is>
-          <t>716,720,000</t>
+          <t>1,302,950,000</t>
         </is>
       </c>
       <c r="Q19" s="6" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
@@ -9805,44 +9809,44 @@
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스</t>
+          <t>니어스랩</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>07-20~07-24</t>
+          <t>08-03~08-07</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>12,000~14,500</t>
+          <t>30,000~41,200</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>910,000</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>60,000,000,000</t>
+          <t>37,492,000,000</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>22.89배 (PER)</t>
+          <t>44.41배 (PER)</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>41,200</t>
         </is>
       </c>
       <c r="H20" s="6" t="n">
-        <v>50.4</v>
+        <v>743.49</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>307</v>
+        <v>1795</v>
       </c>
       <c r="J20" s="18" t="inlineStr">
         <is>
@@ -9857,7 +9861,7 @@
       <c r="L20" s="6" t="inlineStr"/>
       <c r="M20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="N20" s="6" t="inlineStr">
@@ -9868,12 +9872,12 @@
       <c r="O20" s="6" t="inlineStr"/>
       <c r="P20" s="7" t="inlineStr">
         <is>
-          <t>4,095,000,000</t>
+          <t>1,265,355,000</t>
         </is>
       </c>
       <c r="Q20" s="6" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>4.50%</t>
         </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
@@ -9885,44 +9889,44 @@
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>케이앤에스아이앤씨</t>
+          <t>기도산업</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>07-27~07-31</t>
+          <t>07-31~08-06</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>9,000~11,000</t>
+          <t>24,800~28,400</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>2,400,000</t>
+          <t>1,700,000</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>26,400,000,000</t>
+          <t>48,280,000,000</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>42.08배 (PER)</t>
+          <t>10.01배 (PER)</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>11,000</t>
+          <t>28,400</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>938.24</v>
+        <v>213.31</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>2024</v>
+        <v>637</v>
       </c>
       <c r="J21" s="18" t="inlineStr">
         <is>
@@ -9937,23 +9941,23 @@
       <c r="L21" s="6" t="inlineStr"/>
       <c r="M21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="N21" s="6" t="inlineStr">
         <is>
-          <t>아이비케이투자증권</t>
+          <t>미래에셋증권</t>
         </is>
       </c>
       <c r="O21" s="6" t="inlineStr"/>
       <c r="P21" s="7" t="inlineStr">
         <is>
-          <t>1,500,000,000</t>
+          <t>716,720,000</t>
         </is>
       </c>
       <c r="Q21" s="6" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
@@ -9965,44 +9969,44 @@
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>딜리셔스</t>
+          <t>인제니아테라퓨틱스</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>07-23~07-29</t>
+          <t>07-20~07-24</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>5,000~7,000</t>
+          <t>12,000~14,500</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>2,200,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>15,400,000,000</t>
+          <t>60,000,000,000</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>23.93배 (PER)</t>
+          <t>22.89배 (PER)</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>7,000</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="H22" s="6" t="n">
-        <v>184.06</v>
+        <v>50.4</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>441</v>
+        <v>307</v>
       </c>
       <c r="J22" s="18" t="inlineStr">
         <is>
@@ -10017,23 +10021,23 @@
       <c r="L22" s="6" t="inlineStr"/>
       <c r="M22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="N22" s="6" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="O22" s="6" t="inlineStr"/>
       <c r="P22" s="7" t="inlineStr">
         <is>
-          <t>566,500,000</t>
+          <t>4,095,000,000</t>
         </is>
       </c>
       <c r="Q22" s="6" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="R22" s="6" t="inlineStr">
@@ -10045,44 +10049,44 @@
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>에이치엘지노믹스</t>
+          <t>케이앤에스아이앤씨</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>07-02~07-08</t>
+          <t>07-27~07-31</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>18,500~21,500</t>
+          <t>9,000~11,000</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>2,565,000</t>
+          <t>2,400,000</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>55,147,500,000</t>
+          <t>26,400,000,000</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>12.85배 (EV/EBITDA)</t>
+          <t>42.08배 (PER)</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>21,500</t>
+          <t>11,000</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>714.52</v>
+        <v>938.24</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>2148</v>
+        <v>2024</v>
       </c>
       <c r="J23" s="18" t="inlineStr">
         <is>
@@ -10097,27 +10101,23 @@
       <c r="L23" s="6" t="inlineStr"/>
       <c r="M23" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="N23" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
-        </is>
-      </c>
-      <c r="O23" s="6" t="inlineStr">
-        <is>
-          <t>아이비케이투자증권, IBK투자증권, IBK투자증권, IBK투자증권, IBK투자증권, IBK투자증권㈜, 보통주, IBK투자증권㈜</t>
-        </is>
-      </c>
+          <t>아이비케이투자증권</t>
+        </is>
+      </c>
+      <c r="O23" s="6" t="inlineStr"/>
       <c r="P23" s="7" t="inlineStr">
         <is>
-          <t>1,211</t>
+          <t>1,500,000,000</t>
         </is>
       </c>
       <c r="Q23" s="6" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="R23" s="6" t="inlineStr">
@@ -10129,74 +10129,70 @@
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>레메디</t>
-        </is>
-      </c>
-      <c r="B24" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>딜리셔스</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>07-23~07-29</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>17,800~20,700</t>
+          <t>5,000~7,000</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>1,200,000</t>
+          <t>2,200,000</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>24,840,000,000</t>
+          <t>15,400,000,000</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>21.95배 (PER)</t>
+          <t>23.93배 (PER)</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>20,700</t>
-        </is>
-      </c>
-      <c r="H24" s="6" t="inlineStr">
-        <is>
-          <t>1,146.41</t>
-        </is>
-      </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>2,246</t>
-        </is>
+          <t>7,000</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>184.06</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>441</v>
       </c>
       <c r="J24" s="18" t="inlineStr">
         <is>
           <t>수집예정</t>
         </is>
       </c>
-      <c r="K24" s="6" t="inlineStr">
-        <is>
-          <t>1,706.71</t>
+      <c r="K24" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="L24" s="6" t="inlineStr"/>
       <c r="M24" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="N24" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="O24" s="6" t="inlineStr"/>
       <c r="P24" s="7" t="inlineStr">
         <is>
-          <t>1,279</t>
+          <t>566,500,000</t>
         </is>
       </c>
       <c r="Q24" s="6" t="inlineStr">
@@ -10213,55 +10209,59 @@
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>레몬헬스케어</t>
-        </is>
-      </c>
-      <c r="B25" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>에이치엘지노믹스</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>07-02~07-08</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>7,500~10,000</t>
+          <t>18,500~21,500</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>2,565,000</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>55,147,500,000</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>25.48배 (PER)</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="n">
-        <v>10000</v>
+          <t>12.85배 (EV/EBITDA)</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>21,500</t>
+        </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>1238</v>
+        <v>714.52</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>2233</v>
-      </c>
-      <c r="J25" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-24~25</t>
-        </is>
-      </c>
-      <c r="K25" s="6" t="n">
-        <v>1510.57</v>
+        <v>2148</v>
+      </c>
+      <c r="J25" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="K25" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
       </c>
       <c r="L25" s="6" t="inlineStr"/>
       <c r="M25" s="6" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="N25" s="6" t="inlineStr">
@@ -10269,15 +10269,19 @@
           <t>KB</t>
         </is>
       </c>
-      <c r="O25" s="6" t="inlineStr"/>
+      <c r="O25" s="6" t="inlineStr">
+        <is>
+          <t>아이비케이투자증권, IBK투자증권, IBK투자증권, IBK투자증권, IBK투자증권, IBK투자증권㈜, 보통주, IBK투자증권㈜</t>
+        </is>
+      </c>
       <c r="P25" s="7" t="inlineStr">
         <is>
-          <t>824</t>
+          <t>1,211</t>
         </is>
       </c>
       <c r="Q25" s="6" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
@@ -10289,7 +10293,7 @@
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>매드업</t>
+          <t>레메디</t>
         </is>
       </c>
       <c r="B26" s="18" t="inlineStr">
@@ -10299,61 +10303,69 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>7,000~8,000</t>
+          <t>17,800~20,700</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>16,000</t>
+          <t>24,840,000,000</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>24.57배 (PER)</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="n">
-        <v>8000</v>
-      </c>
-      <c r="H26" s="6" t="n">
-        <v>1396.29</v>
-      </c>
-      <c r="I26" s="6" t="n">
-        <v>2392</v>
-      </c>
-      <c r="J26" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-23~24</t>
-        </is>
-      </c>
-      <c r="K26" s="6" t="n">
-        <v>3304.76</v>
+          <t>21.95배 (PER)</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>20,700</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t>1,146.41</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>2,246</t>
+        </is>
+      </c>
+      <c r="J26" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="K26" s="6" t="inlineStr">
+        <is>
+          <t>1,706.71</t>
+        </is>
       </c>
       <c r="L26" s="6" t="inlineStr"/>
       <c r="M26" s="6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="N26" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="O26" s="6" t="inlineStr"/>
       <c r="P26" s="7" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>1,279</t>
         </is>
       </c>
       <c r="Q26" s="6" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
@@ -10365,75 +10377,71 @@
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>한국제16호스팩</t>
-        </is>
-      </c>
-      <c r="B27" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
+          <t>레몬헬스케어</t>
+        </is>
+      </c>
+      <c r="B27" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>7,500~10,000</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>5,500,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>11,000</t>
-        </is>
-      </c>
-      <c r="F27" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>25.48배 (PER)</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>10000</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>1364.09</v>
+        <v>1238</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>2089</v>
+        <v>2233</v>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>2026-06-22~06-23</t>
-        </is>
-      </c>
-      <c r="K27" s="6" t="inlineStr">
-        <is>
-          <t>1,274.77</t>
-        </is>
+          <t>2026-06-24~25</t>
+        </is>
+      </c>
+      <c r="K27" s="6" t="n">
+        <v>1510.57</v>
       </c>
       <c r="L27" s="6" t="inlineStr"/>
       <c r="M27" s="6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="N27" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="O27" s="6" t="inlineStr"/>
       <c r="P27" s="7" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>824</t>
         </is>
       </c>
       <c r="Q27" s="6" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
@@ -10445,7 +10453,7 @@
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>스트라드비젼</t>
+          <t>매드업</t>
         </is>
       </c>
       <c r="B28" s="18" t="inlineStr">
@@ -10455,63 +10463,61 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>12,000~14,000</t>
+          <t>7,000~8,000</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>7,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>84,000</t>
+          <t>16,000</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>37.45배 (PER)</t>
+          <t>24.57배 (PER)</t>
         </is>
       </c>
       <c r="G28" s="6" t="n">
-        <v>12000</v>
+        <v>8000</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>381.3</v>
+        <v>1396.29</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>1604</v>
+        <v>2392</v>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>2026-06-18~06-19</t>
-        </is>
-      </c>
-      <c r="K28" s="6" t="inlineStr">
-        <is>
-          <t>45.81</t>
-        </is>
+          <t>2026-06-23~24</t>
+        </is>
+      </c>
+      <c r="K28" s="6" t="n">
+        <v>3304.76</v>
       </c>
       <c r="L28" s="6" t="inlineStr"/>
       <c r="M28" s="6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="N28" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="O28" s="6" t="inlineStr"/>
       <c r="P28" s="7" t="inlineStr">
         <is>
-          <t>2,575</t>
+          <t>742</t>
         </is>
       </c>
       <c r="Q28" s="6" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
@@ -10523,73 +10529,75 @@
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>져스텍</t>
-        </is>
-      </c>
-      <c r="B29" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>한국제16호스팩</t>
+        </is>
+      </c>
+      <c r="B29" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>10,500~12,500</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>1,600,000</t>
+          <t>5,500,000</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>20,000</t>
-        </is>
-      </c>
-      <c r="F29" s="6" t="inlineStr">
-        <is>
-          <t>26.82배 (PER)</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="n">
-        <v>12500</v>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="F29" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
       </c>
       <c r="H29" s="6" t="n">
-        <v>1294.99</v>
+        <v>1364.09</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>2252</v>
+        <v>2089</v>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>2026-06-18~06-19</t>
+          <t>2026-06-22~06-23</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>2,783.89</t>
+          <t>1,274.77</t>
         </is>
       </c>
       <c r="L29" s="6" t="inlineStr"/>
       <c r="M29" s="6" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="N29" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="O29" s="6" t="inlineStr"/>
       <c r="P29" s="7" t="inlineStr">
         <is>
-          <t>1,164</t>
+          <t>330</t>
         </is>
       </c>
       <c r="Q29" s="6" t="inlineStr">
         <is>
-          <t>5.65%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
@@ -10601,17 +10609,17 @@
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>메리츠제2호스팩</t>
-        </is>
-      </c>
-      <c r="B30" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
+          <t>스트라드비젼</t>
+        </is>
+      </c>
+      <c r="B30" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>12,000~14,000</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
@@ -10621,55 +10629,53 @@
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>14,000</t>
-        </is>
-      </c>
-      <c r="F30" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
+          <t>84,000</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>37.45배 (PER)</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>12000</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>1087.58</v>
+        <v>381.3</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>1798</v>
+        <v>1604</v>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09~06-10</t>
+          <t>2026-06-18~06-19</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>1,338.66</t>
+          <t>45.81</t>
         </is>
       </c>
       <c r="L30" s="6" t="inlineStr"/>
       <c r="M30" s="6" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="N30" s="6" t="inlineStr">
         <is>
-          <t>메리츠</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="O30" s="6" t="inlineStr"/>
       <c r="P30" s="7" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>2,575</t>
         </is>
       </c>
       <c r="Q30" s="6" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
@@ -10681,7 +10687,7 @@
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>피스피스스튜디오</t>
+          <t>져스텍</t>
         </is>
       </c>
       <c r="B31" s="18" t="inlineStr">
@@ -10691,67 +10697,63 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>19,000~21,500</t>
+          <t>10,500~12,500</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>2,272,637</t>
+          <t>1,600,000</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>48,862</t>
+          <t>20,000</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>21.48배 (PER)</t>
+          <t>26.82배 (PER)</t>
         </is>
       </c>
       <c r="G31" s="6" t="n">
-        <v>21500</v>
+        <v>12500</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>847.76</v>
+        <v>1294.99</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>2329</v>
+        <v>2252</v>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>2026-05-26~05-27</t>
+          <t>2026-06-18~06-19</t>
         </is>
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>1,191.15</t>
+          <t>2,783.89</t>
         </is>
       </c>
       <c r="L31" s="6" t="inlineStr"/>
       <c r="M31" s="6" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="N31" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
-        </is>
-      </c>
-      <c r="O31" s="6" t="inlineStr">
-        <is>
-          <t>NH</t>
-        </is>
-      </c>
+          <t>삼성</t>
+        </is>
+      </c>
+      <c r="O31" s="6" t="inlineStr"/>
       <c r="P31" s="7" t="inlineStr">
         <is>
-          <t>1,994</t>
+          <t>1,164</t>
         </is>
       </c>
       <c r="Q31" s="6" t="inlineStr">
         <is>
-          <t>4.00%</t>
+          <t>5.65%</t>
         </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
@@ -10763,7 +10765,7 @@
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>대신밸런스제20호스팩</t>
+          <t>메리츠제2호스팩</t>
         </is>
       </c>
       <c r="B32" s="19" t="inlineStr">
@@ -10778,12 +10780,12 @@
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>6,500,000</t>
+          <t>7,000,000</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>13,000</t>
+          <t>14,000</t>
         </is>
       </c>
       <c r="F32" s="19" t="inlineStr">
@@ -10797,41 +10799,41 @@
         </is>
       </c>
       <c r="H32" s="6" t="n">
-        <v>1327.13</v>
+        <v>1087.58</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>2194</v>
+        <v>1798</v>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>2026-05-22~05-25</t>
+          <t>2026-06-09~06-10</t>
         </is>
       </c>
       <c r="K32" s="6" t="inlineStr">
         <is>
-          <t>1,486.88</t>
+          <t>1,338.66</t>
         </is>
       </c>
       <c r="L32" s="6" t="inlineStr"/>
       <c r="M32" s="6" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="N32" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>메리츠</t>
         </is>
       </c>
       <c r="O32" s="6" t="inlineStr"/>
       <c r="P32" s="7" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>245</t>
         </is>
       </c>
       <c r="Q32" s="6" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="R32" s="6" t="inlineStr">
@@ -10843,7 +10845,7 @@
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>마키나락스</t>
+          <t>피스피스스튜디오</t>
         </is>
       </c>
       <c r="B33" s="18" t="inlineStr">
@@ -10853,47 +10855,47 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>12,500~15,000</t>
+          <t>19,000~21,500</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>2,635,000</t>
+          <t>2,272,637</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>39,525</t>
+          <t>48,862</t>
         </is>
       </c>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>40.5배 (PER)</t>
+          <t>21.48배 (PER)</t>
         </is>
       </c>
       <c r="G33" s="6" t="n">
-        <v>15000</v>
+        <v>21500</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>1196.08</v>
+        <v>847.76</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>2427</v>
+        <v>2329</v>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>2026-05-11~05-12</t>
+          <t>2026-05-26~05-27</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>2,807.79</t>
+          <t>1,191.15</t>
         </is>
       </c>
       <c r="L33" s="6" t="inlineStr"/>
       <c r="M33" s="6" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="N33" s="6" t="inlineStr">
@@ -10901,15 +10903,19 @@
           <t>미래</t>
         </is>
       </c>
-      <c r="O33" s="6" t="inlineStr"/>
+      <c r="O33" s="6" t="inlineStr">
+        <is>
+          <t>NH</t>
+        </is>
+      </c>
       <c r="P33" s="7" t="inlineStr">
         <is>
-          <t>2,026</t>
+          <t>1,994</t>
         </is>
       </c>
       <c r="Q33" s="6" t="inlineStr">
         <is>
-          <t>5.00%</t>
+          <t>4.00%</t>
         </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
@@ -10921,22 +10927,22 @@
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>폴레드</t>
-        </is>
-      </c>
-      <c r="B34" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>대신밸런스제20호스팩</t>
+        </is>
+      </c>
+      <c r="B34" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>4,100~5,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>2,600,000</t>
+          <t>6,500,000</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
@@ -10944,50 +10950,52 @@
           <t>13,000</t>
         </is>
       </c>
-      <c r="F34" s="6" t="inlineStr">
-        <is>
-          <t>19.05배 (PER)</t>
-        </is>
-      </c>
-      <c r="G34" s="6" t="n">
-        <v>5000</v>
+      <c r="F34" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
       </c>
       <c r="H34" s="6" t="n">
-        <v>1486.66</v>
+        <v>1327.13</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>2372</v>
+        <v>2194</v>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>2026-05-04~05-05</t>
+          <t>2026-05-22~05-25</t>
         </is>
       </c>
       <c r="K34" s="6" t="inlineStr">
         <is>
-          <t>3,169.86</t>
+          <t>1,486.88</t>
         </is>
       </c>
       <c r="L34" s="6" t="inlineStr"/>
       <c r="M34" s="6" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="N34" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="O34" s="6" t="inlineStr"/>
       <c r="P34" s="7" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>390</t>
         </is>
       </c>
       <c r="Q34" s="6" t="inlineStr">
         <is>
-          <t>4.03%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
@@ -10999,7 +11007,7 @@
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>코스모로보틱스</t>
+          <t>마키나락스</t>
         </is>
       </c>
       <c r="B35" s="18" t="inlineStr">
@@ -11009,67 +11017,63 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>5,300~6,000</t>
+          <t>12,500~15,000</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>4,170,000</t>
+          <t>2,635,000</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>25,020</t>
+          <t>39,525</t>
         </is>
       </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>47.45배 (PER)</t>
+          <t>40.5배 (PER)</t>
         </is>
       </c>
       <c r="G35" s="6" t="n">
-        <v>6000</v>
+        <v>15000</v>
       </c>
       <c r="H35" s="6" t="n">
-        <v>1140.11</v>
+        <v>1196.08</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>2257</v>
+        <v>2427</v>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>2026-04-27~04-28</t>
+          <t>2026-05-11~05-12</t>
         </is>
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>2,013.80</t>
+          <t>2,807.79</t>
         </is>
       </c>
       <c r="L35" s="6" t="inlineStr"/>
       <c r="M35" s="6" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="N35" s="6" t="inlineStr">
         <is>
-          <t>유진</t>
-        </is>
-      </c>
-      <c r="O35" s="6" t="inlineStr">
-        <is>
-          <t>NH</t>
-        </is>
-      </c>
+          <t>미래</t>
+        </is>
+      </c>
+      <c r="O35" s="6" t="inlineStr"/>
       <c r="P35" s="7" t="inlineStr">
         <is>
-          <t>1,289</t>
+          <t>2,026</t>
         </is>
       </c>
       <c r="Q35" s="6" t="inlineStr">
         <is>
-          <t>3.78%</t>
+          <t>5.00%</t>
         </is>
       </c>
       <c r="R35" s="6" t="inlineStr">
@@ -11081,75 +11085,73 @@
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>신한스팩18호</t>
-        </is>
-      </c>
-      <c r="B36" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
+          <t>폴레드</t>
+        </is>
+      </c>
+      <c r="B36" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>4,100~5,000</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>2,600,000</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>10,000</t>
-        </is>
-      </c>
-      <c r="F36" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="G36" s="6" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
+          <t>13,000</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>19.05배 (PER)</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v>5000</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>1388.6</v>
+        <v>1486.66</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>2044</v>
+        <v>2372</v>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>2026-04-20~04-21</t>
+          <t>2026-05-04~05-05</t>
         </is>
       </c>
       <c r="K36" s="6" t="inlineStr">
         <is>
-          <t>1,601.36</t>
+          <t>3,169.86</t>
         </is>
       </c>
       <c r="L36" s="6" t="inlineStr"/>
       <c r="M36" s="6" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="N36" s="6" t="inlineStr">
         <is>
-          <t>신한</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="O36" s="6" t="inlineStr"/>
       <c r="P36" s="7" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>540</t>
         </is>
       </c>
       <c r="Q36" s="6" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>4.03%</t>
         </is>
       </c>
       <c r="R36" s="6" t="inlineStr">
@@ -11161,7 +11163,7 @@
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>채비</t>
+          <t>코스모로보틱스</t>
         </is>
       </c>
       <c r="B37" s="18" t="inlineStr">
@@ -11171,67 +11173,67 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>12,300~15,300</t>
+          <t>5,300~6,000</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>9,000,000</t>
+          <t>4,170,000</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>110,700</t>
+          <t>25,020</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>24.0배 (EV/EBITDA)</t>
+          <t>47.45배 (PER)</t>
         </is>
       </c>
       <c r="G37" s="6" t="n">
-        <v>12300</v>
+        <v>6000</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>55.23</v>
+        <v>1140.11</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>751</v>
+        <v>2257</v>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>2026-04-20~04-21</t>
+          <t>2026-04-27~04-28</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>302.11</t>
+          <t>2,013.80</t>
         </is>
       </c>
       <c r="L37" s="6" t="inlineStr"/>
       <c r="M37" s="6" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="N37" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>유진</t>
         </is>
       </c>
       <c r="O37" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="P37" s="7" t="inlineStr">
         <is>
-          <t>3,384</t>
+          <t>1,289</t>
         </is>
       </c>
       <c r="Q37" s="6" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>3.78%</t>
         </is>
       </c>
       <c r="R37" s="6" t="inlineStr">
@@ -11243,7 +11245,7 @@
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>키움히어로스펙2호</t>
+          <t>신한스팩18호</t>
         </is>
       </c>
       <c r="B38" s="19" t="inlineStr">
@@ -11258,12 +11260,12 @@
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>6,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="F38" s="19" t="inlineStr">
@@ -11277,41 +11279,41 @@
         </is>
       </c>
       <c r="H38" s="6" t="n">
-        <v>1271.12</v>
+        <v>1388.6</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>2054</v>
+        <v>2044</v>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>2026-04-14~04-15</t>
+          <t>2026-04-20~04-21</t>
         </is>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
-          <t>1,727.59</t>
+          <t>1,601.36</t>
         </is>
       </c>
       <c r="L38" s="6" t="inlineStr"/>
       <c r="M38" s="6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="N38" s="6" t="inlineStr">
         <is>
-          <t>키움</t>
+          <t>신한</t>
         </is>
       </c>
       <c r="O38" s="6" t="inlineStr"/>
       <c r="P38" s="7" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>350</t>
         </is>
       </c>
       <c r="Q38" s="6" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="R38" s="6" t="inlineStr">
@@ -11323,75 +11325,77 @@
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>교보스팩20호</t>
-        </is>
-      </c>
-      <c r="B39" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
+          <t>채비</t>
+        </is>
+      </c>
+      <c r="B39" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>12,300~15,300</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>5,400,000</t>
+          <t>9,000,000</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>10,800</t>
-        </is>
-      </c>
-      <c r="F39" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="G39" s="6" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
+          <t>110,700</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>24.0배 (EV/EBITDA)</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="n">
+        <v>12300</v>
       </c>
       <c r="H39" s="6" t="n">
-        <v>1196.99</v>
+        <v>55.23</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>1855</v>
+        <v>751</v>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
-          <t>2026-03-23~03-24</t>
+          <t>2026-04-20~04-21</t>
         </is>
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>747.00</t>
+          <t>302.11</t>
         </is>
       </c>
       <c r="L39" s="6" t="inlineStr"/>
       <c r="M39" s="6" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="N39" s="6" t="inlineStr">
         <is>
-          <t>교보</t>
-        </is>
-      </c>
-      <c r="O39" s="6" t="inlineStr"/>
+          <t>KB</t>
+        </is>
+      </c>
+      <c r="O39" s="6" t="inlineStr">
+        <is>
+          <t>삼성</t>
+        </is>
+      </c>
       <c r="P39" s="7" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>3,384</t>
         </is>
       </c>
       <c r="Q39" s="6" t="inlineStr">
         <is>
-          <t>2.78%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="R39" s="6" t="inlineStr">
@@ -11403,73 +11407,75 @@
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>인벤테라</t>
-        </is>
-      </c>
-      <c r="B40" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>키움히어로스펙2호</t>
+        </is>
+      </c>
+      <c r="B40" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>12,100~16,600</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>1,180,000</t>
+          <t>6,000,000</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>19,588</t>
-        </is>
-      </c>
-      <c r="F40" s="6" t="inlineStr">
-        <is>
-          <t>24.34배 (PER)</t>
-        </is>
-      </c>
-      <c r="G40" s="6" t="n">
-        <v>16600</v>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="F40" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
       </c>
       <c r="H40" s="6" t="n">
-        <v>1328.82</v>
+        <v>1271.12</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>2309</v>
+        <v>2054</v>
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>2026-03-23~03-24</t>
+          <t>2026-04-14~04-15</t>
         </is>
       </c>
       <c r="K40" s="6" t="inlineStr">
         <is>
-          <t>1,913.00</t>
+          <t>1,727.59</t>
         </is>
       </c>
       <c r="L40" s="6" t="inlineStr"/>
       <c r="M40" s="6" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="N40" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>키움</t>
         </is>
       </c>
       <c r="O40" s="6" t="inlineStr"/>
       <c r="P40" s="7" t="inlineStr">
         <is>
-          <t>1,211</t>
+          <t>300</t>
         </is>
       </c>
       <c r="Q40" s="6" t="inlineStr">
         <is>
-          <t>6.00%</t>
+          <t>2.50%</t>
         </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
@@ -11481,7 +11487,7 @@
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>신한스팩17호</t>
+          <t>교보스팩20호</t>
         </is>
       </c>
       <c r="B41" s="19" t="inlineStr">
@@ -11496,12 +11502,12 @@
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>5,400,000</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>10,800</t>
         </is>
       </c>
       <c r="F41" s="19" t="inlineStr">
@@ -11515,41 +11521,41 @@
         </is>
       </c>
       <c r="H41" s="6" t="n">
-        <v>1343.8</v>
+        <v>1196.99</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>2022</v>
+        <v>1855</v>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>2026-03-19~03-20</t>
+          <t>2026-03-23~03-24</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>1,403.74</t>
+          <t>747.00</t>
         </is>
       </c>
       <c r="L41" s="6" t="inlineStr"/>
       <c r="M41" s="6" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="N41" s="6" t="inlineStr">
         <is>
-          <t>신한</t>
+          <t>교보</t>
         </is>
       </c>
       <c r="O41" s="6" t="inlineStr"/>
       <c r="P41" s="7" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>300</t>
         </is>
       </c>
       <c r="Q41" s="6" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>2.78%</t>
         </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
@@ -11561,7 +11567,7 @@
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>리센스메디컬</t>
+          <t>인벤테라</t>
         </is>
       </c>
       <c r="B42" s="18" t="inlineStr">
@@ -11571,67 +11577,63 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>9,000~11,000</t>
+          <t>12,100~16,600</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>1,400,000</t>
+          <t>1,180,000</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>15,400</t>
+          <t>19,588</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>31.33배 (PER)</t>
+          <t>24.34배 (PER)</t>
         </is>
       </c>
       <c r="G42" s="6" t="n">
-        <v>11000</v>
+        <v>16600</v>
       </c>
       <c r="H42" s="6" t="n">
-        <v>1352.63</v>
+        <v>1328.82</v>
       </c>
       <c r="I42" s="6" t="n">
-        <v>2261</v>
+        <v>2309</v>
       </c>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>2026-03-19~03-20</t>
+          <t>2026-03-23~03-24</t>
         </is>
       </c>
       <c r="K42" s="6" t="inlineStr">
         <is>
-          <t>2,097.68</t>
+          <t>1,913.00</t>
         </is>
       </c>
       <c r="L42" s="6" t="inlineStr"/>
       <c r="M42" s="6" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="N42" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
-        </is>
-      </c>
-      <c r="O42" s="6" t="inlineStr">
-        <is>
-          <t>KB</t>
-        </is>
-      </c>
+          <t>NH</t>
+        </is>
+      </c>
+      <c r="O42" s="6" t="inlineStr"/>
       <c r="P42" s="7" t="inlineStr">
         <is>
-          <t>916</t>
+          <t>1,211</t>
         </is>
       </c>
       <c r="Q42" s="6" t="inlineStr">
         <is>
-          <t>5.77%</t>
+          <t>6.00%</t>
         </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
@@ -11643,7 +11645,7 @@
     <row r="43" ht="30" customHeight="1">
       <c r="A43" s="6" t="inlineStr">
         <is>
-          <t>NH스팩33호</t>
+          <t>신한스팩17호</t>
         </is>
       </c>
       <c r="B43" s="19" t="inlineStr">
@@ -11658,12 +11660,12 @@
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>6,350,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>12,700</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="F43" s="19" t="inlineStr">
@@ -11677,41 +11679,41 @@
         </is>
       </c>
       <c r="H43" s="6" t="n">
-        <v>1228.71</v>
+        <v>1343.8</v>
       </c>
       <c r="I43" s="6" t="n">
-        <v>2058</v>
+        <v>2022</v>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>2026-03-17~03-18</t>
+          <t>2026-03-19~03-20</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>569.27</t>
+          <t>1,403.74</t>
         </is>
       </c>
       <c r="L43" s="6" t="inlineStr"/>
       <c r="M43" s="6" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="N43" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>신한</t>
         </is>
       </c>
       <c r="O43" s="6" t="inlineStr"/>
       <c r="P43" s="7" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>350</t>
         </is>
       </c>
       <c r="Q43" s="6" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
@@ -11723,7 +11725,7 @@
     <row r="44" ht="30" customHeight="1">
       <c r="A44" s="6" t="inlineStr">
         <is>
-          <t>메쥬</t>
+          <t>리센스메디컬</t>
         </is>
       </c>
       <c r="B44" s="18" t="inlineStr">
@@ -11733,63 +11735,67 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>16,700~21,600</t>
+          <t>9,000~11,000</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>1,345,000</t>
+          <t>1,400,000</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>29,052</t>
+          <t>15,400</t>
         </is>
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>20.66배 (PER)</t>
+          <t>31.33배 (PER)</t>
         </is>
       </c>
       <c r="G44" s="6" t="n">
-        <v>21600</v>
+        <v>11000</v>
       </c>
       <c r="H44" s="6" t="n">
-        <v>1108.93</v>
+        <v>1352.63</v>
       </c>
       <c r="I44" s="6" t="n">
-        <v>2320</v>
+        <v>2261</v>
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>2026-03-16~03-17</t>
+          <t>2026-03-19~03-20</t>
         </is>
       </c>
       <c r="K44" s="6" t="inlineStr">
         <is>
-          <t>2,428.25</t>
+          <t>2,097.68</t>
         </is>
       </c>
       <c r="L44" s="6" t="inlineStr"/>
       <c r="M44" s="6" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="N44" s="6" t="inlineStr">
         <is>
-          <t>신한</t>
-        </is>
-      </c>
-      <c r="O44" s="6" t="inlineStr"/>
+          <t>한국</t>
+        </is>
+      </c>
+      <c r="O44" s="6" t="inlineStr">
+        <is>
+          <t>KB</t>
+        </is>
+      </c>
       <c r="P44" s="7" t="inlineStr">
         <is>
-          <t>1,496</t>
+          <t>916</t>
         </is>
       </c>
       <c r="Q44" s="6" t="inlineStr">
         <is>
-          <t>5.00%</t>
+          <t>5.77%</t>
         </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
@@ -11801,73 +11807,75 @@
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="6" t="inlineStr">
         <is>
-          <t>한패스</t>
-        </is>
-      </c>
-      <c r="B45" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>NH스팩33호</t>
+        </is>
+      </c>
+      <c r="B45" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>17,000~19,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>1,100,000</t>
+          <t>6,350,000</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>20,900</t>
-        </is>
-      </c>
-      <c r="F45" s="6" t="inlineStr">
-        <is>
-          <t>29.09배 (PER)</t>
-        </is>
-      </c>
-      <c r="G45" s="6" t="n">
-        <v>19000</v>
+          <t>12,700</t>
+        </is>
+      </c>
+      <c r="F45" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
       </c>
       <c r="H45" s="6" t="n">
-        <v>1172.59</v>
+        <v>1228.71</v>
       </c>
       <c r="I45" s="6" t="n">
-        <v>2229</v>
+        <v>2058</v>
       </c>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>2026-03-16~03-17</t>
+          <t>2026-03-17~03-18</t>
         </is>
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>1,673.04</t>
+          <t>569.27</t>
         </is>
       </c>
       <c r="L45" s="6" t="inlineStr"/>
       <c r="M45" s="6" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="N45" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="O45" s="6" t="inlineStr"/>
       <c r="P45" s="7" t="inlineStr">
         <is>
-          <t>753</t>
+          <t>381</t>
         </is>
       </c>
       <c r="Q45" s="6" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="R45" s="6" t="inlineStr">
@@ -11879,7 +11887,7 @@
     <row r="46" ht="30" customHeight="1">
       <c r="A46" s="6" t="inlineStr">
         <is>
-          <t>아이엠바이오로직스</t>
+          <t>메쥬</t>
         </is>
       </c>
       <c r="B46" s="18" t="inlineStr">
@@ -11889,58 +11897,58 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>19,000~26,000</t>
+          <t>16,700~21,600</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>1,345,000</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>52,000</t>
+          <t>29,052</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>21.46배 (PER)</t>
+          <t>20.66배 (PER)</t>
         </is>
       </c>
       <c r="G46" s="6" t="n">
-        <v>26000</v>
+        <v>21600</v>
       </c>
       <c r="H46" s="6" t="n">
-        <v>839.23</v>
+        <v>1108.93</v>
       </c>
       <c r="I46" s="6" t="n">
-        <v>2333</v>
+        <v>2320</v>
       </c>
       <c r="J46" s="6" t="inlineStr">
         <is>
-          <t>2026-03-11~03-12</t>
+          <t>2026-03-16~03-17</t>
         </is>
       </c>
       <c r="K46" s="6" t="inlineStr">
         <is>
-          <t>1,806.00</t>
+          <t>2,428.25</t>
         </is>
       </c>
       <c r="L46" s="6" t="inlineStr"/>
       <c r="M46" s="6" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="N46" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>신한</t>
         </is>
       </c>
       <c r="O46" s="6" t="inlineStr"/>
       <c r="P46" s="7" t="inlineStr">
         <is>
-          <t>2,650</t>
+          <t>1,496</t>
         </is>
       </c>
       <c r="Q46" s="6" t="inlineStr">
@@ -11957,7 +11965,7 @@
     <row r="47" ht="30" customHeight="1">
       <c r="A47" s="6" t="inlineStr">
         <is>
-          <t>카나프테라퓨틱스</t>
+          <t>한패스</t>
         </is>
       </c>
       <c r="B47" s="18" t="inlineStr">
@@ -11967,47 +11975,47 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>16,000~20,000</t>
+          <t>17,000~19,000</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>1,100,000</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>40,000</t>
+          <t>20,900</t>
         </is>
       </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>23.59배 (PER)</t>
+          <t>29.09배 (PER)</t>
         </is>
       </c>
       <c r="G47" s="6" t="n">
-        <v>20000</v>
+        <v>19000</v>
       </c>
       <c r="H47" s="6" t="n">
-        <v>962.1</v>
+        <v>1172.59</v>
       </c>
       <c r="I47" s="6" t="n">
-        <v>2327</v>
+        <v>2229</v>
       </c>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>2026-03-05~03-06</t>
+          <t>2026-03-16~03-17</t>
         </is>
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>1,899.29</t>
+          <t>1,673.04</t>
         </is>
       </c>
       <c r="L47" s="6" t="inlineStr"/>
       <c r="M47" s="6" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="N47" s="6" t="inlineStr">
@@ -12018,12 +12026,12 @@
       <c r="O47" s="6" t="inlineStr"/>
       <c r="P47" s="7" t="inlineStr">
         <is>
-          <t>2,050</t>
+          <t>753</t>
         </is>
       </c>
       <c r="Q47" s="6" t="inlineStr">
         <is>
-          <t>5.00%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="R47" s="6" t="inlineStr">
@@ -12035,7 +12043,7 @@
     <row r="48" ht="30" customHeight="1">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>액스비스</t>
+          <t>아이엠바이오로직스</t>
         </is>
       </c>
       <c r="B48" s="18" t="inlineStr">
@@ -12045,63 +12053,63 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>10,100~11,500</t>
+          <t>19,000~26,000</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>2,300,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>26,450</t>
+          <t>52,000</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>27.60배 (PER)</t>
+          <t>21.46배 (PER)</t>
         </is>
       </c>
       <c r="G48" s="6" t="n">
-        <v>11500</v>
+        <v>26000</v>
       </c>
       <c r="H48" s="6" t="n">
-        <v>1124.21</v>
+        <v>839.23</v>
       </c>
       <c r="I48" s="6" t="n">
-        <v>2411</v>
+        <v>2333</v>
       </c>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>2026-02-23~02-24</t>
+          <t>2026-03-11~03-12</t>
         </is>
       </c>
       <c r="K48" s="6" t="inlineStr">
         <is>
-          <t>1,960.87</t>
+          <t>1,806.00</t>
         </is>
       </c>
       <c r="L48" s="6" t="inlineStr"/>
       <c r="M48" s="6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="N48" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="O48" s="6" t="inlineStr"/>
       <c r="P48" s="7" t="inlineStr">
         <is>
-          <t>1,090</t>
+          <t>2,650</t>
         </is>
       </c>
       <c r="Q48" s="6" t="inlineStr">
         <is>
-          <t>4.00%</t>
+          <t>5.00%</t>
         </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
@@ -12113,7 +12121,7 @@
     <row r="49" ht="30" customHeight="1">
       <c r="A49" s="6" t="inlineStr">
         <is>
-          <t>에스팀</t>
+          <t>카나프테라퓨틱스</t>
         </is>
       </c>
       <c r="B49" s="18" t="inlineStr">
@@ -12123,47 +12131,47 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>7,000~8,500</t>
+          <t>16,000~20,000</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>1,800,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>15,300</t>
+          <t>40,000</t>
         </is>
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>17.71배 (EV/EBITDA)</t>
+          <t>23.59배 (PER)</t>
         </is>
       </c>
       <c r="G49" s="6" t="n">
-        <v>8500</v>
+        <v>20000</v>
       </c>
       <c r="H49" s="6" t="n">
-        <v>1334.91</v>
+        <v>962.1</v>
       </c>
       <c r="I49" s="6" t="n">
-        <v>2263</v>
+        <v>2327</v>
       </c>
       <c r="J49" s="6" t="inlineStr">
         <is>
-          <t>2026-02-23~02-24</t>
+          <t>2026-03-05~03-06</t>
         </is>
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>1,334.91</t>
+          <t>1,899.29</t>
         </is>
       </c>
       <c r="L49" s="6" t="inlineStr"/>
       <c r="M49" s="6" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="N49" s="6" t="inlineStr">
@@ -12174,7 +12182,7 @@
       <c r="O49" s="6" t="inlineStr"/>
       <c r="P49" s="7" t="inlineStr">
         <is>
-          <t>788</t>
+          <t>2,050</t>
         </is>
       </c>
       <c r="Q49" s="6" t="inlineStr">
@@ -12191,7 +12199,7 @@
     <row r="50" ht="30" customHeight="1">
       <c r="A50" s="6" t="inlineStr">
         <is>
-          <t>케이뱅크 (유가)</t>
+          <t>액스비스</t>
         </is>
       </c>
       <c r="B50" s="18" t="inlineStr">
@@ -12201,67 +12209,63 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>8,300~9,500</t>
+          <t>10,100~11,500</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>60,000,000</t>
+          <t>2,300,000</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>498,000</t>
+          <t>26,450</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>1.80배 (PBR)</t>
+          <t>27.60배 (PER)</t>
         </is>
       </c>
       <c r="G50" s="6" t="n">
-        <v>8300</v>
+        <v>11500</v>
       </c>
       <c r="H50" s="6" t="n">
-        <v>198.53</v>
+        <v>1124.21</v>
       </c>
       <c r="I50" s="6" t="n">
-        <v>2007</v>
+        <v>2411</v>
       </c>
       <c r="J50" s="6" t="inlineStr">
         <is>
-          <t>2026-02-20~23</t>
+          <t>2026-02-23~02-24</t>
         </is>
       </c>
       <c r="K50" s="6" t="inlineStr">
         <is>
-          <t>134.59</t>
+          <t>1,960.87</t>
         </is>
       </c>
       <c r="L50" s="6" t="inlineStr"/>
       <c r="M50" s="6" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="N50" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
-        </is>
-      </c>
-      <c r="O50" s="6" t="inlineStr">
-        <is>
-          <t>삼성</t>
-        </is>
-      </c>
+          <t>미래</t>
+        </is>
+      </c>
+      <c r="O50" s="6" t="inlineStr"/>
       <c r="P50" s="7" t="inlineStr">
         <is>
-          <t>5,976</t>
+          <t>1,090</t>
         </is>
       </c>
       <c r="Q50" s="6" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>4.00%</t>
         </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
@@ -12273,91 +12277,85 @@
     <row r="51" ht="30" customHeight="1">
       <c r="A51" s="6" t="inlineStr">
         <is>
-          <t>세미티에스</t>
-        </is>
-      </c>
-      <c r="B51" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="C51" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="D51" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="E51" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="F51" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="G51" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="H51" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="I51" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="J51" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="K51" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
+          <t>에스팀</t>
+        </is>
+      </c>
+      <c r="B51" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>7,000~8,500</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>1,800,000</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>15,300</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
+        <is>
+          <t>17.71배 (EV/EBITDA)</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="n">
+        <v>8500</v>
+      </c>
+      <c r="H51" s="6" t="n">
+        <v>1334.91</v>
+      </c>
+      <c r="I51" s="6" t="n">
+        <v>2263</v>
+      </c>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-23~02-24</t>
+        </is>
+      </c>
+      <c r="K51" s="6" t="inlineStr">
+        <is>
+          <t>1,334.91</t>
         </is>
       </c>
       <c r="L51" s="6" t="inlineStr"/>
       <c r="M51" s="6" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="N51" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="O51" s="6" t="inlineStr"/>
-      <c r="P51" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="Q51" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
+      <c r="P51" s="7" t="inlineStr">
+        <is>
+          <t>788</t>
+        </is>
+      </c>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>5.00%</t>
         </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
-          <t>상장완료(스팩합병)</t>
+          <t>상장완료</t>
         </is>
       </c>
     </row>
     <row r="52" ht="30" customHeight="1">
       <c r="A52" s="6" t="inlineStr">
         <is>
-          <t>덕양에너젠</t>
+          <t>케이뱅크 (유가)</t>
         </is>
       </c>
       <c r="B52" s="18" t="inlineStr">
@@ -12367,47 +12365,47 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>8,500~10,000</t>
+          <t>8,300~9,500</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>7,500,000</t>
+          <t>60,000,000</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>75,000</t>
+          <t>498,000</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>30.32배 (EV/EBITDA)</t>
+          <t>1.80배 (PBR)</t>
         </is>
       </c>
       <c r="G52" s="6" t="n">
-        <v>10000</v>
+        <v>8300</v>
       </c>
       <c r="H52" s="6" t="n">
-        <v>650.14</v>
+        <v>198.53</v>
       </c>
       <c r="I52" s="6" t="n">
-        <v>2324</v>
+        <v>2007</v>
       </c>
       <c r="J52" s="6" t="inlineStr">
         <is>
-          <t>2026-01-20~01-21</t>
+          <t>2026-02-20~23</t>
         </is>
       </c>
       <c r="K52" s="6" t="inlineStr">
         <is>
-          <t>1,354.00</t>
+          <t>134.59</t>
         </is>
       </c>
       <c r="L52" s="6" t="inlineStr"/>
       <c r="M52" s="6" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="N52" s="6" t="inlineStr">
@@ -12417,17 +12415,17 @@
       </c>
       <c r="O52" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="P52" s="7" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>5,976</t>
         </is>
       </c>
       <c r="Q52" s="6" t="inlineStr">
         <is>
-          <t>2.92%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
@@ -12439,7 +12437,7 @@
     <row r="53" ht="30" customHeight="1">
       <c r="A53" s="6" t="inlineStr">
         <is>
-          <t>케이피항공산업</t>
+          <t>세미티에스</t>
         </is>
       </c>
       <c r="B53" s="19" t="inlineStr">
@@ -12495,7 +12493,7 @@
       <c r="L53" s="6" t="inlineStr"/>
       <c r="M53" s="6" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="N53" s="6" t="inlineStr">
@@ -12523,323 +12521,341 @@
     <row r="54" ht="30" customHeight="1">
       <c r="A54" s="6" t="inlineStr">
         <is>
-          <t>삼성스팩13호</t>
-        </is>
-      </c>
-      <c r="B54" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
+          <t>덕양에너젠</t>
+        </is>
+      </c>
+      <c r="B54" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>8,500~10,000</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>6,000,000</t>
+          <t>7,500,000</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>12,000</t>
-        </is>
-      </c>
-      <c r="F54" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="G54" s="6" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
+          <t>75,000</t>
+        </is>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>30.32배 (EV/EBITDA)</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="n">
+        <v>10000</v>
       </c>
       <c r="H54" s="6" t="n">
-        <v>1159.11</v>
+        <v>650.14</v>
       </c>
       <c r="I54" s="6" t="n">
-        <v>1892</v>
+        <v>2324</v>
       </c>
       <c r="J54" s="6" t="inlineStr">
         <is>
-          <t>2026-01-12~01-13</t>
+          <t>2026-01-20~01-21</t>
         </is>
       </c>
       <c r="K54" s="6" t="inlineStr">
         <is>
-          <t>1,870.40</t>
+          <t>1,354.00</t>
         </is>
       </c>
       <c r="L54" s="6" t="inlineStr"/>
       <c r="M54" s="6" t="inlineStr">
         <is>
+          <t>2026-01-30</t>
+        </is>
+      </c>
+      <c r="N54" s="6" t="inlineStr">
+        <is>
+          <t>NH</t>
+        </is>
+      </c>
+      <c r="O54" s="6" t="inlineStr">
+        <is>
+          <t>미래</t>
+        </is>
+      </c>
+      <c r="P54" s="7" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>2.92%</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>상장완료</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>케이피항공산업</t>
+        </is>
+      </c>
+      <c r="B55" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="C55" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="D55" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="E55" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="F55" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="G55" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="H55" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="I55" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="J55" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="K55" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="L55" s="6" t="inlineStr"/>
+      <c r="M55" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-29</t>
+        </is>
+      </c>
+      <c r="N55" s="6" t="inlineStr">
+        <is>
+          <t>NH</t>
+        </is>
+      </c>
+      <c r="O55" s="6" t="inlineStr"/>
+      <c r="P55" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="Q55" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>상장완료(스팩합병)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="30" customHeight="1">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>삼성스팩13호</t>
+        </is>
+      </c>
+      <c r="B56" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>6,000,000</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>12,000</t>
+        </is>
+      </c>
+      <c r="F56" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="H56" s="6" t="n">
+        <v>1159.11</v>
+      </c>
+      <c r="I56" s="6" t="n">
+        <v>1892</v>
+      </c>
+      <c r="J56" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-12~01-13</t>
+        </is>
+      </c>
+      <c r="K56" s="6" t="inlineStr">
+        <is>
+          <t>1,870.40</t>
+        </is>
+      </c>
+      <c r="L56" s="6" t="inlineStr"/>
+      <c r="M56" s="6" t="inlineStr">
+        <is>
           <t>2026-01-21</t>
         </is>
       </c>
-      <c r="N54" s="6" t="inlineStr">
+      <c r="N56" s="6" t="inlineStr">
         <is>
           <t>삼성</t>
         </is>
       </c>
-      <c r="O54" s="6" t="inlineStr"/>
-      <c r="P54" s="7" t="inlineStr">
+      <c r="O56" s="6" t="inlineStr"/>
+      <c r="P56" s="7" t="inlineStr">
         <is>
           <t>360</t>
         </is>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
+      <c r="Q56" s="6" t="inlineStr">
         <is>
           <t>3.00%</t>
         </is>
       </c>
-      <c r="R54" s="6" t="inlineStr">
+      <c r="R56" s="6" t="inlineStr">
         <is>
           <t>상장완료</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="22" customHeight="1">
-      <c r="A56" s="3" t="inlineStr">
-        <is>
-          <t>■ 공모 진행 (예심 승인법인)  (41건)</t>
-        </is>
-      </c>
-      <c r="B56" s="4" t="n"/>
-      <c r="C56" s="4" t="n"/>
-      <c r="D56" s="4" t="n"/>
-      <c r="E56" s="4" t="n"/>
-      <c r="F56" s="4" t="n"/>
-      <c r="G56" s="4" t="n"/>
-      <c r="H56" s="4" t="n"/>
-      <c r="I56" s="4" t="n"/>
-      <c r="J56" s="4" t="n"/>
-      <c r="K56" s="4" t="n"/>
-      <c r="L56" s="4" t="n"/>
-      <c r="M56" s="4" t="n"/>
-      <c r="N56" s="4" t="n"/>
-      <c r="O56" s="4" t="n"/>
-      <c r="P56" s="4" t="n"/>
-      <c r="Q56" s="4" t="n"/>
-      <c r="R56" s="4" t="n"/>
-    </row>
-    <row r="57" ht="30" customHeight="1">
-      <c r="A57" s="6" t="inlineStr">
-        <is>
-          <t>케이비제34호스팩</t>
-        </is>
-      </c>
-      <c r="B57" s="6" t="inlineStr">
-        <is>
-          <t>09-04~09-07</t>
-        </is>
-      </c>
-      <c r="C57" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="D57" s="7" t="inlineStr">
-        <is>
-          <t>7,000,000</t>
-        </is>
-      </c>
-      <c r="E57" s="7" t="inlineStr">
-        <is>
-          <t>14,000,000,000</t>
-        </is>
-      </c>
-      <c r="F57" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="G57" s="6" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
-      </c>
-      <c r="H57" s="6" t="n">
-        <v>1232.51</v>
-      </c>
-      <c r="I57" s="6" t="n">
-        <v>2001</v>
-      </c>
-      <c r="J57" s="6" t="inlineStr">
-        <is>
-          <t>09-10~09-11</t>
-        </is>
-      </c>
-      <c r="K57" s="6" t="inlineStr">
-        <is>
-          <t>6,777.78</t>
-        </is>
-      </c>
-      <c r="L57" s="6" t="inlineStr"/>
-      <c r="M57" s="6" t="inlineStr"/>
-      <c r="N57" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="O57" s="6" t="inlineStr"/>
-      <c r="P57" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="Q57" s="6" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
-      </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>청약완료·상장대기</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>멜콘</t>
-        </is>
-      </c>
-      <c r="B58" s="6" t="inlineStr">
-        <is>
-          <t>09-16~09-22</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>10,700~12,300</t>
-        </is>
-      </c>
-      <c r="D58" s="7" t="inlineStr">
-        <is>
-          <t>2,500,000</t>
-        </is>
-      </c>
-      <c r="E58" s="7" t="inlineStr">
-        <is>
-          <t>30,750,000,000</t>
-        </is>
-      </c>
-      <c r="F58" s="6" t="inlineStr">
-        <is>
-          <t>26.18배 (PER)</t>
-        </is>
-      </c>
-      <c r="G58" s="6" t="inlineStr">
-        <is>
-          <t>12,300</t>
-        </is>
-      </c>
-      <c r="H58" s="6" t="n">
-        <v>1136.84</v>
-      </c>
-      <c r="I58" s="6" t="n">
-        <v>2405</v>
-      </c>
-      <c r="J58" s="6" t="inlineStr">
-        <is>
-          <t>10-01~10-02</t>
-        </is>
-      </c>
-      <c r="K58" s="6" t="inlineStr">
-        <is>
-          <t>4,284.98</t>
-        </is>
-      </c>
-      <c r="L58" s="6" t="inlineStr"/>
-      <c r="M58" s="6" t="inlineStr"/>
-      <c r="N58" s="6" t="inlineStr">
-        <is>
-          <t>대신증권</t>
-        </is>
-      </c>
-      <c r="O58" s="6" t="inlineStr"/>
-      <c r="P58" s="7" t="inlineStr">
-        <is>
-          <t>826,575,000</t>
-        </is>
-      </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>3.0%</t>
-        </is>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>청약완료·상장대기</t>
-        </is>
-      </c>
+    <row r="58" ht="22" customHeight="1">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>■ 공모 진행 (예심 승인법인)  (43건)</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="n"/>
+      <c r="C58" s="4" t="n"/>
+      <c r="D58" s="4" t="n"/>
+      <c r="E58" s="4" t="n"/>
+      <c r="F58" s="4" t="n"/>
+      <c r="G58" s="4" t="n"/>
+      <c r="H58" s="4" t="n"/>
+      <c r="I58" s="4" t="n"/>
+      <c r="J58" s="4" t="n"/>
+      <c r="K58" s="4" t="n"/>
+      <c r="L58" s="4" t="n"/>
+      <c r="M58" s="4" t="n"/>
+      <c r="N58" s="4" t="n"/>
+      <c r="O58" s="4" t="n"/>
+      <c r="P58" s="4" t="n"/>
+      <c r="Q58" s="4" t="n"/>
+      <c r="R58" s="4" t="n"/>
     </row>
     <row r="59" ht="30" customHeight="1">
       <c r="A59" s="6" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>케이비제34호스팩</t>
         </is>
       </c>
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>09-16~09-22</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>19,500~23,500</t>
+          <t>09-04~09-07</t>
+        </is>
+      </c>
+      <c r="C59" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>852,000</t>
+          <t>7,000,000</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>16,614,000,000</t>
-        </is>
-      </c>
-      <c r="F59" s="6" t="inlineStr">
-        <is>
-          <t>17.61배 (PER)</t>
+          <t>14,000,000,000</t>
+        </is>
+      </c>
+      <c r="F59" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="G59" s="6" t="inlineStr">
         <is>
-          <t>19,500</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="H59" s="6" t="n">
-        <v>1097.62</v>
+        <v>1232.51</v>
       </c>
       <c r="I59" s="6" t="n">
-        <v>2006</v>
+        <v>2001</v>
       </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
-          <t>10-02~10-06</t>
-        </is>
-      </c>
-      <c r="K59" s="6" t="inlineStr"/>
+          <t>09-10~09-11</t>
+        </is>
+      </c>
+      <c r="K59" s="6" t="inlineStr">
+        <is>
+          <t>6,777.78</t>
+        </is>
+      </c>
       <c r="L59" s="6" t="inlineStr"/>
       <c r="M59" s="6" t="inlineStr"/>
-      <c r="N59" s="6" t="inlineStr">
-        <is>
-          <t>하나증권</t>
+      <c r="N59" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="O59" s="6" t="inlineStr"/>
-      <c r="P59" s="7" t="inlineStr">
-        <is>
-          <t>697,788,000</t>
+      <c r="P59" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="Q59" s="6" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="R59" s="6" t="inlineStr">
@@ -12975,7 +12991,11 @@
           <t>10-12~10-13</t>
         </is>
       </c>
-      <c r="K61" s="6" t="inlineStr"/>
+      <c r="K61" s="6" t="inlineStr">
+        <is>
+          <t>5,383.48</t>
+        </is>
+      </c>
       <c r="L61" s="6" t="inlineStr"/>
       <c r="M61" s="6" t="inlineStr"/>
       <c r="N61" s="6" t="inlineStr">
@@ -12996,7 +13016,7 @@
       </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
-          <t>발행조건확정</t>
+          <t>청약완료·상장대기</t>
         </is>
       </c>
     </row>
@@ -13523,32 +13543,32 @@
     <row r="70" ht="30" customHeight="1">
       <c r="A70" s="6" t="inlineStr">
         <is>
-          <t>엠비디</t>
+          <t>아이엠스팩1호</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>10-16~10-22</t>
-        </is>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>9,600~11,700</t>
+          <t>10-19~10-20</t>
+        </is>
+      </c>
+      <c r="C70" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>19,200,000,000</t>
-        </is>
-      </c>
-      <c r="F70" s="6" t="inlineStr">
-        <is>
-          <t>26.87배 (PER)</t>
+          <t>10,000,000,000</t>
+        </is>
+      </c>
+      <c r="F70" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="G70" s="6" t="inlineStr"/>
@@ -13556,26 +13576,26 @@
       <c r="I70" s="6" t="inlineStr"/>
       <c r="J70" s="6" t="inlineStr">
         <is>
-          <t>10-28~10-29</t>
+          <t>10-26~10-27</t>
         </is>
       </c>
       <c r="K70" s="6" t="inlineStr"/>
       <c r="L70" s="6" t="inlineStr"/>
       <c r="M70" s="6" t="inlineStr"/>
-      <c r="N70" s="6" t="inlineStr">
-        <is>
-          <t>하나증권</t>
+      <c r="N70" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="O70" s="6" t="inlineStr"/>
-      <c r="P70" s="7" t="inlineStr">
-        <is>
-          <t>988,800,000</t>
+      <c r="P70" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="Q70" s="6" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="R70" s="6" t="inlineStr">
@@ -13587,32 +13607,32 @@
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>아이엠스팩1호</t>
+          <t>에이엘로봇</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>10-19~10-20</t>
-        </is>
-      </c>
-      <c r="C71" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>10-28~11-03</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>15,700~17,600</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>2,400,000</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>10,000,000,000</t>
-        </is>
-      </c>
-      <c r="F71" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>37,680,000,000</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>37.17배 (PER)</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr"/>
@@ -13620,26 +13640,26 @@
       <c r="I71" s="6" t="inlineStr"/>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>10-26~10-27</t>
+          <t>11-06~11-09</t>
         </is>
       </c>
       <c r="K71" s="6" t="inlineStr"/>
       <c r="L71" s="6" t="inlineStr"/>
       <c r="M71" s="6" t="inlineStr"/>
-      <c r="N71" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="N71" s="6" t="inlineStr">
+        <is>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="O71" s="6" t="inlineStr"/>
-      <c r="P71" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P71" s="7" t="inlineStr">
+        <is>
+          <t>1,160,399,874</t>
         </is>
       </c>
       <c r="Q71" s="6" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="R71" s="6" t="inlineStr">
@@ -13651,32 +13671,32 @@
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>에이엘로봇</t>
+          <t>엠비디</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>10-28~11-03</t>
+          <t>11-02~11-06</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>15,700~17,600</t>
+          <t>9,600~11,700</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>2,400,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>37,680,000,000</t>
+          <t>19,200,000,000</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>37.17배 (PER)</t>
+          <t>27.36배 (PER)</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr"/>
@@ -13684,7 +13704,7 @@
       <c r="I72" s="6" t="inlineStr"/>
       <c r="J72" s="6" t="inlineStr">
         <is>
-          <t>11-06~11-09</t>
+          <t>11-12~11-13</t>
         </is>
       </c>
       <c r="K72" s="6" t="inlineStr"/>
@@ -13692,18 +13712,18 @@
       <c r="M72" s="6" t="inlineStr"/>
       <c r="N72" s="6" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>하나증권</t>
         </is>
       </c>
       <c r="O72" s="6" t="inlineStr"/>
       <c r="P72" s="7" t="inlineStr">
         <is>
-          <t>1,160,399,874</t>
+          <t>988,800,000</t>
         </is>
       </c>
       <c r="Q72" s="6" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="R72" s="6" t="inlineStr">
@@ -13804,7 +13824,7 @@
       </c>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>24.95배 (PER)</t>
+          <t>25.27배 (PER)</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr"/>
@@ -15312,22 +15332,278 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="20" t="inlineStr">
+    <row r="98" ht="30" customHeight="1">
+      <c r="A98" s="6" t="inlineStr">
+        <is>
+          <t>인터엑스</t>
+        </is>
+      </c>
+      <c r="B98" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="C98" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="D98" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="E98" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="F98" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="inlineStr"/>
+      <c r="H98" s="6" t="inlineStr"/>
+      <c r="I98" s="6" t="inlineStr"/>
+      <c r="J98" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="K98" s="6" t="inlineStr"/>
+      <c r="L98" s="6" t="inlineStr"/>
+      <c r="M98" s="6" t="inlineStr"/>
+      <c r="N98" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="O98" s="6" t="inlineStr"/>
+      <c r="P98" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="Q98" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="R98" s="6" t="inlineStr">
+        <is>
+          <t>신고서 대기</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="30" customHeight="1">
+      <c r="A99" s="6" t="inlineStr">
+        <is>
+          <t>씨아이에스케미칼</t>
+        </is>
+      </c>
+      <c r="B99" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="C99" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="D99" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="E99" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="F99" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="G99" s="6" t="inlineStr"/>
+      <c r="H99" s="6" t="inlineStr"/>
+      <c r="I99" s="6" t="inlineStr"/>
+      <c r="J99" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="K99" s="6" t="inlineStr"/>
+      <c r="L99" s="6" t="inlineStr"/>
+      <c r="M99" s="6" t="inlineStr"/>
+      <c r="N99" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="O99" s="6" t="inlineStr"/>
+      <c r="P99" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="Q99" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="R99" s="6" t="inlineStr">
+        <is>
+          <t>신고서 대기</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="30" customHeight="1">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>이노보테라퓨틱스</t>
+        </is>
+      </c>
+      <c r="B100" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="C100" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="D100" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="E100" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="F100" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="G100" s="6" t="inlineStr"/>
+      <c r="H100" s="6" t="inlineStr"/>
+      <c r="I100" s="6" t="inlineStr"/>
+      <c r="J100" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="K100" s="6" t="inlineStr"/>
+      <c r="L100" s="6" t="inlineStr"/>
+      <c r="M100" s="6" t="inlineStr"/>
+      <c r="N100" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="O100" s="6" t="inlineStr"/>
+      <c r="P100" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="Q100" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="R100" s="6" t="inlineStr">
+        <is>
+          <t>신고서 대기</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="30" customHeight="1">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>이나인페이</t>
+        </is>
+      </c>
+      <c r="B101" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="C101" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="D101" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="E101" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="F101" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="G101" s="6" t="inlineStr"/>
+      <c r="H101" s="6" t="inlineStr"/>
+      <c r="I101" s="6" t="inlineStr"/>
+      <c r="J101" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="K101" s="6" t="inlineStr"/>
+      <c r="L101" s="6" t="inlineStr"/>
+      <c r="M101" s="6" t="inlineStr"/>
+      <c r="N101" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="O101" s="6" t="inlineStr"/>
+      <c r="P101" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="Q101" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="R101" s="6" t="inlineStr">
+        <is>
+          <t>신고서 대기</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="20" t="inlineStr">
         <is>
           <t>※ 상장 완료 = KIND 신규상장 페이지 기준(스팩합병 포함) · 스팩 공모상장은 밴드·밸류에이션 등 해당없음(공모가 2,000원 고정).</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="20" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="20" t="inlineStr">
         <is>
           <t>※ 기재정정 신고서 내 정정 전·후 병존 → 자동수집은 "정정 후" 값만 취함.</t>
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="20" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="20" t="inlineStr">
         <is>
           <t>※ 청약경쟁률=일반투자자 청약수량÷최종배정수량 · "MM-DD~"는 종료일 자동수집 예정.</t>
         </is>
@@ -15630,13 +15906,13 @@
         <v>3</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D15" s="6" t="n">
         <v>1</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F15" s="21">
         <f>IF((C15+D15)=0,"-",C15/(C15+D15))</f>
@@ -15699,30 +15975,30 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>284,014,000,000</t>
+          <t>299,100,000,000</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>268,350,000,000</t>
+          <t>284,014,000,000</t>
         </is>
       </c>
     </row>
@@ -15819,37 +16095,37 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>DB증권</t>
+          <t>하나증권</t>
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>46,000,000,000</t>
+          <t>52,428,000,000</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>NH투자증권</t>
+          <t>DB증권</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>41,420,000,000</t>
+          <t>46,000,000,000</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>삼성증권㈜</t>
+          <t>NH투자증권</t>
         </is>
       </c>
       <c r="B30" s="6" t="n">
@@ -15857,22 +16133,22 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>39,060,000,000</t>
+          <t>41,420,000,000</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>하나증권</t>
+          <t>삼성증권㈜</t>
         </is>
       </c>
       <c r="B31" s="6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>35,814,000,000</t>
+          <t>39,060,000,000</t>
         </is>
       </c>
     </row>

--- a/IPO_analysis.xlsx
+++ b/IPO_analysis.xlsx
@@ -618,14 +618,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>기준일 2026-10-15 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
+          <t>기준일 2026-10-16 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>■ 심사 신청(진행중)  (34건)</t>
+          <t>■ 심사 신청(진행중)  (33건)</t>
         </is>
       </c>
       <c r="B4" s="4" t="n"/>
@@ -1746,17 +1746,17 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>에스에프씨</t>
+          <t>에버온</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>유가</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
@@ -1771,27 +1771,27 @@
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>160,792</t>
+          <t>65,225</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>25,509</t>
+          <t>-3,606</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>243,562</t>
+          <t>54,955</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>전기업</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>미래, 한국</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K25" s="6" t="inlineStr">
@@ -1803,12 +1803,12 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>에버온</t>
+          <t>엠디에스코리아</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -1828,22 +1828,22 @@
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>65,225</t>
+          <t>97,972</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>-3,606</t>
+          <t>6,512</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>54,955</t>
+          <t>53,818</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>전기업</t>
+          <t>기타 식품 제조업</t>
         </is>
       </c>
       <c r="J26" s="6" t="inlineStr">
@@ -1860,12 +1860,12 @@
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>엠디에스코리아</t>
+          <t>동승</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -1885,27 +1885,27 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>97,972</t>
+          <t>78,625</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>6,512</t>
+          <t>14,525</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>53,818</t>
+          <t>5,438</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>기타 식품 제조업</t>
+          <t>부동산 임대 및 공급업</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>동승</t>
+          <t>에프엠더블유</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -1942,27 +1942,27 @@
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>78,625</t>
+          <t>30,282</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>14,525</t>
+          <t>4,762</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>5,438</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>부동산 임대 및 공급업</t>
+          <t>기타 식품 제조업</t>
         </is>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>유진</t>
         </is>
       </c>
       <c r="K28" s="6" t="inlineStr">
@@ -1974,22 +1974,22 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>에프엠더블유</t>
+          <t>소노인터내셔널</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>유가</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
@@ -1999,27 +1999,27 @@
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>30,282</t>
+          <t>2,093,051</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>4,762</t>
+          <t>-148,064</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>852,372</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>기타 식품 제조업</t>
+          <t>일반 및 생활 숙박시설 운영업</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>유진</t>
+          <t>대신, 미래</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
@@ -2031,17 +2031,17 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>소노인터내셔널</t>
+          <t>싸이몬</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>유가</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
@@ -2056,27 +2056,27 @@
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>2,093,051</t>
+          <t>48,695</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>-148,064</t>
+          <t>15,714</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>852,372</t>
+          <t>61,761</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>일반 및 생활 숙박시설 운영업</t>
+          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>대신, 미래</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
@@ -2088,12 +2088,12 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>싸이몬</t>
+          <t>바이다</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -2113,27 +2113,27 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>48,695</t>
+          <t>14,432</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>15,714</t>
+          <t>-3,951</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>61,761</t>
+          <t>15,108</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업</t>
+          <t>전자부품 제조업</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K31" s="6" t="inlineStr">
@@ -2145,12 +2145,12 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>바이다</t>
+          <t>아이알큐더스</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -2170,27 +2170,27 @@
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>14,432</t>
+          <t>10,231</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>-3,951</t>
+          <t>-986</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>15,108</t>
+          <t>1,800</t>
         </is>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>전자부품 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="K32" s="6" t="inlineStr">
@@ -2202,12 +2202,12 @@
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>아이알큐더스</t>
+          <t>씨엔티테크</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -2227,17 +2227,17 @@
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>10,231</t>
+          <t>27,015</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>-986</t>
+          <t>3,987</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>1,800</t>
+          <t>2,613</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
@@ -2247,7 +2247,7 @@
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>한화, 하나</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
@@ -2259,12 +2259,12 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>씨엔티테크</t>
+          <t>삼홍아크튜리온</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -2284,27 +2284,27 @@
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>27,015</t>
+          <t>26,162</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>3,987</t>
+          <t>-10,314</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>2,613</t>
+          <t>6,369</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
         </is>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>한화, 하나</t>
+          <t>삼성, 미래</t>
         </is>
       </c>
       <c r="K34" s="6" t="inlineStr">
@@ -2316,12 +2316,12 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>삼홍아크튜리온</t>
+          <t>비앤비코리아</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
@@ -2341,27 +2341,27 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>26,162</t>
+          <t>141,169</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>-10,314</t>
+          <t>21,406</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>6,369</t>
+          <t>43,932</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>삼성, 미래</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K35" s="6" t="inlineStr">
@@ -2373,12 +2373,12 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>비앤비코리아</t>
+          <t>오토핸즈</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -2398,22 +2398,22 @@
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>141,169</t>
+          <t>238,564</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>21,406</t>
+          <t>6,047</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>43,932</t>
+          <t>6,129</t>
         </is>
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>자동차 판매업</t>
         </is>
       </c>
       <c r="J36" s="6" t="inlineStr">
@@ -2430,12 +2430,12 @@
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>오토핸즈</t>
+          <t>아이벡스메디칼시스템즈</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
@@ -2455,27 +2455,27 @@
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>238,564</t>
+          <t>15,282</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>6,047</t>
+          <t>-7,227</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>6,129</t>
+          <t>744</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>자동차 판매업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
@@ -2487,12 +2487,12 @@
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>아이벡스메디칼시스템즈</t>
+          <t>피지티</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
@@ -2512,27 +2512,27 @@
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>15,282</t>
+          <t>40,141</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
         <is>
-          <t>-7,227</t>
+          <t>-69,722</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>6,029</t>
         </is>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K38" s="6" t="inlineStr">
@@ -2541,134 +2541,134 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>피지티</t>
-        </is>
-      </c>
-      <c r="C39" s="6" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>■ 심사 승인  (85건)</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n"/>
+      <c r="C40" s="4" t="n"/>
+      <c r="D40" s="4" t="n"/>
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="4" t="n"/>
+      <c r="G40" s="4" t="n"/>
+      <c r="H40" s="4" t="n"/>
+      <c r="I40" s="4" t="n"/>
+      <c r="J40" s="4" t="n"/>
+      <c r="K40" s="4" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>일자</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>회사명</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>시장</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>상장유형</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>기준연도</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>자기자본</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>업종</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>대표주관사</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>현황</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>인터엑스</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>코스닥</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="D42" s="6" t="inlineStr">
         <is>
           <t>신규상장</t>
         </is>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="E42" s="6" t="inlineStr">
         <is>
           <t>FY25</t>
         </is>
       </c>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>40,141</t>
-        </is>
-      </c>
-      <c r="G39" s="7" t="inlineStr">
-        <is>
-          <t>-69,722</t>
-        </is>
-      </c>
-      <c r="H39" s="7" t="inlineStr">
-        <is>
-          <t>6,029</t>
-        </is>
-      </c>
-      <c r="I39" s="6" t="inlineStr">
-        <is>
-          <t>기타 화학제품 제조업</t>
-        </is>
-      </c>
-      <c r="J39" s="6" t="inlineStr">
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>8,645</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>-20,272</t>
+        </is>
+      </c>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>4,530</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>소프트웨어 개발 및 공급업</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr">
         <is>
           <t>한국</t>
         </is>
       </c>
-      <c r="K39" s="6" t="inlineStr">
-        <is>
-          <t>예심 진행중</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>■ 심사 승인  (84건)</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="n"/>
-      <c r="C41" s="4" t="n"/>
-      <c r="D41" s="4" t="n"/>
-      <c r="E41" s="4" t="n"/>
-      <c r="F41" s="4" t="n"/>
-      <c r="G41" s="4" t="n"/>
-      <c r="H41" s="4" t="n"/>
-      <c r="I41" s="4" t="n"/>
-      <c r="J41" s="4" t="n"/>
-      <c r="K41" s="4" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>일자</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>회사명</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>시장</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>상장유형</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>기준연도</t>
-        </is>
-      </c>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="inlineStr">
-        <is>
-          <t>순이익</t>
-        </is>
-      </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>자기자본</t>
-        </is>
-      </c>
-      <c r="I42" s="5" t="inlineStr">
-        <is>
-          <t>업종</t>
-        </is>
-      </c>
-      <c r="J42" s="5" t="inlineStr">
-        <is>
-          <t>대표주관사</t>
-        </is>
-      </c>
-      <c r="K42" s="5" t="inlineStr">
-        <is>
-          <t>현황</t>
+      <c r="K42" s="6" t="inlineStr">
+        <is>
+          <t>상장전</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>인터엑스</t>
+          <t>씨아이에스케미칼</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
@@ -2700,27 +2700,27 @@
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>8,645</t>
+          <t>15,985</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
         <is>
-          <t>-20,272</t>
+          <t>-11,440</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
         <is>
-          <t>4,530</t>
+          <t>23,706</t>
         </is>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>기초 화학물질 제조업</t>
         </is>
       </c>
       <c r="J43" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="K43" s="6" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>씨아이에스케미칼</t>
+          <t>에스에프씨</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>유가</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
@@ -2757,27 +2757,27 @@
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>15,985</t>
+          <t>160,792</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
         <is>
-          <t>-11,440</t>
+          <t>25,509</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
-          <t>23,706</t>
+          <t>243,562</t>
         </is>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>기초 화학물질 제조업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>미래, 한국</t>
         </is>
       </c>
       <c r="K44" s="6" t="inlineStr">
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K76" s="6" t="inlineStr">
         <is>
-          <t>상장전</t>
+          <t>상장승인(상장예정)</t>
         </is>
       </c>
     </row>
@@ -8521,7 +8521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R105"/>
+  <dimension ref="A1:R106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -12767,7 +12767,7 @@
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>■ 공모 진행 (예심 승인법인)  (43건)</t>
+          <t>■ 공모 진행 (예심 승인법인)  (44건)</t>
         </is>
       </c>
       <c r="B58" s="4" t="n"/>
@@ -13023,67 +13023,67 @@
     <row r="62" ht="30" customHeight="1">
       <c r="A62" s="6" t="inlineStr">
         <is>
-          <t>에스케이증권제14호기업인수목적</t>
+          <t>티앤이코리아</t>
         </is>
       </c>
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>10-12~10-13</t>
-        </is>
-      </c>
-      <c r="C62" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>10-07~10-14</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>12,600~15,300</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>6,500,000</t>
+          <t>2,400,000</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>13,000,000,000</t>
-        </is>
-      </c>
-      <c r="F62" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>36,720,000,000</t>
+        </is>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
+        <is>
+          <t>19.48배 (PER)</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>15,300</t>
         </is>
       </c>
       <c r="H62" s="6" t="n">
-        <v>1228.38</v>
+        <v>1041.02</v>
       </c>
       <c r="I62" s="6" t="n">
-        <v>1945</v>
+        <v>2274</v>
       </c>
       <c r="J62" s="6" t="inlineStr">
         <is>
-          <t>10-15~10-16</t>
+          <t>10-20~10-21</t>
         </is>
       </c>
       <c r="K62" s="6" t="inlineStr"/>
       <c r="L62" s="6" t="inlineStr"/>
       <c r="M62" s="6" t="inlineStr"/>
-      <c r="N62" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="N62" s="6" t="inlineStr">
+        <is>
+          <t>신한투자증권</t>
         </is>
       </c>
       <c r="O62" s="6" t="inlineStr"/>
-      <c r="P62" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P62" s="7" t="inlineStr">
+        <is>
+          <t>1,245,888,000</t>
         </is>
       </c>
       <c r="Q62" s="6" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="R62" s="6" t="inlineStr">
@@ -13095,64 +13095,72 @@
     <row r="63" ht="30" customHeight="1">
       <c r="A63" s="6" t="inlineStr">
         <is>
-          <t>티앤이코리아</t>
+          <t>에스케이증권제14호기업인수목적</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>10-07~10-14</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>12,600~15,300</t>
+          <t>10-12~10-13</t>
+        </is>
+      </c>
+      <c r="C63" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>2,400,000</t>
+          <t>6,500,000</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>30,240,000,000</t>
-        </is>
-      </c>
-      <c r="F63" s="6" t="inlineStr">
-        <is>
-          <t>19.48배 (PER)</t>
-        </is>
-      </c>
-      <c r="G63" s="6" t="inlineStr"/>
-      <c r="H63" s="6" t="inlineStr"/>
-      <c r="I63" s="6" t="inlineStr"/>
+          <t>13,000,000,000</t>
+        </is>
+      </c>
+      <c r="F63" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="H63" s="6" t="n">
+        <v>1228.38</v>
+      </c>
+      <c r="I63" s="6" t="n">
+        <v>1945</v>
+      </c>
       <c r="J63" s="6" t="inlineStr">
         <is>
-          <t>10-20~10-21</t>
+          <t>10-15~10-16</t>
         </is>
       </c>
       <c r="K63" s="6" t="inlineStr"/>
       <c r="L63" s="6" t="inlineStr"/>
       <c r="M63" s="6" t="inlineStr"/>
-      <c r="N63" s="6" t="inlineStr">
-        <is>
-          <t>신한투자증권</t>
+      <c r="N63" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="O63" s="6" t="inlineStr"/>
-      <c r="P63" s="7" t="inlineStr">
-        <is>
-          <t>1,245,888,000</t>
+      <c r="P63" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="Q63" s="6" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="R63" s="6" t="inlineStr">
         <is>
-          <t>정정</t>
+          <t>발행조건확정</t>
         </is>
       </c>
     </row>
@@ -13607,32 +13615,32 @@
     <row r="71" ht="30" customHeight="1">
       <c r="A71" s="6" t="inlineStr">
         <is>
-          <t>에이엘로봇</t>
+          <t>넥스아이</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>10-28~11-03</t>
+          <t>10-22~10-28</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>15,700~17,600</t>
+          <t>10,500~13,000</t>
         </is>
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>2,400,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>37,680,000,000</t>
+          <t>52,500,000,000</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>37.17배 (PER)</t>
+          <t>19.15배 (PER)</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr"/>
@@ -13640,7 +13648,7 @@
       <c r="I71" s="6" t="inlineStr"/>
       <c r="J71" s="6" t="inlineStr">
         <is>
-          <t>11-06~11-09</t>
+          <t>11-03~11-04</t>
         </is>
       </c>
       <c r="K71" s="6" t="inlineStr"/>
@@ -13648,18 +13656,18 @@
       <c r="M71" s="6" t="inlineStr"/>
       <c r="N71" s="6" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="O71" s="6" t="inlineStr"/>
       <c r="P71" s="7" t="inlineStr">
         <is>
-          <t>1,160,399,874</t>
+          <t>2,407,500,000</t>
         </is>
       </c>
       <c r="Q71" s="6" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="R71" s="6" t="inlineStr">
@@ -13671,32 +13679,32 @@
     <row r="72" ht="30" customHeight="1">
       <c r="A72" s="6" t="inlineStr">
         <is>
-          <t>엠비디</t>
+          <t>에이엘로봇</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>11-02~11-06</t>
+          <t>10-28~11-03</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>9,600~11,700</t>
+          <t>15,700~17,600</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>2,400,000</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>19,200,000,000</t>
+          <t>37,680,000,000</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>27.36배 (PER)</t>
+          <t>37.17배 (PER)</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr"/>
@@ -13704,7 +13712,7 @@
       <c r="I72" s="6" t="inlineStr"/>
       <c r="J72" s="6" t="inlineStr">
         <is>
-          <t>11-12~11-13</t>
+          <t>11-06~11-09</t>
         </is>
       </c>
       <c r="K72" s="6" t="inlineStr"/>
@@ -13712,18 +13720,18 @@
       <c r="M72" s="6" t="inlineStr"/>
       <c r="N72" s="6" t="inlineStr">
         <is>
-          <t>하나증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="O72" s="6" t="inlineStr"/>
       <c r="P72" s="7" t="inlineStr">
         <is>
-          <t>988,800,000</t>
+          <t>1,160,399,874</t>
         </is>
       </c>
       <c r="Q72" s="6" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="R72" s="6" t="inlineStr">
@@ -13735,7 +13743,7 @@
     <row r="73" ht="30" customHeight="1">
       <c r="A73" s="6" t="inlineStr">
         <is>
-          <t>다비오</t>
+          <t>엠비디</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
@@ -13745,22 +13753,22 @@
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>12,300~16,600</t>
+          <t>9,600~11,700</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>1,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>12,300,000,000</t>
+          <t>19,200,000,000</t>
         </is>
       </c>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>26.70배 (PER)</t>
+          <t>27.36배 (PER)</t>
         </is>
       </c>
       <c r="G73" s="6" t="inlineStr"/>
@@ -13768,7 +13776,7 @@
       <c r="I73" s="6" t="inlineStr"/>
       <c r="J73" s="6" t="inlineStr">
         <is>
-          <t>11-10~11-11</t>
+          <t>11-12~11-13</t>
         </is>
       </c>
       <c r="K73" s="6" t="inlineStr"/>
@@ -13776,18 +13784,18 @@
       <c r="M73" s="6" t="inlineStr"/>
       <c r="N73" s="6" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>하나증권</t>
         </is>
       </c>
       <c r="O73" s="6" t="inlineStr"/>
       <c r="P73" s="7" t="inlineStr">
         <is>
-          <t>570,105,000</t>
+          <t>988,800,000</t>
         </is>
       </c>
       <c r="Q73" s="6" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="R73" s="6" t="inlineStr">
@@ -13799,59 +13807,59 @@
     <row r="74" ht="30" customHeight="1">
       <c r="A74" s="6" t="inlineStr">
         <is>
-          <t>바로팜</t>
-        </is>
-      </c>
-      <c r="B74" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>다비오</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>11-02~11-06</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>16,400~20,200</t>
+          <t>12,300~16,600</t>
         </is>
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>1,780,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>29,192,000,000</t>
+          <t>12,300,000,000</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>25.27배 (PER)</t>
+          <t>26.70배 (PER)</t>
         </is>
       </c>
       <c r="G74" s="6" t="inlineStr"/>
       <c r="H74" s="6" t="inlineStr"/>
       <c r="I74" s="6" t="inlineStr"/>
-      <c r="J74" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="J74" s="6" t="inlineStr">
+        <is>
+          <t>11-10~11-11</t>
         </is>
       </c>
       <c r="K74" s="6" t="inlineStr"/>
       <c r="L74" s="6" t="inlineStr"/>
       <c r="M74" s="6" t="inlineStr"/>
-      <c r="N74" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="N74" s="6" t="inlineStr">
+        <is>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="O74" s="6" t="inlineStr"/>
-      <c r="P74" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="Q74" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P74" s="7" t="inlineStr">
+        <is>
+          <t>570,105,000</t>
+        </is>
+      </c>
+      <c r="Q74" s="6" t="inlineStr">
+        <is>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="R74" s="6" t="inlineStr">
@@ -13863,54 +13871,54 @@
     <row r="75" ht="30" customHeight="1">
       <c r="A75" s="6" t="inlineStr">
         <is>
-          <t>셀트릭스</t>
-        </is>
-      </c>
-      <c r="B75" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="C75" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="D75" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="E75" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="F75" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>하나에어로다이내믹스</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>11-02~11-06</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>4,700~5,700</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>4,400,000</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>20,680,000,000</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>17.89배 (EV/EBITDA)</t>
         </is>
       </c>
       <c r="G75" s="6" t="inlineStr"/>
       <c r="H75" s="6" t="inlineStr"/>
       <c r="I75" s="6" t="inlineStr"/>
-      <c r="J75" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="J75" s="6" t="inlineStr">
+        <is>
+          <t>11-10~11-11</t>
         </is>
       </c>
       <c r="K75" s="6" t="inlineStr"/>
       <c r="L75" s="6" t="inlineStr"/>
       <c r="M75" s="6" t="inlineStr"/>
-      <c r="N75" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="N75" s="6" t="inlineStr">
+        <is>
+          <t>아이비케이투자증권</t>
         </is>
       </c>
       <c r="O75" s="6" t="inlineStr"/>
-      <c r="P75" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P75" s="7" t="inlineStr">
+        <is>
+          <t>850,000,000</t>
         </is>
       </c>
       <c r="Q75" s="18" t="inlineStr">
@@ -13927,7 +13935,7 @@
     <row r="76" ht="30" customHeight="1">
       <c r="A76" s="6" t="inlineStr">
         <is>
-          <t>솔리스</t>
+          <t>바로팜</t>
         </is>
       </c>
       <c r="B76" s="18" t="inlineStr">
@@ -13935,24 +13943,24 @@
           <t>수집예정</t>
         </is>
       </c>
-      <c r="C76" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="D76" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="E76" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="F76" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>16,400~20,200</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>1,780,000</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>29,192,000,000</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>25.27배 (PER)</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr"/>
@@ -13991,209 +13999,209 @@
     <row r="77" ht="30" customHeight="1">
       <c r="A77" s="6" t="inlineStr">
         <is>
-          <t>옵토닉스</t>
-        </is>
-      </c>
-      <c r="B77" s="6" t="inlineStr">
-        <is>
-          <t>10-21~10-27</t>
-        </is>
-      </c>
-      <c r="C77" s="6" t="inlineStr">
-        <is>
-          <t>10,000~12,000</t>
-        </is>
-      </c>
-      <c r="D77" s="7" t="inlineStr">
-        <is>
-          <t>2,200,000</t>
-        </is>
-      </c>
-      <c r="E77" s="7" t="inlineStr">
-        <is>
-          <t>22,000,000,000</t>
-        </is>
-      </c>
-      <c r="F77" s="6" t="inlineStr">
-        <is>
-          <t>25.27배 (EV/EBITDA)</t>
+          <t>셀트릭스</t>
+        </is>
+      </c>
+      <c r="B77" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="C77" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="D77" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="E77" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="F77" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="G77" s="6" t="inlineStr"/>
       <c r="H77" s="6" t="inlineStr"/>
       <c r="I77" s="6" t="inlineStr"/>
-      <c r="J77" s="6" t="inlineStr">
-        <is>
-          <t>11-05~11-06</t>
+      <c r="J77" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="K77" s="6" t="inlineStr"/>
       <c r="L77" s="6" t="inlineStr"/>
       <c r="M77" s="6" t="inlineStr"/>
-      <c r="N77" s="6" t="inlineStr">
-        <is>
-          <t>한국투자증권</t>
+      <c r="N77" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="O77" s="6" t="inlineStr"/>
-      <c r="P77" s="7" t="inlineStr">
-        <is>
-          <t>1,133,000,000</t>
-        </is>
-      </c>
-      <c r="Q77" s="6" t="inlineStr">
-        <is>
-          <t>5.0%</t>
+      <c r="P77" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="Q77" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="R77" s="6" t="inlineStr">
         <is>
-          <t>최초</t>
+          <t>정정</t>
         </is>
       </c>
     </row>
     <row r="78" ht="30" customHeight="1">
       <c r="A78" s="6" t="inlineStr">
         <is>
-          <t>동원파츠</t>
-        </is>
-      </c>
-      <c r="B78" s="6" t="inlineStr">
-        <is>
-          <t>10-22~10-28</t>
-        </is>
-      </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>23,000~26,500</t>
-        </is>
-      </c>
-      <c r="D78" s="7" t="inlineStr">
-        <is>
-          <t>2,030,000</t>
-        </is>
-      </c>
-      <c r="E78" s="7" t="inlineStr">
-        <is>
-          <t>46,690,000,000</t>
-        </is>
-      </c>
-      <c r="F78" s="6" t="inlineStr">
-        <is>
-          <t>22.91배 (PER)</t>
+          <t>럭스코</t>
+        </is>
+      </c>
+      <c r="B78" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="C78" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="D78" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="E78" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="F78" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="G78" s="6" t="inlineStr"/>
       <c r="H78" s="6" t="inlineStr"/>
       <c r="I78" s="6" t="inlineStr"/>
-      <c r="J78" s="6" t="inlineStr">
-        <is>
-          <t>11-02~11-03</t>
+      <c r="J78" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="K78" s="6" t="inlineStr"/>
       <c r="L78" s="6" t="inlineStr"/>
       <c r="M78" s="6" t="inlineStr"/>
-      <c r="N78" s="6" t="inlineStr">
-        <is>
-          <t>삼성증권</t>
+      <c r="N78" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="O78" s="6" t="inlineStr"/>
-      <c r="P78" s="7" t="inlineStr">
-        <is>
-          <t>1,430,699,820</t>
-        </is>
-      </c>
-      <c r="Q78" s="6" t="inlineStr">
-        <is>
-          <t>3.0%</t>
+      <c r="P78" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="Q78" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="R78" s="6" t="inlineStr">
         <is>
-          <t>최초</t>
+          <t>정정</t>
         </is>
       </c>
     </row>
     <row r="79" ht="30" customHeight="1">
       <c r="A79" s="6" t="inlineStr">
         <is>
-          <t>넥스아이</t>
-        </is>
-      </c>
-      <c r="B79" s="6" t="inlineStr">
-        <is>
-          <t>10-22~10-28</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>10,500~13,000</t>
-        </is>
-      </c>
-      <c r="D79" s="7" t="inlineStr">
-        <is>
-          <t>5,000,000</t>
-        </is>
-      </c>
-      <c r="E79" s="7" t="inlineStr">
-        <is>
-          <t>52,500,000,000</t>
-        </is>
-      </c>
-      <c r="F79" s="6" t="inlineStr">
-        <is>
-          <t>19.15배 (PER)</t>
+          <t>솔리스</t>
+        </is>
+      </c>
+      <c r="B79" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="C79" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="D79" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="E79" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="F79" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="G79" s="6" t="inlineStr"/>
       <c r="H79" s="6" t="inlineStr"/>
       <c r="I79" s="6" t="inlineStr"/>
-      <c r="J79" s="6" t="inlineStr">
-        <is>
-          <t>11-03~11-04</t>
+      <c r="J79" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="K79" s="6" t="inlineStr"/>
       <c r="L79" s="6" t="inlineStr"/>
       <c r="M79" s="6" t="inlineStr"/>
-      <c r="N79" s="6" t="inlineStr">
-        <is>
-          <t>한국투자증권</t>
+      <c r="N79" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="O79" s="6" t="inlineStr"/>
-      <c r="P79" s="7" t="inlineStr">
-        <is>
-          <t>2,407,500,000</t>
-        </is>
-      </c>
-      <c r="Q79" s="6" t="inlineStr">
-        <is>
-          <t>4.5%</t>
+      <c r="P79" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="Q79" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="R79" s="6" t="inlineStr">
         <is>
-          <t>최초</t>
+          <t>정정</t>
         </is>
       </c>
     </row>
     <row r="80" ht="30" customHeight="1">
       <c r="A80" s="6" t="inlineStr">
         <is>
-          <t>제논</t>
+          <t>옵토닉스</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>10-26~10-30</t>
+          <t>10-21~10-27</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>9,700~12,200</t>
+          <t>10,000~12,000</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
@@ -14203,12 +14211,12 @@
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>21,340,000,000</t>
+          <t>22,000,000,000</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr">
         <is>
-          <t>36.49배 (PER)</t>
+          <t>25.27배 (EV/EBITDA)</t>
         </is>
       </c>
       <c r="G80" s="6" t="inlineStr"/>
@@ -14216,7 +14224,7 @@
       <c r="I80" s="6" t="inlineStr"/>
       <c r="J80" s="6" t="inlineStr">
         <is>
-          <t>11-04~11-05</t>
+          <t>11-05~11-06</t>
         </is>
       </c>
       <c r="K80" s="6" t="inlineStr"/>
@@ -14224,18 +14232,18 @@
       <c r="M80" s="6" t="inlineStr"/>
       <c r="N80" s="6" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="O80" s="6" t="inlineStr"/>
       <c r="P80" s="7" t="inlineStr">
         <is>
-          <t>835,247,600</t>
+          <t>1,133,000,000</t>
         </is>
       </c>
       <c r="Q80" s="6" t="inlineStr">
         <is>
-          <t>3.80%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="R80" s="6" t="inlineStr">
@@ -14247,27 +14255,27 @@
     <row r="81" ht="30" customHeight="1">
       <c r="A81" s="6" t="inlineStr">
         <is>
-          <t>영광와이케이엠씨</t>
+          <t>동원파츠</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>10-27~11-02</t>
+          <t>10-22~10-28</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>9,400~11,000</t>
+          <t>23,000~26,500</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>2,300,000</t>
+          <t>2,030,000</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>21,620,000,000</t>
+          <t>46,690,000,000</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr">
@@ -14280,7 +14288,7 @@
       <c r="I81" s="6" t="inlineStr"/>
       <c r="J81" s="6" t="inlineStr">
         <is>
-          <t>11-04~11-05</t>
+          <t>11-02~11-03</t>
         </is>
       </c>
       <c r="K81" s="6" t="inlineStr"/>
@@ -14288,18 +14296,18 @@
       <c r="M81" s="6" t="inlineStr"/>
       <c r="N81" s="6" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="O81" s="6" t="inlineStr"/>
       <c r="P81" s="7" t="inlineStr">
         <is>
-          <t>1,002,087,000</t>
+          <t>1,430,699,820</t>
         </is>
       </c>
       <c r="Q81" s="6" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="R81" s="6" t="inlineStr">
@@ -14311,32 +14319,32 @@
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="6" t="inlineStr">
         <is>
-          <t>하나에어로다이내믹스</t>
+          <t>제논</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>11-02~11-06</t>
+          <t>10-26~10-30</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>4,700~5,700</t>
+          <t>9,700~12,200</t>
         </is>
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>4,400,000</t>
+          <t>2,200,000</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>20,680,000,000</t>
+          <t>21,340,000,000</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr">
         <is>
-          <t>17.89배 (EV/EBITDA)</t>
+          <t>36.49배 (PER)</t>
         </is>
       </c>
       <c r="G82" s="6" t="inlineStr"/>
@@ -14344,7 +14352,7 @@
       <c r="I82" s="6" t="inlineStr"/>
       <c r="J82" s="6" t="inlineStr">
         <is>
-          <t>11-10~11-11</t>
+          <t>11-04~11-05</t>
         </is>
       </c>
       <c r="K82" s="6" t="inlineStr"/>
@@ -14352,18 +14360,18 @@
       <c r="M82" s="6" t="inlineStr"/>
       <c r="N82" s="6" t="inlineStr">
         <is>
-          <t>아이비케이투자증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="O82" s="6" t="inlineStr"/>
       <c r="P82" s="7" t="inlineStr">
         <is>
-          <t>850,000,000</t>
-        </is>
-      </c>
-      <c r="Q82" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>835,247,600</t>
+        </is>
+      </c>
+      <c r="Q82" s="6" t="inlineStr">
+        <is>
+          <t>3.80%</t>
         </is>
       </c>
       <c r="R82" s="6" t="inlineStr">
@@ -14375,32 +14383,32 @@
     <row r="83" ht="30" customHeight="1">
       <c r="A83" s="6" t="inlineStr">
         <is>
-          <t>엔키화이트햇</t>
+          <t>영광와이케이엠씨</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>11-03~11-09</t>
+          <t>10-27~11-02</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>13,000~16,500</t>
+          <t>9,400~11,000</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>1,700,000</t>
+          <t>2,300,000</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>22,100,000,000</t>
+          <t>21,620,000,000</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>24.86배 (PER)</t>
+          <t>22.91배 (PER)</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr"/>
@@ -14408,7 +14416,7 @@
       <c r="I83" s="6" t="inlineStr"/>
       <c r="J83" s="6" t="inlineStr">
         <is>
-          <t>11-12~11-13</t>
+          <t>11-04~11-05</t>
         </is>
       </c>
       <c r="K83" s="6" t="inlineStr"/>
@@ -14416,18 +14424,18 @@
       <c r="M83" s="6" t="inlineStr"/>
       <c r="N83" s="6" t="inlineStr">
         <is>
-          <t>신영증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="O83" s="6" t="inlineStr"/>
       <c r="P83" s="7" t="inlineStr">
         <is>
-          <t>1,138,150,000</t>
+          <t>1,002,087,000</t>
         </is>
       </c>
       <c r="Q83" s="6" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="R83" s="6" t="inlineStr">
@@ -14439,32 +14447,32 @@
     <row r="84" ht="30" customHeight="1">
       <c r="A84" s="6" t="inlineStr">
         <is>
-          <t>아델</t>
+          <t>엔키화이트햇</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>11-12~11-18</t>
+          <t>11-03~11-09</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>18,000~25,000</t>
+          <t>13,000~16,500</t>
         </is>
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>2,170,000</t>
+          <t>1,700,000</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>39,060,000,000</t>
+          <t>22,100,000,000</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr">
         <is>
-          <t>20.91배 (PER)</t>
+          <t>24.86배 (PER)</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr"/>
@@ -14472,7 +14480,7 @@
       <c r="I84" s="6" t="inlineStr"/>
       <c r="J84" s="6" t="inlineStr">
         <is>
-          <t>11-23~11-24</t>
+          <t>11-12~11-13</t>
         </is>
       </c>
       <c r="K84" s="6" t="inlineStr"/>
@@ -14480,18 +14488,18 @@
       <c r="M84" s="6" t="inlineStr"/>
       <c r="N84" s="6" t="inlineStr">
         <is>
-          <t>삼성증권㈜</t>
+          <t>신영증권</t>
         </is>
       </c>
       <c r="O84" s="6" t="inlineStr"/>
       <c r="P84" s="7" t="inlineStr">
         <is>
-          <t>1,041,559,920</t>
+          <t>1,138,150,000</t>
         </is>
       </c>
       <c r="Q84" s="6" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="R84" s="6" t="inlineStr">
@@ -14503,32 +14511,32 @@
     <row r="85" ht="30" customHeight="1">
       <c r="A85" s="6" t="inlineStr">
         <is>
-          <t>케이엠에프</t>
+          <t>제이앤티지</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>11-16~11-20</t>
+          <t>11-03~11-09</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>15,000~17,800</t>
+          <t>26,400~31,900</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>4,300,000</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>30,000,000,000</t>
+          <t>113,520,000,000</t>
         </is>
       </c>
       <c r="F85" s="6" t="inlineStr">
         <is>
-          <t>18.53배 (PER)</t>
+          <t>21.25배 (EV/EBITDA)</t>
         </is>
       </c>
       <c r="G85" s="6" t="inlineStr"/>
@@ -14536,7 +14544,7 @@
       <c r="I85" s="6" t="inlineStr"/>
       <c r="J85" s="6" t="inlineStr">
         <is>
-          <t>11-24~11-25</t>
+          <t>11-12~11-13</t>
         </is>
       </c>
       <c r="K85" s="6" t="inlineStr"/>
@@ -14544,18 +14552,22 @@
       <c r="M85" s="6" t="inlineStr"/>
       <c r="N85" s="6" t="inlineStr">
         <is>
-          <t>아이비케이투자증권</t>
-        </is>
-      </c>
-      <c r="O85" s="6" t="inlineStr"/>
+          <t>대신증권</t>
+        </is>
+      </c>
+      <c r="O85" s="6" t="inlineStr">
+        <is>
+          <t>NH</t>
+        </is>
+      </c>
       <c r="P85" s="7" t="inlineStr">
         <is>
-          <t>927,000,000</t>
+          <t>2,147,249,940</t>
         </is>
       </c>
       <c r="Q85" s="6" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="R85" s="6" t="inlineStr">
@@ -14567,59 +14579,59 @@
     <row r="86" ht="30" customHeight="1">
       <c r="A86" s="6" t="inlineStr">
         <is>
-          <t>럭스코</t>
-        </is>
-      </c>
-      <c r="B86" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="C86" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="D86" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="E86" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="F86" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>아델</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="inlineStr">
+        <is>
+          <t>11-12~11-18</t>
+        </is>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>18,000~25,000</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>2,170,000</t>
+        </is>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
+        <is>
+          <t>39,060,000,000</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>20.91배 (PER)</t>
         </is>
       </c>
       <c r="G86" s="6" t="inlineStr"/>
       <c r="H86" s="6" t="inlineStr"/>
       <c r="I86" s="6" t="inlineStr"/>
-      <c r="J86" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="J86" s="6" t="inlineStr">
+        <is>
+          <t>11-23~11-24</t>
         </is>
       </c>
       <c r="K86" s="6" t="inlineStr"/>
       <c r="L86" s="6" t="inlineStr"/>
       <c r="M86" s="6" t="inlineStr"/>
-      <c r="N86" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="N86" s="6" t="inlineStr">
+        <is>
+          <t>삼성증권㈜</t>
         </is>
       </c>
       <c r="O86" s="6" t="inlineStr"/>
-      <c r="P86" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="Q86" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P86" s="7" t="inlineStr">
+        <is>
+          <t>1,041,559,920</t>
+        </is>
+      </c>
+      <c r="Q86" s="6" t="inlineStr">
+        <is>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="R86" s="6" t="inlineStr">
@@ -14631,71 +14643,71 @@
     <row r="87" ht="30" customHeight="1">
       <c r="A87" s="6" t="inlineStr">
         <is>
-          <t>(주)태석광학</t>
-        </is>
-      </c>
-      <c r="B87" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="C87" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="D87" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="E87" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="F87" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>케이엠에프</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>11-16~11-20</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>15,000~17,800</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>2,000,000</t>
+        </is>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
+        <is>
+          <t>30,000,000,000</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>18.53배 (PER)</t>
         </is>
       </c>
       <c r="G87" s="6" t="inlineStr"/>
       <c r="H87" s="6" t="inlineStr"/>
       <c r="I87" s="6" t="inlineStr"/>
-      <c r="J87" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="J87" s="6" t="inlineStr">
+        <is>
+          <t>11-24~11-25</t>
         </is>
       </c>
       <c r="K87" s="6" t="inlineStr"/>
       <c r="L87" s="6" t="inlineStr"/>
       <c r="M87" s="6" t="inlineStr"/>
-      <c r="N87" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="N87" s="6" t="inlineStr">
+        <is>
+          <t>아이비케이투자증권</t>
         </is>
       </c>
       <c r="O87" s="6" t="inlineStr"/>
-      <c r="P87" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="Q87" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P87" s="7" t="inlineStr">
+        <is>
+          <t>927,000,000</t>
+        </is>
+      </c>
+      <c r="Q87" s="6" t="inlineStr">
+        <is>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="R87" s="6" t="inlineStr">
         <is>
-          <t>corp_code 미확보(수동확인)</t>
+          <t>최초</t>
         </is>
       </c>
     </row>
     <row r="88" ht="30" customHeight="1">
       <c r="A88" s="6" t="inlineStr">
         <is>
-          <t>디티에스</t>
+          <t>씨앤엠</t>
         </is>
       </c>
       <c r="B88" s="18" t="inlineStr">
@@ -14703,24 +14715,24 @@
           <t>수집예정</t>
         </is>
       </c>
-      <c r="C88" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="D88" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="E88" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="F88" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>10,000~13,000</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>2,950,000</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>29,500,000,000</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>24.96배 (PER)</t>
         </is>
       </c>
       <c r="G88" s="6" t="inlineStr"/>
@@ -14752,14 +14764,14 @@
       </c>
       <c r="R88" s="6" t="inlineStr">
         <is>
-          <t>신고서 대기</t>
+          <t>최초</t>
         </is>
       </c>
     </row>
     <row r="89" ht="30" customHeight="1">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>에이엔에이치스트럭쳐</t>
+          <t>(주)태석광학</t>
         </is>
       </c>
       <c r="B89" s="18" t="inlineStr">
@@ -14816,14 +14828,14 @@
       </c>
       <c r="R89" s="6" t="inlineStr">
         <is>
-          <t>신고서 대기</t>
+          <t>corp_code 미확보(수동확인)</t>
         </is>
       </c>
     </row>
     <row r="90" ht="30" customHeight="1">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>이에스티</t>
+          <t>디티에스</t>
         </is>
       </c>
       <c r="B90" s="18" t="inlineStr">
@@ -14887,7 +14899,7 @@
     <row r="91" ht="30" customHeight="1">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>우리투자제1호스팩</t>
+          <t>에이엔에이치스트럭쳐</t>
         </is>
       </c>
       <c r="B91" s="18" t="inlineStr">
@@ -14951,7 +14963,7 @@
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>마더스제약</t>
+          <t>이에스티</t>
         </is>
       </c>
       <c r="B92" s="18" t="inlineStr">
@@ -15015,7 +15027,7 @@
     <row r="93" ht="30" customHeight="1">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>케이티이</t>
+          <t>우리투자제1호스팩</t>
         </is>
       </c>
       <c r="B93" s="18" t="inlineStr">
@@ -15079,7 +15091,7 @@
     <row r="94" ht="30" customHeight="1">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>씨앤엠</t>
+          <t>마더스제약</t>
         </is>
       </c>
       <c r="B94" s="18" t="inlineStr">
@@ -15143,7 +15155,7 @@
     <row r="95" ht="30" customHeight="1">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>제이앤티지</t>
+          <t>케이티이</t>
         </is>
       </c>
       <c r="B95" s="18" t="inlineStr">
@@ -15588,22 +15600,86 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="20" t="inlineStr">
-        <is>
-          <t>※ 상장 완료 = KIND 신규상장 페이지 기준(스팩합병 포함) · 스팩 공모상장은 밴드·밸류에이션 등 해당없음(공모가 2,000원 고정).</t>
+    <row r="102" ht="30" customHeight="1">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>에스에프씨</t>
+        </is>
+      </c>
+      <c r="B102" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="C102" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="D102" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="E102" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="F102" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="inlineStr"/>
+      <c r="H102" s="6" t="inlineStr"/>
+      <c r="I102" s="6" t="inlineStr"/>
+      <c r="J102" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="K102" s="6" t="inlineStr"/>
+      <c r="L102" s="6" t="inlineStr"/>
+      <c r="M102" s="6" t="inlineStr"/>
+      <c r="N102" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="O102" s="6" t="inlineStr"/>
+      <c r="P102" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="Q102" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="R102" s="6" t="inlineStr">
+        <is>
+          <t>신고서 대기</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="20" t="inlineStr">
         <is>
-          <t>※ 기재정정 신고서 내 정정 전·후 병존 → 자동수집은 "정정 후" 값만 취함.</t>
+          <t>※ 상장 완료 = KIND 신규상장 페이지 기준(스팩합병 포함) · 스팩 공모상장은 밴드·밸류에이션 등 해당없음(공모가 2,000원 고정).</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="20" t="inlineStr">
+        <is>
+          <t>※ 기재정정 신고서 내 정정 전·후 병존 → 자동수집은 "정정 후" 값만 취함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="20" t="inlineStr">
         <is>
           <t>※ 청약경쟁률=일반투자자 청약수량÷최종배정수량 · "MM-DD~"는 종료일 자동수집 예정.</t>
         </is>
@@ -15906,7 +15982,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D15" s="6" t="n">
         <v>1</v>
@@ -15979,11 +16055,11 @@
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>299,100,000,000</t>
+          <t>412,620,000,000</t>
         </is>
       </c>
     </row>
@@ -16155,7 +16231,7 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>KB증권</t>
+          <t>신한투자증권</t>
         </is>
       </c>
       <c r="B32" s="6" t="n">
@@ -16163,14 +16239,14 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>31,200,000,000</t>
+          <t>36,720,000,000</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>신한투자증권</t>
+          <t>KB증권</t>
         </is>
       </c>
       <c r="B33" s="6" t="n">
@@ -16178,7 +16254,7 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>30,240,000,000</t>
+          <t>31,200,000,000</t>
         </is>
       </c>
     </row>

--- a/IPO_analysis.xlsx
+++ b/IPO_analysis.xlsx
@@ -618,7 +618,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>기준일 2026-10-16 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
+          <t>기준일 2026-10-17 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
         </is>
       </c>
     </row>

--- a/IPO_analysis.xlsx
+++ b/IPO_analysis.xlsx
@@ -618,7 +618,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>기준일 2026-10-17 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
+          <t>기준일 2026-10-18 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
         </is>
       </c>
     </row>

--- a/IPO_analysis.xlsx
+++ b/IPO_analysis.xlsx
@@ -618,14 +618,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>기준일 2026-10-18 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
+          <t>기준일 2026-10-19 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>■ 심사 신청(진행중)  (33건)</t>
+          <t>■ 심사 신청(진행중)  (32건)</t>
         </is>
       </c>
       <c r="B4" s="4" t="n"/>
@@ -1587,12 +1587,12 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>신영스팩12호</t>
+          <t>범한메카텍</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1610,17 +1610,29 @@
           <t>FY25</t>
         </is>
       </c>
-      <c r="F22" s="7" t="inlineStr"/>
-      <c r="G22" s="7" t="inlineStr"/>
-      <c r="H22" s="7" t="inlineStr"/>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>339,209</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="inlineStr">
+        <is>
+          <t>-18,141</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>265,955</t>
+        </is>
+      </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>금융 지원 서비스업</t>
+          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
         </is>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>신영</t>
+          <t>유진, NH</t>
         </is>
       </c>
       <c r="K22" s="6" t="inlineStr">
@@ -1632,12 +1644,12 @@
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>범한메카텍</t>
+          <t>유림테크</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -1657,27 +1669,27 @@
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>339,209</t>
+          <t>102,586</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
         <is>
-          <t>-18,141</t>
+          <t>-18,278</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
         <is>
-          <t>265,955</t>
+          <t>-4,832</t>
         </is>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
-          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
+          <t>자동차 신품 부품 제조업</t>
         </is>
       </c>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>유진, NH</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="K23" s="6" t="inlineStr">
@@ -1689,12 +1701,12 @@
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>유림테크</t>
+          <t>에버온</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -1714,27 +1726,27 @@
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>102,586</t>
+          <t>65,225</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
         <is>
-          <t>-18,278</t>
+          <t>-3,606</t>
         </is>
       </c>
       <c r="H24" s="7" t="inlineStr">
         <is>
-          <t>-4,832</t>
+          <t>54,955</t>
         </is>
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>자동차 신품 부품 제조업</t>
+          <t>전기업</t>
         </is>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K24" s="6" t="inlineStr">
@@ -1746,12 +1758,12 @@
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>에버온</t>
+          <t>엠디에스코리아</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
@@ -1771,22 +1783,22 @@
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>65,225</t>
+          <t>97,972</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
         <is>
-          <t>-3,606</t>
+          <t>6,512</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
         <is>
-          <t>54,955</t>
+          <t>53,818</t>
         </is>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
-          <t>전기업</t>
+          <t>기타 식품 제조업</t>
         </is>
       </c>
       <c r="J25" s="6" t="inlineStr">
@@ -1803,12 +1815,12 @@
     <row r="26">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>엠디에스코리아</t>
+          <t>동승</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
@@ -1828,27 +1840,27 @@
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>97,972</t>
+          <t>78,625</t>
         </is>
       </c>
       <c r="G26" s="7" t="inlineStr">
         <is>
-          <t>6,512</t>
+          <t>14,525</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
         <is>
-          <t>53,818</t>
+          <t>5,438</t>
         </is>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>기타 식품 제조업</t>
+          <t>부동산 임대 및 공급업</t>
         </is>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr">
@@ -1865,7 +1877,7 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>동승</t>
+          <t>에프엠더블유</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
@@ -1875,7 +1887,7 @@
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
@@ -1885,27 +1897,27 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>78,625</t>
+          <t>30,282</t>
         </is>
       </c>
       <c r="G27" s="7" t="inlineStr">
         <is>
-          <t>14,525</t>
+          <t>4,762</t>
         </is>
       </c>
       <c r="H27" s="7" t="inlineStr">
         <is>
-          <t>5,438</t>
+          <t>32</t>
         </is>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>부동산 임대 및 공급업</t>
+          <t>기타 식품 제조업</t>
         </is>
       </c>
       <c r="J27" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>유진</t>
         </is>
       </c>
       <c r="K27" s="6" t="inlineStr">
@@ -1917,22 +1929,22 @@
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>에프엠더블유</t>
+          <t>소노인터내셔널</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>코스닥</t>
+          <t>유가</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -1942,27 +1954,27 @@
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>30,282</t>
+          <t>2,093,051</t>
         </is>
       </c>
       <c r="G28" s="7" t="inlineStr">
         <is>
-          <t>4,762</t>
+          <t>-148,064</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>852,372</t>
         </is>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>기타 식품 제조업</t>
+          <t>일반 및 생활 숙박시설 운영업</t>
         </is>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>유진</t>
+          <t>대신, 미래</t>
         </is>
       </c>
       <c r="K28" s="6" t="inlineStr">
@@ -1974,17 +1986,17 @@
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>소노인터내셔널</t>
+          <t>싸이몬</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>유가</t>
+          <t>코스닥</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
@@ -1999,27 +2011,27 @@
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>2,093,051</t>
+          <t>48,695</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
         <is>
-          <t>-148,064</t>
+          <t>15,714</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
         <is>
-          <t>852,372</t>
+          <t>61,761</t>
         </is>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
-          <t>일반 및 생활 숙박시설 운영업</t>
+          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업</t>
         </is>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>대신, 미래</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K29" s="6" t="inlineStr">
@@ -2031,12 +2043,12 @@
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>싸이몬</t>
+          <t>바이다</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
@@ -2056,27 +2068,27 @@
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>48,695</t>
+          <t>14,432</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
         <is>
-          <t>15,714</t>
+          <t>-3,951</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
         <is>
-          <t>61,761</t>
+          <t>15,108</t>
         </is>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>측정, 시험, 항해, 제어 및 기타 정밀기기 제조업</t>
+          <t>전자부품 제조업</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
@@ -2088,12 +2100,12 @@
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>바이다</t>
+          <t>아이알큐더스</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
@@ -2113,27 +2125,27 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>14,432</t>
+          <t>10,231</t>
         </is>
       </c>
       <c r="G31" s="7" t="inlineStr">
         <is>
-          <t>-3,951</t>
+          <t>-986</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
         <is>
-          <t>15,108</t>
+          <t>1,800</t>
         </is>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
-          <t>전자부품 제조업</t>
+          <t>소프트웨어 개발 및 공급업</t>
         </is>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>DB</t>
         </is>
       </c>
       <c r="K31" s="6" t="inlineStr">
@@ -2145,12 +2157,12 @@
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>아이알큐더스</t>
+          <t>씨엔티테크</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
@@ -2170,17 +2182,17 @@
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>10,231</t>
+          <t>27,015</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
         <is>
-          <t>-986</t>
+          <t>3,987</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>1,800</t>
+          <t>2,613</t>
         </is>
       </c>
       <c r="I32" s="6" t="inlineStr">
@@ -2190,7 +2202,7 @@
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>DB</t>
+          <t>한화, 하나</t>
         </is>
       </c>
       <c r="K32" s="6" t="inlineStr">
@@ -2202,12 +2214,12 @@
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>씨엔티테크</t>
+          <t>삼홍아크튜리온</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
@@ -2227,27 +2239,27 @@
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>27,015</t>
+          <t>26,162</t>
         </is>
       </c>
       <c r="G33" s="7" t="inlineStr">
         <is>
-          <t>3,987</t>
+          <t>-10,314</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
         <is>
-          <t>2,613</t>
+          <t>6,369</t>
         </is>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어 개발 및 공급업</t>
+          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
         </is>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>한화, 하나</t>
+          <t>삼성, 미래</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
@@ -2259,12 +2271,12 @@
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>삼홍아크튜리온</t>
+          <t>비앤비코리아</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
@@ -2284,27 +2296,27 @@
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>26,162</t>
+          <t>141,169</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
         <is>
-          <t>-10,314</t>
+          <t>21,406</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
         <is>
-          <t>6,369</t>
+          <t>43,932</t>
         </is>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>구조용 금속제품, 탱크 및 증기발생기 제조업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>삼성, 미래</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="K34" s="6" t="inlineStr">
@@ -2316,12 +2328,12 @@
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>비앤비코리아</t>
+          <t>오토핸즈</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
@@ -2331,7 +2343,7 @@
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>신규상장</t>
+          <t>스팩 소멸합병</t>
         </is>
       </c>
       <c r="E35" s="6" t="inlineStr">
@@ -2341,22 +2353,22 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>141,169</t>
+          <t>238,564</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
         <is>
-          <t>21,406</t>
+          <t>6,047</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
         <is>
-          <t>43,932</t>
+          <t>6,129</t>
         </is>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>기타 화학제품 제조업</t>
+          <t>자동차 판매업</t>
         </is>
       </c>
       <c r="J35" s="6" t="inlineStr">
@@ -2373,12 +2385,12 @@
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>오토핸즈</t>
+          <t>아이벡스메디칼시스템즈</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
@@ -2388,7 +2400,7 @@
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>스팩 소멸합병</t>
+          <t>신규상장</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
@@ -2398,27 +2410,27 @@
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>238,564</t>
+          <t>15,282</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
         <is>
-          <t>6,047</t>
+          <t>-7,227</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
         <is>
-          <t>6,129</t>
+          <t>744</t>
         </is>
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>자동차 판매업</t>
+          <t>의료용 기기 제조업</t>
         </is>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="K36" s="6" t="inlineStr">
@@ -2430,12 +2442,12 @@
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>아이벡스메디칼시스템즈</t>
+          <t>피지티</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
@@ -2455,27 +2467,27 @@
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>15,282</t>
+          <t>40,141</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
         <is>
-          <t>-7,227</t>
+          <t>-69,722</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
         <is>
-          <t>744</t>
+          <t>6,029</t>
         </is>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
-          <t>의료용 기기 제조업</t>
+          <t>기타 화학제품 제조업</t>
         </is>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
@@ -2484,134 +2496,122 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>2026-02-27</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>피지티</t>
-        </is>
-      </c>
-      <c r="C38" s="6" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>■ 심사 승인  (86건)</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n"/>
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="4" t="n"/>
+      <c r="E39" s="4" t="n"/>
+      <c r="F39" s="4" t="n"/>
+      <c r="G39" s="4" t="n"/>
+      <c r="H39" s="4" t="n"/>
+      <c r="I39" s="4" t="n"/>
+      <c r="J39" s="4" t="n"/>
+      <c r="K39" s="4" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>일자</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>회사명</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>시장</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>상장유형</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>기준연도</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>매출액</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>순이익</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>자기자본</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>업종</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>대표주관사</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>현황</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>신영스팩12호</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
         <is>
           <t>코스닥</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="D41" s="6" t="inlineStr">
         <is>
           <t>신규상장</t>
         </is>
       </c>
-      <c r="E38" s="6" t="inlineStr">
+      <c r="E41" s="6" t="inlineStr">
         <is>
           <t>FY25</t>
         </is>
       </c>
-      <c r="F38" s="7" t="inlineStr">
-        <is>
-          <t>40,141</t>
-        </is>
-      </c>
-      <c r="G38" s="7" t="inlineStr">
-        <is>
-          <t>-69,722</t>
-        </is>
-      </c>
-      <c r="H38" s="7" t="inlineStr">
-        <is>
-          <t>6,029</t>
-        </is>
-      </c>
-      <c r="I38" s="6" t="inlineStr">
-        <is>
-          <t>기타 화학제품 제조업</t>
-        </is>
-      </c>
-      <c r="J38" s="6" t="inlineStr">
-        <is>
-          <t>한국</t>
-        </is>
-      </c>
-      <c r="K38" s="6" t="inlineStr">
-        <is>
-          <t>예심 진행중</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>■ 심사 승인  (85건)</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="n"/>
-      <c r="C40" s="4" t="n"/>
-      <c r="D40" s="4" t="n"/>
-      <c r="E40" s="4" t="n"/>
-      <c r="F40" s="4" t="n"/>
-      <c r="G40" s="4" t="n"/>
-      <c r="H40" s="4" t="n"/>
-      <c r="I40" s="4" t="n"/>
-      <c r="J40" s="4" t="n"/>
-      <c r="K40" s="4" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>일자</t>
-        </is>
-      </c>
-      <c r="B41" s="5" t="inlineStr">
-        <is>
-          <t>회사명</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
-        <is>
-          <t>시장</t>
-        </is>
-      </c>
-      <c r="D41" s="5" t="inlineStr">
-        <is>
-          <t>상장유형</t>
-        </is>
-      </c>
-      <c r="E41" s="5" t="inlineStr">
-        <is>
-          <t>기준연도</t>
-        </is>
-      </c>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>매출액</t>
-        </is>
-      </c>
-      <c r="G41" s="5" t="inlineStr">
-        <is>
-          <t>순이익</t>
-        </is>
-      </c>
-      <c r="H41" s="5" t="inlineStr">
-        <is>
-          <t>자기자본</t>
-        </is>
-      </c>
-      <c r="I41" s="5" t="inlineStr">
-        <is>
-          <t>업종</t>
-        </is>
-      </c>
-      <c r="J41" s="5" t="inlineStr">
-        <is>
-          <t>대표주관사</t>
-        </is>
-      </c>
-      <c r="K41" s="5" t="inlineStr">
-        <is>
-          <t>현황</t>
+      <c r="F41" s="7" t="inlineStr"/>
+      <c r="G41" s="7" t="inlineStr"/>
+      <c r="H41" s="7" t="inlineStr"/>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>금융 지원 서비스업</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>신영</t>
+        </is>
+      </c>
+      <c r="K41" s="6" t="inlineStr">
+        <is>
+          <t>상장전</t>
         </is>
       </c>
     </row>
@@ -8521,7 +8521,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R106"/>
+  <dimension ref="A1:R107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -12767,7 +12767,7 @@
     <row r="58" ht="22" customHeight="1">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>■ 공모 진행 (예심 승인법인)  (44건)</t>
+          <t>■ 공모 진행 (예심 승인법인)  (45건)</t>
         </is>
       </c>
       <c r="B58" s="4" t="n"/>
@@ -13167,40 +13167,48 @@
     <row r="64" ht="30" customHeight="1">
       <c r="A64" s="6" t="inlineStr">
         <is>
-          <t>유캐스트</t>
+          <t>크리에이츠</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>10-07~10-14</t>
+          <t>10-12~10-16</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>21,000~26,000</t>
+          <t>15,000~18,000</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>800,000</t>
+          <t>1,400,000</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>16,800,000,000</t>
+          <t>21,000,000,000</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>17.97배 (PER)</t>
-        </is>
-      </c>
-      <c r="G64" s="6" t="inlineStr"/>
-      <c r="H64" s="6" t="inlineStr"/>
-      <c r="I64" s="6" t="inlineStr"/>
+          <t>19.15배 (PER)</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>15,000</t>
+        </is>
+      </c>
+      <c r="H64" s="6" t="n">
+        <v>240.46</v>
+      </c>
+      <c r="I64" s="6" t="n">
+        <v>831</v>
+      </c>
       <c r="J64" s="6" t="inlineStr">
         <is>
-          <t>10-19~10-20</t>
+          <t>10-20~10-21</t>
         </is>
       </c>
       <c r="K64" s="6" t="inlineStr"/>
@@ -13208,60 +13216,68 @@
       <c r="M64" s="6" t="inlineStr"/>
       <c r="N64" s="6" t="inlineStr">
         <is>
-          <t>유진투자증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="O64" s="6" t="inlineStr"/>
       <c r="P64" s="7" t="inlineStr">
         <is>
-          <t>1,181,280,000</t>
+          <t>865,200,000</t>
         </is>
       </c>
       <c r="Q64" s="6" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="R64" s="6" t="inlineStr">
         <is>
-          <t>정정</t>
+          <t>발행조건확정</t>
         </is>
       </c>
     </row>
     <row r="65" ht="30" customHeight="1">
       <c r="A65" s="6" t="inlineStr">
         <is>
-          <t>크리에이츠</t>
+          <t>한화플러스제6호스팩</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>10-12~10-16</t>
-        </is>
-      </c>
-      <c r="C65" s="6" t="inlineStr">
-        <is>
-          <t>15,000~18,000</t>
+          <t>10-14~10-15</t>
+        </is>
+      </c>
+      <c r="C65" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>1,400,000</t>
+          <t>6,000,000</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>21,000,000,000</t>
-        </is>
-      </c>
-      <c r="F65" s="6" t="inlineStr">
-        <is>
-          <t>19.15배 (PER)</t>
-        </is>
-      </c>
-      <c r="G65" s="6" t="inlineStr"/>
-      <c r="H65" s="6" t="inlineStr"/>
-      <c r="I65" s="6" t="inlineStr"/>
+          <t>12,000,000,000</t>
+        </is>
+      </c>
+      <c r="F65" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
+      </c>
+      <c r="H65" s="6" t="n">
+        <v>1256.48</v>
+      </c>
+      <c r="I65" s="6" t="n">
+        <v>1927</v>
+      </c>
       <c r="J65" s="6" t="inlineStr">
         <is>
           <t>10-20~10-21</t>
@@ -13270,57 +13286,57 @@
       <c r="K65" s="6" t="inlineStr"/>
       <c r="L65" s="6" t="inlineStr"/>
       <c r="M65" s="6" t="inlineStr"/>
-      <c r="N65" s="6" t="inlineStr">
-        <is>
-          <t>삼성증권</t>
+      <c r="N65" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="O65" s="6" t="inlineStr"/>
-      <c r="P65" s="7" t="inlineStr">
-        <is>
-          <t>865,200,000</t>
+      <c r="P65" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="Q65" s="6" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="R65" s="6" t="inlineStr">
         <is>
-          <t>정정</t>
+          <t>발행조건확정</t>
         </is>
       </c>
     </row>
     <row r="66" ht="30" customHeight="1">
       <c r="A66" s="6" t="inlineStr">
         <is>
-          <t>인텔리빅스</t>
+          <t>유캐스트</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>10-12~10-16</t>
+          <t>10-07~10-14</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>7,600~9,000</t>
+          <t>21,000~26,000</t>
         </is>
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>2,500,000</t>
+          <t>800,000</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>19,000,000,000</t>
+          <t>16,800,000,000</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>22.02배 (PER)</t>
+          <t>17.97배 (PER)</t>
         </is>
       </c>
       <c r="G66" s="6" t="inlineStr"/>
@@ -13328,7 +13344,7 @@
       <c r="I66" s="6" t="inlineStr"/>
       <c r="J66" s="6" t="inlineStr">
         <is>
-          <t>10-21~10-22</t>
+          <t>10-19~10-20</t>
         </is>
       </c>
       <c r="K66" s="6" t="inlineStr"/>
@@ -13336,18 +13352,18 @@
       <c r="M66" s="6" t="inlineStr"/>
       <c r="N66" s="6" t="inlineStr">
         <is>
-          <t>미래에셋증권</t>
+          <t>유진투자증권</t>
         </is>
       </c>
       <c r="O66" s="6" t="inlineStr"/>
       <c r="P66" s="7" t="inlineStr">
         <is>
-          <t>782,800,000</t>
+          <t>1,181,280,000</t>
         </is>
       </c>
       <c r="Q66" s="6" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="R66" s="6" t="inlineStr">
@@ -13359,32 +13375,32 @@
     <row r="67" ht="30" customHeight="1">
       <c r="A67" s="6" t="inlineStr">
         <is>
-          <t>래블업</t>
+          <t>인텔리빅스</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>10-13~10-19</t>
+          <t>10-12~10-16</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>19,000~22,000</t>
+          <t>7,600~9,000</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>2,180,000</t>
+          <t>2,500,000</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>41,420,000,000</t>
+          <t>19,000,000,000</t>
         </is>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>33.6배 (PER)</t>
+          <t>22.02배 (PER)</t>
         </is>
       </c>
       <c r="G67" s="6" t="inlineStr"/>
@@ -13392,7 +13408,7 @@
       <c r="I67" s="6" t="inlineStr"/>
       <c r="J67" s="6" t="inlineStr">
         <is>
-          <t>10-22~10-23</t>
+          <t>10-21~10-22</t>
         </is>
       </c>
       <c r="K67" s="6" t="inlineStr"/>
@@ -13400,18 +13416,18 @@
       <c r="M67" s="6" t="inlineStr"/>
       <c r="N67" s="6" t="inlineStr">
         <is>
-          <t>NH투자증권</t>
+          <t>미래에셋증권</t>
         </is>
       </c>
       <c r="O67" s="6" t="inlineStr"/>
       <c r="P67" s="7" t="inlineStr">
         <is>
-          <t>1,908,899,000</t>
+          <t>782,800,000</t>
         </is>
       </c>
       <c r="Q67" s="6" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="R67" s="6" t="inlineStr">
@@ -13423,7 +13439,7 @@
     <row r="68" ht="30" customHeight="1">
       <c r="A68" s="6" t="inlineStr">
         <is>
-          <t>영광</t>
+          <t>래블업</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
@@ -13433,22 +13449,22 @@
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>14,000~17,000</t>
+          <t>19,000~22,000</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>2,260,000</t>
+          <t>2,180,000</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>31,640,000,000</t>
+          <t>41,420,000,000</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>11.98배 (EV/EBITDA)</t>
+          <t>33.6배 (PER)</t>
         </is>
       </c>
       <c r="G68" s="6" t="inlineStr"/>
@@ -13464,18 +13480,18 @@
       <c r="M68" s="6" t="inlineStr"/>
       <c r="N68" s="6" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>NH투자증권</t>
         </is>
       </c>
       <c r="O68" s="6" t="inlineStr"/>
       <c r="P68" s="7" t="inlineStr">
         <is>
-          <t>977,676,000</t>
-        </is>
-      </c>
-      <c r="Q68" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>1,908,899,000</t>
+        </is>
+      </c>
+      <c r="Q68" s="6" t="inlineStr">
+        <is>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="R68" s="6" t="inlineStr">
@@ -13487,32 +13503,32 @@
     <row r="69" ht="30" customHeight="1">
       <c r="A69" s="6" t="inlineStr">
         <is>
-          <t>한화플러스제6호스팩</t>
+          <t>영광</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>10-14~10-15</t>
-        </is>
-      </c>
-      <c r="C69" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>10-13~10-19</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>14,000~17,000</t>
         </is>
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>6,000,000</t>
+          <t>2,260,000</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>12,000,000,000</t>
-        </is>
-      </c>
-      <c r="F69" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>31,640,000,000</t>
+        </is>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>11.98배 (EV/EBITDA)</t>
         </is>
       </c>
       <c r="G69" s="6" t="inlineStr"/>
@@ -13520,26 +13536,26 @@
       <c r="I69" s="6" t="inlineStr"/>
       <c r="J69" s="6" t="inlineStr">
         <is>
-          <t>10-20~10-21</t>
+          <t>10-22~10-23</t>
         </is>
       </c>
       <c r="K69" s="6" t="inlineStr"/>
       <c r="L69" s="6" t="inlineStr"/>
       <c r="M69" s="6" t="inlineStr"/>
-      <c r="N69" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="N69" s="6" t="inlineStr">
+        <is>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="O69" s="6" t="inlineStr"/>
-      <c r="P69" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="Q69" s="6" t="inlineStr">
-        <is>
-          <t>3.50%</t>
+      <c r="P69" s="7" t="inlineStr">
+        <is>
+          <t>977,676,000</t>
+        </is>
+      </c>
+      <c r="Q69" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="R69" s="6" t="inlineStr">
@@ -14771,7 +14787,7 @@
     <row r="89" ht="30" customHeight="1">
       <c r="A89" s="6" t="inlineStr">
         <is>
-          <t>(주)태석광학</t>
+          <t>씨아이에스케미칼</t>
         </is>
       </c>
       <c r="B89" s="18" t="inlineStr">
@@ -14779,24 +14795,24 @@
           <t>수집예정</t>
         </is>
       </c>
-      <c r="C89" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="D89" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="E89" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
-        </is>
-      </c>
-      <c r="F89" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>5,400~6,800</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>4,000,000</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>21,600,000,000</t>
+        </is>
+      </c>
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>21.24배 (PER)</t>
         </is>
       </c>
       <c r="G89" s="6" t="inlineStr"/>
@@ -14828,14 +14844,14 @@
       </c>
       <c r="R89" s="6" t="inlineStr">
         <is>
-          <t>corp_code 미확보(수동확인)</t>
+          <t>최초</t>
         </is>
       </c>
     </row>
     <row r="90" ht="30" customHeight="1">
       <c r="A90" s="6" t="inlineStr">
         <is>
-          <t>디티에스</t>
+          <t>(주)태석광학</t>
         </is>
       </c>
       <c r="B90" s="18" t="inlineStr">
@@ -14892,14 +14908,14 @@
       </c>
       <c r="R90" s="6" t="inlineStr">
         <is>
-          <t>신고서 대기</t>
+          <t>corp_code 미확보(수동확인)</t>
         </is>
       </c>
     </row>
     <row r="91" ht="30" customHeight="1">
       <c r="A91" s="6" t="inlineStr">
         <is>
-          <t>에이엔에이치스트럭쳐</t>
+          <t>신영스팩12호</t>
         </is>
       </c>
       <c r="B91" s="18" t="inlineStr">
@@ -14956,14 +14972,14 @@
       </c>
       <c r="R91" s="6" t="inlineStr">
         <is>
-          <t>신고서 대기</t>
+          <t>corp_code 미확보(수동확인)</t>
         </is>
       </c>
     </row>
     <row r="92" ht="30" customHeight="1">
       <c r="A92" s="6" t="inlineStr">
         <is>
-          <t>이에스티</t>
+          <t>디티에스</t>
         </is>
       </c>
       <c r="B92" s="18" t="inlineStr">
@@ -15027,7 +15043,7 @@
     <row r="93" ht="30" customHeight="1">
       <c r="A93" s="6" t="inlineStr">
         <is>
-          <t>우리투자제1호스팩</t>
+          <t>에이엔에이치스트럭쳐</t>
         </is>
       </c>
       <c r="B93" s="18" t="inlineStr">
@@ -15091,7 +15107,7 @@
     <row r="94" ht="30" customHeight="1">
       <c r="A94" s="6" t="inlineStr">
         <is>
-          <t>마더스제약</t>
+          <t>이에스티</t>
         </is>
       </c>
       <c r="B94" s="18" t="inlineStr">
@@ -15155,7 +15171,7 @@
     <row r="95" ht="30" customHeight="1">
       <c r="A95" s="6" t="inlineStr">
         <is>
-          <t>케이티이</t>
+          <t>우리투자제1호스팩</t>
         </is>
       </c>
       <c r="B95" s="18" t="inlineStr">
@@ -15219,7 +15235,7 @@
     <row r="96" ht="30" customHeight="1">
       <c r="A96" s="6" t="inlineStr">
         <is>
-          <t>데스틴파워</t>
+          <t>마더스제약</t>
         </is>
       </c>
       <c r="B96" s="18" t="inlineStr">
@@ -15283,7 +15299,7 @@
     <row r="97" ht="30" customHeight="1">
       <c r="A97" s="6" t="inlineStr">
         <is>
-          <t>엘리스</t>
+          <t>케이티이</t>
         </is>
       </c>
       <c r="B97" s="18" t="inlineStr">
@@ -15347,7 +15363,7 @@
     <row r="98" ht="30" customHeight="1">
       <c r="A98" s="6" t="inlineStr">
         <is>
-          <t>인터엑스</t>
+          <t>데스틴파워</t>
         </is>
       </c>
       <c r="B98" s="18" t="inlineStr">
@@ -15411,7 +15427,7 @@
     <row r="99" ht="30" customHeight="1">
       <c r="A99" s="6" t="inlineStr">
         <is>
-          <t>씨아이에스케미칼</t>
+          <t>엘리스</t>
         </is>
       </c>
       <c r="B99" s="18" t="inlineStr">
@@ -15475,7 +15491,7 @@
     <row r="100" ht="30" customHeight="1">
       <c r="A100" s="6" t="inlineStr">
         <is>
-          <t>이노보테라퓨틱스</t>
+          <t>인터엑스</t>
         </is>
       </c>
       <c r="B100" s="18" t="inlineStr">
@@ -15539,7 +15555,7 @@
     <row r="101" ht="30" customHeight="1">
       <c r="A101" s="6" t="inlineStr">
         <is>
-          <t>이나인페이</t>
+          <t>이노보테라퓨틱스</t>
         </is>
       </c>
       <c r="B101" s="18" t="inlineStr">
@@ -15603,7 +15619,7 @@
     <row r="102" ht="30" customHeight="1">
       <c r="A102" s="6" t="inlineStr">
         <is>
-          <t>에스에프씨</t>
+          <t>이나인페이</t>
         </is>
       </c>
       <c r="B102" s="18" t="inlineStr">
@@ -15664,22 +15680,86 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="20" t="inlineStr">
-        <is>
-          <t>※ 상장 완료 = KIND 신규상장 페이지 기준(스팩합병 포함) · 스팩 공모상장은 밴드·밸류에이션 등 해당없음(공모가 2,000원 고정).</t>
+    <row r="103" ht="30" customHeight="1">
+      <c r="A103" s="6" t="inlineStr">
+        <is>
+          <t>에스에프씨</t>
+        </is>
+      </c>
+      <c r="B103" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="C103" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="D103" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="E103" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="F103" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="G103" s="6" t="inlineStr"/>
+      <c r="H103" s="6" t="inlineStr"/>
+      <c r="I103" s="6" t="inlineStr"/>
+      <c r="J103" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="K103" s="6" t="inlineStr"/>
+      <c r="L103" s="6" t="inlineStr"/>
+      <c r="M103" s="6" t="inlineStr"/>
+      <c r="N103" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="O103" s="6" t="inlineStr"/>
+      <c r="P103" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="Q103" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="R103" s="6" t="inlineStr">
+        <is>
+          <t>신고서 대기</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="20" t="inlineStr">
         <is>
-          <t>※ 기재정정 신고서 내 정정 전·후 병존 → 자동수집은 "정정 후" 값만 취함.</t>
+          <t>※ 상장 완료 = KIND 신규상장 페이지 기준(스팩합병 포함) · 스팩 공모상장은 밴드·밸류에이션 등 해당없음(공모가 2,000원 고정).</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="20" t="inlineStr">
+        <is>
+          <t>※ 기재정정 신고서 내 정정 전·후 병존 → 자동수집은 "정정 후" 값만 취함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="20" t="inlineStr">
         <is>
           <t>※ 청약경쟁률=일반투자자 청약수량÷최종배정수량 · "MM-DD~"는 종료일 자동수집 예정.</t>
         </is>
@@ -15982,7 +16062,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D15" s="6" t="n">
         <v>1</v>

--- a/IPO_analysis.xlsx
+++ b/IPO_analysis.xlsx
@@ -618,7 +618,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>기준일 2026-10-19 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
+          <t>기준일 2026-10-20 · 청구일 직전 사업연도 · 별도/개별 재무제표 · 단위 백만원(별도 표기 시 USD)</t>
         </is>
       </c>
     </row>
@@ -4570,7 +4570,7 @@
       </c>
       <c r="K76" s="6" t="inlineStr">
         <is>
-          <t>상장승인(상장예정)</t>
+          <t>상장완료 (2026-10-20)</t>
         </is>
       </c>
     </row>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="K92" s="6" t="inlineStr">
         <is>
-          <t>상장전</t>
+          <t>상장승인(상장예정)</t>
         </is>
       </c>
     </row>
@@ -8737,7 +8737,7 @@
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>■ 상장 완료 (2026)  (50건)</t>
+          <t>■ 상장 완료 (2026)  (51건)</t>
         </is>
       </c>
       <c r="B6" s="4" t="n"/>
@@ -8761,75 +8761,79 @@
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>멜콘</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>09-16~09-22</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>10,700~12,300</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>2,500,000</t>
-        </is>
-      </c>
-      <c r="E7" s="7" t="inlineStr">
-        <is>
-          <t>30,750,000,000</t>
-        </is>
-      </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>26.18배 (PER)</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
-        <is>
-          <t>12,300</t>
-        </is>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>1136.84</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>2405</v>
+          <t>엘리스</t>
+        </is>
+      </c>
+      <c r="B7" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="G7" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="H7" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="I7" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
       </c>
       <c r="J7" s="18" t="inlineStr">
         <is>
           <t>수집예정</t>
         </is>
       </c>
-      <c r="K7" s="6" t="inlineStr">
-        <is>
-          <t>4,284.98</t>
+      <c r="K7" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="L7" s="6" t="inlineStr"/>
       <c r="M7" s="6" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="N7" s="6" t="inlineStr">
-        <is>
-          <t>대신증권</t>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="N7" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="O7" s="6" t="inlineStr"/>
-      <c r="P7" s="7" t="inlineStr">
-        <is>
-          <t>826,575,000</t>
-        </is>
-      </c>
-      <c r="Q7" s="6" t="inlineStr">
-        <is>
-          <t>3.0%</t>
+      <c r="P7" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="Q7" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="R7" s="6" t="inlineStr">
@@ -8841,7 +8845,7 @@
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>멜콘</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
@@ -8851,47 +8855,43 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>19,500~23,500</t>
+          <t>10,700~12,300</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>852,000</t>
+          <t>2,500,000</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>16,614,000,000</t>
+          <t>30,750,000,000</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>17.61배 (PER)</t>
+          <t>26.18배 (PER)</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>19,500</t>
-        </is>
-      </c>
-      <c r="H8" s="6" t="inlineStr">
-        <is>
-          <t>1097.62</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>2006</t>
-        </is>
+          <t>12,300</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>1136.84</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>2405</v>
       </c>
       <c r="J8" s="18" t="inlineStr">
         <is>
           <t>수집예정</t>
         </is>
       </c>
-      <c r="K8" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="K8" s="6" t="inlineStr">
+        <is>
+          <t>4,284.98</t>
         </is>
       </c>
       <c r="L8" s="6" t="inlineStr"/>
@@ -8902,18 +8902,18 @@
       </c>
       <c r="N8" s="6" t="inlineStr">
         <is>
-          <t>하나증권</t>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="O8" s="6" t="inlineStr"/>
       <c r="P8" s="7" t="inlineStr">
         <is>
-          <t>697,788,000</t>
+          <t>826,575,000</t>
         </is>
       </c>
       <c r="Q8" s="6" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="R8" s="6" t="inlineStr">
@@ -8925,32 +8925,32 @@
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>브릴스</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>08-31~09-04</t>
+          <t>09-16~09-22</t>
         </is>
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>16,500~19,500</t>
+          <t>19,500~23,500</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>1,200,000</t>
+          <t>852,000</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>23,400,000,000</t>
+          <t>16,614,000,000</t>
         </is>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
-          <t>13.44 (PSR)</t>
+          <t>17.61배 (PER)</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
@@ -8958,42 +8958,46 @@
           <t>19,500</t>
         </is>
       </c>
-      <c r="H9" s="6" t="n">
-        <v>1187.74</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>2181</v>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>1097.62</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
       </c>
       <c r="J9" s="18" t="inlineStr">
         <is>
           <t>수집예정</t>
         </is>
       </c>
-      <c r="K9" s="6" t="inlineStr">
-        <is>
-          <t>4,418.97</t>
+      <c r="K9" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="L9" s="6" t="inlineStr"/>
       <c r="M9" s="6" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="N9" s="6" t="inlineStr">
         <is>
-          <t>아이비케이투자증권</t>
+          <t>하나증권</t>
         </is>
       </c>
       <c r="O9" s="6" t="inlineStr"/>
       <c r="P9" s="7" t="inlineStr">
         <is>
-          <t>713,790,000</t>
+          <t>697,788,000</t>
         </is>
       </c>
       <c r="Q9" s="6" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
@@ -9005,44 +9009,44 @@
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>브릴스</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>09-08~09-14</t>
+          <t>08-31~09-04</t>
         </is>
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>12,400~14,600</t>
+          <t>16,500~19,500</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>3,000,000</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>43,800,000,000</t>
+          <t>23,400,000,000</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>32.57배 (PER)</t>
+          <t>13.44 (PSR)</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>14,600</t>
+          <t>19,500</t>
         </is>
       </c>
       <c r="H10" s="6" t="n">
-        <v>868.64</v>
+        <v>1187.74</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>2269</v>
+        <v>2181</v>
       </c>
       <c r="J10" s="18" t="inlineStr">
         <is>
@@ -9051,29 +9055,29 @@
       </c>
       <c r="K10" s="6" t="inlineStr">
         <is>
-          <t>1,878.06</t>
+          <t>4,418.97</t>
         </is>
       </c>
       <c r="L10" s="6" t="inlineStr"/>
       <c r="M10" s="6" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>아이비케이투자증권</t>
         </is>
       </c>
       <c r="O10" s="6" t="inlineStr"/>
       <c r="P10" s="7" t="inlineStr">
         <is>
-          <t>1,413,399,926</t>
+          <t>713,790,000</t>
         </is>
       </c>
       <c r="Q10" s="6" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="R10" s="6" t="inlineStr">
@@ -9085,44 +9089,44 @@
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>빅웨이브로보틱스</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>09-07~09-11</t>
+          <t>09-08~09-14</t>
         </is>
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>15,000~18,000</t>
+          <t>12,400~14,600</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>1,600,000</t>
+          <t>3,000,000</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>28,800,000,000</t>
+          <t>43,800,000,000</t>
         </is>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
-          <t>11.15 (PSR)</t>
+          <t>32.57배 (PER)</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>18,000</t>
+          <t>14,600</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>1109.37</v>
+        <v>868.64</v>
       </c>
       <c r="I11" s="6" t="n">
-        <v>2255</v>
+        <v>2269</v>
       </c>
       <c r="J11" s="18" t="inlineStr">
         <is>
@@ -9131,33 +9135,29 @@
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>2,706.30</t>
+          <t>1,878.06</t>
         </is>
       </c>
       <c r="L11" s="6" t="inlineStr"/>
       <c r="M11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="N11" s="6" t="inlineStr">
         <is>
-          <t>유진투자증권</t>
-        </is>
-      </c>
-      <c r="O11" s="6" t="inlineStr">
-        <is>
-          <t>미래</t>
-        </is>
-      </c>
+          <t>대신증권</t>
+        </is>
+      </c>
+      <c r="O11" s="6" t="inlineStr"/>
       <c r="P11" s="7" t="inlineStr">
         <is>
-          <t>378,216,000</t>
+          <t>1,413,399,926</t>
         </is>
       </c>
       <c r="Q11" s="6" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="R11" s="6" t="inlineStr">
@@ -9169,7 +9169,7 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>글로벌테크놀로지</t>
+          <t>빅웨이브로보틱스</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
@@ -9179,34 +9179,34 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>13,000~15,000</t>
+          <t>15,000~18,000</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>4,000,000</t>
+          <t>1,600,000</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>40,000,000,000</t>
+          <t>28,800,000,000</t>
         </is>
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>19.22배 (PER)</t>
+          <t>11.15 (PSR)</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>18,000</t>
         </is>
       </c>
       <c r="H12" s="6" t="n">
-        <v>123.19</v>
+        <v>1109.37</v>
       </c>
       <c r="I12" s="6" t="n">
-        <v>961</v>
+        <v>2255</v>
       </c>
       <c r="J12" s="18" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
       </c>
       <c r="K12" s="6" t="inlineStr">
         <is>
-          <t>57.15</t>
+          <t>2,706.30</t>
         </is>
       </c>
       <c r="L12" s="6" t="inlineStr"/>
@@ -9226,18 +9226,22 @@
       </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
-        </is>
-      </c>
-      <c r="O12" s="6" t="inlineStr"/>
+          <t>유진투자증권</t>
+        </is>
+      </c>
+      <c r="O12" s="6" t="inlineStr">
+        <is>
+          <t>미래</t>
+        </is>
+      </c>
       <c r="P12" s="7" t="inlineStr">
         <is>
-          <t>2,119,999,960</t>
-        </is>
-      </c>
-      <c r="Q12" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>378,216,000</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="R12" s="6" t="inlineStr">
@@ -9249,44 +9253,44 @@
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
-          <t>와이즈플래닛컴퍼니</t>
+          <t>글로벌테크놀로지</t>
         </is>
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>09-04~09-10</t>
+          <t>09-07~09-11</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>10,000~12,000</t>
+          <t>13,000~15,000</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>1,600,000</t>
+          <t>4,000,000</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>19,200,000,000</t>
+          <t>40,000,000,000</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
         <is>
-          <t>20.04배 (PER)</t>
+          <t>19.22배 (PER)</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>1248.47</v>
+        <v>123.19</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>2323</v>
+        <v>961</v>
       </c>
       <c r="J13" s="18" t="inlineStr">
         <is>
@@ -9295,29 +9299,29 @@
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>3,568.86</t>
+          <t>57.15</t>
         </is>
       </c>
       <c r="L13" s="6" t="inlineStr"/>
       <c r="M13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="N13" s="6" t="inlineStr">
         <is>
-          <t>대신증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="O13" s="6" t="inlineStr"/>
       <c r="P13" s="7" t="inlineStr">
         <is>
-          <t>494,400,000</t>
-        </is>
-      </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>3.0%</t>
+          <t>2,119,999,960</t>
+        </is>
+      </c>
+      <c r="Q13" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
@@ -9329,44 +9333,44 @@
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>한국제17호스팩</t>
+          <t>와이즈플래닛컴퍼니</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>09-07~09-08</t>
-        </is>
-      </c>
-      <c r="C14" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>09-04~09-10</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>10,000~12,000</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>7,000,000</t>
+          <t>1,600,000</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>14,000,000,000</t>
-        </is>
-      </c>
-      <c r="F14" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>19,200,000,000</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>20.04배 (PER)</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="H14" s="6" t="n">
-        <v>1270.51</v>
+        <v>1248.47</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>2040</v>
+        <v>2323</v>
       </c>
       <c r="J14" s="18" t="inlineStr">
         <is>
@@ -9375,29 +9379,29 @@
       </c>
       <c r="K14" s="6" t="inlineStr">
         <is>
-          <t>8,291.55</t>
+          <t>3,568.86</t>
         </is>
       </c>
       <c r="L14" s="6" t="inlineStr"/>
       <c r="M14" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="N14" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="N14" s="6" t="inlineStr">
+        <is>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="O14" s="6" t="inlineStr"/>
-      <c r="P14" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>494,400,000</t>
         </is>
       </c>
       <c r="Q14" s="6" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="R14" s="6" t="inlineStr">
@@ -9409,12 +9413,12 @@
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>KB제34호스팩</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>한국제17호스팩</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>09-07~09-08</t>
         </is>
       </c>
       <c r="C15" s="18" t="inlineStr">
@@ -9437,25 +9441,25 @@
           <t>수집예정</t>
         </is>
       </c>
-      <c r="G15" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>2,000</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>1232.51</v>
+        <v>1270.51</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>2001</v>
+        <v>2040</v>
       </c>
       <c r="J15" s="18" t="inlineStr">
         <is>
           <t>수집예정</t>
         </is>
       </c>
-      <c r="K15" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>8,291.55</t>
         </is>
       </c>
       <c r="L15" s="6" t="inlineStr"/>
@@ -9489,75 +9493,75 @@
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>네오사피엔스</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>09-02~09-08</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>13,800~15,800</t>
+          <t>KB제34호스팩</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>7,000,000</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>20,000,000,000</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>26.76배 (PER)</t>
-        </is>
-      </c>
-      <c r="G16" s="6" t="inlineStr">
-        <is>
-          <t>10,000</t>
+          <t>14,000,000,000</t>
+        </is>
+      </c>
+      <c r="F16" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="G16" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="H16" s="6" t="n">
-        <v>219.56</v>
+        <v>1232.51</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>1045</v>
+        <v>2001</v>
       </c>
       <c r="J16" s="18" t="inlineStr">
         <is>
           <t>수집예정</t>
         </is>
       </c>
-      <c r="K16" s="6" t="inlineStr">
-        <is>
-          <t>4,885.53</t>
+      <c r="K16" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="L16" s="6" t="inlineStr"/>
       <c r="M16" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="N16" s="6" t="inlineStr">
-        <is>
-          <t>대신증권</t>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="N16" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="O16" s="6" t="inlineStr"/>
-      <c r="P16" s="7" t="inlineStr">
-        <is>
-          <t>1,080,264,000</t>
+      <c r="P16" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="Q16" s="6" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="R16" s="6" t="inlineStr">
@@ -9569,44 +9573,44 @@
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>엔에이치스팩34호</t>
+          <t>네오사피엔스</t>
         </is>
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>08-24~08-25</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>09-02~09-08</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>13,800~15,800</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>8,500,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>17,000,000,000</t>
-        </is>
-      </c>
-      <c r="F17" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>20,000,000,000</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>26.76배 (PER)</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>1160.7</v>
+        <v>219.56</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>2050</v>
+        <v>1045</v>
       </c>
       <c r="J17" s="18" t="inlineStr">
         <is>
@@ -9615,29 +9619,29 @@
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>16,216.08</t>
+          <t>4,885.53</t>
         </is>
       </c>
       <c r="L17" s="6" t="inlineStr"/>
       <c r="M17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="N17" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="N17" s="6" t="inlineStr">
+        <is>
+          <t>대신증권</t>
         </is>
       </c>
       <c r="O17" s="6" t="inlineStr"/>
-      <c r="P17" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P17" s="7" t="inlineStr">
+        <is>
+          <t>1,080,264,000</t>
         </is>
       </c>
       <c r="Q17" s="6" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="R17" s="6" t="inlineStr">
@@ -9649,44 +9653,44 @@
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>엔에이치스팩34호</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>08-14~08-21</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="inlineStr">
-        <is>
-          <t>13,000~16,000</t>
+          <t>08-24~08-25</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>8,500,000</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>20,000,000,000</t>
-        </is>
-      </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>29.52배 (PER)</t>
+          <t>17,000,000,000</t>
+        </is>
+      </c>
+      <c r="F18" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>10,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="H18" s="6" t="n">
-        <v>63.41</v>
+        <v>1160.7</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>246</v>
+        <v>2050</v>
       </c>
       <c r="J18" s="18" t="inlineStr">
         <is>
@@ -9695,29 +9699,29 @@
       </c>
       <c r="K18" s="6" t="inlineStr">
         <is>
-          <t>88.20</t>
+          <t>16,216.08</t>
         </is>
       </c>
       <c r="L18" s="6" t="inlineStr"/>
       <c r="M18" s="6" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="N18" s="6" t="inlineStr">
-        <is>
-          <t>한국투자증권</t>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="N18" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="O18" s="6" t="inlineStr"/>
-      <c r="P18" s="7" t="inlineStr">
-        <is>
-          <t>1,071,200,000</t>
-        </is>
-      </c>
-      <c r="Q18" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="P18" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>50%</t>
         </is>
       </c>
       <c r="R18" s="6" t="inlineStr">
@@ -9729,75 +9733,75 @@
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>해치텍</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>08-03~08-07</t>
+          <t>08-14~08-21</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>23,000~28,000</t>
+          <t>13,000~16,000</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>1,000,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>23,000,000,000</t>
+          <t>20,000,000,000</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
         <is>
-          <t>36.99배 (PER)</t>
+          <t>29.52배 (PER)</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>10,000</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>101.91</v>
+        <v>63.41</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>321</v>
+        <v>246</v>
       </c>
       <c r="J19" s="18" t="inlineStr">
         <is>
           <t>수집예정</t>
         </is>
       </c>
-      <c r="K19" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>88.20</t>
         </is>
       </c>
       <c r="L19" s="6" t="inlineStr"/>
       <c r="M19" s="6" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="N19" s="6" t="inlineStr">
         <is>
-          <t>DB증권</t>
+          <t>한국투자증권</t>
         </is>
       </c>
       <c r="O19" s="6" t="inlineStr"/>
       <c r="P19" s="7" t="inlineStr">
         <is>
-          <t>1,302,950,000</t>
-        </is>
-      </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>5.5%</t>
+          <t>1,071,200,000</t>
+        </is>
+      </c>
+      <c r="Q19" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
@@ -9809,7 +9813,7 @@
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>니어스랩</t>
+          <t>해치텍</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -9819,34 +9823,34 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>30,000~41,200</t>
+          <t>23,000~28,000</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>910,000</t>
+          <t>1,000,000</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>37,492,000,000</t>
+          <t>23,000,000,000</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>44.41배 (PER)</t>
+          <t>36.99배 (PER)</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>41,200</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="H20" s="6" t="n">
-        <v>743.49</v>
+        <v>101.91</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>1795</v>
+        <v>321</v>
       </c>
       <c r="J20" s="18" t="inlineStr">
         <is>
@@ -9861,23 +9865,23 @@
       <c r="L20" s="6" t="inlineStr"/>
       <c r="M20" s="6" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="N20" s="6" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>DB증권</t>
         </is>
       </c>
       <c r="O20" s="6" t="inlineStr"/>
       <c r="P20" s="7" t="inlineStr">
         <is>
-          <t>1,265,355,000</t>
+          <t>1,302,950,000</t>
         </is>
       </c>
       <c r="Q20" s="6" t="inlineStr">
         <is>
-          <t>4.50%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
@@ -9889,44 +9893,44 @@
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>기도산업</t>
+          <t>니어스랩</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>07-31~08-06</t>
+          <t>08-03~08-07</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>24,800~28,400</t>
+          <t>30,000~41,200</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>1,700,000</t>
+          <t>910,000</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>48,280,000,000</t>
+          <t>37,492,000,000</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>10.01배 (PER)</t>
+          <t>44.41배 (PER)</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>28,400</t>
+          <t>41,200</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>213.31</v>
+        <v>743.49</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>637</v>
+        <v>1795</v>
       </c>
       <c r="J21" s="18" t="inlineStr">
         <is>
@@ -9941,23 +9945,23 @@
       <c r="L21" s="6" t="inlineStr"/>
       <c r="M21" s="6" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="N21" s="6" t="inlineStr">
         <is>
-          <t>미래에셋증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="O21" s="6" t="inlineStr"/>
       <c r="P21" s="7" t="inlineStr">
         <is>
-          <t>716,720,000</t>
+          <t>1,265,355,000</t>
         </is>
       </c>
       <c r="Q21" s="6" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>4.50%</t>
         </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
@@ -9969,44 +9973,44 @@
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스</t>
+          <t>기도산업</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>07-20~07-24</t>
+          <t>07-31~08-06</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>12,000~14,500</t>
+          <t>24,800~28,400</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>1,700,000</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>60,000,000,000</t>
+          <t>48,280,000,000</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>22.89배 (PER)</t>
+          <t>10.01배 (PER)</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>12,000</t>
+          <t>28,400</t>
         </is>
       </c>
       <c r="H22" s="6" t="n">
-        <v>50.4</v>
+        <v>213.31</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>307</v>
+        <v>637</v>
       </c>
       <c r="J22" s="18" t="inlineStr">
         <is>
@@ -10021,23 +10025,23 @@
       <c r="L22" s="6" t="inlineStr"/>
       <c r="M22" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="N22" s="6" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>미래에셋증권</t>
         </is>
       </c>
       <c r="O22" s="6" t="inlineStr"/>
       <c r="P22" s="7" t="inlineStr">
         <is>
-          <t>4,095,000,000</t>
+          <t>716,720,000</t>
         </is>
       </c>
       <c r="Q22" s="6" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="R22" s="6" t="inlineStr">
@@ -10049,44 +10053,44 @@
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t>케이앤에스아이앤씨</t>
+          <t>인제니아테라퓨틱스</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>07-27~07-31</t>
+          <t>07-20~07-24</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>9,000~11,000</t>
+          <t>12,000~14,500</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>2,400,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>26,400,000,000</t>
+          <t>60,000,000,000</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>42.08배 (PER)</t>
+          <t>22.89배 (PER)</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>11,000</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>938.24</v>
+        <v>50.4</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>2024</v>
+        <v>307</v>
       </c>
       <c r="J23" s="18" t="inlineStr">
         <is>
@@ -10101,23 +10105,23 @@
       <c r="L23" s="6" t="inlineStr"/>
       <c r="M23" s="6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="N23" s="6" t="inlineStr">
         <is>
-          <t>아이비케이투자증권</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="O23" s="6" t="inlineStr"/>
       <c r="P23" s="7" t="inlineStr">
         <is>
-          <t>1,500,000,000</t>
+          <t>4,095,000,000</t>
         </is>
       </c>
       <c r="Q23" s="6" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="R23" s="6" t="inlineStr">
@@ -10129,44 +10133,44 @@
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>딜리셔스</t>
+          <t>케이앤에스아이앤씨</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>07-23~07-29</t>
+          <t>07-27~07-31</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>5,000~7,000</t>
+          <t>9,000~11,000</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>2,200,000</t>
+          <t>2,400,000</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>15,400,000,000</t>
+          <t>26,400,000,000</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>23.93배 (PER)</t>
+          <t>42.08배 (PER)</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>7,000</t>
+          <t>11,000</t>
         </is>
       </c>
       <c r="H24" s="6" t="n">
-        <v>184.06</v>
+        <v>938.24</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>441</v>
+        <v>2024</v>
       </c>
       <c r="J24" s="18" t="inlineStr">
         <is>
@@ -10181,23 +10185,23 @@
       <c r="L24" s="6" t="inlineStr"/>
       <c r="M24" s="6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="N24" s="6" t="inlineStr">
         <is>
-          <t>한국투자증권</t>
+          <t>아이비케이투자증권</t>
         </is>
       </c>
       <c r="O24" s="6" t="inlineStr"/>
       <c r="P24" s="7" t="inlineStr">
         <is>
-          <t>566,500,000</t>
+          <t>1,500,000,000</t>
         </is>
       </c>
       <c r="Q24" s="6" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>3.5%</t>
         </is>
       </c>
       <c r="R24" s="6" t="inlineStr">
@@ -10209,44 +10213,44 @@
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>에이치엘지노믹스</t>
+          <t>딜리셔스</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>07-02~07-08</t>
+          <t>07-23~07-29</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>18,500~21,500</t>
+          <t>5,000~7,000</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>2,565,000</t>
+          <t>2,200,000</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>55,147,500,000</t>
+          <t>15,400,000,000</t>
         </is>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>12.85배 (EV/EBITDA)</t>
+          <t>23.93배 (PER)</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>21,500</t>
+          <t>7,000</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>714.52</v>
+        <v>184.06</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>2148</v>
+        <v>441</v>
       </c>
       <c r="J25" s="18" t="inlineStr">
         <is>
@@ -10261,27 +10265,23 @@
       <c r="L25" s="6" t="inlineStr"/>
       <c r="M25" s="6" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="N25" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
-        </is>
-      </c>
-      <c r="O25" s="6" t="inlineStr">
-        <is>
-          <t>아이비케이투자증권, IBK투자증권, IBK투자증권, IBK투자증권, IBK투자증권, IBK투자증권㈜, 보통주, IBK투자증권㈜</t>
-        </is>
-      </c>
+          <t>한국투자증권</t>
+        </is>
+      </c>
+      <c r="O25" s="6" t="inlineStr"/>
       <c r="P25" s="7" t="inlineStr">
         <is>
-          <t>1,211</t>
+          <t>566,500,000</t>
         </is>
       </c>
       <c r="Q25" s="6" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
@@ -10293,63 +10293,59 @@
     <row r="26" ht="30" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t>레메디</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>에이치엘지노믹스</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>07-02~07-08</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>17,800~20,700</t>
+          <t>18,500~21,500</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>1,200,000</t>
+          <t>2,565,000</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>24,840,000,000</t>
+          <t>55,147,500,000</t>
         </is>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>21.95배 (PER)</t>
+          <t>12.85배 (EV/EBITDA)</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>20,700</t>
-        </is>
-      </c>
-      <c r="H26" s="6" t="inlineStr">
-        <is>
-          <t>1,146.41</t>
-        </is>
-      </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>2,246</t>
-        </is>
+          <t>21,500</t>
+        </is>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>714.52</v>
+      </c>
+      <c r="I26" s="6" t="n">
+        <v>2148</v>
       </c>
       <c r="J26" s="18" t="inlineStr">
         <is>
           <t>수집예정</t>
         </is>
       </c>
-      <c r="K26" s="6" t="inlineStr">
-        <is>
-          <t>1,706.71</t>
+      <c r="K26" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="L26" s="6" t="inlineStr"/>
       <c r="M26" s="6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="N26" s="6" t="inlineStr">
@@ -10357,15 +10353,19 @@
           <t>KB</t>
         </is>
       </c>
-      <c r="O26" s="6" t="inlineStr"/>
+      <c r="O26" s="6" t="inlineStr">
+        <is>
+          <t>아이비케이투자증권, IBK투자증권, IBK투자증권, IBK투자증권, IBK투자증권, IBK투자증권㈜, 보통주, IBK투자증권㈜</t>
+        </is>
+      </c>
       <c r="P26" s="7" t="inlineStr">
         <is>
-          <t>1,279</t>
+          <t>1,211</t>
         </is>
       </c>
       <c r="Q26" s="6" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>2.5%</t>
         </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
@@ -10377,7 +10377,7 @@
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="6" t="inlineStr">
         <is>
-          <t>레몬헬스케어</t>
+          <t>레메디</t>
         </is>
       </c>
       <c r="B27" s="18" t="inlineStr">
@@ -10387,45 +10387,53 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>7,500~10,000</t>
+          <t>17,800~20,700</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>2,000,000</t>
+          <t>1,200,000</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>24,840,000,000</t>
         </is>
       </c>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>25.48배 (PER)</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="n">
-        <v>10000</v>
-      </c>
-      <c r="H27" s="6" t="n">
-        <v>1238</v>
-      </c>
-      <c r="I27" s="6" t="n">
-        <v>2233</v>
-      </c>
-      <c r="J27" s="6" t="inlineStr">
-        <is>
-          <t>2026-06-24~25</t>
-        </is>
-      </c>
-      <c r="K27" s="6" t="n">
-        <v>1510.57</v>
+          <t>21.95배 (PER)</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>20,700</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t>1,146.41</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>2,246</t>
+        </is>
+      </c>
+      <c r="J27" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
+        </is>
+      </c>
+      <c r="K27" s="6" t="inlineStr">
+        <is>
+          <t>1,706.71</t>
+        </is>
       </c>
       <c r="L27" s="6" t="inlineStr"/>
       <c r="M27" s="6" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="N27" s="6" t="inlineStr">
@@ -10436,12 +10444,12 @@
       <c r="O27" s="6" t="inlineStr"/>
       <c r="P27" s="7" t="inlineStr">
         <is>
-          <t>824</t>
+          <t>1,279</t>
         </is>
       </c>
       <c r="Q27" s="6" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
@@ -10453,7 +10461,7 @@
     <row r="28" ht="30" customHeight="1">
       <c r="A28" s="6" t="inlineStr">
         <is>
-          <t>매드업</t>
+          <t>레몬헬스케어</t>
         </is>
       </c>
       <c r="B28" s="18" t="inlineStr">
@@ -10463,7 +10471,7 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>7,000~8,000</t>
+          <t>7,500~10,000</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
@@ -10473,51 +10481,51 @@
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>16,000</t>
+          <t>20,000</t>
         </is>
       </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>24.57배 (PER)</t>
+          <t>25.48배 (PER)</t>
         </is>
       </c>
       <c r="G28" s="6" t="n">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>1396.29</v>
+        <v>1238</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>2392</v>
+        <v>2233</v>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>2026-06-23~24</t>
+          <t>2026-06-24~25</t>
         </is>
       </c>
       <c r="K28" s="6" t="n">
-        <v>3304.76</v>
+        <v>1510.57</v>
       </c>
       <c r="L28" s="6" t="inlineStr"/>
       <c r="M28" s="6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="N28" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="O28" s="6" t="inlineStr"/>
       <c r="P28" s="7" t="inlineStr">
         <is>
-          <t>742</t>
+          <t>824</t>
         </is>
       </c>
       <c r="Q28" s="6" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
@@ -10529,75 +10537,71 @@
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>한국제16호스팩</t>
-        </is>
-      </c>
-      <c r="B29" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
+          <t>매드업</t>
+        </is>
+      </c>
+      <c r="B29" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>7,000~8,000</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>5,500,000</t>
+          <t>2,000,000</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>11,000</t>
-        </is>
-      </c>
-      <c r="F29" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
+          <t>16,000</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>24.57배 (PER)</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="n">
+        <v>8000</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>1364.09</v>
+        <v>1396.29</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>2089</v>
+        <v>2392</v>
       </c>
       <c r="J29" s="6" t="inlineStr">
         <is>
-          <t>2026-06-22~06-23</t>
-        </is>
-      </c>
-      <c r="K29" s="6" t="inlineStr">
-        <is>
-          <t>1,274.77</t>
-        </is>
+          <t>2026-06-23~24</t>
+        </is>
+      </c>
+      <c r="K29" s="6" t="n">
+        <v>3304.76</v>
       </c>
       <c r="L29" s="6" t="inlineStr"/>
       <c r="M29" s="6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="N29" s="6" t="inlineStr">
         <is>
-          <t>한국</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="O29" s="6" t="inlineStr"/>
       <c r="P29" s="7" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>742</t>
         </is>
       </c>
       <c r="Q29" s="6" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
@@ -10609,51 +10613,53 @@
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>스트라드비젼</t>
-        </is>
-      </c>
-      <c r="B30" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>한국제16호스팩</t>
+        </is>
+      </c>
+      <c r="B30" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>12,000~14,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>7,000,000</t>
+          <t>5,500,000</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>84,000</t>
-        </is>
-      </c>
-      <c r="F30" s="6" t="inlineStr">
-        <is>
-          <t>37.45배 (PER)</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="n">
-        <v>12000</v>
+          <t>11,000</t>
+        </is>
+      </c>
+      <c r="F30" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
       </c>
       <c r="H30" s="6" t="n">
-        <v>381.3</v>
+        <v>1364.09</v>
       </c>
       <c r="I30" s="6" t="n">
-        <v>1604</v>
+        <v>2089</v>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>2026-06-18~06-19</t>
+          <t>2026-06-22~06-23</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
         <is>
-          <t>45.81</t>
+          <t>1,274.77</t>
         </is>
       </c>
       <c r="L30" s="6" t="inlineStr"/>
@@ -10664,13 +10670,13 @@
       </c>
       <c r="N30" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
+          <t>한국</t>
         </is>
       </c>
       <c r="O30" s="6" t="inlineStr"/>
       <c r="P30" s="7" t="inlineStr">
         <is>
-          <t>2,575</t>
+          <t>330</t>
         </is>
       </c>
       <c r="Q30" s="6" t="inlineStr">
@@ -10687,7 +10693,7 @@
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="6" t="inlineStr">
         <is>
-          <t>져스텍</t>
+          <t>스트라드비젼</t>
         </is>
       </c>
       <c r="B31" s="18" t="inlineStr">
@@ -10697,32 +10703,32 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>10,500~12,500</t>
+          <t>12,000~14,000</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>1,600,000</t>
+          <t>7,000,000</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>84,000</t>
         </is>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>26.82배 (PER)</t>
+          <t>37.45배 (PER)</t>
         </is>
       </c>
       <c r="G31" s="6" t="n">
-        <v>12500</v>
+        <v>12000</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>1294.99</v>
+        <v>381.3</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>2252</v>
+        <v>1604</v>
       </c>
       <c r="J31" s="6" t="inlineStr">
         <is>
@@ -10731,29 +10737,29 @@
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>2,783.89</t>
+          <t>45.81</t>
         </is>
       </c>
       <c r="L31" s="6" t="inlineStr"/>
       <c r="M31" s="6" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="N31" s="6" t="inlineStr">
         <is>
-          <t>삼성</t>
+          <t>KB</t>
         </is>
       </c>
       <c r="O31" s="6" t="inlineStr"/>
       <c r="P31" s="7" t="inlineStr">
         <is>
-          <t>1,164</t>
+          <t>2,575</t>
         </is>
       </c>
       <c r="Q31" s="6" t="inlineStr">
         <is>
-          <t>5.65%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
@@ -10765,75 +10771,73 @@
     <row r="32" ht="30" customHeight="1">
       <c r="A32" s="6" t="inlineStr">
         <is>
-          <t>메리츠제2호스팩</t>
-        </is>
-      </c>
-      <c r="B32" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
+          <t>져스텍</t>
+        </is>
+      </c>
+      <c r="B32" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>10,500~12,500</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>7,000,000</t>
+          <t>1,600,000</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>14,000</t>
-        </is>
-      </c>
-      <c r="F32" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="G32" s="6" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
+          <t>20,000</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>26.82배 (PER)</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>12500</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>1087.58</v>
+        <v>1294.99</v>
       </c>
       <c r="I32" s="6" t="n">
-        <v>1798</v>
+        <v>2252</v>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>2026-06-09~06-10</t>
+          <t>2026-06-18~06-19</t>
         </is>
       </c>
       <c r="K32" s="6" t="inlineStr">
         <is>
-          <t>1,338.66</t>
+          <t>2,783.89</t>
         </is>
       </c>
       <c r="L32" s="6" t="inlineStr"/>
       <c r="M32" s="6" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="N32" s="6" t="inlineStr">
         <is>
-          <t>메리츠</t>
+          <t>삼성</t>
         </is>
       </c>
       <c r="O32" s="6" t="inlineStr"/>
       <c r="P32" s="7" t="inlineStr">
         <is>
-          <t>245</t>
+          <t>1,164</t>
         </is>
       </c>
       <c r="Q32" s="6" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>5.65%</t>
         </is>
       </c>
       <c r="R32" s="6" t="inlineStr">
@@ -10845,77 +10849,75 @@
     <row r="33" ht="30" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t>피스피스스튜디오</t>
-        </is>
-      </c>
-      <c r="B33" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>메리츠제2호스팩</t>
+        </is>
+      </c>
+      <c r="B33" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>19,000~21,500</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>2,272,637</t>
+          <t>7,000,000</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>48,862</t>
-        </is>
-      </c>
-      <c r="F33" s="6" t="inlineStr">
-        <is>
-          <t>21.48배 (PER)</t>
-        </is>
-      </c>
-      <c r="G33" s="6" t="n">
-        <v>21500</v>
+          <t>14,000</t>
+        </is>
+      </c>
+      <c r="F33" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
       </c>
       <c r="H33" s="6" t="n">
-        <v>847.76</v>
+        <v>1087.58</v>
       </c>
       <c r="I33" s="6" t="n">
-        <v>2329</v>
+        <v>1798</v>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>2026-05-26~05-27</t>
+          <t>2026-06-09~06-10</t>
         </is>
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>1,191.15</t>
+          <t>1,338.66</t>
         </is>
       </c>
       <c r="L33" s="6" t="inlineStr"/>
       <c r="M33" s="6" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="N33" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
-        </is>
-      </c>
-      <c r="O33" s="6" t="inlineStr">
-        <is>
-          <t>NH</t>
-        </is>
-      </c>
+          <t>메리츠</t>
+        </is>
+      </c>
+      <c r="O33" s="6" t="inlineStr"/>
       <c r="P33" s="7" t="inlineStr">
         <is>
-          <t>1,994</t>
+          <t>245</t>
         </is>
       </c>
       <c r="Q33" s="6" t="inlineStr">
         <is>
-          <t>4.00%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
@@ -10927,75 +10929,77 @@
     <row r="34" ht="30" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t>대신밸런스제20호스팩</t>
-        </is>
-      </c>
-      <c r="B34" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
+          <t>피스피스스튜디오</t>
+        </is>
+      </c>
+      <c r="B34" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>19,000~21,500</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>6,500,000</t>
+          <t>2,272,637</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>13,000</t>
-        </is>
-      </c>
-      <c r="F34" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="G34" s="6" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
+          <t>48,862</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>21.48배 (PER)</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="n">
+        <v>21500</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>1327.13</v>
+        <v>847.76</v>
       </c>
       <c r="I34" s="6" t="n">
-        <v>2194</v>
+        <v>2329</v>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>2026-05-22~05-25</t>
+          <t>2026-05-26~05-27</t>
         </is>
       </c>
       <c r="K34" s="6" t="inlineStr">
         <is>
-          <t>1,486.88</t>
+          <t>1,191.15</t>
         </is>
       </c>
       <c r="L34" s="6" t="inlineStr"/>
       <c r="M34" s="6" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="N34" s="6" t="inlineStr">
         <is>
-          <t>대신</t>
-        </is>
-      </c>
-      <c r="O34" s="6" t="inlineStr"/>
+          <t>미래</t>
+        </is>
+      </c>
+      <c r="O34" s="6" t="inlineStr">
+        <is>
+          <t>NH</t>
+        </is>
+      </c>
       <c r="P34" s="7" t="inlineStr">
         <is>
-          <t>390</t>
+          <t>1,994</t>
         </is>
       </c>
       <c r="Q34" s="6" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>4.00%</t>
         </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
@@ -11007,73 +11011,75 @@
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t>마키나락스</t>
-        </is>
-      </c>
-      <c r="B35" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>대신밸런스제20호스팩</t>
+        </is>
+      </c>
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>12,500~15,000</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>2,635,000</t>
+          <t>6,500,000</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>39,525</t>
-        </is>
-      </c>
-      <c r="F35" s="6" t="inlineStr">
-        <is>
-          <t>40.5배 (PER)</t>
-        </is>
-      </c>
-      <c r="G35" s="6" t="n">
-        <v>15000</v>
+          <t>13,000</t>
+        </is>
+      </c>
+      <c r="F35" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
       </c>
       <c r="H35" s="6" t="n">
-        <v>1196.08</v>
+        <v>1327.13</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>2427</v>
+        <v>2194</v>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
-          <t>2026-05-11~05-12</t>
+          <t>2026-05-22~05-25</t>
         </is>
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>2,807.79</t>
+          <t>1,486.88</t>
         </is>
       </c>
       <c r="L35" s="6" t="inlineStr"/>
       <c r="M35" s="6" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="N35" s="6" t="inlineStr">
         <is>
-          <t>미래</t>
+          <t>대신</t>
         </is>
       </c>
       <c r="O35" s="6" t="inlineStr"/>
       <c r="P35" s="7" t="inlineStr">
         <is>
-          <t>2,026</t>
+          <t>390</t>
         </is>
       </c>
       <c r="Q35" s="6" t="inlineStr">
         <is>
-          <t>5.00%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="R35" s="6" t="inlineStr">
@@ -11085,7 +11091,7 @@
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>폴레드</t>
+          <t>마키나락스</t>
         </is>
       </c>
       <c r="B36" s="18" t="inlineStr">
@@ -11095,63 +11101,63 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>4,100~5,000</t>
+          <t>12,500~15,000</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>2,600,000</t>
+          <t>2,635,000</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>13,000</t>
+          <t>39,525</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>19.05배 (PER)</t>
+          <t>40.5배 (PER)</t>
         </is>
       </c>
       <c r="G36" s="6" t="n">
-        <v>5000</v>
+        <v>15000</v>
       </c>
       <c r="H36" s="6" t="n">
-        <v>1486.66</v>
+        <v>1196.08</v>
       </c>
       <c r="I36" s="6" t="n">
-        <v>2372</v>
+        <v>2427</v>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>2026-05-04~05-05</t>
+          <t>2026-05-11~05-12</t>
         </is>
       </c>
       <c r="K36" s="6" t="inlineStr">
         <is>
-          <t>3,169.86</t>
+          <t>2,807.79</t>
         </is>
       </c>
       <c r="L36" s="6" t="inlineStr"/>
       <c r="M36" s="6" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="N36" s="6" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>미래</t>
         </is>
       </c>
       <c r="O36" s="6" t="inlineStr"/>
       <c r="P36" s="7" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>2,026</t>
         </is>
       </c>
       <c r="Q36" s="6" t="inlineStr">
         <is>
-          <t>4.03%</t>
+          <t>5.00%</t>
         </is>
       </c>
       <c r="R36" s="6" t="inlineStr">
@@ -11163,7 +11169,7 @@
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
-          <t>코스모로보틱스</t>
+          <t>폴레드</t>
         </is>
       </c>
       <c r="B37" s="18" t="inlineStr">
@@ -11173,67 +11179,63 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>5,300~6,000</t>
+          <t>4,100~5,000</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>4,170,000</t>
+          <t>2,600,000</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>25,020</t>
+          <t>13,000</t>
         </is>
       </c>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>47.45배 (PER)</t>
+          <t>19.05배 (PER)</t>
         </is>
       </c>
       <c r="G37" s="6" t="n">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="H37" s="6" t="n">
-        <v>1140.11</v>
+        <v>1486.66</v>
       </c>
       <c r="I37" s="6" t="n">
-        <v>2257</v>
+        <v>2372</v>
       </c>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>2026-04-27~04-28</t>
+          <t>2026-05-04~05-05</t>
         </is>
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>2,013.80</t>
+          <t>3,169.86</t>
         </is>
       </c>
       <c r="L37" s="6" t="inlineStr"/>
       <c r="M37" s="6" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="N37" s="6" t="inlineStr">
         <is>
-          <t>유진</t>
-        </is>
-      </c>
-      <c r="O37" s="6" t="inlineStr">
-        <is>
           <t>NH</t>
         </is>
       </c>
+      <c r="O37" s="6" t="inlineStr"/>
       <c r="P37" s="7" t="inlineStr">
         <is>
-          <t>1,289</t>
+          <t>540</t>
         </is>
       </c>
       <c r="Q37" s="6" t="inlineStr">
         <is>
-          <t>3.78%</t>
+          <t>4.03%</t>
         </is>
       </c>
       <c r="R37" s="6" t="inlineStr">
@@ -11245,75 +11247,77 @@
     <row r="38" ht="30" customHeight="1">
       <c r="A38" s="6" t="inlineStr">
         <is>
-          <t>신한스팩18호</t>
-        </is>
-      </c>
-      <c r="B38" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
+          <t>코스모로보틱스</t>
+        </is>
+      </c>
+      <c r="B38" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>5,300~6,000</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>5,000,000</t>
+          <t>4,170,000</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>10,000</t>
-        </is>
-      </c>
-      <c r="F38" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="G38" s="6" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
+          <t>25,020</t>
+        </is>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>47.45배 (PER)</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="n">
+        <v>6000</v>
       </c>
       <c r="H38" s="6" t="n">
-        <v>1388.6</v>
+        <v>1140.11</v>
       </c>
       <c r="I38" s="6" t="n">
-        <v>2044</v>
+        <v>2257</v>
       </c>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>2026-04-20~04-21</t>
+          <t>2026-04-27~04-28</t>
         </is>
       </c>
       <c r="K38" s="6" t="inlineStr">
         <is>
-          <t>1,601.36</t>
+          <t>2,013.80</t>
         </is>
       </c>
       <c r="L38" s="6" t="inlineStr"/>
       <c r="M38" s="6" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="N38" s="6" t="inlineStr">
         <is>
-          <t>신한</t>
-        </is>
-      </c>
-      <c r="O38" s="6" t="inlineStr"/>
+          <t>유진</t>
+        </is>
+      </c>
+      <c r="O38" s="6" t="inlineStr">
+        <is>
+          <t>NH</t>
+        </is>
+      </c>
       <c r="P38" s="7" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>1,289</t>
         </is>
       </c>
       <c r="Q38" s="6" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>3.78%</t>
         </is>
       </c>
       <c r="R38" s="6" t="inlineStr">
@@ -11325,42 +11329,44 @@
     <row r="39" ht="30" customHeight="1">
       <c r="A39" s="6" t="inlineStr">
         <is>
-          <t>채비</t>
-        </is>
-      </c>
-      <c r="B39" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>신한스팩18호</t>
+        </is>
+      </c>
+      <c r="B39" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>12,300~15,300</t>
+          <t>2,000</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>9,000,000</t>
+          <t>5,000,000</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>110,700</t>
-        </is>
-      </c>
-      <c r="F39" s="6" t="inlineStr">
-        <is>
-          <t>24.0배 (EV/EBITDA)</t>
-        </is>
-      </c>
-      <c r="G39" s="6" t="n">
-        <v>12300</v>
+          <t>10,000</t>
+        </is>
+      </c>
+      <c r="F39" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>2,000</t>
+        </is>
       </c>
       <c r="H39" s="6" t="n">
-        <v>55.23</v>
+        <v>1388.6</v>
       </c>
       <c r="I39" s="6" t="n">
-        <v>751</v>
+        <v>2044</v>
       </c>
       <c r="J39" s="6" t="inlineStr">
         <is>
@@ -11369,33 +11375,29 @@
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>302.11</t>
+          <t>1,601.36</t>
         </is>
       </c>
       <c r="L39" s="6" t="inlineStr"/>
       <c r="M39" s="6" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="N39" s="6" t="inlineStr">
         <is>
-          <t>KB</t>
-        </is>
-      </c>
-      <c r="O39" s="6" t="inlineStr">
-        <is>
-          <t>삼성</t>
-        </is>
-      </c>
+          <t>신한</t>
+        </is>
+      </c>
+      <c r="O39" s="6" t="inlineStr"/>
       <c r="P39" s="7" t="inlineStr">
         <is>
-          <t>3,384</t>
+          <t>350</t>
         </is>
       </c>
       <c r="Q39" s="6" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>3.50%</t>
         </is>
       </c>
       <c r="R39" s="6" t="inlineStr">
@@ -11407,75 +11409,77 @@
     <row r="40" ht="30" customHeight="1">
       <c r="A40" s="6" t="inlineStr">
         <is>
-          <t>키움히어로스펙2호</t>
-        </is>
-      </c>
-      <c r="B40" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
+          <t>채비</t>
+        </is>
+      </c>
+      <c r="B40" s="18" t="inlineStr">
+        <is>
+          <t>수집예정</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>2,000</t>
+          <t>12,300~15,300</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>6,000,000</t>
+          <t>9,000,000</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>12,000</t>
-        </is>
-      </c>
-      <c r="F40" s="19" t="inlineStr">
-        <is>
-          <t>해당없음</t>
-        </is>
-      </c>
-      <c r="G40" s="6" t="inlineStr">
-        <is>
-          <t>2,000</t>
-        </is>
+          <t>110,700</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>24.0배 (EV/EBITDA)</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="n">
+        <v>12300</v>
       </c>
       <c r="H40" s="6" t="n">
-        <v>1271.12</v>
+        <v>55.23</v>
       </c>
       <c r="I40" s="6" t="n">
-        <v>2054</v>
+        <v>751</v>
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>2026-04-14~04-15</t>
+          <t>2026-04-20~04-21</t>
         </is>
       </c>
       <c r="K40" s="6" t="inlineStr">
         <is>
-          <t>1,727.59</t>
+          <t>302.11</t>
         </is>
       </c>
       <c r="L40" s="6" t="inlineStr"/>
       <c r="M40" s="6" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="N40" s="6" t="inlineStr">
         <is>
-          <t>키움</t>
-        </is>
-      </c>
-      <c r="O40" s="6" t="inlineStr"/>
+          <t>KB</t>
+        </is>
+      </c>
+      <c r="O40" s="6" t="inlineStr">
+        <is>
+          <t>삼성</t>
+        </is>
+      </c>
       <c r="P40" s="7" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>3,384</t>
         </is>
       </c>
       <c r="Q40" s="6" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
@@ -11487,7 +11491,7 @@
     <row r="41" ht="30" customHeight="1">
       <c r="A41" s="6" t="inlineStr">
         <is>
-          <t>교보스팩20호</t>
+          <t>키움히어로스펙2호</t>
         </is>
       </c>
       <c r="B41" s="19" t="inlineStr">
@@ -11502,12 +11506,12 @@
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>5,400,000</t>
+          <t>6,000,000</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>10,800</t>
+          <t>12,000</t>
         </is>
       </c>
       <c r="F41" s="19" t="inlineStr">
@@ -11521,30 +11525,30 @@
         </is>
       </c>
       <c r="H41" s="6" t="n">
-        <v>1196.99</v>
+        <v>1271.12</v>
       </c>
       <c r="I41" s="6" t="n">
-        <v>1855</v>
+        <v>2054</v>
       </c>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>2026-03-23~03-24</t>
+          <t>2026-04-14~04-15</t>
         </is>
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>747.00</t>
+          <t>1,727.59</t>
         </is>
       </c>
       <c r="L41" s="6" t="inlineStr"/>
       <c r="M41" s="6" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="N41" s="6" t="inlineStr">
         <is>
-          <t>교보</t>
+          <t>키움</t>
         </is>
       </c>
       <c r="O41" s="6" t="inlineStr"/>
@@ -11555,7 +11559,7 @@
       </c>
       <c r="Q41" s="6" t="inlineStr">
         <is>
-          <t>2.78%</t>
+          <t>2.50%</t>
         </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
@@ -11567,42 +11571,44 @@
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="6" t="inlineStr">
         <is>
-          <t>인벤테라</t>
-        </is>
-      </c>
-      <c r="B42" s="18" t="inlineStr">
-        <is>
-          <t>수집예정</t>
+          <t>교보스팩20호</t>
+        </is>
+      </c>
+      <c r="B42" s="19" t="inlineStr">
+        <is>
+          <t>해당없음</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>12,100~16,600</t>
+          <t>2,000<